--- a/data/sxbet/ligas/Primera Nacional/trades.xlsx
+++ b/data/sxbet/ligas/Primera Nacional/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V2"/>
+  <dimension ref="A1:V4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,110 +531,318 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>0xb2f3ea804e1760a01d3a93678f0e2119f1ea2a9db0dc4711a06cc7bcba42b0c2</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>17.47</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>1.405</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Primera Nacional</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Estudiantes de Caseros vs Deportivo Madryn</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Estudiantes de Caseros</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Deportivo Madryn</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>0xd61509e26f8645bb9780672f942c72c4b7dab577c2a01f04e1e09bce9b828765</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>L19683453</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>1786190461</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>1786212000</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>43.135802</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>0xa7eafbb77d425fc2347b4ee3e4f4e1b85f6d0f81420605db76ebfeeaa793a428</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>21.69</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>1.4512</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Primera Nacional</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Almirante Brown vs Ciudad Bolivar</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Almirante Brown</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Ciudad Bolivar</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>0xbbcaa253cd967fbf933ff0d87a6f9744cafec0ed59dad5f1f76332aab01a3fa5</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>L19683447</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>1786190458</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>1786212000</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>48.066482</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
           <t>0x5c5b512ea725fac30531bf5fe91f34f3ccc0eeff23890c18f25c3f329007c589</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>1.3638</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>1X2</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>Tie</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>Almirante Brown vs Ciudad Bolivar</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>Almirante Brown</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>Ciudad Bolivar</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>0xd5906ce08d61f7c5ee45fcebd2c8baeed5558387398ea332817a4b632f439b6d</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>L19683447</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>1786125660</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>1786212000</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>2.749141</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/Primera Nacional/trades.xlsx
+++ b/data/sxbet/ligas/Primera Nacional/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V4"/>
+  <dimension ref="A1:V8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,7 +531,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0xb2f3ea804e1760a01d3a93678f0e2119f1ea2a9db0dc4711a06cc7bcba42b0c2</t>
+          <t>0x1b9fcb29010a212f74af57040114154e78748f06a4d826be4397ddadb45ac31b</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -542,12 +542,12 @@
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>17.47</t>
+          <t>21.69</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.405</t>
+          <t>1.4512</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -563,27 +563,27 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Estudiantes de Caseros vs Deportivo Madryn</t>
+          <t>Almirante Brown vs Ciudad Bolivar</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Estudiantes de Caseros</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Ciudad Bolivar</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0xd61509e26f8645bb9780672f942c72c4b7dab577c2a01f04e1e09bce9b828765</t>
+          <t>0xbbcaa253cd967fbf933ff0d87a6f9744cafec0ed59dad5f1f76332aab01a3fa5</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>L19683453</t>
+          <t>L19683447</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1786190461</t>
+          <t>1786190525</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>43.135802</t>
+          <t>48.066482</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -635,23 +635,23 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0xa7eafbb77d425fc2347b4ee3e4f4e1b85f6d0f81420605db76ebfeeaa793a428</t>
+          <t>0x3177792dd6a7185e37ae06612104cf5a35d137d7f535a889a83a7e9b7c174506</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>21.69</t>
+          <t>18.35495</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.4512</t>
+          <t>1.4963</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -712,7 +712,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1786190458</t>
+          <t>1786190491</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -722,7 +722,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>48.066482</t>
+          <t>36.987305</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -739,110 +739,534 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>0x54ed4ee2a6ebdab49498137f1accea542ead806f21430a0a771cc4872a044e43</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>20.10741</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>1.5437</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Over 1.5</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Primera Nacional</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Almirante Brown vs Ciudad Bolivar</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Almirante Brown</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Ciudad Bolivar</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>0xbbcaa253cd967fbf933ff0d87a6f9744cafec0ed59dad5f1f76332aab01a3fa5</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>L19683447</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>1786190485</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>1786212000</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>36.979145</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>0x544fe5c906328d009917b591611ff3438cef85f8b42d9f67732cbbd5eabbb8dd</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>21.69</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>1.4512</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Primera Nacional</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Almirante Brown vs Ciudad Bolivar</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Almirante Brown</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Ciudad Bolivar</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>0xbbcaa253cd967fbf933ff0d87a6f9744cafec0ed59dad5f1f76332aab01a3fa5</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>L19683447</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>1786190485</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>1786212000</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>48.066482</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>0xb2f3ea804e1760a01d3a93678f0e2119f1ea2a9db0dc4711a06cc7bcba42b0c2</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>17.47</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>1.405</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Primera Nacional</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Estudiantes de Caseros vs Deportivo Madryn</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Estudiantes de Caseros</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Deportivo Madryn</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>0xd61509e26f8645bb9780672f942c72c4b7dab577c2a01f04e1e09bce9b828765</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>L19683453</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>1786190461</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>1786212000</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>43.135802</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>0xa7eafbb77d425fc2347b4ee3e4f4e1b85f6d0f81420605db76ebfeeaa793a428</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>21.69</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>1.4512</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Primera Nacional</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Almirante Brown vs Ciudad Bolivar</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Almirante Brown</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Ciudad Bolivar</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>0xbbcaa253cd967fbf933ff0d87a6f9744cafec0ed59dad5f1f76332aab01a3fa5</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>L19683447</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>1786190458</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>1786212000</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>48.066482</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>0x5c5b512ea725fac30531bf5fe91f34f3ccc0eeff23890c18f25c3f329007c589</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>1.3638</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>1X2</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>Tie</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>Almirante Brown vs Ciudad Bolivar</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>Almirante Brown</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>Ciudad Bolivar</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>0xd5906ce08d61f7c5ee45fcebd2c8baeed5558387398ea332817a4b632f439b6d</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>L19683447</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>1786125660</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>1786212000</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>2.749141</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/Primera Nacional/trades.xlsx
+++ b/data/sxbet/ligas/Primera Nacional/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V8"/>
+  <dimension ref="A1:V11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,31 +531,39 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0x1b9fcb29010a212f74af57040114154e78748f06a4d826be4397ddadb45ac31b</t>
+          <t>0x0bb7a6822220bf40d7b279f99a54f46025f393ba95bb38b6d6dc98192886b3ed</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr"/>
+          <t>0xf4a8B27C9a13e298D65b5Cc072d252816B799C81</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>21.69</t>
+          <t>0.99999</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.4512</t>
+          <t>1.5513</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Agropecuario</t>
+        </is>
+      </c>
       <c r="H2" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -563,27 +571,27 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Almirante Brown vs Ciudad Bolivar</t>
+          <t>Agropecuario vs Atletico Guemes</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Ciudad Bolivar</t>
+          <t>Atletico Guemes</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0xbbcaa253cd967fbf933ff0d87a6f9744cafec0ed59dad5f1f76332aab01a3fa5</t>
+          <t>0xae66c7fab3c9c76fbc29d9e9778ef4845d8a6b8d092cff34320f100020113c49</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>L19683447</t>
+          <t>L19683451</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -608,7 +616,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1786190525</t>
+          <t>1786205982</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -618,7 +626,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>48.066482</t>
+          <t>1.814041</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -635,31 +643,39 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0x3177792dd6a7185e37ae06612104cf5a35d137d7f535a889a83a7e9b7c174506</t>
+          <t>0xe17b2546f4b90c8647ba975c279e39dec1fda5a003adfb8a2b39bb12a3519b10</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
+          <t>0xf4a8B27C9a13e298D65b5Cc072d252816B799C81</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>18.35495</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.4963</t>
+          <t>1.3613</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H3" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -682,7 +698,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0xbbcaa253cd967fbf933ff0d87a6f9744cafec0ed59dad5f1f76332aab01a3fa5</t>
+          <t>0xd5906ce08d61f7c5ee45fcebd2c8baeed5558387398ea332817a4b632f439b6d</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -712,7 +728,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1786190491</t>
+          <t>1786205963</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -722,7 +738,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>36.987305</t>
+          <t>2.768166</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -739,12 +755,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0x54ed4ee2a6ebdab49498137f1accea542ead806f21430a0a771cc4872a044e43</t>
+          <t>0xcfe218822e89cbef5841f3045f551cc65acf353d8e240f943e2b61c54ea79a68</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
+          <t>0xf4a8B27C9a13e298D65b5Cc072d252816B799C81</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -754,22 +770,22 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>20.10741</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.5437</t>
+          <t>1.3337</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Over 1.5</t>
+          <t>Tie</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -779,27 +795,27 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Almirante Brown vs Ciudad Bolivar</t>
+          <t>Estudiantes de Caseros vs Deportivo Madryn</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Estudiantes de Caseros</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Ciudad Bolivar</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0xbbcaa253cd967fbf933ff0d87a6f9744cafec0ed59dad5f1f76332aab01a3fa5</t>
+          <t>0xf238b96ec9e2421db79973de945f1fc0c3f8bb99c31cda32d011ebaabfd2db86</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>L19683447</t>
+          <t>L19683453</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -824,7 +840,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1786190485</t>
+          <t>1786205938</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -834,7 +850,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>36.979145</t>
+          <t>2.996255</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -851,7 +867,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0x544fe5c906328d009917b591611ff3438cef85f8b42d9f67732cbbd5eabbb8dd</t>
+          <t>0x1b9fcb29010a212f74af57040114154e78748f06a4d826be4397ddadb45ac31b</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -928,7 +944,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1786190485</t>
+          <t>1786190525</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -955,23 +971,23 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0xb2f3ea804e1760a01d3a93678f0e2119f1ea2a9db0dc4711a06cc7bcba42b0c2</t>
+          <t>0x3177792dd6a7185e37ae06612104cf5a35d137d7f535a889a83a7e9b7c174506</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>17.47</t>
+          <t>18.35495</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.405</t>
+          <t>1.4963</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -987,27 +1003,27 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Estudiantes de Caseros vs Deportivo Madryn</t>
+          <t>Almirante Brown vs Ciudad Bolivar</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Estudiantes de Caseros</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Ciudad Bolivar</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0xd61509e26f8645bb9780672f942c72c4b7dab577c2a01f04e1e09bce9b828765</t>
+          <t>0xbbcaa253cd967fbf933ff0d87a6f9744cafec0ed59dad5f1f76332aab01a3fa5</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>L19683453</t>
+          <t>L19683447</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1032,7 +1048,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1786190461</t>
+          <t>1786190491</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1042,7 +1058,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>43.135802</t>
+          <t>36.987305</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1059,23 +1075,27 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0xa7eafbb77d425fc2347b4ee3e4f4e1b85f6d0f81420605db76ebfeeaa793a428</t>
+          <t>0x54ed4ee2a6ebdab49498137f1accea542ead806f21430a0a771cc4872a044e43</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr"/>
+          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>21.69</t>
+          <t>20.10741</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.4512</t>
+          <t>1.5437</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1083,7 +1103,11 @@
           <t>Under/Over (1.5)</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Over 1.5</t>
+        </is>
+      </c>
       <c r="H7" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -1136,7 +1160,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1786190458</t>
+          <t>1786190485</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1146,7 +1170,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>48.066482</t>
+          <t>36.979145</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1163,110 +1187,422 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>0x544fe5c906328d009917b591611ff3438cef85f8b42d9f67732cbbd5eabbb8dd</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>21.69</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>1.4512</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Primera Nacional</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Almirante Brown vs Ciudad Bolivar</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Almirante Brown</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Ciudad Bolivar</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>0xbbcaa253cd967fbf933ff0d87a6f9744cafec0ed59dad5f1f76332aab01a3fa5</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>L19683447</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>1786190485</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>1786212000</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>48.066482</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>0xb2f3ea804e1760a01d3a93678f0e2119f1ea2a9db0dc4711a06cc7bcba42b0c2</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>17.47</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>1.405</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Primera Nacional</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Estudiantes de Caseros vs Deportivo Madryn</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Estudiantes de Caseros</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Deportivo Madryn</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>0xd61509e26f8645bb9780672f942c72c4b7dab577c2a01f04e1e09bce9b828765</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>L19683453</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>1786190461</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>1786212000</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>43.135802</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>0xa7eafbb77d425fc2347b4ee3e4f4e1b85f6d0f81420605db76ebfeeaa793a428</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>21.69</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>1.4512</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Primera Nacional</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Almirante Brown vs Ciudad Bolivar</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Almirante Brown</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Ciudad Bolivar</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>0xbbcaa253cd967fbf933ff0d87a6f9744cafec0ed59dad5f1f76332aab01a3fa5</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>L19683447</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>1786190458</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>1786212000</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>48.066482</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>0x5c5b512ea725fac30531bf5fe91f34f3ccc0eeff23890c18f25c3f329007c589</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
         <is>
           <t>1.3638</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>1X2</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>Tie</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>Almirante Brown vs Ciudad Bolivar</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>Almirante Brown</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t>Ciudad Bolivar</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>0xd5906ce08d61f7c5ee45fcebd2c8baeed5558387398ea332817a4b632f439b6d</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>L19683447</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr">
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
         <is>
           <t>1786125660</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>1786212000</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>2.749141</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="U11" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="V11" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/Primera Nacional/trades.xlsx
+++ b/data/sxbet/ligas/Primera Nacional/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V11"/>
+  <dimension ref="A1:V22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,39 +531,31 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0x0bb7a6822220bf40d7b279f99a54f46025f393ba95bb38b6d6dc98192886b3ed</t>
+          <t>0x56975f372357be259365cb7d2929c88d4fae157eea7a71d53d57cb234834f2ca</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0xf4a8B27C9a13e298D65b5Cc072d252816B799C81</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.99999</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.5513</t>
+          <t>1.4812</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Agropecuario</t>
-        </is>
-      </c>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -571,27 +563,27 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Agropecuario vs Atletico Guemes</t>
+          <t>Club Atletico Mitre de Santiago del Estero vs Defensores de Belgrano Buenos Aires</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Club Atletico Mitre de Santiago del Estero</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Atletico Guemes</t>
+          <t>Defensores de Belgrano Buenos Aires</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0xae66c7fab3c9c76fbc29d9e9778ef4845d8a6b8d092cff34320f100020113c49</t>
+          <t>0xa8ade64a3adb0ea38de67a61105ef31beb490d5a7287715b76ae124536d359cc</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>L19683451</t>
+          <t>L19683493</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -616,17 +608,17 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1786205982</t>
+          <t>1786215674</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>1786212000</t>
+          <t>1786302000</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1.814041</t>
+          <t>2.077922</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -643,12 +635,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0xe17b2546f4b90c8647ba975c279e39dec1fda5a003adfb8a2b39bb12a3519b10</t>
+          <t>0xff53df1f3446908699196d44fcdb8b39c1bd15c7ed519f0d730e55a51a6eb38f</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0xf4a8B27C9a13e298D65b5Cc072d252816B799C81</t>
+          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -663,7 +655,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.3613</t>
+          <t>1.3713</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -673,7 +665,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tie</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -698,7 +690,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0xd5906ce08d61f7c5ee45fcebd2c8baeed5558387398ea332817a4b632f439b6d</t>
+          <t>0x63a8bf73c1084ef223fdd1096dccd16232e7a455fad77f7f0891be1588ebeb88</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -728,7 +720,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1786205963</t>
+          <t>1786215673</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -738,7 +730,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2.768166</t>
+          <t>2.693603</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -755,12 +747,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0xcfe218822e89cbef5841f3045f551cc65acf353d8e240f943e2b61c54ea79a68</t>
+          <t>0x249d52552e7acb9f472d2a4c48ab754622ba572903281739a3e10b4d509dccb0</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0xf4a8B27C9a13e298D65b5Cc072d252816B799C81</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -770,22 +762,22 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.3337</t>
+          <t>1.2288</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tie</t>
+          <t>Almirante Brown -1</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -795,27 +787,27 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Estudiantes de Caseros vs Deportivo Madryn</t>
+          <t>Almirante Brown vs Ciudad Bolivar</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Estudiantes de Caseros</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Ciudad Bolivar</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0xf238b96ec9e2421db79973de945f1fc0c3f8bb99c31cda32d011ebaabfd2db86</t>
+          <t>0xa6a338c64f062bfd589e8d5d9cea45a27c9e64065f71f800e5966f81ce53c556</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>L19683453</t>
+          <t>L19683447</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -840,7 +832,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1786205938</t>
+          <t>1786214209</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -850,7 +842,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2.996255</t>
+          <t>6.295082</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -867,31 +859,39 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0x1b9fcb29010a212f74af57040114154e78748f06a4d826be4397ddadb45ac31b</t>
+          <t>0xf65c55196eeb0d21e7e3866ad26f8c3f2fee2aef273ddde5423e31fb40a51469</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>21.69</t>
+          <t>121.81</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.4512</t>
+          <t>1.4363</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Almirante Brown</t>
+        </is>
+      </c>
       <c r="H5" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -914,7 +914,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0xbbcaa253cd967fbf933ff0d87a6f9744cafec0ed59dad5f1f76332aab01a3fa5</t>
+          <t>0x63a8bf73c1084ef223fdd1096dccd16232e7a455fad77f7f0891be1588ebeb88</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -944,7 +944,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1786190525</t>
+          <t>1786213844</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>48.066482</t>
+          <t>279.22063</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -971,31 +971,39 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0x3177792dd6a7185e37ae06612104cf5a35d137d7f535a889a83a7e9b7c174506</t>
+          <t>0x1bb20a2bf22e4fe06b44c06b9c2caa21f3f2a7c9d0cce1a2346f79e76022cd1f</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>18.35495</t>
+          <t>21.05</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.4963</t>
+          <t>1.4363</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr"/>
+          <t>Asian Handicap (-0.5)</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Almirante Brown -0.5</t>
+        </is>
+      </c>
       <c r="H6" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -1018,7 +1026,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0xbbcaa253cd967fbf933ff0d87a6f9744cafec0ed59dad5f1f76332aab01a3fa5</t>
+          <t>0xfa00d2f0c7b5053ee336b303a0e7ad9cec0b8d539367773b7efee5c86cb2b59d</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -1048,7 +1056,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1786190491</t>
+          <t>1786213843</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1058,7 +1066,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>36.987305</t>
+          <t>48.252149</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1075,39 +1083,31 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0x54ed4ee2a6ebdab49498137f1accea542ead806f21430a0a771cc4872a044e43</t>
+          <t>0xc51052f8e449b4d56cc87b697bfc8eb0d3a88ae218dee1da3d725fa94163bc75</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>20.10741</t>
+          <t>77.29513</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.5437</t>
+          <t>1.2588</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Over 1.5</t>
-        </is>
-      </c>
+          <t>Primera Nacional</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -1130,7 +1130,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0xbbcaa253cd967fbf933ff0d87a6f9744cafec0ed59dad5f1f76332aab01a3fa5</t>
+          <t>0xaa5316c6f6544d74142ad6db34a3745918f237ffb1a657e000693947e81b65d6</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1160,7 +1160,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1786190485</t>
+          <t>1786212849</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1170,7 +1170,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>36.979145</t>
+          <t>298.72514</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1187,28 +1187,28 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0x544fe5c906328d009917b591611ff3438cef85f8b42d9f67732cbbd5eabbb8dd</t>
+          <t>0x0aeb4fe40f7d734cf244c144e6c064568b40b222193c9f93c641d1b31af3752e</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>21.69</t>
+          <t>16.89162</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.4512</t>
+          <t>1.2588</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
+          <t>Primera Nacional</t>
         </is>
       </c>
       <c r="G8" t="inlineStr"/>
@@ -1234,7 +1234,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0xbbcaa253cd967fbf933ff0d87a6f9744cafec0ed59dad5f1f76332aab01a3fa5</t>
+          <t>0xaa5316c6f6544d74142ad6db34a3745918f237ffb1a657e000693947e81b65d6</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1786190485</t>
+          <t>1786212805</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>48.066482</t>
+          <t>65.281623</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1291,31 +1291,39 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0xb2f3ea804e1760a01d3a93678f0e2119f1ea2a9db0dc4711a06cc7bcba42b0c2</t>
+          <t>0x383b895a5fe529a887369a0f113c516fdc7f6125d54381acf9695997ef22d039</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>17.47</t>
+          <t>11.26905</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.405</t>
+          <t>1.745</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr"/>
+          <t>Primera Nacional</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Almirante Brown</t>
+        </is>
+      </c>
       <c r="H9" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -1323,27 +1331,27 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Estudiantes de Caseros vs Deportivo Madryn</t>
+          <t>Almirante Brown vs Ciudad Bolivar</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Estudiantes de Caseros</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Ciudad Bolivar</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0xd61509e26f8645bb9780672f942c72c4b7dab577c2a01f04e1e09bce9b828765</t>
+          <t>0xaa5316c6f6544d74142ad6db34a3745918f237ffb1a657e000693947e81b65d6</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>L19683453</t>
+          <t>L19683447</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1368,7 +1376,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1786190461</t>
+          <t>1786211779</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1378,7 +1386,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>43.135802</t>
+          <t>15.126242</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1395,7 +1403,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0xa7eafbb77d425fc2347b4ee3e4f4e1b85f6d0f81420605db76ebfeeaa793a428</t>
+          <t>0xcfb6add6f8610a64ffc187beb9e16bf2bacb27b54a0f0aaefa6bfb437239b893</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1403,23 +1411,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr"/>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>21.69</t>
+          <t>24.89998</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.4512</t>
+          <t>1.745</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr"/>
+          <t>Primera Nacional</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Almirante Brown</t>
+        </is>
+      </c>
       <c r="H10" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -1442,7 +1458,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0xbbcaa253cd967fbf933ff0d87a6f9744cafec0ed59dad5f1f76332aab01a3fa5</t>
+          <t>0xaa5316c6f6544d74142ad6db34a3745918f237ffb1a657e000693947e81b65d6</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1472,7 +1488,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1786190458</t>
+          <t>1786211777</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1482,7 +1498,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>48.066482</t>
+          <t>33.422792</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1499,110 +1515,1294 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>0xd41652604437a4e92e0d78b653d4d49d8dedd2e153d1340dad89b9b93e182a48</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>0xf4a8B27C9a13e298D65b5Cc072d252816B799C81</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>1.4163</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Atl. Rafaela</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Primera Nacional</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Atl. Rafaela vs Chacarita Juniors</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Atl. Rafaela</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Chacarita Juniors</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>0xe738e9ba05492fab73eaaf6da211b84caadc72b08b26f1cd30fa8737e283bb44</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>L19683450</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>1786211028</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>1786215600</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>2.402402</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>0x562fd7c6419c807ed04d3cacac95f861805f96704bd535e265399fb9d2c2b609</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>5.32</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>1.405</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Primera Nacional</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Estudiantes de Caseros vs Deportivo Madryn</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Estudiantes de Caseros</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Deportivo Madryn</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>0xd61509e26f8645bb9780672f942c72c4b7dab577c2a01f04e1e09bce9b828765</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>L19683453</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>1786210845</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>1786212000</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>13.135802</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>0x0bb7a6822220bf40d7b279f99a54f46025f393ba95bb38b6d6dc98192886b3ed</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>0xf4a8B27C9a13e298D65b5Cc072d252816B799C81</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>0.99999</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>1.5513</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Agropecuario</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Primera Nacional</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Agropecuario vs Atletico Guemes</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Agropecuario</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Atletico Guemes</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>0xae66c7fab3c9c76fbc29d9e9778ef4845d8a6b8d092cff34320f100020113c49</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>L19683451</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>1786205982</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>1786212000</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>1.814041</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>0xe17b2546f4b90c8647ba975c279e39dec1fda5a003adfb8a2b39bb12a3519b10</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>0xf4a8B27C9a13e298D65b5Cc072d252816B799C81</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>1.3613</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Primera Nacional</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Almirante Brown vs Ciudad Bolivar</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Almirante Brown</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Ciudad Bolivar</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>0xd5906ce08d61f7c5ee45fcebd2c8baeed5558387398ea332817a4b632f439b6d</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>L19683447</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>1786205963</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>1786212000</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>2.768166</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>0xcfe218822e89cbef5841f3045f551cc65acf353d8e240f943e2b61c54ea79a68</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>0xf4a8B27C9a13e298D65b5Cc072d252816B799C81</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>1.3337</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Primera Nacional</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Estudiantes de Caseros vs Deportivo Madryn</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Estudiantes de Caseros</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Deportivo Madryn</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>0xf238b96ec9e2421db79973de945f1fc0c3f8bb99c31cda32d011ebaabfd2db86</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>L19683453</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>1786205938</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>1786212000</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>2.996255</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>0x1b9fcb29010a212f74af57040114154e78748f06a4d826be4397ddadb45ac31b</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>21.69</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>1.4512</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Primera Nacional</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Almirante Brown vs Ciudad Bolivar</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Almirante Brown</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Ciudad Bolivar</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>0xbbcaa253cd967fbf933ff0d87a6f9744cafec0ed59dad5f1f76332aab01a3fa5</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>L19683447</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>1786190525</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>1786212000</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>48.066482</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>0x3177792dd6a7185e37ae06612104cf5a35d137d7f535a889a83a7e9b7c174506</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>18.35495</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>1.4963</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Primera Nacional</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Almirante Brown vs Ciudad Bolivar</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Almirante Brown</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Ciudad Bolivar</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>0xbbcaa253cd967fbf933ff0d87a6f9744cafec0ed59dad5f1f76332aab01a3fa5</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>L19683447</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>1786190491</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>1786212000</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>36.987305</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>0x54ed4ee2a6ebdab49498137f1accea542ead806f21430a0a771cc4872a044e43</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>20.10741</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>1.5437</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Over 1.5</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Primera Nacional</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Almirante Brown vs Ciudad Bolivar</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Almirante Brown</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Ciudad Bolivar</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>0xbbcaa253cd967fbf933ff0d87a6f9744cafec0ed59dad5f1f76332aab01a3fa5</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>L19683447</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>1786190485</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>1786212000</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>36.979145</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>0x544fe5c906328d009917b591611ff3438cef85f8b42d9f67732cbbd5eabbb8dd</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>21.69</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>1.4512</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Primera Nacional</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Almirante Brown vs Ciudad Bolivar</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Almirante Brown</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Ciudad Bolivar</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>0xbbcaa253cd967fbf933ff0d87a6f9744cafec0ed59dad5f1f76332aab01a3fa5</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>L19683447</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>1786190485</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>1786212000</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>48.066482</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>0xb2f3ea804e1760a01d3a93678f0e2119f1ea2a9db0dc4711a06cc7bcba42b0c2</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>17.47</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>1.405</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Primera Nacional</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Estudiantes de Caseros vs Deportivo Madryn</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Estudiantes de Caseros</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Deportivo Madryn</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>0xd61509e26f8645bb9780672f942c72c4b7dab577c2a01f04e1e09bce9b828765</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>L19683453</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>1786190461</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>1786212000</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>43.135802</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>0xa7eafbb77d425fc2347b4ee3e4f4e1b85f6d0f81420605db76ebfeeaa793a428</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>21.69</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>1.4512</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Primera Nacional</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Almirante Brown vs Ciudad Bolivar</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Almirante Brown</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Ciudad Bolivar</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>0xbbcaa253cd967fbf933ff0d87a6f9744cafec0ed59dad5f1f76332aab01a3fa5</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>L19683447</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>1786190458</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>1786212000</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>48.066482</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
           <t>0x5c5b512ea725fac30531bf5fe91f34f3ccc0eeff23890c18f25c3f329007c589</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
         <is>
           <t>1.3638</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>1X2</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>Tie</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="H22" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t>Almirante Brown vs Ciudad Bolivar</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="J22" t="inlineStr">
         <is>
           <t>Almirante Brown</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="K22" t="inlineStr">
         <is>
           <t>Ciudad Bolivar</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="L22" t="inlineStr">
         <is>
           <t>0xd5906ce08d61f7c5ee45fcebd2c8baeed5558387398ea332817a4b632f439b6d</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="M22" t="inlineStr">
         <is>
           <t>L19683447</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
         <is>
           <t>1786125660</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="S22" t="inlineStr">
         <is>
           <t>1786212000</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="T22" t="inlineStr">
         <is>
           <t>2.749141</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="U22" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="V22" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/Primera Nacional/trades.xlsx
+++ b/data/sxbet/ligas/Primera Nacional/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V22"/>
+  <dimension ref="A1:V24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,31 +531,39 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0x56975f372357be259365cb7d2929c88d4fae157eea7a71d53d57cb234834f2ca</t>
+          <t>0x0a5de930b5a6b8aca1699b666034af3891a3aa920021791d6d13e0297fb7903f</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr"/>
+          <t>0x4a09916b1325Eed50eE8973B13742a205B0B7c7E</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>49.99999</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.4812</t>
+          <t>1.6175</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr"/>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Almirante Brown -1</t>
+        </is>
+      </c>
       <c r="H2" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -563,27 +571,27 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Club Atletico Mitre de Santiago del Estero vs Defensores de Belgrano Buenos Aires</t>
+          <t>Almirante Brown vs Ciudad Bolivar</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Club Atletico Mitre de Santiago del Estero</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano Buenos Aires</t>
+          <t>Ciudad Bolivar</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0xa8ade64a3adb0ea38de67a61105ef31beb490d5a7287715b76ae124536d359cc</t>
+          <t>0xa6a338c64f062bfd589e8d5d9cea45a27c9e64065f71f800e5966f81ce53c556</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>L19683493</t>
+          <t>L19683447</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -608,17 +616,17 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1786215674</t>
+          <t>1786218515</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>1786302000</t>
+          <t>1786212000</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2.077922</t>
+          <t>80.971644</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -635,54 +643,46 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0xff53df1f3446908699196d44fcdb8b39c1bd15c7ed519f0d730e55a51a6eb38f</t>
+          <t>0x17d5a08f8fa305f31f27442393c64f497dd3893417da6e76c321c4c2a187320d</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>49.18897</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.3713</t>
+          <t>1.4737</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Primera Nacional</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Almirante Brown vs Ciudad Bolivar</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
         <is>
           <t>Almirante Brown</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Primera Nacional</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Almirante Brown vs Ciudad Bolivar</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Almirante Brown</t>
-        </is>
-      </c>
       <c r="K3" t="inlineStr">
         <is>
           <t>Ciudad Bolivar</t>
@@ -690,7 +690,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0x63a8bf73c1084ef223fdd1096dccd16232e7a455fad77f7f0891be1588ebeb88</t>
+          <t>0xa6a338c64f062bfd589e8d5d9cea45a27c9e64065f71f800e5966f81ce53c556</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -720,7 +720,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1786215673</t>
+          <t>1786218084</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -730,7 +730,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2.693603</t>
+          <t>103.82896</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -747,39 +747,31 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0x249d52552e7acb9f472d2a4c48ab754622ba572903281739a3e10b4d509dccb0</t>
+          <t>0x56975f372357be259365cb7d2929c88d4fae157eea7a71d53d57cb234834f2ca</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.2288</t>
+          <t>1.4812</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Almirante Brown -1</t>
-        </is>
-      </c>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -787,27 +779,27 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Almirante Brown vs Ciudad Bolivar</t>
+          <t>Club Atletico Mitre de Santiago del Estero vs Defensores de Belgrano Buenos Aires</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Club Atletico Mitre de Santiago del Estero</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Ciudad Bolivar</t>
+          <t>Defensores de Belgrano Buenos Aires</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0xa6a338c64f062bfd589e8d5d9cea45a27c9e64065f71f800e5966f81ce53c556</t>
+          <t>0xa8ade64a3adb0ea38de67a61105ef31beb490d5a7287715b76ae124536d359cc</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>L19683447</t>
+          <t>L19683493</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -832,17 +824,17 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1786214209</t>
+          <t>1786215674</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>1786212000</t>
+          <t>1786302000</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>6.295082</t>
+          <t>2.077922</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -859,12 +851,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0xf65c55196eeb0d21e7e3866ad26f8c3f2fee2aef273ddde5423e31fb40a51469</t>
+          <t>0xff53df1f3446908699196d44fcdb8b39c1bd15c7ed519f0d730e55a51a6eb38f</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -874,12 +866,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>121.81</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.4363</t>
+          <t>1.3713</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -944,7 +936,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1786213844</t>
+          <t>1786215673</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -954,7 +946,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>279.22063</t>
+          <t>2.693603</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -971,12 +963,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0x1bb20a2bf22e4fe06b44c06b9c2caa21f3f2a7c9d0cce1a2346f79e76022cd1f</t>
+          <t>0x249d52552e7acb9f472d2a4c48ab754622ba572903281739a3e10b4d509dccb0</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -986,22 +978,22 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>21.05</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.4363</t>
+          <t>1.2288</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Almirante Brown -0.5</t>
+          <t>Almirante Brown -1</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1026,7 +1018,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0xfa00d2f0c7b5053ee336b303a0e7ad9cec0b8d539367773b7efee5c86cb2b59d</t>
+          <t>0xa6a338c64f062bfd589e8d5d9cea45a27c9e64065f71f800e5966f81ce53c556</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -1056,7 +1048,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1786213843</t>
+          <t>1786214209</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1066,7 +1058,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>48.252149</t>
+          <t>6.295082</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1083,7 +1075,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0xc51052f8e449b4d56cc87b697bfc8eb0d3a88ae218dee1da3d725fa94163bc75</t>
+          <t>0xf65c55196eeb0d21e7e3866ad26f8c3f2fee2aef273ddde5423e31fb40a51469</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1091,28 +1083,36 @@
           <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>77.29513</t>
+          <t>121.81</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.2588</t>
+          <t>1.4363</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Almirante Brown</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
           <t>Primera Nacional</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Primera Nacional</t>
-        </is>
-      </c>
       <c r="I7" t="inlineStr">
         <is>
           <t>Almirante Brown vs Ciudad Bolivar</t>
@@ -1130,7 +1130,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0xaa5316c6f6544d74142ad6db34a3745918f237ffb1a657e000693947e81b65d6</t>
+          <t>0x63a8bf73c1084ef223fdd1096dccd16232e7a455fad77f7f0891be1588ebeb88</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1160,7 +1160,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1786212849</t>
+          <t>1786213844</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1170,7 +1170,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>298.72514</t>
+          <t>279.22063</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1187,7 +1187,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0x0aeb4fe40f7d734cf244c144e6c064568b40b222193c9f93c641d1b31af3752e</t>
+          <t>0x1bb20a2bf22e4fe06b44c06b9c2caa21f3f2a7c9d0cce1a2346f79e76022cd1f</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1195,28 +1195,36 @@
           <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>16.89162</t>
+          <t>21.05</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.2588</t>
+          <t>1.4363</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
+          <t>Asian Handicap (-0.5)</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Almirante Brown -0.5</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
           <t>Primera Nacional</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Primera Nacional</t>
-        </is>
-      </c>
       <c r="I8" t="inlineStr">
         <is>
           <t>Almirante Brown vs Ciudad Bolivar</t>
@@ -1234,7 +1242,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0xaa5316c6f6544d74142ad6db34a3745918f237ffb1a657e000693947e81b65d6</t>
+          <t>0xfa00d2f0c7b5053ee336b303a0e7ad9cec0b8d539367773b7efee5c86cb2b59d</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1264,7 +1272,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1786212805</t>
+          <t>1786213843</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1274,7 +1282,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>65.281623</t>
+          <t>48.252149</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1291,7 +1299,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0x383b895a5fe529a887369a0f113c516fdc7f6125d54381acf9695997ef22d039</t>
+          <t>0xc51052f8e449b4d56cc87b697bfc8eb0d3a88ae218dee1da3d725fa94163bc75</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1299,19 +1307,15 @@
           <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>11.26905</t>
+          <t>77.29513</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.745</t>
+          <t>1.2588</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1319,26 +1323,22 @@
           <t>Primera Nacional</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Primera Nacional</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Almirante Brown vs Ciudad Bolivar</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
         <is>
           <t>Almirante Brown</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Primera Nacional</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>Almirante Brown vs Ciudad Bolivar</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>Almirante Brown</t>
-        </is>
-      </c>
       <c r="K9" t="inlineStr">
         <is>
           <t>Ciudad Bolivar</t>
@@ -1376,7 +1376,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1786211779</t>
+          <t>1786212849</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1386,7 +1386,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>15.126242</t>
+          <t>298.72514</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1403,27 +1403,23 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0xcfb6add6f8610a64ffc187beb9e16bf2bacb27b54a0f0aaefa6bfb437239b893</t>
+          <t>0x0aeb4fe40f7d734cf244c144e6c064568b40b222193c9f93c641d1b31af3752e</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>24.89998</t>
+          <t>16.89162</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.745</t>
+          <t>1.2588</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1431,26 +1427,22 @@
           <t>Primera Nacional</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Primera Nacional</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Almirante Brown vs Ciudad Bolivar</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
         <is>
           <t>Almirante Brown</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Primera Nacional</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>Almirante Brown vs Ciudad Bolivar</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>Almirante Brown</t>
-        </is>
-      </c>
       <c r="K10" t="inlineStr">
         <is>
           <t>Ciudad Bolivar</t>
@@ -1488,7 +1480,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1786211777</t>
+          <t>1786212805</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1498,7 +1490,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>33.422792</t>
+          <t>65.281623</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1515,12 +1507,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0xd41652604437a4e92e0d78b653d4d49d8dedd2e153d1340dad89b9b93e182a48</t>
+          <t>0x383b895a5fe529a887369a0f113c516fdc7f6125d54381acf9695997ef22d039</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0xf4a8B27C9a13e298D65b5Cc072d252816B799C81</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1530,22 +1522,22 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>11.26905</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.4163</t>
+          <t>1.745</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Primera Nacional</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Atl. Rafaela</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1555,27 +1547,27 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Atl. Rafaela vs Chacarita Juniors</t>
+          <t>Almirante Brown vs Ciudad Bolivar</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Atl. Rafaela</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Ciudad Bolivar</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0xe738e9ba05492fab73eaaf6da211b84caadc72b08b26f1cd30fa8737e283bb44</t>
+          <t>0xaa5316c6f6544d74142ad6db34a3745918f237ffb1a657e000693947e81b65d6</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>L19683450</t>
+          <t>L19683447</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1600,17 +1592,17 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1786211028</t>
+          <t>1786211779</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>1786215600</t>
+          <t>1786212000</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2.402402</t>
+          <t>15.126242</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1627,7 +1619,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0x562fd7c6419c807ed04d3cacac95f861805f96704bd535e265399fb9d2c2b609</t>
+          <t>0xcfb6add6f8610a64ffc187beb9e16bf2bacb27b54a0f0aaefa6bfb437239b893</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1635,23 +1627,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr"/>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>5.32</t>
+          <t>24.89998</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.405</t>
+          <t>1.745</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr"/>
+          <t>Primera Nacional</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Almirante Brown</t>
+        </is>
+      </c>
       <c r="H12" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -1659,27 +1659,27 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Estudiantes de Caseros vs Deportivo Madryn</t>
+          <t>Almirante Brown vs Ciudad Bolivar</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Estudiantes de Caseros</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Ciudad Bolivar</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>0xd61509e26f8645bb9780672f942c72c4b7dab577c2a01f04e1e09bce9b828765</t>
+          <t>0xaa5316c6f6544d74142ad6db34a3745918f237ffb1a657e000693947e81b65d6</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>L19683453</t>
+          <t>L19683447</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1704,7 +1704,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1786210845</t>
+          <t>1786211777</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>13.135802</t>
+          <t>33.422792</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1731,7 +1731,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0x0bb7a6822220bf40d7b279f99a54f46025f393ba95bb38b6d6dc98192886b3ed</t>
+          <t>0xd41652604437a4e92e0d78b653d4d49d8dedd2e153d1340dad89b9b93e182a48</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1746,12 +1746,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>0.99999</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.5513</t>
+          <t>1.4163</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1761,7 +1761,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Atl. Rafaela</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1771,27 +1771,27 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Agropecuario vs Atletico Guemes</t>
+          <t>Atl. Rafaela vs Chacarita Juniors</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Atl. Rafaela</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Atletico Guemes</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>0xae66c7fab3c9c76fbc29d9e9778ef4845d8a6b8d092cff34320f100020113c49</t>
+          <t>0xe738e9ba05492fab73eaaf6da211b84caadc72b08b26f1cd30fa8737e283bb44</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>L19683451</t>
+          <t>L19683450</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1786205982</t>
+          <t>1786211028</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>1786212000</t>
+          <t>1786215600</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>1.814041</t>
+          <t>2.402402</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1843,39 +1843,31 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0xe17b2546f4b90c8647ba975c279e39dec1fda5a003adfb8a2b39bb12a3519b10</t>
+          <t>0x562fd7c6419c807ed04d3cacac95f861805f96704bd535e265399fb9d2c2b609</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0xf4a8B27C9a13e298D65b5Cc072d252816B799C81</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5.32</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1.3613</t>
+          <t>1.405</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -1883,27 +1875,27 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Almirante Brown vs Ciudad Bolivar</t>
+          <t>Estudiantes de Caseros vs Deportivo Madryn</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Estudiantes de Caseros</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Ciudad Bolivar</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>0xd5906ce08d61f7c5ee45fcebd2c8baeed5558387398ea332817a4b632f439b6d</t>
+          <t>0xd61509e26f8645bb9780672f942c72c4b7dab577c2a01f04e1e09bce9b828765</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>L19683447</t>
+          <t>L19683453</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1928,7 +1920,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1786205963</t>
+          <t>1786210845</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -1938,7 +1930,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2.768166</t>
+          <t>13.135802</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -1955,7 +1947,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0xcfe218822e89cbef5841f3045f551cc65acf353d8e240f943e2b61c54ea79a68</t>
+          <t>0x0bb7a6822220bf40d7b279f99a54f46025f393ba95bb38b6d6dc98192886b3ed</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1970,12 +1962,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0.99999</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1.3337</t>
+          <t>1.5513</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1985,7 +1977,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tie</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1995,27 +1987,27 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Estudiantes de Caseros vs Deportivo Madryn</t>
+          <t>Agropecuario vs Atletico Guemes</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Estudiantes de Caseros</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Atletico Guemes</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>0xf238b96ec9e2421db79973de945f1fc0c3f8bb99c31cda32d011ebaabfd2db86</t>
+          <t>0xae66c7fab3c9c76fbc29d9e9778ef4845d8a6b8d092cff34320f100020113c49</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>L19683453</t>
+          <t>L19683451</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -2040,7 +2032,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>1786205938</t>
+          <t>1786205982</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -2050,7 +2042,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2.996255</t>
+          <t>1.814041</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2067,31 +2059,39 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0x1b9fcb29010a212f74af57040114154e78748f06a4d826be4397ddadb45ac31b</t>
+          <t>0xe17b2546f4b90c8647ba975c279e39dec1fda5a003adfb8a2b39bb12a3519b10</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr"/>
+          <t>0xf4a8B27C9a13e298D65b5Cc072d252816B799C81</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>21.69</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1.4512</t>
+          <t>1.3613</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H16" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>0xbbcaa253cd967fbf933ff0d87a6f9744cafec0ed59dad5f1f76332aab01a3fa5</t>
+          <t>0xd5906ce08d61f7c5ee45fcebd2c8baeed5558387398ea332817a4b632f439b6d</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -2144,7 +2144,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1786190525</t>
+          <t>1786205963</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2154,7 +2154,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>48.066482</t>
+          <t>2.768166</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2171,31 +2171,39 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0x3177792dd6a7185e37ae06612104cf5a35d137d7f535a889a83a7e9b7c174506</t>
+          <t>0xcfe218822e89cbef5841f3045f551cc65acf353d8e240f943e2b61c54ea79a68</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr"/>
+          <t>0xf4a8B27C9a13e298D65b5Cc072d252816B799C81</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>18.35495</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.4963</t>
+          <t>1.3337</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H17" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -2203,27 +2211,27 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Almirante Brown vs Ciudad Bolivar</t>
+          <t>Estudiantes de Caseros vs Deportivo Madryn</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Estudiantes de Caseros</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Ciudad Bolivar</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>0xbbcaa253cd967fbf933ff0d87a6f9744cafec0ed59dad5f1f76332aab01a3fa5</t>
+          <t>0xf238b96ec9e2421db79973de945f1fc0c3f8bb99c31cda32d011ebaabfd2db86</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>L19683447</t>
+          <t>L19683453</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -2248,7 +2256,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>1786190491</t>
+          <t>1786205938</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -2258,7 +2266,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>36.987305</t>
+          <t>2.996255</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2275,27 +2283,23 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0x54ed4ee2a6ebdab49498137f1accea542ead806f21430a0a771cc4872a044e43</t>
+          <t>0x1b9fcb29010a212f74af57040114154e78748f06a4d826be4397ddadb45ac31b</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>20.10741</t>
+          <t>21.69</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.5437</t>
+          <t>1.4512</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -2303,11 +2307,7 @@
           <t>Under/Over (1.5)</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>Over 1.5</t>
-        </is>
-      </c>
+      <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -2360,7 +2360,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>1786190485</t>
+          <t>1786190525</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2370,7 +2370,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>36.979145</t>
+          <t>48.066482</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2387,23 +2387,23 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0x544fe5c906328d009917b591611ff3438cef85f8b42d9f67732cbbd5eabbb8dd</t>
+          <t>0x3177792dd6a7185e37ae06612104cf5a35d137d7f535a889a83a7e9b7c174506</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>21.69</t>
+          <t>18.35495</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1.4512</t>
+          <t>1.4963</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>1786190485</t>
+          <t>1786190491</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -2474,7 +2474,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>48.066482</t>
+          <t>36.987305</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2491,23 +2491,27 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0xb2f3ea804e1760a01d3a93678f0e2119f1ea2a9db0dc4711a06cc7bcba42b0c2</t>
+          <t>0x54ed4ee2a6ebdab49498137f1accea542ead806f21430a0a771cc4872a044e43</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr"/>
+          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>17.47</t>
+          <t>20.10741</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.405</t>
+          <t>1.5437</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -2515,7 +2519,11 @@
           <t>Under/Over (1.5)</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Over 1.5</t>
+        </is>
+      </c>
       <c r="H20" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -2523,27 +2531,27 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Estudiantes de Caseros vs Deportivo Madryn</t>
+          <t>Almirante Brown vs Ciudad Bolivar</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Estudiantes de Caseros</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Ciudad Bolivar</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0xd61509e26f8645bb9780672f942c72c4b7dab577c2a01f04e1e09bce9b828765</t>
+          <t>0xbbcaa253cd967fbf933ff0d87a6f9744cafec0ed59dad5f1f76332aab01a3fa5</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>L19683453</t>
+          <t>L19683447</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -2568,7 +2576,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>1786190461</t>
+          <t>1786190485</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -2578,7 +2586,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>43.135802</t>
+          <t>36.979145</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2595,7 +2603,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0xa7eafbb77d425fc2347b4ee3e4f4e1b85f6d0f81420605db76ebfeeaa793a428</t>
+          <t>0x544fe5c906328d009917b591611ff3438cef85f8b42d9f67732cbbd5eabbb8dd</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2672,7 +2680,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>1786190458</t>
+          <t>1786190485</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -2699,110 +2707,318 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>0xb2f3ea804e1760a01d3a93678f0e2119f1ea2a9db0dc4711a06cc7bcba42b0c2</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>17.47</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>1.405</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Primera Nacional</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Estudiantes de Caseros vs Deportivo Madryn</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Estudiantes de Caseros</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Deportivo Madryn</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>0xd61509e26f8645bb9780672f942c72c4b7dab577c2a01f04e1e09bce9b828765</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>L19683453</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>1786190461</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>1786212000</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>43.135802</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>0xa7eafbb77d425fc2347b4ee3e4f4e1b85f6d0f81420605db76ebfeeaa793a428</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>21.69</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>1.4512</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Primera Nacional</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Almirante Brown vs Ciudad Bolivar</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Almirante Brown</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Ciudad Bolivar</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>0xbbcaa253cd967fbf933ff0d87a6f9744cafec0ed59dad5f1f76332aab01a3fa5</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>L19683447</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>1786190458</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>1786212000</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>48.066482</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
           <t>0x5c5b512ea725fac30531bf5fe91f34f3ccc0eeff23890c18f25c3f329007c589</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
         <is>
           <t>1.3638</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t>1X2</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t>Tie</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="H24" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
+      <c r="I24" t="inlineStr">
         <is>
           <t>Almirante Brown vs Ciudad Bolivar</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
+      <c r="J24" t="inlineStr">
         <is>
           <t>Almirante Brown</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr">
+      <c r="K24" t="inlineStr">
         <is>
           <t>Ciudad Bolivar</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr">
+      <c r="L24" t="inlineStr">
         <is>
           <t>0xd5906ce08d61f7c5ee45fcebd2c8baeed5558387398ea332817a4b632f439b6d</t>
         </is>
       </c>
-      <c r="M22" t="inlineStr">
+      <c r="M24" t="inlineStr">
         <is>
           <t>L19683447</t>
         </is>
       </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P22" t="inlineStr">
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R22" t="inlineStr">
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
         <is>
           <t>1786125660</t>
         </is>
       </c>
-      <c r="S22" t="inlineStr">
+      <c r="S24" t="inlineStr">
         <is>
           <t>1786212000</t>
         </is>
       </c>
-      <c r="T22" t="inlineStr">
+      <c r="T24" t="inlineStr">
         <is>
           <t>2.749141</t>
         </is>
       </c>
-      <c r="U22" t="inlineStr">
+      <c r="U24" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V22" t="inlineStr">
+      <c r="V24" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/Primera Nacional/trades.xlsx
+++ b/data/sxbet/ligas/Primera Nacional/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V24"/>
+  <dimension ref="A1:V25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,12 +531,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0x0a5de930b5a6b8aca1699b666034af3891a3aa920021791d6d13e0297fb7903f</t>
+          <t>0x86f4b24298f4c19f9f856cb19af2a260f24dc2d391f252248469436057ea1d1a</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0x4a09916b1325Eed50eE8973B13742a205B0B7c7E</t>
+          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -546,12 +546,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>49.99999</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.6175</t>
+          <t>1.5263</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -561,7 +561,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Almirante Brown -1</t>
+          <t>Deportivo Moron -1</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -571,27 +571,27 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Almirante Brown vs Ciudad Bolivar</t>
+          <t>Deportivo Moron vs Acassuso</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Deportivo Moron</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Ciudad Bolivar</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0xa6a338c64f062bfd589e8d5d9cea45a27c9e64065f71f800e5966f81ce53c556</t>
+          <t>0xb61b063252c01d0525ae633a0276dc1830eabd418482fddec925fcbd602a2a75</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>L19683447</t>
+          <t>L19683452</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -616,17 +616,17 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1786218515</t>
+          <t>1786220171</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>1786212000</t>
+          <t>1786298400</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>80.971644</t>
+          <t>1.900238</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -643,23 +643,27 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0x17d5a08f8fa305f31f27442393c64f497dd3893417da6e76c321c4c2a187320d</t>
+          <t>0x0a5de930b5a6b8aca1699b666034af3891a3aa920021791d6d13e0297fb7903f</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
+          <t>0x4a09916b1325Eed50eE8973B13742a205B0B7c7E</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>49.18897</t>
+          <t>49.99999</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.4737</t>
+          <t>1.6175</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -667,7 +671,11 @@
           <t>Asian Handicap (-1)</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Almirante Brown -1</t>
+        </is>
+      </c>
       <c r="H3" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -720,7 +728,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1786218084</t>
+          <t>1786218515</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -730,7 +738,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>103.82896</t>
+          <t>80.971644</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -747,28 +755,28 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0x56975f372357be259365cb7d2929c88d4fae157eea7a71d53d57cb234834f2ca</t>
+          <t>0x17d5a08f8fa305f31f27442393c64f497dd3893417da6e76c321c4c2a187320d</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>49.18897</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.4812</t>
+          <t>1.4737</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G4" t="inlineStr"/>
@@ -779,27 +787,27 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Club Atletico Mitre de Santiago del Estero vs Defensores de Belgrano Buenos Aires</t>
+          <t>Almirante Brown vs Ciudad Bolivar</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Club Atletico Mitre de Santiago del Estero</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano Buenos Aires</t>
+          <t>Ciudad Bolivar</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0xa8ade64a3adb0ea38de67a61105ef31beb490d5a7287715b76ae124536d359cc</t>
+          <t>0xa6a338c64f062bfd589e8d5d9cea45a27c9e64065f71f800e5966f81ce53c556</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>L19683493</t>
+          <t>L19683447</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -824,17 +832,17 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1786215674</t>
+          <t>1786218084</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>1786302000</t>
+          <t>1786212000</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2.077922</t>
+          <t>103.82896</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -851,7 +859,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0xff53df1f3446908699196d44fcdb8b39c1bd15c7ed519f0d730e55a51a6eb38f</t>
+          <t>0x56975f372357be259365cb7d2929c88d4fae157eea7a71d53d57cb234834f2ca</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -859,11 +867,7 @@
           <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
           <t>1</t>
@@ -871,19 +875,15 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.3713</t>
+          <t>1.4812</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Almirante Brown</t>
-        </is>
-      </c>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -891,27 +891,27 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Almirante Brown vs Ciudad Bolivar</t>
+          <t>Club Atletico Mitre de Santiago del Estero vs Defensores de Belgrano Buenos Aires</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Club Atletico Mitre de Santiago del Estero</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Ciudad Bolivar</t>
+          <t>Defensores de Belgrano Buenos Aires</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0x63a8bf73c1084ef223fdd1096dccd16232e7a455fad77f7f0891be1588ebeb88</t>
+          <t>0xa8ade64a3adb0ea38de67a61105ef31beb490d5a7287715b76ae124536d359cc</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>L19683447</t>
+          <t>L19683493</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -936,17 +936,17 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1786215673</t>
+          <t>1786215674</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>1786212000</t>
+          <t>1786302000</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2.693603</t>
+          <t>2.077922</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -963,12 +963,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0x249d52552e7acb9f472d2a4c48ab754622ba572903281739a3e10b4d509dccb0</t>
+          <t>0xff53df1f3446908699196d44fcdb8b39c1bd15c7ed519f0d730e55a51a6eb38f</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -978,22 +978,22 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.2288</t>
+          <t>1.3713</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Almirante Brown -1</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1018,7 +1018,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0xa6a338c64f062bfd589e8d5d9cea45a27c9e64065f71f800e5966f81ce53c556</t>
+          <t>0x63a8bf73c1084ef223fdd1096dccd16232e7a455fad77f7f0891be1588ebeb88</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -1048,7 +1048,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1786214209</t>
+          <t>1786215673</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1058,7 +1058,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>6.295082</t>
+          <t>2.693603</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1075,12 +1075,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0xf65c55196eeb0d21e7e3866ad26f8c3f2fee2aef273ddde5423e31fb40a51469</t>
+          <t>0x249d52552e7acb9f472d2a4c48ab754622ba572903281739a3e10b4d509dccb0</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1090,39 +1090,39 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>121.81</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.4363</t>
+          <t>1.2288</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
+          <t>Almirante Brown -1</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Primera Nacional</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Almirante Brown vs Ciudad Bolivar</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>Almirante Brown</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Primera Nacional</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>Almirante Brown vs Ciudad Bolivar</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>Almirante Brown</t>
-        </is>
-      </c>
       <c r="K7" t="inlineStr">
         <is>
           <t>Ciudad Bolivar</t>
@@ -1130,7 +1130,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0x63a8bf73c1084ef223fdd1096dccd16232e7a455fad77f7f0891be1588ebeb88</t>
+          <t>0xa6a338c64f062bfd589e8d5d9cea45a27c9e64065f71f800e5966f81ce53c556</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1160,7 +1160,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1786213844</t>
+          <t>1786214209</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1170,7 +1170,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>279.22063</t>
+          <t>6.295082</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1187,7 +1187,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0x1bb20a2bf22e4fe06b44c06b9c2caa21f3f2a7c9d0cce1a2346f79e76022cd1f</t>
+          <t>0xf65c55196eeb0d21e7e3866ad26f8c3f2fee2aef273ddde5423e31fb40a51469</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>21.05</t>
+          <t>121.81</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1212,12 +1212,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Almirante Brown -0.5</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0xfa00d2f0c7b5053ee336b303a0e7ad9cec0b8d539367773b7efee5c86cb2b59d</t>
+          <t>0x63a8bf73c1084ef223fdd1096dccd16232e7a455fad77f7f0891be1588ebeb88</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1786213843</t>
+          <t>1786213844</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1282,7 +1282,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>48.252149</t>
+          <t>279.22063</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1299,7 +1299,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0xc51052f8e449b4d56cc87b697bfc8eb0d3a88ae218dee1da3d725fa94163bc75</t>
+          <t>0x1bb20a2bf22e4fe06b44c06b9c2caa21f3f2a7c9d0cce1a2346f79e76022cd1f</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1307,28 +1307,36 @@
           <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>77.29513</t>
+          <t>21.05</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.2588</t>
+          <t>1.4363</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
+          <t>Asian Handicap (-0.5)</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Almirante Brown -0.5</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
           <t>Primera Nacional</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Primera Nacional</t>
-        </is>
-      </c>
       <c r="I9" t="inlineStr">
         <is>
           <t>Almirante Brown vs Ciudad Bolivar</t>
@@ -1346,7 +1354,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0xaa5316c6f6544d74142ad6db34a3745918f237ffb1a657e000693947e81b65d6</t>
+          <t>0xfa00d2f0c7b5053ee336b303a0e7ad9cec0b8d539367773b7efee5c86cb2b59d</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1376,7 +1384,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1786212849</t>
+          <t>1786213843</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1386,7 +1394,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>298.72514</t>
+          <t>48.252149</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1403,7 +1411,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0x0aeb4fe40f7d734cf244c144e6c064568b40b222193c9f93c641d1b31af3752e</t>
+          <t>0xc51052f8e449b4d56cc87b697bfc8eb0d3a88ae218dee1da3d725fa94163bc75</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1414,7 +1422,7 @@
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>16.89162</t>
+          <t>77.29513</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1480,7 +1488,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1786212805</t>
+          <t>1786212849</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1490,7 +1498,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>65.281623</t>
+          <t>298.72514</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1507,7 +1515,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0x383b895a5fe529a887369a0f113c516fdc7f6125d54381acf9695997ef22d039</t>
+          <t>0x0aeb4fe40f7d734cf244c144e6c064568b40b222193c9f93c641d1b31af3752e</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1515,19 +1523,15 @@
           <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>11.26905</t>
+          <t>16.89162</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.745</t>
+          <t>1.2588</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1535,26 +1539,22 @@
           <t>Primera Nacional</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Primera Nacional</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Almirante Brown vs Ciudad Bolivar</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
         <is>
           <t>Almirante Brown</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Primera Nacional</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>Almirante Brown vs Ciudad Bolivar</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>Almirante Brown</t>
-        </is>
-      </c>
       <c r="K11" t="inlineStr">
         <is>
           <t>Ciudad Bolivar</t>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1786211779</t>
+          <t>1786212805</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1602,7 +1602,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>15.126242</t>
+          <t>65.281623</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1619,12 +1619,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0xcfb6add6f8610a64ffc187beb9e16bf2bacb27b54a0f0aaefa6bfb437239b893</t>
+          <t>0x383b895a5fe529a887369a0f113c516fdc7f6125d54381acf9695997ef22d039</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>24.89998</t>
+          <t>11.26905</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1704,7 +1704,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1786211777</t>
+          <t>1786211779</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>33.422792</t>
+          <t>15.126242</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1731,12 +1731,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0xd41652604437a4e92e0d78b653d4d49d8dedd2e153d1340dad89b9b93e182a48</t>
+          <t>0xcfb6add6f8610a64ffc187beb9e16bf2bacb27b54a0f0aaefa6bfb437239b893</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0xf4a8B27C9a13e298D65b5Cc072d252816B799C81</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1746,22 +1746,22 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>24.89998</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.4163</t>
+          <t>1.745</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Primera Nacional</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Atl. Rafaela</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1771,27 +1771,27 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Atl. Rafaela vs Chacarita Juniors</t>
+          <t>Almirante Brown vs Ciudad Bolivar</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Atl. Rafaela</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Ciudad Bolivar</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>0xe738e9ba05492fab73eaaf6da211b84caadc72b08b26f1cd30fa8737e283bb44</t>
+          <t>0xaa5316c6f6544d74142ad6db34a3745918f237ffb1a657e000693947e81b65d6</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>L19683450</t>
+          <t>L19683447</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1786211028</t>
+          <t>1786211777</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>1786215600</t>
+          <t>1786212000</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2.402402</t>
+          <t>33.422792</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1843,31 +1843,39 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0x562fd7c6419c807ed04d3cacac95f861805f96704bd535e265399fb9d2c2b609</t>
+          <t>0xd41652604437a4e92e0d78b653d4d49d8dedd2e153d1340dad89b9b93e182a48</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr"/>
+          <t>0xf4a8B27C9a13e298D65b5Cc072d252816B799C81</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>5.32</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1.405</t>
+          <t>1.4163</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Atl. Rafaela</t>
+        </is>
+      </c>
       <c r="H14" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -1875,27 +1883,27 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Estudiantes de Caseros vs Deportivo Madryn</t>
+          <t>Atl. Rafaela vs Chacarita Juniors</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Estudiantes de Caseros</t>
+          <t>Atl. Rafaela</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>0xd61509e26f8645bb9780672f942c72c4b7dab577c2a01f04e1e09bce9b828765</t>
+          <t>0xe738e9ba05492fab73eaaf6da211b84caadc72b08b26f1cd30fa8737e283bb44</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>L19683453</t>
+          <t>L19683450</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1920,17 +1928,17 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1786210845</t>
+          <t>1786211028</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>1786212000</t>
+          <t>1786215600</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>13.135802</t>
+          <t>2.402402</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -1947,39 +1955,31 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0x0bb7a6822220bf40d7b279f99a54f46025f393ba95bb38b6d6dc98192886b3ed</t>
+          <t>0x562fd7c6419c807ed04d3cacac95f861805f96704bd535e265399fb9d2c2b609</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0xf4a8B27C9a13e298D65b5Cc072d252816B799C81</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>0.99999</t>
+          <t>5.32</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1.5513</t>
+          <t>1.405</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Agropecuario</t>
-        </is>
-      </c>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -1987,27 +1987,27 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Agropecuario vs Atletico Guemes</t>
+          <t>Estudiantes de Caseros vs Deportivo Madryn</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Estudiantes de Caseros</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Atletico Guemes</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>0xae66c7fab3c9c76fbc29d9e9778ef4845d8a6b8d092cff34320f100020113c49</t>
+          <t>0xd61509e26f8645bb9780672f942c72c4b7dab577c2a01f04e1e09bce9b828765</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>L19683451</t>
+          <t>L19683453</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -2032,7 +2032,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>1786205982</t>
+          <t>1786210845</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -2042,7 +2042,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>1.814041</t>
+          <t>13.135802</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2059,7 +2059,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0xe17b2546f4b90c8647ba975c279e39dec1fda5a003adfb8a2b39bb12a3519b10</t>
+          <t>0x0bb7a6822220bf40d7b279f99a54f46025f393ba95bb38b6d6dc98192886b3ed</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2074,12 +2074,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0.99999</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1.3613</t>
+          <t>1.5513</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -2089,7 +2089,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tie</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2099,27 +2099,27 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Almirante Brown vs Ciudad Bolivar</t>
+          <t>Agropecuario vs Atletico Guemes</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Ciudad Bolivar</t>
+          <t>Atletico Guemes</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>0xd5906ce08d61f7c5ee45fcebd2c8baeed5558387398ea332817a4b632f439b6d</t>
+          <t>0xae66c7fab3c9c76fbc29d9e9778ef4845d8a6b8d092cff34320f100020113c49</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>L19683447</t>
+          <t>L19683451</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -2144,7 +2144,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1786205963</t>
+          <t>1786205982</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2154,7 +2154,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2.768166</t>
+          <t>1.814041</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2171,7 +2171,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0xcfe218822e89cbef5841f3045f551cc65acf353d8e240f943e2b61c54ea79a68</t>
+          <t>0xe17b2546f4b90c8647ba975c279e39dec1fda5a003adfb8a2b39bb12a3519b10</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2191,7 +2191,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.3337</t>
+          <t>1.3613</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -2211,27 +2211,27 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Estudiantes de Caseros vs Deportivo Madryn</t>
+          <t>Almirante Brown vs Ciudad Bolivar</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Estudiantes de Caseros</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Ciudad Bolivar</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>0xf238b96ec9e2421db79973de945f1fc0c3f8bb99c31cda32d011ebaabfd2db86</t>
+          <t>0xd5906ce08d61f7c5ee45fcebd2c8baeed5558387398ea332817a4b632f439b6d</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>L19683453</t>
+          <t>L19683447</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>1786205938</t>
+          <t>1786205963</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -2266,7 +2266,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2.996255</t>
+          <t>2.768166</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2283,31 +2283,39 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0x1b9fcb29010a212f74af57040114154e78748f06a4d826be4397ddadb45ac31b</t>
+          <t>0xcfe218822e89cbef5841f3045f551cc65acf353d8e240f943e2b61c54ea79a68</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr"/>
+          <t>0xf4a8B27C9a13e298D65b5Cc072d252816B799C81</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>21.69</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.4512</t>
+          <t>1.3337</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H18" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -2315,27 +2323,27 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Almirante Brown vs Ciudad Bolivar</t>
+          <t>Estudiantes de Caseros vs Deportivo Madryn</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Estudiantes de Caseros</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Ciudad Bolivar</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>0xbbcaa253cd967fbf933ff0d87a6f9744cafec0ed59dad5f1f76332aab01a3fa5</t>
+          <t>0xf238b96ec9e2421db79973de945f1fc0c3f8bb99c31cda32d011ebaabfd2db86</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>L19683447</t>
+          <t>L19683453</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -2360,7 +2368,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>1786190525</t>
+          <t>1786205938</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2370,7 +2378,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>48.066482</t>
+          <t>2.996255</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2387,23 +2395,23 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0x3177792dd6a7185e37ae06612104cf5a35d137d7f535a889a83a7e9b7c174506</t>
+          <t>0x1b9fcb29010a212f74af57040114154e78748f06a4d826be4397ddadb45ac31b</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>18.35495</t>
+          <t>21.69</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1.4963</t>
+          <t>1.4512</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -2464,7 +2472,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>1786190491</t>
+          <t>1786190525</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -2474,7 +2482,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>36.987305</t>
+          <t>48.066482</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2491,7 +2499,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0x54ed4ee2a6ebdab49498137f1accea542ead806f21430a0a771cc4872a044e43</t>
+          <t>0x3177792dd6a7185e37ae06612104cf5a35d137d7f535a889a83a7e9b7c174506</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2499,19 +2507,15 @@
           <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>20.10741</t>
+          <t>18.35495</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.5437</t>
+          <t>1.4963</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -2519,11 +2523,7 @@
           <t>Under/Over (1.5)</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>Over 1.5</t>
-        </is>
-      </c>
+      <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -2576,7 +2576,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>1786190485</t>
+          <t>1786190491</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>36.979145</t>
+          <t>36.987305</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2603,23 +2603,27 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0x544fe5c906328d009917b591611ff3438cef85f8b42d9f67732cbbd5eabbb8dd</t>
+          <t>0x54ed4ee2a6ebdab49498137f1accea542ead806f21430a0a771cc4872a044e43</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr"/>
+          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>21.69</t>
+          <t>20.10741</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1.4512</t>
+          <t>1.5437</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -2627,7 +2631,11 @@
           <t>Under/Over (1.5)</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Over 1.5</t>
+        </is>
+      </c>
       <c r="H21" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -2690,7 +2698,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>48.066482</t>
+          <t>36.979145</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -2707,7 +2715,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0xb2f3ea804e1760a01d3a93678f0e2119f1ea2a9db0dc4711a06cc7bcba42b0c2</t>
+          <t>0x544fe5c906328d009917b591611ff3438cef85f8b42d9f67732cbbd5eabbb8dd</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2718,12 +2726,12 @@
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
-          <t>17.47</t>
+          <t>21.69</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1.405</t>
+          <t>1.4512</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -2739,27 +2747,27 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Estudiantes de Caseros vs Deportivo Madryn</t>
+          <t>Almirante Brown vs Ciudad Bolivar</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Estudiantes de Caseros</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Ciudad Bolivar</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0xd61509e26f8645bb9780672f942c72c4b7dab577c2a01f04e1e09bce9b828765</t>
+          <t>0xbbcaa253cd967fbf933ff0d87a6f9744cafec0ed59dad5f1f76332aab01a3fa5</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>L19683453</t>
+          <t>L19683447</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -2784,7 +2792,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>1786190461</t>
+          <t>1786190485</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -2794,7 +2802,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>43.135802</t>
+          <t>48.066482</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -2811,7 +2819,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0xa7eafbb77d425fc2347b4ee3e4f4e1b85f6d0f81420605db76ebfeeaa793a428</t>
+          <t>0xb2f3ea804e1760a01d3a93678f0e2119f1ea2a9db0dc4711a06cc7bcba42b0c2</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2822,12 +2830,12 @@
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>21.69</t>
+          <t>17.47</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1.4512</t>
+          <t>1.405</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -2843,27 +2851,27 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Almirante Brown vs Ciudad Bolivar</t>
+          <t>Estudiantes de Caseros vs Deportivo Madryn</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Estudiantes de Caseros</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Ciudad Bolivar</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0xbbcaa253cd967fbf933ff0d87a6f9744cafec0ed59dad5f1f76332aab01a3fa5</t>
+          <t>0xd61509e26f8645bb9780672f942c72c4b7dab577c2a01f04e1e09bce9b828765</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>L19683447</t>
+          <t>L19683453</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -2888,7 +2896,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>1786190458</t>
+          <t>1786190461</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -2898,7 +2906,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>48.066482</t>
+          <t>43.135802</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -2915,110 +2923,214 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>0xa7eafbb77d425fc2347b4ee3e4f4e1b85f6d0f81420605db76ebfeeaa793a428</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>21.69</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>1.4512</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Primera Nacional</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Almirante Brown vs Ciudad Bolivar</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Almirante Brown</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Ciudad Bolivar</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>0xbbcaa253cd967fbf933ff0d87a6f9744cafec0ed59dad5f1f76332aab01a3fa5</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>L19683447</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>1786190458</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>1786212000</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>48.066482</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
           <t>0x5c5b512ea725fac30531bf5fe91f34f3ccc0eeff23890c18f25c3f329007c589</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
         <is>
           <t>1.3638</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>1X2</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t>Tie</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="H25" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
+      <c r="I25" t="inlineStr">
         <is>
           <t>Almirante Brown vs Ciudad Bolivar</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr">
+      <c r="J25" t="inlineStr">
         <is>
           <t>Almirante Brown</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr">
+      <c r="K25" t="inlineStr">
         <is>
           <t>Ciudad Bolivar</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr">
+      <c r="L25" t="inlineStr">
         <is>
           <t>0xd5906ce08d61f7c5ee45fcebd2c8baeed5558387398ea332817a4b632f439b6d</t>
         </is>
       </c>
-      <c r="M24" t="inlineStr">
+      <c r="M25" t="inlineStr">
         <is>
           <t>L19683447</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P24" t="inlineStr">
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R24" t="inlineStr">
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
         <is>
           <t>1786125660</t>
         </is>
       </c>
-      <c r="S24" t="inlineStr">
+      <c r="S25" t="inlineStr">
         <is>
           <t>1786212000</t>
         </is>
       </c>
-      <c r="T24" t="inlineStr">
+      <c r="T25" t="inlineStr">
         <is>
           <t>2.749141</t>
         </is>
       </c>
-      <c r="U24" t="inlineStr">
+      <c r="U25" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V24" t="inlineStr">
+      <c r="V25" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/Primera Nacional/trades.xlsx
+++ b/data/sxbet/ligas/Primera Nacional/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V25"/>
+  <dimension ref="A1:V26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,7 +531,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0x86f4b24298f4c19f9f856cb19af2a260f24dc2d391f252248469436057ea1d1a</t>
+          <t>0xd3b94d194e43cc84f0a1b82723594ea6689a6aa2a4a7dccbc8a3d19fc321e49b</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -539,11 +539,7 @@
           <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>1</t>
@@ -551,19 +547,15 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.5263</t>
+          <t>1.5238</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Deportivo Moron -1</t>
-        </is>
-      </c>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -586,7 +578,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0xb61b063252c01d0525ae633a0276dc1830eabd418482fddec925fcbd602a2a75</t>
+          <t>0x108eaba0441fb45ec8e0073e945ae0ac1e138c933e4f2839816cd3198d7dd4d2</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -616,7 +608,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1786220171</t>
+          <t>1786225000</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -626,7 +618,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1.900238</t>
+          <t>1.909308</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -643,12 +635,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0x0a5de930b5a6b8aca1699b666034af3891a3aa920021791d6d13e0297fb7903f</t>
+          <t>0x86f4b24298f4c19f9f856cb19af2a260f24dc2d391f252248469436057ea1d1a</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0x4a09916b1325Eed50eE8973B13742a205B0B7c7E</t>
+          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -658,12 +650,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>49.99999</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.6175</t>
+          <t>1.5263</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -673,7 +665,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Almirante Brown -1</t>
+          <t>Deportivo Moron -1</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -683,27 +675,27 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Almirante Brown vs Ciudad Bolivar</t>
+          <t>Deportivo Moron vs Acassuso</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Deportivo Moron</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Ciudad Bolivar</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0xa6a338c64f062bfd589e8d5d9cea45a27c9e64065f71f800e5966f81ce53c556</t>
+          <t>0xb61b063252c01d0525ae633a0276dc1830eabd418482fddec925fcbd602a2a75</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>L19683447</t>
+          <t>L19683452</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -728,17 +720,17 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1786218515</t>
+          <t>1786220171</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>1786212000</t>
+          <t>1786298400</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>80.971644</t>
+          <t>1.900238</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -755,23 +747,27 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0x17d5a08f8fa305f31f27442393c64f497dd3893417da6e76c321c4c2a187320d</t>
+          <t>0x0a5de930b5a6b8aca1699b666034af3891a3aa920021791d6d13e0297fb7903f</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
+          <t>0x4a09916b1325Eed50eE8973B13742a205B0B7c7E</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>49.18897</t>
+          <t>49.99999</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.4737</t>
+          <t>1.6175</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -779,7 +775,11 @@
           <t>Asian Handicap (-1)</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Almirante Brown -1</t>
+        </is>
+      </c>
       <c r="H4" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -832,7 +832,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1786218084</t>
+          <t>1786218515</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>103.82896</t>
+          <t>80.971644</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -859,28 +859,28 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0x56975f372357be259365cb7d2929c88d4fae157eea7a71d53d57cb234834f2ca</t>
+          <t>0x17d5a08f8fa305f31f27442393c64f497dd3893417da6e76c321c4c2a187320d</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>49.18897</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.4812</t>
+          <t>1.4737</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
@@ -891,27 +891,27 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Club Atletico Mitre de Santiago del Estero vs Defensores de Belgrano Buenos Aires</t>
+          <t>Almirante Brown vs Ciudad Bolivar</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Club Atletico Mitre de Santiago del Estero</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano Buenos Aires</t>
+          <t>Ciudad Bolivar</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0xa8ade64a3adb0ea38de67a61105ef31beb490d5a7287715b76ae124536d359cc</t>
+          <t>0xa6a338c64f062bfd589e8d5d9cea45a27c9e64065f71f800e5966f81ce53c556</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>L19683493</t>
+          <t>L19683447</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -936,17 +936,17 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1786215674</t>
+          <t>1786218084</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>1786302000</t>
+          <t>1786212000</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2.077922</t>
+          <t>103.82896</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -963,7 +963,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0xff53df1f3446908699196d44fcdb8b39c1bd15c7ed519f0d730e55a51a6eb38f</t>
+          <t>0x56975f372357be259365cb7d2929c88d4fae157eea7a71d53d57cb234834f2ca</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -971,11 +971,7 @@
           <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
           <t>1</t>
@@ -983,19 +979,15 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.3713</t>
+          <t>1.4812</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Almirante Brown</t>
-        </is>
-      </c>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -1003,27 +995,27 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Almirante Brown vs Ciudad Bolivar</t>
+          <t>Club Atletico Mitre de Santiago del Estero vs Defensores de Belgrano Buenos Aires</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Club Atletico Mitre de Santiago del Estero</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Ciudad Bolivar</t>
+          <t>Defensores de Belgrano Buenos Aires</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0x63a8bf73c1084ef223fdd1096dccd16232e7a455fad77f7f0891be1588ebeb88</t>
+          <t>0xa8ade64a3adb0ea38de67a61105ef31beb490d5a7287715b76ae124536d359cc</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>L19683447</t>
+          <t>L19683493</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1048,17 +1040,17 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1786215673</t>
+          <t>1786215674</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>1786212000</t>
+          <t>1786302000</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2.693603</t>
+          <t>2.077922</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1075,12 +1067,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0x249d52552e7acb9f472d2a4c48ab754622ba572903281739a3e10b4d509dccb0</t>
+          <t>0xff53df1f3446908699196d44fcdb8b39c1bd15c7ed519f0d730e55a51a6eb38f</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1090,22 +1082,22 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.2288</t>
+          <t>1.3713</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Almirante Brown -1</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1130,7 +1122,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0xa6a338c64f062bfd589e8d5d9cea45a27c9e64065f71f800e5966f81ce53c556</t>
+          <t>0x63a8bf73c1084ef223fdd1096dccd16232e7a455fad77f7f0891be1588ebeb88</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1160,7 +1152,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1786214209</t>
+          <t>1786215673</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1170,7 +1162,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>6.295082</t>
+          <t>2.693603</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1187,12 +1179,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0xf65c55196eeb0d21e7e3866ad26f8c3f2fee2aef273ddde5423e31fb40a51469</t>
+          <t>0x249d52552e7acb9f472d2a4c48ab754622ba572903281739a3e10b4d509dccb0</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1202,39 +1194,39 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>121.81</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.4363</t>
+          <t>1.2288</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
+          <t>Almirante Brown -1</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Primera Nacional</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Almirante Brown vs Ciudad Bolivar</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>Almirante Brown</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Primera Nacional</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>Almirante Brown vs Ciudad Bolivar</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>Almirante Brown</t>
-        </is>
-      </c>
       <c r="K8" t="inlineStr">
         <is>
           <t>Ciudad Bolivar</t>
@@ -1242,7 +1234,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0x63a8bf73c1084ef223fdd1096dccd16232e7a455fad77f7f0891be1588ebeb88</t>
+          <t>0xa6a338c64f062bfd589e8d5d9cea45a27c9e64065f71f800e5966f81ce53c556</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1272,7 +1264,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1786213844</t>
+          <t>1786214209</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1282,7 +1274,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>279.22063</t>
+          <t>6.295082</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1299,7 +1291,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0x1bb20a2bf22e4fe06b44c06b9c2caa21f3f2a7c9d0cce1a2346f79e76022cd1f</t>
+          <t>0xf65c55196eeb0d21e7e3866ad26f8c3f2fee2aef273ddde5423e31fb40a51469</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1314,7 +1306,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>21.05</t>
+          <t>121.81</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1324,12 +1316,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Almirante Brown -0.5</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1354,7 +1346,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0xfa00d2f0c7b5053ee336b303a0e7ad9cec0b8d539367773b7efee5c86cb2b59d</t>
+          <t>0x63a8bf73c1084ef223fdd1096dccd16232e7a455fad77f7f0891be1588ebeb88</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1384,7 +1376,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1786213843</t>
+          <t>1786213844</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1394,7 +1386,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>48.252149</t>
+          <t>279.22063</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1411,7 +1403,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0xc51052f8e449b4d56cc87b697bfc8eb0d3a88ae218dee1da3d725fa94163bc75</t>
+          <t>0x1bb20a2bf22e4fe06b44c06b9c2caa21f3f2a7c9d0cce1a2346f79e76022cd1f</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1419,28 +1411,36 @@
           <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr"/>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>77.29513</t>
+          <t>21.05</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.2588</t>
+          <t>1.4363</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
+          <t>Asian Handicap (-0.5)</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Almirante Brown -0.5</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
           <t>Primera Nacional</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Primera Nacional</t>
-        </is>
-      </c>
       <c r="I10" t="inlineStr">
         <is>
           <t>Almirante Brown vs Ciudad Bolivar</t>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0xaa5316c6f6544d74142ad6db34a3745918f237ffb1a657e000693947e81b65d6</t>
+          <t>0xfa00d2f0c7b5053ee336b303a0e7ad9cec0b8d539367773b7efee5c86cb2b59d</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1488,7 +1488,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1786212849</t>
+          <t>1786213843</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1498,7 +1498,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>298.72514</t>
+          <t>48.252149</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1515,7 +1515,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0x0aeb4fe40f7d734cf244c144e6c064568b40b222193c9f93c641d1b31af3752e</t>
+          <t>0xc51052f8e449b4d56cc87b697bfc8eb0d3a88ae218dee1da3d725fa94163bc75</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1526,7 +1526,7 @@
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>16.89162</t>
+          <t>77.29513</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1592,7 +1592,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1786212805</t>
+          <t>1786212849</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1602,7 +1602,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>65.281623</t>
+          <t>298.72514</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1619,7 +1619,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0x383b895a5fe529a887369a0f113c516fdc7f6125d54381acf9695997ef22d039</t>
+          <t>0x0aeb4fe40f7d734cf244c144e6c064568b40b222193c9f93c641d1b31af3752e</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1627,19 +1627,15 @@
           <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>11.26905</t>
+          <t>16.89162</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.745</t>
+          <t>1.2588</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1647,26 +1643,22 @@
           <t>Primera Nacional</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Primera Nacional</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Almirante Brown vs Ciudad Bolivar</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
         <is>
           <t>Almirante Brown</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Primera Nacional</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>Almirante Brown vs Ciudad Bolivar</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>Almirante Brown</t>
-        </is>
-      </c>
       <c r="K12" t="inlineStr">
         <is>
           <t>Ciudad Bolivar</t>
@@ -1704,7 +1696,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1786211779</t>
+          <t>1786212805</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -1714,7 +1706,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>15.126242</t>
+          <t>65.281623</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1731,12 +1723,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0xcfb6add6f8610a64ffc187beb9e16bf2bacb27b54a0f0aaefa6bfb437239b893</t>
+          <t>0x383b895a5fe529a887369a0f113c516fdc7f6125d54381acf9695997ef22d039</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1746,7 +1738,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>24.89998</t>
+          <t>11.26905</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1816,7 +1808,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1786211777</t>
+          <t>1786211779</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1826,7 +1818,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>33.422792</t>
+          <t>15.126242</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1843,12 +1835,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0xd41652604437a4e92e0d78b653d4d49d8dedd2e153d1340dad89b9b93e182a48</t>
+          <t>0xcfb6add6f8610a64ffc187beb9e16bf2bacb27b54a0f0aaefa6bfb437239b893</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0xf4a8B27C9a13e298D65b5Cc072d252816B799C81</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1858,22 +1850,22 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>24.89998</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1.4163</t>
+          <t>1.745</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Primera Nacional</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Atl. Rafaela</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1883,27 +1875,27 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Atl. Rafaela vs Chacarita Juniors</t>
+          <t>Almirante Brown vs Ciudad Bolivar</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Atl. Rafaela</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Ciudad Bolivar</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>0xe738e9ba05492fab73eaaf6da211b84caadc72b08b26f1cd30fa8737e283bb44</t>
+          <t>0xaa5316c6f6544d74142ad6db34a3745918f237ffb1a657e000693947e81b65d6</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>L19683450</t>
+          <t>L19683447</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1928,17 +1920,17 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1786211028</t>
+          <t>1786211777</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>1786215600</t>
+          <t>1786212000</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2.402402</t>
+          <t>33.422792</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -1955,31 +1947,39 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0x562fd7c6419c807ed04d3cacac95f861805f96704bd535e265399fb9d2c2b609</t>
+          <t>0xd41652604437a4e92e0d78b653d4d49d8dedd2e153d1340dad89b9b93e182a48</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr"/>
+          <t>0xf4a8B27C9a13e298D65b5Cc072d252816B799C81</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>5.32</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1.405</t>
+          <t>1.4163</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Atl. Rafaela</t>
+        </is>
+      </c>
       <c r="H15" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -1987,27 +1987,27 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Estudiantes de Caseros vs Deportivo Madryn</t>
+          <t>Atl. Rafaela vs Chacarita Juniors</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Estudiantes de Caseros</t>
+          <t>Atl. Rafaela</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>0xd61509e26f8645bb9780672f942c72c4b7dab577c2a01f04e1e09bce9b828765</t>
+          <t>0xe738e9ba05492fab73eaaf6da211b84caadc72b08b26f1cd30fa8737e283bb44</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>L19683453</t>
+          <t>L19683450</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -2032,17 +2032,17 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>1786210845</t>
+          <t>1786211028</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>1786212000</t>
+          <t>1786215600</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>13.135802</t>
+          <t>2.402402</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2059,39 +2059,31 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0x0bb7a6822220bf40d7b279f99a54f46025f393ba95bb38b6d6dc98192886b3ed</t>
+          <t>0x562fd7c6419c807ed04d3cacac95f861805f96704bd535e265399fb9d2c2b609</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0xf4a8B27C9a13e298D65b5Cc072d252816B799C81</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>0.99999</t>
+          <t>5.32</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1.5513</t>
+          <t>1.405</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Agropecuario</t>
-        </is>
-      </c>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -2099,27 +2091,27 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Agropecuario vs Atletico Guemes</t>
+          <t>Estudiantes de Caseros vs Deportivo Madryn</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Estudiantes de Caseros</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Atletico Guemes</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>0xae66c7fab3c9c76fbc29d9e9778ef4845d8a6b8d092cff34320f100020113c49</t>
+          <t>0xd61509e26f8645bb9780672f942c72c4b7dab577c2a01f04e1e09bce9b828765</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>L19683451</t>
+          <t>L19683453</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -2144,7 +2136,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1786205982</t>
+          <t>1786210845</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2154,7 +2146,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>1.814041</t>
+          <t>13.135802</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2171,7 +2163,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0xe17b2546f4b90c8647ba975c279e39dec1fda5a003adfb8a2b39bb12a3519b10</t>
+          <t>0x0bb7a6822220bf40d7b279f99a54f46025f393ba95bb38b6d6dc98192886b3ed</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2186,12 +2178,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0.99999</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.3613</t>
+          <t>1.5513</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -2201,7 +2193,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tie</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2211,27 +2203,27 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Almirante Brown vs Ciudad Bolivar</t>
+          <t>Agropecuario vs Atletico Guemes</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Ciudad Bolivar</t>
+          <t>Atletico Guemes</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>0xd5906ce08d61f7c5ee45fcebd2c8baeed5558387398ea332817a4b632f439b6d</t>
+          <t>0xae66c7fab3c9c76fbc29d9e9778ef4845d8a6b8d092cff34320f100020113c49</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>L19683447</t>
+          <t>L19683451</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -2256,7 +2248,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>1786205963</t>
+          <t>1786205982</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -2266,7 +2258,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2.768166</t>
+          <t>1.814041</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2283,7 +2275,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0xcfe218822e89cbef5841f3045f551cc65acf353d8e240f943e2b61c54ea79a68</t>
+          <t>0xe17b2546f4b90c8647ba975c279e39dec1fda5a003adfb8a2b39bb12a3519b10</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2303,7 +2295,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.3337</t>
+          <t>1.3613</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -2323,27 +2315,27 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Estudiantes de Caseros vs Deportivo Madryn</t>
+          <t>Almirante Brown vs Ciudad Bolivar</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Estudiantes de Caseros</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Ciudad Bolivar</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>0xf238b96ec9e2421db79973de945f1fc0c3f8bb99c31cda32d011ebaabfd2db86</t>
+          <t>0xd5906ce08d61f7c5ee45fcebd2c8baeed5558387398ea332817a4b632f439b6d</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>L19683453</t>
+          <t>L19683447</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -2368,7 +2360,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>1786205938</t>
+          <t>1786205963</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2378,7 +2370,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2.996255</t>
+          <t>2.768166</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2395,31 +2387,39 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0x1b9fcb29010a212f74af57040114154e78748f06a4d826be4397ddadb45ac31b</t>
+          <t>0xcfe218822e89cbef5841f3045f551cc65acf353d8e240f943e2b61c54ea79a68</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr"/>
+          <t>0xf4a8B27C9a13e298D65b5Cc072d252816B799C81</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>21.69</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1.4512</t>
+          <t>1.3337</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H19" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -2427,27 +2427,27 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Almirante Brown vs Ciudad Bolivar</t>
+          <t>Estudiantes de Caseros vs Deportivo Madryn</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Estudiantes de Caseros</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Ciudad Bolivar</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>0xbbcaa253cd967fbf933ff0d87a6f9744cafec0ed59dad5f1f76332aab01a3fa5</t>
+          <t>0xf238b96ec9e2421db79973de945f1fc0c3f8bb99c31cda32d011ebaabfd2db86</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>L19683447</t>
+          <t>L19683453</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -2472,7 +2472,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>1786190525</t>
+          <t>1786205938</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -2482,7 +2482,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>48.066482</t>
+          <t>2.996255</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2499,23 +2499,23 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0x3177792dd6a7185e37ae06612104cf5a35d137d7f535a889a83a7e9b7c174506</t>
+          <t>0x1b9fcb29010a212f74af57040114154e78748f06a4d826be4397ddadb45ac31b</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>18.35495</t>
+          <t>21.69</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.4963</t>
+          <t>1.4512</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>1786190491</t>
+          <t>1786190525</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>36.987305</t>
+          <t>48.066482</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2603,7 +2603,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0x54ed4ee2a6ebdab49498137f1accea542ead806f21430a0a771cc4872a044e43</t>
+          <t>0x3177792dd6a7185e37ae06612104cf5a35d137d7f535a889a83a7e9b7c174506</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2611,19 +2611,15 @@
           <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>20.10741</t>
+          <t>18.35495</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1.5437</t>
+          <t>1.4963</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -2631,11 +2627,7 @@
           <t>Under/Over (1.5)</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Over 1.5</t>
-        </is>
-      </c>
+      <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -2688,7 +2680,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>1786190485</t>
+          <t>1786190491</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -2698,7 +2690,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>36.979145</t>
+          <t>36.987305</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -2715,23 +2707,27 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0x544fe5c906328d009917b591611ff3438cef85f8b42d9f67732cbbd5eabbb8dd</t>
+          <t>0x54ed4ee2a6ebdab49498137f1accea542ead806f21430a0a771cc4872a044e43</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr"/>
+          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>21.69</t>
+          <t>20.10741</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1.4512</t>
+          <t>1.5437</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -2739,7 +2735,11 @@
           <t>Under/Over (1.5)</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Over 1.5</t>
+        </is>
+      </c>
       <c r="H22" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -2802,7 +2802,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>48.066482</t>
+          <t>36.979145</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -2819,7 +2819,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0xb2f3ea804e1760a01d3a93678f0e2119f1ea2a9db0dc4711a06cc7bcba42b0c2</t>
+          <t>0x544fe5c906328d009917b591611ff3438cef85f8b42d9f67732cbbd5eabbb8dd</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2830,12 +2830,12 @@
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>17.47</t>
+          <t>21.69</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1.405</t>
+          <t>1.4512</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -2851,27 +2851,27 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Estudiantes de Caseros vs Deportivo Madryn</t>
+          <t>Almirante Brown vs Ciudad Bolivar</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Estudiantes de Caseros</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Ciudad Bolivar</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0xd61509e26f8645bb9780672f942c72c4b7dab577c2a01f04e1e09bce9b828765</t>
+          <t>0xbbcaa253cd967fbf933ff0d87a6f9744cafec0ed59dad5f1f76332aab01a3fa5</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>L19683453</t>
+          <t>L19683447</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -2896,7 +2896,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>1786190461</t>
+          <t>1786190485</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -2906,7 +2906,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>43.135802</t>
+          <t>48.066482</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -2923,7 +2923,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0xa7eafbb77d425fc2347b4ee3e4f4e1b85f6d0f81420605db76ebfeeaa793a428</t>
+          <t>0xb2f3ea804e1760a01d3a93678f0e2119f1ea2a9db0dc4711a06cc7bcba42b0c2</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2934,12 +2934,12 @@
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
-          <t>21.69</t>
+          <t>17.47</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1.4512</t>
+          <t>1.405</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -2955,27 +2955,27 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Almirante Brown vs Ciudad Bolivar</t>
+          <t>Estudiantes de Caseros vs Deportivo Madryn</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Estudiantes de Caseros</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Ciudad Bolivar</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0xbbcaa253cd967fbf933ff0d87a6f9744cafec0ed59dad5f1f76332aab01a3fa5</t>
+          <t>0xd61509e26f8645bb9780672f942c72c4b7dab577c2a01f04e1e09bce9b828765</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>L19683447</t>
+          <t>L19683453</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -3000,7 +3000,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>1786190458</t>
+          <t>1786190461</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -3010,7 +3010,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>48.066482</t>
+          <t>43.135802</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -3027,110 +3027,214 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>0xa7eafbb77d425fc2347b4ee3e4f4e1b85f6d0f81420605db76ebfeeaa793a428</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>21.69</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>1.4512</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Primera Nacional</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Almirante Brown vs Ciudad Bolivar</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Almirante Brown</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Ciudad Bolivar</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>0xbbcaa253cd967fbf933ff0d87a6f9744cafec0ed59dad5f1f76332aab01a3fa5</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>L19683447</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>1786190458</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>1786212000</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>48.066482</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
           <t>0x5c5b512ea725fac30531bf5fe91f34f3ccc0eeff23890c18f25c3f329007c589</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
         <is>
           <t>1.3638</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>1X2</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t>Tie</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="H26" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
+      <c r="I26" t="inlineStr">
         <is>
           <t>Almirante Brown vs Ciudad Bolivar</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr">
+      <c r="J26" t="inlineStr">
         <is>
           <t>Almirante Brown</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr">
+      <c r="K26" t="inlineStr">
         <is>
           <t>Ciudad Bolivar</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr">
+      <c r="L26" t="inlineStr">
         <is>
           <t>0xd5906ce08d61f7c5ee45fcebd2c8baeed5558387398ea332817a4b632f439b6d</t>
         </is>
       </c>
-      <c r="M25" t="inlineStr">
+      <c r="M26" t="inlineStr">
         <is>
           <t>L19683447</t>
         </is>
       </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P25" t="inlineStr">
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R25" t="inlineStr">
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
         <is>
           <t>1786125660</t>
         </is>
       </c>
-      <c r="S25" t="inlineStr">
+      <c r="S26" t="inlineStr">
         <is>
           <t>1786212000</t>
         </is>
       </c>
-      <c r="T25" t="inlineStr">
+      <c r="T26" t="inlineStr">
         <is>
           <t>2.749141</t>
         </is>
       </c>
-      <c r="U25" t="inlineStr">
+      <c r="U26" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V25" t="inlineStr">
+      <c r="V26" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/Primera Nacional/trades.xlsx
+++ b/data/sxbet/ligas/Primera Nacional/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V26"/>
+  <dimension ref="A1:V28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,15 +531,19 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0xd3b94d194e43cc84f0a1b82723594ea6689a6aa2a4a7dccbc8a3d19fc321e49b</t>
+          <t>0x4e811c319e5e3a1fc1968ce0f31b4c15eb7222daa616252d99f9abc611408746</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr"/>
+          <t>0x155C76202e45BE70c50bfeD7eAeA3B98e7716Ff7</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
           <t>1</t>
@@ -547,15 +551,19 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.5238</t>
+          <t>1.2925</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H2" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -563,27 +571,27 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Deportivo Moron vs Acassuso</t>
+          <t>Colon de Santa Fe vs San Telmo</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Deportivo Moron</t>
+          <t>Colon de Santa Fe</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0x108eaba0441fb45ec8e0073e945ae0ac1e138c933e4f2839816cd3198d7dd4d2</t>
+          <t>0x2e49527408facf21253a0a1eafe51280b82e4c31919e91a396332f19ec366401</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>L19683452</t>
+          <t>L19683494</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -608,17 +616,17 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1786225000</t>
+          <t>1786243741</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>1786298400</t>
+          <t>1786300200</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1.909308</t>
+          <t>3.418803</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -635,12 +643,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0x86f4b24298f4c19f9f856cb19af2a260f24dc2d391f252248469436057ea1d1a</t>
+          <t>0xb8631aeb398192a03386505542f05fa15e34db501204baa8745a4d4b5c1651b7</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
+          <t>0x155C76202e45BE70c50bfeD7eAeA3B98e7716Ff7</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -650,22 +658,22 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0.99999</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.5263</t>
+          <t>1.6538</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Deportivo Moron -1</t>
+          <t>Deportivo Moron</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -690,7 +698,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0xb61b063252c01d0525ae633a0276dc1830eabd418482fddec925fcbd602a2a75</t>
+          <t>0x7514a255ce41be3c5db9f8849ba04e78dab80f02d1fe78c2aae82bbc843a9745</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -720,7 +728,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1786220171</t>
+          <t>1786243225</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -730,7 +738,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1.900238</t>
+          <t>1.529621</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -747,39 +755,31 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0x0a5de930b5a6b8aca1699b666034af3891a3aa920021791d6d13e0297fb7903f</t>
+          <t>0xd3b94d194e43cc84f0a1b82723594ea6689a6aa2a4a7dccbc8a3d19fc321e49b</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0x4a09916b1325Eed50eE8973B13742a205B0B7c7E</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>49.99999</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.6175</t>
+          <t>1.5238</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Almirante Brown -1</t>
-        </is>
-      </c>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -787,27 +787,27 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Almirante Brown vs Ciudad Bolivar</t>
+          <t>Deportivo Moron vs Acassuso</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Deportivo Moron</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Ciudad Bolivar</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0xa6a338c64f062bfd589e8d5d9cea45a27c9e64065f71f800e5966f81ce53c556</t>
+          <t>0x108eaba0441fb45ec8e0073e945ae0ac1e138c933e4f2839816cd3198d7dd4d2</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>L19683447</t>
+          <t>L19683452</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -832,17 +832,17 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1786218515</t>
+          <t>1786225000</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>1786212000</t>
+          <t>1786298400</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>80.971644</t>
+          <t>1.909308</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -859,23 +859,27 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0x17d5a08f8fa305f31f27442393c64f497dd3893417da6e76c321c4c2a187320d</t>
+          <t>0x86f4b24298f4c19f9f856cb19af2a260f24dc2d391f252248469436057ea1d1a</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr"/>
+          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>49.18897</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.4737</t>
+          <t>1.5263</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -883,7 +887,11 @@
           <t>Asian Handicap (-1)</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Deportivo Moron -1</t>
+        </is>
+      </c>
       <c r="H5" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -891,27 +899,27 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Almirante Brown vs Ciudad Bolivar</t>
+          <t>Deportivo Moron vs Acassuso</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Deportivo Moron</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Ciudad Bolivar</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0xa6a338c64f062bfd589e8d5d9cea45a27c9e64065f71f800e5966f81ce53c556</t>
+          <t>0xb61b063252c01d0525ae633a0276dc1830eabd418482fddec925fcbd602a2a75</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>L19683447</t>
+          <t>L19683452</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -936,17 +944,17 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1786218084</t>
+          <t>1786220171</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>1786212000</t>
+          <t>1786298400</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>103.82896</t>
+          <t>1.900238</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -963,31 +971,39 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0x56975f372357be259365cb7d2929c88d4fae157eea7a71d53d57cb234834f2ca</t>
+          <t>0x0a5de930b5a6b8aca1699b666034af3891a3aa920021791d6d13e0297fb7903f</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr"/>
+          <t>0x4a09916b1325Eed50eE8973B13742a205B0B7c7E</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>49.99999</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.4812</t>
+          <t>1.6175</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr"/>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Almirante Brown -1</t>
+        </is>
+      </c>
       <c r="H6" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -995,27 +1011,27 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Club Atletico Mitre de Santiago del Estero vs Defensores de Belgrano Buenos Aires</t>
+          <t>Almirante Brown vs Ciudad Bolivar</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Club Atletico Mitre de Santiago del Estero</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano Buenos Aires</t>
+          <t>Ciudad Bolivar</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0xa8ade64a3adb0ea38de67a61105ef31beb490d5a7287715b76ae124536d359cc</t>
+          <t>0xa6a338c64f062bfd589e8d5d9cea45a27c9e64065f71f800e5966f81ce53c556</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>L19683493</t>
+          <t>L19683447</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1040,17 +1056,17 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1786215674</t>
+          <t>1786218515</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>1786302000</t>
+          <t>1786212000</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2.077922</t>
+          <t>80.971644</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1067,54 +1083,46 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0xff53df1f3446908699196d44fcdb8b39c1bd15c7ed519f0d730e55a51a6eb38f</t>
+          <t>0x17d5a08f8fa305f31f27442393c64f497dd3893417da6e76c321c4c2a187320d</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>49.18897</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.3713</t>
+          <t>1.4737</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Primera Nacional</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Almirante Brown vs Ciudad Bolivar</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
         <is>
           <t>Almirante Brown</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Primera Nacional</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>Almirante Brown vs Ciudad Bolivar</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>Almirante Brown</t>
-        </is>
-      </c>
       <c r="K7" t="inlineStr">
         <is>
           <t>Ciudad Bolivar</t>
@@ -1122,7 +1130,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0x63a8bf73c1084ef223fdd1096dccd16232e7a455fad77f7f0891be1588ebeb88</t>
+          <t>0xa6a338c64f062bfd589e8d5d9cea45a27c9e64065f71f800e5966f81ce53c556</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1152,7 +1160,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1786215673</t>
+          <t>1786218084</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1162,7 +1170,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2.693603</t>
+          <t>103.82896</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1179,39 +1187,31 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0x249d52552e7acb9f472d2a4c48ab754622ba572903281739a3e10b4d509dccb0</t>
+          <t>0x56975f372357be259365cb7d2929c88d4fae157eea7a71d53d57cb234834f2ca</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.2288</t>
+          <t>1.4812</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Almirante Brown -1</t>
-        </is>
-      </c>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -1219,27 +1219,27 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Almirante Brown vs Ciudad Bolivar</t>
+          <t>Club Atletico Mitre de Santiago del Estero vs Defensores de Belgrano Buenos Aires</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Club Atletico Mitre de Santiago del Estero</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Ciudad Bolivar</t>
+          <t>Defensores de Belgrano Buenos Aires</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0xa6a338c64f062bfd589e8d5d9cea45a27c9e64065f71f800e5966f81ce53c556</t>
+          <t>0xa8ade64a3adb0ea38de67a61105ef31beb490d5a7287715b76ae124536d359cc</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>L19683447</t>
+          <t>L19683493</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1264,17 +1264,17 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1786214209</t>
+          <t>1786215674</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>1786212000</t>
+          <t>1786302000</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>6.295082</t>
+          <t>2.077922</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1291,12 +1291,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0xf65c55196eeb0d21e7e3866ad26f8c3f2fee2aef273ddde5423e31fb40a51469</t>
+          <t>0xff53df1f3446908699196d44fcdb8b39c1bd15c7ed519f0d730e55a51a6eb38f</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1306,12 +1306,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>121.81</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.4363</t>
+          <t>1.3713</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1376,7 +1376,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1786213844</t>
+          <t>1786215673</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1386,7 +1386,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>279.22063</t>
+          <t>2.693603</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1403,12 +1403,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0x1bb20a2bf22e4fe06b44c06b9c2caa21f3f2a7c9d0cce1a2346f79e76022cd1f</t>
+          <t>0x249d52552e7acb9f472d2a4c48ab754622ba572903281739a3e10b4d509dccb0</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1418,22 +1418,22 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>21.05</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.4363</t>
+          <t>1.2288</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Almirante Brown -0.5</t>
+          <t>Almirante Brown -1</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1458,7 +1458,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0xfa00d2f0c7b5053ee336b303a0e7ad9cec0b8d539367773b7efee5c86cb2b59d</t>
+          <t>0xa6a338c64f062bfd589e8d5d9cea45a27c9e64065f71f800e5966f81ce53c556</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1488,7 +1488,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1786213843</t>
+          <t>1786214209</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1498,7 +1498,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>48.252149</t>
+          <t>6.295082</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1515,7 +1515,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0xc51052f8e449b4d56cc87b697bfc8eb0d3a88ae218dee1da3d725fa94163bc75</t>
+          <t>0xf65c55196eeb0d21e7e3866ad26f8c3f2fee2aef273ddde5423e31fb40a51469</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1523,28 +1523,36 @@
           <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr"/>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>77.29513</t>
+          <t>121.81</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.2588</t>
+          <t>1.4363</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Almirante Brown</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
           <t>Primera Nacional</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Primera Nacional</t>
-        </is>
-      </c>
       <c r="I11" t="inlineStr">
         <is>
           <t>Almirante Brown vs Ciudad Bolivar</t>
@@ -1562,7 +1570,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0xaa5316c6f6544d74142ad6db34a3745918f237ffb1a657e000693947e81b65d6</t>
+          <t>0x63a8bf73c1084ef223fdd1096dccd16232e7a455fad77f7f0891be1588ebeb88</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1592,7 +1600,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1786212849</t>
+          <t>1786213844</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1602,7 +1610,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>298.72514</t>
+          <t>279.22063</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1619,7 +1627,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0x0aeb4fe40f7d734cf244c144e6c064568b40b222193c9f93c641d1b31af3752e</t>
+          <t>0x1bb20a2bf22e4fe06b44c06b9c2caa21f3f2a7c9d0cce1a2346f79e76022cd1f</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1627,28 +1635,36 @@
           <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr"/>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>16.89162</t>
+          <t>21.05</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.2588</t>
+          <t>1.4363</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
+          <t>Asian Handicap (-0.5)</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Almirante Brown -0.5</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
           <t>Primera Nacional</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Primera Nacional</t>
-        </is>
-      </c>
       <c r="I12" t="inlineStr">
         <is>
           <t>Almirante Brown vs Ciudad Bolivar</t>
@@ -1666,7 +1682,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>0xaa5316c6f6544d74142ad6db34a3745918f237ffb1a657e000693947e81b65d6</t>
+          <t>0xfa00d2f0c7b5053ee336b303a0e7ad9cec0b8d539367773b7efee5c86cb2b59d</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1696,7 +1712,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1786212805</t>
+          <t>1786213843</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -1706,7 +1722,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>65.281623</t>
+          <t>48.252149</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1723,7 +1739,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0x383b895a5fe529a887369a0f113c516fdc7f6125d54381acf9695997ef22d039</t>
+          <t>0xc51052f8e449b4d56cc87b697bfc8eb0d3a88ae218dee1da3d725fa94163bc75</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1731,19 +1747,15 @@
           <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>11.26905</t>
+          <t>77.29513</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.745</t>
+          <t>1.2588</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1751,26 +1763,22 @@
           <t>Primera Nacional</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Primera Nacional</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Almirante Brown vs Ciudad Bolivar</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
         <is>
           <t>Almirante Brown</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Primera Nacional</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>Almirante Brown vs Ciudad Bolivar</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>Almirante Brown</t>
-        </is>
-      </c>
       <c r="K13" t="inlineStr">
         <is>
           <t>Ciudad Bolivar</t>
@@ -1808,7 +1816,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1786211779</t>
+          <t>1786212849</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1818,7 +1826,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>15.126242</t>
+          <t>298.72514</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1835,27 +1843,23 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0xcfb6add6f8610a64ffc187beb9e16bf2bacb27b54a0f0aaefa6bfb437239b893</t>
+          <t>0x0aeb4fe40f7d734cf244c144e6c064568b40b222193c9f93c641d1b31af3752e</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>24.89998</t>
+          <t>16.89162</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1.745</t>
+          <t>1.2588</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1863,26 +1867,22 @@
           <t>Primera Nacional</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Primera Nacional</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Almirante Brown vs Ciudad Bolivar</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
         <is>
           <t>Almirante Brown</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Primera Nacional</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>Almirante Brown vs Ciudad Bolivar</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>Almirante Brown</t>
-        </is>
-      </c>
       <c r="K14" t="inlineStr">
         <is>
           <t>Ciudad Bolivar</t>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1786211777</t>
+          <t>1786212805</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -1930,7 +1930,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>33.422792</t>
+          <t>65.281623</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -1947,12 +1947,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0xd41652604437a4e92e0d78b653d4d49d8dedd2e153d1340dad89b9b93e182a48</t>
+          <t>0x383b895a5fe529a887369a0f113c516fdc7f6125d54381acf9695997ef22d039</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0xf4a8B27C9a13e298D65b5Cc072d252816B799C81</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1962,22 +1962,22 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>11.26905</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1.4163</t>
+          <t>1.745</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Primera Nacional</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Atl. Rafaela</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1987,27 +1987,27 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Atl. Rafaela vs Chacarita Juniors</t>
+          <t>Almirante Brown vs Ciudad Bolivar</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Atl. Rafaela</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Ciudad Bolivar</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>0xe738e9ba05492fab73eaaf6da211b84caadc72b08b26f1cd30fa8737e283bb44</t>
+          <t>0xaa5316c6f6544d74142ad6db34a3745918f237ffb1a657e000693947e81b65d6</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>L19683450</t>
+          <t>L19683447</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -2032,17 +2032,17 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>1786211028</t>
+          <t>1786211779</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>1786215600</t>
+          <t>1786212000</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2.402402</t>
+          <t>15.126242</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2059,7 +2059,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0x562fd7c6419c807ed04d3cacac95f861805f96704bd535e265399fb9d2c2b609</t>
+          <t>0xcfb6add6f8610a64ffc187beb9e16bf2bacb27b54a0f0aaefa6bfb437239b893</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2067,23 +2067,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr"/>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>5.32</t>
+          <t>24.89998</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1.405</t>
+          <t>1.745</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr"/>
+          <t>Primera Nacional</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Almirante Brown</t>
+        </is>
+      </c>
       <c r="H16" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -2091,27 +2099,27 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Estudiantes de Caseros vs Deportivo Madryn</t>
+          <t>Almirante Brown vs Ciudad Bolivar</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Estudiantes de Caseros</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Ciudad Bolivar</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>0xd61509e26f8645bb9780672f942c72c4b7dab577c2a01f04e1e09bce9b828765</t>
+          <t>0xaa5316c6f6544d74142ad6db34a3745918f237ffb1a657e000693947e81b65d6</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>L19683453</t>
+          <t>L19683447</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -2136,7 +2144,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1786210845</t>
+          <t>1786211777</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2146,7 +2154,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>13.135802</t>
+          <t>33.422792</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2163,7 +2171,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0x0bb7a6822220bf40d7b279f99a54f46025f393ba95bb38b6d6dc98192886b3ed</t>
+          <t>0xd41652604437a4e92e0d78b653d4d49d8dedd2e153d1340dad89b9b93e182a48</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2178,12 +2186,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>0.99999</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.5513</t>
+          <t>1.4163</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -2193,7 +2201,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Atl. Rafaela</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2203,27 +2211,27 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Agropecuario vs Atletico Guemes</t>
+          <t>Atl. Rafaela vs Chacarita Juniors</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Atl. Rafaela</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Atletico Guemes</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>0xae66c7fab3c9c76fbc29d9e9778ef4845d8a6b8d092cff34320f100020113c49</t>
+          <t>0xe738e9ba05492fab73eaaf6da211b84caadc72b08b26f1cd30fa8737e283bb44</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>L19683451</t>
+          <t>L19683450</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -2248,17 +2256,17 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>1786205982</t>
+          <t>1786211028</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>1786212000</t>
+          <t>1786215600</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>1.814041</t>
+          <t>2.402402</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2275,39 +2283,31 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0xe17b2546f4b90c8647ba975c279e39dec1fda5a003adfb8a2b39bb12a3519b10</t>
+          <t>0x562fd7c6419c807ed04d3cacac95f861805f96704bd535e265399fb9d2c2b609</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0xf4a8B27C9a13e298D65b5Cc072d252816B799C81</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5.32</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.3613</t>
+          <t>1.405</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -2315,27 +2315,27 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Almirante Brown vs Ciudad Bolivar</t>
+          <t>Estudiantes de Caseros vs Deportivo Madryn</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Estudiantes de Caseros</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Ciudad Bolivar</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>0xd5906ce08d61f7c5ee45fcebd2c8baeed5558387398ea332817a4b632f439b6d</t>
+          <t>0xd61509e26f8645bb9780672f942c72c4b7dab577c2a01f04e1e09bce9b828765</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>L19683447</t>
+          <t>L19683453</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -2360,7 +2360,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>1786205963</t>
+          <t>1786210845</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2370,7 +2370,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2.768166</t>
+          <t>13.135802</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2387,7 +2387,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0xcfe218822e89cbef5841f3045f551cc65acf353d8e240f943e2b61c54ea79a68</t>
+          <t>0x0bb7a6822220bf40d7b279f99a54f46025f393ba95bb38b6d6dc98192886b3ed</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2402,12 +2402,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0.99999</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1.3337</t>
+          <t>1.5513</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -2417,7 +2417,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tie</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2427,27 +2427,27 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Estudiantes de Caseros vs Deportivo Madryn</t>
+          <t>Agropecuario vs Atletico Guemes</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Estudiantes de Caseros</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Atletico Guemes</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>0xf238b96ec9e2421db79973de945f1fc0c3f8bb99c31cda32d011ebaabfd2db86</t>
+          <t>0xae66c7fab3c9c76fbc29d9e9778ef4845d8a6b8d092cff34320f100020113c49</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>L19683453</t>
+          <t>L19683451</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -2472,7 +2472,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>1786205938</t>
+          <t>1786205982</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -2482,7 +2482,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2.996255</t>
+          <t>1.814041</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2499,31 +2499,39 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0x1b9fcb29010a212f74af57040114154e78748f06a4d826be4397ddadb45ac31b</t>
+          <t>0xe17b2546f4b90c8647ba975c279e39dec1fda5a003adfb8a2b39bb12a3519b10</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr"/>
+          <t>0xf4a8B27C9a13e298D65b5Cc072d252816B799C81</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>21.69</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.4512</t>
+          <t>1.3613</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H20" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -2546,7 +2554,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0xbbcaa253cd967fbf933ff0d87a6f9744cafec0ed59dad5f1f76332aab01a3fa5</t>
+          <t>0xd5906ce08d61f7c5ee45fcebd2c8baeed5558387398ea332817a4b632f439b6d</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -2576,7 +2584,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>1786190525</t>
+          <t>1786205963</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -2586,7 +2594,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>48.066482</t>
+          <t>2.768166</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2603,31 +2611,39 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0x3177792dd6a7185e37ae06612104cf5a35d137d7f535a889a83a7e9b7c174506</t>
+          <t>0xcfe218822e89cbef5841f3045f551cc65acf353d8e240f943e2b61c54ea79a68</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr"/>
+          <t>0xf4a8B27C9a13e298D65b5Cc072d252816B799C81</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>18.35495</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1.4963</t>
+          <t>1.3337</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H21" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -2635,27 +2651,27 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Almirante Brown vs Ciudad Bolivar</t>
+          <t>Estudiantes de Caseros vs Deportivo Madryn</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Estudiantes de Caseros</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Ciudad Bolivar</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0xbbcaa253cd967fbf933ff0d87a6f9744cafec0ed59dad5f1f76332aab01a3fa5</t>
+          <t>0xf238b96ec9e2421db79973de945f1fc0c3f8bb99c31cda32d011ebaabfd2db86</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>L19683447</t>
+          <t>L19683453</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -2680,7 +2696,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>1786190491</t>
+          <t>1786205938</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -2690,7 +2706,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>36.987305</t>
+          <t>2.996255</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -2707,27 +2723,23 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0x54ed4ee2a6ebdab49498137f1accea542ead806f21430a0a771cc4872a044e43</t>
+          <t>0x1b9fcb29010a212f74af57040114154e78748f06a4d826be4397ddadb45ac31b</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
-          <t>20.10741</t>
+          <t>21.69</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1.5437</t>
+          <t>1.4512</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -2735,11 +2747,7 @@
           <t>Under/Over (1.5)</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>Over 1.5</t>
-        </is>
-      </c>
+      <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -2792,7 +2800,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>1786190485</t>
+          <t>1786190525</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -2802,7 +2810,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>36.979145</t>
+          <t>48.066482</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -2819,23 +2827,23 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0x544fe5c906328d009917b591611ff3438cef85f8b42d9f67732cbbd5eabbb8dd</t>
+          <t>0x3177792dd6a7185e37ae06612104cf5a35d137d7f535a889a83a7e9b7c174506</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>21.69</t>
+          <t>18.35495</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1.4512</t>
+          <t>1.4963</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -2896,7 +2904,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>1786190485</t>
+          <t>1786190491</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -2906,7 +2914,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>48.066482</t>
+          <t>36.987305</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -2923,23 +2931,27 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0xb2f3ea804e1760a01d3a93678f0e2119f1ea2a9db0dc4711a06cc7bcba42b0c2</t>
+          <t>0x54ed4ee2a6ebdab49498137f1accea542ead806f21430a0a771cc4872a044e43</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr"/>
+          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>17.47</t>
+          <t>20.10741</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1.405</t>
+          <t>1.5437</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -2947,7 +2959,11 @@
           <t>Under/Over (1.5)</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Over 1.5</t>
+        </is>
+      </c>
       <c r="H24" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -2955,27 +2971,27 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Estudiantes de Caseros vs Deportivo Madryn</t>
+          <t>Almirante Brown vs Ciudad Bolivar</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Estudiantes de Caseros</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Ciudad Bolivar</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0xd61509e26f8645bb9780672f942c72c4b7dab577c2a01f04e1e09bce9b828765</t>
+          <t>0xbbcaa253cd967fbf933ff0d87a6f9744cafec0ed59dad5f1f76332aab01a3fa5</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>L19683453</t>
+          <t>L19683447</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -3000,7 +3016,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>1786190461</t>
+          <t>1786190485</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -3010,7 +3026,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>43.135802</t>
+          <t>36.979145</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -3027,7 +3043,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0xa7eafbb77d425fc2347b4ee3e4f4e1b85f6d0f81420605db76ebfeeaa793a428</t>
+          <t>0x544fe5c906328d009917b591611ff3438cef85f8b42d9f67732cbbd5eabbb8dd</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3104,7 +3120,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>1786190458</t>
+          <t>1786190485</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
@@ -3131,110 +3147,318 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>0xb2f3ea804e1760a01d3a93678f0e2119f1ea2a9db0dc4711a06cc7bcba42b0c2</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>17.47</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>1.405</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Primera Nacional</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Estudiantes de Caseros vs Deportivo Madryn</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Estudiantes de Caseros</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Deportivo Madryn</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>0xd61509e26f8645bb9780672f942c72c4b7dab577c2a01f04e1e09bce9b828765</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>L19683453</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>1786190461</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>1786212000</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>43.135802</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>0xa7eafbb77d425fc2347b4ee3e4f4e1b85f6d0f81420605db76ebfeeaa793a428</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>21.69</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>1.4512</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Primera Nacional</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Almirante Brown vs Ciudad Bolivar</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Almirante Brown</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Ciudad Bolivar</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>0xbbcaa253cd967fbf933ff0d87a6f9744cafec0ed59dad5f1f76332aab01a3fa5</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>L19683447</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>1786190458</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>1786212000</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>48.066482</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
           <t>0x5c5b512ea725fac30531bf5fe91f34f3ccc0eeff23890c18f25c3f329007c589</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
         <is>
           <t>1.3638</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="F28" t="inlineStr">
         <is>
           <t>1X2</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="G28" t="inlineStr">
         <is>
           <t>Tie</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="H28" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
+      <c r="I28" t="inlineStr">
         <is>
           <t>Almirante Brown vs Ciudad Bolivar</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr">
+      <c r="J28" t="inlineStr">
         <is>
           <t>Almirante Brown</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr">
+      <c r="K28" t="inlineStr">
         <is>
           <t>Ciudad Bolivar</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr">
+      <c r="L28" t="inlineStr">
         <is>
           <t>0xd5906ce08d61f7c5ee45fcebd2c8baeed5558387398ea332817a4b632f439b6d</t>
         </is>
       </c>
-      <c r="M26" t="inlineStr">
+      <c r="M28" t="inlineStr">
         <is>
           <t>L19683447</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P26" t="inlineStr">
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R26" t="inlineStr">
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
         <is>
           <t>1786125660</t>
         </is>
       </c>
-      <c r="S26" t="inlineStr">
+      <c r="S28" t="inlineStr">
         <is>
           <t>1786212000</t>
         </is>
       </c>
-      <c r="T26" t="inlineStr">
+      <c r="T28" t="inlineStr">
         <is>
           <t>2.749141</t>
         </is>
       </c>
-      <c r="U26" t="inlineStr">
+      <c r="U28" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V26" t="inlineStr">
+      <c r="V28" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/Primera Nacional/trades.xlsx
+++ b/data/sxbet/ligas/Primera Nacional/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V28"/>
+  <dimension ref="A1:V29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,12 +531,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0x4e811c319e5e3a1fc1968ce0f31b4c15eb7222daa616252d99f9abc611408746</t>
+          <t>0x2121e08c4ea1fe2d49a3bb388fba9e232ef9c06335c04e5eae0bf7766975512a</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0x155C76202e45BE70c50bfeD7eAeA3B98e7716Ff7</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -546,12 +546,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>30.06</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.2925</t>
+          <t>1.6262</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -561,7 +561,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tie</t>
+          <t>Colon de Santa Fe</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -586,7 +586,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0x2e49527408facf21253a0a1eafe51280b82e4c31919e91a396332f19ec366401</t>
+          <t>0x1a11ec80edeaae24566c4f4f891cc2afc56b377b24997a6e8ee533eeaaad5c92</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -616,7 +616,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1786243741</t>
+          <t>1786253941</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -626,7 +626,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>3.418803</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -643,7 +643,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0xb8631aeb398192a03386505542f05fa15e34db501204baa8745a4d4b5c1651b7</t>
+          <t>0x4e811c319e5e3a1fc1968ce0f31b4c15eb7222daa616252d99f9abc611408746</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -658,12 +658,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.99999</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.6538</t>
+          <t>1.2925</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -673,7 +673,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Deportivo Moron</t>
+          <t>Tie</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -683,27 +683,27 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Deportivo Moron vs Acassuso</t>
+          <t>Colon de Santa Fe vs San Telmo</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Deportivo Moron</t>
+          <t>Colon de Santa Fe</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0x7514a255ce41be3c5db9f8849ba04e78dab80f02d1fe78c2aae82bbc843a9745</t>
+          <t>0x2e49527408facf21253a0a1eafe51280b82e4c31919e91a396332f19ec366401</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>L19683452</t>
+          <t>L19683494</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -728,17 +728,17 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1786243225</t>
+          <t>1786243741</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>1786298400</t>
+          <t>1786300200</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1.529621</t>
+          <t>3.418803</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -755,31 +755,39 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0xd3b94d194e43cc84f0a1b82723594ea6689a6aa2a4a7dccbc8a3d19fc321e49b</t>
+          <t>0xb8631aeb398192a03386505542f05fa15e34db501204baa8745a4d4b5c1651b7</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
+          <t>0x155C76202e45BE70c50bfeD7eAeA3B98e7716Ff7</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0.99999</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.5238</t>
+          <t>1.6538</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Deportivo Moron</t>
+        </is>
+      </c>
       <c r="H4" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -802,7 +810,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0x108eaba0441fb45ec8e0073e945ae0ac1e138c933e4f2839816cd3198d7dd4d2</t>
+          <t>0x7514a255ce41be3c5db9f8849ba04e78dab80f02d1fe78c2aae82bbc843a9745</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -832,7 +840,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1786225000</t>
+          <t>1786243225</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -842,7 +850,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1.909308</t>
+          <t>1.529621</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -859,7 +867,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0x86f4b24298f4c19f9f856cb19af2a260f24dc2d391f252248469436057ea1d1a</t>
+          <t>0xd3b94d194e43cc84f0a1b82723594ea6689a6aa2a4a7dccbc8a3d19fc321e49b</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -867,11 +875,7 @@
           <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
           <t>1</t>
@@ -879,19 +883,15 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.5263</t>
+          <t>1.5238</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Deportivo Moron -1</t>
-        </is>
-      </c>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -914,7 +914,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0xb61b063252c01d0525ae633a0276dc1830eabd418482fddec925fcbd602a2a75</t>
+          <t>0x108eaba0441fb45ec8e0073e945ae0ac1e138c933e4f2839816cd3198d7dd4d2</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -944,7 +944,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1786220171</t>
+          <t>1786225000</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1.900238</t>
+          <t>1.909308</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -971,12 +971,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0x0a5de930b5a6b8aca1699b666034af3891a3aa920021791d6d13e0297fb7903f</t>
+          <t>0x86f4b24298f4c19f9f856cb19af2a260f24dc2d391f252248469436057ea1d1a</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0x4a09916b1325Eed50eE8973B13742a205B0B7c7E</t>
+          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -986,12 +986,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>49.99999</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.6175</t>
+          <t>1.5263</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1001,7 +1001,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Almirante Brown -1</t>
+          <t>Deportivo Moron -1</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1011,27 +1011,27 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Almirante Brown vs Ciudad Bolivar</t>
+          <t>Deportivo Moron vs Acassuso</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Deportivo Moron</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Ciudad Bolivar</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0xa6a338c64f062bfd589e8d5d9cea45a27c9e64065f71f800e5966f81ce53c556</t>
+          <t>0xb61b063252c01d0525ae633a0276dc1830eabd418482fddec925fcbd602a2a75</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>L19683447</t>
+          <t>L19683452</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1056,17 +1056,17 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1786218515</t>
+          <t>1786220171</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>1786212000</t>
+          <t>1786298400</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>80.971644</t>
+          <t>1.900238</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1083,23 +1083,27 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0x17d5a08f8fa305f31f27442393c64f497dd3893417da6e76c321c4c2a187320d</t>
+          <t>0x0a5de930b5a6b8aca1699b666034af3891a3aa920021791d6d13e0297fb7903f</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr"/>
+          <t>0x4a09916b1325Eed50eE8973B13742a205B0B7c7E</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>49.18897</t>
+          <t>49.99999</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.4737</t>
+          <t>1.6175</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1107,7 +1111,11 @@
           <t>Asian Handicap (-1)</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Almirante Brown -1</t>
+        </is>
+      </c>
       <c r="H7" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -1160,7 +1168,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1786218084</t>
+          <t>1786218515</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1170,7 +1178,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>103.82896</t>
+          <t>80.971644</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1187,28 +1195,28 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0x56975f372357be259365cb7d2929c88d4fae157eea7a71d53d57cb234834f2ca</t>
+          <t>0x17d5a08f8fa305f31f27442393c64f497dd3893417da6e76c321c4c2a187320d</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>49.18897</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.4812</t>
+          <t>1.4737</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G8" t="inlineStr"/>
@@ -1219,27 +1227,27 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Club Atletico Mitre de Santiago del Estero vs Defensores de Belgrano Buenos Aires</t>
+          <t>Almirante Brown vs Ciudad Bolivar</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Club Atletico Mitre de Santiago del Estero</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano Buenos Aires</t>
+          <t>Ciudad Bolivar</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0xa8ade64a3adb0ea38de67a61105ef31beb490d5a7287715b76ae124536d359cc</t>
+          <t>0xa6a338c64f062bfd589e8d5d9cea45a27c9e64065f71f800e5966f81ce53c556</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>L19683493</t>
+          <t>L19683447</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1264,17 +1272,17 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1786215674</t>
+          <t>1786218084</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>1786302000</t>
+          <t>1786212000</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2.077922</t>
+          <t>103.82896</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1291,7 +1299,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0xff53df1f3446908699196d44fcdb8b39c1bd15c7ed519f0d730e55a51a6eb38f</t>
+          <t>0x56975f372357be259365cb7d2929c88d4fae157eea7a71d53d57cb234834f2ca</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1299,11 +1307,7 @@
           <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
           <t>1</t>
@@ -1311,19 +1315,15 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.3713</t>
+          <t>1.4812</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Almirante Brown</t>
-        </is>
-      </c>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -1331,27 +1331,27 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Almirante Brown vs Ciudad Bolivar</t>
+          <t>Club Atletico Mitre de Santiago del Estero vs Defensores de Belgrano Buenos Aires</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Club Atletico Mitre de Santiago del Estero</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Ciudad Bolivar</t>
+          <t>Defensores de Belgrano Buenos Aires</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0x63a8bf73c1084ef223fdd1096dccd16232e7a455fad77f7f0891be1588ebeb88</t>
+          <t>0xa8ade64a3adb0ea38de67a61105ef31beb490d5a7287715b76ae124536d359cc</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>L19683447</t>
+          <t>L19683493</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1376,17 +1376,17 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1786215673</t>
+          <t>1786215674</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>1786212000</t>
+          <t>1786302000</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2.693603</t>
+          <t>2.077922</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1403,12 +1403,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0x249d52552e7acb9f472d2a4c48ab754622ba572903281739a3e10b4d509dccb0</t>
+          <t>0xff53df1f3446908699196d44fcdb8b39c1bd15c7ed519f0d730e55a51a6eb38f</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1418,22 +1418,22 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.2288</t>
+          <t>1.3713</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Almirante Brown -1</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1458,7 +1458,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0xa6a338c64f062bfd589e8d5d9cea45a27c9e64065f71f800e5966f81ce53c556</t>
+          <t>0x63a8bf73c1084ef223fdd1096dccd16232e7a455fad77f7f0891be1588ebeb88</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1488,7 +1488,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1786214209</t>
+          <t>1786215673</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1498,7 +1498,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>6.295082</t>
+          <t>2.693603</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1515,12 +1515,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0xf65c55196eeb0d21e7e3866ad26f8c3f2fee2aef273ddde5423e31fb40a51469</t>
+          <t>0x249d52552e7acb9f472d2a4c48ab754622ba572903281739a3e10b4d509dccb0</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1530,39 +1530,39 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>121.81</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.4363</t>
+          <t>1.2288</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
+          <t>Almirante Brown -1</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Primera Nacional</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Almirante Brown vs Ciudad Bolivar</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
           <t>Almirante Brown</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Primera Nacional</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>Almirante Brown vs Ciudad Bolivar</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>Almirante Brown</t>
-        </is>
-      </c>
       <c r="K11" t="inlineStr">
         <is>
           <t>Ciudad Bolivar</t>
@@ -1570,7 +1570,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0x63a8bf73c1084ef223fdd1096dccd16232e7a455fad77f7f0891be1588ebeb88</t>
+          <t>0xa6a338c64f062bfd589e8d5d9cea45a27c9e64065f71f800e5966f81ce53c556</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1600,7 +1600,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1786213844</t>
+          <t>1786214209</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1610,7 +1610,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>279.22063</t>
+          <t>6.295082</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1627,7 +1627,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0x1bb20a2bf22e4fe06b44c06b9c2caa21f3f2a7c9d0cce1a2346f79e76022cd1f</t>
+          <t>0xf65c55196eeb0d21e7e3866ad26f8c3f2fee2aef273ddde5423e31fb40a51469</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1642,7 +1642,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>21.05</t>
+          <t>121.81</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1652,12 +1652,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Almirante Brown -0.5</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1682,7 +1682,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>0xfa00d2f0c7b5053ee336b303a0e7ad9cec0b8d539367773b7efee5c86cb2b59d</t>
+          <t>0x63a8bf73c1084ef223fdd1096dccd16232e7a455fad77f7f0891be1588ebeb88</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1712,7 +1712,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1786213843</t>
+          <t>1786213844</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -1722,7 +1722,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>48.252149</t>
+          <t>279.22063</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1739,7 +1739,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0xc51052f8e449b4d56cc87b697bfc8eb0d3a88ae218dee1da3d725fa94163bc75</t>
+          <t>0x1bb20a2bf22e4fe06b44c06b9c2caa21f3f2a7c9d0cce1a2346f79e76022cd1f</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1747,28 +1747,36 @@
           <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr"/>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>77.29513</t>
+          <t>21.05</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.2588</t>
+          <t>1.4363</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
+          <t>Asian Handicap (-0.5)</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Almirante Brown -0.5</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
           <t>Primera Nacional</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Primera Nacional</t>
-        </is>
-      </c>
       <c r="I13" t="inlineStr">
         <is>
           <t>Almirante Brown vs Ciudad Bolivar</t>
@@ -1786,7 +1794,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>0xaa5316c6f6544d74142ad6db34a3745918f237ffb1a657e000693947e81b65d6</t>
+          <t>0xfa00d2f0c7b5053ee336b303a0e7ad9cec0b8d539367773b7efee5c86cb2b59d</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1816,7 +1824,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1786212849</t>
+          <t>1786213843</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1826,7 +1834,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>298.72514</t>
+          <t>48.252149</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1843,7 +1851,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0x0aeb4fe40f7d734cf244c144e6c064568b40b222193c9f93c641d1b31af3752e</t>
+          <t>0xc51052f8e449b4d56cc87b697bfc8eb0d3a88ae218dee1da3d725fa94163bc75</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1854,7 +1862,7 @@
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>16.89162</t>
+          <t>77.29513</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1920,7 +1928,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1786212805</t>
+          <t>1786212849</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -1930,7 +1938,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>65.281623</t>
+          <t>298.72514</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -1947,7 +1955,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0x383b895a5fe529a887369a0f113c516fdc7f6125d54381acf9695997ef22d039</t>
+          <t>0x0aeb4fe40f7d734cf244c144e6c064568b40b222193c9f93c641d1b31af3752e</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1955,19 +1963,15 @@
           <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>11.26905</t>
+          <t>16.89162</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1.745</t>
+          <t>1.2588</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1975,26 +1979,22 @@
           <t>Primera Nacional</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Primera Nacional</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Almirante Brown vs Ciudad Bolivar</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
         <is>
           <t>Almirante Brown</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Primera Nacional</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>Almirante Brown vs Ciudad Bolivar</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>Almirante Brown</t>
-        </is>
-      </c>
       <c r="K15" t="inlineStr">
         <is>
           <t>Ciudad Bolivar</t>
@@ -2032,7 +2032,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>1786211779</t>
+          <t>1786212805</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -2042,7 +2042,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>15.126242</t>
+          <t>65.281623</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2059,12 +2059,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0xcfb6add6f8610a64ffc187beb9e16bf2bacb27b54a0f0aaefa6bfb437239b893</t>
+          <t>0x383b895a5fe529a887369a0f113c516fdc7f6125d54381acf9695997ef22d039</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2074,7 +2074,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>24.89998</t>
+          <t>11.26905</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -2144,7 +2144,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1786211777</t>
+          <t>1786211779</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2154,7 +2154,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>33.422792</t>
+          <t>15.126242</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2171,12 +2171,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0xd41652604437a4e92e0d78b653d4d49d8dedd2e153d1340dad89b9b93e182a48</t>
+          <t>0xcfb6add6f8610a64ffc187beb9e16bf2bacb27b54a0f0aaefa6bfb437239b893</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0xf4a8B27C9a13e298D65b5Cc072d252816B799C81</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2186,22 +2186,22 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>24.89998</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.4163</t>
+          <t>1.745</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Primera Nacional</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Atl. Rafaela</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2211,27 +2211,27 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Atl. Rafaela vs Chacarita Juniors</t>
+          <t>Almirante Brown vs Ciudad Bolivar</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Atl. Rafaela</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Ciudad Bolivar</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>0xe738e9ba05492fab73eaaf6da211b84caadc72b08b26f1cd30fa8737e283bb44</t>
+          <t>0xaa5316c6f6544d74142ad6db34a3745918f237ffb1a657e000693947e81b65d6</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>L19683450</t>
+          <t>L19683447</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -2256,17 +2256,17 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>1786211028</t>
+          <t>1786211777</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>1786215600</t>
+          <t>1786212000</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2.402402</t>
+          <t>33.422792</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2283,31 +2283,39 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0x562fd7c6419c807ed04d3cacac95f861805f96704bd535e265399fb9d2c2b609</t>
+          <t>0xd41652604437a4e92e0d78b653d4d49d8dedd2e153d1340dad89b9b93e182a48</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr"/>
+          <t>0xf4a8B27C9a13e298D65b5Cc072d252816B799C81</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>5.32</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.405</t>
+          <t>1.4163</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Atl. Rafaela</t>
+        </is>
+      </c>
       <c r="H18" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -2315,27 +2323,27 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Estudiantes de Caseros vs Deportivo Madryn</t>
+          <t>Atl. Rafaela vs Chacarita Juniors</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Estudiantes de Caseros</t>
+          <t>Atl. Rafaela</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>0xd61509e26f8645bb9780672f942c72c4b7dab577c2a01f04e1e09bce9b828765</t>
+          <t>0xe738e9ba05492fab73eaaf6da211b84caadc72b08b26f1cd30fa8737e283bb44</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>L19683453</t>
+          <t>L19683450</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -2360,17 +2368,17 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>1786210845</t>
+          <t>1786211028</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>1786212000</t>
+          <t>1786215600</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>13.135802</t>
+          <t>2.402402</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2387,39 +2395,31 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0x0bb7a6822220bf40d7b279f99a54f46025f393ba95bb38b6d6dc98192886b3ed</t>
+          <t>0x562fd7c6419c807ed04d3cacac95f861805f96704bd535e265399fb9d2c2b609</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0xf4a8B27C9a13e298D65b5Cc072d252816B799C81</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>0.99999</t>
+          <t>5.32</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1.5513</t>
+          <t>1.405</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>Agropecuario</t>
-        </is>
-      </c>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -2427,27 +2427,27 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Agropecuario vs Atletico Guemes</t>
+          <t>Estudiantes de Caseros vs Deportivo Madryn</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Estudiantes de Caseros</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Atletico Guemes</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>0xae66c7fab3c9c76fbc29d9e9778ef4845d8a6b8d092cff34320f100020113c49</t>
+          <t>0xd61509e26f8645bb9780672f942c72c4b7dab577c2a01f04e1e09bce9b828765</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>L19683451</t>
+          <t>L19683453</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -2472,7 +2472,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>1786205982</t>
+          <t>1786210845</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -2482,7 +2482,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>1.814041</t>
+          <t>13.135802</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2499,7 +2499,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0xe17b2546f4b90c8647ba975c279e39dec1fda5a003adfb8a2b39bb12a3519b10</t>
+          <t>0x0bb7a6822220bf40d7b279f99a54f46025f393ba95bb38b6d6dc98192886b3ed</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2514,12 +2514,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0.99999</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.3613</t>
+          <t>1.5513</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -2529,7 +2529,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tie</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2539,27 +2539,27 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Almirante Brown vs Ciudad Bolivar</t>
+          <t>Agropecuario vs Atletico Guemes</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Ciudad Bolivar</t>
+          <t>Atletico Guemes</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0xd5906ce08d61f7c5ee45fcebd2c8baeed5558387398ea332817a4b632f439b6d</t>
+          <t>0xae66c7fab3c9c76fbc29d9e9778ef4845d8a6b8d092cff34320f100020113c49</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>L19683447</t>
+          <t>L19683451</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -2584,7 +2584,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>1786205963</t>
+          <t>1786205982</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -2594,7 +2594,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2.768166</t>
+          <t>1.814041</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2611,7 +2611,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0xcfe218822e89cbef5841f3045f551cc65acf353d8e240f943e2b61c54ea79a68</t>
+          <t>0xe17b2546f4b90c8647ba975c279e39dec1fda5a003adfb8a2b39bb12a3519b10</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1.3337</t>
+          <t>1.3613</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -2651,27 +2651,27 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Estudiantes de Caseros vs Deportivo Madryn</t>
+          <t>Almirante Brown vs Ciudad Bolivar</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Estudiantes de Caseros</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Ciudad Bolivar</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0xf238b96ec9e2421db79973de945f1fc0c3f8bb99c31cda32d011ebaabfd2db86</t>
+          <t>0xd5906ce08d61f7c5ee45fcebd2c8baeed5558387398ea332817a4b632f439b6d</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>L19683453</t>
+          <t>L19683447</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -2696,7 +2696,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>1786205938</t>
+          <t>1786205963</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -2706,7 +2706,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2.996255</t>
+          <t>2.768166</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -2723,31 +2723,39 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0x1b9fcb29010a212f74af57040114154e78748f06a4d826be4397ddadb45ac31b</t>
+          <t>0xcfe218822e89cbef5841f3045f551cc65acf353d8e240f943e2b61c54ea79a68</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr"/>
+          <t>0xf4a8B27C9a13e298D65b5Cc072d252816B799C81</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>21.69</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1.4512</t>
+          <t>1.3337</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H22" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -2755,27 +2763,27 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Almirante Brown vs Ciudad Bolivar</t>
+          <t>Estudiantes de Caseros vs Deportivo Madryn</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Estudiantes de Caseros</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Ciudad Bolivar</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0xbbcaa253cd967fbf933ff0d87a6f9744cafec0ed59dad5f1f76332aab01a3fa5</t>
+          <t>0xf238b96ec9e2421db79973de945f1fc0c3f8bb99c31cda32d011ebaabfd2db86</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>L19683447</t>
+          <t>L19683453</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -2800,7 +2808,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>1786190525</t>
+          <t>1786205938</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -2810,7 +2818,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>48.066482</t>
+          <t>2.996255</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -2827,23 +2835,23 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0x3177792dd6a7185e37ae06612104cf5a35d137d7f535a889a83a7e9b7c174506</t>
+          <t>0x1b9fcb29010a212f74af57040114154e78748f06a4d826be4397ddadb45ac31b</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>18.35495</t>
+          <t>21.69</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1.4963</t>
+          <t>1.4512</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -2904,7 +2912,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>1786190491</t>
+          <t>1786190525</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -2914,7 +2922,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>36.987305</t>
+          <t>48.066482</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -2931,7 +2939,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0x54ed4ee2a6ebdab49498137f1accea542ead806f21430a0a771cc4872a044e43</t>
+          <t>0x3177792dd6a7185e37ae06612104cf5a35d137d7f535a889a83a7e9b7c174506</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2939,19 +2947,15 @@
           <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
-          <t>20.10741</t>
+          <t>18.35495</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1.5437</t>
+          <t>1.4963</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -2959,11 +2963,7 @@
           <t>Under/Over (1.5)</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>Over 1.5</t>
-        </is>
-      </c>
+      <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -3016,7 +3016,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>1786190485</t>
+          <t>1786190491</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -3026,7 +3026,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>36.979145</t>
+          <t>36.987305</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -3043,23 +3043,27 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0x544fe5c906328d009917b591611ff3438cef85f8b42d9f67732cbbd5eabbb8dd</t>
+          <t>0x54ed4ee2a6ebdab49498137f1accea542ead806f21430a0a771cc4872a044e43</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr"/>
+          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>21.69</t>
+          <t>20.10741</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1.4512</t>
+          <t>1.5437</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -3067,7 +3071,11 @@
           <t>Under/Over (1.5)</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Over 1.5</t>
+        </is>
+      </c>
       <c r="H25" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -3130,7 +3138,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>48.066482</t>
+          <t>36.979145</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3147,7 +3155,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0xb2f3ea804e1760a01d3a93678f0e2119f1ea2a9db0dc4711a06cc7bcba42b0c2</t>
+          <t>0x544fe5c906328d009917b591611ff3438cef85f8b42d9f67732cbbd5eabbb8dd</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3158,12 +3166,12 @@
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
-          <t>17.47</t>
+          <t>21.69</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1.405</t>
+          <t>1.4512</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -3179,27 +3187,27 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Estudiantes de Caseros vs Deportivo Madryn</t>
+          <t>Almirante Brown vs Ciudad Bolivar</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Estudiantes de Caseros</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Ciudad Bolivar</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>0xd61509e26f8645bb9780672f942c72c4b7dab577c2a01f04e1e09bce9b828765</t>
+          <t>0xbbcaa253cd967fbf933ff0d87a6f9744cafec0ed59dad5f1f76332aab01a3fa5</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>L19683453</t>
+          <t>L19683447</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -3224,7 +3232,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>1786190461</t>
+          <t>1786190485</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -3234,7 +3242,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>43.135802</t>
+          <t>48.066482</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -3251,7 +3259,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0xa7eafbb77d425fc2347b4ee3e4f4e1b85f6d0f81420605db76ebfeeaa793a428</t>
+          <t>0xb2f3ea804e1760a01d3a93678f0e2119f1ea2a9db0dc4711a06cc7bcba42b0c2</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3262,12 +3270,12 @@
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t>21.69</t>
+          <t>17.47</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1.4512</t>
+          <t>1.405</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -3283,27 +3291,27 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Almirante Brown vs Ciudad Bolivar</t>
+          <t>Estudiantes de Caseros vs Deportivo Madryn</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Estudiantes de Caseros</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>Ciudad Bolivar</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>0xbbcaa253cd967fbf933ff0d87a6f9744cafec0ed59dad5f1f76332aab01a3fa5</t>
+          <t>0xd61509e26f8645bb9780672f942c72c4b7dab577c2a01f04e1e09bce9b828765</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>L19683447</t>
+          <t>L19683453</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -3328,7 +3336,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>1786190458</t>
+          <t>1786190461</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -3338,7 +3346,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>48.066482</t>
+          <t>43.135802</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -3355,110 +3363,214 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>0xa7eafbb77d425fc2347b4ee3e4f4e1b85f6d0f81420605db76ebfeeaa793a428</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>21.69</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>1.4512</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Primera Nacional</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Almirante Brown vs Ciudad Bolivar</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Almirante Brown</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Ciudad Bolivar</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>0xbbcaa253cd967fbf933ff0d87a6f9744cafec0ed59dad5f1f76332aab01a3fa5</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>L19683447</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>1786190458</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>1786212000</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>48.066482</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
           <t>0x5c5b512ea725fac30531bf5fe91f34f3ccc0eeff23890c18f25c3f329007c589</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
         <is>
           <t>1.3638</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="F29" t="inlineStr">
         <is>
           <t>1X2</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="G29" t="inlineStr">
         <is>
           <t>Tie</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
+      <c r="H29" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
+      <c r="I29" t="inlineStr">
         <is>
           <t>Almirante Brown vs Ciudad Bolivar</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr">
+      <c r="J29" t="inlineStr">
         <is>
           <t>Almirante Brown</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr">
+      <c r="K29" t="inlineStr">
         <is>
           <t>Ciudad Bolivar</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr">
+      <c r="L29" t="inlineStr">
         <is>
           <t>0xd5906ce08d61f7c5ee45fcebd2c8baeed5558387398ea332817a4b632f439b6d</t>
         </is>
       </c>
-      <c r="M28" t="inlineStr">
+      <c r="M29" t="inlineStr">
         <is>
           <t>L19683447</t>
         </is>
       </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O28" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P28" t="inlineStr">
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R28" t="inlineStr">
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
         <is>
           <t>1786125660</t>
         </is>
       </c>
-      <c r="S28" t="inlineStr">
+      <c r="S29" t="inlineStr">
         <is>
           <t>1786212000</t>
         </is>
       </c>
-      <c r="T28" t="inlineStr">
+      <c r="T29" t="inlineStr">
         <is>
           <t>2.749141</t>
         </is>
       </c>
-      <c r="U28" t="inlineStr">
+      <c r="U29" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V28" t="inlineStr">
+      <c r="V29" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/Primera Nacional/trades.xlsx
+++ b/data/sxbet/ligas/Primera Nacional/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V29"/>
+  <dimension ref="A1:V30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,12 +531,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0x2121e08c4ea1fe2d49a3bb388fba9e232ef9c06335c04e5eae0bf7766975512a</t>
+          <t>0x0847a2541998eecfe02d138796b14ef3d6719061787498f4888f6e14c0d196ff</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0xf068eF8DF8f47185D02d59Bb33d9eC7A057a571E</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -546,12 +546,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>30.06</t>
+          <t>38.54</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.6262</t>
+          <t>1.125</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -561,7 +561,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Colon de Santa Fe</t>
+          <t>Club Almagro</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -571,27 +571,27 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Colon de Santa Fe vs San Telmo</t>
+          <t>Quilmes vs Club Almagro</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Colon de Santa Fe</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Club Almagro</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0x1a11ec80edeaae24566c4f4f891cc2afc56b377b24997a6e8ee533eeaaad5c92</t>
+          <t>0x03ed0858b563c1becf38b195ad94b1a84eb89c3ca8ca10b1a34220bff142f9b2</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>L19683494</t>
+          <t>L19683499</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -616,17 +616,17 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1786253941</t>
+          <t>1786270828</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>1786300200</t>
+          <t>1786305600</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>48.0</t>
+          <t>308.32</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -643,12 +643,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0x4e811c319e5e3a1fc1968ce0f31b4c15eb7222daa616252d99f9abc611408746</t>
+          <t>0x2121e08c4ea1fe2d49a3bb388fba9e232ef9c06335c04e5eae0bf7766975512a</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0x155C76202e45BE70c50bfeD7eAeA3B98e7716Ff7</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -658,12 +658,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>30.06</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.2925</t>
+          <t>1.6262</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -673,7 +673,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tie</t>
+          <t>Colon de Santa Fe</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -698,7 +698,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0x2e49527408facf21253a0a1eafe51280b82e4c31919e91a396332f19ec366401</t>
+          <t>0x1a11ec80edeaae24566c4f4f891cc2afc56b377b24997a6e8ee533eeaaad5c92</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -728,7 +728,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1786243741</t>
+          <t>1786253941</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -738,7 +738,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>3.418803</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -755,7 +755,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0xb8631aeb398192a03386505542f05fa15e34db501204baa8745a4d4b5c1651b7</t>
+          <t>0x4e811c319e5e3a1fc1968ce0f31b4c15eb7222daa616252d99f9abc611408746</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -770,12 +770,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.99999</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.6538</t>
+          <t>1.2925</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Deportivo Moron</t>
+          <t>Tie</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -795,27 +795,27 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Deportivo Moron vs Acassuso</t>
+          <t>Colon de Santa Fe vs San Telmo</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Deportivo Moron</t>
+          <t>Colon de Santa Fe</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0x7514a255ce41be3c5db9f8849ba04e78dab80f02d1fe78c2aae82bbc843a9745</t>
+          <t>0x2e49527408facf21253a0a1eafe51280b82e4c31919e91a396332f19ec366401</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>L19683452</t>
+          <t>L19683494</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -840,17 +840,17 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1786243225</t>
+          <t>1786243741</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>1786298400</t>
+          <t>1786300200</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1.529621</t>
+          <t>3.418803</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -867,31 +867,39 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0xd3b94d194e43cc84f0a1b82723594ea6689a6aa2a4a7dccbc8a3d19fc321e49b</t>
+          <t>0xb8631aeb398192a03386505542f05fa15e34db501204baa8745a4d4b5c1651b7</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr"/>
+          <t>0x155C76202e45BE70c50bfeD7eAeA3B98e7716Ff7</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0.99999</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.5238</t>
+          <t>1.6538</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Deportivo Moron</t>
+        </is>
+      </c>
       <c r="H5" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -914,7 +922,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0x108eaba0441fb45ec8e0073e945ae0ac1e138c933e4f2839816cd3198d7dd4d2</t>
+          <t>0x7514a255ce41be3c5db9f8849ba04e78dab80f02d1fe78c2aae82bbc843a9745</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -944,7 +952,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1786225000</t>
+          <t>1786243225</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -954,7 +962,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1.909308</t>
+          <t>1.529621</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -971,7 +979,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0x86f4b24298f4c19f9f856cb19af2a260f24dc2d391f252248469436057ea1d1a</t>
+          <t>0xd3b94d194e43cc84f0a1b82723594ea6689a6aa2a4a7dccbc8a3d19fc321e49b</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -979,11 +987,7 @@
           <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
           <t>1</t>
@@ -991,19 +995,15 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.5263</t>
+          <t>1.5238</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Deportivo Moron -1</t>
-        </is>
-      </c>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0xb61b063252c01d0525ae633a0276dc1830eabd418482fddec925fcbd602a2a75</t>
+          <t>0x108eaba0441fb45ec8e0073e945ae0ac1e138c933e4f2839816cd3198d7dd4d2</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1786220171</t>
+          <t>1786225000</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1066,7 +1066,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1.900238</t>
+          <t>1.909308</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1083,12 +1083,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0x0a5de930b5a6b8aca1699b666034af3891a3aa920021791d6d13e0297fb7903f</t>
+          <t>0x86f4b24298f4c19f9f856cb19af2a260f24dc2d391f252248469436057ea1d1a</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0x4a09916b1325Eed50eE8973B13742a205B0B7c7E</t>
+          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1098,12 +1098,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>49.99999</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.6175</t>
+          <t>1.5263</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1113,7 +1113,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Almirante Brown -1</t>
+          <t>Deportivo Moron -1</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1123,27 +1123,27 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Almirante Brown vs Ciudad Bolivar</t>
+          <t>Deportivo Moron vs Acassuso</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Deportivo Moron</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Ciudad Bolivar</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0xa6a338c64f062bfd589e8d5d9cea45a27c9e64065f71f800e5966f81ce53c556</t>
+          <t>0xb61b063252c01d0525ae633a0276dc1830eabd418482fddec925fcbd602a2a75</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>L19683447</t>
+          <t>L19683452</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1168,17 +1168,17 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1786218515</t>
+          <t>1786220171</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>1786212000</t>
+          <t>1786298400</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>80.971644</t>
+          <t>1.900238</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1195,23 +1195,27 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0x17d5a08f8fa305f31f27442393c64f497dd3893417da6e76c321c4c2a187320d</t>
+          <t>0x0a5de930b5a6b8aca1699b666034af3891a3aa920021791d6d13e0297fb7903f</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr"/>
+          <t>0x4a09916b1325Eed50eE8973B13742a205B0B7c7E</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>49.18897</t>
+          <t>49.99999</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.4737</t>
+          <t>1.6175</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1219,7 +1223,11 @@
           <t>Asian Handicap (-1)</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Almirante Brown -1</t>
+        </is>
+      </c>
       <c r="H8" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -1272,7 +1280,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1786218084</t>
+          <t>1786218515</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1282,7 +1290,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>103.82896</t>
+          <t>80.971644</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1299,28 +1307,28 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0x56975f372357be259365cb7d2929c88d4fae157eea7a71d53d57cb234834f2ca</t>
+          <t>0x17d5a08f8fa305f31f27442393c64f497dd3893417da6e76c321c4c2a187320d</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>49.18897</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.4812</t>
+          <t>1.4737</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G9" t="inlineStr"/>
@@ -1331,27 +1339,27 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Club Atletico Mitre de Santiago del Estero vs Defensores de Belgrano Buenos Aires</t>
+          <t>Almirante Brown vs Ciudad Bolivar</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Club Atletico Mitre de Santiago del Estero</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano Buenos Aires</t>
+          <t>Ciudad Bolivar</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0xa8ade64a3adb0ea38de67a61105ef31beb490d5a7287715b76ae124536d359cc</t>
+          <t>0xa6a338c64f062bfd589e8d5d9cea45a27c9e64065f71f800e5966f81ce53c556</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>L19683493</t>
+          <t>L19683447</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1376,17 +1384,17 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1786215674</t>
+          <t>1786218084</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>1786302000</t>
+          <t>1786212000</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2.077922</t>
+          <t>103.82896</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1403,7 +1411,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0xff53df1f3446908699196d44fcdb8b39c1bd15c7ed519f0d730e55a51a6eb38f</t>
+          <t>0x56975f372357be259365cb7d2929c88d4fae157eea7a71d53d57cb234834f2ca</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1411,11 +1419,7 @@
           <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
           <t>1</t>
@@ -1423,19 +1427,15 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.3713</t>
+          <t>1.4812</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Almirante Brown</t>
-        </is>
-      </c>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -1443,27 +1443,27 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Almirante Brown vs Ciudad Bolivar</t>
+          <t>Club Atletico Mitre de Santiago del Estero vs Defensores de Belgrano Buenos Aires</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Club Atletico Mitre de Santiago del Estero</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Ciudad Bolivar</t>
+          <t>Defensores de Belgrano Buenos Aires</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0x63a8bf73c1084ef223fdd1096dccd16232e7a455fad77f7f0891be1588ebeb88</t>
+          <t>0xa8ade64a3adb0ea38de67a61105ef31beb490d5a7287715b76ae124536d359cc</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>L19683447</t>
+          <t>L19683493</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1488,17 +1488,17 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1786215673</t>
+          <t>1786215674</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>1786212000</t>
+          <t>1786302000</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2.693603</t>
+          <t>2.077922</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1515,12 +1515,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0x249d52552e7acb9f472d2a4c48ab754622ba572903281739a3e10b4d509dccb0</t>
+          <t>0xff53df1f3446908699196d44fcdb8b39c1bd15c7ed519f0d730e55a51a6eb38f</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1530,22 +1530,22 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.2288</t>
+          <t>1.3713</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Almirante Brown -1</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1570,7 +1570,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0xa6a338c64f062bfd589e8d5d9cea45a27c9e64065f71f800e5966f81ce53c556</t>
+          <t>0x63a8bf73c1084ef223fdd1096dccd16232e7a455fad77f7f0891be1588ebeb88</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1600,7 +1600,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1786214209</t>
+          <t>1786215673</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1610,7 +1610,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>6.295082</t>
+          <t>2.693603</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1627,12 +1627,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0xf65c55196eeb0d21e7e3866ad26f8c3f2fee2aef273ddde5423e31fb40a51469</t>
+          <t>0x249d52552e7acb9f472d2a4c48ab754622ba572903281739a3e10b4d509dccb0</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1642,39 +1642,39 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>121.81</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.4363</t>
+          <t>1.2288</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
+          <t>Almirante Brown -1</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Primera Nacional</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Almirante Brown vs Ciudad Bolivar</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
           <t>Almirante Brown</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Primera Nacional</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>Almirante Brown vs Ciudad Bolivar</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>Almirante Brown</t>
-        </is>
-      </c>
       <c r="K12" t="inlineStr">
         <is>
           <t>Ciudad Bolivar</t>
@@ -1682,7 +1682,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>0x63a8bf73c1084ef223fdd1096dccd16232e7a455fad77f7f0891be1588ebeb88</t>
+          <t>0xa6a338c64f062bfd589e8d5d9cea45a27c9e64065f71f800e5966f81ce53c556</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1712,7 +1712,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1786213844</t>
+          <t>1786214209</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -1722,7 +1722,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>279.22063</t>
+          <t>6.295082</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1739,7 +1739,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0x1bb20a2bf22e4fe06b44c06b9c2caa21f3f2a7c9d0cce1a2346f79e76022cd1f</t>
+          <t>0xf65c55196eeb0d21e7e3866ad26f8c3f2fee2aef273ddde5423e31fb40a51469</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1754,7 +1754,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>21.05</t>
+          <t>121.81</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1764,12 +1764,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Almirante Brown -0.5</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>0xfa00d2f0c7b5053ee336b303a0e7ad9cec0b8d539367773b7efee5c86cb2b59d</t>
+          <t>0x63a8bf73c1084ef223fdd1096dccd16232e7a455fad77f7f0891be1588ebeb88</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1786213843</t>
+          <t>1786213844</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1834,7 +1834,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>48.252149</t>
+          <t>279.22063</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1851,7 +1851,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0xc51052f8e449b4d56cc87b697bfc8eb0d3a88ae218dee1da3d725fa94163bc75</t>
+          <t>0x1bb20a2bf22e4fe06b44c06b9c2caa21f3f2a7c9d0cce1a2346f79e76022cd1f</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1859,28 +1859,36 @@
           <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr"/>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>77.29513</t>
+          <t>21.05</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1.2588</t>
+          <t>1.4363</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
+          <t>Asian Handicap (-0.5)</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Almirante Brown -0.5</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
           <t>Primera Nacional</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Primera Nacional</t>
-        </is>
-      </c>
       <c r="I14" t="inlineStr">
         <is>
           <t>Almirante Brown vs Ciudad Bolivar</t>
@@ -1898,7 +1906,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>0xaa5316c6f6544d74142ad6db34a3745918f237ffb1a657e000693947e81b65d6</t>
+          <t>0xfa00d2f0c7b5053ee336b303a0e7ad9cec0b8d539367773b7efee5c86cb2b59d</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1928,7 +1936,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1786212849</t>
+          <t>1786213843</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -1938,7 +1946,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>298.72514</t>
+          <t>48.252149</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -1955,7 +1963,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0x0aeb4fe40f7d734cf244c144e6c064568b40b222193c9f93c641d1b31af3752e</t>
+          <t>0xc51052f8e449b4d56cc87b697bfc8eb0d3a88ae218dee1da3d725fa94163bc75</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1966,7 +1974,7 @@
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>16.89162</t>
+          <t>77.29513</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -2032,7 +2040,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>1786212805</t>
+          <t>1786212849</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -2042,7 +2050,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>65.281623</t>
+          <t>298.72514</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2059,7 +2067,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0x383b895a5fe529a887369a0f113c516fdc7f6125d54381acf9695997ef22d039</t>
+          <t>0x0aeb4fe40f7d734cf244c144e6c064568b40b222193c9f93c641d1b31af3752e</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2067,19 +2075,15 @@
           <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>11.26905</t>
+          <t>16.89162</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1.745</t>
+          <t>1.2588</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -2087,26 +2091,22 @@
           <t>Primera Nacional</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Primera Nacional</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Almirante Brown vs Ciudad Bolivar</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
         <is>
           <t>Almirante Brown</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Primera Nacional</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>Almirante Brown vs Ciudad Bolivar</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>Almirante Brown</t>
-        </is>
-      </c>
       <c r="K16" t="inlineStr">
         <is>
           <t>Ciudad Bolivar</t>
@@ -2144,7 +2144,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1786211779</t>
+          <t>1786212805</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2154,7 +2154,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>15.126242</t>
+          <t>65.281623</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2171,12 +2171,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0xcfb6add6f8610a64ffc187beb9e16bf2bacb27b54a0f0aaefa6bfb437239b893</t>
+          <t>0x383b895a5fe529a887369a0f113c516fdc7f6125d54381acf9695997ef22d039</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>24.89998</t>
+          <t>11.26905</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>1786211777</t>
+          <t>1786211779</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -2266,7 +2266,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>33.422792</t>
+          <t>15.126242</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2283,12 +2283,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0xd41652604437a4e92e0d78b653d4d49d8dedd2e153d1340dad89b9b93e182a48</t>
+          <t>0xcfb6add6f8610a64ffc187beb9e16bf2bacb27b54a0f0aaefa6bfb437239b893</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0xf4a8B27C9a13e298D65b5Cc072d252816B799C81</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2298,22 +2298,22 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>24.89998</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.4163</t>
+          <t>1.745</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Primera Nacional</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Atl. Rafaela</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2323,27 +2323,27 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Atl. Rafaela vs Chacarita Juniors</t>
+          <t>Almirante Brown vs Ciudad Bolivar</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Atl. Rafaela</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Ciudad Bolivar</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>0xe738e9ba05492fab73eaaf6da211b84caadc72b08b26f1cd30fa8737e283bb44</t>
+          <t>0xaa5316c6f6544d74142ad6db34a3745918f237ffb1a657e000693947e81b65d6</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>L19683450</t>
+          <t>L19683447</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -2368,17 +2368,17 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>1786211028</t>
+          <t>1786211777</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>1786215600</t>
+          <t>1786212000</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2.402402</t>
+          <t>33.422792</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2395,31 +2395,39 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0x562fd7c6419c807ed04d3cacac95f861805f96704bd535e265399fb9d2c2b609</t>
+          <t>0xd41652604437a4e92e0d78b653d4d49d8dedd2e153d1340dad89b9b93e182a48</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr"/>
+          <t>0xf4a8B27C9a13e298D65b5Cc072d252816B799C81</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>5.32</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1.405</t>
+          <t>1.4163</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Atl. Rafaela</t>
+        </is>
+      </c>
       <c r="H19" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -2427,27 +2435,27 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Estudiantes de Caseros vs Deportivo Madryn</t>
+          <t>Atl. Rafaela vs Chacarita Juniors</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Estudiantes de Caseros</t>
+          <t>Atl. Rafaela</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>0xd61509e26f8645bb9780672f942c72c4b7dab577c2a01f04e1e09bce9b828765</t>
+          <t>0xe738e9ba05492fab73eaaf6da211b84caadc72b08b26f1cd30fa8737e283bb44</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>L19683453</t>
+          <t>L19683450</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -2472,17 +2480,17 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>1786210845</t>
+          <t>1786211028</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>1786212000</t>
+          <t>1786215600</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>13.135802</t>
+          <t>2.402402</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2499,39 +2507,31 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0x0bb7a6822220bf40d7b279f99a54f46025f393ba95bb38b6d6dc98192886b3ed</t>
+          <t>0x562fd7c6419c807ed04d3cacac95f861805f96704bd535e265399fb9d2c2b609</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0xf4a8B27C9a13e298D65b5Cc072d252816B799C81</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>0.99999</t>
+          <t>5.32</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.5513</t>
+          <t>1.405</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>Agropecuario</t>
-        </is>
-      </c>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -2539,27 +2539,27 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Agropecuario vs Atletico Guemes</t>
+          <t>Estudiantes de Caseros vs Deportivo Madryn</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Estudiantes de Caseros</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Atletico Guemes</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0xae66c7fab3c9c76fbc29d9e9778ef4845d8a6b8d092cff34320f100020113c49</t>
+          <t>0xd61509e26f8645bb9780672f942c72c4b7dab577c2a01f04e1e09bce9b828765</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>L19683451</t>
+          <t>L19683453</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -2584,7 +2584,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>1786205982</t>
+          <t>1786210845</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -2594,7 +2594,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>1.814041</t>
+          <t>13.135802</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2611,7 +2611,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0xe17b2546f4b90c8647ba975c279e39dec1fda5a003adfb8a2b39bb12a3519b10</t>
+          <t>0x0bb7a6822220bf40d7b279f99a54f46025f393ba95bb38b6d6dc98192886b3ed</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2626,12 +2626,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0.99999</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1.3613</t>
+          <t>1.5513</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -2641,7 +2641,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tie</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2651,27 +2651,27 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Almirante Brown vs Ciudad Bolivar</t>
+          <t>Agropecuario vs Atletico Guemes</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Ciudad Bolivar</t>
+          <t>Atletico Guemes</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0xd5906ce08d61f7c5ee45fcebd2c8baeed5558387398ea332817a4b632f439b6d</t>
+          <t>0xae66c7fab3c9c76fbc29d9e9778ef4845d8a6b8d092cff34320f100020113c49</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>L19683447</t>
+          <t>L19683451</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -2696,7 +2696,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>1786205963</t>
+          <t>1786205982</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -2706,7 +2706,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2.768166</t>
+          <t>1.814041</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -2723,7 +2723,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0xcfe218822e89cbef5841f3045f551cc65acf353d8e240f943e2b61c54ea79a68</t>
+          <t>0xe17b2546f4b90c8647ba975c279e39dec1fda5a003adfb8a2b39bb12a3519b10</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2743,7 +2743,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1.3337</t>
+          <t>1.3613</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -2763,27 +2763,27 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Estudiantes de Caseros vs Deportivo Madryn</t>
+          <t>Almirante Brown vs Ciudad Bolivar</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Estudiantes de Caseros</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Ciudad Bolivar</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0xf238b96ec9e2421db79973de945f1fc0c3f8bb99c31cda32d011ebaabfd2db86</t>
+          <t>0xd5906ce08d61f7c5ee45fcebd2c8baeed5558387398ea332817a4b632f439b6d</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>L19683453</t>
+          <t>L19683447</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -2808,7 +2808,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>1786205938</t>
+          <t>1786205963</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -2818,7 +2818,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2.996255</t>
+          <t>2.768166</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -2835,31 +2835,39 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0x1b9fcb29010a212f74af57040114154e78748f06a4d826be4397ddadb45ac31b</t>
+          <t>0xcfe218822e89cbef5841f3045f551cc65acf353d8e240f943e2b61c54ea79a68</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr"/>
+          <t>0xf4a8B27C9a13e298D65b5Cc072d252816B799C81</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>21.69</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1.4512</t>
+          <t>1.3337</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H23" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -2867,27 +2875,27 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Almirante Brown vs Ciudad Bolivar</t>
+          <t>Estudiantes de Caseros vs Deportivo Madryn</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Estudiantes de Caseros</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Ciudad Bolivar</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0xbbcaa253cd967fbf933ff0d87a6f9744cafec0ed59dad5f1f76332aab01a3fa5</t>
+          <t>0xf238b96ec9e2421db79973de945f1fc0c3f8bb99c31cda32d011ebaabfd2db86</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>L19683447</t>
+          <t>L19683453</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -2912,7 +2920,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>1786190525</t>
+          <t>1786205938</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -2922,7 +2930,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>48.066482</t>
+          <t>2.996255</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -2939,23 +2947,23 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0x3177792dd6a7185e37ae06612104cf5a35d137d7f535a889a83a7e9b7c174506</t>
+          <t>0x1b9fcb29010a212f74af57040114154e78748f06a4d826be4397ddadb45ac31b</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
-          <t>18.35495</t>
+          <t>21.69</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1.4963</t>
+          <t>1.4512</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -3016,7 +3024,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>1786190491</t>
+          <t>1786190525</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -3026,7 +3034,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>36.987305</t>
+          <t>48.066482</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -3043,7 +3051,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0x54ed4ee2a6ebdab49498137f1accea542ead806f21430a0a771cc4872a044e43</t>
+          <t>0x3177792dd6a7185e37ae06612104cf5a35d137d7f535a889a83a7e9b7c174506</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3051,19 +3059,15 @@
           <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
-          <t>20.10741</t>
+          <t>18.35495</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1.5437</t>
+          <t>1.4963</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -3071,11 +3075,7 @@
           <t>Under/Over (1.5)</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>Over 1.5</t>
-        </is>
-      </c>
+      <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -3128,7 +3128,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>1786190485</t>
+          <t>1786190491</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
@@ -3138,7 +3138,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>36.979145</t>
+          <t>36.987305</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3155,23 +3155,27 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0x544fe5c906328d009917b591611ff3438cef85f8b42d9f67732cbbd5eabbb8dd</t>
+          <t>0x54ed4ee2a6ebdab49498137f1accea542ead806f21430a0a771cc4872a044e43</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr"/>
+          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>21.69</t>
+          <t>20.10741</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1.4512</t>
+          <t>1.5437</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -3179,7 +3183,11 @@
           <t>Under/Over (1.5)</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Over 1.5</t>
+        </is>
+      </c>
       <c r="H26" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -3242,7 +3250,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>48.066482</t>
+          <t>36.979145</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -3259,7 +3267,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0xb2f3ea804e1760a01d3a93678f0e2119f1ea2a9db0dc4711a06cc7bcba42b0c2</t>
+          <t>0x544fe5c906328d009917b591611ff3438cef85f8b42d9f67732cbbd5eabbb8dd</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3270,12 +3278,12 @@
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t>17.47</t>
+          <t>21.69</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1.405</t>
+          <t>1.4512</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -3291,27 +3299,27 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Estudiantes de Caseros vs Deportivo Madryn</t>
+          <t>Almirante Brown vs Ciudad Bolivar</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Estudiantes de Caseros</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Ciudad Bolivar</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>0xd61509e26f8645bb9780672f942c72c4b7dab577c2a01f04e1e09bce9b828765</t>
+          <t>0xbbcaa253cd967fbf933ff0d87a6f9744cafec0ed59dad5f1f76332aab01a3fa5</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>L19683453</t>
+          <t>L19683447</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -3336,7 +3344,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>1786190461</t>
+          <t>1786190485</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -3346,7 +3354,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>43.135802</t>
+          <t>48.066482</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -3363,7 +3371,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0xa7eafbb77d425fc2347b4ee3e4f4e1b85f6d0f81420605db76ebfeeaa793a428</t>
+          <t>0xb2f3ea804e1760a01d3a93678f0e2119f1ea2a9db0dc4711a06cc7bcba42b0c2</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3374,12 +3382,12 @@
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
-          <t>21.69</t>
+          <t>17.47</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>1.4512</t>
+          <t>1.405</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -3395,27 +3403,27 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Almirante Brown vs Ciudad Bolivar</t>
+          <t>Estudiantes de Caseros vs Deportivo Madryn</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Estudiantes de Caseros</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>Ciudad Bolivar</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>0xbbcaa253cd967fbf933ff0d87a6f9744cafec0ed59dad5f1f76332aab01a3fa5</t>
+          <t>0xd61509e26f8645bb9780672f942c72c4b7dab577c2a01f04e1e09bce9b828765</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>L19683447</t>
+          <t>L19683453</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -3440,7 +3448,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>1786190458</t>
+          <t>1786190461</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
@@ -3450,7 +3458,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>48.066482</t>
+          <t>43.135802</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -3467,110 +3475,214 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
+          <t>0xa7eafbb77d425fc2347b4ee3e4f4e1b85f6d0f81420605db76ebfeeaa793a428</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>21.69</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>1.4512</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Primera Nacional</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Almirante Brown vs Ciudad Bolivar</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Almirante Brown</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Ciudad Bolivar</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>0xbbcaa253cd967fbf933ff0d87a6f9744cafec0ed59dad5f1f76332aab01a3fa5</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>L19683447</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>1786190458</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>1786212000</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>48.066482</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
           <t>0x5c5b512ea725fac30531bf5fe91f34f3ccc0eeff23890c18f25c3f329007c589</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
         <is>
           <t>1.3638</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="F30" t="inlineStr">
         <is>
           <t>1X2</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="G30" t="inlineStr">
         <is>
           <t>Tie</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
+      <c r="H30" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
+      <c r="I30" t="inlineStr">
         <is>
           <t>Almirante Brown vs Ciudad Bolivar</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr">
+      <c r="J30" t="inlineStr">
         <is>
           <t>Almirante Brown</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr">
+      <c r="K30" t="inlineStr">
         <is>
           <t>Ciudad Bolivar</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr">
+      <c r="L30" t="inlineStr">
         <is>
           <t>0xd5906ce08d61f7c5ee45fcebd2c8baeed5558387398ea332817a4b632f439b6d</t>
         </is>
       </c>
-      <c r="M29" t="inlineStr">
+      <c r="M30" t="inlineStr">
         <is>
           <t>L19683447</t>
         </is>
       </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O29" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P29" t="inlineStr">
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R29" t="inlineStr">
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
         <is>
           <t>1786125660</t>
         </is>
       </c>
-      <c r="S29" t="inlineStr">
+      <c r="S30" t="inlineStr">
         <is>
           <t>1786212000</t>
         </is>
       </c>
-      <c r="T29" t="inlineStr">
+      <c r="T30" t="inlineStr">
         <is>
           <t>2.749141</t>
         </is>
       </c>
-      <c r="U29" t="inlineStr">
+      <c r="U30" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V29" t="inlineStr">
+      <c r="V30" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/Primera Nacional/trades.xlsx
+++ b/data/sxbet/ligas/Primera Nacional/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V30"/>
+  <dimension ref="A1:V51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,12 +531,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0x0847a2541998eecfe02d138796b14ef3d6719061787498f4888f6e14c0d196ff</t>
+          <t>0x680d5db234b802aa2845f16e9d23d635dd89870065c6bfb6f6f1bde25c321bae</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0xf068eF8DF8f47185D02d59Bb33d9eC7A057a571E</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -546,22 +546,22 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>38.54</t>
+          <t>24.36</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.125</t>
+          <t>1.475</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Club Almagro</t>
+          <t>CA Colegiales -0.5</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -571,27 +571,27 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Quilmes vs Club Almagro</t>
+          <t>CA Colegiales vs Patronato</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>CA Colegiales</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Club Almagro</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0x03ed0858b563c1becf38b195ad94b1a84eb89c3ca8ca10b1a34220bff142f9b2</t>
+          <t>0x50a3f0e4e982cdda0b9c4b9e2e1c50c67d93fbf7a068b43dbdf733c0b8d09050</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>L19683499</t>
+          <t>L19683449</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -616,17 +616,17 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1786270828</t>
+          <t>1786287181</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>1786305600</t>
+          <t>1786298400</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>308.32</t>
+          <t>51.284211</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -643,7 +643,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0x2121e08c4ea1fe2d49a3bb388fba9e232ef9c06335c04e5eae0bf7766975512a</t>
+          <t>0x5a5b6f41ac2a593747a9419c020abd417423350c2cf0a14d8cb9ef8a25d04f18</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -651,31 +651,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>30.06</t>
+          <t>8.81755</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.6262</t>
+          <t>1.6325</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Colon de Santa Fe</t>
-        </is>
-      </c>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -683,27 +675,27 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Colon de Santa Fe vs San Telmo</t>
+          <t>Quilmes vs Club Almagro</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Colon de Santa Fe</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Club Almagro</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0x1a11ec80edeaae24566c4f4f891cc2afc56b377b24997a6e8ee533eeaaad5c92</t>
+          <t>0x86a790846c1cb1bed065ac37c41b727461e30e0a9e0f9e2370ef61f6213ed31f</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>L19683494</t>
+          <t>L19683499</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -728,17 +720,17 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1786253941</t>
+          <t>1786284071</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>1786300200</t>
+          <t>1786305600</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>48.0</t>
+          <t>13.940791</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -755,39 +747,31 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0x4e811c319e5e3a1fc1968ce0f31b4c15eb7222daa616252d99f9abc611408746</t>
+          <t>0x9ae6e679c8fc9ed20977676ba3160d389287dd8808ea2610d0f168f9c3a42c11</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0x155C76202e45BE70c50bfeD7eAeA3B98e7716Ff7</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>21.58999</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.2925</t>
+          <t>1.6325</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -795,27 +779,27 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Colon de Santa Fe vs San Telmo</t>
+          <t>Quilmes vs Club Almagro</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Colon de Santa Fe</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Club Almagro</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0x2e49527408facf21253a0a1eafe51280b82e4c31919e91a396332f19ec366401</t>
+          <t>0x86a790846c1cb1bed065ac37c41b727461e30e0a9e0f9e2370ef61f6213ed31f</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>L19683494</t>
+          <t>L19683499</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -840,17 +824,17 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1786243741</t>
+          <t>1786284003</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>1786300200</t>
+          <t>1786305600</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>3.418803</t>
+          <t>34.134372</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -867,39 +851,31 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0xb8631aeb398192a03386505542f05fa15e34db501204baa8745a4d4b5c1651b7</t>
+          <t>0x6771b333646b031b4dc4cfea8f533b040a6ed0a66012cdc416a7aaa5b89f7988</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0x155C76202e45BE70c50bfeD7eAeA3B98e7716Ff7</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.99999</t>
+          <t>19.2</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.6538</t>
+          <t>1.5425</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Deportivo Moron</t>
-        </is>
-      </c>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -907,27 +883,27 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Deportivo Moron vs Acassuso</t>
+          <t>Colon de Santa Fe vs San Telmo</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Deportivo Moron</t>
+          <t>Colon de Santa Fe</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0x7514a255ce41be3c5db9f8849ba04e78dab80f02d1fe78c2aae82bbc843a9745</t>
+          <t>0x4b323aab38dd8f5096dcd1965ce7dc05c69ab73371e55e810b7a5aee356bf244</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>L19683452</t>
+          <t>L19683494</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -952,17 +928,17 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1786243225</t>
+          <t>1786283290</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>1786298400</t>
+          <t>1786300200</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1.529621</t>
+          <t>35.391705</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -979,23 +955,23 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0xd3b94d194e43cc84f0a1b82723594ea6689a6aa2a4a7dccbc8a3d19fc321e49b</t>
+          <t>0x8809f3e942a9cc8dca00d48b07cfe53a328d6ba2b60742c63e144e3d8cf2eaa1</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>23.25749</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.5238</t>
+          <t>1.4838</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1011,27 +987,27 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Deportivo Moron vs Acassuso</t>
+          <t>Colon de Santa Fe vs San Telmo</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Deportivo Moron</t>
+          <t>Colon de Santa Fe</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0x108eaba0441fb45ec8e0073e945ae0ac1e138c933e4f2839816cd3198d7dd4d2</t>
+          <t>0xc91217dfcd3944893195656945526d39efcd315aa93101aa312de5303c04d446</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>L19683452</t>
+          <t>L19683494</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1056,17 +1032,17 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1786225000</t>
+          <t>1786281248</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>1786298400</t>
+          <t>1786300200</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1.909308</t>
+          <t>48.077499</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1083,39 +1059,31 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0x86f4b24298f4c19f9f856cb19af2a260f24dc2d391f252248469436057ea1d1a</t>
+          <t>0xe5b95b7ede820952a7e6f5c1b2139a8092b51c4de75567f117f1291461ec6fbe</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>23.55844</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.5263</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Deportivo Moron -1</t>
-        </is>
-      </c>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -1123,27 +1091,27 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Deportivo Moron vs Acassuso</t>
+          <t>Colon de Santa Fe vs San Telmo</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Deportivo Moron</t>
+          <t>Colon de Santa Fe</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0xb61b063252c01d0525ae633a0276dc1830eabd418482fddec925fcbd602a2a75</t>
+          <t>0xc91217dfcd3944893195656945526d39efcd315aa93101aa312de5303c04d446</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>L19683452</t>
+          <t>L19683494</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1168,17 +1136,17 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1786220171</t>
+          <t>1786281243</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>1786298400</t>
+          <t>1786300200</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1.900238</t>
+          <t>48.078449</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1195,39 +1163,31 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0x0a5de930b5a6b8aca1699b666034af3891a3aa920021791d6d13e0297fb7903f</t>
+          <t>0x4d872ac34cfff98634d3d50362fe725a3f4ea55d64ddd9e3d7d811b073f350ab</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0x4a09916b1325Eed50eE8973B13742a205B0B7c7E</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>49.99999</t>
+          <t>17.30813</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.6175</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Almirante Brown -1</t>
-        </is>
-      </c>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -1235,27 +1195,27 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Almirante Brown vs Ciudad Bolivar</t>
+          <t>Colon de Santa Fe vs San Telmo</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Colon de Santa Fe</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Ciudad Bolivar</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0xa6a338c64f062bfd589e8d5d9cea45a27c9e64065f71f800e5966f81ce53c556</t>
+          <t>0xd638a8ee6393f88ca538cc4fe6ac8cdf722bcfe6277a5ebd9387222eade88ba3</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>L19683447</t>
+          <t>L19683494</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1280,17 +1240,17 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1786218515</t>
+          <t>1786281243</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>1786212000</t>
+          <t>1786300200</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>80.971644</t>
+          <t>48.078139</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1307,28 +1267,28 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0x17d5a08f8fa305f31f27442393c64f497dd3893417da6e76c321c4c2a187320d</t>
+          <t>0x8f782cb5f7b30f6c129f6031ec6368ed75ea36897066f1761d9054013f56567d</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>49.18897</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.4737</t>
+          <t>1.4187</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Primera Nacional</t>
         </is>
       </c>
       <c r="G9" t="inlineStr"/>
@@ -1339,27 +1299,27 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Almirante Brown vs Ciudad Bolivar</t>
+          <t>Club Atletico Mitre de Santiago del Estero vs Defensores de Belgrano Buenos Aires</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Club Atletico Mitre de Santiago del Estero</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Ciudad Bolivar</t>
+          <t>Defensores de Belgrano Buenos Aires</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0xa6a338c64f062bfd589e8d5d9cea45a27c9e64065f71f800e5966f81ce53c556</t>
+          <t>0x2d371e1a8a9d98624f046ea3d7126e47308ffbc183b66b1e2fba81e5ae69d7dd</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>L19683447</t>
+          <t>L19683493</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1384,17 +1344,17 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1786218084</t>
+          <t>1786280425</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>1786212000</t>
+          <t>1786302000</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>103.82896</t>
+          <t>23.880597</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1411,28 +1371,28 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0x56975f372357be259365cb7d2929c88d4fae157eea7a71d53d57cb234834f2ca</t>
+          <t>0xfe8890b155a19f7eb888456b555a7a6d8c293f8ecabeb69d2abd10210f520589</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.4812</t>
+          <t>1.4475</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
+          <t>Under/Over (2)</t>
         </is>
       </c>
       <c r="G10" t="inlineStr"/>
@@ -1443,27 +1403,27 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Club Atletico Mitre de Santiago del Estero vs Defensores de Belgrano Buenos Aires</t>
+          <t>Colon de Santa Fe vs San Telmo</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Club Atletico Mitre de Santiago del Estero</t>
+          <t>Colon de Santa Fe</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano Buenos Aires</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0xa8ade64a3adb0ea38de67a61105ef31beb490d5a7287715b76ae124536d359cc</t>
+          <t>0xc91217dfcd3944893195656945526d39efcd315aa93101aa312de5303c04d446</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>L19683493</t>
+          <t>L19683494</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1488,17 +1448,17 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1786215674</t>
+          <t>1786280403</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>1786302000</t>
+          <t>1786300200</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2.077922</t>
+          <t>22.346369</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1515,12 +1475,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0xff53df1f3446908699196d44fcdb8b39c1bd15c7ed519f0d730e55a51a6eb38f</t>
+          <t>0x60e023296ac2f9f58237fa345b3aa08fb4f997dd34c5384f371782bf7bbd5a40</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1530,22 +1490,22 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>26.11999</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.3713</t>
+          <t>1.5488</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (2)</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Over 2.0</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1555,27 +1515,27 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Almirante Brown vs Ciudad Bolivar</t>
+          <t>Colon de Santa Fe vs San Telmo</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Colon de Santa Fe</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Ciudad Bolivar</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0x63a8bf73c1084ef223fdd1096dccd16232e7a455fad77f7f0891be1588ebeb88</t>
+          <t>0xc91217dfcd3944893195656945526d39efcd315aa93101aa312de5303c04d446</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>L19683447</t>
+          <t>L19683494</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1600,17 +1560,17 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1786215673</t>
+          <t>1786280403</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>1786212000</t>
+          <t>1786300200</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2.693603</t>
+          <t>47.599071</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1627,7 +1587,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0x249d52552e7acb9f472d2a4c48ab754622ba572903281739a3e10b4d509dccb0</t>
+          <t>0x2d118800c100a2a41a19c2053cbf355561a08867f99163fb40955a4ab012ce39</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1635,31 +1595,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>20.07999</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.2288</t>
+          <t>1.7363</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Almirante Brown -1</t>
-        </is>
-      </c>
+          <t>Asian Handicap (-1.5)</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -1667,27 +1619,27 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Almirante Brown vs Ciudad Bolivar</t>
+          <t>Godoy Cruz vs Chaco For Ever</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Ciudad Bolivar</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>0xa6a338c64f062bfd589e8d5d9cea45a27c9e64065f71f800e5966f81ce53c556</t>
+          <t>0x60e111ebf03c4965ff049e67cf10f93f5cca143023c6104aab59162863b5b8a8</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>L19683447</t>
+          <t>L19683484</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1712,17 +1664,17 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1786214209</t>
+          <t>1786279900</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>1786212000</t>
+          <t>1786303800</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>6.295082</t>
+          <t>27.273331</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1739,12 +1691,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0xf65c55196eeb0d21e7e3866ad26f8c3f2fee2aef273ddde5423e31fb40a51469</t>
+          <t>0x904e2e53a604aa6663de774d4bd9ddf8af7459ef1c4fa1bb14486300917ac211</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1754,12 +1706,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>121.81</t>
+          <t>3.96</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.4363</t>
+          <t>1.2837</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1769,7 +1721,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Tie</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1779,27 +1731,27 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Almirante Brown vs Ciudad Bolivar</t>
+          <t>Godoy Cruz vs Chaco For Ever</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Ciudad Bolivar</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>0x63a8bf73c1084ef223fdd1096dccd16232e7a455fad77f7f0891be1588ebeb88</t>
+          <t>0x08dce15d4ca4845359c2f121bce305fd3a0fe7422d497000c713e29463c6be79</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>L19683447</t>
+          <t>L19683484</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1824,17 +1776,17 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1786213844</t>
+          <t>1786279851</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>1786212000</t>
+          <t>1786303800</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>279.22063</t>
+          <t>13.955947</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1851,39 +1803,31 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0x1bb20a2bf22e4fe06b44c06b9c2caa21f3f2a7c9d0cce1a2346f79e76022cd1f</t>
+          <t>0x19a6c0536a5dea88055519ff16050cdde80d42121bb75c5045e3b562a7c1d4bb</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>21.05</t>
+          <t>7.50547</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1.4363</t>
+          <t>1.4287</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Almirante Brown -0.5</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -1891,27 +1835,27 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Almirante Brown vs Ciudad Bolivar</t>
+          <t>Godoy Cruz vs Chaco For Ever</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Ciudad Bolivar</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>0xfa00d2f0c7b5053ee336b303a0e7ad9cec0b8d539367773b7efee5c86cb2b59d</t>
+          <t>0xa5f02d0d08d0dcc4818948397f0f26c77f90b87182cec4d62ab01f77352671a1</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>L19683447</t>
+          <t>L19683484</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1936,17 +1880,17 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1786213843</t>
+          <t>1786279821</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>1786212000</t>
+          <t>1786303800</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>48.252149</t>
+          <t>17.505469</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -1963,28 +1907,28 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0xc51052f8e449b4d56cc87b697bfc8eb0d3a88ae218dee1da3d725fa94163bc75</t>
+          <t>0x4c44e2c0c492a5115b342a42a552a040cb800bd582b07c12f1ea9161b861b487</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>77.29513</t>
+          <t>11.30844</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1.2588</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Primera Nacional</t>
+          <t>Under/Over (2)</t>
         </is>
       </c>
       <c r="G15" t="inlineStr"/>
@@ -1995,27 +1939,27 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Almirante Brown vs Ciudad Bolivar</t>
+          <t>Deportivo Moron vs Acassuso</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Deportivo Moron</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Ciudad Bolivar</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>0xaa5316c6f6544d74142ad6db34a3745918f237ffb1a657e000693947e81b65d6</t>
+          <t>0x108eaba0441fb45ec8e0073e945ae0ac1e138c933e4f2839816cd3198d7dd4d2</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>L19683447</t>
+          <t>L19683452</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -2040,17 +1984,17 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>1786212849</t>
+          <t>1786278950</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>1786212000</t>
+          <t>1786298400</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>298.72514</t>
+          <t>23.078449</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2067,28 +2011,28 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0x0aeb4fe40f7d734cf244c144e6c064568b40b222193c9f93c641d1b31af3752e</t>
+          <t>0x5a5ccf0d5f6cbac6813d25e4e1e96b25b5c5a4ff8f6378d7e69d6bd3c29295ae</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>16.89162</t>
+          <t>12.25</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1.2588</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Primera Nacional</t>
+          <t>Under/Over (2)</t>
         </is>
       </c>
       <c r="G16" t="inlineStr"/>
@@ -2099,27 +2043,27 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Almirante Brown vs Ciudad Bolivar</t>
+          <t>Deportivo Moron vs Acassuso</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Deportivo Moron</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Ciudad Bolivar</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>0xaa5316c6f6544d74142ad6db34a3745918f237ffb1a657e000693947e81b65d6</t>
+          <t>0x108eaba0441fb45ec8e0073e945ae0ac1e138c933e4f2839816cd3198d7dd4d2</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>L19683447</t>
+          <t>L19683452</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -2144,17 +2088,17 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1786212805</t>
+          <t>1786278094</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>1786212000</t>
+          <t>1786298400</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>65.281623</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2171,67 +2115,59 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0x383b895a5fe529a887369a0f113c516fdc7f6125d54381acf9695997ef22d039</t>
+          <t>0x5f3419242a87ff17c0cb508ade95d27a54429124d36280a1dff2efa2fa0b3510</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>11.26905</t>
+          <t>20.41999</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.745</t>
+          <t>1.7087</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr">
+        <is>
           <t>Primera Nacional</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Almirante Brown</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Primera Nacional</t>
-        </is>
-      </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Almirante Brown vs Ciudad Bolivar</t>
+          <t>CA Los Andes vs Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>CA Los Andes</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Ciudad Bolivar</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>0xaa5316c6f6544d74142ad6db34a3745918f237ffb1a657e000693947e81b65d6</t>
+          <t>0x31115553050eabb8d3f6a72cf2865c16175783383dcfc674615e74ed88cabaee</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>L19683447</t>
+          <t>L19659153</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -2256,17 +2192,17 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>1786211779</t>
+          <t>1786277884</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>1786212000</t>
+          <t>1786296600</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>15.126242</t>
+          <t>28.811273</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2283,7 +2219,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0xcfb6add6f8610a64ffc187beb9e16bf2bacb27b54a0f0aaefa6bfb437239b893</t>
+          <t>0xe6b14424302d9ef7ea2000cef83e38549f6a38c12d57faa6dd76dd84e631a5ca</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2291,59 +2227,51 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>24.89998</t>
+          <t>12.13</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.745</t>
+          <t>1.3613</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr">
+        <is>
           <t>Primera Nacional</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>Almirante Brown</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Primera Nacional</t>
-        </is>
-      </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Almirante Brown vs Ciudad Bolivar</t>
+          <t>Deportivo Moron vs Acassuso</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Deportivo Moron</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Ciudad Bolivar</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>0xaa5316c6f6544d74142ad6db34a3745918f237ffb1a657e000693947e81b65d6</t>
+          <t>0x3f34d112cfb9f093c57a3e094be078f9eea2715f97797e20d86942d58f5cc8d6</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>L19683447</t>
+          <t>L19683452</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -2368,17 +2296,17 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>1786211777</t>
+          <t>1786277708</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>1786212000</t>
+          <t>1786298400</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>33.422792</t>
+          <t>33.577855</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2395,39 +2323,31 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0xd41652604437a4e92e0d78b653d4d49d8dedd2e153d1340dad89b9b93e182a48</t>
+          <t>0xd7a2e43ba1564f619200938b384123dd68adb783742fc7b32ee335ee489d1302</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0xf4a8B27C9a13e298D65b5Cc072d252816B799C81</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10.58</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1.4163</t>
+          <t>1.485</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>Atl. Rafaela</t>
-        </is>
-      </c>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -2435,27 +2355,27 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Atl. Rafaela vs Chacarita Juniors</t>
+          <t>Deportivo Moron vs Acassuso</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Atl. Rafaela</t>
+          <t>Deportivo Moron</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>0xe738e9ba05492fab73eaaf6da211b84caadc72b08b26f1cd30fa8737e283bb44</t>
+          <t>0x108eaba0441fb45ec8e0073e945ae0ac1e138c933e4f2839816cd3198d7dd4d2</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>L19683450</t>
+          <t>L19683452</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -2480,17 +2400,17 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>1786211028</t>
+          <t>1786277679</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>1786215600</t>
+          <t>1786298400</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2.402402</t>
+          <t>21.814433</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2507,7 +2427,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0x562fd7c6419c807ed04d3cacac95f861805f96704bd535e265399fb9d2c2b609</t>
+          <t>0xb25fa423ffb1a1464f100f2a2e9a1beac36661b9e37c8b09ecc7d3fd5a80312f</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2518,17 +2438,17 @@
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>5.32</t>
+          <t>25.88</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.405</t>
+          <t>1.6038</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
+          <t>Under/Over (2)</t>
         </is>
       </c>
       <c r="G20" t="inlineStr"/>
@@ -2539,27 +2459,27 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Estudiantes de Caseros vs Deportivo Madryn</t>
+          <t>CA Colegiales vs Patronato</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Estudiantes de Caseros</t>
+          <t>CA Colegiales</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0xd61509e26f8645bb9780672f942c72c4b7dab577c2a01f04e1e09bce9b828765</t>
+          <t>0x18dd2fdd93f5029a20e6a76c47c4f0e5c3c25768ad7f1b46a833287f8b7fcc13</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>L19683453</t>
+          <t>L19683449</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -2584,17 +2504,17 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>1786210845</t>
+          <t>1786277040</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>1786212000</t>
+          <t>1786298400</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>13.135802</t>
+          <t>42.865424</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2611,39 +2531,31 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0x0bb7a6822220bf40d7b279f99a54f46025f393ba95bb38b6d6dc98192886b3ed</t>
+          <t>0xfe815be8a10a6ad2cda012e463a244232a6f6c80544018f6dda52d723946b659</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0xf4a8B27C9a13e298D65b5Cc072d252816B799C81</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0.99999</t>
+          <t>29.02571</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1.5513</t>
+          <t>1.6038</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Agropecuario</t>
-        </is>
-      </c>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -2651,27 +2563,27 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Agropecuario vs Atletico Guemes</t>
+          <t>CA Colegiales vs Patronato</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>CA Colegiales</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Atletico Guemes</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0xae66c7fab3c9c76fbc29d9e9778ef4845d8a6b8d092cff34320f100020113c49</t>
+          <t>0x18dd2fdd93f5029a20e6a76c47c4f0e5c3c25768ad7f1b46a833287f8b7fcc13</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>L19683451</t>
+          <t>L19683449</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -2696,17 +2608,17 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>1786205982</t>
+          <t>1786276809</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>1786212000</t>
+          <t>1786298400</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>1.814041</t>
+          <t>48.07571</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -2723,39 +2635,31 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0xe17b2546f4b90c8647ba975c279e39dec1fda5a003adfb8a2b39bb12a3519b10</t>
+          <t>0xdb83c52876b68624e093c25e35d11910f4fbef2394ff947b658f8ea5cdb3fa88</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0xf4a8B27C9a13e298D65b5Cc072d252816B799C81</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>16.96</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1.3613</t>
+          <t>1.4463</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -2763,27 +2667,27 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Almirante Brown vs Ciudad Bolivar</t>
+          <t>CA Colegiales vs Patronato</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>CA Colegiales</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Ciudad Bolivar</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0xd5906ce08d61f7c5ee45fcebd2c8baeed5558387398ea332817a4b632f439b6d</t>
+          <t>0x30a6561de28b35c5bb0557dcbfc7b23e7a62558d3b0f5cfcafb67d7a07e0dd21</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>L19683447</t>
+          <t>L19683449</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -2808,17 +2712,17 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>1786205963</t>
+          <t>1786276809</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>1786212000</t>
+          <t>1786298400</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2.768166</t>
+          <t>38.005602</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -2835,12 +2739,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0xcfe218822e89cbef5841f3045f551cc65acf353d8e240f943e2b61c54ea79a68</t>
+          <t>0x0847a2541998eecfe02d138796b14ef3d6719061787498f4888f6e14c0d196ff</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0xf4a8B27C9a13e298D65b5Cc072d252816B799C81</t>
+          <t>0xf068eF8DF8f47185D02d59Bb33d9eC7A057a571E</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2850,12 +2754,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>38.54</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1.3337</t>
+          <t>1.125</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -2865,7 +2769,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tie</t>
+          <t>Club Almagro</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2875,27 +2779,27 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Estudiantes de Caseros vs Deportivo Madryn</t>
+          <t>Quilmes vs Club Almagro</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Estudiantes de Caseros</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Club Almagro</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0xf238b96ec9e2421db79973de945f1fc0c3f8bb99c31cda32d011ebaabfd2db86</t>
+          <t>0x03ed0858b563c1becf38b195ad94b1a84eb89c3ca8ca10b1a34220bff142f9b2</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>L19683453</t>
+          <t>L19683499</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -2920,17 +2824,17 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>1786205938</t>
+          <t>1786270828</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>1786212000</t>
+          <t>1786305600</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2.996255</t>
+          <t>308.32</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -2947,7 +2851,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0x1b9fcb29010a212f74af57040114154e78748f06a4d826be4397ddadb45ac31b</t>
+          <t>0x2121e08c4ea1fe2d49a3bb388fba9e232ef9c06335c04e5eae0bf7766975512a</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2955,23 +2859,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr"/>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>21.69</t>
+          <t>30.06</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1.4512</t>
+          <t>1.6262</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Colon de Santa Fe</t>
+        </is>
+      </c>
       <c r="H24" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -2979,27 +2891,27 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Almirante Brown vs Ciudad Bolivar</t>
+          <t>Colon de Santa Fe vs San Telmo</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Colon de Santa Fe</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Ciudad Bolivar</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0xbbcaa253cd967fbf933ff0d87a6f9744cafec0ed59dad5f1f76332aab01a3fa5</t>
+          <t>0x1a11ec80edeaae24566c4f4f891cc2afc56b377b24997a6e8ee533eeaaad5c92</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>L19683447</t>
+          <t>L19683494</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -3024,17 +2936,17 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>1786190525</t>
+          <t>1786253941</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>1786212000</t>
+          <t>1786300200</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>48.066482</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -3051,31 +2963,39 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0x3177792dd6a7185e37ae06612104cf5a35d137d7f535a889a83a7e9b7c174506</t>
+          <t>0x4e811c319e5e3a1fc1968ce0f31b4c15eb7222daa616252d99f9abc611408746</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr"/>
+          <t>0x155C76202e45BE70c50bfeD7eAeA3B98e7716Ff7</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>18.35495</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1.4963</t>
+          <t>1.2925</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H25" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -3083,27 +3003,27 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Almirante Brown vs Ciudad Bolivar</t>
+          <t>Colon de Santa Fe vs San Telmo</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Colon de Santa Fe</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Ciudad Bolivar</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0xbbcaa253cd967fbf933ff0d87a6f9744cafec0ed59dad5f1f76332aab01a3fa5</t>
+          <t>0x2e49527408facf21253a0a1eafe51280b82e4c31919e91a396332f19ec366401</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>L19683447</t>
+          <t>L19683494</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -3128,17 +3048,17 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>1786190491</t>
+          <t>1786243741</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>1786212000</t>
+          <t>1786300200</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>36.987305</t>
+          <t>3.418803</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3155,12 +3075,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0x54ed4ee2a6ebdab49498137f1accea542ead806f21430a0a771cc4872a044e43</t>
+          <t>0xb8631aeb398192a03386505542f05fa15e34db501204baa8745a4d4b5c1651b7</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
+          <t>0x155C76202e45BE70c50bfeD7eAeA3B98e7716Ff7</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3170,22 +3090,22 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>20.10741</t>
+          <t>0.99999</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1.5437</t>
+          <t>1.6538</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Over 1.5</t>
+          <t>Deportivo Moron</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3195,27 +3115,27 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Almirante Brown vs Ciudad Bolivar</t>
+          <t>Deportivo Moron vs Acassuso</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Deportivo Moron</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>Ciudad Bolivar</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>0xbbcaa253cd967fbf933ff0d87a6f9744cafec0ed59dad5f1f76332aab01a3fa5</t>
+          <t>0x7514a255ce41be3c5db9f8849ba04e78dab80f02d1fe78c2aae82bbc843a9745</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>L19683447</t>
+          <t>L19683452</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -3240,17 +3160,17 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>1786190485</t>
+          <t>1786243225</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>1786212000</t>
+          <t>1786298400</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>36.979145</t>
+          <t>1.529621</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -3267,28 +3187,28 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0x544fe5c906328d009917b591611ff3438cef85f8b42d9f67732cbbd5eabbb8dd</t>
+          <t>0xd3b94d194e43cc84f0a1b82723594ea6689a6aa2a4a7dccbc8a3d19fc321e49b</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
         </is>
       </c>
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t>21.69</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1.4512</t>
+          <t>1.5238</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
+          <t>Under/Over (2)</t>
         </is>
       </c>
       <c r="G27" t="inlineStr"/>
@@ -3299,27 +3219,27 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Almirante Brown vs Ciudad Bolivar</t>
+          <t>Deportivo Moron vs Acassuso</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Deportivo Moron</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>Ciudad Bolivar</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>0xbbcaa253cd967fbf933ff0d87a6f9744cafec0ed59dad5f1f76332aab01a3fa5</t>
+          <t>0x108eaba0441fb45ec8e0073e945ae0ac1e138c933e4f2839816cd3198d7dd4d2</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>L19683447</t>
+          <t>L19683452</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -3344,17 +3264,17 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>1786190485</t>
+          <t>1786225000</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>1786212000</t>
+          <t>1786298400</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>48.066482</t>
+          <t>1.909308</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -3371,31 +3291,39 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0xb2f3ea804e1760a01d3a93678f0e2119f1ea2a9db0dc4711a06cc7bcba42b0c2</t>
+          <t>0x86f4b24298f4c19f9f856cb19af2a260f24dc2d391f252248469436057ea1d1a</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr"/>
+          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>17.47</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>1.405</t>
+          <t>1.5263</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr"/>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Deportivo Moron -1</t>
+        </is>
+      </c>
       <c r="H28" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -3403,27 +3331,27 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Estudiantes de Caseros vs Deportivo Madryn</t>
+          <t>Deportivo Moron vs Acassuso</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Estudiantes de Caseros</t>
+          <t>Deportivo Moron</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>0xd61509e26f8645bb9780672f942c72c4b7dab577c2a01f04e1e09bce9b828765</t>
+          <t>0xb61b063252c01d0525ae633a0276dc1830eabd418482fddec925fcbd602a2a75</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>L19683453</t>
+          <t>L19683452</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -3448,17 +3376,17 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>1786190461</t>
+          <t>1786220171</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>1786212000</t>
+          <t>1786298400</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>43.135802</t>
+          <t>1.900238</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -3475,31 +3403,39 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0xa7eafbb77d425fc2347b4ee3e4f4e1b85f6d0f81420605db76ebfeeaa793a428</t>
+          <t>0x0a5de930b5a6b8aca1699b666034af3891a3aa920021791d6d13e0297fb7903f</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr"/>
+          <t>0x4a09916b1325Eed50eE8973B13742a205B0B7c7E</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>21.69</t>
+          <t>49.99999</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>1.4512</t>
+          <t>1.6175</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr"/>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Almirante Brown -1</t>
+        </is>
+      </c>
       <c r="H29" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -3522,7 +3458,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>0xbbcaa253cd967fbf933ff0d87a6f9744cafec0ed59dad5f1f76332aab01a3fa5</t>
+          <t>0xa6a338c64f062bfd589e8d5d9cea45a27c9e64065f71f800e5966f81ce53c556</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -3552,7 +3488,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>1786190458</t>
+          <t>1786218515</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
@@ -3562,7 +3498,7 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>48.066482</t>
+          <t>80.971644</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -3579,110 +3515,2382 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
+          <t>0x17d5a08f8fa305f31f27442393c64f497dd3893417da6e76c321c4c2a187320d</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>49.18897</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>1.4737</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Primera Nacional</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Almirante Brown vs Ciudad Bolivar</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Almirante Brown</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Ciudad Bolivar</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>0xa6a338c64f062bfd589e8d5d9cea45a27c9e64065f71f800e5966f81ce53c556</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>L19683447</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>1786218084</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>1786212000</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>103.82896</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>0x56975f372357be259365cb7d2929c88d4fae157eea7a71d53d57cb234834f2ca</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>1.4812</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Primera Nacional</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Club Atletico Mitre de Santiago del Estero vs Defensores de Belgrano Buenos Aires</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Club Atletico Mitre de Santiago del Estero</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Defensores de Belgrano Buenos Aires</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>0xa8ade64a3adb0ea38de67a61105ef31beb490d5a7287715b76ae124536d359cc</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>L19683493</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>1786215674</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>1786302000</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>2.077922</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>0xff53df1f3446908699196d44fcdb8b39c1bd15c7ed519f0d730e55a51a6eb38f</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>1.3713</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Almirante Brown</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Primera Nacional</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Almirante Brown vs Ciudad Bolivar</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Almirante Brown</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Ciudad Bolivar</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>0x63a8bf73c1084ef223fdd1096dccd16232e7a455fad77f7f0891be1588ebeb88</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>L19683447</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>1786215673</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>1786212000</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>2.693603</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>0x249d52552e7acb9f472d2a4c48ab754622ba572903281739a3e10b4d509dccb0</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>1.44</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>1.2288</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Almirante Brown -1</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Primera Nacional</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Almirante Brown vs Ciudad Bolivar</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Almirante Brown</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Ciudad Bolivar</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>0xa6a338c64f062bfd589e8d5d9cea45a27c9e64065f71f800e5966f81ce53c556</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>L19683447</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>1786214209</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>1786212000</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>6.295082</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>0xf65c55196eeb0d21e7e3866ad26f8c3f2fee2aef273ddde5423e31fb40a51469</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>121.81</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>1.4363</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Almirante Brown</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Primera Nacional</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Almirante Brown vs Ciudad Bolivar</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Almirante Brown</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Ciudad Bolivar</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>0x63a8bf73c1084ef223fdd1096dccd16232e7a455fad77f7f0891be1588ebeb88</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>L19683447</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>1786213844</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>1786212000</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>279.22063</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>0x1bb20a2bf22e4fe06b44c06b9c2caa21f3f2a7c9d0cce1a2346f79e76022cd1f</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>21.05</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>1.4363</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-0.5)</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Almirante Brown -0.5</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Primera Nacional</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Almirante Brown vs Ciudad Bolivar</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Almirante Brown</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Ciudad Bolivar</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>0xfa00d2f0c7b5053ee336b303a0e7ad9cec0b8d539367773b7efee5c86cb2b59d</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>L19683447</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>1786213843</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>1786212000</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>48.252149</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>0xc51052f8e449b4d56cc87b697bfc8eb0d3a88ae218dee1da3d725fa94163bc75</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr"/>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>77.29513</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>1.2588</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Primera Nacional</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Primera Nacional</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Almirante Brown vs Ciudad Bolivar</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Almirante Brown</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Ciudad Bolivar</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>0xaa5316c6f6544d74142ad6db34a3745918f237ffb1a657e000693947e81b65d6</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>L19683447</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>1786212849</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>1786212000</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>298.72514</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>0x0aeb4fe40f7d734cf244c144e6c064568b40b222193c9f93c641d1b31af3752e</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr"/>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>16.89162</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>1.2588</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Primera Nacional</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Primera Nacional</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Almirante Brown vs Ciudad Bolivar</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Almirante Brown</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Ciudad Bolivar</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>0xaa5316c6f6544d74142ad6db34a3745918f237ffb1a657e000693947e81b65d6</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>L19683447</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>1786212805</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>1786212000</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>65.281623</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>0x383b895a5fe529a887369a0f113c516fdc7f6125d54381acf9695997ef22d039</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>11.26905</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>1.745</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Primera Nacional</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Almirante Brown</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Primera Nacional</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Almirante Brown vs Ciudad Bolivar</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Almirante Brown</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Ciudad Bolivar</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>0xaa5316c6f6544d74142ad6db34a3745918f237ffb1a657e000693947e81b65d6</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>L19683447</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>1786211779</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>1786212000</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>15.126242</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>0xcfb6add6f8610a64ffc187beb9e16bf2bacb27b54a0f0aaefa6bfb437239b893</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>24.89998</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>1.745</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Primera Nacional</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Almirante Brown</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Primera Nacional</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Almirante Brown vs Ciudad Bolivar</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Almirante Brown</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Ciudad Bolivar</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>0xaa5316c6f6544d74142ad6db34a3745918f237ffb1a657e000693947e81b65d6</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>L19683447</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>1786211777</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>1786212000</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>33.422792</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>0xd41652604437a4e92e0d78b653d4d49d8dedd2e153d1340dad89b9b93e182a48</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>0xf4a8B27C9a13e298D65b5Cc072d252816B799C81</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>1.4163</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Atl. Rafaela</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Primera Nacional</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Atl. Rafaela vs Chacarita Juniors</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>Atl. Rafaela</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Chacarita Juniors</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>0xe738e9ba05492fab73eaaf6da211b84caadc72b08b26f1cd30fa8737e283bb44</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>L19683450</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>1786211028</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>1786215600</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>2.402402</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>0x562fd7c6419c807ed04d3cacac95f861805f96704bd535e265399fb9d2c2b609</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr"/>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>5.32</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>1.405</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Primera Nacional</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Estudiantes de Caseros vs Deportivo Madryn</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Estudiantes de Caseros</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Deportivo Madryn</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>0xd61509e26f8645bb9780672f942c72c4b7dab577c2a01f04e1e09bce9b828765</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>L19683453</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>1786210845</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>1786212000</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>13.135802</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>0x0bb7a6822220bf40d7b279f99a54f46025f393ba95bb38b6d6dc98192886b3ed</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>0xf4a8B27C9a13e298D65b5Cc072d252816B799C81</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>0.99999</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>1.5513</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Agropecuario</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Primera Nacional</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Agropecuario vs Atletico Guemes</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Agropecuario</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Atletico Guemes</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>0xae66c7fab3c9c76fbc29d9e9778ef4845d8a6b8d092cff34320f100020113c49</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>L19683451</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>1786205982</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>1786212000</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>1.814041</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>0xe17b2546f4b90c8647ba975c279e39dec1fda5a003adfb8a2b39bb12a3519b10</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>0xf4a8B27C9a13e298D65b5Cc072d252816B799C81</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>1.3613</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Primera Nacional</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Almirante Brown vs Ciudad Bolivar</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>Almirante Brown</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Ciudad Bolivar</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>0xd5906ce08d61f7c5ee45fcebd2c8baeed5558387398ea332817a4b632f439b6d</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>L19683447</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>1786205963</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>1786212000</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>2.768166</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>0xcfe218822e89cbef5841f3045f551cc65acf353d8e240f943e2b61c54ea79a68</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>0xf4a8B27C9a13e298D65b5Cc072d252816B799C81</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>1.3337</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Primera Nacional</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Estudiantes de Caseros vs Deportivo Madryn</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>Estudiantes de Caseros</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Deportivo Madryn</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>0xf238b96ec9e2421db79973de945f1fc0c3f8bb99c31cda32d011ebaabfd2db86</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>L19683453</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>1786205938</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>1786212000</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>2.996255</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>0x1b9fcb29010a212f74af57040114154e78748f06a4d826be4397ddadb45ac31b</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr"/>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>21.69</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>1.4512</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Primera Nacional</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Almirante Brown vs Ciudad Bolivar</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>Almirante Brown</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Ciudad Bolivar</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>0xbbcaa253cd967fbf933ff0d87a6f9744cafec0ed59dad5f1f76332aab01a3fa5</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>L19683447</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>1786190525</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>1786212000</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>48.066482</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>0x3177792dd6a7185e37ae06612104cf5a35d137d7f535a889a83a7e9b7c174506</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr"/>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>18.35495</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>1.4963</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Primera Nacional</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Almirante Brown vs Ciudad Bolivar</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>Almirante Brown</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Ciudad Bolivar</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>0xbbcaa253cd967fbf933ff0d87a6f9744cafec0ed59dad5f1f76332aab01a3fa5</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>L19683447</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>1786190491</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>1786212000</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>36.987305</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>0x54ed4ee2a6ebdab49498137f1accea542ead806f21430a0a771cc4872a044e43</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>20.10741</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>1.5437</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Over 1.5</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Primera Nacional</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Almirante Brown vs Ciudad Bolivar</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>Almirante Brown</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Ciudad Bolivar</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>0xbbcaa253cd967fbf933ff0d87a6f9744cafec0ed59dad5f1f76332aab01a3fa5</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>L19683447</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>1786190485</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>1786212000</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>36.979145</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>0x544fe5c906328d009917b591611ff3438cef85f8b42d9f67732cbbd5eabbb8dd</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr"/>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>21.69</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>1.4512</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Primera Nacional</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Almirante Brown vs Ciudad Bolivar</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>Almirante Brown</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Ciudad Bolivar</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>0xbbcaa253cd967fbf933ff0d87a6f9744cafec0ed59dad5f1f76332aab01a3fa5</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>L19683447</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>1786190485</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>1786212000</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>48.066482</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>0xb2f3ea804e1760a01d3a93678f0e2119f1ea2a9db0dc4711a06cc7bcba42b0c2</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr"/>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>17.47</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>1.405</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Primera Nacional</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Estudiantes de Caseros vs Deportivo Madryn</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>Estudiantes de Caseros</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Deportivo Madryn</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>0xd61509e26f8645bb9780672f942c72c4b7dab577c2a01f04e1e09bce9b828765</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>L19683453</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>1786190461</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>1786212000</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>43.135802</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>0xa7eafbb77d425fc2347b4ee3e4f4e1b85f6d0f81420605db76ebfeeaa793a428</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr"/>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>21.69</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>1.4512</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Primera Nacional</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Almirante Brown vs Ciudad Bolivar</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>Almirante Brown</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Ciudad Bolivar</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>0xbbcaa253cd967fbf933ff0d87a6f9744cafec0ed59dad5f1f76332aab01a3fa5</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>L19683447</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>1786190458</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>1786212000</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>48.066482</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
           <t>0x5c5b512ea725fac30531bf5fe91f34f3ccc0eeff23890c18f25c3f329007c589</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B51" t="inlineStr">
         <is>
           <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
         <is>
           <t>1.3638</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="F51" t="inlineStr">
         <is>
           <t>1X2</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="G51" t="inlineStr">
         <is>
           <t>Tie</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
+      <c r="H51" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
+      <c r="I51" t="inlineStr">
         <is>
           <t>Almirante Brown vs Ciudad Bolivar</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr">
+      <c r="J51" t="inlineStr">
         <is>
           <t>Almirante Brown</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr">
+      <c r="K51" t="inlineStr">
         <is>
           <t>Ciudad Bolivar</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr">
+      <c r="L51" t="inlineStr">
         <is>
           <t>0xd5906ce08d61f7c5ee45fcebd2c8baeed5558387398ea332817a4b632f439b6d</t>
         </is>
       </c>
-      <c r="M30" t="inlineStr">
+      <c r="M51" t="inlineStr">
         <is>
           <t>L19683447</t>
         </is>
       </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O30" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P30" t="inlineStr">
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R30" t="inlineStr">
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R51" t="inlineStr">
         <is>
           <t>1786125660</t>
         </is>
       </c>
-      <c r="S30" t="inlineStr">
+      <c r="S51" t="inlineStr">
         <is>
           <t>1786212000</t>
         </is>
       </c>
-      <c r="T30" t="inlineStr">
+      <c r="T51" t="inlineStr">
         <is>
           <t>2.749141</t>
         </is>
       </c>
-      <c r="U30" t="inlineStr">
+      <c r="U51" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V30" t="inlineStr">
+      <c r="V51" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/Primera Nacional/trades.xlsx
+++ b/data/sxbet/ligas/Primera Nacional/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V51"/>
+  <dimension ref="A1:V56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,39 +531,31 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0x680d5db234b802aa2845f16e9d23d635dd89870065c6bfb6f6f1bde25c321bae</t>
+          <t>0xae3b69e222676c5f5930a25ee6fc677945888fbd4b45894897e8c0b45b324e25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>24.36</t>
+          <t>12.72</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.475</t>
+          <t>1.4512</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>CA Colegiales -0.5</t>
-        </is>
-      </c>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -571,27 +563,27 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>CA Colegiales vs Patronato</t>
+          <t>CA Los Andes vs Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>CA Colegiales</t>
+          <t>CA Los Andes</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0x50a3f0e4e982cdda0b9c4b9e2e1c50c67d93fbf7a068b43dbdf733c0b8d09050</t>
+          <t>0x555a8472fba9017aa83a61e5e7cf7b05dc2822d1d1cc6174412760fc412637f7</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>L19683449</t>
+          <t>L19659153</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -616,17 +608,17 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1786287181</t>
+          <t>1786288547</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>1786298400</t>
+          <t>1786296600</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>51.284211</t>
+          <t>28.188366</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -643,28 +635,28 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0x5a5b6f41ac2a593747a9419c020abd417423350c2cf0a14d8cb9ef8a25d04f18</t>
+          <t>0x4bb954aaa9ecad68c0eb53f2341bb75f7b8daa072a3f151571ab136be22b78df</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x71CE4A2C734a76f4C86A0D80122C4014c1F52F6e</t>
         </is>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>8.81755</t>
+          <t>29.37999</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.6325</t>
+          <t>1.6113</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>Under/Over (2)</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
@@ -675,27 +667,27 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Quilmes vs Club Almagro</t>
+          <t>CA Los Andes vs Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>CA Los Andes</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Club Almagro</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0x86a790846c1cb1bed065ac37c41b727461e30e0a9e0f9e2370ef61f6213ed31f</t>
+          <t>0x653af58a9c77cb072171a76bcd9ca8adee427601f3ecd186c8154c81f8736395</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>L19683499</t>
+          <t>L19659153</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -720,17 +712,17 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1786284071</t>
+          <t>1786288517</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>1786305600</t>
+          <t>1786296600</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>13.940791</t>
+          <t>48.065423</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -747,7 +739,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0x9ae6e679c8fc9ed20977676ba3160d389287dd8808ea2610d0f168f9c3a42c11</t>
+          <t>0xd5a2ddd8c8b6cc9bdb1c507276d3a192a5f24d46e2d3c01bfb07011263030bdd</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -758,17 +750,17 @@
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>21.58999</t>
+          <t>5.67</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.6325</t>
+          <t>1.2975</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>Primera Nacional</t>
         </is>
       </c>
       <c r="G4" t="inlineStr"/>
@@ -779,27 +771,27 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Quilmes vs Club Almagro</t>
+          <t>CA Colegiales vs Patronato</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>CA Colegiales</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Club Almagro</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0x86a790846c1cb1bed065ac37c41b727461e30e0a9e0f9e2370ef61f6213ed31f</t>
+          <t>0x710e5bf3f6759bd93c59fc8788916c16c7302071968dfba2d053e2d10f7858bf</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>L19683499</t>
+          <t>L19683449</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -824,17 +816,17 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1786284003</t>
+          <t>1786288450</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>1786305600</t>
+          <t>1786298400</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>34.134372</t>
+          <t>19.058824</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -851,7 +843,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0x6771b333646b031b4dc4cfea8f533b040a6ed0a66012cdc416a7aaa5b89f7988</t>
+          <t>0xad9f4feea88f83ae2e46756e7d54faa300a82e055c196c70c84019780ecb560c</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -862,17 +854,17 @@
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>19.2</t>
+          <t>21.69</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.5425</t>
+          <t>1.4512</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Under/Over (1.5)</t>
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
@@ -883,27 +875,27 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Colon de Santa Fe vs San Telmo</t>
+          <t>CA Los Andes vs Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Colon de Santa Fe</t>
+          <t>CA Los Andes</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0x4b323aab38dd8f5096dcd1965ce7dc05c69ab73371e55e810b7a5aee356bf244</t>
+          <t>0x555a8472fba9017aa83a61e5e7cf7b05dc2822d1d1cc6174412760fc412637f7</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>L19683494</t>
+          <t>L19659153</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -928,17 +920,17 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1786283290</t>
+          <t>1786288436</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>1786300200</t>
+          <t>1786296600</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>35.391705</t>
+          <t>48.066482</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -955,7 +947,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0x8809f3e942a9cc8dca00d48b07cfe53a328d6ba2b60742c63e144e3d8cf2eaa1</t>
+          <t>0x168e5ea2716a187c94a1c77c4c8b2523b31163ed118e4986c68c79a21d013932</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -966,12 +958,12 @@
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>23.25749</t>
+          <t>29.38716</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.4838</t>
+          <t>1.6113</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -987,27 +979,27 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Colon de Santa Fe vs San Telmo</t>
+          <t>CA Los Andes vs Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Colon de Santa Fe</t>
+          <t>CA Los Andes</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0xc91217dfcd3944893195656945526d39efcd315aa93101aa312de5303c04d446</t>
+          <t>0x653af58a9c77cb072171a76bcd9ca8adee427601f3ecd186c8154c81f8736395</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>L19683494</t>
+          <t>L19659153</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1032,17 +1024,17 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1786281248</t>
+          <t>1786288436</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>1786300200</t>
+          <t>1786296600</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>48.077499</t>
+          <t>48.077153</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1059,31 +1051,39 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0xe5b95b7ede820952a7e6f5c1b2139a8092b51c4de75567f117f1291461ec6fbe</t>
+          <t>0x680d5db234b802aa2845f16e9d23d635dd89870065c6bfb6f6f1bde25c321bae</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr"/>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>23.55844</t>
+          <t>24.36</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.475</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr"/>
+          <t>Asian Handicap (-0.5)</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>CA Colegiales -0.5</t>
+        </is>
+      </c>
       <c r="H7" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -1091,27 +1091,27 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Colon de Santa Fe vs San Telmo</t>
+          <t>CA Colegiales vs Patronato</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Colon de Santa Fe</t>
+          <t>CA Colegiales</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0xc91217dfcd3944893195656945526d39efcd315aa93101aa312de5303c04d446</t>
+          <t>0x50a3f0e4e982cdda0b9c4b9e2e1c50c67d93fbf7a068b43dbdf733c0b8d09050</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>L19683494</t>
+          <t>L19683449</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1136,17 +1136,17 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1786281243</t>
+          <t>1786287181</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>1786300200</t>
+          <t>1786298400</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>48.078449</t>
+          <t>51.284211</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1163,7 +1163,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0x4d872ac34cfff98634d3d50362fe725a3f4ea55d64ddd9e3d7d811b073f350ab</t>
+          <t>0x5a5b6f41ac2a593747a9419c020abd417423350c2cf0a14d8cb9ef8a25d04f18</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1174,17 +1174,17 @@
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>17.30813</t>
+          <t>8.81755</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.6325</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G8" t="inlineStr"/>
@@ -1195,27 +1195,27 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Colon de Santa Fe vs San Telmo</t>
+          <t>Quilmes vs Club Almagro</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Colon de Santa Fe</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Club Almagro</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0xd638a8ee6393f88ca538cc4fe6ac8cdf722bcfe6277a5ebd9387222eade88ba3</t>
+          <t>0x86a790846c1cb1bed065ac37c41b727461e30e0a9e0f9e2370ef61f6213ed31f</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>L19683494</t>
+          <t>L19683499</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1240,17 +1240,17 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1786281243</t>
+          <t>1786284071</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>1786300200</t>
+          <t>1786305600</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>48.078139</t>
+          <t>13.940791</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1267,7 +1267,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0x8f782cb5f7b30f6c129f6031ec6368ed75ea36897066f1761d9054013f56567d</t>
+          <t>0x9ae6e679c8fc9ed20977676ba3160d389287dd8808ea2610d0f168f9c3a42c11</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1278,17 +1278,17 @@
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>21.58999</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.4187</t>
+          <t>1.6325</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Primera Nacional</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G9" t="inlineStr"/>
@@ -1299,27 +1299,27 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Club Atletico Mitre de Santiago del Estero vs Defensores de Belgrano Buenos Aires</t>
+          <t>Quilmes vs Club Almagro</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Club Atletico Mitre de Santiago del Estero</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano Buenos Aires</t>
+          <t>Club Almagro</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0x2d371e1a8a9d98624f046ea3d7126e47308ffbc183b66b1e2fba81e5ae69d7dd</t>
+          <t>0x86a790846c1cb1bed065ac37c41b727461e30e0a9e0f9e2370ef61f6213ed31f</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>L19683493</t>
+          <t>L19683499</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1344,17 +1344,17 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1786280425</t>
+          <t>1786284003</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>1786302000</t>
+          <t>1786305600</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>23.880597</t>
+          <t>34.134372</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1371,7 +1371,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0xfe8890b155a19f7eb888456b555a7a6d8c293f8ecabeb69d2abd10210f520589</t>
+          <t>0x6771b333646b031b4dc4cfea8f533b040a6ed0a66012cdc416a7aaa5b89f7988</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1382,17 +1382,17 @@
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>19.2</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.4475</t>
+          <t>1.5425</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G10" t="inlineStr"/>
@@ -1418,7 +1418,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0xc91217dfcd3944893195656945526d39efcd315aa93101aa312de5303c04d446</t>
+          <t>0x4b323aab38dd8f5096dcd1965ce7dc05c69ab73371e55e810b7a5aee356bf244</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1448,7 +1448,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1786280403</t>
+          <t>1786283290</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1458,7 +1458,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>22.346369</t>
+          <t>35.391705</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1475,7 +1475,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0x60e023296ac2f9f58237fa345b3aa08fb4f997dd34c5384f371782bf7bbd5a40</t>
+          <t>0x8809f3e942a9cc8dca00d48b07cfe53a328d6ba2b60742c63e144e3d8cf2eaa1</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1483,19 +1483,15 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>26.11999</t>
+          <t>23.25749</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.5488</t>
+          <t>1.4838</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1503,11 +1499,7 @@
           <t>Under/Over (2)</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Over 2.0</t>
-        </is>
-      </c>
+      <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -1560,7 +1552,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1786280403</t>
+          <t>1786281248</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1570,7 +1562,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>47.599071</t>
+          <t>48.077499</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1587,7 +1579,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0x2d118800c100a2a41a19c2053cbf355561a08867f99163fb40955a4ab012ce39</t>
+          <t>0xe5b95b7ede820952a7e6f5c1b2139a8092b51c4de75567f117f1291461ec6fbe</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1598,17 +1590,17 @@
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>20.07999</t>
+          <t>23.55844</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.7363</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
+          <t>Under/Over (2)</t>
         </is>
       </c>
       <c r="G12" t="inlineStr"/>
@@ -1619,27 +1611,27 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Godoy Cruz vs Chaco For Ever</t>
+          <t>Colon de Santa Fe vs San Telmo</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Colon de Santa Fe</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>0x60e111ebf03c4965ff049e67cf10f93f5cca143023c6104aab59162863b5b8a8</t>
+          <t>0xc91217dfcd3944893195656945526d39efcd315aa93101aa312de5303c04d446</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>L19683484</t>
+          <t>L19683494</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1664,17 +1656,17 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1786279900</t>
+          <t>1786281243</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>1786303800</t>
+          <t>1786300200</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>27.273331</t>
+          <t>48.078449</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1691,7 +1683,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0x904e2e53a604aa6663de774d4bd9ddf8af7459ef1c4fa1bb14486300917ac211</t>
+          <t>0x4d872ac34cfff98634d3d50362fe725a3f4ea55d64ddd9e3d7d811b073f350ab</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1699,31 +1691,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>3.96</t>
+          <t>17.30813</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.2837</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -1731,27 +1715,27 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Godoy Cruz vs Chaco For Ever</t>
+          <t>Colon de Santa Fe vs San Telmo</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Colon de Santa Fe</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>0x08dce15d4ca4845359c2f121bce305fd3a0fe7422d497000c713e29463c6be79</t>
+          <t>0xd638a8ee6393f88ca538cc4fe6ac8cdf722bcfe6277a5ebd9387222eade88ba3</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>L19683484</t>
+          <t>L19683494</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1776,17 +1760,17 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1786279851</t>
+          <t>1786281243</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>1786303800</t>
+          <t>1786300200</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>13.955947</t>
+          <t>48.078139</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1803,7 +1787,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0x19a6c0536a5dea88055519ff16050cdde80d42121bb75c5045e3b562a7c1d4bb</t>
+          <t>0x8f782cb5f7b30f6c129f6031ec6368ed75ea36897066f1761d9054013f56567d</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1814,17 +1798,17 @@
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>7.50547</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1.4287</t>
+          <t>1.4187</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Primera Nacional</t>
         </is>
       </c>
       <c r="G14" t="inlineStr"/>
@@ -1835,27 +1819,27 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Godoy Cruz vs Chaco For Ever</t>
+          <t>Club Atletico Mitre de Santiago del Estero vs Defensores de Belgrano Buenos Aires</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Club Atletico Mitre de Santiago del Estero</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Defensores de Belgrano Buenos Aires</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>0xa5f02d0d08d0dcc4818948397f0f26c77f90b87182cec4d62ab01f77352671a1</t>
+          <t>0x2d371e1a8a9d98624f046ea3d7126e47308ffbc183b66b1e2fba81e5ae69d7dd</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>L19683484</t>
+          <t>L19683493</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1880,17 +1864,17 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1786279821</t>
+          <t>1786280425</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>1786303800</t>
+          <t>1786302000</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>17.505469</t>
+          <t>23.880597</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -1907,7 +1891,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0x4c44e2c0c492a5115b342a42a552a040cb800bd582b07c12f1ea9161b861b487</t>
+          <t>0xfe8890b155a19f7eb888456b555a7a6d8c293f8ecabeb69d2abd10210f520589</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1918,12 +1902,12 @@
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>11.30844</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.4475</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1939,27 +1923,27 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Deportivo Moron vs Acassuso</t>
+          <t>Colon de Santa Fe vs San Telmo</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Deportivo Moron</t>
+          <t>Colon de Santa Fe</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>0x108eaba0441fb45ec8e0073e945ae0ac1e138c933e4f2839816cd3198d7dd4d2</t>
+          <t>0xc91217dfcd3944893195656945526d39efcd315aa93101aa312de5303c04d446</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>L19683452</t>
+          <t>L19683494</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -1984,17 +1968,17 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>1786278950</t>
+          <t>1786280403</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>1786298400</t>
+          <t>1786300200</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>23.078449</t>
+          <t>22.346369</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2011,7 +1995,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0x5a5ccf0d5f6cbac6813d25e4e1e96b25b5c5a4ff8f6378d7e69d6bd3c29295ae</t>
+          <t>0x60e023296ac2f9f58237fa345b3aa08fb4f997dd34c5384f371782bf7bbd5a40</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2019,15 +2003,19 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr"/>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>12.25</t>
+          <t>26.11999</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.5488</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -2035,7 +2023,11 @@
           <t>Under/Over (2)</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Over 2.0</t>
+        </is>
+      </c>
       <c r="H16" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -2043,27 +2035,27 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Deportivo Moron vs Acassuso</t>
+          <t>Colon de Santa Fe vs San Telmo</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Deportivo Moron</t>
+          <t>Colon de Santa Fe</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>0x108eaba0441fb45ec8e0073e945ae0ac1e138c933e4f2839816cd3198d7dd4d2</t>
+          <t>0xc91217dfcd3944893195656945526d39efcd315aa93101aa312de5303c04d446</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>L19683452</t>
+          <t>L19683494</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -2088,17 +2080,17 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1786278094</t>
+          <t>1786280403</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>1786298400</t>
+          <t>1786300200</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>47.599071</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2115,7 +2107,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0x5f3419242a87ff17c0cb508ade95d27a54429124d36280a1dff2efa2fa0b3510</t>
+          <t>0x2d118800c100a2a41a19c2053cbf355561a08867f99163fb40955a4ab012ce39</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2126,17 +2118,17 @@
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>20.41999</t>
+          <t>20.07999</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.7087</t>
+          <t>1.7363</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-1.5)</t>
         </is>
       </c>
       <c r="G17" t="inlineStr"/>
@@ -2147,27 +2139,27 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>CA Los Andes vs Ferro Carril Oeste</t>
+          <t>Godoy Cruz vs Chaco For Ever</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>CA Los Andes</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>0x31115553050eabb8d3f6a72cf2865c16175783383dcfc674615e74ed88cabaee</t>
+          <t>0x60e111ebf03c4965ff049e67cf10f93f5cca143023c6104aab59162863b5b8a8</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>L19659153</t>
+          <t>L19683484</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -2192,17 +2184,17 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>1786277884</t>
+          <t>1786279900</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>1786296600</t>
+          <t>1786303800</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>28.811273</t>
+          <t>27.273331</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2219,7 +2211,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0xe6b14424302d9ef7ea2000cef83e38549f6a38c12d57faa6dd76dd84e631a5ca</t>
+          <t>0x904e2e53a604aa6663de774d4bd9ddf8af7459ef1c4fa1bb14486300917ac211</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2227,23 +2219,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr"/>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>12.13</t>
+          <t>3.96</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.3613</t>
+          <t>1.2837</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H18" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -2251,27 +2251,27 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Deportivo Moron vs Acassuso</t>
+          <t>Godoy Cruz vs Chaco For Ever</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Deportivo Moron</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>0x3f34d112cfb9f093c57a3e094be078f9eea2715f97797e20d86942d58f5cc8d6</t>
+          <t>0x08dce15d4ca4845359c2f121bce305fd3a0fe7422d497000c713e29463c6be79</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>L19683452</t>
+          <t>L19683484</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -2296,17 +2296,17 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>1786277708</t>
+          <t>1786279851</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>1786298400</t>
+          <t>1786303800</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>33.577855</t>
+          <t>13.955947</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2323,7 +2323,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0xd7a2e43ba1564f619200938b384123dd68adb783742fc7b32ee335ee489d1302</t>
+          <t>0x19a6c0536a5dea88055519ff16050cdde80d42121bb75c5045e3b562a7c1d4bb</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2334,17 +2334,17 @@
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>10.58</t>
+          <t>7.50547</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1.485</t>
+          <t>1.4287</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G19" t="inlineStr"/>
@@ -2355,27 +2355,27 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Deportivo Moron vs Acassuso</t>
+          <t>Godoy Cruz vs Chaco For Ever</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Deportivo Moron</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>0x108eaba0441fb45ec8e0073e945ae0ac1e138c933e4f2839816cd3198d7dd4d2</t>
+          <t>0xa5f02d0d08d0dcc4818948397f0f26c77f90b87182cec4d62ab01f77352671a1</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>L19683452</t>
+          <t>L19683484</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -2400,17 +2400,17 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>1786277679</t>
+          <t>1786279821</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>1786298400</t>
+          <t>1786303800</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>21.814433</t>
+          <t>17.505469</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2427,7 +2427,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0xb25fa423ffb1a1464f100f2a2e9a1beac36661b9e37c8b09ecc7d3fd5a80312f</t>
+          <t>0x4c44e2c0c492a5115b342a42a552a040cb800bd582b07c12f1ea9161b861b487</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2438,12 +2438,12 @@
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>25.88</t>
+          <t>11.30844</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.6038</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -2459,27 +2459,27 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>CA Colegiales vs Patronato</t>
+          <t>Deportivo Moron vs Acassuso</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>CA Colegiales</t>
+          <t>Deportivo Moron</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0x18dd2fdd93f5029a20e6a76c47c4f0e5c3c25768ad7f1b46a833287f8b7fcc13</t>
+          <t>0x108eaba0441fb45ec8e0073e945ae0ac1e138c933e4f2839816cd3198d7dd4d2</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>L19683449</t>
+          <t>L19683452</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>1786277040</t>
+          <t>1786278950</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -2514,7 +2514,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>42.865424</t>
+          <t>23.078449</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2531,7 +2531,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0xfe815be8a10a6ad2cda012e463a244232a6f6c80544018f6dda52d723946b659</t>
+          <t>0x5a5ccf0d5f6cbac6813d25e4e1e96b25b5c5a4ff8f6378d7e69d6bd3c29295ae</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2542,12 +2542,12 @@
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>29.02571</t>
+          <t>12.25</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1.6038</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -2563,27 +2563,27 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>CA Colegiales vs Patronato</t>
+          <t>Deportivo Moron vs Acassuso</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>CA Colegiales</t>
+          <t>Deportivo Moron</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0x18dd2fdd93f5029a20e6a76c47c4f0e5c3c25768ad7f1b46a833287f8b7fcc13</t>
+          <t>0x108eaba0441fb45ec8e0073e945ae0ac1e138c933e4f2839816cd3198d7dd4d2</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>L19683449</t>
+          <t>L19683452</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -2608,7 +2608,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>1786276809</t>
+          <t>1786278094</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>48.07571</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -2635,7 +2635,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0xdb83c52876b68624e093c25e35d11910f4fbef2394ff947b658f8ea5cdb3fa88</t>
+          <t>0x5f3419242a87ff17c0cb508ade95d27a54429124d36280a1dff2efa2fa0b3510</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2646,17 +2646,17 @@
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
-          <t>16.96</t>
+          <t>20.41999</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1.4463</t>
+          <t>1.7087</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G22" t="inlineStr"/>
@@ -2667,27 +2667,27 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>CA Colegiales vs Patronato</t>
+          <t>CA Los Andes vs Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>CA Colegiales</t>
+          <t>CA Los Andes</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0x30a6561de28b35c5bb0557dcbfc7b23e7a62558d3b0f5cfcafb67d7a07e0dd21</t>
+          <t>0x31115553050eabb8d3f6a72cf2865c16175783383dcfc674615e74ed88cabaee</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>L19683449</t>
+          <t>L19659153</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -2712,17 +2712,17 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>1786276809</t>
+          <t>1786277884</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>1786298400</t>
+          <t>1786296600</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>38.005602</t>
+          <t>28.811273</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -2739,39 +2739,31 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0x0847a2541998eecfe02d138796b14ef3d6719061787498f4888f6e14c0d196ff</t>
+          <t>0xe6b14424302d9ef7ea2000cef83e38549f6a38c12d57faa6dd76dd84e631a5ca</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0xf068eF8DF8f47185D02d59Bb33d9eC7A057a571E</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>38.54</t>
+          <t>12.13</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1.125</t>
+          <t>1.3613</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>Club Almagro</t>
-        </is>
-      </c>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -2779,27 +2771,27 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Quilmes vs Club Almagro</t>
+          <t>Deportivo Moron vs Acassuso</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Deportivo Moron</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Club Almagro</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0x03ed0858b563c1becf38b195ad94b1a84eb89c3ca8ca10b1a34220bff142f9b2</t>
+          <t>0x3f34d112cfb9f093c57a3e094be078f9eea2715f97797e20d86942d58f5cc8d6</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>L19683499</t>
+          <t>L19683452</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -2824,17 +2816,17 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>1786270828</t>
+          <t>1786277708</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>1786305600</t>
+          <t>1786298400</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>308.32</t>
+          <t>33.577855</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -2851,7 +2843,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0x2121e08c4ea1fe2d49a3bb388fba9e232ef9c06335c04e5eae0bf7766975512a</t>
+          <t>0xd7a2e43ba1564f619200938b384123dd68adb783742fc7b32ee335ee489d1302</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2859,31 +2851,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
-          <t>30.06</t>
+          <t>10.58</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1.6262</t>
+          <t>1.485</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>Colon de Santa Fe</t>
-        </is>
-      </c>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -2891,27 +2875,27 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Colon de Santa Fe vs San Telmo</t>
+          <t>Deportivo Moron vs Acassuso</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Colon de Santa Fe</t>
+          <t>Deportivo Moron</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0x1a11ec80edeaae24566c4f4f891cc2afc56b377b24997a6e8ee533eeaaad5c92</t>
+          <t>0x108eaba0441fb45ec8e0073e945ae0ac1e138c933e4f2839816cd3198d7dd4d2</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>L19683494</t>
+          <t>L19683452</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -2936,17 +2920,17 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>1786253941</t>
+          <t>1786277679</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>1786300200</t>
+          <t>1786298400</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>48.0</t>
+          <t>21.814433</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -2963,39 +2947,31 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0x4e811c319e5e3a1fc1968ce0f31b4c15eb7222daa616252d99f9abc611408746</t>
+          <t>0xb25fa423ffb1a1464f100f2a2e9a1beac36661b9e37c8b09ecc7d3fd5a80312f</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0x155C76202e45BE70c50bfeD7eAeA3B98e7716Ff7</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>25.88</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1.2925</t>
+          <t>1.6038</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -3003,27 +2979,27 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Colon de Santa Fe vs San Telmo</t>
+          <t>CA Colegiales vs Patronato</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Colon de Santa Fe</t>
+          <t>CA Colegiales</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0x2e49527408facf21253a0a1eafe51280b82e4c31919e91a396332f19ec366401</t>
+          <t>0x18dd2fdd93f5029a20e6a76c47c4f0e5c3c25768ad7f1b46a833287f8b7fcc13</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>L19683494</t>
+          <t>L19683449</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -3048,17 +3024,17 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>1786243741</t>
+          <t>1786277040</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>1786300200</t>
+          <t>1786298400</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>3.418803</t>
+          <t>42.865424</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3075,39 +3051,31 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0xb8631aeb398192a03386505542f05fa15e34db501204baa8745a4d4b5c1651b7</t>
+          <t>0xfe815be8a10a6ad2cda012e463a244232a6f6c80544018f6dda52d723946b659</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>0x155C76202e45BE70c50bfeD7eAeA3B98e7716Ff7</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
-          <t>0.99999</t>
+          <t>29.02571</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1.6538</t>
+          <t>1.6038</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>Deportivo Moron</t>
-        </is>
-      </c>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -3115,27 +3083,27 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Deportivo Moron vs Acassuso</t>
+          <t>CA Colegiales vs Patronato</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Deportivo Moron</t>
+          <t>CA Colegiales</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>0x7514a255ce41be3c5db9f8849ba04e78dab80f02d1fe78c2aae82bbc843a9745</t>
+          <t>0x18dd2fdd93f5029a20e6a76c47c4f0e5c3c25768ad7f1b46a833287f8b7fcc13</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>L19683452</t>
+          <t>L19683449</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -3160,7 +3128,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>1786243225</t>
+          <t>1786276809</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -3170,7 +3138,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>1.529621</t>
+          <t>48.07571</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -3187,28 +3155,28 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0xd3b94d194e43cc84f0a1b82723594ea6689a6aa2a4a7dccbc8a3d19fc321e49b</t>
+          <t>0xdb83c52876b68624e093c25e35d11910f4fbef2394ff947b658f8ea5cdb3fa88</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>16.96</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1.5238</t>
+          <t>1.4463</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
+          <t>Under/Over (1.5)</t>
         </is>
       </c>
       <c r="G27" t="inlineStr"/>
@@ -3219,27 +3187,27 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Deportivo Moron vs Acassuso</t>
+          <t>CA Colegiales vs Patronato</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Deportivo Moron</t>
+          <t>CA Colegiales</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>0x108eaba0441fb45ec8e0073e945ae0ac1e138c933e4f2839816cd3198d7dd4d2</t>
+          <t>0x30a6561de28b35c5bb0557dcbfc7b23e7a62558d3b0f5cfcafb67d7a07e0dd21</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>L19683452</t>
+          <t>L19683449</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -3264,7 +3232,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>1786225000</t>
+          <t>1786276809</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -3274,7 +3242,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>1.909308</t>
+          <t>38.005602</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -3291,12 +3259,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0x86f4b24298f4c19f9f856cb19af2a260f24dc2d391f252248469436057ea1d1a</t>
+          <t>0x0847a2541998eecfe02d138796b14ef3d6719061787498f4888f6e14c0d196ff</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
+          <t>0xf068eF8DF8f47185D02d59Bb33d9eC7A057a571E</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -3306,22 +3274,22 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>38.54</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>1.5263</t>
+          <t>1.125</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Deportivo Moron -1</t>
+          <t>Club Almagro</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3331,27 +3299,27 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Deportivo Moron vs Acassuso</t>
+          <t>Quilmes vs Club Almagro</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Deportivo Moron</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Club Almagro</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>0xb61b063252c01d0525ae633a0276dc1830eabd418482fddec925fcbd602a2a75</t>
+          <t>0x03ed0858b563c1becf38b195ad94b1a84eb89c3ca8ca10b1a34220bff142f9b2</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>L19683452</t>
+          <t>L19683499</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -3376,17 +3344,17 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>1786220171</t>
+          <t>1786270828</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>1786298400</t>
+          <t>1786305600</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>1.900238</t>
+          <t>308.32</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -3403,12 +3371,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0x0a5de930b5a6b8aca1699b666034af3891a3aa920021791d6d13e0297fb7903f</t>
+          <t>0x2121e08c4ea1fe2d49a3bb388fba9e232ef9c06335c04e5eae0bf7766975512a</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>0x4a09916b1325Eed50eE8973B13742a205B0B7c7E</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -3418,22 +3386,22 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>49.99999</t>
+          <t>30.06</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>1.6175</t>
+          <t>1.6262</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Almirante Brown -1</t>
+          <t>Colon de Santa Fe</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -3443,27 +3411,27 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Almirante Brown vs Ciudad Bolivar</t>
+          <t>Colon de Santa Fe vs San Telmo</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Colon de Santa Fe</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>Ciudad Bolivar</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>0xa6a338c64f062bfd589e8d5d9cea45a27c9e64065f71f800e5966f81ce53c556</t>
+          <t>0x1a11ec80edeaae24566c4f4f891cc2afc56b377b24997a6e8ee533eeaaad5c92</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>L19683447</t>
+          <t>L19683494</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -3488,17 +3456,17 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>1786218515</t>
+          <t>1786253941</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>1786212000</t>
+          <t>1786300200</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>80.971644</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -3515,31 +3483,39 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0x17d5a08f8fa305f31f27442393c64f497dd3893417da6e76c321c4c2a187320d</t>
+          <t>0x4e811c319e5e3a1fc1968ce0f31b4c15eb7222daa616252d99f9abc611408746</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr"/>
+          <t>0x155C76202e45BE70c50bfeD7eAeA3B98e7716Ff7</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>49.18897</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1.4737</t>
+          <t>1.2925</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H30" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -3547,27 +3523,27 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Almirante Brown vs Ciudad Bolivar</t>
+          <t>Colon de Santa Fe vs San Telmo</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Colon de Santa Fe</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>Ciudad Bolivar</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>0xa6a338c64f062bfd589e8d5d9cea45a27c9e64065f71f800e5966f81ce53c556</t>
+          <t>0x2e49527408facf21253a0a1eafe51280b82e4c31919e91a396332f19ec366401</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>L19683447</t>
+          <t>L19683494</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -3592,17 +3568,17 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>1786218084</t>
+          <t>1786243741</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>1786212000</t>
+          <t>1786300200</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>103.82896</t>
+          <t>3.418803</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -3619,31 +3595,39 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0x56975f372357be259365cb7d2929c88d4fae157eea7a71d53d57cb234834f2ca</t>
+          <t>0xb8631aeb398192a03386505542f05fa15e34db501204baa8745a4d4b5c1651b7</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr"/>
+          <t>0x155C76202e45BE70c50bfeD7eAeA3B98e7716Ff7</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0.99999</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1.4812</t>
+          <t>1.6538</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Deportivo Moron</t>
+        </is>
+      </c>
       <c r="H31" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -3651,27 +3635,27 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Club Atletico Mitre de Santiago del Estero vs Defensores de Belgrano Buenos Aires</t>
+          <t>Deportivo Moron vs Acassuso</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Club Atletico Mitre de Santiago del Estero</t>
+          <t>Deportivo Moron</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano Buenos Aires</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>0xa8ade64a3adb0ea38de67a61105ef31beb490d5a7287715b76ae124536d359cc</t>
+          <t>0x7514a255ce41be3c5db9f8849ba04e78dab80f02d1fe78c2aae82bbc843a9745</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>L19683493</t>
+          <t>L19683452</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -3696,17 +3680,17 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>1786215674</t>
+          <t>1786243225</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>1786302000</t>
+          <t>1786298400</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>2.077922</t>
+          <t>1.529621</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -3723,7 +3707,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0xff53df1f3446908699196d44fcdb8b39c1bd15c7ed519f0d730e55a51a6eb38f</t>
+          <t>0xd3b94d194e43cc84f0a1b82723594ea6689a6aa2a4a7dccbc8a3d19fc321e49b</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3731,11 +3715,7 @@
           <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
           <t>1</t>
@@ -3743,19 +3723,15 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>1.3713</t>
+          <t>1.5238</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>Almirante Brown</t>
-        </is>
-      </c>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -3763,27 +3739,27 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Almirante Brown vs Ciudad Bolivar</t>
+          <t>Deportivo Moron vs Acassuso</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Deportivo Moron</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>Ciudad Bolivar</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0x63a8bf73c1084ef223fdd1096dccd16232e7a455fad77f7f0891be1588ebeb88</t>
+          <t>0x108eaba0441fb45ec8e0073e945ae0ac1e138c933e4f2839816cd3198d7dd4d2</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>L19683447</t>
+          <t>L19683452</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -3808,17 +3784,17 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>1786215673</t>
+          <t>1786225000</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>1786212000</t>
+          <t>1786298400</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>2.693603</t>
+          <t>1.909308</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -3835,12 +3811,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0x249d52552e7acb9f472d2a4c48ab754622ba572903281739a3e10b4d509dccb0</t>
+          <t>0x86f4b24298f4c19f9f856cb19af2a260f24dc2d391f252248469436057ea1d1a</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -3850,12 +3826,12 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>1.2288</t>
+          <t>1.5263</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -3865,7 +3841,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Almirante Brown -1</t>
+          <t>Deportivo Moron -1</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -3875,27 +3851,27 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Almirante Brown vs Ciudad Bolivar</t>
+          <t>Deportivo Moron vs Acassuso</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Deportivo Moron</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>Ciudad Bolivar</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>0xa6a338c64f062bfd589e8d5d9cea45a27c9e64065f71f800e5966f81ce53c556</t>
+          <t>0xb61b063252c01d0525ae633a0276dc1830eabd418482fddec925fcbd602a2a75</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>L19683447</t>
+          <t>L19683452</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -3920,17 +3896,17 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>1786214209</t>
+          <t>1786220171</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>1786212000</t>
+          <t>1786298400</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>6.295082</t>
+          <t>1.900238</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -3947,12 +3923,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0xf65c55196eeb0d21e7e3866ad26f8c3f2fee2aef273ddde5423e31fb40a51469</t>
+          <t>0x0a5de930b5a6b8aca1699b666034af3891a3aa920021791d6d13e0297fb7903f</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x4a09916b1325Eed50eE8973B13742a205B0B7c7E</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -3962,39 +3938,39 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>121.81</t>
+          <t>49.99999</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>1.4363</t>
+          <t>1.6175</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
+          <t>Almirante Brown -1</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Primera Nacional</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Almirante Brown vs Ciudad Bolivar</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
           <t>Almirante Brown</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>Primera Nacional</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>Almirante Brown vs Ciudad Bolivar</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>Almirante Brown</t>
-        </is>
-      </c>
       <c r="K34" t="inlineStr">
         <is>
           <t>Ciudad Bolivar</t>
@@ -4002,7 +3978,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0x63a8bf73c1084ef223fdd1096dccd16232e7a455fad77f7f0891be1588ebeb88</t>
+          <t>0xa6a338c64f062bfd589e8d5d9cea45a27c9e64065f71f800e5966f81ce53c556</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -4032,7 +4008,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>1786213844</t>
+          <t>1786218515</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
@@ -4042,7 +4018,7 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>279.22063</t>
+          <t>80.971644</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -4059,7 +4035,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0x1bb20a2bf22e4fe06b44c06b9c2caa21f3f2a7c9d0cce1a2346f79e76022cd1f</t>
+          <t>0x17d5a08f8fa305f31f27442393c64f497dd3893417da6e76c321c4c2a187320d</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4067,31 +4043,23 @@
           <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
-          <t>21.05</t>
+          <t>49.18897</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>1.4363</t>
+          <t>1.4737</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>Almirante Brown -0.5</t>
-        </is>
-      </c>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -4114,7 +4082,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>0xfa00d2f0c7b5053ee336b303a0e7ad9cec0b8d539367773b7efee5c86cb2b59d</t>
+          <t>0xa6a338c64f062bfd589e8d5d9cea45a27c9e64065f71f800e5966f81ce53c556</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -4144,7 +4112,7 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>1786213843</t>
+          <t>1786218084</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
@@ -4154,7 +4122,7 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>48.252149</t>
+          <t>103.82896</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
@@ -4171,28 +4139,28 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0xc51052f8e449b4d56cc87b697bfc8eb0d3a88ae218dee1da3d725fa94163bc75</t>
+          <t>0x56975f372357be259365cb7d2929c88d4fae157eea7a71d53d57cb234834f2ca</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
         </is>
       </c>
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
-          <t>77.29513</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>1.2588</t>
+          <t>1.4812</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Primera Nacional</t>
+          <t>Under/Over (1.5)</t>
         </is>
       </c>
       <c r="G36" t="inlineStr"/>
@@ -4203,27 +4171,27 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Almirante Brown vs Ciudad Bolivar</t>
+          <t>Club Atletico Mitre de Santiago del Estero vs Defensores de Belgrano Buenos Aires</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Club Atletico Mitre de Santiago del Estero</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>Ciudad Bolivar</t>
+          <t>Defensores de Belgrano Buenos Aires</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>0xaa5316c6f6544d74142ad6db34a3745918f237ffb1a657e000693947e81b65d6</t>
+          <t>0xa8ade64a3adb0ea38de67a61105ef31beb490d5a7287715b76ae124536d359cc</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>L19683447</t>
+          <t>L19683493</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -4248,17 +4216,17 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>1786212849</t>
+          <t>1786215674</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>1786212000</t>
+          <t>1786302000</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>298.72514</t>
+          <t>2.077922</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
@@ -4275,36 +4243,44 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0x0aeb4fe40f7d734cf244c144e6c064568b40b222193c9f93c641d1b31af3752e</t>
+          <t>0xff53df1f3446908699196d44fcdb8b39c1bd15c7ed519f0d730e55a51a6eb38f</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr"/>
+          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>16.89162</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>1.2588</t>
+          <t>1.3713</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Almirante Brown</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
           <t>Primera Nacional</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>Primera Nacional</t>
-        </is>
-      </c>
       <c r="I37" t="inlineStr">
         <is>
           <t>Almirante Brown vs Ciudad Bolivar</t>
@@ -4322,7 +4298,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>0xaa5316c6f6544d74142ad6db34a3745918f237ffb1a657e000693947e81b65d6</t>
+          <t>0x63a8bf73c1084ef223fdd1096dccd16232e7a455fad77f7f0891be1588ebeb88</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -4352,7 +4328,7 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>1786212805</t>
+          <t>1786215673</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
@@ -4362,7 +4338,7 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>65.281623</t>
+          <t>2.693603</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
@@ -4379,12 +4355,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0x383b895a5fe529a887369a0f113c516fdc7f6125d54381acf9695997ef22d039</t>
+          <t>0x249d52552e7acb9f472d2a4c48ab754622ba572903281739a3e10b4d509dccb0</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -4394,39 +4370,39 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>11.26905</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>1.745</t>
+          <t>1.2288</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Almirante Brown -1</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
           <t>Primera Nacional</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Almirante Brown vs Ciudad Bolivar</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
         <is>
           <t>Almirante Brown</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>Primera Nacional</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>Almirante Brown vs Ciudad Bolivar</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>Almirante Brown</t>
-        </is>
-      </c>
       <c r="K38" t="inlineStr">
         <is>
           <t>Ciudad Bolivar</t>
@@ -4434,7 +4410,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>0xaa5316c6f6544d74142ad6db34a3745918f237ffb1a657e000693947e81b65d6</t>
+          <t>0xa6a338c64f062bfd589e8d5d9cea45a27c9e64065f71f800e5966f81ce53c556</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -4464,7 +4440,7 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>1786211779</t>
+          <t>1786214209</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
@@ -4474,7 +4450,7 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>15.126242</t>
+          <t>6.295082</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
@@ -4491,12 +4467,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0xcfb6add6f8610a64ffc187beb9e16bf2bacb27b54a0f0aaefa6bfb437239b893</t>
+          <t>0xf65c55196eeb0d21e7e3866ad26f8c3f2fee2aef273ddde5423e31fb40a51469</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -4506,39 +4482,39 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>24.89998</t>
+          <t>121.81</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>1.745</t>
+          <t>1.4363</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Almirante Brown</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
           <t>Primera Nacional</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Almirante Brown vs Ciudad Bolivar</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
         <is>
           <t>Almirante Brown</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>Primera Nacional</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>Almirante Brown vs Ciudad Bolivar</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>Almirante Brown</t>
-        </is>
-      </c>
       <c r="K39" t="inlineStr">
         <is>
           <t>Ciudad Bolivar</t>
@@ -4546,7 +4522,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>0xaa5316c6f6544d74142ad6db34a3745918f237ffb1a657e000693947e81b65d6</t>
+          <t>0x63a8bf73c1084ef223fdd1096dccd16232e7a455fad77f7f0891be1588ebeb88</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -4576,7 +4552,7 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>1786211777</t>
+          <t>1786213844</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
@@ -4586,7 +4562,7 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>33.422792</t>
+          <t>279.22063</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
@@ -4603,12 +4579,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0xd41652604437a4e92e0d78b653d4d49d8dedd2e153d1340dad89b9b93e182a48</t>
+          <t>0x1bb20a2bf22e4fe06b44c06b9c2caa21f3f2a7c9d0cce1a2346f79e76022cd1f</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>0xf4a8B27C9a13e298D65b5Cc072d252816B799C81</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -4618,22 +4594,22 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>21.05</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>1.4163</t>
+          <t>1.4363</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Atl. Rafaela</t>
+          <t>Almirante Brown -0.5</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -4643,27 +4619,27 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Atl. Rafaela vs Chacarita Juniors</t>
+          <t>Almirante Brown vs Ciudad Bolivar</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Atl. Rafaela</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Ciudad Bolivar</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>0xe738e9ba05492fab73eaaf6da211b84caadc72b08b26f1cd30fa8737e283bb44</t>
+          <t>0xfa00d2f0c7b5053ee336b303a0e7ad9cec0b8d539367773b7efee5c86cb2b59d</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>L19683450</t>
+          <t>L19683447</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -4688,17 +4664,17 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>1786211028</t>
+          <t>1786213843</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>1786215600</t>
+          <t>1786212000</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>2.402402</t>
+          <t>48.252149</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
@@ -4715,28 +4691,28 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0x562fd7c6419c807ed04d3cacac95f861805f96704bd535e265399fb9d2c2b609</t>
+          <t>0xc51052f8e449b4d56cc87b697bfc8eb0d3a88ae218dee1da3d725fa94163bc75</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr">
         <is>
-          <t>5.32</t>
+          <t>77.29513</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>1.405</t>
+          <t>1.2588</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
+          <t>Primera Nacional</t>
         </is>
       </c>
       <c r="G41" t="inlineStr"/>
@@ -4747,27 +4723,27 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Estudiantes de Caseros vs Deportivo Madryn</t>
+          <t>Almirante Brown vs Ciudad Bolivar</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Estudiantes de Caseros</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Ciudad Bolivar</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>0xd61509e26f8645bb9780672f942c72c4b7dab577c2a01f04e1e09bce9b828765</t>
+          <t>0xaa5316c6f6544d74142ad6db34a3745918f237ffb1a657e000693947e81b65d6</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>L19683453</t>
+          <t>L19683447</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -4792,7 +4768,7 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>1786210845</t>
+          <t>1786212849</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
@@ -4802,7 +4778,7 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>13.135802</t>
+          <t>298.72514</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
@@ -4819,39 +4795,31 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0x0bb7a6822220bf40d7b279f99a54f46025f393ba95bb38b6d6dc98192886b3ed</t>
+          <t>0x0aeb4fe40f7d734cf244c144e6c064568b40b222193c9f93c641d1b31af3752e</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>0xf4a8B27C9a13e298D65b5Cc072d252816B799C81</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr">
         <is>
-          <t>0.99999</t>
+          <t>16.89162</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>1.5513</t>
+          <t>1.2588</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>Agropecuario</t>
-        </is>
-      </c>
+          <t>Primera Nacional</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -4859,27 +4827,27 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Agropecuario vs Atletico Guemes</t>
+          <t>Almirante Brown vs Ciudad Bolivar</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>Atletico Guemes</t>
+          <t>Ciudad Bolivar</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>0xae66c7fab3c9c76fbc29d9e9778ef4845d8a6b8d092cff34320f100020113c49</t>
+          <t>0xaa5316c6f6544d74142ad6db34a3745918f237ffb1a657e000693947e81b65d6</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>L19683451</t>
+          <t>L19683447</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -4904,7 +4872,7 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>1786205982</t>
+          <t>1786212805</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
@@ -4914,7 +4882,7 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>1.814041</t>
+          <t>65.281623</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
@@ -4931,12 +4899,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0xe17b2546f4b90c8647ba975c279e39dec1fda5a003adfb8a2b39bb12a3519b10</t>
+          <t>0x383b895a5fe529a887369a0f113c516fdc7f6125d54381acf9695997ef22d039</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>0xf4a8B27C9a13e298D65b5Cc072d252816B799C81</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -4946,22 +4914,22 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>11.26905</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>1.3613</t>
+          <t>1.745</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Primera Nacional</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Tie</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -4986,7 +4954,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>0xd5906ce08d61f7c5ee45fcebd2c8baeed5558387398ea332817a4b632f439b6d</t>
+          <t>0xaa5316c6f6544d74142ad6db34a3745918f237ffb1a657e000693947e81b65d6</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -5016,7 +4984,7 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>1786205963</t>
+          <t>1786211779</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
@@ -5026,7 +4994,7 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>2.768166</t>
+          <t>15.126242</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
@@ -5043,12 +5011,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0xcfe218822e89cbef5841f3045f551cc65acf353d8e240f943e2b61c54ea79a68</t>
+          <t>0xcfb6add6f8610a64ffc187beb9e16bf2bacb27b54a0f0aaefa6bfb437239b893</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>0xf4a8B27C9a13e298D65b5Cc072d252816B799C81</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -5058,22 +5026,22 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>24.89998</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>1.3337</t>
+          <t>1.745</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Primera Nacional</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Tie</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -5083,27 +5051,27 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Estudiantes de Caseros vs Deportivo Madryn</t>
+          <t>Almirante Brown vs Ciudad Bolivar</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Estudiantes de Caseros</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Ciudad Bolivar</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>0xf238b96ec9e2421db79973de945f1fc0c3f8bb99c31cda32d011ebaabfd2db86</t>
+          <t>0xaa5316c6f6544d74142ad6db34a3745918f237ffb1a657e000693947e81b65d6</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>L19683453</t>
+          <t>L19683447</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -5128,7 +5096,7 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>1786205938</t>
+          <t>1786211777</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
@@ -5138,7 +5106,7 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>2.996255</t>
+          <t>33.422792</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
@@ -5155,31 +5123,39 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0x1b9fcb29010a212f74af57040114154e78748f06a4d826be4397ddadb45ac31b</t>
+          <t>0xd41652604437a4e92e0d78b653d4d49d8dedd2e153d1340dad89b9b93e182a48</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr"/>
+          <t>0xf4a8B27C9a13e298D65b5Cc072d252816B799C81</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>21.69</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>1.4512</t>
+          <t>1.4163</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Atl. Rafaela</t>
+        </is>
+      </c>
       <c r="H45" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -5187,27 +5163,27 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Almirante Brown vs Ciudad Bolivar</t>
+          <t>Atl. Rafaela vs Chacarita Juniors</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Atl. Rafaela</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>Ciudad Bolivar</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>0xbbcaa253cd967fbf933ff0d87a6f9744cafec0ed59dad5f1f76332aab01a3fa5</t>
+          <t>0xe738e9ba05492fab73eaaf6da211b84caadc72b08b26f1cd30fa8737e283bb44</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>L19683447</t>
+          <t>L19683450</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -5232,17 +5208,17 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>1786190525</t>
+          <t>1786211028</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>1786212000</t>
+          <t>1786215600</t>
         </is>
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>48.066482</t>
+          <t>2.402402</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
@@ -5259,23 +5235,23 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0x3177792dd6a7185e37ae06612104cf5a35d137d7f535a889a83a7e9b7c174506</t>
+          <t>0x562fd7c6419c807ed04d3cacac95f861805f96704bd535e265399fb9d2c2b609</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr">
         <is>
-          <t>18.35495</t>
+          <t>5.32</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>1.4963</t>
+          <t>1.405</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -5291,27 +5267,27 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Almirante Brown vs Ciudad Bolivar</t>
+          <t>Estudiantes de Caseros vs Deportivo Madryn</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Estudiantes de Caseros</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>Ciudad Bolivar</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>0xbbcaa253cd967fbf933ff0d87a6f9744cafec0ed59dad5f1f76332aab01a3fa5</t>
+          <t>0xd61509e26f8645bb9780672f942c72c4b7dab577c2a01f04e1e09bce9b828765</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>L19683447</t>
+          <t>L19683453</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -5336,7 +5312,7 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>1786190491</t>
+          <t>1786210845</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
@@ -5346,7 +5322,7 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>36.987305</t>
+          <t>13.135802</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
@@ -5363,12 +5339,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0x54ed4ee2a6ebdab49498137f1accea542ead806f21430a0a771cc4872a044e43</t>
+          <t>0x0bb7a6822220bf40d7b279f99a54f46025f393ba95bb38b6d6dc98192886b3ed</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
+          <t>0xf4a8B27C9a13e298D65b5Cc072d252816B799C81</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -5378,22 +5354,22 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>20.10741</t>
+          <t>0.99999</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>1.5437</t>
+          <t>1.5513</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Over 1.5</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -5403,27 +5379,27 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Almirante Brown vs Ciudad Bolivar</t>
+          <t>Agropecuario vs Atletico Guemes</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>Ciudad Bolivar</t>
+          <t>Atletico Guemes</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>0xbbcaa253cd967fbf933ff0d87a6f9744cafec0ed59dad5f1f76332aab01a3fa5</t>
+          <t>0xae66c7fab3c9c76fbc29d9e9778ef4845d8a6b8d092cff34320f100020113c49</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>L19683447</t>
+          <t>L19683451</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -5448,7 +5424,7 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>1786190485</t>
+          <t>1786205982</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
@@ -5458,7 +5434,7 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>36.979145</t>
+          <t>1.814041</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
@@ -5475,31 +5451,39 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0x544fe5c906328d009917b591611ff3438cef85f8b42d9f67732cbbd5eabbb8dd</t>
+          <t>0xe17b2546f4b90c8647ba975c279e39dec1fda5a003adfb8a2b39bb12a3519b10</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr"/>
+          <t>0xf4a8B27C9a13e298D65b5Cc072d252816B799C81</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>21.69</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>1.4512</t>
+          <t>1.3613</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H48" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -5522,7 +5506,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>0xbbcaa253cd967fbf933ff0d87a6f9744cafec0ed59dad5f1f76332aab01a3fa5</t>
+          <t>0xd5906ce08d61f7c5ee45fcebd2c8baeed5558387398ea332817a4b632f439b6d</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -5552,7 +5536,7 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>1786190485</t>
+          <t>1786205963</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
@@ -5562,7 +5546,7 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>48.066482</t>
+          <t>2.768166</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
@@ -5579,31 +5563,39 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0xb2f3ea804e1760a01d3a93678f0e2119f1ea2a9db0dc4711a06cc7bcba42b0c2</t>
+          <t>0xcfe218822e89cbef5841f3045f551cc65acf353d8e240f943e2b61c54ea79a68</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr"/>
+          <t>0xf4a8B27C9a13e298D65b5Cc072d252816B799C81</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>17.47</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>1.405</t>
+          <t>1.3337</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H49" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -5626,7 +5618,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>0xd61509e26f8645bb9780672f942c72c4b7dab577c2a01f04e1e09bce9b828765</t>
+          <t>0xf238b96ec9e2421db79973de945f1fc0c3f8bb99c31cda32d011ebaabfd2db86</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -5656,7 +5648,7 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>1786190461</t>
+          <t>1786205938</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
@@ -5666,7 +5658,7 @@
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>43.135802</t>
+          <t>2.996255</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
@@ -5683,7 +5675,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0xa7eafbb77d425fc2347b4ee3e4f4e1b85f6d0f81420605db76ebfeeaa793a428</t>
+          <t>0x1b9fcb29010a212f74af57040114154e78748f06a4d826be4397ddadb45ac31b</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5760,7 +5752,7 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>1786190458</t>
+          <t>1786190525</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
@@ -5787,110 +5779,638 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
+          <t>0x3177792dd6a7185e37ae06612104cf5a35d137d7f535a889a83a7e9b7c174506</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr"/>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>18.35495</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>1.4963</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Primera Nacional</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Almirante Brown vs Ciudad Bolivar</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>Almirante Brown</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Ciudad Bolivar</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>0xbbcaa253cd967fbf933ff0d87a6f9744cafec0ed59dad5f1f76332aab01a3fa5</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>L19683447</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>1786190491</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>1786212000</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>36.987305</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>0x54ed4ee2a6ebdab49498137f1accea542ead806f21430a0a771cc4872a044e43</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>20.10741</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>1.5437</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Over 1.5</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Primera Nacional</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>Almirante Brown vs Ciudad Bolivar</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>Almirante Brown</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Ciudad Bolivar</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>0xbbcaa253cd967fbf933ff0d87a6f9744cafec0ed59dad5f1f76332aab01a3fa5</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>L19683447</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>1786190485</t>
+        </is>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>1786212000</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>36.979145</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>0x544fe5c906328d009917b591611ff3438cef85f8b42d9f67732cbbd5eabbb8dd</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr"/>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>21.69</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>1.4512</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Primera Nacional</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Almirante Brown vs Ciudad Bolivar</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>Almirante Brown</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Ciudad Bolivar</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>0xbbcaa253cd967fbf933ff0d87a6f9744cafec0ed59dad5f1f76332aab01a3fa5</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>L19683447</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>1786190485</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>1786212000</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>48.066482</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>0xb2f3ea804e1760a01d3a93678f0e2119f1ea2a9db0dc4711a06cc7bcba42b0c2</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr"/>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>17.47</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>1.405</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Primera Nacional</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Estudiantes de Caseros vs Deportivo Madryn</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>Estudiantes de Caseros</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Deportivo Madryn</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>0xd61509e26f8645bb9780672f942c72c4b7dab577c2a01f04e1e09bce9b828765</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>L19683453</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>1786190461</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>1786212000</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>43.135802</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>0xa7eafbb77d425fc2347b4ee3e4f4e1b85f6d0f81420605db76ebfeeaa793a428</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr"/>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>21.69</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>1.4512</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Primera Nacional</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>Almirante Brown vs Ciudad Bolivar</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>Almirante Brown</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Ciudad Bolivar</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>0xbbcaa253cd967fbf933ff0d87a6f9744cafec0ed59dad5f1f76332aab01a3fa5</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>L19683447</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>1786190458</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>1786212000</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>48.066482</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
           <t>0x5c5b512ea725fac30531bf5fe91f34f3ccc0eeff23890c18f25c3f329007c589</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
+      <c r="B56" t="inlineStr">
         <is>
           <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
         <is>
           <t>1.3638</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
+      <c r="F56" t="inlineStr">
         <is>
           <t>1X2</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr">
+      <c r="G56" t="inlineStr">
         <is>
           <t>Tie</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
+      <c r="H56" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr">
+      <c r="I56" t="inlineStr">
         <is>
           <t>Almirante Brown vs Ciudad Bolivar</t>
         </is>
       </c>
-      <c r="J51" t="inlineStr">
+      <c r="J56" t="inlineStr">
         <is>
           <t>Almirante Brown</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr">
+      <c r="K56" t="inlineStr">
         <is>
           <t>Ciudad Bolivar</t>
         </is>
       </c>
-      <c r="L51" t="inlineStr">
+      <c r="L56" t="inlineStr">
         <is>
           <t>0xd5906ce08d61f7c5ee45fcebd2c8baeed5558387398ea332817a4b632f439b6d</t>
         </is>
       </c>
-      <c r="M51" t="inlineStr">
+      <c r="M56" t="inlineStr">
         <is>
           <t>L19683447</t>
         </is>
       </c>
-      <c r="N51" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O51" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P51" t="inlineStr">
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q51" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R51" t="inlineStr">
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R56" t="inlineStr">
         <is>
           <t>1786125660</t>
         </is>
       </c>
-      <c r="S51" t="inlineStr">
+      <c r="S56" t="inlineStr">
         <is>
           <t>1786212000</t>
         </is>
       </c>
-      <c r="T51" t="inlineStr">
+      <c r="T56" t="inlineStr">
         <is>
           <t>2.749141</t>
         </is>
       </c>
-      <c r="U51" t="inlineStr">
+      <c r="U56" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V51" t="inlineStr">
+      <c r="V56" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/Primera Nacional/trades.xlsx
+++ b/data/sxbet/ligas/Primera Nacional/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V56"/>
+  <dimension ref="A1:V65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,7 +531,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0xae3b69e222676c5f5930a25ee6fc677945888fbd4b45894897e8c0b45b324e25</t>
+          <t>0x972e5a678ec56c15f03cbf0d14d7070ad000111adf76887dc34cc27780792e32</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -542,17 +542,17 @@
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>12.72</t>
+          <t>24.07997</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.4512</t>
+          <t>1.8675</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G2" t="inlineStr"/>
@@ -563,27 +563,27 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>CA Los Andes vs Ferro Carril Oeste</t>
+          <t>Godoy Cruz vs Chaco For Ever</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>CA Los Andes</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0x555a8472fba9017aa83a61e5e7cf7b05dc2822d1d1cc6174412760fc412637f7</t>
+          <t>0x9c19e4c1fd9646506f8ea14e2b1be19b49a5ab4dc1a7bf40167705a4ae2b338b</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>L19659153</t>
+          <t>L19683484</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -608,17 +608,17 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1786288547</t>
+          <t>1786297771</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>1786296600</t>
+          <t>1786303800</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>28.188366</t>
+          <t>27.75789</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -635,31 +635,39 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0x4bb954aaa9ecad68c0eb53f2341bb75f7b8daa072a3f151571ab136be22b78df</t>
+          <t>0x1da1f134f1ec859a8260a79216b9030b9f0b715d9a51d09741ff884111dcde2b</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0x71CE4A2C734a76f4C86A0D80122C4014c1F52F6e</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
+          <t>0x311AE302984D8b1cf53D6bfB0a6672f05c423AE6</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>29.37999</t>
+          <t>37.76669</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.6113</t>
+          <t>1.5837</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr"/>
+          <t>Asian Handicap (-0.5)</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Godoy Cruz -0.5</t>
+        </is>
+      </c>
       <c r="H3" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -667,27 +675,27 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>CA Los Andes vs Ferro Carril Oeste</t>
+          <t>Godoy Cruz vs Chaco For Ever</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>CA Los Andes</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0x653af58a9c77cb072171a76bcd9ca8adee427601f3ecd186c8154c81f8736395</t>
+          <t>0xb2c04ce7cffc1005eb6199d3c34d31b109e8af04a357b4f8eb9f6b8362ba33c2</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>L19659153</t>
+          <t>L19683484</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -712,17 +720,17 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1786288517</t>
+          <t>1786297676</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>1786296600</t>
+          <t>1786303800</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>48.065423</t>
+          <t>64.696685</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -739,7 +747,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0xd5a2ddd8c8b6cc9bdb1c507276d3a192a5f24d46e2d3c01bfb07011263030bdd</t>
+          <t>0xfccc36b3cd4c4e2276a7540f5bb389b40f91c9998d31903af7864027f93d335e</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -747,51 +755,59 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>5.67</t>
+          <t>56.81</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.2975</t>
+          <t>1.3588</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
           <t>Primera Nacional</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Primera Nacional</t>
-        </is>
-      </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>CA Colegiales vs Patronato</t>
+          <t>CA Los Andes vs Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>CA Colegiales</t>
+          <t>CA Los Andes</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0x710e5bf3f6759bd93c59fc8788916c16c7302071968dfba2d053e2d10f7858bf</t>
+          <t>0x834e52f6ff115c72424372c131d41b8d94cffe6e0131918e3f85e2146509d14b</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>L19683449</t>
+          <t>L19659153</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -816,17 +832,17 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1786288450</t>
+          <t>1786297373</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>1786298400</t>
+          <t>1786296600</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>19.058824</t>
+          <t>158.355401</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -843,7 +859,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0xad9f4feea88f83ae2e46756e7d54faa300a82e055c196c70c84019780ecb560c</t>
+          <t>0x48c1aed95e65b653ffb51380d6066948766a0030b4adf3bf05d152a5766c29cf</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -854,17 +870,17 @@
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>21.69</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.4512</t>
+          <t>1.6425</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
+          <t>Asian Handicap (-1.5)</t>
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
@@ -875,27 +891,27 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>CA Los Andes vs Ferro Carril Oeste</t>
+          <t>Colon de Santa Fe vs San Telmo</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>CA Los Andes</t>
+          <t>Colon de Santa Fe</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0x555a8472fba9017aa83a61e5e7cf7b05dc2822d1d1cc6174412760fc412637f7</t>
+          <t>0x79905ae58e04af69981e4a95c3d57b98dc3c1dd1d3e7aeb4e6a7640714001f3b</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>L19659153</t>
+          <t>L19683494</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -920,17 +936,17 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1786288436</t>
+          <t>1786293588</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>1786296600</t>
+          <t>1786300200</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>48.066482</t>
+          <t>15.564202</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -947,28 +963,28 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0x168e5ea2716a187c94a1c77c4c8b2523b31163ed118e4986c68c79a21d013932</t>
+          <t>0x3d4ee2d1cf7066373ffe56d01727fc04ce4ae0e1203194a2877d6ba90d9d4fcb</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>29.38716</t>
+          <t>16.53143</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.6113</t>
+          <t>1.3438</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
+          <t>Primera Nacional</t>
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
@@ -979,27 +995,27 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>CA Los Andes vs Ferro Carril Oeste</t>
+          <t>Atlanta vs Temperley</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>CA Los Andes</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0x653af58a9c77cb072171a76bcd9ca8adee427601f3ecd186c8154c81f8736395</t>
+          <t>0xc67c753c7ce425d2b225c54e0abf1308c3593fa6789a95fd59198b3a0f7a3ddd</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>L19659153</t>
+          <t>L19683448</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1024,17 +1040,17 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1786288436</t>
+          <t>1786293565</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>1786296600</t>
+          <t>1786294800</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>48.077153</t>
+          <t>48.091433</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1051,39 +1067,31 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0x680d5db234b802aa2845f16e9d23d635dd89870065c6bfb6f6f1bde25c321bae</t>
+          <t>0x5decd74680fc49716c54620aa922234edac874fb77b6369067e932fb5a40aed8</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>24.36</t>
+          <t>16.98847</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.475</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>CA Colegiales -0.5</t>
-        </is>
-      </c>
+          <t>Primera Nacional</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -1091,27 +1099,27 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>CA Colegiales vs Patronato</t>
+          <t>San Martin Tucuman vs San Martín de San Juan</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>CA Colegiales</t>
+          <t>San Martin Tucuman</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>San Martín de San Juan</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0x50a3f0e4e982cdda0b9c4b9e2e1c50c67d93fbf7a068b43dbdf733c0b8d09050</t>
+          <t>0x4f02331cd42a68f65ea16d62aac0c6b123d9400d12a4d556f3a72df894da02fb</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>L19683449</t>
+          <t>L19682528</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1136,17 +1144,17 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1786287181</t>
+          <t>1786293511</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>1786298400</t>
+          <t>1786309200</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>51.284211</t>
+          <t>48.538486</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1163,7 +1171,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0x5a5b6f41ac2a593747a9419c020abd417423350c2cf0a14d8cb9ef8a25d04f18</t>
+          <t>0x6376c34d63b4968409b909753114511b32d1413abbfce5d71dcd6fa7bb384028</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1174,17 +1182,17 @@
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.81755</t>
+          <t>30.89</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.6325</t>
+          <t>1.6425</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>Asian Handicap (-1.5)</t>
         </is>
       </c>
       <c r="G8" t="inlineStr"/>
@@ -1195,27 +1203,27 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Quilmes vs Club Almagro</t>
+          <t>Colon de Santa Fe vs San Telmo</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Colon de Santa Fe</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Club Almagro</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0x86a790846c1cb1bed065ac37c41b727461e30e0a9e0f9e2370ef61f6213ed31f</t>
+          <t>0x79905ae58e04af69981e4a95c3d57b98dc3c1dd1d3e7aeb4e6a7640714001f3b</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>L19683499</t>
+          <t>L19683494</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1240,17 +1248,17 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1786284071</t>
+          <t>1786293434</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>1786305600</t>
+          <t>1786300200</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>13.940791</t>
+          <t>48.077821</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1267,7 +1275,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0x9ae6e679c8fc9ed20977676ba3160d389287dd8808ea2610d0f168f9c3a42c11</t>
+          <t>0xa534180ddbde4d456a67f71365d2341259c4ca0b20e45041701c1d345202335e</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1278,7 +1286,7 @@
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>21.58999</t>
+          <t>13.52</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1344,7 +1352,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1786284003</t>
+          <t>1786293430</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1354,7 +1362,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>34.134372</t>
+          <t>21.375494</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1371,7 +1379,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0x6771b333646b031b4dc4cfea8f533b040a6ed0a66012cdc416a7aaa5b89f7988</t>
+          <t>0xe6cbce05bf55e4a2647eb39e1cb6d7afdafec60905e09f42fb3552a02a5fcbd6</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1382,17 +1390,17 @@
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>19.2</t>
+          <t>16.88999</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.5425</t>
+          <t>1.6325</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G10" t="inlineStr"/>
@@ -1403,27 +1411,27 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Colon de Santa Fe vs San Telmo</t>
+          <t>Quilmes vs Club Almagro</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Colon de Santa Fe</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Club Almagro</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0x4b323aab38dd8f5096dcd1965ce7dc05c69ab73371e55e810b7a5aee356bf244</t>
+          <t>0x86a790846c1cb1bed065ac37c41b727461e30e0a9e0f9e2370ef61f6213ed31f</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>L19683494</t>
+          <t>L19683499</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1448,17 +1456,17 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1786283290</t>
+          <t>1786293428</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>1786300200</t>
+          <t>1786305600</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>35.391705</t>
+          <t>26.703542</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1475,7 +1483,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0x8809f3e942a9cc8dca00d48b07cfe53a328d6ba2b60742c63e144e3d8cf2eaa1</t>
+          <t>0xae3b69e222676c5f5930a25ee6fc677945888fbd4b45894897e8c0b45b324e25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1486,17 +1494,17 @@
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>23.25749</t>
+          <t>12.72</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.4838</t>
+          <t>1.4512</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
+          <t>Under/Over (1.5)</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
@@ -1507,27 +1515,27 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Colon de Santa Fe vs San Telmo</t>
+          <t>CA Los Andes vs Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Colon de Santa Fe</t>
+          <t>CA Los Andes</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0xc91217dfcd3944893195656945526d39efcd315aa93101aa312de5303c04d446</t>
+          <t>0x555a8472fba9017aa83a61e5e7cf7b05dc2822d1d1cc6174412760fc412637f7</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>L19683494</t>
+          <t>L19659153</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1552,17 +1560,17 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1786281248</t>
+          <t>1786288547</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>1786300200</t>
+          <t>1786296600</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>48.077499</t>
+          <t>28.188366</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1579,23 +1587,23 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0xe5b95b7ede820952a7e6f5c1b2139a8092b51c4de75567f117f1291461ec6fbe</t>
+          <t>0x4bb954aaa9ecad68c0eb53f2341bb75f7b8daa072a3f151571ab136be22b78df</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x71CE4A2C734a76f4C86A0D80122C4014c1F52F6e</t>
         </is>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>23.55844</t>
+          <t>29.37999</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.6113</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1611,27 +1619,27 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Colon de Santa Fe vs San Telmo</t>
+          <t>CA Los Andes vs Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Colon de Santa Fe</t>
+          <t>CA Los Andes</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>0xc91217dfcd3944893195656945526d39efcd315aa93101aa312de5303c04d446</t>
+          <t>0x653af58a9c77cb072171a76bcd9ca8adee427601f3ecd186c8154c81f8736395</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>L19683494</t>
+          <t>L19659153</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1656,17 +1664,17 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1786281243</t>
+          <t>1786288517</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>1786300200</t>
+          <t>1786296600</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>48.078449</t>
+          <t>48.065423</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1683,7 +1691,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0x4d872ac34cfff98634d3d50362fe725a3f4ea55d64ddd9e3d7d811b073f350ab</t>
+          <t>0xd5a2ddd8c8b6cc9bdb1c507276d3a192a5f24d46e2d3c01bfb07011263030bdd</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1694,17 +1702,17 @@
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>17.30813</t>
+          <t>5.67</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.2975</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
+          <t>Primera Nacional</t>
         </is>
       </c>
       <c r="G13" t="inlineStr"/>
@@ -1715,27 +1723,27 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Colon de Santa Fe vs San Telmo</t>
+          <t>CA Colegiales vs Patronato</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Colon de Santa Fe</t>
+          <t>CA Colegiales</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>0xd638a8ee6393f88ca538cc4fe6ac8cdf722bcfe6277a5ebd9387222eade88ba3</t>
+          <t>0x710e5bf3f6759bd93c59fc8788916c16c7302071968dfba2d053e2d10f7858bf</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>L19683494</t>
+          <t>L19683449</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1760,17 +1768,17 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1786281243</t>
+          <t>1786288450</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>1786300200</t>
+          <t>1786298400</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>48.078139</t>
+          <t>19.058824</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1787,7 +1795,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0x8f782cb5f7b30f6c129f6031ec6368ed75ea36897066f1761d9054013f56567d</t>
+          <t>0xad9f4feea88f83ae2e46756e7d54faa300a82e055c196c70c84019780ecb560c</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1798,17 +1806,17 @@
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>21.69</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1.4187</t>
+          <t>1.4512</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Primera Nacional</t>
+          <t>Under/Over (1.5)</t>
         </is>
       </c>
       <c r="G14" t="inlineStr"/>
@@ -1819,27 +1827,27 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Club Atletico Mitre de Santiago del Estero vs Defensores de Belgrano Buenos Aires</t>
+          <t>CA Los Andes vs Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Club Atletico Mitre de Santiago del Estero</t>
+          <t>CA Los Andes</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano Buenos Aires</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>0x2d371e1a8a9d98624f046ea3d7126e47308ffbc183b66b1e2fba81e5ae69d7dd</t>
+          <t>0x555a8472fba9017aa83a61e5e7cf7b05dc2822d1d1cc6174412760fc412637f7</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>L19683493</t>
+          <t>L19659153</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1864,17 +1872,17 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1786280425</t>
+          <t>1786288436</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>1786302000</t>
+          <t>1786296600</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>23.880597</t>
+          <t>48.066482</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -1891,7 +1899,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0xfe8890b155a19f7eb888456b555a7a6d8c293f8ecabeb69d2abd10210f520589</t>
+          <t>0x168e5ea2716a187c94a1c77c4c8b2523b31163ed118e4986c68c79a21d013932</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1902,12 +1910,12 @@
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>29.38716</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1.4475</t>
+          <t>1.6113</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1923,27 +1931,27 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Colon de Santa Fe vs San Telmo</t>
+          <t>CA Los Andes vs Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Colon de Santa Fe</t>
+          <t>CA Los Andes</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>0xc91217dfcd3944893195656945526d39efcd315aa93101aa312de5303c04d446</t>
+          <t>0x653af58a9c77cb072171a76bcd9ca8adee427601f3ecd186c8154c81f8736395</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>L19683494</t>
+          <t>L19659153</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -1968,17 +1976,17 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>1786280403</t>
+          <t>1786288436</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>1786300200</t>
+          <t>1786296600</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>22.346369</t>
+          <t>48.077153</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -1995,12 +2003,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0x60e023296ac2f9f58237fa345b3aa08fb4f997dd34c5384f371782bf7bbd5a40</t>
+          <t>0x680d5db234b802aa2845f16e9d23d635dd89870065c6bfb6f6f1bde25c321bae</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2010,22 +2018,22 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>26.11999</t>
+          <t>24.36</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1.5488</t>
+          <t>1.475</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
+          <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Over 2.0</t>
+          <t>CA Colegiales -0.5</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2035,27 +2043,27 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Colon de Santa Fe vs San Telmo</t>
+          <t>CA Colegiales vs Patronato</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Colon de Santa Fe</t>
+          <t>CA Colegiales</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>0xc91217dfcd3944893195656945526d39efcd315aa93101aa312de5303c04d446</t>
+          <t>0x50a3f0e4e982cdda0b9c4b9e2e1c50c67d93fbf7a068b43dbdf733c0b8d09050</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>L19683494</t>
+          <t>L19683449</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -2080,17 +2088,17 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1786280403</t>
+          <t>1786287181</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>1786300200</t>
+          <t>1786298400</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>47.599071</t>
+          <t>51.284211</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2107,7 +2115,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0x2d118800c100a2a41a19c2053cbf355561a08867f99163fb40955a4ab012ce39</t>
+          <t>0x5a5b6f41ac2a593747a9419c020abd417423350c2cf0a14d8cb9ef8a25d04f18</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2118,17 +2126,17 @@
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>20.07999</t>
+          <t>8.81755</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.7363</t>
+          <t>1.6325</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G17" t="inlineStr"/>
@@ -2139,27 +2147,27 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Godoy Cruz vs Chaco For Ever</t>
+          <t>Quilmes vs Club Almagro</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Club Almagro</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>0x60e111ebf03c4965ff049e67cf10f93f5cca143023c6104aab59162863b5b8a8</t>
+          <t>0x86a790846c1cb1bed065ac37c41b727461e30e0a9e0f9e2370ef61f6213ed31f</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>L19683484</t>
+          <t>L19683499</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -2184,17 +2192,17 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>1786279900</t>
+          <t>1786284071</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>1786303800</t>
+          <t>1786305600</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>27.273331</t>
+          <t>13.940791</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2211,7 +2219,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0x904e2e53a604aa6663de774d4bd9ddf8af7459ef1c4fa1bb14486300917ac211</t>
+          <t>0x9ae6e679c8fc9ed20977676ba3160d389287dd8808ea2610d0f168f9c3a42c11</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2219,31 +2227,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>3.96</t>
+          <t>21.58999</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.2837</t>
+          <t>1.6325</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -2251,27 +2251,27 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Godoy Cruz vs Chaco For Ever</t>
+          <t>Quilmes vs Club Almagro</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Club Almagro</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>0x08dce15d4ca4845359c2f121bce305fd3a0fe7422d497000c713e29463c6be79</t>
+          <t>0x86a790846c1cb1bed065ac37c41b727461e30e0a9e0f9e2370ef61f6213ed31f</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>L19683484</t>
+          <t>L19683499</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -2296,17 +2296,17 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>1786279851</t>
+          <t>1786284003</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>1786303800</t>
+          <t>1786305600</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>13.955947</t>
+          <t>34.134372</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2323,7 +2323,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0x19a6c0536a5dea88055519ff16050cdde80d42121bb75c5045e3b562a7c1d4bb</t>
+          <t>0x6771b333646b031b4dc4cfea8f533b040a6ed0a66012cdc416a7aaa5b89f7988</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2334,17 +2334,17 @@
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>7.50547</t>
+          <t>19.2</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1.4287</t>
+          <t>1.5425</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G19" t="inlineStr"/>
@@ -2355,27 +2355,27 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Godoy Cruz vs Chaco For Ever</t>
+          <t>Colon de Santa Fe vs San Telmo</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Colon de Santa Fe</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>0xa5f02d0d08d0dcc4818948397f0f26c77f90b87182cec4d62ab01f77352671a1</t>
+          <t>0x4b323aab38dd8f5096dcd1965ce7dc05c69ab73371e55e810b7a5aee356bf244</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>L19683484</t>
+          <t>L19683494</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -2400,17 +2400,17 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>1786279821</t>
+          <t>1786283290</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>1786303800</t>
+          <t>1786300200</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>17.505469</t>
+          <t>35.391705</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2427,7 +2427,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0x4c44e2c0c492a5115b342a42a552a040cb800bd582b07c12f1ea9161b861b487</t>
+          <t>0x8809f3e942a9cc8dca00d48b07cfe53a328d6ba2b60742c63e144e3d8cf2eaa1</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2438,12 +2438,12 @@
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>11.30844</t>
+          <t>23.25749</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.4838</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -2459,27 +2459,27 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Deportivo Moron vs Acassuso</t>
+          <t>Colon de Santa Fe vs San Telmo</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Deportivo Moron</t>
+          <t>Colon de Santa Fe</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0x108eaba0441fb45ec8e0073e945ae0ac1e138c933e4f2839816cd3198d7dd4d2</t>
+          <t>0xc91217dfcd3944893195656945526d39efcd315aa93101aa312de5303c04d446</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>L19683452</t>
+          <t>L19683494</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -2504,17 +2504,17 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>1786278950</t>
+          <t>1786281248</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>1786298400</t>
+          <t>1786300200</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>23.078449</t>
+          <t>48.077499</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2531,7 +2531,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0x5a5ccf0d5f6cbac6813d25e4e1e96b25b5c5a4ff8f6378d7e69d6bd3c29295ae</t>
+          <t>0xe5b95b7ede820952a7e6f5c1b2139a8092b51c4de75567f117f1291461ec6fbe</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2542,7 +2542,7 @@
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>12.25</t>
+          <t>23.55844</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -2563,27 +2563,27 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Deportivo Moron vs Acassuso</t>
+          <t>Colon de Santa Fe vs San Telmo</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Deportivo Moron</t>
+          <t>Colon de Santa Fe</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0x108eaba0441fb45ec8e0073e945ae0ac1e138c933e4f2839816cd3198d7dd4d2</t>
+          <t>0xc91217dfcd3944893195656945526d39efcd315aa93101aa312de5303c04d446</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>L19683452</t>
+          <t>L19683494</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -2608,17 +2608,17 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>1786278094</t>
+          <t>1786281243</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>1786298400</t>
+          <t>1786300200</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>48.078449</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -2635,7 +2635,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0x5f3419242a87ff17c0cb508ade95d27a54429124d36280a1dff2efa2fa0b3510</t>
+          <t>0x4d872ac34cfff98634d3d50362fe725a3f4ea55d64ddd9e3d7d811b073f350ab</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2646,17 +2646,17 @@
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
-          <t>20.41999</t>
+          <t>17.30813</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1.7087</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (1.5)</t>
         </is>
       </c>
       <c r="G22" t="inlineStr"/>
@@ -2667,27 +2667,27 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>CA Los Andes vs Ferro Carril Oeste</t>
+          <t>Colon de Santa Fe vs San Telmo</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>CA Los Andes</t>
+          <t>Colon de Santa Fe</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0x31115553050eabb8d3f6a72cf2865c16175783383dcfc674615e74ed88cabaee</t>
+          <t>0xd638a8ee6393f88ca538cc4fe6ac8cdf722bcfe6277a5ebd9387222eade88ba3</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>L19659153</t>
+          <t>L19683494</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -2712,17 +2712,17 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>1786277884</t>
+          <t>1786281243</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>1786296600</t>
+          <t>1786300200</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>28.811273</t>
+          <t>48.078139</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -2739,7 +2739,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0xe6b14424302d9ef7ea2000cef83e38549f6a38c12d57faa6dd76dd84e631a5ca</t>
+          <t>0x8f782cb5f7b30f6c129f6031ec6368ed75ea36897066f1761d9054013f56567d</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2750,17 +2750,17 @@
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>12.13</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1.3613</t>
+          <t>1.4187</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
+          <t>Primera Nacional</t>
         </is>
       </c>
       <c r="G23" t="inlineStr"/>
@@ -2771,27 +2771,27 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Deportivo Moron vs Acassuso</t>
+          <t>Club Atletico Mitre de Santiago del Estero vs Defensores de Belgrano Buenos Aires</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Deportivo Moron</t>
+          <t>Club Atletico Mitre de Santiago del Estero</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Defensores de Belgrano Buenos Aires</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0x3f34d112cfb9f093c57a3e094be078f9eea2715f97797e20d86942d58f5cc8d6</t>
+          <t>0x2d371e1a8a9d98624f046ea3d7126e47308ffbc183b66b1e2fba81e5ae69d7dd</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>L19683452</t>
+          <t>L19683493</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -2816,17 +2816,17 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>1786277708</t>
+          <t>1786280425</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>1786298400</t>
+          <t>1786302000</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>33.577855</t>
+          <t>23.880597</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -2843,7 +2843,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0xd7a2e43ba1564f619200938b384123dd68adb783742fc7b32ee335ee489d1302</t>
+          <t>0xfe8890b155a19f7eb888456b555a7a6d8c293f8ecabeb69d2abd10210f520589</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2854,12 +2854,12 @@
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
-          <t>10.58</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1.485</t>
+          <t>1.4475</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -2875,27 +2875,27 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Deportivo Moron vs Acassuso</t>
+          <t>Colon de Santa Fe vs San Telmo</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Deportivo Moron</t>
+          <t>Colon de Santa Fe</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0x108eaba0441fb45ec8e0073e945ae0ac1e138c933e4f2839816cd3198d7dd4d2</t>
+          <t>0xc91217dfcd3944893195656945526d39efcd315aa93101aa312de5303c04d446</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>L19683452</t>
+          <t>L19683494</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -2920,17 +2920,17 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>1786277679</t>
+          <t>1786280403</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>1786298400</t>
+          <t>1786300200</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>21.814433</t>
+          <t>22.346369</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -2947,7 +2947,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0xb25fa423ffb1a1464f100f2a2e9a1beac36661b9e37c8b09ecc7d3fd5a80312f</t>
+          <t>0x60e023296ac2f9f58237fa345b3aa08fb4f997dd34c5384f371782bf7bbd5a40</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2955,15 +2955,19 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr"/>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>25.88</t>
+          <t>26.11999</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1.6038</t>
+          <t>1.5488</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -2971,7 +2975,11 @@
           <t>Under/Over (2)</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Over 2.0</t>
+        </is>
+      </c>
       <c r="H25" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -2979,27 +2987,27 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>CA Colegiales vs Patronato</t>
+          <t>Colon de Santa Fe vs San Telmo</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>CA Colegiales</t>
+          <t>Colon de Santa Fe</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0x18dd2fdd93f5029a20e6a76c47c4f0e5c3c25768ad7f1b46a833287f8b7fcc13</t>
+          <t>0xc91217dfcd3944893195656945526d39efcd315aa93101aa312de5303c04d446</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>L19683449</t>
+          <t>L19683494</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -3024,17 +3032,17 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>1786277040</t>
+          <t>1786280403</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>1786298400</t>
+          <t>1786300200</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>42.865424</t>
+          <t>47.599071</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3051,7 +3059,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0xfe815be8a10a6ad2cda012e463a244232a6f6c80544018f6dda52d723946b659</t>
+          <t>0x2d118800c100a2a41a19c2053cbf355561a08867f99163fb40955a4ab012ce39</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3062,17 +3070,17 @@
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
-          <t>29.02571</t>
+          <t>20.07999</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1.6038</t>
+          <t>1.7363</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
+          <t>Asian Handicap (-1.5)</t>
         </is>
       </c>
       <c r="G26" t="inlineStr"/>
@@ -3083,27 +3091,27 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>CA Colegiales vs Patronato</t>
+          <t>Godoy Cruz vs Chaco For Ever</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>CA Colegiales</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>0x18dd2fdd93f5029a20e6a76c47c4f0e5c3c25768ad7f1b46a833287f8b7fcc13</t>
+          <t>0x60e111ebf03c4965ff049e67cf10f93f5cca143023c6104aab59162863b5b8a8</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>L19683449</t>
+          <t>L19683484</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -3128,17 +3136,17 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>1786276809</t>
+          <t>1786279900</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>1786298400</t>
+          <t>1786303800</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>48.07571</t>
+          <t>27.273331</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -3155,7 +3163,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0xdb83c52876b68624e093c25e35d11910f4fbef2394ff947b658f8ea5cdb3fa88</t>
+          <t>0x904e2e53a604aa6663de774d4bd9ddf8af7459ef1c4fa1bb14486300917ac211</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3163,23 +3171,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr"/>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>16.96</t>
+          <t>3.96</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1.4463</t>
+          <t>1.2837</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H27" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -3187,27 +3203,27 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>CA Colegiales vs Patronato</t>
+          <t>Godoy Cruz vs Chaco For Ever</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>CA Colegiales</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>0x30a6561de28b35c5bb0557dcbfc7b23e7a62558d3b0f5cfcafb67d7a07e0dd21</t>
+          <t>0x08dce15d4ca4845359c2f121bce305fd3a0fe7422d497000c713e29463c6be79</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>L19683449</t>
+          <t>L19683484</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -3232,17 +3248,17 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>1786276809</t>
+          <t>1786279851</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>1786298400</t>
+          <t>1786303800</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>38.005602</t>
+          <t>13.955947</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -3259,27 +3275,23 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0x0847a2541998eecfe02d138796b14ef3d6719061787498f4888f6e14c0d196ff</t>
+          <t>0x19a6c0536a5dea88055519ff16050cdde80d42121bb75c5045e3b562a7c1d4bb</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>0xf068eF8DF8f47185D02d59Bb33d9eC7A057a571E</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
-          <t>38.54</t>
+          <t>7.50547</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>1.125</t>
+          <t>1.4287</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -3287,11 +3299,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>Club Almagro</t>
-        </is>
-      </c>
+      <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -3299,27 +3307,27 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Quilmes vs Club Almagro</t>
+          <t>Godoy Cruz vs Chaco For Ever</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>Club Almagro</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>0x03ed0858b563c1becf38b195ad94b1a84eb89c3ca8ca10b1a34220bff142f9b2</t>
+          <t>0xa5f02d0d08d0dcc4818948397f0f26c77f90b87182cec4d62ab01f77352671a1</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>L19683499</t>
+          <t>L19683484</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -3344,17 +3352,17 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>1786270828</t>
+          <t>1786279821</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>1786305600</t>
+          <t>1786303800</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>308.32</t>
+          <t>17.505469</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -3371,7 +3379,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0x2121e08c4ea1fe2d49a3bb388fba9e232ef9c06335c04e5eae0bf7766975512a</t>
+          <t>0x4c44e2c0c492a5115b342a42a552a040cb800bd582b07c12f1ea9161b861b487</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3379,31 +3387,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
-          <t>30.06</t>
+          <t>11.30844</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>1.6262</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>Colon de Santa Fe</t>
-        </is>
-      </c>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -3411,27 +3411,27 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Colon de Santa Fe vs San Telmo</t>
+          <t>Deportivo Moron vs Acassuso</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Colon de Santa Fe</t>
+          <t>Deportivo Moron</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>0x1a11ec80edeaae24566c4f4f891cc2afc56b377b24997a6e8ee533eeaaad5c92</t>
+          <t>0x108eaba0441fb45ec8e0073e945ae0ac1e138c933e4f2839816cd3198d7dd4d2</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>L19683494</t>
+          <t>L19683452</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -3456,17 +3456,17 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>1786253941</t>
+          <t>1786278950</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>1786300200</t>
+          <t>1786298400</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>48.0</t>
+          <t>23.078449</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -3483,39 +3483,31 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0x4e811c319e5e3a1fc1968ce0f31b4c15eb7222daa616252d99f9abc611408746</t>
+          <t>0x5a5ccf0d5f6cbac6813d25e4e1e96b25b5c5a4ff8f6378d7e69d6bd3c29295ae</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>0x155C76202e45BE70c50bfeD7eAeA3B98e7716Ff7</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>12.25</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1.2925</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -3523,27 +3515,27 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Colon de Santa Fe vs San Telmo</t>
+          <t>Deportivo Moron vs Acassuso</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Colon de Santa Fe</t>
+          <t>Deportivo Moron</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>0x2e49527408facf21253a0a1eafe51280b82e4c31919e91a396332f19ec366401</t>
+          <t>0x108eaba0441fb45ec8e0073e945ae0ac1e138c933e4f2839816cd3198d7dd4d2</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>L19683494</t>
+          <t>L19683452</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -3568,17 +3560,17 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>1786243741</t>
+          <t>1786278094</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>1786300200</t>
+          <t>1786298400</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>3.418803</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -3595,27 +3587,23 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0xb8631aeb398192a03386505542f05fa15e34db501204baa8745a4d4b5c1651b7</t>
+          <t>0x5f3419242a87ff17c0cb508ade95d27a54429124d36280a1dff2efa2fa0b3510</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>0x155C76202e45BE70c50bfeD7eAeA3B98e7716Ff7</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
-          <t>0.99999</t>
+          <t>20.41999</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1.6538</t>
+          <t>1.7087</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -3623,11 +3611,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>Deportivo Moron</t>
-        </is>
-      </c>
+      <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -3635,27 +3619,27 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Deportivo Moron vs Acassuso</t>
+          <t>CA Los Andes vs Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Deportivo Moron</t>
+          <t>CA Los Andes</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>0x7514a255ce41be3c5db9f8849ba04e78dab80f02d1fe78c2aae82bbc843a9745</t>
+          <t>0x31115553050eabb8d3f6a72cf2865c16175783383dcfc674615e74ed88cabaee</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>L19683452</t>
+          <t>L19659153</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -3680,17 +3664,17 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>1786243225</t>
+          <t>1786277884</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>1786298400</t>
+          <t>1786296600</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>1.529621</t>
+          <t>28.811273</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -3707,28 +3691,28 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0xd3b94d194e43cc84f0a1b82723594ea6689a6aa2a4a7dccbc8a3d19fc321e49b</t>
+          <t>0xe6b14424302d9ef7ea2000cef83e38549f6a38c12d57faa6dd76dd84e631a5ca</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>12.13</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>1.5238</t>
+          <t>1.3613</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
+          <t>Under/Over (1.5)</t>
         </is>
       </c>
       <c r="G32" t="inlineStr"/>
@@ -3754,7 +3738,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0x108eaba0441fb45ec8e0073e945ae0ac1e138c933e4f2839816cd3198d7dd4d2</t>
+          <t>0x3f34d112cfb9f093c57a3e094be078f9eea2715f97797e20d86942d58f5cc8d6</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -3784,7 +3768,7 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>1786225000</t>
+          <t>1786277708</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
@@ -3794,7 +3778,7 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>1.909308</t>
+          <t>33.577855</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -3811,39 +3795,31 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0x86f4b24298f4c19f9f856cb19af2a260f24dc2d391f252248469436057ea1d1a</t>
+          <t>0xd7a2e43ba1564f619200938b384123dd68adb783742fc7b32ee335ee489d1302</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10.58</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>1.5263</t>
+          <t>1.485</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>Deportivo Moron -1</t>
-        </is>
-      </c>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -3866,7 +3842,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>0xb61b063252c01d0525ae633a0276dc1830eabd418482fddec925fcbd602a2a75</t>
+          <t>0x108eaba0441fb45ec8e0073e945ae0ac1e138c933e4f2839816cd3198d7dd4d2</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -3896,7 +3872,7 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>1786220171</t>
+          <t>1786277679</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
@@ -3906,7 +3882,7 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>1.900238</t>
+          <t>21.814433</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -3923,39 +3899,31 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0x0a5de930b5a6b8aca1699b666034af3891a3aa920021791d6d13e0297fb7903f</t>
+          <t>0xb25fa423ffb1a1464f100f2a2e9a1beac36661b9e37c8b09ecc7d3fd5a80312f</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>0x4a09916b1325Eed50eE8973B13742a205B0B7c7E</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
-          <t>49.99999</t>
+          <t>25.88</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>1.6175</t>
+          <t>1.6038</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>Almirante Brown -1</t>
-        </is>
-      </c>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -3963,27 +3931,27 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Almirante Brown vs Ciudad Bolivar</t>
+          <t>CA Colegiales vs Patronato</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>CA Colegiales</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>Ciudad Bolivar</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0xa6a338c64f062bfd589e8d5d9cea45a27c9e64065f71f800e5966f81ce53c556</t>
+          <t>0x18dd2fdd93f5029a20e6a76c47c4f0e5c3c25768ad7f1b46a833287f8b7fcc13</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>L19683447</t>
+          <t>L19683449</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -4008,17 +3976,17 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>1786218515</t>
+          <t>1786277040</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>1786212000</t>
+          <t>1786298400</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>80.971644</t>
+          <t>42.865424</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -4035,28 +4003,28 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0x17d5a08f8fa305f31f27442393c64f497dd3893417da6e76c321c4c2a187320d</t>
+          <t>0xfe815be8a10a6ad2cda012e463a244232a6f6c80544018f6dda52d723946b659</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
-          <t>49.18897</t>
+          <t>29.02571</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>1.4737</t>
+          <t>1.6038</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Under/Over (2)</t>
         </is>
       </c>
       <c r="G35" t="inlineStr"/>
@@ -4067,27 +4035,27 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Almirante Brown vs Ciudad Bolivar</t>
+          <t>CA Colegiales vs Patronato</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>CA Colegiales</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>Ciudad Bolivar</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>0xa6a338c64f062bfd589e8d5d9cea45a27c9e64065f71f800e5966f81ce53c556</t>
+          <t>0x18dd2fdd93f5029a20e6a76c47c4f0e5c3c25768ad7f1b46a833287f8b7fcc13</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>L19683447</t>
+          <t>L19683449</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -4112,17 +4080,17 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>1786218084</t>
+          <t>1786276809</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>1786212000</t>
+          <t>1786298400</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>103.82896</t>
+          <t>48.07571</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
@@ -4139,23 +4107,23 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0x56975f372357be259365cb7d2929c88d4fae157eea7a71d53d57cb234834f2ca</t>
+          <t>0xdb83c52876b68624e093c25e35d11910f4fbef2394ff947b658f8ea5cdb3fa88</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>16.96</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>1.4812</t>
+          <t>1.4463</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -4171,27 +4139,27 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Club Atletico Mitre de Santiago del Estero vs Defensores de Belgrano Buenos Aires</t>
+          <t>CA Colegiales vs Patronato</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Club Atletico Mitre de Santiago del Estero</t>
+          <t>CA Colegiales</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano Buenos Aires</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>0xa8ade64a3adb0ea38de67a61105ef31beb490d5a7287715b76ae124536d359cc</t>
+          <t>0x30a6561de28b35c5bb0557dcbfc7b23e7a62558d3b0f5cfcafb67d7a07e0dd21</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>L19683493</t>
+          <t>L19683449</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -4216,17 +4184,17 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>1786215674</t>
+          <t>1786276809</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>1786302000</t>
+          <t>1786298400</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>2.077922</t>
+          <t>38.005602</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
@@ -4243,12 +4211,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0xff53df1f3446908699196d44fcdb8b39c1bd15c7ed519f0d730e55a51a6eb38f</t>
+          <t>0x0847a2541998eecfe02d138796b14ef3d6719061787498f4888f6e14c0d196ff</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
+          <t>0xf068eF8DF8f47185D02d59Bb33d9eC7A057a571E</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -4258,12 +4226,12 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>38.54</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>1.3713</t>
+          <t>1.125</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -4273,7 +4241,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Club Almagro</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -4283,27 +4251,27 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Almirante Brown vs Ciudad Bolivar</t>
+          <t>Quilmes vs Club Almagro</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>Ciudad Bolivar</t>
+          <t>Club Almagro</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>0x63a8bf73c1084ef223fdd1096dccd16232e7a455fad77f7f0891be1588ebeb88</t>
+          <t>0x03ed0858b563c1becf38b195ad94b1a84eb89c3ca8ca10b1a34220bff142f9b2</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>L19683447</t>
+          <t>L19683499</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -4328,17 +4296,17 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>1786215673</t>
+          <t>1786270828</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>1786212000</t>
+          <t>1786305600</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>2.693603</t>
+          <t>308.32</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
@@ -4355,7 +4323,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0x249d52552e7acb9f472d2a4c48ab754622ba572903281739a3e10b4d509dccb0</t>
+          <t>0x2121e08c4ea1fe2d49a3bb388fba9e232ef9c06335c04e5eae0bf7766975512a</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4370,22 +4338,22 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>30.06</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>1.2288</t>
+          <t>1.6262</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Almirante Brown -1</t>
+          <t>Colon de Santa Fe</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -4395,27 +4363,27 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Almirante Brown vs Ciudad Bolivar</t>
+          <t>Colon de Santa Fe vs San Telmo</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Colon de Santa Fe</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>Ciudad Bolivar</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>0xa6a338c64f062bfd589e8d5d9cea45a27c9e64065f71f800e5966f81ce53c556</t>
+          <t>0x1a11ec80edeaae24566c4f4f891cc2afc56b377b24997a6e8ee533eeaaad5c92</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>L19683447</t>
+          <t>L19683494</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -4440,17 +4408,17 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>1786214209</t>
+          <t>1786253941</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>1786212000</t>
+          <t>1786300200</t>
         </is>
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>6.295082</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
@@ -4467,12 +4435,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0xf65c55196eeb0d21e7e3866ad26f8c3f2fee2aef273ddde5423e31fb40a51469</t>
+          <t>0x4e811c319e5e3a1fc1968ce0f31b4c15eb7222daa616252d99f9abc611408746</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x155C76202e45BE70c50bfeD7eAeA3B98e7716Ff7</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -4482,12 +4450,12 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>121.81</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>1.4363</t>
+          <t>1.2925</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -4497,7 +4465,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Tie</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -4507,27 +4475,27 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Almirante Brown vs Ciudad Bolivar</t>
+          <t>Colon de Santa Fe vs San Telmo</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Colon de Santa Fe</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>Ciudad Bolivar</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>0x63a8bf73c1084ef223fdd1096dccd16232e7a455fad77f7f0891be1588ebeb88</t>
+          <t>0x2e49527408facf21253a0a1eafe51280b82e4c31919e91a396332f19ec366401</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>L19683447</t>
+          <t>L19683494</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -4552,17 +4520,17 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>1786213844</t>
+          <t>1786243741</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>1786212000</t>
+          <t>1786300200</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>279.22063</t>
+          <t>3.418803</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
@@ -4579,12 +4547,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0x1bb20a2bf22e4fe06b44c06b9c2caa21f3f2a7c9d0cce1a2346f79e76022cd1f</t>
+          <t>0xb8631aeb398192a03386505542f05fa15e34db501204baa8745a4d4b5c1651b7</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x155C76202e45BE70c50bfeD7eAeA3B98e7716Ff7</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -4594,22 +4562,22 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>21.05</t>
+          <t>0.99999</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>1.4363</t>
+          <t>1.6538</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Almirante Brown -0.5</t>
+          <t>Deportivo Moron</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -4619,27 +4587,27 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Almirante Brown vs Ciudad Bolivar</t>
+          <t>Deportivo Moron vs Acassuso</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Deportivo Moron</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>Ciudad Bolivar</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>0xfa00d2f0c7b5053ee336b303a0e7ad9cec0b8d539367773b7efee5c86cb2b59d</t>
+          <t>0x7514a255ce41be3c5db9f8849ba04e78dab80f02d1fe78c2aae82bbc843a9745</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>L19683447</t>
+          <t>L19683452</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -4664,17 +4632,17 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>1786213843</t>
+          <t>1786243225</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>1786212000</t>
+          <t>1786298400</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>48.252149</t>
+          <t>1.529621</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
@@ -4691,28 +4659,28 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0xc51052f8e449b4d56cc87b697bfc8eb0d3a88ae218dee1da3d725fa94163bc75</t>
+          <t>0xd3b94d194e43cc84f0a1b82723594ea6689a6aa2a4a7dccbc8a3d19fc321e49b</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
         </is>
       </c>
       <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr">
         <is>
-          <t>77.29513</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>1.2588</t>
+          <t>1.5238</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Primera Nacional</t>
+          <t>Under/Over (2)</t>
         </is>
       </c>
       <c r="G41" t="inlineStr"/>
@@ -4723,27 +4691,27 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Almirante Brown vs Ciudad Bolivar</t>
+          <t>Deportivo Moron vs Acassuso</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Deportivo Moron</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>Ciudad Bolivar</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>0xaa5316c6f6544d74142ad6db34a3745918f237ffb1a657e000693947e81b65d6</t>
+          <t>0x108eaba0441fb45ec8e0073e945ae0ac1e138c933e4f2839816cd3198d7dd4d2</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>L19683447</t>
+          <t>L19683452</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -4768,17 +4736,17 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>1786212849</t>
+          <t>1786225000</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>1786212000</t>
+          <t>1786298400</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>298.72514</t>
+          <t>1.909308</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
@@ -4795,59 +4763,67 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0x0aeb4fe40f7d734cf244c144e6c064568b40b222193c9f93c641d1b31af3752e</t>
+          <t>0x86f4b24298f4c19f9f856cb19af2a260f24dc2d391f252248469436057ea1d1a</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr"/>
+          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>16.89162</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>1.2588</t>
+          <t>1.5263</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Deportivo Moron -1</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
           <t>Primera Nacional</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>Primera Nacional</t>
-        </is>
-      </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Almirante Brown vs Ciudad Bolivar</t>
+          <t>Deportivo Moron vs Acassuso</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Deportivo Moron</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>Ciudad Bolivar</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>0xaa5316c6f6544d74142ad6db34a3745918f237ffb1a657e000693947e81b65d6</t>
+          <t>0xb61b063252c01d0525ae633a0276dc1830eabd418482fddec925fcbd602a2a75</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>L19683447</t>
+          <t>L19683452</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -4872,17 +4848,17 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>1786212805</t>
+          <t>1786220171</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>1786212000</t>
+          <t>1786298400</t>
         </is>
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>65.281623</t>
+          <t>1.900238</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
@@ -4899,12 +4875,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0x383b895a5fe529a887369a0f113c516fdc7f6125d54381acf9695997ef22d039</t>
+          <t>0x0a5de930b5a6b8aca1699b666034af3891a3aa920021791d6d13e0297fb7903f</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x4a09916b1325Eed50eE8973B13742a205B0B7c7E</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -4914,39 +4890,39 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>11.26905</t>
+          <t>49.99999</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>1.745</t>
+          <t>1.6175</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Almirante Brown -1</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
           <t>Primera Nacional</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Almirante Brown vs Ciudad Bolivar</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
         <is>
           <t>Almirante Brown</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>Primera Nacional</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>Almirante Brown vs Ciudad Bolivar</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>Almirante Brown</t>
-        </is>
-      </c>
       <c r="K43" t="inlineStr">
         <is>
           <t>Ciudad Bolivar</t>
@@ -4954,7 +4930,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>0xaa5316c6f6544d74142ad6db34a3745918f237ffb1a657e000693947e81b65d6</t>
+          <t>0xa6a338c64f062bfd589e8d5d9cea45a27c9e64065f71f800e5966f81ce53c556</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -4984,7 +4960,7 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>1786211779</t>
+          <t>1786218515</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
@@ -4994,7 +4970,7 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>15.126242</t>
+          <t>80.971644</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
@@ -5011,54 +4987,46 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0xcfb6add6f8610a64ffc187beb9e16bf2bacb27b54a0f0aaefa6bfb437239b893</t>
+          <t>0x17d5a08f8fa305f31f27442393c64f497dd3893417da6e76c321c4c2a187320d</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr">
         <is>
-          <t>24.89998</t>
+          <t>49.18897</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>1.745</t>
+          <t>1.4737</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr">
+        <is>
           <t>Primera Nacional</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr">
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Almirante Brown vs Ciudad Bolivar</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
         <is>
           <t>Almirante Brown</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>Primera Nacional</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>Almirante Brown vs Ciudad Bolivar</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>Almirante Brown</t>
-        </is>
-      </c>
       <c r="K44" t="inlineStr">
         <is>
           <t>Ciudad Bolivar</t>
@@ -5066,7 +5034,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>0xaa5316c6f6544d74142ad6db34a3745918f237ffb1a657e000693947e81b65d6</t>
+          <t>0xa6a338c64f062bfd589e8d5d9cea45a27c9e64065f71f800e5966f81ce53c556</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -5096,7 +5064,7 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>1786211777</t>
+          <t>1786218084</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
@@ -5106,7 +5074,7 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>33.422792</t>
+          <t>103.82896</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
@@ -5123,19 +5091,15 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0xd41652604437a4e92e0d78b653d4d49d8dedd2e153d1340dad89b9b93e182a48</t>
+          <t>0x56975f372357be259365cb7d2929c88d4fae157eea7a71d53d57cb234834f2ca</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>0xf4a8B27C9a13e298D65b5Cc072d252816B799C81</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr">
         <is>
           <t>1</t>
@@ -5143,19 +5107,15 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>1.4163</t>
+          <t>1.4812</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>Atl. Rafaela</t>
-        </is>
-      </c>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -5163,27 +5123,27 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Atl. Rafaela vs Chacarita Juniors</t>
+          <t>Club Atletico Mitre de Santiago del Estero vs Defensores de Belgrano Buenos Aires</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Atl. Rafaela</t>
+          <t>Club Atletico Mitre de Santiago del Estero</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Defensores de Belgrano Buenos Aires</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>0xe738e9ba05492fab73eaaf6da211b84caadc72b08b26f1cd30fa8737e283bb44</t>
+          <t>0xa8ade64a3adb0ea38de67a61105ef31beb490d5a7287715b76ae124536d359cc</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>L19683450</t>
+          <t>L19683493</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -5208,17 +5168,17 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>1786211028</t>
+          <t>1786215674</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>1786215600</t>
+          <t>1786302000</t>
         </is>
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>2.402402</t>
+          <t>2.077922</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
@@ -5235,31 +5195,39 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0x562fd7c6419c807ed04d3cacac95f861805f96704bd535e265399fb9d2c2b609</t>
+          <t>0xff53df1f3446908699196d44fcdb8b39c1bd15c7ed519f0d730e55a51a6eb38f</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr"/>
+          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>5.32</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>1.405</t>
+          <t>1.3713</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Almirante Brown</t>
+        </is>
+      </c>
       <c r="H46" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -5267,27 +5235,27 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Estudiantes de Caseros vs Deportivo Madryn</t>
+          <t>Almirante Brown vs Ciudad Bolivar</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Estudiantes de Caseros</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Ciudad Bolivar</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>0xd61509e26f8645bb9780672f942c72c4b7dab577c2a01f04e1e09bce9b828765</t>
+          <t>0x63a8bf73c1084ef223fdd1096dccd16232e7a455fad77f7f0891be1588ebeb88</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>L19683453</t>
+          <t>L19683447</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -5312,7 +5280,7 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>1786210845</t>
+          <t>1786215673</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
@@ -5322,7 +5290,7 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>13.135802</t>
+          <t>2.693603</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
@@ -5339,12 +5307,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0x0bb7a6822220bf40d7b279f99a54f46025f393ba95bb38b6d6dc98192886b3ed</t>
+          <t>0x249d52552e7acb9f472d2a4c48ab754622ba572903281739a3e10b4d509dccb0</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>0xf4a8B27C9a13e298D65b5Cc072d252816B799C81</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -5354,22 +5322,22 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>0.99999</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>1.5513</t>
+          <t>1.2288</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Almirante Brown -1</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -5379,27 +5347,27 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Agropecuario vs Atletico Guemes</t>
+          <t>Almirante Brown vs Ciudad Bolivar</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>Atletico Guemes</t>
+          <t>Ciudad Bolivar</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>0xae66c7fab3c9c76fbc29d9e9778ef4845d8a6b8d092cff34320f100020113c49</t>
+          <t>0xa6a338c64f062bfd589e8d5d9cea45a27c9e64065f71f800e5966f81ce53c556</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>L19683451</t>
+          <t>L19683447</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -5424,7 +5392,7 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>1786205982</t>
+          <t>1786214209</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
@@ -5434,7 +5402,7 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>1.814041</t>
+          <t>6.295082</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
@@ -5451,12 +5419,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0xe17b2546f4b90c8647ba975c279e39dec1fda5a003adfb8a2b39bb12a3519b10</t>
+          <t>0xf65c55196eeb0d21e7e3866ad26f8c3f2fee2aef273ddde5423e31fb40a51469</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>0xf4a8B27C9a13e298D65b5Cc072d252816B799C81</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -5466,12 +5434,12 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>121.81</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>1.3613</t>
+          <t>1.4363</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -5481,7 +5449,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Tie</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -5506,7 +5474,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>0xd5906ce08d61f7c5ee45fcebd2c8baeed5558387398ea332817a4b632f439b6d</t>
+          <t>0x63a8bf73c1084ef223fdd1096dccd16232e7a455fad77f7f0891be1588ebeb88</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -5536,7 +5504,7 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>1786205963</t>
+          <t>1786213844</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
@@ -5546,7 +5514,7 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>2.768166</t>
+          <t>279.22063</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
@@ -5563,12 +5531,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0xcfe218822e89cbef5841f3045f551cc65acf353d8e240f943e2b61c54ea79a68</t>
+          <t>0x1bb20a2bf22e4fe06b44c06b9c2caa21f3f2a7c9d0cce1a2346f79e76022cd1f</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>0xf4a8B27C9a13e298D65b5Cc072d252816B799C81</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -5578,22 +5546,22 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>21.05</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>1.3337</t>
+          <t>1.4363</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Tie</t>
+          <t>Almirante Brown -0.5</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -5603,27 +5571,27 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Estudiantes de Caseros vs Deportivo Madryn</t>
+          <t>Almirante Brown vs Ciudad Bolivar</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Estudiantes de Caseros</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Ciudad Bolivar</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>0xf238b96ec9e2421db79973de945f1fc0c3f8bb99c31cda32d011ebaabfd2db86</t>
+          <t>0xfa00d2f0c7b5053ee336b303a0e7ad9cec0b8d539367773b7efee5c86cb2b59d</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>L19683453</t>
+          <t>L19683447</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -5648,7 +5616,7 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>1786205938</t>
+          <t>1786213843</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
@@ -5658,7 +5626,7 @@
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>2.996255</t>
+          <t>48.252149</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
@@ -5675,28 +5643,28 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0x1b9fcb29010a212f74af57040114154e78748f06a4d826be4397ddadb45ac31b</t>
+          <t>0xc51052f8e449b4d56cc87b697bfc8eb0d3a88ae218dee1da3d725fa94163bc75</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr">
         <is>
-          <t>21.69</t>
+          <t>77.29513</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>1.4512</t>
+          <t>1.2588</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
+          <t>Primera Nacional</t>
         </is>
       </c>
       <c r="G50" t="inlineStr"/>
@@ -5722,7 +5690,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>0xbbcaa253cd967fbf933ff0d87a6f9744cafec0ed59dad5f1f76332aab01a3fa5</t>
+          <t>0xaa5316c6f6544d74142ad6db34a3745918f237ffb1a657e000693947e81b65d6</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -5752,7 +5720,7 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>1786190525</t>
+          <t>1786212849</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
@@ -5762,7 +5730,7 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>48.066482</t>
+          <t>298.72514</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
@@ -5779,28 +5747,28 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0x3177792dd6a7185e37ae06612104cf5a35d137d7f535a889a83a7e9b7c174506</t>
+          <t>0x0aeb4fe40f7d734cf244c144e6c064568b40b222193c9f93c641d1b31af3752e</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr">
         <is>
-          <t>18.35495</t>
+          <t>16.89162</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>1.4963</t>
+          <t>1.2588</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
+          <t>Primera Nacional</t>
         </is>
       </c>
       <c r="G51" t="inlineStr"/>
@@ -5826,7 +5794,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>0xbbcaa253cd967fbf933ff0d87a6f9744cafec0ed59dad5f1f76332aab01a3fa5</t>
+          <t>0xaa5316c6f6544d74142ad6db34a3745918f237ffb1a657e000693947e81b65d6</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -5856,7 +5824,7 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>1786190491</t>
+          <t>1786212805</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
@@ -5866,7 +5834,7 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>36.987305</t>
+          <t>65.281623</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
@@ -5883,12 +5851,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0x54ed4ee2a6ebdab49498137f1accea542ead806f21430a0a771cc4872a044e43</t>
+          <t>0x383b895a5fe529a887369a0f113c516fdc7f6125d54381acf9695997ef22d039</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -5898,22 +5866,22 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>20.10741</t>
+          <t>11.26905</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>1.5437</t>
+          <t>1.745</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
+          <t>Primera Nacional</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Over 1.5</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -5938,7 +5906,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>0xbbcaa253cd967fbf933ff0d87a6f9744cafec0ed59dad5f1f76332aab01a3fa5</t>
+          <t>0xaa5316c6f6544d74142ad6db34a3745918f237ffb1a657e000693947e81b65d6</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
@@ -5968,7 +5936,7 @@
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>1786190485</t>
+          <t>1786211779</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
@@ -5978,7 +5946,7 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>36.979145</t>
+          <t>15.126242</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
@@ -5995,7 +5963,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0x544fe5c906328d009917b591611ff3438cef85f8b42d9f67732cbbd5eabbb8dd</t>
+          <t>0xcfb6add6f8610a64ffc187beb9e16bf2bacb27b54a0f0aaefa6bfb437239b893</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -6003,23 +5971,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr"/>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>21.69</t>
+          <t>24.89998</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>1.4512</t>
+          <t>1.745</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr"/>
+          <t>Primera Nacional</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Almirante Brown</t>
+        </is>
+      </c>
       <c r="H53" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -6042,7 +6018,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>0xbbcaa253cd967fbf933ff0d87a6f9744cafec0ed59dad5f1f76332aab01a3fa5</t>
+          <t>0xaa5316c6f6544d74142ad6db34a3745918f237ffb1a657e000693947e81b65d6</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
@@ -6072,7 +6048,7 @@
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>1786190485</t>
+          <t>1786211777</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
@@ -6082,7 +6058,7 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>48.066482</t>
+          <t>33.422792</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
@@ -6099,31 +6075,39 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0xb2f3ea804e1760a01d3a93678f0e2119f1ea2a9db0dc4711a06cc7bcba42b0c2</t>
+          <t>0xd41652604437a4e92e0d78b653d4d49d8dedd2e153d1340dad89b9b93e182a48</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr"/>
+          <t>0xf4a8B27C9a13e298D65b5Cc072d252816B799C81</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>17.47</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>1.405</t>
+          <t>1.4163</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Atl. Rafaela</t>
+        </is>
+      </c>
       <c r="H54" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -6131,27 +6115,27 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Estudiantes de Caseros vs Deportivo Madryn</t>
+          <t>Atl. Rafaela vs Chacarita Juniors</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Estudiantes de Caseros</t>
+          <t>Atl. Rafaela</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>0xd61509e26f8645bb9780672f942c72c4b7dab577c2a01f04e1e09bce9b828765</t>
+          <t>0xe738e9ba05492fab73eaaf6da211b84caadc72b08b26f1cd30fa8737e283bb44</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>L19683453</t>
+          <t>L19683450</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -6176,17 +6160,17 @@
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>1786190461</t>
+          <t>1786211028</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>1786212000</t>
+          <t>1786215600</t>
         </is>
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>43.135802</t>
+          <t>2.402402</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
@@ -6203,7 +6187,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0xa7eafbb77d425fc2347b4ee3e4f4e1b85f6d0f81420605db76ebfeeaa793a428</t>
+          <t>0x562fd7c6419c807ed04d3cacac95f861805f96704bd535e265399fb9d2c2b609</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -6214,12 +6198,12 @@
       <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr">
         <is>
-          <t>21.69</t>
+          <t>5.32</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>1.4512</t>
+          <t>1.405</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -6235,27 +6219,27 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Almirante Brown vs Ciudad Bolivar</t>
+          <t>Estudiantes de Caseros vs Deportivo Madryn</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Estudiantes de Caseros</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>Ciudad Bolivar</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>0xbbcaa253cd967fbf933ff0d87a6f9744cafec0ed59dad5f1f76332aab01a3fa5</t>
+          <t>0xd61509e26f8645bb9780672f942c72c4b7dab577c2a01f04e1e09bce9b828765</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>L19683447</t>
+          <t>L19683453</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -6280,7 +6264,7 @@
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>1786190458</t>
+          <t>1786210845</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
@@ -6290,7 +6274,7 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>48.066482</t>
+          <t>13.135802</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
@@ -6307,110 +6291,1078 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
+          <t>0x0bb7a6822220bf40d7b279f99a54f46025f393ba95bb38b6d6dc98192886b3ed</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>0xf4a8B27C9a13e298D65b5Cc072d252816B799C81</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>0.99999</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>1.5513</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Agropecuario</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Primera Nacional</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>Agropecuario vs Atletico Guemes</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>Agropecuario</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Atletico Guemes</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>0xae66c7fab3c9c76fbc29d9e9778ef4845d8a6b8d092cff34320f100020113c49</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>L19683451</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>1786205982</t>
+        </is>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>1786212000</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>1.814041</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>0xe17b2546f4b90c8647ba975c279e39dec1fda5a003adfb8a2b39bb12a3519b10</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>0xf4a8B27C9a13e298D65b5Cc072d252816B799C81</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>1.3613</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Primera Nacional</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Almirante Brown vs Ciudad Bolivar</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>Almirante Brown</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Ciudad Bolivar</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>0xd5906ce08d61f7c5ee45fcebd2c8baeed5558387398ea332817a4b632f439b6d</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>L19683447</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>1786205963</t>
+        </is>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>1786212000</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>2.768166</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>0xcfe218822e89cbef5841f3045f551cc65acf353d8e240f943e2b61c54ea79a68</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>0xf4a8B27C9a13e298D65b5Cc072d252816B799C81</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>1.3337</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Primera Nacional</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>Estudiantes de Caseros vs Deportivo Madryn</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>Estudiantes de Caseros</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Deportivo Madryn</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>0xf238b96ec9e2421db79973de945f1fc0c3f8bb99c31cda32d011ebaabfd2db86</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>L19683453</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R58" t="inlineStr">
+        <is>
+          <t>1786205938</t>
+        </is>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>1786212000</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>2.996255</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>0x1b9fcb29010a212f74af57040114154e78748f06a4d826be4397ddadb45ac31b</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr"/>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>21.69</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>1.4512</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr"/>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Primera Nacional</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>Almirante Brown vs Ciudad Bolivar</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>Almirante Brown</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Ciudad Bolivar</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>0xbbcaa253cd967fbf933ff0d87a6f9744cafec0ed59dad5f1f76332aab01a3fa5</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>L19683447</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>1786190525</t>
+        </is>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>1786212000</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>48.066482</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>0x3177792dd6a7185e37ae06612104cf5a35d137d7f535a889a83a7e9b7c174506</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr"/>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>18.35495</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>1.4963</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr"/>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Primera Nacional</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>Almirante Brown vs Ciudad Bolivar</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>Almirante Brown</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Ciudad Bolivar</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>0xbbcaa253cd967fbf933ff0d87a6f9744cafec0ed59dad5f1f76332aab01a3fa5</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>L19683447</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>1786190491</t>
+        </is>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>1786212000</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>36.987305</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>0x54ed4ee2a6ebdab49498137f1accea542ead806f21430a0a771cc4872a044e43</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>20.10741</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>1.5437</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Over 1.5</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Primera Nacional</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>Almirante Brown vs Ciudad Bolivar</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>Almirante Brown</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Ciudad Bolivar</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>0xbbcaa253cd967fbf933ff0d87a6f9744cafec0ed59dad5f1f76332aab01a3fa5</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>L19683447</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>1786190485</t>
+        </is>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>1786212000</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>36.979145</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>0x544fe5c906328d009917b591611ff3438cef85f8b42d9f67732cbbd5eabbb8dd</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr"/>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>21.69</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>1.4512</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr"/>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Primera Nacional</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>Almirante Brown vs Ciudad Bolivar</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>Almirante Brown</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Ciudad Bolivar</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>0xbbcaa253cd967fbf933ff0d87a6f9744cafec0ed59dad5f1f76332aab01a3fa5</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>L19683447</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R62" t="inlineStr">
+        <is>
+          <t>1786190485</t>
+        </is>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>1786212000</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>48.066482</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>0xb2f3ea804e1760a01d3a93678f0e2119f1ea2a9db0dc4711a06cc7bcba42b0c2</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr"/>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>17.47</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>1.405</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr"/>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Primera Nacional</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>Estudiantes de Caseros vs Deportivo Madryn</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>Estudiantes de Caseros</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Deportivo Madryn</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>0xd61509e26f8645bb9780672f942c72c4b7dab577c2a01f04e1e09bce9b828765</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>L19683453</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R63" t="inlineStr">
+        <is>
+          <t>1786190461</t>
+        </is>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>1786212000</t>
+        </is>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>43.135802</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>0xa7eafbb77d425fc2347b4ee3e4f4e1b85f6d0f81420605db76ebfeeaa793a428</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr"/>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>21.69</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>1.4512</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr"/>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Primera Nacional</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>Almirante Brown vs Ciudad Bolivar</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>Almirante Brown</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Ciudad Bolivar</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>0xbbcaa253cd967fbf933ff0d87a6f9744cafec0ed59dad5f1f76332aab01a3fa5</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>L19683447</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R64" t="inlineStr">
+        <is>
+          <t>1786190458</t>
+        </is>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>1786212000</t>
+        </is>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>48.066482</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
           <t>0x5c5b512ea725fac30531bf5fe91f34f3ccc0eeff23890c18f25c3f329007c589</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
+      <c r="B65" t="inlineStr">
         <is>
           <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
         <is>
           <t>1.3638</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr">
+      <c r="F65" t="inlineStr">
         <is>
           <t>1X2</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr">
+      <c r="G65" t="inlineStr">
         <is>
           <t>Tie</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
+      <c r="H65" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr">
+      <c r="I65" t="inlineStr">
         <is>
           <t>Almirante Brown vs Ciudad Bolivar</t>
         </is>
       </c>
-      <c r="J56" t="inlineStr">
+      <c r="J65" t="inlineStr">
         <is>
           <t>Almirante Brown</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr">
+      <c r="K65" t="inlineStr">
         <is>
           <t>Ciudad Bolivar</t>
         </is>
       </c>
-      <c r="L56" t="inlineStr">
+      <c r="L65" t="inlineStr">
         <is>
           <t>0xd5906ce08d61f7c5ee45fcebd2c8baeed5558387398ea332817a4b632f439b6d</t>
         </is>
       </c>
-      <c r="M56" t="inlineStr">
+      <c r="M65" t="inlineStr">
         <is>
           <t>L19683447</t>
         </is>
       </c>
-      <c r="N56" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O56" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P56" t="inlineStr">
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q56" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R56" t="inlineStr">
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R65" t="inlineStr">
         <is>
           <t>1786125660</t>
         </is>
       </c>
-      <c r="S56" t="inlineStr">
+      <c r="S65" t="inlineStr">
         <is>
           <t>1786212000</t>
         </is>
       </c>
-      <c r="T56" t="inlineStr">
+      <c r="T65" t="inlineStr">
         <is>
           <t>2.749141</t>
         </is>
       </c>
-      <c r="U56" t="inlineStr">
+      <c r="U65" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V56" t="inlineStr">
+      <c r="V65" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/Primera Nacional/trades.xlsx
+++ b/data/sxbet/ligas/Primera Nacional/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V65"/>
+  <dimension ref="A1:V76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,23 +531,23 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0x972e5a678ec56c15f03cbf0d14d7070ad000111adf76887dc34cc27780792e32</t>
+          <t>0xaef8a42b6335c8c59cb7bb616441203e8516097ce0e7adb9c1dfe622d7b8a46a</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>24.07997</t>
+          <t>14.3554</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.8675</t>
+          <t>1.0513</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -563,27 +563,27 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Godoy Cruz vs Chaco For Ever</t>
+          <t>Deportivo Moron vs Acassuso</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Deportivo Moron</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0x9c19e4c1fd9646506f8ea14e2b1be19b49a5ab4dc1a7bf40167705a4ae2b338b</t>
+          <t>0x7514a255ce41be3c5db9f8849ba04e78dab80f02d1fe78c2aae82bbc843a9745</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>L19683484</t>
+          <t>L19683452</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -608,17 +608,17 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1786297771</t>
+          <t>1786301685</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>1786303800</t>
+          <t>1786298400</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>27.75789</t>
+          <t>280.105366</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -635,39 +635,31 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0x1da1f134f1ec859a8260a79216b9030b9f0b715d9a51d09741ff884111dcde2b</t>
+          <t>0x9cd0c1e560dfbdd3bb0ca9522422167bdbc75ef5c7813dbe00ce4bee50d0f1be</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0x311AE302984D8b1cf53D6bfB0a6672f05c423AE6</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>37.76669</t>
+          <t>13.80272</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.5837</t>
+          <t>1.0488</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Godoy Cruz -0.5</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -675,27 +667,27 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Godoy Cruz vs Chaco For Ever</t>
+          <t>Deportivo Moron vs Acassuso</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Deportivo Moron</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0xb2c04ce7cffc1005eb6199d3c34d31b109e8af04a357b4f8eb9f6b8362ba33c2</t>
+          <t>0x7514a255ce41be3c5db9f8849ba04e78dab80f02d1fe78c2aae82bbc843a9745</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>L19683484</t>
+          <t>L19683452</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -720,17 +712,17 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1786297676</t>
+          <t>1786301534</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>1786303800</t>
+          <t>1786298400</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>64.696685</t>
+          <t>283.132718</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -747,12 +739,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0xfccc36b3cd4c4e2276a7540f5bb389b40f91c9998d31903af7864027f93d335e</t>
+          <t>0x9036645c2b6fdeee93c9912e60b360f0e894db0b98a32ed8106dd074362ac356</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -762,12 +754,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>56.81</t>
+          <t>37.59</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.3588</t>
+          <t>1.1225</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -777,7 +769,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tie</t>
+          <t>CA Colegiales</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -787,27 +779,27 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>CA Los Andes vs Ferro Carril Oeste</t>
+          <t>CA Colegiales vs Patronato</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>CA Los Andes</t>
+          <t>CA Colegiales</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0x834e52f6ff115c72424372c131d41b8d94cffe6e0131918e3f85e2146509d14b</t>
+          <t>0x6033340ba69fb7874ae22715f395c0926449aa18c6ec5295e2568fe9a173664d</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>L19659153</t>
+          <t>L19683449</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -832,17 +824,17 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1786297373</t>
+          <t>1786301228</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>1786296600</t>
+          <t>1786298400</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>158.355401</t>
+          <t>306.857143</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -859,31 +851,39 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0x48c1aed95e65b653ffb51380d6066948766a0030b4adf3bf05d152a5766c29cf</t>
+          <t>0xd9eff492baa46fea0da1221b63ca70a7e18beec129de6ebec5453a1b9e6bfcf8</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr"/>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.6425</t>
+          <t>1.4263</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr"/>
+          <t>Asian Handicap (0.5)</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>CA Colegiales +0.5</t>
+        </is>
+      </c>
       <c r="H5" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -891,27 +891,27 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Colon de Santa Fe vs San Telmo</t>
+          <t>CA Colegiales vs Patronato</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Colon de Santa Fe</t>
+          <t>CA Colegiales</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0x79905ae58e04af69981e4a95c3d57b98dc3c1dd1d3e7aeb4e6a7640714001f3b</t>
+          <t>0xf03b2761ed02376d644cd19d08d1923efb50cd17956a930c587e812207a86746</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>L19683494</t>
+          <t>L19683449</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -936,17 +936,17 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1786293588</t>
+          <t>1786301216</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>1786300200</t>
+          <t>1786298400</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>15.564202</t>
+          <t>46.920821</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -963,59 +963,67 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0x3d4ee2d1cf7066373ffe56d01727fc04ce4ae0e1203194a2877d6ba90d9d4fcb</t>
+          <t>0xc72322e8ff04e28165d90bbcfa3c4b34aa19dd5fc1215e13ba7e1ce6362a9292</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>16.53143</t>
+          <t>7.93</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.3438</t>
+          <t>1.4263</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Racing de Cordoba</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
           <t>Primera Nacional</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Primera Nacional</t>
-        </is>
-      </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Atlanta vs Temperley</t>
+          <t>Racing de Cordoba vs San Miguel</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Racing de Cordoba</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0xc67c753c7ce425d2b225c54e0abf1308c3593fa6789a95fd59198b3a0f7a3ddd</t>
+          <t>0x48447168804e92d195e0c849cfb7ae548e076f102e1005f3756585b3d18ea65c</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>L19683448</t>
+          <t>L19683501</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1040,17 +1048,17 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1786293565</t>
+          <t>1786301162</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>1786294800</t>
+          <t>1786302000</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>48.091433</t>
+          <t>18.604106</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1067,59 +1075,67 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0x5decd74680fc49716c54620aa922234edac874fb77b6369067e932fb5a40aed8</t>
+          <t>0xd37a1d074e8819ce033a62d6fe3bb026c46529f33aed65aaac63e3d53cb8ce3e</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr"/>
+          <t>0x5022174051792ac42d3af7Ff6bC9cf78a6aE3f32</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>16.98847</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.4287</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
+          <t>Under/Over (0.5)</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Over 0.5</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
           <t>Primera Nacional</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Primera Nacional</t>
-        </is>
-      </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>San Martin Tucuman vs San Martín de San Juan</t>
+          <t>Atlanta vs Temperley</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>San Martin Tucuman</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>San Martín de San Juan</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0x4f02331cd42a68f65ea16d62aac0c6b123d9400d12a4d556f3a72df894da02fb</t>
+          <t>0x84c2bb083fa51c1fc591f5ac9524e09d26434823e44ca466e2af8bd17ae651cb</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>L19682528</t>
+          <t>L19683448</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1144,17 +1160,17 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1786293511</t>
+          <t>1786300699</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>1786309200</t>
+          <t>1786294800</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>48.538486</t>
+          <t>11.661808</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1171,28 +1187,28 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0x6376c34d63b4968409b909753114511b32d1413abbfce5d71dcd6fa7bb384028</t>
+          <t>0x0199716d54c5764cbf1a6783da6c106cf378f2c6b96892a13d7019f5cb41b3fa</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>30.89</t>
+          <t>16.84</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.6425</t>
+          <t>1.1262</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
+          <t>Under/Over (0.5)</t>
         </is>
       </c>
       <c r="G8" t="inlineStr"/>
@@ -1203,27 +1219,27 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Colon de Santa Fe vs San Telmo</t>
+          <t>Godoy Cruz vs Chaco For Ever</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Colon de Santa Fe</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0x79905ae58e04af69981e4a95c3d57b98dc3c1dd1d3e7aeb4e6a7640714001f3b</t>
+          <t>0x9c696117152178b9240c2e3eddca6b53432d4a4937a20042677cd1f666604f23</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>L19683494</t>
+          <t>L19683484</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1248,17 +1264,17 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1786293434</t>
+          <t>1786300516</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>1786300200</t>
+          <t>1786303800</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>48.077821</t>
+          <t>133.386139</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1275,28 +1291,28 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0xa534180ddbde4d456a67f71365d2341259c4ca0b20e45041701c1d345202335e</t>
+          <t>0x84f162af96f80a1f61f37a3b12a3dab48dcffde9bd10d0cea022df759f18111f</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>13.52</t>
+          <t>36.84547</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.6325</t>
+          <t>1.1362</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>Primera Nacional</t>
         </is>
       </c>
       <c r="G9" t="inlineStr"/>
@@ -1307,27 +1323,27 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Quilmes vs Club Almagro</t>
+          <t>Colon de Santa Fe vs San Telmo</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Colon de Santa Fe</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Club Almagro</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0x86a790846c1cb1bed065ac37c41b727461e30e0a9e0f9e2370ef61f6213ed31f</t>
+          <t>0xbca9ed7d23a7df6c8ab98ab2ffc6649f2d4bd3d9007bd0ecf103e453c87addac</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>L19683499</t>
+          <t>L19683494</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1352,17 +1368,17 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1786293430</t>
+          <t>1786300513</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>1786305600</t>
+          <t>1786300200</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>21.375494</t>
+          <t>270.425468</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1379,31 +1395,39 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0xe6cbce05bf55e4a2647eb39e1cb6d7afdafec60905e09f42fb3552a02a5fcbd6</t>
+          <t>0x2f3773fa15124937ec4965274c782b70d022a4fb2a2c8e85fe36a66e0dcc1a53</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr"/>
+          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>16.88999</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.6325</t>
+          <t>1.2563</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>San Miguel</t>
+        </is>
+      </c>
       <c r="H10" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -1411,27 +1435,27 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Quilmes vs Club Almagro</t>
+          <t>Racing de Cordoba vs San Miguel</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Racing de Cordoba</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Club Almagro</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0x86a790846c1cb1bed065ac37c41b727461e30e0a9e0f9e2370ef61f6213ed31f</t>
+          <t>0x8ddab476b71709486e3a0e2118fafcb483076bd09c1c25dcce66244486fed688</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>L19683499</t>
+          <t>L19683501</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1456,17 +1480,17 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1786293428</t>
+          <t>1786300245</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>1786305600</t>
+          <t>1786302000</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>26.703542</t>
+          <t>3.902439</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1483,7 +1507,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0xae3b69e222676c5f5930a25ee6fc677945888fbd4b45894897e8c0b45b324e25</t>
+          <t>0x4334abae5afdbf026c92af25200b83381434248bdfca39224de3957cba46f6e4</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1491,23 +1515,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr"/>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>12.72</t>
+          <t>52.38</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.4512</t>
+          <t>1.675</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr"/>
+          <t>Primera Nacional</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>CA Colegiales 0</t>
+        </is>
+      </c>
       <c r="H11" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -1515,27 +1547,27 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>CA Los Andes vs Ferro Carril Oeste</t>
+          <t>CA Colegiales vs Patronato</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>CA Los Andes</t>
+          <t>CA Colegiales</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0x555a8472fba9017aa83a61e5e7cf7b05dc2822d1d1cc6174412760fc412637f7</t>
+          <t>0x3fa48fbf2a59e0b45def889e06df3d2da646e9465f9af4f1b88581fea7fb4496</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>L19659153</t>
+          <t>L19683449</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1560,17 +1592,17 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1786288547</t>
+          <t>1786300042</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>1786296600</t>
+          <t>1786298400</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>28.188366</t>
+          <t>77.6</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1587,31 +1619,39 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0x4bb954aaa9ecad68c0eb53f2341bb75f7b8daa072a3f151571ab136be22b78df</t>
+          <t>0xad7255fad3f7d526c2f80d7968fa11121b17d106e3df35095d9b411cead706b0</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0x71CE4A2C734a76f4C86A0D80122C4014c1F52F6e</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>29.37999</t>
+          <t>3.02932</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.6113</t>
+          <t>1.2325</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>San Miguel</t>
+        </is>
+      </c>
       <c r="H12" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -1619,27 +1659,27 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>CA Los Andes vs Ferro Carril Oeste</t>
+          <t>Racing de Cordoba vs San Miguel</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>CA Los Andes</t>
+          <t>Racing de Cordoba</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>0x653af58a9c77cb072171a76bcd9ca8adee427601f3ecd186c8154c81f8736395</t>
+          <t>0x8ddab476b71709486e3a0e2118fafcb483076bd09c1c25dcce66244486fed688</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>L19659153</t>
+          <t>L19683501</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1664,17 +1704,17 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1786288517</t>
+          <t>1786298930</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>1786296600</t>
+          <t>1786302000</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>48.065423</t>
+          <t>13.029333</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1691,7 +1731,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0xd5a2ddd8c8b6cc9bdb1c507276d3a192a5f24d46e2d3c01bfb07011263030bdd</t>
+          <t>0x972e5a678ec56c15f03cbf0d14d7070ad000111adf76887dc34cc27780792e32</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1702,17 +1742,17 @@
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>5.67</t>
+          <t>24.07997</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.2975</t>
+          <t>1.8675</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Primera Nacional</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G13" t="inlineStr"/>
@@ -1723,27 +1763,27 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>CA Colegiales vs Patronato</t>
+          <t>Godoy Cruz vs Chaco For Ever</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>CA Colegiales</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>0x710e5bf3f6759bd93c59fc8788916c16c7302071968dfba2d053e2d10f7858bf</t>
+          <t>0x9c19e4c1fd9646506f8ea14e2b1be19b49a5ab4dc1a7bf40167705a4ae2b338b</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>L19683449</t>
+          <t>L19683484</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1768,17 +1808,17 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1786288450</t>
+          <t>1786297771</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>1786298400</t>
+          <t>1786303800</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>19.058824</t>
+          <t>27.75789</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1795,31 +1835,39 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0xad9f4feea88f83ae2e46756e7d54faa300a82e055c196c70c84019780ecb560c</t>
+          <t>0x1da1f134f1ec859a8260a79216b9030b9f0b715d9a51d09741ff884111dcde2b</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr"/>
+          <t>0x311AE302984D8b1cf53D6bfB0a6672f05c423AE6</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>21.69</t>
+          <t>37.76669</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1.4512</t>
+          <t>1.5837</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr"/>
+          <t>Asian Handicap (-0.5)</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Godoy Cruz -0.5</t>
+        </is>
+      </c>
       <c r="H14" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -1827,27 +1875,27 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>CA Los Andes vs Ferro Carril Oeste</t>
+          <t>Godoy Cruz vs Chaco For Ever</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>CA Los Andes</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>0x555a8472fba9017aa83a61e5e7cf7b05dc2822d1d1cc6174412760fc412637f7</t>
+          <t>0xb2c04ce7cffc1005eb6199d3c34d31b109e8af04a357b4f8eb9f6b8362ba33c2</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>L19659153</t>
+          <t>L19683484</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1872,17 +1920,17 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1786288436</t>
+          <t>1786297676</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>1786296600</t>
+          <t>1786303800</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>48.066482</t>
+          <t>64.696685</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -1899,7 +1947,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0x168e5ea2716a187c94a1c77c4c8b2523b31163ed118e4986c68c79a21d013932</t>
+          <t>0xfccc36b3cd4c4e2276a7540f5bb389b40f91c9998d31903af7864027f93d335e</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1907,23 +1955,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr"/>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>29.38716</t>
+          <t>56.81</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1.6113</t>
+          <t>1.3588</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H15" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -1946,7 +2002,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>0x653af58a9c77cb072171a76bcd9ca8adee427601f3ecd186c8154c81f8736395</t>
+          <t>0x834e52f6ff115c72424372c131d41b8d94cffe6e0131918e3f85e2146509d14b</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1976,7 +2032,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>1786288436</t>
+          <t>1786297373</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -1986,7 +2042,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>48.077153</t>
+          <t>158.355401</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2003,39 +2059,31 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0x680d5db234b802aa2845f16e9d23d635dd89870065c6bfb6f6f1bde25c321bae</t>
+          <t>0x48c1aed95e65b653ffb51380d6066948766a0030b4adf3bf05d152a5766c29cf</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>24.36</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1.475</t>
+          <t>1.6425</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>CA Colegiales -0.5</t>
-        </is>
-      </c>
+          <t>Asian Handicap (-1.5)</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -2043,27 +2091,27 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>CA Colegiales vs Patronato</t>
+          <t>Colon de Santa Fe vs San Telmo</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>CA Colegiales</t>
+          <t>Colon de Santa Fe</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>0x50a3f0e4e982cdda0b9c4b9e2e1c50c67d93fbf7a068b43dbdf733c0b8d09050</t>
+          <t>0x79905ae58e04af69981e4a95c3d57b98dc3c1dd1d3e7aeb4e6a7640714001f3b</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>L19683449</t>
+          <t>L19683494</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -2088,17 +2136,17 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1786287181</t>
+          <t>1786293588</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>1786298400</t>
+          <t>1786300200</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>51.284211</t>
+          <t>15.564202</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2115,28 +2163,28 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0x5a5b6f41ac2a593747a9419c020abd417423350c2cf0a14d8cb9ef8a25d04f18</t>
+          <t>0x3d4ee2d1cf7066373ffe56d01727fc04ce4ae0e1203194a2877d6ba90d9d4fcb</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>8.81755</t>
+          <t>16.53143</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.6325</t>
+          <t>1.3438</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>Primera Nacional</t>
         </is>
       </c>
       <c r="G17" t="inlineStr"/>
@@ -2147,27 +2195,27 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Quilmes vs Club Almagro</t>
+          <t>Atlanta vs Temperley</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Club Almagro</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>0x86a790846c1cb1bed065ac37c41b727461e30e0a9e0f9e2370ef61f6213ed31f</t>
+          <t>0xc67c753c7ce425d2b225c54e0abf1308c3593fa6789a95fd59198b3a0f7a3ddd</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>L19683499</t>
+          <t>L19683448</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -2192,17 +2240,17 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>1786284071</t>
+          <t>1786293565</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>1786305600</t>
+          <t>1786294800</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>13.940791</t>
+          <t>48.091433</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2219,7 +2267,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0x9ae6e679c8fc9ed20977676ba3160d389287dd8808ea2610d0f168f9c3a42c11</t>
+          <t>0x5decd74680fc49716c54620aa922234edac874fb77b6369067e932fb5a40aed8</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2230,17 +2278,17 @@
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>21.58999</t>
+          <t>16.98847</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.6325</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>Primera Nacional</t>
         </is>
       </c>
       <c r="G18" t="inlineStr"/>
@@ -2251,27 +2299,27 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Quilmes vs Club Almagro</t>
+          <t>San Martin Tucuman vs San Martín de San Juan</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>San Martin Tucuman</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Club Almagro</t>
+          <t>San Martín de San Juan</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>0x86a790846c1cb1bed065ac37c41b727461e30e0a9e0f9e2370ef61f6213ed31f</t>
+          <t>0x4f02331cd42a68f65ea16d62aac0c6b123d9400d12a4d556f3a72df894da02fb</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>L19683499</t>
+          <t>L19682528</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -2296,17 +2344,17 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>1786284003</t>
+          <t>1786293511</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>1786305600</t>
+          <t>1786309200</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>34.134372</t>
+          <t>48.538486</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2323,7 +2371,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0x6771b333646b031b4dc4cfea8f533b040a6ed0a66012cdc416a7aaa5b89f7988</t>
+          <t>0x6376c34d63b4968409b909753114511b32d1413abbfce5d71dcd6fa7bb384028</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2334,17 +2382,17 @@
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>19.2</t>
+          <t>30.89</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1.5425</t>
+          <t>1.6425</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Asian Handicap (-1.5)</t>
         </is>
       </c>
       <c r="G19" t="inlineStr"/>
@@ -2370,7 +2418,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>0x4b323aab38dd8f5096dcd1965ce7dc05c69ab73371e55e810b7a5aee356bf244</t>
+          <t>0x79905ae58e04af69981e4a95c3d57b98dc3c1dd1d3e7aeb4e6a7640714001f3b</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -2400,7 +2448,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>1786283290</t>
+          <t>1786293434</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -2410,7 +2458,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>35.391705</t>
+          <t>48.077821</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2427,7 +2475,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0x8809f3e942a9cc8dca00d48b07cfe53a328d6ba2b60742c63e144e3d8cf2eaa1</t>
+          <t>0xa534180ddbde4d456a67f71365d2341259c4ca0b20e45041701c1d345202335e</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2438,17 +2486,17 @@
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>23.25749</t>
+          <t>13.52</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.4838</t>
+          <t>1.6325</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G20" t="inlineStr"/>
@@ -2459,27 +2507,27 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Colon de Santa Fe vs San Telmo</t>
+          <t>Quilmes vs Club Almagro</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Colon de Santa Fe</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Club Almagro</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0xc91217dfcd3944893195656945526d39efcd315aa93101aa312de5303c04d446</t>
+          <t>0x86a790846c1cb1bed065ac37c41b727461e30e0a9e0f9e2370ef61f6213ed31f</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>L19683494</t>
+          <t>L19683499</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -2504,17 +2552,17 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>1786281248</t>
+          <t>1786293430</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>1786300200</t>
+          <t>1786305600</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>48.077499</t>
+          <t>21.375494</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2531,7 +2579,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0xe5b95b7ede820952a7e6f5c1b2139a8092b51c4de75567f117f1291461ec6fbe</t>
+          <t>0xe6cbce05bf55e4a2647eb39e1cb6d7afdafec60905e09f42fb3552a02a5fcbd6</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2542,17 +2590,17 @@
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>23.55844</t>
+          <t>16.88999</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.6325</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G21" t="inlineStr"/>
@@ -2563,27 +2611,27 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Colon de Santa Fe vs San Telmo</t>
+          <t>Quilmes vs Club Almagro</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Colon de Santa Fe</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Club Almagro</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0xc91217dfcd3944893195656945526d39efcd315aa93101aa312de5303c04d446</t>
+          <t>0x86a790846c1cb1bed065ac37c41b727461e30e0a9e0f9e2370ef61f6213ed31f</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>L19683494</t>
+          <t>L19683499</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -2608,17 +2656,17 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>1786281243</t>
+          <t>1786293428</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>1786300200</t>
+          <t>1786305600</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>48.078449</t>
+          <t>26.703542</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -2635,7 +2683,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0x4d872ac34cfff98634d3d50362fe725a3f4ea55d64ddd9e3d7d811b073f350ab</t>
+          <t>0xae3b69e222676c5f5930a25ee6fc677945888fbd4b45894897e8c0b45b324e25</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2646,12 +2694,12 @@
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
-          <t>17.30813</t>
+          <t>12.72</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.4512</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -2667,27 +2715,27 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Colon de Santa Fe vs San Telmo</t>
+          <t>CA Los Andes vs Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Colon de Santa Fe</t>
+          <t>CA Los Andes</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0xd638a8ee6393f88ca538cc4fe6ac8cdf722bcfe6277a5ebd9387222eade88ba3</t>
+          <t>0x555a8472fba9017aa83a61e5e7cf7b05dc2822d1d1cc6174412760fc412637f7</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>L19683494</t>
+          <t>L19659153</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -2712,17 +2760,17 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>1786281243</t>
+          <t>1786288547</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>1786300200</t>
+          <t>1786296600</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>48.078139</t>
+          <t>28.188366</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -2739,28 +2787,28 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0x8f782cb5f7b30f6c129f6031ec6368ed75ea36897066f1761d9054013f56567d</t>
+          <t>0x4bb954aaa9ecad68c0eb53f2341bb75f7b8daa072a3f151571ab136be22b78df</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x71CE4A2C734a76f4C86A0D80122C4014c1F52F6e</t>
         </is>
       </c>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>29.37999</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1.4187</t>
+          <t>1.6113</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Primera Nacional</t>
+          <t>Under/Over (2)</t>
         </is>
       </c>
       <c r="G23" t="inlineStr"/>
@@ -2771,27 +2819,27 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Club Atletico Mitre de Santiago del Estero vs Defensores de Belgrano Buenos Aires</t>
+          <t>CA Los Andes vs Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Club Atletico Mitre de Santiago del Estero</t>
+          <t>CA Los Andes</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano Buenos Aires</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0x2d371e1a8a9d98624f046ea3d7126e47308ffbc183b66b1e2fba81e5ae69d7dd</t>
+          <t>0x653af58a9c77cb072171a76bcd9ca8adee427601f3ecd186c8154c81f8736395</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>L19683493</t>
+          <t>L19659153</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -2816,17 +2864,17 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>1786280425</t>
+          <t>1786288517</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>1786302000</t>
+          <t>1786296600</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>23.880597</t>
+          <t>48.065423</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -2843,7 +2891,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0xfe8890b155a19f7eb888456b555a7a6d8c293f8ecabeb69d2abd10210f520589</t>
+          <t>0xd5a2ddd8c8b6cc9bdb1c507276d3a192a5f24d46e2d3c01bfb07011263030bdd</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2854,17 +2902,17 @@
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5.67</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1.4475</t>
+          <t>1.2975</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
+          <t>Primera Nacional</t>
         </is>
       </c>
       <c r="G24" t="inlineStr"/>
@@ -2875,27 +2923,27 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Colon de Santa Fe vs San Telmo</t>
+          <t>CA Colegiales vs Patronato</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Colon de Santa Fe</t>
+          <t>CA Colegiales</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0xc91217dfcd3944893195656945526d39efcd315aa93101aa312de5303c04d446</t>
+          <t>0x710e5bf3f6759bd93c59fc8788916c16c7302071968dfba2d053e2d10f7858bf</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>L19683494</t>
+          <t>L19683449</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -2920,17 +2968,17 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>1786280403</t>
+          <t>1786288450</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>1786300200</t>
+          <t>1786298400</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>22.346369</t>
+          <t>19.058824</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -2947,7 +2995,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0x60e023296ac2f9f58237fa345b3aa08fb4f997dd34c5384f371782bf7bbd5a40</t>
+          <t>0xad9f4feea88f83ae2e46756e7d54faa300a82e055c196c70c84019780ecb560c</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2955,31 +3003,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
-          <t>26.11999</t>
+          <t>21.69</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1.5488</t>
+          <t>1.4512</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>Over 2.0</t>
-        </is>
-      </c>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -2987,27 +3027,27 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Colon de Santa Fe vs San Telmo</t>
+          <t>CA Los Andes vs Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Colon de Santa Fe</t>
+          <t>CA Los Andes</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0xc91217dfcd3944893195656945526d39efcd315aa93101aa312de5303c04d446</t>
+          <t>0x555a8472fba9017aa83a61e5e7cf7b05dc2822d1d1cc6174412760fc412637f7</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>L19683494</t>
+          <t>L19659153</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -3032,17 +3072,17 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>1786280403</t>
+          <t>1786288436</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>1786300200</t>
+          <t>1786296600</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>47.599071</t>
+          <t>48.066482</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3059,7 +3099,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0x2d118800c100a2a41a19c2053cbf355561a08867f99163fb40955a4ab012ce39</t>
+          <t>0x168e5ea2716a187c94a1c77c4c8b2523b31163ed118e4986c68c79a21d013932</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3070,17 +3110,17 @@
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
-          <t>20.07999</t>
+          <t>29.38716</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1.7363</t>
+          <t>1.6113</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
+          <t>Under/Over (2)</t>
         </is>
       </c>
       <c r="G26" t="inlineStr"/>
@@ -3091,27 +3131,27 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Godoy Cruz vs Chaco For Ever</t>
+          <t>CA Los Andes vs Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>CA Los Andes</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>0x60e111ebf03c4965ff049e67cf10f93f5cca143023c6104aab59162863b5b8a8</t>
+          <t>0x653af58a9c77cb072171a76bcd9ca8adee427601f3ecd186c8154c81f8736395</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>L19683484</t>
+          <t>L19659153</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -3136,17 +3176,17 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>1786279900</t>
+          <t>1786288436</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>1786303800</t>
+          <t>1786296600</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>27.273331</t>
+          <t>48.077153</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -3163,12 +3203,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0x904e2e53a604aa6663de774d4bd9ddf8af7459ef1c4fa1bb14486300917ac211</t>
+          <t>0x680d5db234b802aa2845f16e9d23d635dd89870065c6bfb6f6f1bde25c321bae</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -3178,22 +3218,22 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>3.96</t>
+          <t>24.36</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1.2837</t>
+          <t>1.475</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tie</t>
+          <t>CA Colegiales -0.5</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3203,27 +3243,27 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Godoy Cruz vs Chaco For Ever</t>
+          <t>CA Colegiales vs Patronato</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>CA Colegiales</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>0x08dce15d4ca4845359c2f121bce305fd3a0fe7422d497000c713e29463c6be79</t>
+          <t>0x50a3f0e4e982cdda0b9c4b9e2e1c50c67d93fbf7a068b43dbdf733c0b8d09050</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>L19683484</t>
+          <t>L19683449</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -3248,17 +3288,17 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>1786279851</t>
+          <t>1786287181</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>1786303800</t>
+          <t>1786298400</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>13.955947</t>
+          <t>51.284211</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -3275,7 +3315,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0x19a6c0536a5dea88055519ff16050cdde80d42121bb75c5045e3b562a7c1d4bb</t>
+          <t>0x5a5b6f41ac2a593747a9419c020abd417423350c2cf0a14d8cb9ef8a25d04f18</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3286,17 +3326,17 @@
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
-          <t>7.50547</t>
+          <t>8.81755</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>1.4287</t>
+          <t>1.6325</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G28" t="inlineStr"/>
@@ -3307,27 +3347,27 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Godoy Cruz vs Chaco For Ever</t>
+          <t>Quilmes vs Club Almagro</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Club Almagro</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>0xa5f02d0d08d0dcc4818948397f0f26c77f90b87182cec4d62ab01f77352671a1</t>
+          <t>0x86a790846c1cb1bed065ac37c41b727461e30e0a9e0f9e2370ef61f6213ed31f</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>L19683484</t>
+          <t>L19683499</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -3352,17 +3392,17 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>1786279821</t>
+          <t>1786284071</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>1786303800</t>
+          <t>1786305600</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>17.505469</t>
+          <t>13.940791</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -3379,7 +3419,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0x4c44e2c0c492a5115b342a42a552a040cb800bd582b07c12f1ea9161b861b487</t>
+          <t>0x9ae6e679c8fc9ed20977676ba3160d389287dd8808ea2610d0f168f9c3a42c11</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3390,17 +3430,17 @@
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
-          <t>11.30844</t>
+          <t>21.58999</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.6325</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G29" t="inlineStr"/>
@@ -3411,27 +3451,27 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Deportivo Moron vs Acassuso</t>
+          <t>Quilmes vs Club Almagro</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Deportivo Moron</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Club Almagro</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>0x108eaba0441fb45ec8e0073e945ae0ac1e138c933e4f2839816cd3198d7dd4d2</t>
+          <t>0x86a790846c1cb1bed065ac37c41b727461e30e0a9e0f9e2370ef61f6213ed31f</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>L19683452</t>
+          <t>L19683499</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -3456,17 +3496,17 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>1786278950</t>
+          <t>1786284003</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>1786298400</t>
+          <t>1786305600</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>23.078449</t>
+          <t>34.134372</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -3483,7 +3523,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0x5a5ccf0d5f6cbac6813d25e4e1e96b25b5c5a4ff8f6378d7e69d6bd3c29295ae</t>
+          <t>0x6771b333646b031b4dc4cfea8f533b040a6ed0a66012cdc416a7aaa5b89f7988</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3494,17 +3534,17 @@
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
-          <t>12.25</t>
+          <t>19.2</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.5425</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G30" t="inlineStr"/>
@@ -3515,27 +3555,27 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Deportivo Moron vs Acassuso</t>
+          <t>Colon de Santa Fe vs San Telmo</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Deportivo Moron</t>
+          <t>Colon de Santa Fe</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>0x108eaba0441fb45ec8e0073e945ae0ac1e138c933e4f2839816cd3198d7dd4d2</t>
+          <t>0x4b323aab38dd8f5096dcd1965ce7dc05c69ab73371e55e810b7a5aee356bf244</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>L19683452</t>
+          <t>L19683494</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -3560,17 +3600,17 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>1786278094</t>
+          <t>1786283290</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>1786298400</t>
+          <t>1786300200</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>35.391705</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -3587,7 +3627,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0x5f3419242a87ff17c0cb508ade95d27a54429124d36280a1dff2efa2fa0b3510</t>
+          <t>0x8809f3e942a9cc8dca00d48b07cfe53a328d6ba2b60742c63e144e3d8cf2eaa1</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3598,17 +3638,17 @@
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
-          <t>20.41999</t>
+          <t>23.25749</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1.7087</t>
+          <t>1.4838</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (2)</t>
         </is>
       </c>
       <c r="G31" t="inlineStr"/>
@@ -3619,27 +3659,27 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>CA Los Andes vs Ferro Carril Oeste</t>
+          <t>Colon de Santa Fe vs San Telmo</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>CA Los Andes</t>
+          <t>Colon de Santa Fe</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>0x31115553050eabb8d3f6a72cf2865c16175783383dcfc674615e74ed88cabaee</t>
+          <t>0xc91217dfcd3944893195656945526d39efcd315aa93101aa312de5303c04d446</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>L19659153</t>
+          <t>L19683494</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -3664,17 +3704,17 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>1786277884</t>
+          <t>1786281248</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>1786296600</t>
+          <t>1786300200</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>28.811273</t>
+          <t>48.077499</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -3691,7 +3731,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0xe6b14424302d9ef7ea2000cef83e38549f6a38c12d57faa6dd76dd84e631a5ca</t>
+          <t>0xe5b95b7ede820952a7e6f5c1b2139a8092b51c4de75567f117f1291461ec6fbe</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3702,17 +3742,17 @@
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
-          <t>12.13</t>
+          <t>23.55844</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>1.3613</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
+          <t>Under/Over (2)</t>
         </is>
       </c>
       <c r="G32" t="inlineStr"/>
@@ -3723,27 +3763,27 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Deportivo Moron vs Acassuso</t>
+          <t>Colon de Santa Fe vs San Telmo</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Deportivo Moron</t>
+          <t>Colon de Santa Fe</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0x3f34d112cfb9f093c57a3e094be078f9eea2715f97797e20d86942d58f5cc8d6</t>
+          <t>0xc91217dfcd3944893195656945526d39efcd315aa93101aa312de5303c04d446</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>L19683452</t>
+          <t>L19683494</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -3768,17 +3808,17 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>1786277708</t>
+          <t>1786281243</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>1786298400</t>
+          <t>1786300200</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>33.577855</t>
+          <t>48.078449</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -3795,7 +3835,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0xd7a2e43ba1564f619200938b384123dd68adb783742fc7b32ee335ee489d1302</t>
+          <t>0x4d872ac34cfff98634d3d50362fe725a3f4ea55d64ddd9e3d7d811b073f350ab</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3806,17 +3846,17 @@
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr">
         <is>
-          <t>10.58</t>
+          <t>17.30813</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>1.485</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
+          <t>Under/Over (1.5)</t>
         </is>
       </c>
       <c r="G33" t="inlineStr"/>
@@ -3827,27 +3867,27 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Deportivo Moron vs Acassuso</t>
+          <t>Colon de Santa Fe vs San Telmo</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Deportivo Moron</t>
+          <t>Colon de Santa Fe</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>0x108eaba0441fb45ec8e0073e945ae0ac1e138c933e4f2839816cd3198d7dd4d2</t>
+          <t>0xd638a8ee6393f88ca538cc4fe6ac8cdf722bcfe6277a5ebd9387222eade88ba3</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>L19683452</t>
+          <t>L19683494</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -3872,17 +3912,17 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>1786277679</t>
+          <t>1786281243</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>1786298400</t>
+          <t>1786300200</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>21.814433</t>
+          <t>48.078139</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -3899,7 +3939,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0xb25fa423ffb1a1464f100f2a2e9a1beac36661b9e37c8b09ecc7d3fd5a80312f</t>
+          <t>0x8f782cb5f7b30f6c129f6031ec6368ed75ea36897066f1761d9054013f56567d</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3910,17 +3950,17 @@
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
-          <t>25.88</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>1.6038</t>
+          <t>1.4187</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
+          <t>Primera Nacional</t>
         </is>
       </c>
       <c r="G34" t="inlineStr"/>
@@ -3931,27 +3971,27 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>CA Colegiales vs Patronato</t>
+          <t>Club Atletico Mitre de Santiago del Estero vs Defensores de Belgrano Buenos Aires</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>CA Colegiales</t>
+          <t>Club Atletico Mitre de Santiago del Estero</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Defensores de Belgrano Buenos Aires</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0x18dd2fdd93f5029a20e6a76c47c4f0e5c3c25768ad7f1b46a833287f8b7fcc13</t>
+          <t>0x2d371e1a8a9d98624f046ea3d7126e47308ffbc183b66b1e2fba81e5ae69d7dd</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>L19683449</t>
+          <t>L19683493</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -3976,17 +4016,17 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>1786277040</t>
+          <t>1786280425</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>1786298400</t>
+          <t>1786302000</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>42.865424</t>
+          <t>23.880597</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -4003,7 +4043,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0xfe815be8a10a6ad2cda012e463a244232a6f6c80544018f6dda52d723946b659</t>
+          <t>0xfe8890b155a19f7eb888456b555a7a6d8c293f8ecabeb69d2abd10210f520589</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4014,12 +4054,12 @@
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
-          <t>29.02571</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>1.6038</t>
+          <t>1.4475</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -4035,27 +4075,27 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>CA Colegiales vs Patronato</t>
+          <t>Colon de Santa Fe vs San Telmo</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>CA Colegiales</t>
+          <t>Colon de Santa Fe</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>0x18dd2fdd93f5029a20e6a76c47c4f0e5c3c25768ad7f1b46a833287f8b7fcc13</t>
+          <t>0xc91217dfcd3944893195656945526d39efcd315aa93101aa312de5303c04d446</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>L19683449</t>
+          <t>L19683494</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -4080,17 +4120,17 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>1786276809</t>
+          <t>1786280403</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>1786298400</t>
+          <t>1786300200</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>48.07571</t>
+          <t>22.346369</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
@@ -4107,7 +4147,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0xdb83c52876b68624e093c25e35d11910f4fbef2394ff947b658f8ea5cdb3fa88</t>
+          <t>0x60e023296ac2f9f58237fa345b3aa08fb4f997dd34c5384f371782bf7bbd5a40</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4115,23 +4155,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr"/>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>16.96</t>
+          <t>26.11999</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>1.4463</t>
+          <t>1.5488</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr"/>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Over 2.0</t>
+        </is>
+      </c>
       <c r="H36" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -4139,27 +4187,27 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>CA Colegiales vs Patronato</t>
+          <t>Colon de Santa Fe vs San Telmo</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>CA Colegiales</t>
+          <t>Colon de Santa Fe</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>0x30a6561de28b35c5bb0557dcbfc7b23e7a62558d3b0f5cfcafb67d7a07e0dd21</t>
+          <t>0xc91217dfcd3944893195656945526d39efcd315aa93101aa312de5303c04d446</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>L19683449</t>
+          <t>L19683494</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -4184,17 +4232,17 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>1786276809</t>
+          <t>1786280403</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>1786298400</t>
+          <t>1786300200</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>38.005602</t>
+          <t>47.599071</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
@@ -4211,39 +4259,31 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0x0847a2541998eecfe02d138796b14ef3d6719061787498f4888f6e14c0d196ff</t>
+          <t>0x2d118800c100a2a41a19c2053cbf355561a08867f99163fb40955a4ab012ce39</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>0xf068eF8DF8f47185D02d59Bb33d9eC7A057a571E</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr">
         <is>
-          <t>38.54</t>
+          <t>20.07999</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>1.125</t>
+          <t>1.7363</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>Club Almagro</t>
-        </is>
-      </c>
+          <t>Asian Handicap (-1.5)</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -4251,27 +4291,27 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Quilmes vs Club Almagro</t>
+          <t>Godoy Cruz vs Chaco For Ever</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>Club Almagro</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>0x03ed0858b563c1becf38b195ad94b1a84eb89c3ca8ca10b1a34220bff142f9b2</t>
+          <t>0x60e111ebf03c4965ff049e67cf10f93f5cca143023c6104aab59162863b5b8a8</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>L19683499</t>
+          <t>L19683484</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -4296,17 +4336,17 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>1786270828</t>
+          <t>1786279900</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>1786305600</t>
+          <t>1786303800</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>308.32</t>
+          <t>27.273331</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
@@ -4323,7 +4363,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0x2121e08c4ea1fe2d49a3bb388fba9e232ef9c06335c04e5eae0bf7766975512a</t>
+          <t>0x904e2e53a604aa6663de774d4bd9ddf8af7459ef1c4fa1bb14486300917ac211</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4338,12 +4378,12 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>30.06</t>
+          <t>3.96</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>1.6262</t>
+          <t>1.2837</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -4353,7 +4393,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Colon de Santa Fe</t>
+          <t>Tie</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -4363,27 +4403,27 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Colon de Santa Fe vs San Telmo</t>
+          <t>Godoy Cruz vs Chaco For Ever</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Colon de Santa Fe</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>0x1a11ec80edeaae24566c4f4f891cc2afc56b377b24997a6e8ee533eeaaad5c92</t>
+          <t>0x08dce15d4ca4845359c2f121bce305fd3a0fe7422d497000c713e29463c6be79</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>L19683494</t>
+          <t>L19683484</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -4408,17 +4448,17 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>1786253941</t>
+          <t>1786279851</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>1786300200</t>
+          <t>1786303800</t>
         </is>
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>48.0</t>
+          <t>13.955947</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
@@ -4435,27 +4475,23 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0x4e811c319e5e3a1fc1968ce0f31b4c15eb7222daa616252d99f9abc611408746</t>
+          <t>0x19a6c0536a5dea88055519ff16050cdde80d42121bb75c5045e3b562a7c1d4bb</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>0x155C76202e45BE70c50bfeD7eAeA3B98e7716Ff7</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7.50547</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>1.2925</t>
+          <t>1.4287</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -4463,11 +4499,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+      <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -4475,27 +4507,27 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Colon de Santa Fe vs San Telmo</t>
+          <t>Godoy Cruz vs Chaco For Ever</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Colon de Santa Fe</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>0x2e49527408facf21253a0a1eafe51280b82e4c31919e91a396332f19ec366401</t>
+          <t>0xa5f02d0d08d0dcc4818948397f0f26c77f90b87182cec4d62ab01f77352671a1</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>L19683494</t>
+          <t>L19683484</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -4520,17 +4552,17 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>1786243741</t>
+          <t>1786279821</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>1786300200</t>
+          <t>1786303800</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>3.418803</t>
+          <t>17.505469</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
@@ -4547,54 +4579,46 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0xb8631aeb398192a03386505542f05fa15e34db501204baa8745a4d4b5c1651b7</t>
+          <t>0x4c44e2c0c492a5115b342a42a552a040cb800bd582b07c12f1ea9161b861b487</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>0x155C76202e45BE70c50bfeD7eAeA3B98e7716Ff7</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr">
         <is>
-          <t>0.99999</t>
+          <t>11.30844</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>1.6538</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Primera Nacional</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Deportivo Moron vs Acassuso</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
         <is>
           <t>Deportivo Moron</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>Primera Nacional</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>Deportivo Moron vs Acassuso</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>Deportivo Moron</t>
-        </is>
-      </c>
       <c r="K40" t="inlineStr">
         <is>
           <t>Acassuso</t>
@@ -4602,7 +4626,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>0x7514a255ce41be3c5db9f8849ba04e78dab80f02d1fe78c2aae82bbc843a9745</t>
+          <t>0x108eaba0441fb45ec8e0073e945ae0ac1e138c933e4f2839816cd3198d7dd4d2</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -4632,7 +4656,7 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>1786243225</t>
+          <t>1786278950</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
@@ -4642,7 +4666,7 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>1.529621</t>
+          <t>23.078449</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
@@ -4659,23 +4683,23 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0xd3b94d194e43cc84f0a1b82723594ea6689a6aa2a4a7dccbc8a3d19fc321e49b</t>
+          <t>0x5a5ccf0d5f6cbac6813d25e4e1e96b25b5c5a4ff8f6378d7e69d6bd3c29295ae</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>12.25</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>1.5238</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -4736,7 +4760,7 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>1786225000</t>
+          <t>1786278094</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
@@ -4746,7 +4770,7 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>1.909308</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
@@ -4763,39 +4787,31 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0x86f4b24298f4c19f9f856cb19af2a260f24dc2d391f252248469436057ea1d1a</t>
+          <t>0x5f3419242a87ff17c0cb508ade95d27a54429124d36280a1dff2efa2fa0b3510</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20.41999</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>1.5263</t>
+          <t>1.7087</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>Deportivo Moron -1</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -4803,27 +4819,27 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Deportivo Moron vs Acassuso</t>
+          <t>CA Los Andes vs Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Deportivo Moron</t>
+          <t>CA Los Andes</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>0xb61b063252c01d0525ae633a0276dc1830eabd418482fddec925fcbd602a2a75</t>
+          <t>0x31115553050eabb8d3f6a72cf2865c16175783383dcfc674615e74ed88cabaee</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>L19683452</t>
+          <t>L19659153</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -4848,17 +4864,17 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>1786220171</t>
+          <t>1786277884</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>1786298400</t>
+          <t>1786296600</t>
         </is>
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>1.900238</t>
+          <t>28.811273</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
@@ -4875,39 +4891,31 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0x0a5de930b5a6b8aca1699b666034af3891a3aa920021791d6d13e0297fb7903f</t>
+          <t>0xe6b14424302d9ef7ea2000cef83e38549f6a38c12d57faa6dd76dd84e631a5ca</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>0x4a09916b1325Eed50eE8973B13742a205B0B7c7E</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr">
         <is>
-          <t>49.99999</t>
+          <t>12.13</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>1.6175</t>
+          <t>1.3613</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>Almirante Brown -1</t>
-        </is>
-      </c>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -4915,27 +4923,27 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Almirante Brown vs Ciudad Bolivar</t>
+          <t>Deportivo Moron vs Acassuso</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Deportivo Moron</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>Ciudad Bolivar</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>0xa6a338c64f062bfd589e8d5d9cea45a27c9e64065f71f800e5966f81ce53c556</t>
+          <t>0x3f34d112cfb9f093c57a3e094be078f9eea2715f97797e20d86942d58f5cc8d6</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>L19683447</t>
+          <t>L19683452</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -4960,17 +4968,17 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>1786218515</t>
+          <t>1786277708</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>1786212000</t>
+          <t>1786298400</t>
         </is>
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>80.971644</t>
+          <t>33.577855</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
@@ -4987,28 +4995,28 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0x17d5a08f8fa305f31f27442393c64f497dd3893417da6e76c321c4c2a187320d</t>
+          <t>0xd7a2e43ba1564f619200938b384123dd68adb783742fc7b32ee335ee489d1302</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr">
         <is>
-          <t>49.18897</t>
+          <t>10.58</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>1.4737</t>
+          <t>1.485</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Under/Over (2)</t>
         </is>
       </c>
       <c r="G44" t="inlineStr"/>
@@ -5019,27 +5027,27 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Almirante Brown vs Ciudad Bolivar</t>
+          <t>Deportivo Moron vs Acassuso</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Deportivo Moron</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>Ciudad Bolivar</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>0xa6a338c64f062bfd589e8d5d9cea45a27c9e64065f71f800e5966f81ce53c556</t>
+          <t>0x108eaba0441fb45ec8e0073e945ae0ac1e138c933e4f2839816cd3198d7dd4d2</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>L19683447</t>
+          <t>L19683452</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -5064,17 +5072,17 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>1786218084</t>
+          <t>1786277679</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>1786212000</t>
+          <t>1786298400</t>
         </is>
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>103.82896</t>
+          <t>21.814433</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
@@ -5091,28 +5099,28 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0x56975f372357be259365cb7d2929c88d4fae157eea7a71d53d57cb234834f2ca</t>
+          <t>0xb25fa423ffb1a1464f100f2a2e9a1beac36661b9e37c8b09ecc7d3fd5a80312f</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>25.88</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>1.4812</t>
+          <t>1.6038</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
+          <t>Under/Over (2)</t>
         </is>
       </c>
       <c r="G45" t="inlineStr"/>
@@ -5123,27 +5131,27 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Club Atletico Mitre de Santiago del Estero vs Defensores de Belgrano Buenos Aires</t>
+          <t>CA Colegiales vs Patronato</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Club Atletico Mitre de Santiago del Estero</t>
+          <t>CA Colegiales</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano Buenos Aires</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>0xa8ade64a3adb0ea38de67a61105ef31beb490d5a7287715b76ae124536d359cc</t>
+          <t>0x18dd2fdd93f5029a20e6a76c47c4f0e5c3c25768ad7f1b46a833287f8b7fcc13</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>L19683493</t>
+          <t>L19683449</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -5168,17 +5176,17 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>1786215674</t>
+          <t>1786277040</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>1786302000</t>
+          <t>1786298400</t>
         </is>
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>2.077922</t>
+          <t>42.865424</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
@@ -5195,39 +5203,31 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0xff53df1f3446908699196d44fcdb8b39c1bd15c7ed519f0d730e55a51a6eb38f</t>
+          <t>0xfe815be8a10a6ad2cda012e463a244232a6f6c80544018f6dda52d723946b659</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>29.02571</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>1.3713</t>
+          <t>1.6038</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>Almirante Brown</t>
-        </is>
-      </c>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr"/>
       <c r="H46" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -5235,27 +5235,27 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Almirante Brown vs Ciudad Bolivar</t>
+          <t>CA Colegiales vs Patronato</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>CA Colegiales</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>Ciudad Bolivar</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>0x63a8bf73c1084ef223fdd1096dccd16232e7a455fad77f7f0891be1588ebeb88</t>
+          <t>0x18dd2fdd93f5029a20e6a76c47c4f0e5c3c25768ad7f1b46a833287f8b7fcc13</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>L19683447</t>
+          <t>L19683449</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -5280,17 +5280,17 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>1786215673</t>
+          <t>1786276809</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>1786212000</t>
+          <t>1786298400</t>
         </is>
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>2.693603</t>
+          <t>48.07571</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
@@ -5307,7 +5307,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0x249d52552e7acb9f472d2a4c48ab754622ba572903281739a3e10b4d509dccb0</t>
+          <t>0xdb83c52876b68624e093c25e35d11910f4fbef2394ff947b658f8ea5cdb3fa88</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5315,31 +5315,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>16.96</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>1.2288</t>
+          <t>1.4463</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>Almirante Brown -1</t>
-        </is>
-      </c>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr"/>
       <c r="H47" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -5347,27 +5339,27 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Almirante Brown vs Ciudad Bolivar</t>
+          <t>CA Colegiales vs Patronato</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>CA Colegiales</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>Ciudad Bolivar</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>0xa6a338c64f062bfd589e8d5d9cea45a27c9e64065f71f800e5966f81ce53c556</t>
+          <t>0x30a6561de28b35c5bb0557dcbfc7b23e7a62558d3b0f5cfcafb67d7a07e0dd21</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>L19683447</t>
+          <t>L19683449</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -5392,17 +5384,17 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>1786214209</t>
+          <t>1786276809</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>1786212000</t>
+          <t>1786298400</t>
         </is>
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>6.295082</t>
+          <t>38.005602</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
@@ -5419,12 +5411,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0xf65c55196eeb0d21e7e3866ad26f8c3f2fee2aef273ddde5423e31fb40a51469</t>
+          <t>0x0847a2541998eecfe02d138796b14ef3d6719061787498f4888f6e14c0d196ff</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xf068eF8DF8f47185D02d59Bb33d9eC7A057a571E</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -5434,12 +5426,12 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>121.81</t>
+          <t>38.54</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>1.4363</t>
+          <t>1.125</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -5449,7 +5441,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Club Almagro</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -5459,27 +5451,27 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Almirante Brown vs Ciudad Bolivar</t>
+          <t>Quilmes vs Club Almagro</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>Ciudad Bolivar</t>
+          <t>Club Almagro</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>0x63a8bf73c1084ef223fdd1096dccd16232e7a455fad77f7f0891be1588ebeb88</t>
+          <t>0x03ed0858b563c1becf38b195ad94b1a84eb89c3ca8ca10b1a34220bff142f9b2</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>L19683447</t>
+          <t>L19683499</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -5504,17 +5496,17 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>1786213844</t>
+          <t>1786270828</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>1786212000</t>
+          <t>1786305600</t>
         </is>
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>279.22063</t>
+          <t>308.32</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
@@ -5531,12 +5523,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0x1bb20a2bf22e4fe06b44c06b9c2caa21f3f2a7c9d0cce1a2346f79e76022cd1f</t>
+          <t>0x2121e08c4ea1fe2d49a3bb388fba9e232ef9c06335c04e5eae0bf7766975512a</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -5546,22 +5538,22 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>21.05</t>
+          <t>30.06</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>1.4363</t>
+          <t>1.6262</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Almirante Brown -0.5</t>
+          <t>Colon de Santa Fe</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -5571,27 +5563,27 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Almirante Brown vs Ciudad Bolivar</t>
+          <t>Colon de Santa Fe vs San Telmo</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Colon de Santa Fe</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>Ciudad Bolivar</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>0xfa00d2f0c7b5053ee336b303a0e7ad9cec0b8d539367773b7efee5c86cb2b59d</t>
+          <t>0x1a11ec80edeaae24566c4f4f891cc2afc56b377b24997a6e8ee533eeaaad5c92</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>L19683447</t>
+          <t>L19683494</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -5616,17 +5608,17 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>1786213843</t>
+          <t>1786253941</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>1786212000</t>
+          <t>1786300200</t>
         </is>
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>48.252149</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
@@ -5643,59 +5635,67 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0xc51052f8e449b4d56cc87b697bfc8eb0d3a88ae218dee1da3d725fa94163bc75</t>
+          <t>0x4e811c319e5e3a1fc1968ce0f31b4c15eb7222daa616252d99f9abc611408746</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr"/>
+          <t>0x155C76202e45BE70c50bfeD7eAeA3B98e7716Ff7</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>77.29513</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>1.2588</t>
+          <t>1.2925</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
           <t>Primera Nacional</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr"/>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>Primera Nacional</t>
-        </is>
-      </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Almirante Brown vs Ciudad Bolivar</t>
+          <t>Colon de Santa Fe vs San Telmo</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Colon de Santa Fe</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>Ciudad Bolivar</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>0xaa5316c6f6544d74142ad6db34a3745918f237ffb1a657e000693947e81b65d6</t>
+          <t>0x2e49527408facf21253a0a1eafe51280b82e4c31919e91a396332f19ec366401</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>L19683447</t>
+          <t>L19683494</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -5720,17 +5720,17 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>1786212849</t>
+          <t>1786243741</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>1786212000</t>
+          <t>1786300200</t>
         </is>
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>298.72514</t>
+          <t>3.418803</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
@@ -5747,59 +5747,67 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0x0aeb4fe40f7d734cf244c144e6c064568b40b222193c9f93c641d1b31af3752e</t>
+          <t>0xb8631aeb398192a03386505542f05fa15e34db501204baa8745a4d4b5c1651b7</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr"/>
+          <t>0x155C76202e45BE70c50bfeD7eAeA3B98e7716Ff7</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>16.89162</t>
+          <t>0.99999</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>1.2588</t>
+          <t>1.6538</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Deportivo Moron</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
           <t>Primera Nacional</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr"/>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>Primera Nacional</t>
-        </is>
-      </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Almirante Brown vs Ciudad Bolivar</t>
+          <t>Deportivo Moron vs Acassuso</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Deportivo Moron</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>Ciudad Bolivar</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>0xaa5316c6f6544d74142ad6db34a3745918f237ffb1a657e000693947e81b65d6</t>
+          <t>0x7514a255ce41be3c5db9f8849ba04e78dab80f02d1fe78c2aae82bbc843a9745</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>L19683447</t>
+          <t>L19683452</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -5824,17 +5832,17 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>1786212805</t>
+          <t>1786243225</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>1786212000</t>
+          <t>1786298400</t>
         </is>
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>65.281623</t>
+          <t>1.529621</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
@@ -5851,67 +5859,59 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0x383b895a5fe529a887369a0f113c516fdc7f6125d54381acf9695997ef22d039</t>
+          <t>0xd3b94d194e43cc84f0a1b82723594ea6689a6aa2a4a7dccbc8a3d19fc321e49b</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr">
         <is>
-          <t>11.26905</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>1.745</t>
+          <t>1.5238</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr">
+        <is>
           <t>Primera Nacional</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>Almirante Brown</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>Primera Nacional</t>
-        </is>
-      </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Almirante Brown vs Ciudad Bolivar</t>
+          <t>Deportivo Moron vs Acassuso</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Deportivo Moron</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>Ciudad Bolivar</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>0xaa5316c6f6544d74142ad6db34a3745918f237ffb1a657e000693947e81b65d6</t>
+          <t>0x108eaba0441fb45ec8e0073e945ae0ac1e138c933e4f2839816cd3198d7dd4d2</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>L19683447</t>
+          <t>L19683452</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -5936,17 +5936,17 @@
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>1786211779</t>
+          <t>1786225000</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>1786212000</t>
+          <t>1786298400</t>
         </is>
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>15.126242</t>
+          <t>1.909308</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
@@ -5963,12 +5963,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0xcfb6add6f8610a64ffc187beb9e16bf2bacb27b54a0f0aaefa6bfb437239b893</t>
+          <t>0x86f4b24298f4c19f9f856cb19af2a260f24dc2d391f252248469436057ea1d1a</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -5978,52 +5978,52 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>24.89998</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>1.745</t>
+          <t>1.5263</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Deportivo Moron -1</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
           <t>Primera Nacional</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>Almirante Brown</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>Primera Nacional</t>
-        </is>
-      </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Almirante Brown vs Ciudad Bolivar</t>
+          <t>Deportivo Moron vs Acassuso</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Deportivo Moron</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>Ciudad Bolivar</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>0xaa5316c6f6544d74142ad6db34a3745918f237ffb1a657e000693947e81b65d6</t>
+          <t>0xb61b063252c01d0525ae633a0276dc1830eabd418482fddec925fcbd602a2a75</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>L19683447</t>
+          <t>L19683452</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -6048,17 +6048,17 @@
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>1786211777</t>
+          <t>1786220171</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>1786212000</t>
+          <t>1786298400</t>
         </is>
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>33.422792</t>
+          <t>1.900238</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
@@ -6075,12 +6075,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0xd41652604437a4e92e0d78b653d4d49d8dedd2e153d1340dad89b9b93e182a48</t>
+          <t>0x0a5de930b5a6b8aca1699b666034af3891a3aa920021791d6d13e0297fb7903f</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>0xf4a8B27C9a13e298D65b5Cc072d252816B799C81</t>
+          <t>0x4a09916b1325Eed50eE8973B13742a205B0B7c7E</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -6090,22 +6090,22 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>49.99999</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>1.4163</t>
+          <t>1.6175</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Atl. Rafaela</t>
+          <t>Almirante Brown -1</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -6115,27 +6115,27 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Atl. Rafaela vs Chacarita Juniors</t>
+          <t>Almirante Brown vs Ciudad Bolivar</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Atl. Rafaela</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Ciudad Bolivar</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>0xe738e9ba05492fab73eaaf6da211b84caadc72b08b26f1cd30fa8737e283bb44</t>
+          <t>0xa6a338c64f062bfd589e8d5d9cea45a27c9e64065f71f800e5966f81ce53c556</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>L19683450</t>
+          <t>L19683447</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -6160,17 +6160,17 @@
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>1786211028</t>
+          <t>1786218515</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>1786215600</t>
+          <t>1786212000</t>
         </is>
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>2.402402</t>
+          <t>80.971644</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
@@ -6187,28 +6187,28 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0x562fd7c6419c807ed04d3cacac95f861805f96704bd535e265399fb9d2c2b609</t>
+          <t>0x17d5a08f8fa305f31f27442393c64f497dd3893417da6e76c321c4c2a187320d</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr">
         <is>
-          <t>5.32</t>
+          <t>49.18897</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>1.405</t>
+          <t>1.4737</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G55" t="inlineStr"/>
@@ -6219,27 +6219,27 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Estudiantes de Caseros vs Deportivo Madryn</t>
+          <t>Almirante Brown vs Ciudad Bolivar</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Estudiantes de Caseros</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Ciudad Bolivar</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>0xd61509e26f8645bb9780672f942c72c4b7dab577c2a01f04e1e09bce9b828765</t>
+          <t>0xa6a338c64f062bfd589e8d5d9cea45a27c9e64065f71f800e5966f81ce53c556</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>L19683453</t>
+          <t>L19683447</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -6264,7 +6264,7 @@
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>1786210845</t>
+          <t>1786218084</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
@@ -6274,7 +6274,7 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>13.135802</t>
+          <t>103.82896</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
@@ -6291,39 +6291,31 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0x0bb7a6822220bf40d7b279f99a54f46025f393ba95bb38b6d6dc98192886b3ed</t>
+          <t>0x56975f372357be259365cb7d2929c88d4fae157eea7a71d53d57cb234834f2ca</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>0xf4a8B27C9a13e298D65b5Cc072d252816B799C81</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr">
         <is>
-          <t>0.99999</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>1.5513</t>
+          <t>1.4812</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>Agropecuario</t>
-        </is>
-      </c>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr"/>
       <c r="H56" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -6331,27 +6323,27 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Agropecuario vs Atletico Guemes</t>
+          <t>Club Atletico Mitre de Santiago del Estero vs Defensores de Belgrano Buenos Aires</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Club Atletico Mitre de Santiago del Estero</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>Atletico Guemes</t>
+          <t>Defensores de Belgrano Buenos Aires</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>0xae66c7fab3c9c76fbc29d9e9778ef4845d8a6b8d092cff34320f100020113c49</t>
+          <t>0xa8ade64a3adb0ea38de67a61105ef31beb490d5a7287715b76ae124536d359cc</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>L19683451</t>
+          <t>L19683493</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -6376,17 +6368,17 @@
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>1786205982</t>
+          <t>1786215674</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>1786212000</t>
+          <t>1786302000</t>
         </is>
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>1.814041</t>
+          <t>2.077922</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
@@ -6403,12 +6395,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>0xe17b2546f4b90c8647ba975c279e39dec1fda5a003adfb8a2b39bb12a3519b10</t>
+          <t>0xff53df1f3446908699196d44fcdb8b39c1bd15c7ed519f0d730e55a51a6eb38f</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>0xf4a8B27C9a13e298D65b5Cc072d252816B799C81</t>
+          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -6423,7 +6415,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>1.3613</t>
+          <t>1.3713</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -6433,7 +6425,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Tie</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -6458,7 +6450,7 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>0xd5906ce08d61f7c5ee45fcebd2c8baeed5558387398ea332817a4b632f439b6d</t>
+          <t>0x63a8bf73c1084ef223fdd1096dccd16232e7a455fad77f7f0891be1588ebeb88</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
@@ -6488,7 +6480,7 @@
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>1786205963</t>
+          <t>1786215673</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
@@ -6498,7 +6490,7 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>2.768166</t>
+          <t>2.693603</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
@@ -6515,12 +6507,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>0xcfe218822e89cbef5841f3045f551cc65acf353d8e240f943e2b61c54ea79a68</t>
+          <t>0x249d52552e7acb9f472d2a4c48ab754622ba572903281739a3e10b4d509dccb0</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>0xf4a8B27C9a13e298D65b5Cc072d252816B799C81</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -6530,22 +6522,22 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>1.3337</t>
+          <t>1.2288</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Tie</t>
+          <t>Almirante Brown -1</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -6555,27 +6547,27 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Estudiantes de Caseros vs Deportivo Madryn</t>
+          <t>Almirante Brown vs Ciudad Bolivar</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>Estudiantes de Caseros</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Ciudad Bolivar</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>0xf238b96ec9e2421db79973de945f1fc0c3f8bb99c31cda32d011ebaabfd2db86</t>
+          <t>0xa6a338c64f062bfd589e8d5d9cea45a27c9e64065f71f800e5966f81ce53c556</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>L19683453</t>
+          <t>L19683447</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -6600,7 +6592,7 @@
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>1786205938</t>
+          <t>1786214209</t>
         </is>
       </c>
       <c r="S58" t="inlineStr">
@@ -6610,7 +6602,7 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>2.996255</t>
+          <t>6.295082</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
@@ -6627,31 +6619,39 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>0x1b9fcb29010a212f74af57040114154e78748f06a4d826be4397ddadb45ac31b</t>
+          <t>0xf65c55196eeb0d21e7e3866ad26f8c3f2fee2aef273ddde5423e31fb40a51469</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>21.69</t>
+          <t>121.81</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>1.4512</t>
+          <t>1.4363</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Almirante Brown</t>
+        </is>
+      </c>
       <c r="H59" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -6674,7 +6674,7 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>0xbbcaa253cd967fbf933ff0d87a6f9744cafec0ed59dad5f1f76332aab01a3fa5</t>
+          <t>0x63a8bf73c1084ef223fdd1096dccd16232e7a455fad77f7f0891be1588ebeb88</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
@@ -6704,7 +6704,7 @@
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>1786190525</t>
+          <t>1786213844</t>
         </is>
       </c>
       <c r="S59" t="inlineStr">
@@ -6714,7 +6714,7 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>48.066482</t>
+          <t>279.22063</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
@@ -6731,31 +6731,39 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>0x3177792dd6a7185e37ae06612104cf5a35d137d7f535a889a83a7e9b7c174506</t>
+          <t>0x1bb20a2bf22e4fe06b44c06b9c2caa21f3f2a7c9d0cce1a2346f79e76022cd1f</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>18.35495</t>
+          <t>21.05</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>1.4963</t>
+          <t>1.4363</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr"/>
+          <t>Asian Handicap (-0.5)</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Almirante Brown -0.5</t>
+        </is>
+      </c>
       <c r="H60" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -6778,7 +6786,7 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>0xbbcaa253cd967fbf933ff0d87a6f9744cafec0ed59dad5f1f76332aab01a3fa5</t>
+          <t>0xfa00d2f0c7b5053ee336b303a0e7ad9cec0b8d539367773b7efee5c86cb2b59d</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
@@ -6808,7 +6816,7 @@
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>1786190491</t>
+          <t>1786213843</t>
         </is>
       </c>
       <c r="S60" t="inlineStr">
@@ -6818,7 +6826,7 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>36.987305</t>
+          <t>48.252149</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
@@ -6835,39 +6843,31 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>0x54ed4ee2a6ebdab49498137f1accea542ead806f21430a0a771cc4872a044e43</t>
+          <t>0xc51052f8e449b4d56cc87b697bfc8eb0d3a88ae218dee1da3d725fa94163bc75</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr"/>
       <c r="D61" t="inlineStr">
         <is>
-          <t>20.10741</t>
+          <t>77.29513</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>1.5437</t>
+          <t>1.2588</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>Over 1.5</t>
-        </is>
-      </c>
+          <t>Primera Nacional</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr"/>
       <c r="H61" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -6890,7 +6890,7 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>0xbbcaa253cd967fbf933ff0d87a6f9744cafec0ed59dad5f1f76332aab01a3fa5</t>
+          <t>0xaa5316c6f6544d74142ad6db34a3745918f237ffb1a657e000693947e81b65d6</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
@@ -6920,7 +6920,7 @@
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>1786190485</t>
+          <t>1786212849</t>
         </is>
       </c>
       <c r="S61" t="inlineStr">
@@ -6930,7 +6930,7 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>36.979145</t>
+          <t>298.72514</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
@@ -6947,28 +6947,28 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>0x544fe5c906328d009917b591611ff3438cef85f8b42d9f67732cbbd5eabbb8dd</t>
+          <t>0x0aeb4fe40f7d734cf244c144e6c064568b40b222193c9f93c641d1b31af3752e</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C62" t="inlineStr"/>
       <c r="D62" t="inlineStr">
         <is>
-          <t>21.69</t>
+          <t>16.89162</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>1.4512</t>
+          <t>1.2588</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
+          <t>Primera Nacional</t>
         </is>
       </c>
       <c r="G62" t="inlineStr"/>
@@ -6994,7 +6994,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>0xbbcaa253cd967fbf933ff0d87a6f9744cafec0ed59dad5f1f76332aab01a3fa5</t>
+          <t>0xaa5316c6f6544d74142ad6db34a3745918f237ffb1a657e000693947e81b65d6</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
@@ -7024,7 +7024,7 @@
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>1786190485</t>
+          <t>1786212805</t>
         </is>
       </c>
       <c r="S62" t="inlineStr">
@@ -7034,7 +7034,7 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>48.066482</t>
+          <t>65.281623</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
@@ -7051,31 +7051,39 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>0xb2f3ea804e1760a01d3a93678f0e2119f1ea2a9db0dc4711a06cc7bcba42b0c2</t>
+          <t>0x383b895a5fe529a887369a0f113c516fdc7f6125d54381acf9695997ef22d039</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>17.47</t>
+          <t>11.26905</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>1.405</t>
+          <t>1.745</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr"/>
+          <t>Primera Nacional</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Almirante Brown</t>
+        </is>
+      </c>
       <c r="H63" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -7083,27 +7091,27 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Estudiantes de Caseros vs Deportivo Madryn</t>
+          <t>Almirante Brown vs Ciudad Bolivar</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>Estudiantes de Caseros</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Ciudad Bolivar</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>0xd61509e26f8645bb9780672f942c72c4b7dab577c2a01f04e1e09bce9b828765</t>
+          <t>0xaa5316c6f6544d74142ad6db34a3745918f237ffb1a657e000693947e81b65d6</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>L19683453</t>
+          <t>L19683447</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
@@ -7128,7 +7136,7 @@
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>1786190461</t>
+          <t>1786211779</t>
         </is>
       </c>
       <c r="S63" t="inlineStr">
@@ -7138,7 +7146,7 @@
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>43.135802</t>
+          <t>15.126242</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
@@ -7155,7 +7163,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>0xa7eafbb77d425fc2347b4ee3e4f4e1b85f6d0f81420605db76ebfeeaa793a428</t>
+          <t>0xcfb6add6f8610a64ffc187beb9e16bf2bacb27b54a0f0aaefa6bfb437239b893</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -7163,23 +7171,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr"/>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>21.69</t>
+          <t>24.89998</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>1.4512</t>
+          <t>1.745</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr"/>
+          <t>Primera Nacional</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Almirante Brown</t>
+        </is>
+      </c>
       <c r="H64" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -7202,7 +7218,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>0xbbcaa253cd967fbf933ff0d87a6f9744cafec0ed59dad5f1f76332aab01a3fa5</t>
+          <t>0xaa5316c6f6544d74142ad6db34a3745918f237ffb1a657e000693947e81b65d6</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
@@ -7232,7 +7248,7 @@
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>1786190458</t>
+          <t>1786211777</t>
         </is>
       </c>
       <c r="S64" t="inlineStr">
@@ -7242,7 +7258,7 @@
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>48.066482</t>
+          <t>33.422792</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
@@ -7259,110 +7275,1294 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
+          <t>0xd41652604437a4e92e0d78b653d4d49d8dedd2e153d1340dad89b9b93e182a48</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>0xf4a8B27C9a13e298D65b5Cc072d252816B799C81</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>1.4163</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Atl. Rafaela</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Primera Nacional</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>Atl. Rafaela vs Chacarita Juniors</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>Atl. Rafaela</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Chacarita Juniors</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>0xe738e9ba05492fab73eaaf6da211b84caadc72b08b26f1cd30fa8737e283bb44</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>L19683450</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R65" t="inlineStr">
+        <is>
+          <t>1786211028</t>
+        </is>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>1786215600</t>
+        </is>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>2.402402</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>0x562fd7c6419c807ed04d3cacac95f861805f96704bd535e265399fb9d2c2b609</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr"/>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>5.32</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>1.405</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr"/>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Primera Nacional</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>Estudiantes de Caseros vs Deportivo Madryn</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>Estudiantes de Caseros</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Deportivo Madryn</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>0xd61509e26f8645bb9780672f942c72c4b7dab577c2a01f04e1e09bce9b828765</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>L19683453</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R66" t="inlineStr">
+        <is>
+          <t>1786210845</t>
+        </is>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>1786212000</t>
+        </is>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>13.135802</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>0x0bb7a6822220bf40d7b279f99a54f46025f393ba95bb38b6d6dc98192886b3ed</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>0xf4a8B27C9a13e298D65b5Cc072d252816B799C81</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>0.99999</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>1.5513</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Agropecuario</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Primera Nacional</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>Agropecuario vs Atletico Guemes</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>Agropecuario</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Atletico Guemes</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>0xae66c7fab3c9c76fbc29d9e9778ef4845d8a6b8d092cff34320f100020113c49</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>L19683451</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R67" t="inlineStr">
+        <is>
+          <t>1786205982</t>
+        </is>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>1786212000</t>
+        </is>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>1.814041</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>0xe17b2546f4b90c8647ba975c279e39dec1fda5a003adfb8a2b39bb12a3519b10</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>0xf4a8B27C9a13e298D65b5Cc072d252816B799C81</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>1.3613</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Primera Nacional</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>Almirante Brown vs Ciudad Bolivar</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>Almirante Brown</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Ciudad Bolivar</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>0xd5906ce08d61f7c5ee45fcebd2c8baeed5558387398ea332817a4b632f439b6d</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>L19683447</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R68" t="inlineStr">
+        <is>
+          <t>1786205963</t>
+        </is>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>1786212000</t>
+        </is>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>2.768166</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>0xcfe218822e89cbef5841f3045f551cc65acf353d8e240f943e2b61c54ea79a68</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>0xf4a8B27C9a13e298D65b5Cc072d252816B799C81</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>1.3337</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Primera Nacional</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>Estudiantes de Caseros vs Deportivo Madryn</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>Estudiantes de Caseros</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Deportivo Madryn</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>0xf238b96ec9e2421db79973de945f1fc0c3f8bb99c31cda32d011ebaabfd2db86</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>L19683453</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R69" t="inlineStr">
+        <is>
+          <t>1786205938</t>
+        </is>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>1786212000</t>
+        </is>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>2.996255</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>0x1b9fcb29010a212f74af57040114154e78748f06a4d826be4397ddadb45ac31b</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr"/>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>21.69</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>1.4512</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr"/>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Primera Nacional</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>Almirante Brown vs Ciudad Bolivar</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>Almirante Brown</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Ciudad Bolivar</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>0xbbcaa253cd967fbf933ff0d87a6f9744cafec0ed59dad5f1f76332aab01a3fa5</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>L19683447</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R70" t="inlineStr">
+        <is>
+          <t>1786190525</t>
+        </is>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>1786212000</t>
+        </is>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>48.066482</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>0x3177792dd6a7185e37ae06612104cf5a35d137d7f535a889a83a7e9b7c174506</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr"/>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>18.35495</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>1.4963</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr"/>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Primera Nacional</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>Almirante Brown vs Ciudad Bolivar</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>Almirante Brown</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Ciudad Bolivar</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>0xbbcaa253cd967fbf933ff0d87a6f9744cafec0ed59dad5f1f76332aab01a3fa5</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>L19683447</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q71" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R71" t="inlineStr">
+        <is>
+          <t>1786190491</t>
+        </is>
+      </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>1786212000</t>
+        </is>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>36.987305</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>0x54ed4ee2a6ebdab49498137f1accea542ead806f21430a0a771cc4872a044e43</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>20.10741</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>1.5437</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Over 1.5</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Primera Nacional</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>Almirante Brown vs Ciudad Bolivar</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>Almirante Brown</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Ciudad Bolivar</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>0xbbcaa253cd967fbf933ff0d87a6f9744cafec0ed59dad5f1f76332aab01a3fa5</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>L19683447</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R72" t="inlineStr">
+        <is>
+          <t>1786190485</t>
+        </is>
+      </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>1786212000</t>
+        </is>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>36.979145</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>0x544fe5c906328d009917b591611ff3438cef85f8b42d9f67732cbbd5eabbb8dd</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr"/>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>21.69</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>1.4512</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr"/>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Primera Nacional</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>Almirante Brown vs Ciudad Bolivar</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>Almirante Brown</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Ciudad Bolivar</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>0xbbcaa253cd967fbf933ff0d87a6f9744cafec0ed59dad5f1f76332aab01a3fa5</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>L19683447</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R73" t="inlineStr">
+        <is>
+          <t>1786190485</t>
+        </is>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>1786212000</t>
+        </is>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>48.066482</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>0xb2f3ea804e1760a01d3a93678f0e2119f1ea2a9db0dc4711a06cc7bcba42b0c2</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr"/>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>17.47</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>1.405</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr"/>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Primera Nacional</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>Estudiantes de Caseros vs Deportivo Madryn</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>Estudiantes de Caseros</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Deportivo Madryn</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>0xd61509e26f8645bb9780672f942c72c4b7dab577c2a01f04e1e09bce9b828765</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>L19683453</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q74" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R74" t="inlineStr">
+        <is>
+          <t>1786190461</t>
+        </is>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>1786212000</t>
+        </is>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>43.135802</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>0xa7eafbb77d425fc2347b4ee3e4f4e1b85f6d0f81420605db76ebfeeaa793a428</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr"/>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>21.69</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>1.4512</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr"/>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Primera Nacional</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>Almirante Brown vs Ciudad Bolivar</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>Almirante Brown</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Ciudad Bolivar</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>0xbbcaa253cd967fbf933ff0d87a6f9744cafec0ed59dad5f1f76332aab01a3fa5</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>L19683447</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q75" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R75" t="inlineStr">
+        <is>
+          <t>1786190458</t>
+        </is>
+      </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>1786212000</t>
+        </is>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>48.066482</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
           <t>0x5c5b512ea725fac30531bf5fe91f34f3ccc0eeff23890c18f25c3f329007c589</t>
         </is>
       </c>
-      <c r="B65" t="inlineStr">
+      <c r="B76" t="inlineStr">
         <is>
           <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr">
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
         <is>
           <t>1.3638</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr">
+      <c r="F76" t="inlineStr">
         <is>
           <t>1X2</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr">
+      <c r="G76" t="inlineStr">
         <is>
           <t>Tie</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
+      <c r="H76" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr">
+      <c r="I76" t="inlineStr">
         <is>
           <t>Almirante Brown vs Ciudad Bolivar</t>
         </is>
       </c>
-      <c r="J65" t="inlineStr">
+      <c r="J76" t="inlineStr">
         <is>
           <t>Almirante Brown</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr">
+      <c r="K76" t="inlineStr">
         <is>
           <t>Ciudad Bolivar</t>
         </is>
       </c>
-      <c r="L65" t="inlineStr">
+      <c r="L76" t="inlineStr">
         <is>
           <t>0xd5906ce08d61f7c5ee45fcebd2c8baeed5558387398ea332817a4b632f439b6d</t>
         </is>
       </c>
-      <c r="M65" t="inlineStr">
+      <c r="M76" t="inlineStr">
         <is>
           <t>L19683447</t>
         </is>
       </c>
-      <c r="N65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P65" t="inlineStr">
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q65" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R65" t="inlineStr">
+      <c r="Q76" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R76" t="inlineStr">
         <is>
           <t>1786125660</t>
         </is>
       </c>
-      <c r="S65" t="inlineStr">
+      <c r="S76" t="inlineStr">
         <is>
           <t>1786212000</t>
         </is>
       </c>
-      <c r="T65" t="inlineStr">
+      <c r="T76" t="inlineStr">
         <is>
           <t>2.749141</t>
         </is>
       </c>
-      <c r="U65" t="inlineStr">
+      <c r="U76" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V65" t="inlineStr">
+      <c r="V76" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/Primera Nacional/trades.xlsx
+++ b/data/sxbet/ligas/Primera Nacional/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V76"/>
+  <dimension ref="A1:V98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,23 +531,23 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0xaef8a42b6335c8c59cb7bb616441203e8516097ce0e7adb9c1dfe622d7b8a46a</t>
+          <t>0x2ce4118d8299ef054cc6439e8191ab57041190d43c1b322f7656f46a915f66a7</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>14.3554</t>
+          <t>11.65</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.0513</t>
+          <t>1.0888</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -563,27 +563,27 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Deportivo Moron vs Acassuso</t>
+          <t>Godoy Cruz vs Chaco For Ever</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Deportivo Moron</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0x7514a255ce41be3c5db9f8849ba04e78dab80f02d1fe78c2aae82bbc843a9745</t>
+          <t>0xa5f02d0d08d0dcc4818948397f0f26c77f90b87182cec4d62ab01f77352671a1</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>L19683452</t>
+          <t>L19683484</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -608,17 +608,17 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1786301685</t>
+          <t>1786305067</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>1786298400</t>
+          <t>1786303800</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>280.105366</t>
+          <t>131.267606</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -635,7 +635,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0x9cd0c1e560dfbdd3bb0ca9522422167bdbc75ef5c7813dbe00ce4bee50d0f1be</t>
+          <t>0x72a01c47ea710f8819c55b38617462ca579e333f91db40e5ab1feff1d3de96c8</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,23 +643,31 @@
           <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>13.80272</t>
+          <t>102.18997</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.0488</t>
+          <t>1.8087</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr"/>
+          <t>Primera Nacional</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Colon de Santa Fe</t>
+        </is>
+      </c>
       <c r="H3" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -667,27 +675,27 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Deportivo Moron vs Acassuso</t>
+          <t>Colon de Santa Fe vs San Telmo</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Deportivo Moron</t>
+          <t>Colon de Santa Fe</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0x7514a255ce41be3c5db9f8849ba04e78dab80f02d1fe78c2aae82bbc843a9745</t>
+          <t>0xbca9ed7d23a7df6c8ab98ab2ffc6649f2d4bd3d9007bd0ecf103e453c87addac</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>L19683452</t>
+          <t>L19683494</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -712,17 +720,17 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1786301534</t>
+          <t>1786305018</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>1786298400</t>
+          <t>1786300200</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>283.132718</t>
+          <t>126.35545</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -739,7 +747,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0x9036645c2b6fdeee93c9912e60b360f0e894db0b98a32ed8106dd074362ac356</t>
+          <t>0x48ad1a825a577db64992a5c2f61f562d82c8f17820251af179f0cdf9d5e6b577</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -754,22 +762,22 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>37.59</t>
+          <t>102.18997</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.1225</t>
+          <t>1.8087</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Primera Nacional</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>CA Colegiales</t>
+          <t>Colon de Santa Fe 0</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -779,27 +787,27 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>CA Colegiales vs Patronato</t>
+          <t>Colon de Santa Fe vs San Telmo</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>CA Colegiales</t>
+          <t>Colon de Santa Fe</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0x6033340ba69fb7874ae22715f395c0926449aa18c6ec5295e2568fe9a173664d</t>
+          <t>0x9c15c50c33bf4b091bef5a468ce1fe4a2593b78db6048cae08ab186caadf08a9</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>L19683449</t>
+          <t>L19683494</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -824,17 +832,17 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1786301228</t>
+          <t>1786305018</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>1786298400</t>
+          <t>1786300200</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>306.857143</t>
+          <t>126.35545</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -851,39 +859,31 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0xd9eff492baa46fea0da1221b63ca70a7e18beec129de6ebec5453a1b9e6bfcf8</t>
+          <t>0x241c6cdee87bcff9c9e1e77941a5ecd05acb972d4c07e1cfc562414003f5c59c</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>63.89997</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.4263</t>
+          <t>1.8912</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Asian Handicap (0.5)</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>CA Colegiales +0.5</t>
-        </is>
-      </c>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -891,27 +891,27 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>CA Colegiales vs Patronato</t>
+          <t>Racing de Cordoba vs San Miguel</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>CA Colegiales</t>
+          <t>Racing de Cordoba</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0xf03b2761ed02376d644cd19d08d1923efb50cd17956a930c587e812207a86746</t>
+          <t>0xb00a08202acc66af81e3cc28141951f5744b2edb09c13699c361640638e0580a</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>L19683449</t>
+          <t>L19683501</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -936,17 +936,17 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1786301216</t>
+          <t>1786304709</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>1786298400</t>
+          <t>1786302000</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>46.920821</t>
+          <t>71.697021</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -963,7 +963,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0xc72322e8ff04e28165d90bbcfa3c4b34aa19dd5fc1215e13ba7e1ce6362a9292</t>
+          <t>0xfb092fb802f6de6249f78cd6b0c995923dcd8a18d766d60718068deca14131d2</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -971,46 +971,38 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>7.93</t>
+          <t>52.23996</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.4263</t>
+          <t>1.8912</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Primera Nacional</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Racing de Cordoba vs San Miguel</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
         <is>
           <t>Racing de Cordoba</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Primera Nacional</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Racing de Cordoba vs San Miguel</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>Racing de Cordoba</t>
-        </is>
-      </c>
       <c r="K6" t="inlineStr">
         <is>
           <t>San Miguel</t>
@@ -1018,7 +1010,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0x48447168804e92d195e0c849cfb7ae548e076f102e1005f3756585b3d18ea65c</t>
+          <t>0xb00a08202acc66af81e3cc28141951f5744b2edb09c13699c361640638e0580a</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -1048,7 +1040,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1786301162</t>
+          <t>1786304687</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1058,7 +1050,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>18.604106</t>
+          <t>58.614261</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1075,39 +1067,31 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0xd37a1d074e8819ce033a62d6fe3bb026c46529f33aed65aaac63e3d53cb8ce3e</t>
+          <t>0xdaad372a2d56f6f987e31c931aed692c41df131e0f5ffc29a5e5b9202518a8ad</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0x5022174051792ac42d3af7Ff6bC9cf78a6aE3f32</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.4287</t>
+          <t>1.2563</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Under/Over (0.5)</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Over 0.5</t>
-        </is>
-      </c>
+          <t>Asian Handicap (0.5)</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -1115,27 +1099,27 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Atlanta vs Temperley</t>
+          <t>Racing de Cordoba vs San Miguel</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Racing de Cordoba</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0x84c2bb083fa51c1fc591f5ac9524e09d26434823e44ca466e2af8bd17ae651cb</t>
+          <t>0x6dbad77d129f55a581762668ca1964af6cce4241516257e981ed02638805382a</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>L19683448</t>
+          <t>L19683501</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1160,17 +1144,17 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1786300699</t>
+          <t>1786304596</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>1786294800</t>
+          <t>1786302000</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>11.661808</t>
+          <t>39.02439</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1187,28 +1171,28 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0x0199716d54c5764cbf1a6783da6c106cf378f2c6b96892a13d7019f5cb41b3fa</t>
+          <t>0xd8c270eff581f800f6dfee154ad07fcaa13887305309b80012750a0200954653</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>16.84</t>
+          <t>104.40999</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.1262</t>
+          <t>1.685</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Under/Over (0.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G8" t="inlineStr"/>
@@ -1219,27 +1203,27 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Godoy Cruz vs Chaco For Ever</t>
+          <t>Racing de Cordoba vs San Miguel</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Racing de Cordoba</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0x9c696117152178b9240c2e3eddca6b53432d4a4937a20042677cd1f666604f23</t>
+          <t>0x48447168804e92d195e0c849cfb7ae548e076f102e1005f3756585b3d18ea65c</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>L19683484</t>
+          <t>L19683501</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1264,17 +1248,17 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1786300516</t>
+          <t>1786304566</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>1786303800</t>
+          <t>1786302000</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>133.386139</t>
+          <t>152.423343</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1291,28 +1275,28 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0x84f162af96f80a1f61f37a3b12a3dab48dcffde9bd10d0cea022df759f18111f</t>
+          <t>0x584df9c83be504ffadc29cf9bc05886a622203a90bdf8fd90fe15998dca2c79a</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>36.84547</t>
+          <t>30.76</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.1362</t>
+          <t>1.8388</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Primera Nacional</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G9" t="inlineStr"/>
@@ -1323,27 +1307,27 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Colon de Santa Fe vs San Telmo</t>
+          <t>Godoy Cruz vs Chaco For Ever</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Colon de Santa Fe</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0xbca9ed7d23a7df6c8ab98ab2ffc6649f2d4bd3d9007bd0ecf103e453c87addac</t>
+          <t>0x9c19e4c1fd9646506f8ea14e2b1be19b49a5ab4dc1a7bf40167705a4ae2b338b</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>L19683494</t>
+          <t>L19683484</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1368,17 +1352,17 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1786300513</t>
+          <t>1786304409</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>1786300200</t>
+          <t>1786303800</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>270.425468</t>
+          <t>36.673621</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1395,12 +1379,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0x2f3773fa15124937ec4965274c782b70d022a4fb2a2c8e85fe36a66e0dcc1a53</t>
+          <t>0x80bb89bcfcad865ae79dd791b8e50e1efe79465dcaef80ef22f91624a9a206e0</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1410,12 +1394,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>164.56999</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.2563</t>
+          <t>1.5875</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1425,7 +1409,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Tie</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1435,27 +1419,27 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Racing de Cordoba vs San Miguel</t>
+          <t>CA Colegiales vs Patronato</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Racing de Cordoba</t>
+          <t>CA Colegiales</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0x8ddab476b71709486e3a0e2118fafcb483076bd09c1c25dcce66244486fed688</t>
+          <t>0x08cf3f4d7a357213e26484ea0db7a018932df0928a98202f91241b88b1990c60</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>L19683501</t>
+          <t>L19683449</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1480,17 +1464,17 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1786300245</t>
+          <t>1786304222</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>1786302000</t>
+          <t>1786298400</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>3.902439</t>
+          <t>280.119132</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1507,12 +1491,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0x4334abae5afdbf026c92af25200b83381434248bdfca39224de3957cba46f6e4</t>
+          <t>0x4a29c98cff774b7281c745ce8241168cf83b95715fb62c195dfe0bdfd4993ffa</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1522,12 +1506,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>52.38</t>
+          <t>50.96999</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.675</t>
+          <t>1.6187</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1592,7 +1576,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1786300042</t>
+          <t>1786304216</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1602,7 +1586,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>77.6</t>
+          <t>82.375741</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1619,7 +1603,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0xad7255fad3f7d526c2f80d7968fa11121b17d106e3df35095d9b411cead706b0</t>
+          <t>0x606477ca73e4e38677cfe19e9dbb8d21dd44116004cd1a6b689a66845a1f33c5</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1634,12 +1618,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>3.02932</t>
+          <t>47.49</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.2325</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1649,7 +1633,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Tie</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1659,27 +1643,27 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Racing de Cordoba vs San Miguel</t>
+          <t>CA Colegiales vs Patronato</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Racing de Cordoba</t>
+          <t>CA Colegiales</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>0x8ddab476b71709486e3a0e2118fafcb483076bd09c1c25dcce66244486fed688</t>
+          <t>0x08cf3f4d7a357213e26484ea0db7a018932df0928a98202f91241b88b1990c60</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>L19683501</t>
+          <t>L19683449</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1704,17 +1688,17 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1786298930</t>
+          <t>1786304193</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>1786302000</t>
+          <t>1786298400</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>13.029333</t>
+          <t>79.15</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1731,31 +1715,39 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0x972e5a678ec56c15f03cbf0d14d7070ad000111adf76887dc34cc27780792e32</t>
+          <t>0x471461bdea5d2a1f048ae19a536ae904425043d9ce35e662e416d1892b8ab682</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>24.07997</t>
+          <t>45.36</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.8675</t>
+          <t>1.6275</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr"/>
+          <t>Primera Nacional</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>CA Colegiales 0</t>
+        </is>
+      </c>
       <c r="H13" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -1763,27 +1755,27 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Godoy Cruz vs Chaco For Ever</t>
+          <t>CA Colegiales vs Patronato</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>CA Colegiales</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>0x9c19e4c1fd9646506f8ea14e2b1be19b49a5ab4dc1a7bf40167705a4ae2b338b</t>
+          <t>0x3fa48fbf2a59e0b45def889e06df3d2da646e9465f9af4f1b88581fea7fb4496</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>L19683484</t>
+          <t>L19683449</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1808,17 +1800,17 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1786297771</t>
+          <t>1786304137</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>1786303800</t>
+          <t>1786298400</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>27.75789</t>
+          <t>72.286853</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1835,39 +1827,31 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0x1da1f134f1ec859a8260a79216b9030b9f0b715d9a51d09741ff884111dcde2b</t>
+          <t>0x2b918c36189e27805e61d743881205705b15ab4bdbf93fa4149c03b299488496</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0x311AE302984D8b1cf53D6bfB0a6672f05c423AE6</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>37.76669</t>
+          <t>291.91999</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1.5837</t>
+          <t>1.8125</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Godoy Cruz -0.5</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -1875,27 +1859,27 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Godoy Cruz vs Chaco For Ever</t>
+          <t>CA Colegiales vs Patronato</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>CA Colegiales</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>0xb2c04ce7cffc1005eb6199d3c34d31b109e8af04a357b4f8eb9f6b8362ba33c2</t>
+          <t>0x08cf3f4d7a357213e26484ea0db7a018932df0928a98202f91241b88b1990c60</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>L19683484</t>
+          <t>L19683449</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1920,17 +1904,17 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1786297676</t>
+          <t>1786304032</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>1786303800</t>
+          <t>1786298400</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>64.696685</t>
+          <t>359.286142</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -1947,12 +1931,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0xfccc36b3cd4c4e2276a7540f5bb389b40f91c9998d31903af7864027f93d335e</t>
+          <t>0x0c986442e558e0ecef4ac6ae5c05b398f82bc22bf0a12f073b441ebce3f8f73e</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x161ba9aad05022c88726A1D1244fDF624e51BFD5</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1962,12 +1946,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>56.81</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1.3588</t>
+          <t>1.5063</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1977,7 +1961,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tie</t>
+          <t>Colon de Santa Fe</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1987,27 +1971,27 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>CA Los Andes vs Ferro Carril Oeste</t>
+          <t>Colon de Santa Fe vs San Telmo</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>CA Los Andes</t>
+          <t>Colon de Santa Fe</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>0x834e52f6ff115c72424372c131d41b8d94cffe6e0131918e3f85e2146509d14b</t>
+          <t>0x1a11ec80edeaae24566c4f4f891cc2afc56b377b24997a6e8ee533eeaaad5c92</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>L19659153</t>
+          <t>L19683494</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -2032,17 +2016,17 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>1786297373</t>
+          <t>1786303960</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>1786296600</t>
+          <t>1786300200</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>158.355401</t>
+          <t>4.938272</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2059,28 +2043,28 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0x48c1aed95e65b653ffb51380d6066948766a0030b4adf3bf05d152a5766c29cf</t>
+          <t>0x2a347762aef526a0953efcb99ce105f109d3055f0d91ab8c6f756cd50ff191d0</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
         </is>
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1.07999</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1.6425</t>
+          <t>1.5775</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
+          <t>Under/Over (2)</t>
         </is>
       </c>
       <c r="G16" t="inlineStr"/>
@@ -2091,27 +2075,27 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Colon de Santa Fe vs San Telmo</t>
+          <t>Godoy Cruz vs Chaco For Ever</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Colon de Santa Fe</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>0x79905ae58e04af69981e4a95c3d57b98dc3c1dd1d3e7aeb4e6a7640714001f3b</t>
+          <t>0x8a3835f02766a90c02150e223fdcaa0f380cffe1bd489dd896b621cb4de6a216</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>L19683494</t>
+          <t>L19683484</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -2136,17 +2120,17 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1786293588</t>
+          <t>1786303869</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>1786300200</t>
+          <t>1786303800</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>15.564202</t>
+          <t>1.870113</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2163,7 +2147,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0x3d4ee2d1cf7066373ffe56d01727fc04ce4ae0e1203194a2877d6ba90d9d4fcb</t>
+          <t>0xf1ea587ba3fa2b6f394d282689f029176ee146013ab745dcfa61570d0ec1af54</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2174,17 +2158,17 @@
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>16.53143</t>
+          <t>66.77496</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.3438</t>
+          <t>1.1938</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Primera Nacional</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G17" t="inlineStr"/>
@@ -2195,27 +2179,27 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Atlanta vs Temperley</t>
+          <t>CA Colegiales vs Patronato</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>CA Colegiales</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>0xc67c753c7ce425d2b225c54e0abf1308c3593fa6789a95fd59198b3a0f7a3ddd</t>
+          <t>0x6033340ba69fb7874ae22715f395c0926449aa18c6ec5295e2568fe9a173664d</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>L19683448</t>
+          <t>L19683449</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -2240,17 +2224,17 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>1786293565</t>
+          <t>1786303811</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>1786294800</t>
+          <t>1786298400</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>48.091433</t>
+          <t>344.644955</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2267,28 +2251,28 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0x5decd74680fc49716c54620aa922234edac874fb77b6369067e932fb5a40aed8</t>
+          <t>0x83f468f50e882b1c9b4663834cfdbddae84368823e2297b07a8a228b7252f9d0</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>16.98847</t>
+          <t>20.75148</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.4275</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Primera Nacional</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G18" t="inlineStr"/>
@@ -2299,27 +2283,27 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>San Martin Tucuman vs San Martín de San Juan</t>
+          <t>CA Colegiales vs Patronato</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>San Martin Tucuman</t>
+          <t>CA Colegiales</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>San Martín de San Juan</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>0x4f02331cd42a68f65ea16d62aac0c6b123d9400d12a4d556f3a72df894da02fb</t>
+          <t>0x5063fd7c88c1b369ed4a83e39411f4287c83048fafbc24740f9ecb68019a60ec</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>L19682528</t>
+          <t>L19683449</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -2344,17 +2328,17 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>1786293511</t>
+          <t>1786303811</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>1786309200</t>
+          <t>1786298400</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>48.538486</t>
+          <t>48.541474</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2371,7 +2355,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0x6376c34d63b4968409b909753114511b32d1413abbfce5d71dcd6fa7bb384028</t>
+          <t>0x5d59910b62dd3a569254988b87a126db28ce8123f67bea999e650c42a85e456c</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2382,17 +2366,17 @@
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>30.89</t>
+          <t>64.86487</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1.6425</t>
+          <t>1.075</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
+          <t>Under/Over (0.5)</t>
         </is>
       </c>
       <c r="G19" t="inlineStr"/>
@@ -2403,27 +2387,27 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Colon de Santa Fe vs San Telmo</t>
+          <t>Club Atletico Mitre de Santiago del Estero vs Defensores de Belgrano Buenos Aires</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Colon de Santa Fe</t>
+          <t>Club Atletico Mitre de Santiago del Estero</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Defensores de Belgrano Buenos Aires</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>0x79905ae58e04af69981e4a95c3d57b98dc3c1dd1d3e7aeb4e6a7640714001f3b</t>
+          <t>0x7423d14fbc1277a1b44ab6287b237b4f12599476710984e2df8514e1e505203b</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>L19683494</t>
+          <t>L19683493</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -2448,17 +2432,17 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>1786293434</t>
+          <t>1786303551</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>1786300200</t>
+          <t>1786302000</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>48.077821</t>
+          <t>864.864933</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2475,7 +2459,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0xa534180ddbde4d456a67f71365d2341259c4ca0b20e45041701c1d345202335e</t>
+          <t>0x54e4c2b9fcb34a87d3118c2c4aa1d528e53ecdeb3b19d58ec93ceabdcf9789a0</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2486,17 +2470,17 @@
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>13.52</t>
+          <t>155.22388</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.6325</t>
+          <t>1.1625</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>Under/Over (1)</t>
         </is>
       </c>
       <c r="G20" t="inlineStr"/>
@@ -2507,27 +2491,27 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Quilmes vs Club Almagro</t>
+          <t>Club Atletico Mitre de Santiago del Estero vs Defensores de Belgrano Buenos Aires</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Club Atletico Mitre de Santiago del Estero</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Club Almagro</t>
+          <t>Defensores de Belgrano Buenos Aires</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0x86a790846c1cb1bed065ac37c41b727461e30e0a9e0f9e2370ef61f6213ed31f</t>
+          <t>0x4f7afe558099a628e7275525f608e3e5d976f6f0ae76324c03ac2a8d33384e1b</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>L19683499</t>
+          <t>L19683493</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -2552,17 +2536,17 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>1786293430</t>
+          <t>1786303551</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>1786305600</t>
+          <t>1786302000</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>21.375494</t>
+          <t>955.223877</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2579,7 +2563,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0xe6cbce05bf55e4a2647eb39e1cb6d7afdafec60905e09f42fb3552a02a5fcbd6</t>
+          <t>0xac12d313bf6318f639126e42c96989b9e78cbb4aeafba2d7a6842ecaab1d4679</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2590,17 +2574,17 @@
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>16.88999</t>
+          <t>29.36999</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1.6325</t>
+          <t>1.6288</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G21" t="inlineStr"/>
@@ -2611,27 +2595,27 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Quilmes vs Club Almagro</t>
+          <t>Racing de Cordoba vs San Miguel</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Racing de Cordoba</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Club Almagro</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0x86a790846c1cb1bed065ac37c41b727461e30e0a9e0f9e2370ef61f6213ed31f</t>
+          <t>0x48447168804e92d195e0c849cfb7ae548e076f102e1005f3756585b3d18ea65c</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>L19683499</t>
+          <t>L19683501</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -2656,17 +2640,17 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>1786293428</t>
+          <t>1786303457</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>1786305600</t>
+          <t>1786302000</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>26.703542</t>
+          <t>46.711714</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -2683,31 +2667,39 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0xae3b69e222676c5f5930a25ee6fc677945888fbd4b45894897e8c0b45b324e25</t>
+          <t>0xab77c0bf2f6ec1315e378c5db8b6863eb08357a9b49d9ba43bcce724926da176</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr"/>
+          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>12.72</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1.4512</t>
+          <t>1.5175</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr"/>
+          <t>Asian Handicap (-0.5)</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Colon de Santa Fe -0.5</t>
+        </is>
+      </c>
       <c r="H22" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -2715,27 +2707,27 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>CA Los Andes vs Ferro Carril Oeste</t>
+          <t>Colon de Santa Fe vs San Telmo</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>CA Los Andes</t>
+          <t>Colon de Santa Fe</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0x555a8472fba9017aa83a61e5e7cf7b05dc2822d1d1cc6174412760fc412637f7</t>
+          <t>0x12375b1d9ef51c6465eb968d63b1ce25f63b0af22de8742ede4e1070f2e04c6b</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>L19659153</t>
+          <t>L19683494</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -2760,17 +2752,17 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>1786288547</t>
+          <t>1786302968</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>1786296600</t>
+          <t>1786300200</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>28.188366</t>
+          <t>2.801932</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -2787,31 +2779,39 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0x4bb954aaa9ecad68c0eb53f2341bb75f7b8daa072a3f151571ab136be22b78df</t>
+          <t>0x7262b8ffc279b263369649339936e85dc19d4d92bf11fad680b40a45ad4a7442</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0x71CE4A2C734a76f4C86A0D80122C4014c1F52F6e</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>29.37999</t>
+          <t>23.24</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1.6113</t>
+          <t>1.3388</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr"/>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Colon de Santa Fe -1</t>
+        </is>
+      </c>
       <c r="H23" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -2819,27 +2819,27 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>CA Los Andes vs Ferro Carril Oeste</t>
+          <t>Colon de Santa Fe vs San Telmo</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>CA Los Andes</t>
+          <t>Colon de Santa Fe</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0x653af58a9c77cb072171a76bcd9ca8adee427601f3ecd186c8154c81f8736395</t>
+          <t>0x4b323aab38dd8f5096dcd1965ce7dc05c69ab73371e55e810b7a5aee356bf244</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>L19659153</t>
+          <t>L19683494</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -2864,17 +2864,17 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>1786288517</t>
+          <t>1786302417</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>1786296600</t>
+          <t>1786300200</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>48.065423</t>
+          <t>68.605166</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -2891,28 +2891,28 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0xd5a2ddd8c8b6cc9bdb1c507276d3a192a5f24d46e2d3c01bfb07011263030bdd</t>
+          <t>0xaef8a42b6335c8c59cb7bb616441203e8516097ce0e7adb9c1dfe622d7b8a46a</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
-          <t>5.67</t>
+          <t>14.3554</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1.2975</t>
+          <t>1.0513</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Primera Nacional</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G24" t="inlineStr"/>
@@ -2923,27 +2923,27 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>CA Colegiales vs Patronato</t>
+          <t>Deportivo Moron vs Acassuso</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>CA Colegiales</t>
+          <t>Deportivo Moron</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0x710e5bf3f6759bd93c59fc8788916c16c7302071968dfba2d053e2d10f7858bf</t>
+          <t>0x7514a255ce41be3c5db9f8849ba04e78dab80f02d1fe78c2aae82bbc843a9745</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>L19683449</t>
+          <t>L19683452</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -2968,7 +2968,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>1786288450</t>
+          <t>1786301685</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -2978,7 +2978,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>19.058824</t>
+          <t>280.105366</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -2995,28 +2995,28 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0xad9f4feea88f83ae2e46756e7d54faa300a82e055c196c70c84019780ecb560c</t>
+          <t>0x9cd0c1e560dfbdd3bb0ca9522422167bdbc75ef5c7813dbe00ce4bee50d0f1be</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
-          <t>21.69</t>
+          <t>13.80272</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1.4512</t>
+          <t>1.0488</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G25" t="inlineStr"/>
@@ -3027,27 +3027,27 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>CA Los Andes vs Ferro Carril Oeste</t>
+          <t>Deportivo Moron vs Acassuso</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>CA Los Andes</t>
+          <t>Deportivo Moron</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0x555a8472fba9017aa83a61e5e7cf7b05dc2822d1d1cc6174412760fc412637f7</t>
+          <t>0x7514a255ce41be3c5db9f8849ba04e78dab80f02d1fe78c2aae82bbc843a9745</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>L19659153</t>
+          <t>L19683452</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -3072,17 +3072,17 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>1786288436</t>
+          <t>1786301534</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>1786296600</t>
+          <t>1786298400</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>48.066482</t>
+          <t>283.132718</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3099,31 +3099,39 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0x168e5ea2716a187c94a1c77c4c8b2523b31163ed118e4986c68c79a21d013932</t>
+          <t>0x9036645c2b6fdeee93c9912e60b360f0e894db0b98a32ed8106dd074362ac356</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>29.38716</t>
+          <t>37.59</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1.6113</t>
+          <t>1.1225</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>CA Colegiales</t>
+        </is>
+      </c>
       <c r="H26" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -3131,27 +3139,27 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>CA Los Andes vs Ferro Carril Oeste</t>
+          <t>CA Colegiales vs Patronato</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>CA Los Andes</t>
+          <t>CA Colegiales</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>0x653af58a9c77cb072171a76bcd9ca8adee427601f3ecd186c8154c81f8736395</t>
+          <t>0x6033340ba69fb7874ae22715f395c0926449aa18c6ec5295e2568fe9a173664d</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>L19659153</t>
+          <t>L19683449</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -3176,17 +3184,17 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>1786288436</t>
+          <t>1786301228</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>1786296600</t>
+          <t>1786298400</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>48.077153</t>
+          <t>306.857143</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -3203,7 +3211,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0x680d5db234b802aa2845f16e9d23d635dd89870065c6bfb6f6f1bde25c321bae</t>
+          <t>0xd9eff492baa46fea0da1221b63ca70a7e18beec129de6ebec5453a1b9e6bfcf8</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3218,22 +3226,22 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>24.36</t>
+          <t>20</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1.475</t>
+          <t>1.4263</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
+          <t>Asian Handicap (0.5)</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>CA Colegiales -0.5</t>
+          <t>CA Colegiales +0.5</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3258,7 +3266,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>0x50a3f0e4e982cdda0b9c4b9e2e1c50c67d93fbf7a068b43dbdf733c0b8d09050</t>
+          <t>0xf03b2761ed02376d644cd19d08d1923efb50cd17956a930c587e812207a86746</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -3288,7 +3296,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>1786287181</t>
+          <t>1786301216</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -3298,7 +3306,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>51.284211</t>
+          <t>46.920821</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -3315,7 +3323,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0x5a5b6f41ac2a593747a9419c020abd417423350c2cf0a14d8cb9ef8a25d04f18</t>
+          <t>0xc72322e8ff04e28165d90bbcfa3c4b34aa19dd5fc1215e13ba7e1ce6362a9292</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3323,23 +3331,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr"/>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>8.81755</t>
+          <t>7.93</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>1.6325</t>
+          <t>1.4263</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Racing de Cordoba</t>
+        </is>
+      </c>
       <c r="H28" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -3347,27 +3363,27 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Quilmes vs Club Almagro</t>
+          <t>Racing de Cordoba vs San Miguel</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Racing de Cordoba</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>Club Almagro</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>0x86a790846c1cb1bed065ac37c41b727461e30e0a9e0f9e2370ef61f6213ed31f</t>
+          <t>0x48447168804e92d195e0c849cfb7ae548e076f102e1005f3756585b3d18ea65c</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>L19683499</t>
+          <t>L19683501</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -3392,17 +3408,17 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>1786284071</t>
+          <t>1786301162</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>1786305600</t>
+          <t>1786302000</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>13.940791</t>
+          <t>18.604106</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -3419,31 +3435,39 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0x9ae6e679c8fc9ed20977676ba3160d389287dd8808ea2610d0f168f9c3a42c11</t>
+          <t>0xd37a1d074e8819ce033a62d6fe3bb026c46529f33aed65aaac63e3d53cb8ce3e</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr"/>
+          <t>0x5022174051792ac42d3af7Ff6bC9cf78a6aE3f32</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>21.58999</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>1.6325</t>
+          <t>1.4287</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr"/>
+          <t>Under/Over (0.5)</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Over 0.5</t>
+        </is>
+      </c>
       <c r="H29" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -3451,27 +3475,27 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Quilmes vs Club Almagro</t>
+          <t>Atlanta vs Temperley</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>Club Almagro</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>0x86a790846c1cb1bed065ac37c41b727461e30e0a9e0f9e2370ef61f6213ed31f</t>
+          <t>0x84c2bb083fa51c1fc591f5ac9524e09d26434823e44ca466e2af8bd17ae651cb</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>L19683499</t>
+          <t>L19683448</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -3496,17 +3520,17 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>1786284003</t>
+          <t>1786300699</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>1786305600</t>
+          <t>1786294800</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>34.134372</t>
+          <t>11.661808</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -3523,28 +3547,28 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0x6771b333646b031b4dc4cfea8f533b040a6ed0a66012cdc416a7aaa5b89f7988</t>
+          <t>0x0199716d54c5764cbf1a6783da6c106cf378f2c6b96892a13d7019f5cb41b3fa</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
-          <t>19.2</t>
+          <t>16.84</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1.5425</t>
+          <t>1.1262</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Under/Over (0.5)</t>
         </is>
       </c>
       <c r="G30" t="inlineStr"/>
@@ -3555,27 +3579,27 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Colon de Santa Fe vs San Telmo</t>
+          <t>Godoy Cruz vs Chaco For Ever</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Colon de Santa Fe</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>0x4b323aab38dd8f5096dcd1965ce7dc05c69ab73371e55e810b7a5aee356bf244</t>
+          <t>0x9c696117152178b9240c2e3eddca6b53432d4a4937a20042677cd1f666604f23</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>L19683494</t>
+          <t>L19683484</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -3600,17 +3624,17 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>1786283290</t>
+          <t>1786300516</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>1786300200</t>
+          <t>1786303800</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>35.391705</t>
+          <t>133.386139</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -3627,28 +3651,28 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0x8809f3e942a9cc8dca00d48b07cfe53a328d6ba2b60742c63e144e3d8cf2eaa1</t>
+          <t>0x84f162af96f80a1f61f37a3b12a3dab48dcffde9bd10d0cea022df759f18111f</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
-          <t>23.25749</t>
+          <t>36.84547</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1.4838</t>
+          <t>1.1362</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
+          <t>Primera Nacional</t>
         </is>
       </c>
       <c r="G31" t="inlineStr"/>
@@ -3674,7 +3698,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>0xc91217dfcd3944893195656945526d39efcd315aa93101aa312de5303c04d446</t>
+          <t>0xbca9ed7d23a7df6c8ab98ab2ffc6649f2d4bd3d9007bd0ecf103e453c87addac</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -3704,7 +3728,7 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>1786281248</t>
+          <t>1786300513</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
@@ -3714,7 +3738,7 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>48.077499</t>
+          <t>270.425468</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -3731,31 +3755,39 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0xe5b95b7ede820952a7e6f5c1b2139a8092b51c4de75567f117f1291461ec6fbe</t>
+          <t>0x2f3773fa15124937ec4965274c782b70d022a4fb2a2c8e85fe36a66e0dcc1a53</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr"/>
+          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>23.55844</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.2563</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>San Miguel</t>
+        </is>
+      </c>
       <c r="H32" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -3763,27 +3795,27 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Colon de Santa Fe vs San Telmo</t>
+          <t>Racing de Cordoba vs San Miguel</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Colon de Santa Fe</t>
+          <t>Racing de Cordoba</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0xc91217dfcd3944893195656945526d39efcd315aa93101aa312de5303c04d446</t>
+          <t>0x8ddab476b71709486e3a0e2118fafcb483076bd09c1c25dcce66244486fed688</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>L19683494</t>
+          <t>L19683501</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -3808,17 +3840,17 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>1786281243</t>
+          <t>1786300245</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>1786300200</t>
+          <t>1786302000</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>48.078449</t>
+          <t>3.902439</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -3835,7 +3867,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0x4d872ac34cfff98634d3d50362fe725a3f4ea55d64ddd9e3d7d811b073f350ab</t>
+          <t>0x4334abae5afdbf026c92af25200b83381434248bdfca39224de3957cba46f6e4</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3843,23 +3875,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr"/>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>17.30813</t>
+          <t>52.38</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.675</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr"/>
+          <t>Primera Nacional</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>CA Colegiales 0</t>
+        </is>
+      </c>
       <c r="H33" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -3867,27 +3907,27 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Colon de Santa Fe vs San Telmo</t>
+          <t>CA Colegiales vs Patronato</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Colon de Santa Fe</t>
+          <t>CA Colegiales</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>0xd638a8ee6393f88ca538cc4fe6ac8cdf722bcfe6277a5ebd9387222eade88ba3</t>
+          <t>0x3fa48fbf2a59e0b45def889e06df3d2da646e9465f9af4f1b88581fea7fb4496</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>L19683494</t>
+          <t>L19683449</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -3912,17 +3952,17 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>1786281243</t>
+          <t>1786300042</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>1786300200</t>
+          <t>1786298400</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>48.078139</t>
+          <t>77.6</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -3939,7 +3979,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0x8f782cb5f7b30f6c129f6031ec6368ed75ea36897066f1761d9054013f56567d</t>
+          <t>0xad7255fad3f7d526c2f80d7968fa11121b17d106e3df35095d9b411cead706b0</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3947,23 +3987,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr"/>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3.02932</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>1.4187</t>
+          <t>1.2325</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Primera Nacional</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>San Miguel</t>
+        </is>
+      </c>
       <c r="H34" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -3971,27 +4019,27 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Club Atletico Mitre de Santiago del Estero vs Defensores de Belgrano Buenos Aires</t>
+          <t>Racing de Cordoba vs San Miguel</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Club Atletico Mitre de Santiago del Estero</t>
+          <t>Racing de Cordoba</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano Buenos Aires</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0x2d371e1a8a9d98624f046ea3d7126e47308ffbc183b66b1e2fba81e5ae69d7dd</t>
+          <t>0x8ddab476b71709486e3a0e2118fafcb483076bd09c1c25dcce66244486fed688</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>L19683493</t>
+          <t>L19683501</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -4016,7 +4064,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>1786280425</t>
+          <t>1786298930</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
@@ -4026,7 +4074,7 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>23.880597</t>
+          <t>13.029333</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -4043,7 +4091,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0xfe8890b155a19f7eb888456b555a7a6d8c293f8ecabeb69d2abd10210f520589</t>
+          <t>0x972e5a678ec56c15f03cbf0d14d7070ad000111adf76887dc34cc27780792e32</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4054,17 +4102,17 @@
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>24.07997</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>1.4475</t>
+          <t>1.8675</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G35" t="inlineStr"/>
@@ -4075,27 +4123,27 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Colon de Santa Fe vs San Telmo</t>
+          <t>Godoy Cruz vs Chaco For Ever</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Colon de Santa Fe</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>0xc91217dfcd3944893195656945526d39efcd315aa93101aa312de5303c04d446</t>
+          <t>0x9c19e4c1fd9646506f8ea14e2b1be19b49a5ab4dc1a7bf40167705a4ae2b338b</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>L19683494</t>
+          <t>L19683484</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -4120,17 +4168,17 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>1786280403</t>
+          <t>1786297771</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>1786300200</t>
+          <t>1786303800</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>22.346369</t>
+          <t>27.75789</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
@@ -4147,12 +4195,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0x60e023296ac2f9f58237fa345b3aa08fb4f997dd34c5384f371782bf7bbd5a40</t>
+          <t>0x1da1f134f1ec859a8260a79216b9030b9f0b715d9a51d09741ff884111dcde2b</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x311AE302984D8b1cf53D6bfB0a6672f05c423AE6</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -4162,22 +4210,22 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>26.11999</t>
+          <t>37.76669</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>1.5488</t>
+          <t>1.5837</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
+          <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Over 2.0</t>
+          <t>Godoy Cruz -0.5</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -4187,27 +4235,27 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Colon de Santa Fe vs San Telmo</t>
+          <t>Godoy Cruz vs Chaco For Ever</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Colon de Santa Fe</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>0xc91217dfcd3944893195656945526d39efcd315aa93101aa312de5303c04d446</t>
+          <t>0xb2c04ce7cffc1005eb6199d3c34d31b109e8af04a357b4f8eb9f6b8362ba33c2</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>L19683494</t>
+          <t>L19683484</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -4232,17 +4280,17 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>1786280403</t>
+          <t>1786297676</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>1786300200</t>
+          <t>1786303800</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>47.599071</t>
+          <t>64.696685</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
@@ -4259,7 +4307,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0x2d118800c100a2a41a19c2053cbf355561a08867f99163fb40955a4ab012ce39</t>
+          <t>0xfccc36b3cd4c4e2276a7540f5bb389b40f91c9998d31903af7864027f93d335e</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4267,23 +4315,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr"/>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>20.07999</t>
+          <t>56.81</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>1.7363</t>
+          <t>1.3588</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H37" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -4291,27 +4347,27 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Godoy Cruz vs Chaco For Ever</t>
+          <t>CA Los Andes vs Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>CA Los Andes</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>0x60e111ebf03c4965ff049e67cf10f93f5cca143023c6104aab59162863b5b8a8</t>
+          <t>0x834e52f6ff115c72424372c131d41b8d94cffe6e0131918e3f85e2146509d14b</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>L19683484</t>
+          <t>L19659153</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -4336,17 +4392,17 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>1786279900</t>
+          <t>1786297373</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>1786303800</t>
+          <t>1786296600</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>27.273331</t>
+          <t>158.355401</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
@@ -4363,7 +4419,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0x904e2e53a604aa6663de774d4bd9ddf8af7459ef1c4fa1bb14486300917ac211</t>
+          <t>0x48c1aed95e65b653ffb51380d6066948766a0030b4adf3bf05d152a5766c29cf</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4371,31 +4427,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr">
         <is>
-          <t>3.96</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>1.2837</t>
+          <t>1.6425</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+          <t>Asian Handicap (-1.5)</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -4403,27 +4451,27 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Godoy Cruz vs Chaco For Ever</t>
+          <t>Colon de Santa Fe vs San Telmo</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Colon de Santa Fe</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>0x08dce15d4ca4845359c2f121bce305fd3a0fe7422d497000c713e29463c6be79</t>
+          <t>0x79905ae58e04af69981e4a95c3d57b98dc3c1dd1d3e7aeb4e6a7640714001f3b</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>L19683484</t>
+          <t>L19683494</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -4448,17 +4496,17 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>1786279851</t>
+          <t>1786293588</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>1786303800</t>
+          <t>1786300200</t>
         </is>
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>13.955947</t>
+          <t>15.564202</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
@@ -4475,28 +4523,28 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0x19a6c0536a5dea88055519ff16050cdde80d42121bb75c5045e3b562a7c1d4bb</t>
+          <t>0x3d4ee2d1cf7066373ffe56d01727fc04ce4ae0e1203194a2877d6ba90d9d4fcb</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr">
         <is>
-          <t>7.50547</t>
+          <t>16.53143</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>1.4287</t>
+          <t>1.3438</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Primera Nacional</t>
         </is>
       </c>
       <c r="G39" t="inlineStr"/>
@@ -4507,27 +4555,27 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Godoy Cruz vs Chaco For Ever</t>
+          <t>Atlanta vs Temperley</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>0xa5f02d0d08d0dcc4818948397f0f26c77f90b87182cec4d62ab01f77352671a1</t>
+          <t>0xc67c753c7ce425d2b225c54e0abf1308c3593fa6789a95fd59198b3a0f7a3ddd</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>L19683484</t>
+          <t>L19683448</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -4552,17 +4600,17 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>1786279821</t>
+          <t>1786293565</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>1786303800</t>
+          <t>1786294800</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>17.505469</t>
+          <t>48.091433</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
@@ -4579,7 +4627,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0x4c44e2c0c492a5115b342a42a552a040cb800bd582b07c12f1ea9161b861b487</t>
+          <t>0x5decd74680fc49716c54620aa922234edac874fb77b6369067e932fb5a40aed8</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4590,17 +4638,17 @@
       <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr">
         <is>
-          <t>11.30844</t>
+          <t>16.98847</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
+          <t>Primera Nacional</t>
         </is>
       </c>
       <c r="G40" t="inlineStr"/>
@@ -4611,27 +4659,27 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Deportivo Moron vs Acassuso</t>
+          <t>San Martin Tucuman vs San Martín de San Juan</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Deportivo Moron</t>
+          <t>San Martin Tucuman</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>San Martín de San Juan</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>0x108eaba0441fb45ec8e0073e945ae0ac1e138c933e4f2839816cd3198d7dd4d2</t>
+          <t>0x4f02331cd42a68f65ea16d62aac0c6b123d9400d12a4d556f3a72df894da02fb</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>L19683452</t>
+          <t>L19682528</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -4656,17 +4704,17 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>1786278950</t>
+          <t>1786293511</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>1786298400</t>
+          <t>1786309200</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>23.078449</t>
+          <t>48.538486</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
@@ -4683,7 +4731,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0x5a5ccf0d5f6cbac6813d25e4e1e96b25b5c5a4ff8f6378d7e69d6bd3c29295ae</t>
+          <t>0x6376c34d63b4968409b909753114511b32d1413abbfce5d71dcd6fa7bb384028</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4694,17 +4742,17 @@
       <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr">
         <is>
-          <t>12.25</t>
+          <t>30.89</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.6425</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
+          <t>Asian Handicap (-1.5)</t>
         </is>
       </c>
       <c r="G41" t="inlineStr"/>
@@ -4715,27 +4763,27 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Deportivo Moron vs Acassuso</t>
+          <t>Colon de Santa Fe vs San Telmo</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Deportivo Moron</t>
+          <t>Colon de Santa Fe</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>0x108eaba0441fb45ec8e0073e945ae0ac1e138c933e4f2839816cd3198d7dd4d2</t>
+          <t>0x79905ae58e04af69981e4a95c3d57b98dc3c1dd1d3e7aeb4e6a7640714001f3b</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>L19683452</t>
+          <t>L19683494</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -4760,17 +4808,17 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>1786278094</t>
+          <t>1786293434</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>1786298400</t>
+          <t>1786300200</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>48.077821</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
@@ -4787,7 +4835,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0x5f3419242a87ff17c0cb508ade95d27a54429124d36280a1dff2efa2fa0b3510</t>
+          <t>0xa534180ddbde4d456a67f71365d2341259c4ca0b20e45041701c1d345202335e</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4798,17 +4846,17 @@
       <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr">
         <is>
-          <t>20.41999</t>
+          <t>13.52</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>1.7087</t>
+          <t>1.6325</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G42" t="inlineStr"/>
@@ -4819,27 +4867,27 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>CA Los Andes vs Ferro Carril Oeste</t>
+          <t>Quilmes vs Club Almagro</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>CA Los Andes</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Club Almagro</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>0x31115553050eabb8d3f6a72cf2865c16175783383dcfc674615e74ed88cabaee</t>
+          <t>0x86a790846c1cb1bed065ac37c41b727461e30e0a9e0f9e2370ef61f6213ed31f</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>L19659153</t>
+          <t>L19683499</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -4864,17 +4912,17 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>1786277884</t>
+          <t>1786293430</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>1786296600</t>
+          <t>1786305600</t>
         </is>
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>28.811273</t>
+          <t>21.375494</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
@@ -4891,7 +4939,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0xe6b14424302d9ef7ea2000cef83e38549f6a38c12d57faa6dd76dd84e631a5ca</t>
+          <t>0xe6cbce05bf55e4a2647eb39e1cb6d7afdafec60905e09f42fb3552a02a5fcbd6</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4902,17 +4950,17 @@
       <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr">
         <is>
-          <t>12.13</t>
+          <t>16.88999</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>1.3613</t>
+          <t>1.6325</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G43" t="inlineStr"/>
@@ -4923,27 +4971,27 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Deportivo Moron vs Acassuso</t>
+          <t>Quilmes vs Club Almagro</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Deportivo Moron</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Club Almagro</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>0x3f34d112cfb9f093c57a3e094be078f9eea2715f97797e20d86942d58f5cc8d6</t>
+          <t>0x86a790846c1cb1bed065ac37c41b727461e30e0a9e0f9e2370ef61f6213ed31f</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>L19683452</t>
+          <t>L19683499</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -4968,17 +5016,17 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>1786277708</t>
+          <t>1786293428</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>1786298400</t>
+          <t>1786305600</t>
         </is>
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>33.577855</t>
+          <t>26.703542</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
@@ -4995,7 +5043,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0xd7a2e43ba1564f619200938b384123dd68adb783742fc7b32ee335ee489d1302</t>
+          <t>0xae3b69e222676c5f5930a25ee6fc677945888fbd4b45894897e8c0b45b324e25</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5006,17 +5054,17 @@
       <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr">
         <is>
-          <t>10.58</t>
+          <t>12.72</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>1.485</t>
+          <t>1.4512</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
+          <t>Under/Over (1.5)</t>
         </is>
       </c>
       <c r="G44" t="inlineStr"/>
@@ -5027,27 +5075,27 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Deportivo Moron vs Acassuso</t>
+          <t>CA Los Andes vs Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Deportivo Moron</t>
+          <t>CA Los Andes</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>0x108eaba0441fb45ec8e0073e945ae0ac1e138c933e4f2839816cd3198d7dd4d2</t>
+          <t>0x555a8472fba9017aa83a61e5e7cf7b05dc2822d1d1cc6174412760fc412637f7</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>L19683452</t>
+          <t>L19659153</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -5072,17 +5120,17 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>1786277679</t>
+          <t>1786288547</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>1786298400</t>
+          <t>1786296600</t>
         </is>
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>21.814433</t>
+          <t>28.188366</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
@@ -5099,23 +5147,23 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0xb25fa423ffb1a1464f100f2a2e9a1beac36661b9e37c8b09ecc7d3fd5a80312f</t>
+          <t>0x4bb954aaa9ecad68c0eb53f2341bb75f7b8daa072a3f151571ab136be22b78df</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x71CE4A2C734a76f4C86A0D80122C4014c1F52F6e</t>
         </is>
       </c>
       <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr">
         <is>
-          <t>25.88</t>
+          <t>29.37999</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>1.6038</t>
+          <t>1.6113</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -5131,27 +5179,27 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>CA Colegiales vs Patronato</t>
+          <t>CA Los Andes vs Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>CA Colegiales</t>
+          <t>CA Los Andes</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>0x18dd2fdd93f5029a20e6a76c47c4f0e5c3c25768ad7f1b46a833287f8b7fcc13</t>
+          <t>0x653af58a9c77cb072171a76bcd9ca8adee427601f3ecd186c8154c81f8736395</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>L19683449</t>
+          <t>L19659153</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -5176,17 +5224,17 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>1786277040</t>
+          <t>1786288517</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>1786298400</t>
+          <t>1786296600</t>
         </is>
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>42.865424</t>
+          <t>48.065423</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
@@ -5203,7 +5251,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0xfe815be8a10a6ad2cda012e463a244232a6f6c80544018f6dda52d723946b659</t>
+          <t>0xd5a2ddd8c8b6cc9bdb1c507276d3a192a5f24d46e2d3c01bfb07011263030bdd</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5214,17 +5262,17 @@
       <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr">
         <is>
-          <t>29.02571</t>
+          <t>5.67</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>1.6038</t>
+          <t>1.2975</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
+          <t>Primera Nacional</t>
         </is>
       </c>
       <c r="G46" t="inlineStr"/>
@@ -5250,7 +5298,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>0x18dd2fdd93f5029a20e6a76c47c4f0e5c3c25768ad7f1b46a833287f8b7fcc13</t>
+          <t>0x710e5bf3f6759bd93c59fc8788916c16c7302071968dfba2d053e2d10f7858bf</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -5280,7 +5328,7 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>1786276809</t>
+          <t>1786288450</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
@@ -5290,7 +5338,7 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>48.07571</t>
+          <t>19.058824</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
@@ -5307,7 +5355,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0xdb83c52876b68624e093c25e35d11910f4fbef2394ff947b658f8ea5cdb3fa88</t>
+          <t>0xad9f4feea88f83ae2e46756e7d54faa300a82e055c196c70c84019780ecb560c</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5318,12 +5366,12 @@
       <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr">
         <is>
-          <t>16.96</t>
+          <t>21.69</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>1.4463</t>
+          <t>1.4512</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -5339,27 +5387,27 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>CA Colegiales vs Patronato</t>
+          <t>CA Los Andes vs Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>CA Colegiales</t>
+          <t>CA Los Andes</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>0x30a6561de28b35c5bb0557dcbfc7b23e7a62558d3b0f5cfcafb67d7a07e0dd21</t>
+          <t>0x555a8472fba9017aa83a61e5e7cf7b05dc2822d1d1cc6174412760fc412637f7</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>L19683449</t>
+          <t>L19659153</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -5384,17 +5432,17 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>1786276809</t>
+          <t>1786288436</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>1786298400</t>
+          <t>1786296600</t>
         </is>
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>38.005602</t>
+          <t>48.066482</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
@@ -5411,39 +5459,31 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0x0847a2541998eecfe02d138796b14ef3d6719061787498f4888f6e14c0d196ff</t>
+          <t>0x168e5ea2716a187c94a1c77c4c8b2523b31163ed118e4986c68c79a21d013932</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>0xf068eF8DF8f47185D02d59Bb33d9eC7A057a571E</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr">
         <is>
-          <t>38.54</t>
+          <t>29.38716</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>1.125</t>
+          <t>1.6113</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>Club Almagro</t>
-        </is>
-      </c>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr"/>
       <c r="H48" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -5451,27 +5491,27 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Quilmes vs Club Almagro</t>
+          <t>CA Los Andes vs Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>CA Los Andes</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>Club Almagro</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>0x03ed0858b563c1becf38b195ad94b1a84eb89c3ca8ca10b1a34220bff142f9b2</t>
+          <t>0x653af58a9c77cb072171a76bcd9ca8adee427601f3ecd186c8154c81f8736395</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>L19683499</t>
+          <t>L19659153</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -5496,17 +5536,17 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>1786270828</t>
+          <t>1786288436</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>1786305600</t>
+          <t>1786296600</t>
         </is>
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>308.32</t>
+          <t>48.077153</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
@@ -5523,12 +5563,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0x2121e08c4ea1fe2d49a3bb388fba9e232ef9c06335c04e5eae0bf7766975512a</t>
+          <t>0x680d5db234b802aa2845f16e9d23d635dd89870065c6bfb6f6f1bde25c321bae</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -5538,22 +5578,22 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>30.06</t>
+          <t>24.36</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>1.6262</t>
+          <t>1.475</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Colon de Santa Fe</t>
+          <t>CA Colegiales -0.5</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -5563,27 +5603,27 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Colon de Santa Fe vs San Telmo</t>
+          <t>CA Colegiales vs Patronato</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Colon de Santa Fe</t>
+          <t>CA Colegiales</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>0x1a11ec80edeaae24566c4f4f891cc2afc56b377b24997a6e8ee533eeaaad5c92</t>
+          <t>0x50a3f0e4e982cdda0b9c4b9e2e1c50c67d93fbf7a068b43dbdf733c0b8d09050</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>L19683494</t>
+          <t>L19683449</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -5608,17 +5648,17 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>1786253941</t>
+          <t>1786287181</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>1786300200</t>
+          <t>1786298400</t>
         </is>
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>48.0</t>
+          <t>51.284211</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
@@ -5635,39 +5675,31 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0x4e811c319e5e3a1fc1968ce0f31b4c15eb7222daa616252d99f9abc611408746</t>
+          <t>0x5a5b6f41ac2a593747a9419c020abd417423350c2cf0a14d8cb9ef8a25d04f18</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>0x155C76202e45BE70c50bfeD7eAeA3B98e7716Ff7</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8.81755</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>1.2925</t>
+          <t>1.6325</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr"/>
       <c r="H50" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -5675,27 +5707,27 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Colon de Santa Fe vs San Telmo</t>
+          <t>Quilmes vs Club Almagro</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Colon de Santa Fe</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Club Almagro</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>0x2e49527408facf21253a0a1eafe51280b82e4c31919e91a396332f19ec366401</t>
+          <t>0x86a790846c1cb1bed065ac37c41b727461e30e0a9e0f9e2370ef61f6213ed31f</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>L19683494</t>
+          <t>L19683499</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -5720,17 +5752,17 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>1786243741</t>
+          <t>1786284071</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>1786300200</t>
+          <t>1786305600</t>
         </is>
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>3.418803</t>
+          <t>13.940791</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
@@ -5747,39 +5779,31 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0xb8631aeb398192a03386505542f05fa15e34db501204baa8745a4d4b5c1651b7</t>
+          <t>0x9ae6e679c8fc9ed20977676ba3160d389287dd8808ea2610d0f168f9c3a42c11</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>0x155C76202e45BE70c50bfeD7eAeA3B98e7716Ff7</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr">
         <is>
-          <t>0.99999</t>
+          <t>21.58999</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>1.6538</t>
+          <t>1.6325</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>Deportivo Moron</t>
-        </is>
-      </c>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr"/>
       <c r="H51" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -5787,27 +5811,27 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Deportivo Moron vs Acassuso</t>
+          <t>Quilmes vs Club Almagro</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Deportivo Moron</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Club Almagro</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>0x7514a255ce41be3c5db9f8849ba04e78dab80f02d1fe78c2aae82bbc843a9745</t>
+          <t>0x86a790846c1cb1bed065ac37c41b727461e30e0a9e0f9e2370ef61f6213ed31f</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>L19683452</t>
+          <t>L19683499</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -5832,17 +5856,17 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>1786243225</t>
+          <t>1786284003</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>1786298400</t>
+          <t>1786305600</t>
         </is>
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>1.529621</t>
+          <t>34.134372</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
@@ -5859,28 +5883,28 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0xd3b94d194e43cc84f0a1b82723594ea6689a6aa2a4a7dccbc8a3d19fc321e49b</t>
+          <t>0x6771b333646b031b4dc4cfea8f533b040a6ed0a66012cdc416a7aaa5b89f7988</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>19.2</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>1.5238</t>
+          <t>1.5425</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G52" t="inlineStr"/>
@@ -5891,27 +5915,27 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Deportivo Moron vs Acassuso</t>
+          <t>Colon de Santa Fe vs San Telmo</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Deportivo Moron</t>
+          <t>Colon de Santa Fe</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>0x108eaba0441fb45ec8e0073e945ae0ac1e138c933e4f2839816cd3198d7dd4d2</t>
+          <t>0x4b323aab38dd8f5096dcd1965ce7dc05c69ab73371e55e810b7a5aee356bf244</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>L19683452</t>
+          <t>L19683494</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -5936,17 +5960,17 @@
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>1786225000</t>
+          <t>1786283290</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>1786298400</t>
+          <t>1786300200</t>
         </is>
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>1.909308</t>
+          <t>35.391705</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
@@ -5963,39 +5987,31 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0x86f4b24298f4c19f9f856cb19af2a260f24dc2d391f252248469436057ea1d1a</t>
+          <t>0x8809f3e942a9cc8dca00d48b07cfe53a328d6ba2b60742c63e144e3d8cf2eaa1</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>23.25749</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>1.5263</t>
+          <t>1.4838</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>Deportivo Moron -1</t>
-        </is>
-      </c>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -6003,27 +6019,27 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Deportivo Moron vs Acassuso</t>
+          <t>Colon de Santa Fe vs San Telmo</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Deportivo Moron</t>
+          <t>Colon de Santa Fe</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>0xb61b063252c01d0525ae633a0276dc1830eabd418482fddec925fcbd602a2a75</t>
+          <t>0xc91217dfcd3944893195656945526d39efcd315aa93101aa312de5303c04d446</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>L19683452</t>
+          <t>L19683494</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -6048,17 +6064,17 @@
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>1786220171</t>
+          <t>1786281248</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>1786298400</t>
+          <t>1786300200</t>
         </is>
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>1.900238</t>
+          <t>48.077499</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
@@ -6075,39 +6091,31 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0x0a5de930b5a6b8aca1699b666034af3891a3aa920021791d6d13e0297fb7903f</t>
+          <t>0xe5b95b7ede820952a7e6f5c1b2139a8092b51c4de75567f117f1291461ec6fbe</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>0x4a09916b1325Eed50eE8973B13742a205B0B7c7E</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr">
         <is>
-          <t>49.99999</t>
+          <t>23.55844</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>1.6175</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>Almirante Brown -1</t>
-        </is>
-      </c>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr"/>
       <c r="H54" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -6115,27 +6123,27 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Almirante Brown vs Ciudad Bolivar</t>
+          <t>Colon de Santa Fe vs San Telmo</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Colon de Santa Fe</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>Ciudad Bolivar</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>0xa6a338c64f062bfd589e8d5d9cea45a27c9e64065f71f800e5966f81ce53c556</t>
+          <t>0xc91217dfcd3944893195656945526d39efcd315aa93101aa312de5303c04d446</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>L19683447</t>
+          <t>L19683494</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -6160,17 +6168,17 @@
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>1786218515</t>
+          <t>1786281243</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>1786212000</t>
+          <t>1786300200</t>
         </is>
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>80.971644</t>
+          <t>48.078449</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
@@ -6187,28 +6195,28 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0x17d5a08f8fa305f31f27442393c64f497dd3893417da6e76c321c4c2a187320d</t>
+          <t>0x4d872ac34cfff98634d3d50362fe725a3f4ea55d64ddd9e3d7d811b073f350ab</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr">
         <is>
-          <t>49.18897</t>
+          <t>17.30813</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>1.4737</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Under/Over (1.5)</t>
         </is>
       </c>
       <c r="G55" t="inlineStr"/>
@@ -6219,27 +6227,27 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Almirante Brown vs Ciudad Bolivar</t>
+          <t>Colon de Santa Fe vs San Telmo</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Colon de Santa Fe</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>Ciudad Bolivar</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>0xa6a338c64f062bfd589e8d5d9cea45a27c9e64065f71f800e5966f81ce53c556</t>
+          <t>0xd638a8ee6393f88ca538cc4fe6ac8cdf722bcfe6277a5ebd9387222eade88ba3</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>L19683447</t>
+          <t>L19683494</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -6264,17 +6272,17 @@
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>1786218084</t>
+          <t>1786281243</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>1786212000</t>
+          <t>1786300200</t>
         </is>
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>103.82896</t>
+          <t>48.078139</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
@@ -6291,28 +6299,28 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0x56975f372357be259365cb7d2929c88d4fae157eea7a71d53d57cb234834f2ca</t>
+          <t>0x8f782cb5f7b30f6c129f6031ec6368ed75ea36897066f1761d9054013f56567d</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>1.4812</t>
+          <t>1.4187</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
+          <t>Primera Nacional</t>
         </is>
       </c>
       <c r="G56" t="inlineStr"/>
@@ -6338,7 +6346,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>0xa8ade64a3adb0ea38de67a61105ef31beb490d5a7287715b76ae124536d359cc</t>
+          <t>0x2d371e1a8a9d98624f046ea3d7126e47308ffbc183b66b1e2fba81e5ae69d7dd</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -6368,7 +6376,7 @@
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>1786215674</t>
+          <t>1786280425</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
@@ -6378,7 +6386,7 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>2.077922</t>
+          <t>23.880597</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
@@ -6395,39 +6403,31 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>0xff53df1f3446908699196d44fcdb8b39c1bd15c7ed519f0d730e55a51a6eb38f</t>
+          <t>0xfe8890b155a19f7eb888456b555a7a6d8c293f8ecabeb69d2abd10210f520589</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>1.3713</t>
+          <t>1.4475</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>Almirante Brown</t>
-        </is>
-      </c>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr"/>
       <c r="H57" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -6435,27 +6435,27 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Almirante Brown vs Ciudad Bolivar</t>
+          <t>Colon de Santa Fe vs San Telmo</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Colon de Santa Fe</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>Ciudad Bolivar</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>0x63a8bf73c1084ef223fdd1096dccd16232e7a455fad77f7f0891be1588ebeb88</t>
+          <t>0xc91217dfcd3944893195656945526d39efcd315aa93101aa312de5303c04d446</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>L19683447</t>
+          <t>L19683494</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -6480,17 +6480,17 @@
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>1786215673</t>
+          <t>1786280403</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>1786212000</t>
+          <t>1786300200</t>
         </is>
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>2.693603</t>
+          <t>22.346369</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
@@ -6507,7 +6507,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>0x249d52552e7acb9f472d2a4c48ab754622ba572903281739a3e10b4d509dccb0</t>
+          <t>0x60e023296ac2f9f58237fa345b3aa08fb4f997dd34c5384f371782bf7bbd5a40</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -6522,22 +6522,22 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>26.11999</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>1.2288</t>
+          <t>1.5488</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Under/Over (2)</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Almirante Brown -1</t>
+          <t>Over 2.0</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -6547,27 +6547,27 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Almirante Brown vs Ciudad Bolivar</t>
+          <t>Colon de Santa Fe vs San Telmo</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Colon de Santa Fe</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>Ciudad Bolivar</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>0xa6a338c64f062bfd589e8d5d9cea45a27c9e64065f71f800e5966f81ce53c556</t>
+          <t>0xc91217dfcd3944893195656945526d39efcd315aa93101aa312de5303c04d446</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>L19683447</t>
+          <t>L19683494</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -6592,17 +6592,17 @@
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>1786214209</t>
+          <t>1786280403</t>
         </is>
       </c>
       <c r="S58" t="inlineStr">
         <is>
-          <t>1786212000</t>
+          <t>1786300200</t>
         </is>
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>6.295082</t>
+          <t>47.599071</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
@@ -6619,39 +6619,31 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>0xf65c55196eeb0d21e7e3866ad26f8c3f2fee2aef273ddde5423e31fb40a51469</t>
+          <t>0x2d118800c100a2a41a19c2053cbf355561a08867f99163fb40955a4ab012ce39</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr">
         <is>
-          <t>121.81</t>
+          <t>20.07999</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>1.4363</t>
+          <t>1.7363</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>Almirante Brown</t>
-        </is>
-      </c>
+          <t>Asian Handicap (-1.5)</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr"/>
       <c r="H59" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -6659,27 +6651,27 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Almirante Brown vs Ciudad Bolivar</t>
+          <t>Godoy Cruz vs Chaco For Ever</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>Ciudad Bolivar</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>0x63a8bf73c1084ef223fdd1096dccd16232e7a455fad77f7f0891be1588ebeb88</t>
+          <t>0x60e111ebf03c4965ff049e67cf10f93f5cca143023c6104aab59162863b5b8a8</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>L19683447</t>
+          <t>L19683484</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -6704,17 +6696,17 @@
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>1786213844</t>
+          <t>1786279900</t>
         </is>
       </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t>1786212000</t>
+          <t>1786303800</t>
         </is>
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>279.22063</t>
+          <t>27.273331</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
@@ -6731,12 +6723,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>0x1bb20a2bf22e4fe06b44c06b9c2caa21f3f2a7c9d0cce1a2346f79e76022cd1f</t>
+          <t>0x904e2e53a604aa6663de774d4bd9ddf8af7459ef1c4fa1bb14486300917ac211</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -6746,22 +6738,22 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>21.05</t>
+          <t>3.96</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>1.4363</t>
+          <t>1.2837</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Almirante Brown -0.5</t>
+          <t>Tie</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -6771,27 +6763,27 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Almirante Brown vs Ciudad Bolivar</t>
+          <t>Godoy Cruz vs Chaco For Ever</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>Ciudad Bolivar</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>0xfa00d2f0c7b5053ee336b303a0e7ad9cec0b8d539367773b7efee5c86cb2b59d</t>
+          <t>0x08dce15d4ca4845359c2f121bce305fd3a0fe7422d497000c713e29463c6be79</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>L19683447</t>
+          <t>L19683484</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
@@ -6816,17 +6808,17 @@
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>1786213843</t>
+          <t>1786279851</t>
         </is>
       </c>
       <c r="S60" t="inlineStr">
         <is>
-          <t>1786212000</t>
+          <t>1786303800</t>
         </is>
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>48.252149</t>
+          <t>13.955947</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
@@ -6843,28 +6835,28 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>0xc51052f8e449b4d56cc87b697bfc8eb0d3a88ae218dee1da3d725fa94163bc75</t>
+          <t>0x19a6c0536a5dea88055519ff16050cdde80d42121bb75c5045e3b562a7c1d4bb</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C61" t="inlineStr"/>
       <c r="D61" t="inlineStr">
         <is>
-          <t>77.29513</t>
+          <t>7.50547</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>1.2588</t>
+          <t>1.4287</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Primera Nacional</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G61" t="inlineStr"/>
@@ -6875,27 +6867,27 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Almirante Brown vs Ciudad Bolivar</t>
+          <t>Godoy Cruz vs Chaco For Ever</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>Ciudad Bolivar</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>0xaa5316c6f6544d74142ad6db34a3745918f237ffb1a657e000693947e81b65d6</t>
+          <t>0xa5f02d0d08d0dcc4818948397f0f26c77f90b87182cec4d62ab01f77352671a1</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>L19683447</t>
+          <t>L19683484</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
@@ -6920,17 +6912,17 @@
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>1786212849</t>
+          <t>1786279821</t>
         </is>
       </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t>1786212000</t>
+          <t>1786303800</t>
         </is>
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>298.72514</t>
+          <t>17.505469</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
@@ -6947,28 +6939,28 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>0x0aeb4fe40f7d734cf244c144e6c064568b40b222193c9f93c641d1b31af3752e</t>
+          <t>0x4c44e2c0c492a5115b342a42a552a040cb800bd582b07c12f1ea9161b861b487</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C62" t="inlineStr"/>
       <c r="D62" t="inlineStr">
         <is>
-          <t>16.89162</t>
+          <t>11.30844</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>1.2588</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Primera Nacional</t>
+          <t>Under/Over (2)</t>
         </is>
       </c>
       <c r="G62" t="inlineStr"/>
@@ -6979,27 +6971,27 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Almirante Brown vs Ciudad Bolivar</t>
+          <t>Deportivo Moron vs Acassuso</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Deportivo Moron</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>Ciudad Bolivar</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>0xaa5316c6f6544d74142ad6db34a3745918f237ffb1a657e000693947e81b65d6</t>
+          <t>0x108eaba0441fb45ec8e0073e945ae0ac1e138c933e4f2839816cd3198d7dd4d2</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>L19683447</t>
+          <t>L19683452</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
@@ -7024,17 +7016,17 @@
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>1786212805</t>
+          <t>1786278950</t>
         </is>
       </c>
       <c r="S62" t="inlineStr">
         <is>
-          <t>1786212000</t>
+          <t>1786298400</t>
         </is>
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>65.281623</t>
+          <t>23.078449</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
@@ -7051,39 +7043,31 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>0x383b895a5fe529a887369a0f113c516fdc7f6125d54381acf9695997ef22d039</t>
+          <t>0x5a5ccf0d5f6cbac6813d25e4e1e96b25b5c5a4ff8f6378d7e69d6bd3c29295ae</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr"/>
       <c r="D63" t="inlineStr">
         <is>
-          <t>11.26905</t>
+          <t>12.25</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>1.745</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Primera Nacional</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>Almirante Brown</t>
-        </is>
-      </c>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr"/>
       <c r="H63" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -7091,27 +7075,27 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Almirante Brown vs Ciudad Bolivar</t>
+          <t>Deportivo Moron vs Acassuso</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Deportivo Moron</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>Ciudad Bolivar</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>0xaa5316c6f6544d74142ad6db34a3745918f237ffb1a657e000693947e81b65d6</t>
+          <t>0x108eaba0441fb45ec8e0073e945ae0ac1e138c933e4f2839816cd3198d7dd4d2</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>L19683447</t>
+          <t>L19683452</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
@@ -7136,17 +7120,17 @@
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>1786211779</t>
+          <t>1786278094</t>
         </is>
       </c>
       <c r="S63" t="inlineStr">
         <is>
-          <t>1786212000</t>
+          <t>1786298400</t>
         </is>
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>15.126242</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
@@ -7163,7 +7147,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>0xcfb6add6f8610a64ffc187beb9e16bf2bacb27b54a0f0aaefa6bfb437239b893</t>
+          <t>0x5f3419242a87ff17c0cb508ade95d27a54429124d36280a1dff2efa2fa0b3510</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -7171,31 +7155,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C64" t="inlineStr"/>
       <c r="D64" t="inlineStr">
         <is>
-          <t>24.89998</t>
+          <t>20.41999</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>1.745</t>
+          <t>1.7087</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Primera Nacional</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>Almirante Brown</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr"/>
       <c r="H64" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -7203,27 +7179,27 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Almirante Brown vs Ciudad Bolivar</t>
+          <t>CA Los Andes vs Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>CA Los Andes</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>Ciudad Bolivar</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>0xaa5316c6f6544d74142ad6db34a3745918f237ffb1a657e000693947e81b65d6</t>
+          <t>0x31115553050eabb8d3f6a72cf2865c16175783383dcfc674615e74ed88cabaee</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>L19683447</t>
+          <t>L19659153</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
@@ -7248,17 +7224,17 @@
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>1786211777</t>
+          <t>1786277884</t>
         </is>
       </c>
       <c r="S64" t="inlineStr">
         <is>
-          <t>1786212000</t>
+          <t>1786296600</t>
         </is>
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>33.422792</t>
+          <t>28.811273</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
@@ -7275,39 +7251,31 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>0xd41652604437a4e92e0d78b653d4d49d8dedd2e153d1340dad89b9b93e182a48</t>
+          <t>0xe6b14424302d9ef7ea2000cef83e38549f6a38c12d57faa6dd76dd84e631a5ca</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>0xf4a8B27C9a13e298D65b5Cc072d252816B799C81</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr"/>
       <c r="D65" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>12.13</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>1.4163</t>
+          <t>1.3613</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>Atl. Rafaela</t>
-        </is>
-      </c>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr"/>
       <c r="H65" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -7315,27 +7283,27 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Atl. Rafaela vs Chacarita Juniors</t>
+          <t>Deportivo Moron vs Acassuso</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>Atl. Rafaela</t>
+          <t>Deportivo Moron</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>0xe738e9ba05492fab73eaaf6da211b84caadc72b08b26f1cd30fa8737e283bb44</t>
+          <t>0x3f34d112cfb9f093c57a3e094be078f9eea2715f97797e20d86942d58f5cc8d6</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>L19683450</t>
+          <t>L19683452</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
@@ -7360,17 +7328,17 @@
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>1786211028</t>
+          <t>1786277708</t>
         </is>
       </c>
       <c r="S65" t="inlineStr">
         <is>
-          <t>1786215600</t>
+          <t>1786298400</t>
         </is>
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>2.402402</t>
+          <t>33.577855</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
@@ -7387,7 +7355,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>0x562fd7c6419c807ed04d3cacac95f861805f96704bd535e265399fb9d2c2b609</t>
+          <t>0xd7a2e43ba1564f619200938b384123dd68adb783742fc7b32ee335ee489d1302</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -7398,17 +7366,17 @@
       <c r="C66" t="inlineStr"/>
       <c r="D66" t="inlineStr">
         <is>
-          <t>5.32</t>
+          <t>10.58</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>1.405</t>
+          <t>1.485</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
+          <t>Under/Over (2)</t>
         </is>
       </c>
       <c r="G66" t="inlineStr"/>
@@ -7419,27 +7387,27 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Estudiantes de Caseros vs Deportivo Madryn</t>
+          <t>Deportivo Moron vs Acassuso</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Estudiantes de Caseros</t>
+          <t>Deportivo Moron</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>0xd61509e26f8645bb9780672f942c72c4b7dab577c2a01f04e1e09bce9b828765</t>
+          <t>0x108eaba0441fb45ec8e0073e945ae0ac1e138c933e4f2839816cd3198d7dd4d2</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>L19683453</t>
+          <t>L19683452</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
@@ -7464,17 +7432,17 @@
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>1786210845</t>
+          <t>1786277679</t>
         </is>
       </c>
       <c r="S66" t="inlineStr">
         <is>
-          <t>1786212000</t>
+          <t>1786298400</t>
         </is>
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>13.135802</t>
+          <t>21.814433</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
@@ -7491,39 +7459,31 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>0x0bb7a6822220bf40d7b279f99a54f46025f393ba95bb38b6d6dc98192886b3ed</t>
+          <t>0xb25fa423ffb1a1464f100f2a2e9a1beac36661b9e37c8b09ecc7d3fd5a80312f</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>0xf4a8B27C9a13e298D65b5Cc072d252816B799C81</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr"/>
       <c r="D67" t="inlineStr">
         <is>
-          <t>0.99999</t>
+          <t>25.88</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>1.5513</t>
+          <t>1.6038</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>Agropecuario</t>
-        </is>
-      </c>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr"/>
       <c r="H67" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -7531,27 +7491,27 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Agropecuario vs Atletico Guemes</t>
+          <t>CA Colegiales vs Patronato</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>CA Colegiales</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>Atletico Guemes</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>0xae66c7fab3c9c76fbc29d9e9778ef4845d8a6b8d092cff34320f100020113c49</t>
+          <t>0x18dd2fdd93f5029a20e6a76c47c4f0e5c3c25768ad7f1b46a833287f8b7fcc13</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>L19683451</t>
+          <t>L19683449</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
@@ -7576,17 +7536,17 @@
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>1786205982</t>
+          <t>1786277040</t>
         </is>
       </c>
       <c r="S67" t="inlineStr">
         <is>
-          <t>1786212000</t>
+          <t>1786298400</t>
         </is>
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>1.814041</t>
+          <t>42.865424</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
@@ -7603,39 +7563,31 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>0xe17b2546f4b90c8647ba975c279e39dec1fda5a003adfb8a2b39bb12a3519b10</t>
+          <t>0xfe815be8a10a6ad2cda012e463a244232a6f6c80544018f6dda52d723946b659</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>0xf4a8B27C9a13e298D65b5Cc072d252816B799C81</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr"/>
       <c r="D68" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>29.02571</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>1.3613</t>
+          <t>1.6038</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr"/>
       <c r="H68" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -7643,27 +7595,27 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Almirante Brown vs Ciudad Bolivar</t>
+          <t>CA Colegiales vs Patronato</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>CA Colegiales</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>Ciudad Bolivar</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>0xd5906ce08d61f7c5ee45fcebd2c8baeed5558387398ea332817a4b632f439b6d</t>
+          <t>0x18dd2fdd93f5029a20e6a76c47c4f0e5c3c25768ad7f1b46a833287f8b7fcc13</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>L19683447</t>
+          <t>L19683449</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
@@ -7688,17 +7640,17 @@
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>1786205963</t>
+          <t>1786276809</t>
         </is>
       </c>
       <c r="S68" t="inlineStr">
         <is>
-          <t>1786212000</t>
+          <t>1786298400</t>
         </is>
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>2.768166</t>
+          <t>48.07571</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
@@ -7715,39 +7667,31 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>0xcfe218822e89cbef5841f3045f551cc65acf353d8e240f943e2b61c54ea79a68</t>
+          <t>0xdb83c52876b68624e093c25e35d11910f4fbef2394ff947b658f8ea5cdb3fa88</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>0xf4a8B27C9a13e298D65b5Cc072d252816B799C81</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr"/>
       <c r="D69" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>16.96</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>1.3337</t>
+          <t>1.4463</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr"/>
       <c r="H69" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -7755,27 +7699,27 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Estudiantes de Caseros vs Deportivo Madryn</t>
+          <t>CA Colegiales vs Patronato</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>Estudiantes de Caseros</t>
+          <t>CA Colegiales</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>0xf238b96ec9e2421db79973de945f1fc0c3f8bb99c31cda32d011ebaabfd2db86</t>
+          <t>0x30a6561de28b35c5bb0557dcbfc7b23e7a62558d3b0f5cfcafb67d7a07e0dd21</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>L19683453</t>
+          <t>L19683449</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
@@ -7800,17 +7744,17 @@
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>1786205938</t>
+          <t>1786276809</t>
         </is>
       </c>
       <c r="S69" t="inlineStr">
         <is>
-          <t>1786212000</t>
+          <t>1786298400</t>
         </is>
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>2.996255</t>
+          <t>38.005602</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
@@ -7827,31 +7771,39 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>0x1b9fcb29010a212f74af57040114154e78748f06a4d826be4397ddadb45ac31b</t>
+          <t>0x0847a2541998eecfe02d138796b14ef3d6719061787498f4888f6e14c0d196ff</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr"/>
+          <t>0xf068eF8DF8f47185D02d59Bb33d9eC7A057a571E</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>21.69</t>
+          <t>38.54</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>1.4512</t>
+          <t>1.125</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Club Almagro</t>
+        </is>
+      </c>
       <c r="H70" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -7859,27 +7811,27 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Almirante Brown vs Ciudad Bolivar</t>
+          <t>Quilmes vs Club Almagro</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>Ciudad Bolivar</t>
+          <t>Club Almagro</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>0xbbcaa253cd967fbf933ff0d87a6f9744cafec0ed59dad5f1f76332aab01a3fa5</t>
+          <t>0x03ed0858b563c1becf38b195ad94b1a84eb89c3ca8ca10b1a34220bff142f9b2</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>L19683447</t>
+          <t>L19683499</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
@@ -7904,17 +7856,17 @@
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>1786190525</t>
+          <t>1786270828</t>
         </is>
       </c>
       <c r="S70" t="inlineStr">
         <is>
-          <t>1786212000</t>
+          <t>1786305600</t>
         </is>
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>48.066482</t>
+          <t>308.32</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
@@ -7931,31 +7883,39 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>0x3177792dd6a7185e37ae06612104cf5a35d137d7f535a889a83a7e9b7c174506</t>
+          <t>0x2121e08c4ea1fe2d49a3bb388fba9e232ef9c06335c04e5eae0bf7766975512a</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>18.35495</t>
+          <t>30.06</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>1.4963</t>
+          <t>1.6262</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Colon de Santa Fe</t>
+        </is>
+      </c>
       <c r="H71" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -7963,27 +7923,27 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>Almirante Brown vs Ciudad Bolivar</t>
+          <t>Colon de Santa Fe vs San Telmo</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Colon de Santa Fe</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>Ciudad Bolivar</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>0xbbcaa253cd967fbf933ff0d87a6f9744cafec0ed59dad5f1f76332aab01a3fa5</t>
+          <t>0x1a11ec80edeaae24566c4f4f891cc2afc56b377b24997a6e8ee533eeaaad5c92</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>L19683447</t>
+          <t>L19683494</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
@@ -8008,17 +7968,17 @@
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>1786190491</t>
+          <t>1786253941</t>
         </is>
       </c>
       <c r="S71" t="inlineStr">
         <is>
-          <t>1786212000</t>
+          <t>1786300200</t>
         </is>
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>36.987305</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
@@ -8035,12 +7995,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>0x54ed4ee2a6ebdab49498137f1accea542ead806f21430a0a771cc4872a044e43</t>
+          <t>0x4e811c319e5e3a1fc1968ce0f31b4c15eb7222daa616252d99f9abc611408746</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
+          <t>0x155C76202e45BE70c50bfeD7eAeA3B98e7716Ff7</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -8050,22 +8010,22 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>20.10741</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>1.5437</t>
+          <t>1.2925</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Over 1.5</t>
+          <t>Tie</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -8075,27 +8035,27 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>Almirante Brown vs Ciudad Bolivar</t>
+          <t>Colon de Santa Fe vs San Telmo</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Colon de Santa Fe</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>Ciudad Bolivar</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>0xbbcaa253cd967fbf933ff0d87a6f9744cafec0ed59dad5f1f76332aab01a3fa5</t>
+          <t>0x2e49527408facf21253a0a1eafe51280b82e4c31919e91a396332f19ec366401</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>L19683447</t>
+          <t>L19683494</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
@@ -8120,17 +8080,17 @@
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>1786190485</t>
+          <t>1786243741</t>
         </is>
       </c>
       <c r="S72" t="inlineStr">
         <is>
-          <t>1786212000</t>
+          <t>1786300200</t>
         </is>
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>36.979145</t>
+          <t>3.418803</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
@@ -8147,31 +8107,39 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>0x544fe5c906328d009917b591611ff3438cef85f8b42d9f67732cbbd5eabbb8dd</t>
+          <t>0xb8631aeb398192a03386505542f05fa15e34db501204baa8745a4d4b5c1651b7</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr"/>
+          <t>0x155C76202e45BE70c50bfeD7eAeA3B98e7716Ff7</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>21.69</t>
+          <t>0.99999</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>1.4512</t>
+          <t>1.6538</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Deportivo Moron</t>
+        </is>
+      </c>
       <c r="H73" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -8179,27 +8147,27 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Almirante Brown vs Ciudad Bolivar</t>
+          <t>Deportivo Moron vs Acassuso</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Deportivo Moron</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>Ciudad Bolivar</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>0xbbcaa253cd967fbf933ff0d87a6f9744cafec0ed59dad5f1f76332aab01a3fa5</t>
+          <t>0x7514a255ce41be3c5db9f8849ba04e78dab80f02d1fe78c2aae82bbc843a9745</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>L19683447</t>
+          <t>L19683452</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
@@ -8224,17 +8192,17 @@
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>1786190485</t>
+          <t>1786243225</t>
         </is>
       </c>
       <c r="S73" t="inlineStr">
         <is>
-          <t>1786212000</t>
+          <t>1786298400</t>
         </is>
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>48.066482</t>
+          <t>1.529621</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
@@ -8251,28 +8219,28 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>0xb2f3ea804e1760a01d3a93678f0e2119f1ea2a9db0dc4711a06cc7bcba42b0c2</t>
+          <t>0xd3b94d194e43cc84f0a1b82723594ea6689a6aa2a4a7dccbc8a3d19fc321e49b</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
         </is>
       </c>
       <c r="C74" t="inlineStr"/>
       <c r="D74" t="inlineStr">
         <is>
-          <t>17.47</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>1.405</t>
+          <t>1.5238</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
+          <t>Under/Over (2)</t>
         </is>
       </c>
       <c r="G74" t="inlineStr"/>
@@ -8283,27 +8251,27 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>Estudiantes de Caseros vs Deportivo Madryn</t>
+          <t>Deportivo Moron vs Acassuso</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>Estudiantes de Caseros</t>
+          <t>Deportivo Moron</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>0xd61509e26f8645bb9780672f942c72c4b7dab577c2a01f04e1e09bce9b828765</t>
+          <t>0x108eaba0441fb45ec8e0073e945ae0ac1e138c933e4f2839816cd3198d7dd4d2</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>L19683453</t>
+          <t>L19683452</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
@@ -8328,17 +8296,17 @@
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>1786190461</t>
+          <t>1786225000</t>
         </is>
       </c>
       <c r="S74" t="inlineStr">
         <is>
-          <t>1786212000</t>
+          <t>1786298400</t>
         </is>
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>43.135802</t>
+          <t>1.909308</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
@@ -8355,31 +8323,39 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>0xa7eafbb77d425fc2347b4ee3e4f4e1b85f6d0f81420605db76ebfeeaa793a428</t>
+          <t>0x86f4b24298f4c19f9f856cb19af2a260f24dc2d391f252248469436057ea1d1a</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr"/>
+          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>21.69</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>1.4512</t>
+          <t>1.5263</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr"/>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Deportivo Moron -1</t>
+        </is>
+      </c>
       <c r="H75" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -8387,27 +8363,27 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>Almirante Brown vs Ciudad Bolivar</t>
+          <t>Deportivo Moron vs Acassuso</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Deportivo Moron</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>Ciudad Bolivar</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>0xbbcaa253cd967fbf933ff0d87a6f9744cafec0ed59dad5f1f76332aab01a3fa5</t>
+          <t>0xb61b063252c01d0525ae633a0276dc1830eabd418482fddec925fcbd602a2a75</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>L19683447</t>
+          <t>L19683452</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
@@ -8432,17 +8408,17 @@
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>1786190458</t>
+          <t>1786220171</t>
         </is>
       </c>
       <c r="S75" t="inlineStr">
         <is>
-          <t>1786212000</t>
+          <t>1786298400</t>
         </is>
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>48.066482</t>
+          <t>1.900238</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
@@ -8459,110 +8435,2494 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
+          <t>0x0a5de930b5a6b8aca1699b666034af3891a3aa920021791d6d13e0297fb7903f</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>0x4a09916b1325Eed50eE8973B13742a205B0B7c7E</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>49.99999</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>1.6175</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Almirante Brown -1</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Primera Nacional</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>Almirante Brown vs Ciudad Bolivar</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>Almirante Brown</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Ciudad Bolivar</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>0xa6a338c64f062bfd589e8d5d9cea45a27c9e64065f71f800e5966f81ce53c556</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>L19683447</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q76" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R76" t="inlineStr">
+        <is>
+          <t>1786218515</t>
+        </is>
+      </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>1786212000</t>
+        </is>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>80.971644</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>0x17d5a08f8fa305f31f27442393c64f497dd3893417da6e76c321c4c2a187320d</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr"/>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>49.18897</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>1.4737</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr"/>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Primera Nacional</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>Almirante Brown vs Ciudad Bolivar</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>Almirante Brown</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Ciudad Bolivar</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>0xa6a338c64f062bfd589e8d5d9cea45a27c9e64065f71f800e5966f81ce53c556</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>L19683447</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q77" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R77" t="inlineStr">
+        <is>
+          <t>1786218084</t>
+        </is>
+      </c>
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>1786212000</t>
+        </is>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>103.82896</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>0x56975f372357be259365cb7d2929c88d4fae157eea7a71d53d57cb234834f2ca</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr"/>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>1.4812</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr"/>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Primera Nacional</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>Club Atletico Mitre de Santiago del Estero vs Defensores de Belgrano Buenos Aires</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>Club Atletico Mitre de Santiago del Estero</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Defensores de Belgrano Buenos Aires</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>0xa8ade64a3adb0ea38de67a61105ef31beb490d5a7287715b76ae124536d359cc</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>L19683493</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q78" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R78" t="inlineStr">
+        <is>
+          <t>1786215674</t>
+        </is>
+      </c>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>1786302000</t>
+        </is>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>2.077922</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>0xff53df1f3446908699196d44fcdb8b39c1bd15c7ed519f0d730e55a51a6eb38f</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>1.3713</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Almirante Brown</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Primera Nacional</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>Almirante Brown vs Ciudad Bolivar</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>Almirante Brown</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Ciudad Bolivar</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>0x63a8bf73c1084ef223fdd1096dccd16232e7a455fad77f7f0891be1588ebeb88</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>L19683447</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q79" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R79" t="inlineStr">
+        <is>
+          <t>1786215673</t>
+        </is>
+      </c>
+      <c r="S79" t="inlineStr">
+        <is>
+          <t>1786212000</t>
+        </is>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>2.693603</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>0x249d52552e7acb9f472d2a4c48ab754622ba572903281739a3e10b4d509dccb0</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>1.44</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>1.2288</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Almirante Brown -1</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Primera Nacional</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>Almirante Brown vs Ciudad Bolivar</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>Almirante Brown</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Ciudad Bolivar</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>0xa6a338c64f062bfd589e8d5d9cea45a27c9e64065f71f800e5966f81ce53c556</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>L19683447</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q80" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R80" t="inlineStr">
+        <is>
+          <t>1786214209</t>
+        </is>
+      </c>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>1786212000</t>
+        </is>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>6.295082</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>0xf65c55196eeb0d21e7e3866ad26f8c3f2fee2aef273ddde5423e31fb40a51469</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>121.81</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>1.4363</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Almirante Brown</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Primera Nacional</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>Almirante Brown vs Ciudad Bolivar</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>Almirante Brown</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Ciudad Bolivar</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>0x63a8bf73c1084ef223fdd1096dccd16232e7a455fad77f7f0891be1588ebeb88</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>L19683447</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q81" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R81" t="inlineStr">
+        <is>
+          <t>1786213844</t>
+        </is>
+      </c>
+      <c r="S81" t="inlineStr">
+        <is>
+          <t>1786212000</t>
+        </is>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>279.22063</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>0x1bb20a2bf22e4fe06b44c06b9c2caa21f3f2a7c9d0cce1a2346f79e76022cd1f</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>21.05</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>1.4363</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-0.5)</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Almirante Brown -0.5</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Primera Nacional</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>Almirante Brown vs Ciudad Bolivar</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>Almirante Brown</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Ciudad Bolivar</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>0xfa00d2f0c7b5053ee336b303a0e7ad9cec0b8d539367773b7efee5c86cb2b59d</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>L19683447</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q82" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R82" t="inlineStr">
+        <is>
+          <t>1786213843</t>
+        </is>
+      </c>
+      <c r="S82" t="inlineStr">
+        <is>
+          <t>1786212000</t>
+        </is>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>48.252149</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>0xc51052f8e449b4d56cc87b697bfc8eb0d3a88ae218dee1da3d725fa94163bc75</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr"/>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>77.29513</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>1.2588</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Primera Nacional</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr"/>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Primera Nacional</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>Almirante Brown vs Ciudad Bolivar</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>Almirante Brown</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Ciudad Bolivar</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>0xaa5316c6f6544d74142ad6db34a3745918f237ffb1a657e000693947e81b65d6</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>L19683447</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q83" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R83" t="inlineStr">
+        <is>
+          <t>1786212849</t>
+        </is>
+      </c>
+      <c r="S83" t="inlineStr">
+        <is>
+          <t>1786212000</t>
+        </is>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>298.72514</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>0x0aeb4fe40f7d734cf244c144e6c064568b40b222193c9f93c641d1b31af3752e</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr"/>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>16.89162</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>1.2588</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Primera Nacional</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr"/>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Primera Nacional</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>Almirante Brown vs Ciudad Bolivar</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>Almirante Brown</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Ciudad Bolivar</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>0xaa5316c6f6544d74142ad6db34a3745918f237ffb1a657e000693947e81b65d6</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>L19683447</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q84" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R84" t="inlineStr">
+        <is>
+          <t>1786212805</t>
+        </is>
+      </c>
+      <c r="S84" t="inlineStr">
+        <is>
+          <t>1786212000</t>
+        </is>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>65.281623</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>0x383b895a5fe529a887369a0f113c516fdc7f6125d54381acf9695997ef22d039</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>11.26905</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>1.745</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Primera Nacional</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Almirante Brown</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Primera Nacional</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>Almirante Brown vs Ciudad Bolivar</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>Almirante Brown</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>Ciudad Bolivar</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>0xaa5316c6f6544d74142ad6db34a3745918f237ffb1a657e000693947e81b65d6</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>L19683447</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q85" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R85" t="inlineStr">
+        <is>
+          <t>1786211779</t>
+        </is>
+      </c>
+      <c r="S85" t="inlineStr">
+        <is>
+          <t>1786212000</t>
+        </is>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>15.126242</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>0xcfb6add6f8610a64ffc187beb9e16bf2bacb27b54a0f0aaefa6bfb437239b893</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>24.89998</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>1.745</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Primera Nacional</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Almirante Brown</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Primera Nacional</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>Almirante Brown vs Ciudad Bolivar</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>Almirante Brown</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Ciudad Bolivar</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>0xaa5316c6f6544d74142ad6db34a3745918f237ffb1a657e000693947e81b65d6</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>L19683447</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q86" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R86" t="inlineStr">
+        <is>
+          <t>1786211777</t>
+        </is>
+      </c>
+      <c r="S86" t="inlineStr">
+        <is>
+          <t>1786212000</t>
+        </is>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>33.422792</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>0xd41652604437a4e92e0d78b653d4d49d8dedd2e153d1340dad89b9b93e182a48</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>0xf4a8B27C9a13e298D65b5Cc072d252816B799C81</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>1.4163</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Atl. Rafaela</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Primera Nacional</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>Atl. Rafaela vs Chacarita Juniors</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>Atl. Rafaela</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>Chacarita Juniors</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>0xe738e9ba05492fab73eaaf6da211b84caadc72b08b26f1cd30fa8737e283bb44</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>L19683450</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q87" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R87" t="inlineStr">
+        <is>
+          <t>1786211028</t>
+        </is>
+      </c>
+      <c r="S87" t="inlineStr">
+        <is>
+          <t>1786215600</t>
+        </is>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>2.402402</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>0x562fd7c6419c807ed04d3cacac95f861805f96704bd535e265399fb9d2c2b609</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr"/>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>5.32</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>1.405</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr"/>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Primera Nacional</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>Estudiantes de Caseros vs Deportivo Madryn</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>Estudiantes de Caseros</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Deportivo Madryn</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>0xd61509e26f8645bb9780672f942c72c4b7dab577c2a01f04e1e09bce9b828765</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>L19683453</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q88" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R88" t="inlineStr">
+        <is>
+          <t>1786210845</t>
+        </is>
+      </c>
+      <c r="S88" t="inlineStr">
+        <is>
+          <t>1786212000</t>
+        </is>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>13.135802</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>0x0bb7a6822220bf40d7b279f99a54f46025f393ba95bb38b6d6dc98192886b3ed</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>0xf4a8B27C9a13e298D65b5Cc072d252816B799C81</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>0.99999</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>1.5513</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Agropecuario</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Primera Nacional</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>Agropecuario vs Atletico Guemes</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>Agropecuario</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Atletico Guemes</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>0xae66c7fab3c9c76fbc29d9e9778ef4845d8a6b8d092cff34320f100020113c49</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>L19683451</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q89" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R89" t="inlineStr">
+        <is>
+          <t>1786205982</t>
+        </is>
+      </c>
+      <c r="S89" t="inlineStr">
+        <is>
+          <t>1786212000</t>
+        </is>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>1.814041</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>0xe17b2546f4b90c8647ba975c279e39dec1fda5a003adfb8a2b39bb12a3519b10</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>0xf4a8B27C9a13e298D65b5Cc072d252816B799C81</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>1.3613</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Primera Nacional</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>Almirante Brown vs Ciudad Bolivar</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>Almirante Brown</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>Ciudad Bolivar</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>0xd5906ce08d61f7c5ee45fcebd2c8baeed5558387398ea332817a4b632f439b6d</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>L19683447</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q90" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R90" t="inlineStr">
+        <is>
+          <t>1786205963</t>
+        </is>
+      </c>
+      <c r="S90" t="inlineStr">
+        <is>
+          <t>1786212000</t>
+        </is>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>2.768166</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>0xcfe218822e89cbef5841f3045f551cc65acf353d8e240f943e2b61c54ea79a68</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>0xf4a8B27C9a13e298D65b5Cc072d252816B799C81</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>1.3337</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Primera Nacional</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>Estudiantes de Caseros vs Deportivo Madryn</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>Estudiantes de Caseros</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Deportivo Madryn</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>0xf238b96ec9e2421db79973de945f1fc0c3f8bb99c31cda32d011ebaabfd2db86</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>L19683453</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q91" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R91" t="inlineStr">
+        <is>
+          <t>1786205938</t>
+        </is>
+      </c>
+      <c r="S91" t="inlineStr">
+        <is>
+          <t>1786212000</t>
+        </is>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>2.996255</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>0x1b9fcb29010a212f74af57040114154e78748f06a4d826be4397ddadb45ac31b</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr"/>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>21.69</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>1.4512</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr"/>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Primera Nacional</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>Almirante Brown vs Ciudad Bolivar</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>Almirante Brown</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Ciudad Bolivar</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>0xbbcaa253cd967fbf933ff0d87a6f9744cafec0ed59dad5f1f76332aab01a3fa5</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>L19683447</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q92" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R92" t="inlineStr">
+        <is>
+          <t>1786190525</t>
+        </is>
+      </c>
+      <c r="S92" t="inlineStr">
+        <is>
+          <t>1786212000</t>
+        </is>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>48.066482</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>0x3177792dd6a7185e37ae06612104cf5a35d137d7f535a889a83a7e9b7c174506</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr"/>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>18.35495</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>1.4963</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr"/>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Primera Nacional</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>Almirante Brown vs Ciudad Bolivar</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>Almirante Brown</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>Ciudad Bolivar</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>0xbbcaa253cd967fbf933ff0d87a6f9744cafec0ed59dad5f1f76332aab01a3fa5</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>L19683447</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q93" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R93" t="inlineStr">
+        <is>
+          <t>1786190491</t>
+        </is>
+      </c>
+      <c r="S93" t="inlineStr">
+        <is>
+          <t>1786212000</t>
+        </is>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>36.987305</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>0x54ed4ee2a6ebdab49498137f1accea542ead806f21430a0a771cc4872a044e43</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>20.10741</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>1.5437</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Over 1.5</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Primera Nacional</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>Almirante Brown vs Ciudad Bolivar</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>Almirante Brown</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Ciudad Bolivar</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>0xbbcaa253cd967fbf933ff0d87a6f9744cafec0ed59dad5f1f76332aab01a3fa5</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>L19683447</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O94" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q94" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R94" t="inlineStr">
+        <is>
+          <t>1786190485</t>
+        </is>
+      </c>
+      <c r="S94" t="inlineStr">
+        <is>
+          <t>1786212000</t>
+        </is>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>36.979145</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>0x544fe5c906328d009917b591611ff3438cef85f8b42d9f67732cbbd5eabbb8dd</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr"/>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>21.69</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>1.4512</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr"/>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Primera Nacional</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>Almirante Brown vs Ciudad Bolivar</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>Almirante Brown</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Ciudad Bolivar</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>0xbbcaa253cd967fbf933ff0d87a6f9744cafec0ed59dad5f1f76332aab01a3fa5</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>L19683447</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O95" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q95" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R95" t="inlineStr">
+        <is>
+          <t>1786190485</t>
+        </is>
+      </c>
+      <c r="S95" t="inlineStr">
+        <is>
+          <t>1786212000</t>
+        </is>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>48.066482</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>0xb2f3ea804e1760a01d3a93678f0e2119f1ea2a9db0dc4711a06cc7bcba42b0c2</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr"/>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>17.47</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>1.405</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr"/>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Primera Nacional</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>Estudiantes de Caseros vs Deportivo Madryn</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>Estudiantes de Caseros</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>Deportivo Madryn</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>0xd61509e26f8645bb9780672f942c72c4b7dab577c2a01f04e1e09bce9b828765</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>L19683453</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O96" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q96" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R96" t="inlineStr">
+        <is>
+          <t>1786190461</t>
+        </is>
+      </c>
+      <c r="S96" t="inlineStr">
+        <is>
+          <t>1786212000</t>
+        </is>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>43.135802</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>0xa7eafbb77d425fc2347b4ee3e4f4e1b85f6d0f81420605db76ebfeeaa793a428</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr"/>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>21.69</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>1.4512</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr"/>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Primera Nacional</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>Almirante Brown vs Ciudad Bolivar</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>Almirante Brown</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>Ciudad Bolivar</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>0xbbcaa253cd967fbf933ff0d87a6f9744cafec0ed59dad5f1f76332aab01a3fa5</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>L19683447</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O97" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q97" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R97" t="inlineStr">
+        <is>
+          <t>1786190458</t>
+        </is>
+      </c>
+      <c r="S97" t="inlineStr">
+        <is>
+          <t>1786212000</t>
+        </is>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>48.066482</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
           <t>0x5c5b512ea725fac30531bf5fe91f34f3ccc0eeff23890c18f25c3f329007c589</t>
         </is>
       </c>
-      <c r="B76" t="inlineStr">
+      <c r="B98" t="inlineStr">
         <is>
           <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
         </is>
       </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E76" t="inlineStr">
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
         <is>
           <t>1.3638</t>
         </is>
       </c>
-      <c r="F76" t="inlineStr">
+      <c r="F98" t="inlineStr">
         <is>
           <t>1X2</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr">
+      <c r="G98" t="inlineStr">
         <is>
           <t>Tie</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>Primera Nacional</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Primera Nacional</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
         <is>
           <t>Almirante Brown vs Ciudad Bolivar</t>
         </is>
       </c>
-      <c r="J76" t="inlineStr">
+      <c r="J98" t="inlineStr">
         <is>
           <t>Almirante Brown</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr">
+      <c r="K98" t="inlineStr">
         <is>
           <t>Ciudad Bolivar</t>
         </is>
       </c>
-      <c r="L76" t="inlineStr">
+      <c r="L98" t="inlineStr">
         <is>
           <t>0xd5906ce08d61f7c5ee45fcebd2c8baeed5558387398ea332817a4b632f439b6d</t>
         </is>
       </c>
-      <c r="M76" t="inlineStr">
+      <c r="M98" t="inlineStr">
         <is>
           <t>L19683447</t>
         </is>
       </c>
-      <c r="N76" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O76" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P76" t="inlineStr">
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O98" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P98" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q76" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R76" t="inlineStr">
+      <c r="Q98" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R98" t="inlineStr">
         <is>
           <t>1786125660</t>
         </is>
       </c>
-      <c r="S76" t="inlineStr">
+      <c r="S98" t="inlineStr">
         <is>
           <t>1786212000</t>
         </is>
       </c>
-      <c r="T76" t="inlineStr">
+      <c r="T98" t="inlineStr">
         <is>
           <t>2.749141</t>
         </is>
       </c>
-      <c r="U76" t="inlineStr">
+      <c r="U98" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V76" t="inlineStr">
+      <c r="V98" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/Primera Nacional/trades.xlsx
+++ b/data/sxbet/ligas/Primera Nacional/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V98"/>
+  <dimension ref="A1:V107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,23 +531,23 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0x2ce4118d8299ef054cc6439e8191ab57041190d43c1b322f7656f46a915f66a7</t>
+          <t>0xe70516113cb626418e16d5940b7952c123bd3afbc9ae8fb08b6d8a46cfc93917</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x49c03d69c92f4aEa65FBF1F149A1ac3Bf31A37C6</t>
         </is>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>11.65</t>
+          <t>231.99994</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.0888</t>
+          <t>1.89</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -563,27 +563,27 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Godoy Cruz vs Chaco For Ever</t>
+          <t>San Martin Tucuman vs San Martín de San Juan</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>San Martin Tucuman</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>San Martín de San Juan</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0xa5f02d0d08d0dcc4818948397f0f26c77f90b87182cec4d62ab01f77352671a1</t>
+          <t>0x20f1a35dae3d2a458c7a6a3e312e646a320245e89d843105ba9b217e1cd46c9e</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>L19683484</t>
+          <t>L19682528</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -608,17 +608,17 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1786305067</t>
+          <t>1786315295</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>1786303800</t>
+          <t>1786309200</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>131.267606</t>
+          <t>260.67409</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -635,7 +635,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0x72a01c47ea710f8819c55b38617462ca579e333f91db40e5ab1feff1d3de96c8</t>
+          <t>0x8a82110b5ad97ac1c2de4721106d20fdd9060513206960520e7155a6e2b20612</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,19 +643,15 @@
           <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>102.18997</t>
+          <t>18.85306</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.8087</t>
+          <t>1.3875</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -663,11 +659,7 @@
           <t>Primera Nacional</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Colon de Santa Fe</t>
-        </is>
-      </c>
+      <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -675,27 +667,27 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Colon de Santa Fe vs San Telmo</t>
+          <t>San Martin Tucuman vs San Martín de San Juan</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Colon de Santa Fe</t>
+          <t>San Martin Tucuman</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>San Martín de San Juan</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0xbca9ed7d23a7df6c8ab98ab2ffc6649f2d4bd3d9007bd0ecf103e453c87addac</t>
+          <t>0x710577a276e495ee3f90c1efed84c57aad13b2a5a77b9b1f1045dc6c20df1b82</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>L19683494</t>
+          <t>L19682528</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -720,17 +712,17 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1786305018</t>
+          <t>1786315013</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>1786300200</t>
+          <t>1786309200</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>126.35545</t>
+          <t>48.653058</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -747,7 +739,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0x48ad1a825a577db64992a5c2f61f562d82c8f17820251af179f0cdf9d5e6b577</t>
+          <t>0x99cae5762d48bf6225a2833cebf0caac6f2be5141693c86d119bba55fecb00af</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -755,19 +747,15 @@
           <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>102.18997</t>
+          <t>117.43306</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.8087</t>
+          <t>1.3875</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -775,11 +763,7 @@
           <t>Primera Nacional</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Colon de Santa Fe 0</t>
-        </is>
-      </c>
+      <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -787,27 +771,27 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Colon de Santa Fe vs San Telmo</t>
+          <t>San Martin Tucuman vs San Martín de San Juan</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Colon de Santa Fe</t>
+          <t>San Martin Tucuman</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>San Martín de San Juan</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0x9c15c50c33bf4b091bef5a468ce1fe4a2593b78db6048cae08ab186caadf08a9</t>
+          <t>0x4f02331cd42a68f65ea16d62aac0c6b123d9400d12a4d556f3a72df894da02fb</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>L19683494</t>
+          <t>L19682528</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -832,17 +816,17 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1786305018</t>
+          <t>1786314895</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>1786300200</t>
+          <t>1786309200</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>126.35545</t>
+          <t>303.053058</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -859,7 +843,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0x241c6cdee87bcff9c9e1e77941a5ecd05acb972d4c07e1cfc562414003f5c59c</t>
+          <t>0x4030f87453819c2a532820e812d084e6b4bb480048daa74b20c2d6e02cb96f44</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -870,17 +854,17 @@
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>63.89997</t>
+          <t>0.25944</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.8912</t>
+          <t>1.3675</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>Primera Nacional</t>
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
@@ -891,27 +875,27 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Racing de Cordoba vs San Miguel</t>
+          <t>San Martin Tucuman vs San Martín de San Juan</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Racing de Cordoba</t>
+          <t>San Martin Tucuman</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>San Martín de San Juan</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0xb00a08202acc66af81e3cc28141951f5744b2edb09c13699c361640638e0580a</t>
+          <t>0x710577a276e495ee3f90c1efed84c57aad13b2a5a77b9b1f1045dc6c20df1b82</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>L19683501</t>
+          <t>L19682528</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -936,17 +920,17 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1786304709</t>
+          <t>1786311747</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>1786302000</t>
+          <t>1786309200</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>71.697021</t>
+          <t>0.705959</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -963,31 +947,39 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0xfb092fb802f6de6249f78cd6b0c995923dcd8a18d766d60718068deca14131d2</t>
+          <t>0x94334ff3be3abb398e288ea2bdc325dbea166976a777d4b3565d6adf6e74cceb</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr"/>
+          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>52.23996</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.8912</t>
+          <t>1.545</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr"/>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Over 1.5</t>
+        </is>
+      </c>
       <c r="H6" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -995,27 +987,27 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Racing de Cordoba vs San Miguel</t>
+          <t>San Martin Tucuman vs San Martín de San Juan</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Racing de Cordoba</t>
+          <t>San Martin Tucuman</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>San Martín de San Juan</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0xb00a08202acc66af81e3cc28141951f5744b2edb09c13699c361640638e0580a</t>
+          <t>0x59f5c83d1ebabf219c4e416ecb6303622840a732d32e28a4ca19fdba0d4e206d</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>L19683501</t>
+          <t>L19682528</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1040,17 +1032,17 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1786304687</t>
+          <t>1786309862</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>1786302000</t>
+          <t>1786309200</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>58.614261</t>
+          <t>1.834862</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1067,28 +1059,28 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0xdaad372a2d56f6f987e31c931aed692c41df131e0f5ffc29a5e5b9202518a8ad</t>
+          <t>0xc96803526daa07f4eae1fbfe8d09be9d49a0e7e2ce24d0288f9d3ab9ec387e36</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x4a09916b1325Eed50eE8973B13742a205B0B7c7E</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>50</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.2563</t>
+          <t>1.825</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Asian Handicap (0.5)</t>
+          <t>Under/Over (2)</t>
         </is>
       </c>
       <c r="G7" t="inlineStr"/>
@@ -1114,7 +1106,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0x6dbad77d129f55a581762668ca1964af6cce4241516257e981ed02638805382a</t>
+          <t>0xb291f54e66fa1539bf7206876cb79292f9c9cd3cebed6ca59247514b369a28fb</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1144,7 +1136,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1786304596</t>
+          <t>1786307586</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1154,7 +1146,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>39.02439</t>
+          <t>60.606061</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1171,31 +1163,39 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0xd8c270eff581f800f6dfee154ad07fcaa13887305309b80012750a0200954653</t>
+          <t>0xe508af858531cbb110be0edc19b46f9f847f5373f422a56dc4f6091f724877c2</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>104.40999</t>
+          <t>42.02</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.685</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr"/>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Over 2.5</t>
+        </is>
+      </c>
       <c r="H8" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0x48447168804e92d195e0c849cfb7ae548e076f102e1005f3756585b3d18ea65c</t>
+          <t>0xb00a08202acc66af81e3cc28141951f5744b2edb09c13699c361640638e0580a</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1786304566</t>
+          <t>1786306456</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1258,7 +1258,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>152.423343</t>
+          <t>525.25</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1275,31 +1275,39 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0x584df9c83be504ffadc29cf9bc05886a622203a90bdf8fd90fe15998dca2c79a</t>
+          <t>0x6d0e9cce02624418d7b75dc11802dbf4900745db1d1f0ec0ee6d8804e67faced</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>30.76</t>
+          <t>42.02</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.8388</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr"/>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Over 2.5</t>
+        </is>
+      </c>
       <c r="H9" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -1307,27 +1315,27 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Godoy Cruz vs Chaco For Ever</t>
+          <t>Racing de Cordoba vs San Miguel</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Racing de Cordoba</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0x9c19e4c1fd9646506f8ea14e2b1be19b49a5ab4dc1a7bf40167705a4ae2b338b</t>
+          <t>0xb00a08202acc66af81e3cc28141951f5744b2edb09c13699c361640638e0580a</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>L19683484</t>
+          <t>L19683501</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1352,17 +1360,17 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1786304409</t>
+          <t>1786306379</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>1786303800</t>
+          <t>1786302000</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>36.673621</t>
+          <t>525.25</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1379,7 +1387,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0x80bb89bcfcad865ae79dd791b8e50e1efe79465dcaef80ef22f91624a9a206e0</t>
+          <t>0xfbf539c8fecb9ae92fbe1749fa31c242f747ee8b7d8b6d79b9eb6a315ac4109a</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1394,22 +1402,22 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>164.56999</t>
+          <t>25.88</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.5875</t>
+          <t>1.0962</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (2)</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tie</t>
+          <t>Over 2.0</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1419,27 +1427,27 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>CA Colegiales vs Patronato</t>
+          <t>Racing de Cordoba vs San Miguel</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>CA Colegiales</t>
+          <t>Racing de Cordoba</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0x08cf3f4d7a357213e26484ea0db7a018932df0928a98202f91241b88b1990c60</t>
+          <t>0xb291f54e66fa1539bf7206876cb79292f9c9cd3cebed6ca59247514b369a28fb</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>L19683449</t>
+          <t>L19683501</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1464,17 +1472,17 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1786304222</t>
+          <t>1786306378</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>1786298400</t>
+          <t>1786302000</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>280.119132</t>
+          <t>268.883117</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1491,39 +1499,31 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0x4a29c98cff774b7281c745ce8241168cf83b95715fb62c195dfe0bdfd4993ffa</t>
+          <t>0x2ce4118d8299ef054cc6439e8191ab57041190d43c1b322f7656f46a915f66a7</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>50.96999</t>
+          <t>11.65</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.6187</t>
+          <t>1.0888</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Primera Nacional</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>CA Colegiales 0</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -1531,27 +1531,27 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>CA Colegiales vs Patronato</t>
+          <t>Godoy Cruz vs Chaco For Ever</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>CA Colegiales</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0x3fa48fbf2a59e0b45def889e06df3d2da646e9465f9af4f1b88581fea7fb4496</t>
+          <t>0xa5f02d0d08d0dcc4818948397f0f26c77f90b87182cec4d62ab01f77352671a1</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>L19683449</t>
+          <t>L19683484</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1576,17 +1576,17 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1786304216</t>
+          <t>1786305067</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>1786298400</t>
+          <t>1786303800</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>82.375741</t>
+          <t>131.267606</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1603,12 +1603,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0x606477ca73e4e38677cfe19e9dbb8d21dd44116004cd1a6b689a66845a1f33c5</t>
+          <t>0x72a01c47ea710f8819c55b38617462ca579e333f91db40e5ab1feff1d3de96c8</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1618,22 +1618,22 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>47.49</t>
+          <t>102.18997</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.8087</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Primera Nacional</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tie</t>
+          <t>Colon de Santa Fe</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1643,27 +1643,27 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>CA Colegiales vs Patronato</t>
+          <t>Colon de Santa Fe vs San Telmo</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>CA Colegiales</t>
+          <t>Colon de Santa Fe</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>0x08cf3f4d7a357213e26484ea0db7a018932df0928a98202f91241b88b1990c60</t>
+          <t>0xbca9ed7d23a7df6c8ab98ab2ffc6649f2d4bd3d9007bd0ecf103e453c87addac</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>L19683449</t>
+          <t>L19683494</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1688,17 +1688,17 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1786304193</t>
+          <t>1786305018</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>1786298400</t>
+          <t>1786300200</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>79.15</t>
+          <t>126.35545</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1715,7 +1715,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0x471461bdea5d2a1f048ae19a536ae904425043d9ce35e662e416d1892b8ab682</t>
+          <t>0x48ad1a825a577db64992a5c2f61f562d82c8f17820251af179f0cdf9d5e6b577</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>45.36</t>
+          <t>102.18997</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.6275</t>
+          <t>1.8087</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1745,7 +1745,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>CA Colegiales 0</t>
+          <t>Colon de Santa Fe 0</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1755,27 +1755,27 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>CA Colegiales vs Patronato</t>
+          <t>Colon de Santa Fe vs San Telmo</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>CA Colegiales</t>
+          <t>Colon de Santa Fe</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>0x3fa48fbf2a59e0b45def889e06df3d2da646e9465f9af4f1b88581fea7fb4496</t>
+          <t>0x9c15c50c33bf4b091bef5a468ce1fe4a2593b78db6048cae08ab186caadf08a9</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>L19683449</t>
+          <t>L19683494</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1800,17 +1800,17 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1786304137</t>
+          <t>1786305018</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>1786298400</t>
+          <t>1786300200</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>72.286853</t>
+          <t>126.35545</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1827,7 +1827,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0x2b918c36189e27805e61d743881205705b15ab4bdbf93fa4149c03b299488496</t>
+          <t>0x241c6cdee87bcff9c9e1e77941a5ecd05acb972d4c07e1cfc562414003f5c59c</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1838,17 +1838,17 @@
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>291.91999</t>
+          <t>63.89997</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1.8125</t>
+          <t>1.8912</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G14" t="inlineStr"/>
@@ -1859,27 +1859,27 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>CA Colegiales vs Patronato</t>
+          <t>Racing de Cordoba vs San Miguel</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>CA Colegiales</t>
+          <t>Racing de Cordoba</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>0x08cf3f4d7a357213e26484ea0db7a018932df0928a98202f91241b88b1990c60</t>
+          <t>0xb00a08202acc66af81e3cc28141951f5744b2edb09c13699c361640638e0580a</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>L19683449</t>
+          <t>L19683501</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1904,17 +1904,17 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1786304032</t>
+          <t>1786304709</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>1786298400</t>
+          <t>1786302000</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>359.286142</t>
+          <t>71.697021</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -1931,39 +1931,31 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0x0c986442e558e0ecef4ac6ae5c05b398f82bc22bf0a12f073b441ebce3f8f73e</t>
+          <t>0xfb092fb802f6de6249f78cd6b0c995923dcd8a18d766d60718068deca14131d2</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0x161ba9aad05022c88726A1D1244fDF624e51BFD5</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>52.23996</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1.5063</t>
+          <t>1.8912</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Colon de Santa Fe</t>
-        </is>
-      </c>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -1971,27 +1963,27 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Colon de Santa Fe vs San Telmo</t>
+          <t>Racing de Cordoba vs San Miguel</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Colon de Santa Fe</t>
+          <t>Racing de Cordoba</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>0x1a11ec80edeaae24566c4f4f891cc2afc56b377b24997a6e8ee533eeaaad5c92</t>
+          <t>0xb00a08202acc66af81e3cc28141951f5744b2edb09c13699c361640638e0580a</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>L19683494</t>
+          <t>L19683501</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -2016,17 +2008,17 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>1786303960</t>
+          <t>1786304687</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>1786300200</t>
+          <t>1786302000</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>4.938272</t>
+          <t>58.614261</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2043,28 +2035,28 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0x2a347762aef526a0953efcb99ce105f109d3055f0d91ab8c6f756cd50ff191d0</t>
+          <t>0xdaad372a2d56f6f987e31c931aed692c41df131e0f5ffc29a5e5b9202518a8ad</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1.07999</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1.5775</t>
+          <t>1.2563</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
+          <t>Asian Handicap (0.5)</t>
         </is>
       </c>
       <c r="G16" t="inlineStr"/>
@@ -2075,27 +2067,27 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Godoy Cruz vs Chaco For Ever</t>
+          <t>Racing de Cordoba vs San Miguel</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Racing de Cordoba</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>0x8a3835f02766a90c02150e223fdcaa0f380cffe1bd489dd896b621cb4de6a216</t>
+          <t>0x6dbad77d129f55a581762668ca1964af6cce4241516257e981ed02638805382a</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>L19683484</t>
+          <t>L19683501</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -2120,17 +2112,17 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1786303869</t>
+          <t>1786304596</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>1786303800</t>
+          <t>1786302000</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>1.870113</t>
+          <t>39.02439</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2147,23 +2139,23 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0xf1ea587ba3fa2b6f394d282689f029176ee146013ab745dcfa61570d0ec1af54</t>
+          <t>0xd8c270eff581f800f6dfee154ad07fcaa13887305309b80012750a0200954653</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>66.77496</t>
+          <t>104.40999</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.1938</t>
+          <t>1.685</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -2179,27 +2171,27 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>CA Colegiales vs Patronato</t>
+          <t>Racing de Cordoba vs San Miguel</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>CA Colegiales</t>
+          <t>Racing de Cordoba</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>0x6033340ba69fb7874ae22715f395c0926449aa18c6ec5295e2568fe9a173664d</t>
+          <t>0x48447168804e92d195e0c849cfb7ae548e076f102e1005f3756585b3d18ea65c</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>L19683449</t>
+          <t>L19683501</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -2224,17 +2216,17 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>1786303811</t>
+          <t>1786304566</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>1786298400</t>
+          <t>1786302000</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>344.644955</t>
+          <t>152.423343</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2251,28 +2243,28 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0x83f468f50e882b1c9b4663834cfdbddae84368823e2297b07a8a228b7252f9d0</t>
+          <t>0x584df9c83be504ffadc29cf9bc05886a622203a90bdf8fd90fe15998dca2c79a</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>20.75148</t>
+          <t>30.76</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.4275</t>
+          <t>1.8388</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G18" t="inlineStr"/>
@@ -2283,27 +2275,27 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>CA Colegiales vs Patronato</t>
+          <t>Godoy Cruz vs Chaco For Ever</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>CA Colegiales</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>0x5063fd7c88c1b369ed4a83e39411f4287c83048fafbc24740f9ecb68019a60ec</t>
+          <t>0x9c19e4c1fd9646506f8ea14e2b1be19b49a5ab4dc1a7bf40167705a4ae2b338b</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>L19683449</t>
+          <t>L19683484</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -2328,17 +2320,17 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>1786303811</t>
+          <t>1786304409</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>1786298400</t>
+          <t>1786303800</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>48.541474</t>
+          <t>36.673621</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2355,31 +2347,39 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0x5d59910b62dd3a569254988b87a126db28ce8123f67bea999e650c42a85e456c</t>
+          <t>0x80bb89bcfcad865ae79dd791b8e50e1efe79465dcaef80ef22f91624a9a206e0</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>64.86487</t>
+          <t>164.56999</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1.075</t>
+          <t>1.5875</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Under/Over (0.5)</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H19" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -2387,27 +2387,27 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Club Atletico Mitre de Santiago del Estero vs Defensores de Belgrano Buenos Aires</t>
+          <t>CA Colegiales vs Patronato</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Club Atletico Mitre de Santiago del Estero</t>
+          <t>CA Colegiales</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano Buenos Aires</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>0x7423d14fbc1277a1b44ab6287b237b4f12599476710984e2df8514e1e505203b</t>
+          <t>0x08cf3f4d7a357213e26484ea0db7a018932df0928a98202f91241b88b1990c60</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>L19683493</t>
+          <t>L19683449</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -2432,17 +2432,17 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>1786303551</t>
+          <t>1786304222</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>1786302000</t>
+          <t>1786298400</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>864.864933</t>
+          <t>280.119132</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2459,31 +2459,39 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0x54e4c2b9fcb34a87d3118c2c4aa1d528e53ecdeb3b19d58ec93ceabdcf9789a0</t>
+          <t>0x4a29c98cff774b7281c745ce8241168cf83b95715fb62c195dfe0bdfd4993ffa</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>155.22388</t>
+          <t>50.96999</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.1625</t>
+          <t>1.6187</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Under/Over (1)</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr"/>
+          <t>Primera Nacional</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>CA Colegiales 0</t>
+        </is>
+      </c>
       <c r="H20" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -2491,27 +2499,27 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Club Atletico Mitre de Santiago del Estero vs Defensores de Belgrano Buenos Aires</t>
+          <t>CA Colegiales vs Patronato</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Club Atletico Mitre de Santiago del Estero</t>
+          <t>CA Colegiales</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano Buenos Aires</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0x4f7afe558099a628e7275525f608e3e5d976f6f0ae76324c03ac2a8d33384e1b</t>
+          <t>0x3fa48fbf2a59e0b45def889e06df3d2da646e9465f9af4f1b88581fea7fb4496</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>L19683493</t>
+          <t>L19683449</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -2536,17 +2544,17 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>1786303551</t>
+          <t>1786304216</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>1786302000</t>
+          <t>1786298400</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>955.223877</t>
+          <t>82.375741</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2563,7 +2571,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0xac12d313bf6318f639126e42c96989b9e78cbb4aeafba2d7a6842ecaab1d4679</t>
+          <t>0x606477ca73e4e38677cfe19e9dbb8d21dd44116004cd1a6b689a66845a1f33c5</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2571,15 +2579,19 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr"/>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>29.36999</t>
+          <t>47.49</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1.6288</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -2587,7 +2599,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H21" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -2595,27 +2611,27 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Racing de Cordoba vs San Miguel</t>
+          <t>CA Colegiales vs Patronato</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Racing de Cordoba</t>
+          <t>CA Colegiales</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0x48447168804e92d195e0c849cfb7ae548e076f102e1005f3756585b3d18ea65c</t>
+          <t>0x08cf3f4d7a357213e26484ea0db7a018932df0928a98202f91241b88b1990c60</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>L19683501</t>
+          <t>L19683449</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -2640,17 +2656,17 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>1786303457</t>
+          <t>1786304193</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>1786302000</t>
+          <t>1786298400</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>46.711714</t>
+          <t>79.15</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -2667,12 +2683,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0xab77c0bf2f6ec1315e378c5db8b6863eb08357a9b49d9ba43bcce724926da176</t>
+          <t>0x471461bdea5d2a1f048ae19a536ae904425043d9ce35e662e416d1892b8ab682</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -2682,22 +2698,22 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>45.36</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1.5175</t>
+          <t>1.6275</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
+          <t>Primera Nacional</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Colon de Santa Fe -0.5</t>
+          <t>CA Colegiales 0</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2707,27 +2723,27 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Colon de Santa Fe vs San Telmo</t>
+          <t>CA Colegiales vs Patronato</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Colon de Santa Fe</t>
+          <t>CA Colegiales</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0x12375b1d9ef51c6465eb968d63b1ce25f63b0af22de8742ede4e1070f2e04c6b</t>
+          <t>0x3fa48fbf2a59e0b45def889e06df3d2da646e9465f9af4f1b88581fea7fb4496</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>L19683494</t>
+          <t>L19683449</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -2752,17 +2768,17 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>1786302968</t>
+          <t>1786304137</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>1786300200</t>
+          <t>1786298400</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2.801932</t>
+          <t>72.286853</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -2779,39 +2795,31 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0x7262b8ffc279b263369649339936e85dc19d4d92bf11fad680b40a45ad4a7442</t>
+          <t>0x2b918c36189e27805e61d743881205705b15ab4bdbf93fa4149c03b299488496</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>23.24</t>
+          <t>291.91999</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1.3388</t>
+          <t>1.8125</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>Colon de Santa Fe -1</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -2819,27 +2827,27 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Colon de Santa Fe vs San Telmo</t>
+          <t>CA Colegiales vs Patronato</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Colon de Santa Fe</t>
+          <t>CA Colegiales</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0x4b323aab38dd8f5096dcd1965ce7dc05c69ab73371e55e810b7a5aee356bf244</t>
+          <t>0x08cf3f4d7a357213e26484ea0db7a018932df0928a98202f91241b88b1990c60</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>L19683494</t>
+          <t>L19683449</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -2864,17 +2872,17 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>1786302417</t>
+          <t>1786304032</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>1786300200</t>
+          <t>1786298400</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>68.605166</t>
+          <t>359.286142</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -2891,23 +2899,27 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0xaef8a42b6335c8c59cb7bb616441203e8516097ce0e7adb9c1dfe622d7b8a46a</t>
+          <t>0x0c986442e558e0ecef4ac6ae5c05b398f82bc22bf0a12f073b441ebce3f8f73e</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr"/>
+          <t>0x161ba9aad05022c88726A1D1244fDF624e51BFD5</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>14.3554</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1.0513</t>
+          <t>1.5063</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -2915,7 +2927,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Colon de Santa Fe</t>
+        </is>
+      </c>
       <c r="H24" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -2923,27 +2939,27 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Deportivo Moron vs Acassuso</t>
+          <t>Colon de Santa Fe vs San Telmo</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Deportivo Moron</t>
+          <t>Colon de Santa Fe</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0x7514a255ce41be3c5db9f8849ba04e78dab80f02d1fe78c2aae82bbc843a9745</t>
+          <t>0x1a11ec80edeaae24566c4f4f891cc2afc56b377b24997a6e8ee533eeaaad5c92</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>L19683452</t>
+          <t>L19683494</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -2968,17 +2984,17 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>1786301685</t>
+          <t>1786303960</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>1786298400</t>
+          <t>1786300200</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>280.105366</t>
+          <t>4.938272</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -2995,28 +3011,28 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0x9cd0c1e560dfbdd3bb0ca9522422167bdbc75ef5c7813dbe00ce4bee50d0f1be</t>
+          <t>0x2a347762aef526a0953efcb99ce105f109d3055f0d91ab8c6f756cd50ff191d0</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
         </is>
       </c>
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
-          <t>13.80272</t>
+          <t>1.07999</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1.0488</t>
+          <t>1.5775</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (2)</t>
         </is>
       </c>
       <c r="G25" t="inlineStr"/>
@@ -3027,27 +3043,27 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Deportivo Moron vs Acassuso</t>
+          <t>Godoy Cruz vs Chaco For Ever</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Deportivo Moron</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0x7514a255ce41be3c5db9f8849ba04e78dab80f02d1fe78c2aae82bbc843a9745</t>
+          <t>0x8a3835f02766a90c02150e223fdcaa0f380cffe1bd489dd896b621cb4de6a216</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>L19683452</t>
+          <t>L19683484</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -3072,17 +3088,17 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>1786301534</t>
+          <t>1786303869</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>1786298400</t>
+          <t>1786303800</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>283.132718</t>
+          <t>1.870113</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3099,7 +3115,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0x9036645c2b6fdeee93c9912e60b360f0e894db0b98a32ed8106dd074362ac356</t>
+          <t>0xf1ea587ba3fa2b6f394d282689f029176ee146013ab745dcfa61570d0ec1af54</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3107,19 +3123,15 @@
           <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
-          <t>37.59</t>
+          <t>66.77496</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1.1225</t>
+          <t>1.1938</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -3127,26 +3139,22 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Primera Nacional</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>CA Colegiales vs Patronato</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
         <is>
           <t>CA Colegiales</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Primera Nacional</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>CA Colegiales vs Patronato</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>CA Colegiales</t>
-        </is>
-      </c>
       <c r="K26" t="inlineStr">
         <is>
           <t>Patronato</t>
@@ -3184,7 +3192,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>1786301228</t>
+          <t>1786303811</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -3194,7 +3202,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>306.857143</t>
+          <t>344.644955</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -3211,39 +3219,31 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0xd9eff492baa46fea0da1221b63ca70a7e18beec129de6ebec5453a1b9e6bfcf8</t>
+          <t>0x83f468f50e882b1c9b4663834cfdbddae84368823e2297b07a8a228b7252f9d0</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>20.75148</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1.4263</t>
+          <t>1.4275</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Asian Handicap (0.5)</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>CA Colegiales +0.5</t>
-        </is>
-      </c>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -3266,7 +3266,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>0xf03b2761ed02376d644cd19d08d1923efb50cd17956a930c587e812207a86746</t>
+          <t>0x5063fd7c88c1b369ed4a83e39411f4287c83048fafbc24740f9ecb68019a60ec</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>1786301216</t>
+          <t>1786303811</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>46.920821</t>
+          <t>48.541474</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -3323,7 +3323,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0xc72322e8ff04e28165d90bbcfa3c4b34aa19dd5fc1215e13ba7e1ce6362a9292</t>
+          <t>0x5d59910b62dd3a569254988b87a126db28ce8123f67bea999e650c42a85e456c</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3331,31 +3331,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
-          <t>7.93</t>
+          <t>64.86487</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>1.4263</t>
+          <t>1.075</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>Racing de Cordoba</t>
-        </is>
-      </c>
+          <t>Under/Over (0.5)</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -3363,27 +3355,27 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Racing de Cordoba vs San Miguel</t>
+          <t>Club Atletico Mitre de Santiago del Estero vs Defensores de Belgrano Buenos Aires</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Racing de Cordoba</t>
+          <t>Club Atletico Mitre de Santiago del Estero</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Defensores de Belgrano Buenos Aires</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>0x48447168804e92d195e0c849cfb7ae548e076f102e1005f3756585b3d18ea65c</t>
+          <t>0x7423d14fbc1277a1b44ab6287b237b4f12599476710984e2df8514e1e505203b</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>L19683501</t>
+          <t>L19683493</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -3408,7 +3400,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>1786301162</t>
+          <t>1786303551</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
@@ -3418,7 +3410,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>18.604106</t>
+          <t>864.864933</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -3435,39 +3427,31 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0xd37a1d074e8819ce033a62d6fe3bb026c46529f33aed65aaac63e3d53cb8ce3e</t>
+          <t>0x54e4c2b9fcb34a87d3118c2c4aa1d528e53ecdeb3b19d58ec93ceabdcf9789a0</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>0x5022174051792ac42d3af7Ff6bC9cf78a6aE3f32</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>155.22388</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>1.4287</t>
+          <t>1.1625</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Under/Over (0.5)</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>Over 0.5</t>
-        </is>
-      </c>
+          <t>Under/Over (1)</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -3475,27 +3459,27 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Atlanta vs Temperley</t>
+          <t>Club Atletico Mitre de Santiago del Estero vs Defensores de Belgrano Buenos Aires</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Club Atletico Mitre de Santiago del Estero</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Defensores de Belgrano Buenos Aires</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>0x84c2bb083fa51c1fc591f5ac9524e09d26434823e44ca466e2af8bd17ae651cb</t>
+          <t>0x4f7afe558099a628e7275525f608e3e5d976f6f0ae76324c03ac2a8d33384e1b</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>L19683448</t>
+          <t>L19683493</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -3520,17 +3504,17 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>1786300699</t>
+          <t>1786303551</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>1786294800</t>
+          <t>1786302000</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>11.661808</t>
+          <t>955.223877</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -3547,28 +3531,28 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0x0199716d54c5764cbf1a6783da6c106cf378f2c6b96892a13d7019f5cb41b3fa</t>
+          <t>0xac12d313bf6318f639126e42c96989b9e78cbb4aeafba2d7a6842ecaab1d4679</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
-          <t>16.84</t>
+          <t>29.36999</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1.1262</t>
+          <t>1.6288</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Under/Over (0.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G30" t="inlineStr"/>
@@ -3579,27 +3563,27 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Godoy Cruz vs Chaco For Ever</t>
+          <t>Racing de Cordoba vs San Miguel</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Racing de Cordoba</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>0x9c696117152178b9240c2e3eddca6b53432d4a4937a20042677cd1f666604f23</t>
+          <t>0x48447168804e92d195e0c849cfb7ae548e076f102e1005f3756585b3d18ea65c</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>L19683484</t>
+          <t>L19683501</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -3624,17 +3608,17 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>1786300516</t>
+          <t>1786303457</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>1786303800</t>
+          <t>1786302000</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>133.386139</t>
+          <t>46.711714</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -3651,31 +3635,39 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0x84f162af96f80a1f61f37a3b12a3dab48dcffde9bd10d0cea022df759f18111f</t>
+          <t>0xab77c0bf2f6ec1315e378c5db8b6863eb08357a9b49d9ba43bcce724926da176</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr"/>
+          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>36.84547</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1.1362</t>
+          <t>1.5175</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Primera Nacional</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr"/>
+          <t>Asian Handicap (-0.5)</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Colon de Santa Fe -0.5</t>
+        </is>
+      </c>
       <c r="H31" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -3698,7 +3690,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>0xbca9ed7d23a7df6c8ab98ab2ffc6649f2d4bd3d9007bd0ecf103e453c87addac</t>
+          <t>0x12375b1d9ef51c6465eb968d63b1ce25f63b0af22de8742ede4e1070f2e04c6b</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -3728,7 +3720,7 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>1786300513</t>
+          <t>1786302968</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
@@ -3738,7 +3730,7 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>270.425468</t>
+          <t>2.801932</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -3755,12 +3747,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0x2f3773fa15124937ec4965274c782b70d022a4fb2a2c8e85fe36a66e0dcc1a53</t>
+          <t>0x7262b8ffc279b263369649339936e85dc19d4d92bf11fad680b40a45ad4a7442</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -3770,22 +3762,22 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>23.24</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>1.2563</t>
+          <t>1.3388</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Colon de Santa Fe -1</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -3795,27 +3787,27 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Racing de Cordoba vs San Miguel</t>
+          <t>Colon de Santa Fe vs San Telmo</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Racing de Cordoba</t>
+          <t>Colon de Santa Fe</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0x8ddab476b71709486e3a0e2118fafcb483076bd09c1c25dcce66244486fed688</t>
+          <t>0x4b323aab38dd8f5096dcd1965ce7dc05c69ab73371e55e810b7a5aee356bf244</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>L19683501</t>
+          <t>L19683494</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -3840,17 +3832,17 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>1786300245</t>
+          <t>1786302417</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>1786302000</t>
+          <t>1786300200</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>3.902439</t>
+          <t>68.605166</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -3867,39 +3859,31 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0x4334abae5afdbf026c92af25200b83381434248bdfca39224de3957cba46f6e4</t>
+          <t>0xaef8a42b6335c8c59cb7bb616441203e8516097ce0e7adb9c1dfe622d7b8a46a</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr">
         <is>
-          <t>52.38</t>
+          <t>14.3554</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>1.675</t>
+          <t>1.0513</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Primera Nacional</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>CA Colegiales 0</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -3907,27 +3891,27 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>CA Colegiales vs Patronato</t>
+          <t>Deportivo Moron vs Acassuso</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>CA Colegiales</t>
+          <t>Deportivo Moron</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>0x3fa48fbf2a59e0b45def889e06df3d2da646e9465f9af4f1b88581fea7fb4496</t>
+          <t>0x7514a255ce41be3c5db9f8849ba04e78dab80f02d1fe78c2aae82bbc843a9745</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>L19683449</t>
+          <t>L19683452</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -3952,7 +3936,7 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>1786300042</t>
+          <t>1786301685</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
@@ -3962,7 +3946,7 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>77.6</t>
+          <t>280.105366</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -3979,27 +3963,23 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0xad7255fad3f7d526c2f80d7968fa11121b17d106e3df35095d9b411cead706b0</t>
+          <t>0x9cd0c1e560dfbdd3bb0ca9522422167bdbc75ef5c7813dbe00ce4bee50d0f1be</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
-          <t>3.02932</t>
+          <t>13.80272</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>1.2325</t>
+          <t>1.0488</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -4007,11 +3987,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>San Miguel</t>
-        </is>
-      </c>
+      <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -4019,27 +3995,27 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Racing de Cordoba vs San Miguel</t>
+          <t>Deportivo Moron vs Acassuso</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Racing de Cordoba</t>
+          <t>Deportivo Moron</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0x8ddab476b71709486e3a0e2118fafcb483076bd09c1c25dcce66244486fed688</t>
+          <t>0x7514a255ce41be3c5db9f8849ba04e78dab80f02d1fe78c2aae82bbc843a9745</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>L19683501</t>
+          <t>L19683452</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -4064,17 +4040,17 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>1786298930</t>
+          <t>1786301534</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>1786302000</t>
+          <t>1786298400</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>13.029333</t>
+          <t>283.132718</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -4091,23 +4067,27 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0x972e5a678ec56c15f03cbf0d14d7070ad000111adf76887dc34cc27780792e32</t>
+          <t>0x9036645c2b6fdeee93c9912e60b360f0e894db0b98a32ed8106dd074362ac356</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>24.07997</t>
+          <t>37.59</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>1.8675</t>
+          <t>1.1225</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -4115,7 +4095,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr"/>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>CA Colegiales</t>
+        </is>
+      </c>
       <c r="H35" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -4123,27 +4107,27 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Godoy Cruz vs Chaco For Ever</t>
+          <t>CA Colegiales vs Patronato</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>CA Colegiales</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>0x9c19e4c1fd9646506f8ea14e2b1be19b49a5ab4dc1a7bf40167705a4ae2b338b</t>
+          <t>0x6033340ba69fb7874ae22715f395c0926449aa18c6ec5295e2568fe9a173664d</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>L19683484</t>
+          <t>L19683449</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -4168,17 +4152,17 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>1786297771</t>
+          <t>1786301228</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>1786303800</t>
+          <t>1786298400</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>27.75789</t>
+          <t>306.857143</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
@@ -4195,12 +4179,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0x1da1f134f1ec859a8260a79216b9030b9f0b715d9a51d09741ff884111dcde2b</t>
+          <t>0xd9eff492baa46fea0da1221b63ca70a7e18beec129de6ebec5453a1b9e6bfcf8</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>0x311AE302984D8b1cf53D6bfB0a6672f05c423AE6</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -4210,22 +4194,22 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>37.76669</t>
+          <t>20</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>1.5837</t>
+          <t>1.4263</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
+          <t>Asian Handicap (0.5)</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Godoy Cruz -0.5</t>
+          <t>CA Colegiales +0.5</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -4235,27 +4219,27 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Godoy Cruz vs Chaco For Ever</t>
+          <t>CA Colegiales vs Patronato</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>CA Colegiales</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>0xb2c04ce7cffc1005eb6199d3c34d31b109e8af04a357b4f8eb9f6b8362ba33c2</t>
+          <t>0xf03b2761ed02376d644cd19d08d1923efb50cd17956a930c587e812207a86746</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>L19683484</t>
+          <t>L19683449</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -4280,17 +4264,17 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>1786297676</t>
+          <t>1786301216</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>1786303800</t>
+          <t>1786298400</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>64.696685</t>
+          <t>46.920821</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
@@ -4307,7 +4291,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0xfccc36b3cd4c4e2276a7540f5bb389b40f91c9998d31903af7864027f93d335e</t>
+          <t>0xc72322e8ff04e28165d90bbcfa3c4b34aa19dd5fc1215e13ba7e1ce6362a9292</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4322,12 +4306,12 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>56.81</t>
+          <t>7.93</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>1.3588</t>
+          <t>1.4263</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -4337,7 +4321,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Tie</t>
+          <t>Racing de Cordoba</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -4347,27 +4331,27 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>CA Los Andes vs Ferro Carril Oeste</t>
+          <t>Racing de Cordoba vs San Miguel</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>CA Los Andes</t>
+          <t>Racing de Cordoba</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>0x834e52f6ff115c72424372c131d41b8d94cffe6e0131918e3f85e2146509d14b</t>
+          <t>0x48447168804e92d195e0c849cfb7ae548e076f102e1005f3756585b3d18ea65c</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>L19659153</t>
+          <t>L19683501</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -4392,17 +4376,17 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>1786297373</t>
+          <t>1786301162</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>1786296600</t>
+          <t>1786302000</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>158.355401</t>
+          <t>18.604106</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
@@ -4419,31 +4403,39 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0x48c1aed95e65b653ffb51380d6066948766a0030b4adf3bf05d152a5766c29cf</t>
+          <t>0xd37a1d074e8819ce033a62d6fe3bb026c46529f33aed65aaac63e3d53cb8ce3e</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr"/>
+          <t>0x5022174051792ac42d3af7Ff6bC9cf78a6aE3f32</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>1.6425</t>
+          <t>1.4287</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr"/>
+          <t>Under/Over (0.5)</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Over 0.5</t>
+        </is>
+      </c>
       <c r="H38" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -4451,27 +4443,27 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Colon de Santa Fe vs San Telmo</t>
+          <t>Atlanta vs Temperley</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Colon de Santa Fe</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>0x79905ae58e04af69981e4a95c3d57b98dc3c1dd1d3e7aeb4e6a7640714001f3b</t>
+          <t>0x84c2bb083fa51c1fc591f5ac9524e09d26434823e44ca466e2af8bd17ae651cb</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>L19683494</t>
+          <t>L19683448</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -4496,17 +4488,17 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>1786293588</t>
+          <t>1786300699</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>1786300200</t>
+          <t>1786294800</t>
         </is>
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>15.564202</t>
+          <t>11.661808</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
@@ -4523,28 +4515,28 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0x3d4ee2d1cf7066373ffe56d01727fc04ce4ae0e1203194a2877d6ba90d9d4fcb</t>
+          <t>0x0199716d54c5764cbf1a6783da6c106cf378f2c6b96892a13d7019f5cb41b3fa</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr">
         <is>
-          <t>16.53143</t>
+          <t>16.84</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>1.3438</t>
+          <t>1.1262</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Primera Nacional</t>
+          <t>Under/Over (0.5)</t>
         </is>
       </c>
       <c r="G39" t="inlineStr"/>
@@ -4555,27 +4547,27 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Atlanta vs Temperley</t>
+          <t>Godoy Cruz vs Chaco For Ever</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>0xc67c753c7ce425d2b225c54e0abf1308c3593fa6789a95fd59198b3a0f7a3ddd</t>
+          <t>0x9c696117152178b9240c2e3eddca6b53432d4a4937a20042677cd1f666604f23</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>L19683448</t>
+          <t>L19683484</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -4600,17 +4592,17 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>1786293565</t>
+          <t>1786300516</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>1786294800</t>
+          <t>1786303800</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>48.091433</t>
+          <t>133.386139</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
@@ -4627,23 +4619,23 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0x5decd74680fc49716c54620aa922234edac874fb77b6369067e932fb5a40aed8</t>
+          <t>0x84f162af96f80a1f61f37a3b12a3dab48dcffde9bd10d0cea022df759f18111f</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr">
         <is>
-          <t>16.98847</t>
+          <t>36.84547</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.1362</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -4659,27 +4651,27 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>San Martin Tucuman vs San Martín de San Juan</t>
+          <t>Colon de Santa Fe vs San Telmo</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>San Martin Tucuman</t>
+          <t>Colon de Santa Fe</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>San Martín de San Juan</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>0x4f02331cd42a68f65ea16d62aac0c6b123d9400d12a4d556f3a72df894da02fb</t>
+          <t>0xbca9ed7d23a7df6c8ab98ab2ffc6649f2d4bd3d9007bd0ecf103e453c87addac</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>L19682528</t>
+          <t>L19683494</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -4704,17 +4696,17 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>1786293511</t>
+          <t>1786300513</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>1786309200</t>
+          <t>1786300200</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>48.538486</t>
+          <t>270.425468</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
@@ -4731,31 +4723,39 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0x6376c34d63b4968409b909753114511b32d1413abbfce5d71dcd6fa7bb384028</t>
+          <t>0x2f3773fa15124937ec4965274c782b70d022a4fb2a2c8e85fe36a66e0dcc1a53</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr"/>
+          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>30.89</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>1.6425</t>
+          <t>1.2563</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>San Miguel</t>
+        </is>
+      </c>
       <c r="H41" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -4763,27 +4763,27 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Colon de Santa Fe vs San Telmo</t>
+          <t>Racing de Cordoba vs San Miguel</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Colon de Santa Fe</t>
+          <t>Racing de Cordoba</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>0x79905ae58e04af69981e4a95c3d57b98dc3c1dd1d3e7aeb4e6a7640714001f3b</t>
+          <t>0x8ddab476b71709486e3a0e2118fafcb483076bd09c1c25dcce66244486fed688</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>L19683494</t>
+          <t>L19683501</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -4808,17 +4808,17 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>1786293434</t>
+          <t>1786300245</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>1786300200</t>
+          <t>1786302000</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>48.077821</t>
+          <t>3.902439</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
@@ -4835,7 +4835,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0xa534180ddbde4d456a67f71365d2341259c4ca0b20e45041701c1d345202335e</t>
+          <t>0x4334abae5afdbf026c92af25200b83381434248bdfca39224de3957cba46f6e4</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4843,23 +4843,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr"/>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>13.52</t>
+          <t>52.38</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>1.6325</t>
+          <t>1.675</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr"/>
+          <t>Primera Nacional</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>CA Colegiales 0</t>
+        </is>
+      </c>
       <c r="H42" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -4867,27 +4875,27 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Quilmes vs Club Almagro</t>
+          <t>CA Colegiales vs Patronato</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>CA Colegiales</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>Club Almagro</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>0x86a790846c1cb1bed065ac37c41b727461e30e0a9e0f9e2370ef61f6213ed31f</t>
+          <t>0x3fa48fbf2a59e0b45def889e06df3d2da646e9465f9af4f1b88581fea7fb4496</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>L19683499</t>
+          <t>L19683449</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -4912,17 +4920,17 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>1786293430</t>
+          <t>1786300042</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>1786305600</t>
+          <t>1786298400</t>
         </is>
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>21.375494</t>
+          <t>77.6</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
@@ -4939,7 +4947,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0xe6cbce05bf55e4a2647eb39e1cb6d7afdafec60905e09f42fb3552a02a5fcbd6</t>
+          <t>0xad7255fad3f7d526c2f80d7968fa11121b17d106e3df35095d9b411cead706b0</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4947,23 +4955,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr"/>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>16.88999</t>
+          <t>3.02932</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>1.6325</t>
+          <t>1.2325</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>San Miguel</t>
+        </is>
+      </c>
       <c r="H43" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -4971,27 +4987,27 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Quilmes vs Club Almagro</t>
+          <t>Racing de Cordoba vs San Miguel</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Racing de Cordoba</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>Club Almagro</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>0x86a790846c1cb1bed065ac37c41b727461e30e0a9e0f9e2370ef61f6213ed31f</t>
+          <t>0x8ddab476b71709486e3a0e2118fafcb483076bd09c1c25dcce66244486fed688</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>L19683499</t>
+          <t>L19683501</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -5016,17 +5032,17 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>1786293428</t>
+          <t>1786298930</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>1786305600</t>
+          <t>1786302000</t>
         </is>
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>26.703542</t>
+          <t>13.029333</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
@@ -5043,7 +5059,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0xae3b69e222676c5f5930a25ee6fc677945888fbd4b45894897e8c0b45b324e25</t>
+          <t>0x972e5a678ec56c15f03cbf0d14d7070ad000111adf76887dc34cc27780792e32</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5054,17 +5070,17 @@
       <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr">
         <is>
-          <t>12.72</t>
+          <t>24.07997</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>1.4512</t>
+          <t>1.8675</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G44" t="inlineStr"/>
@@ -5075,27 +5091,27 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>CA Los Andes vs Ferro Carril Oeste</t>
+          <t>Godoy Cruz vs Chaco For Ever</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>CA Los Andes</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>0x555a8472fba9017aa83a61e5e7cf7b05dc2822d1d1cc6174412760fc412637f7</t>
+          <t>0x9c19e4c1fd9646506f8ea14e2b1be19b49a5ab4dc1a7bf40167705a4ae2b338b</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>L19659153</t>
+          <t>L19683484</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -5120,17 +5136,17 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>1786288547</t>
+          <t>1786297771</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>1786296600</t>
+          <t>1786303800</t>
         </is>
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>28.188366</t>
+          <t>27.75789</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
@@ -5147,31 +5163,39 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0x4bb954aaa9ecad68c0eb53f2341bb75f7b8daa072a3f151571ab136be22b78df</t>
+          <t>0x1da1f134f1ec859a8260a79216b9030b9f0b715d9a51d09741ff884111dcde2b</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>0x71CE4A2C734a76f4C86A0D80122C4014c1F52F6e</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr"/>
+          <t>0x311AE302984D8b1cf53D6bfB0a6672f05c423AE6</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>29.37999</t>
+          <t>37.76669</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>1.6113</t>
+          <t>1.5837</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr"/>
+          <t>Asian Handicap (-0.5)</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Godoy Cruz -0.5</t>
+        </is>
+      </c>
       <c r="H45" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -5179,27 +5203,27 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>CA Los Andes vs Ferro Carril Oeste</t>
+          <t>Godoy Cruz vs Chaco For Ever</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>CA Los Andes</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>0x653af58a9c77cb072171a76bcd9ca8adee427601f3ecd186c8154c81f8736395</t>
+          <t>0xb2c04ce7cffc1005eb6199d3c34d31b109e8af04a357b4f8eb9f6b8362ba33c2</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>L19659153</t>
+          <t>L19683484</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -5224,17 +5248,17 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>1786288517</t>
+          <t>1786297676</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>1786296600</t>
+          <t>1786303800</t>
         </is>
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>48.065423</t>
+          <t>64.696685</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
@@ -5251,7 +5275,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0xd5a2ddd8c8b6cc9bdb1c507276d3a192a5f24d46e2d3c01bfb07011263030bdd</t>
+          <t>0xfccc36b3cd4c4e2276a7540f5bb389b40f91c9998d31903af7864027f93d335e</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5259,23 +5283,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr"/>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>5.67</t>
+          <t>56.81</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>1.2975</t>
+          <t>1.3588</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Primera Nacional</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H46" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -5283,27 +5315,27 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>CA Colegiales vs Patronato</t>
+          <t>CA Los Andes vs Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>CA Colegiales</t>
+          <t>CA Los Andes</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>0x710e5bf3f6759bd93c59fc8788916c16c7302071968dfba2d053e2d10f7858bf</t>
+          <t>0x834e52f6ff115c72424372c131d41b8d94cffe6e0131918e3f85e2146509d14b</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>L19683449</t>
+          <t>L19659153</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -5328,17 +5360,17 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>1786288450</t>
+          <t>1786297373</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>1786298400</t>
+          <t>1786296600</t>
         </is>
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>19.058824</t>
+          <t>158.355401</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
@@ -5355,7 +5387,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0xad9f4feea88f83ae2e46756e7d54faa300a82e055c196c70c84019780ecb560c</t>
+          <t>0x48c1aed95e65b653ffb51380d6066948766a0030b4adf3bf05d152a5766c29cf</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5366,17 +5398,17 @@
       <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr">
         <is>
-          <t>21.69</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>1.4512</t>
+          <t>1.6425</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
+          <t>Asian Handicap (-1.5)</t>
         </is>
       </c>
       <c r="G47" t="inlineStr"/>
@@ -5387,27 +5419,27 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>CA Los Andes vs Ferro Carril Oeste</t>
+          <t>Colon de Santa Fe vs San Telmo</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>CA Los Andes</t>
+          <t>Colon de Santa Fe</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>0x555a8472fba9017aa83a61e5e7cf7b05dc2822d1d1cc6174412760fc412637f7</t>
+          <t>0x79905ae58e04af69981e4a95c3d57b98dc3c1dd1d3e7aeb4e6a7640714001f3b</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>L19659153</t>
+          <t>L19683494</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -5432,17 +5464,17 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>1786288436</t>
+          <t>1786293588</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>1786296600</t>
+          <t>1786300200</t>
         </is>
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>48.066482</t>
+          <t>15.564202</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
@@ -5459,28 +5491,28 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0x168e5ea2716a187c94a1c77c4c8b2523b31163ed118e4986c68c79a21d013932</t>
+          <t>0x3d4ee2d1cf7066373ffe56d01727fc04ce4ae0e1203194a2877d6ba90d9d4fcb</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr">
         <is>
-          <t>29.38716</t>
+          <t>16.53143</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>1.6113</t>
+          <t>1.3438</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
+          <t>Primera Nacional</t>
         </is>
       </c>
       <c r="G48" t="inlineStr"/>
@@ -5491,27 +5523,27 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>CA Los Andes vs Ferro Carril Oeste</t>
+          <t>Atlanta vs Temperley</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>CA Los Andes</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>0x653af58a9c77cb072171a76bcd9ca8adee427601f3ecd186c8154c81f8736395</t>
+          <t>0xc67c753c7ce425d2b225c54e0abf1308c3593fa6789a95fd59198b3a0f7a3ddd</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>L19659153</t>
+          <t>L19683448</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -5536,17 +5568,17 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>1786288436</t>
+          <t>1786293565</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>1786296600</t>
+          <t>1786294800</t>
         </is>
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>48.077153</t>
+          <t>48.091433</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
@@ -5563,39 +5595,31 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0x680d5db234b802aa2845f16e9d23d635dd89870065c6bfb6f6f1bde25c321bae</t>
+          <t>0x5decd74680fc49716c54620aa922234edac874fb77b6369067e932fb5a40aed8</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr">
         <is>
-          <t>24.36</t>
+          <t>16.98847</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>1.475</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>CA Colegiales -0.5</t>
-        </is>
-      </c>
+          <t>Primera Nacional</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -5603,27 +5627,27 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>CA Colegiales vs Patronato</t>
+          <t>San Martin Tucuman vs San Martín de San Juan</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>CA Colegiales</t>
+          <t>San Martin Tucuman</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>San Martín de San Juan</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>0x50a3f0e4e982cdda0b9c4b9e2e1c50c67d93fbf7a068b43dbdf733c0b8d09050</t>
+          <t>0x4f02331cd42a68f65ea16d62aac0c6b123d9400d12a4d556f3a72df894da02fb</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>L19683449</t>
+          <t>L19682528</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -5648,17 +5672,17 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>1786287181</t>
+          <t>1786293511</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>1786298400</t>
+          <t>1786309200</t>
         </is>
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>51.284211</t>
+          <t>48.538486</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
@@ -5675,7 +5699,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0x5a5b6f41ac2a593747a9419c020abd417423350c2cf0a14d8cb9ef8a25d04f18</t>
+          <t>0x6376c34d63b4968409b909753114511b32d1413abbfce5d71dcd6fa7bb384028</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5686,17 +5710,17 @@
       <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr">
         <is>
-          <t>8.81755</t>
+          <t>30.89</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>1.6325</t>
+          <t>1.6425</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>Asian Handicap (-1.5)</t>
         </is>
       </c>
       <c r="G50" t="inlineStr"/>
@@ -5707,27 +5731,27 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Quilmes vs Club Almagro</t>
+          <t>Colon de Santa Fe vs San Telmo</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Colon de Santa Fe</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>Club Almagro</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>0x86a790846c1cb1bed065ac37c41b727461e30e0a9e0f9e2370ef61f6213ed31f</t>
+          <t>0x79905ae58e04af69981e4a95c3d57b98dc3c1dd1d3e7aeb4e6a7640714001f3b</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>L19683499</t>
+          <t>L19683494</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -5752,17 +5776,17 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>1786284071</t>
+          <t>1786293434</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>1786305600</t>
+          <t>1786300200</t>
         </is>
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>13.940791</t>
+          <t>48.077821</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
@@ -5779,7 +5803,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0x9ae6e679c8fc9ed20977676ba3160d389287dd8808ea2610d0f168f9c3a42c11</t>
+          <t>0xa534180ddbde4d456a67f71365d2341259c4ca0b20e45041701c1d345202335e</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5790,7 +5814,7 @@
       <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr">
         <is>
-          <t>21.58999</t>
+          <t>13.52</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -5856,7 +5880,7 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>1786284003</t>
+          <t>1786293430</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
@@ -5866,7 +5890,7 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>34.134372</t>
+          <t>21.375494</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
@@ -5883,7 +5907,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0x6771b333646b031b4dc4cfea8f533b040a6ed0a66012cdc416a7aaa5b89f7988</t>
+          <t>0xe6cbce05bf55e4a2647eb39e1cb6d7afdafec60905e09f42fb3552a02a5fcbd6</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5894,17 +5918,17 @@
       <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr">
         <is>
-          <t>19.2</t>
+          <t>16.88999</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>1.5425</t>
+          <t>1.6325</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G52" t="inlineStr"/>
@@ -5915,27 +5939,27 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Colon de Santa Fe vs San Telmo</t>
+          <t>Quilmes vs Club Almagro</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Colon de Santa Fe</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Club Almagro</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>0x4b323aab38dd8f5096dcd1965ce7dc05c69ab73371e55e810b7a5aee356bf244</t>
+          <t>0x86a790846c1cb1bed065ac37c41b727461e30e0a9e0f9e2370ef61f6213ed31f</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>L19683494</t>
+          <t>L19683499</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -5960,17 +5984,17 @@
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>1786283290</t>
+          <t>1786293428</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>1786300200</t>
+          <t>1786305600</t>
         </is>
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>35.391705</t>
+          <t>26.703542</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
@@ -5987,7 +6011,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0x8809f3e942a9cc8dca00d48b07cfe53a328d6ba2b60742c63e144e3d8cf2eaa1</t>
+          <t>0xae3b69e222676c5f5930a25ee6fc677945888fbd4b45894897e8c0b45b324e25</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5998,17 +6022,17 @@
       <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr">
         <is>
-          <t>23.25749</t>
+          <t>12.72</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>1.4838</t>
+          <t>1.4512</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
+          <t>Under/Over (1.5)</t>
         </is>
       </c>
       <c r="G53" t="inlineStr"/>
@@ -6019,27 +6043,27 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Colon de Santa Fe vs San Telmo</t>
+          <t>CA Los Andes vs Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Colon de Santa Fe</t>
+          <t>CA Los Andes</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>0xc91217dfcd3944893195656945526d39efcd315aa93101aa312de5303c04d446</t>
+          <t>0x555a8472fba9017aa83a61e5e7cf7b05dc2822d1d1cc6174412760fc412637f7</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>L19683494</t>
+          <t>L19659153</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -6064,17 +6088,17 @@
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>1786281248</t>
+          <t>1786288547</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>1786300200</t>
+          <t>1786296600</t>
         </is>
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>48.077499</t>
+          <t>28.188366</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
@@ -6091,23 +6115,23 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0xe5b95b7ede820952a7e6f5c1b2139a8092b51c4de75567f117f1291461ec6fbe</t>
+          <t>0x4bb954aaa9ecad68c0eb53f2341bb75f7b8daa072a3f151571ab136be22b78df</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x71CE4A2C734a76f4C86A0D80122C4014c1F52F6e</t>
         </is>
       </c>
       <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr">
         <is>
-          <t>23.55844</t>
+          <t>29.37999</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.6113</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -6123,27 +6147,27 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Colon de Santa Fe vs San Telmo</t>
+          <t>CA Los Andes vs Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Colon de Santa Fe</t>
+          <t>CA Los Andes</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>0xc91217dfcd3944893195656945526d39efcd315aa93101aa312de5303c04d446</t>
+          <t>0x653af58a9c77cb072171a76bcd9ca8adee427601f3ecd186c8154c81f8736395</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>L19683494</t>
+          <t>L19659153</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -6168,17 +6192,17 @@
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>1786281243</t>
+          <t>1786288517</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>1786300200</t>
+          <t>1786296600</t>
         </is>
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>48.078449</t>
+          <t>48.065423</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
@@ -6195,7 +6219,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0x4d872ac34cfff98634d3d50362fe725a3f4ea55d64ddd9e3d7d811b073f350ab</t>
+          <t>0xd5a2ddd8c8b6cc9bdb1c507276d3a192a5f24d46e2d3c01bfb07011263030bdd</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -6206,17 +6230,17 @@
       <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr">
         <is>
-          <t>17.30813</t>
+          <t>5.67</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.2975</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
+          <t>Primera Nacional</t>
         </is>
       </c>
       <c r="G55" t="inlineStr"/>
@@ -6227,27 +6251,27 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Colon de Santa Fe vs San Telmo</t>
+          <t>CA Colegiales vs Patronato</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Colon de Santa Fe</t>
+          <t>CA Colegiales</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>0xd638a8ee6393f88ca538cc4fe6ac8cdf722bcfe6277a5ebd9387222eade88ba3</t>
+          <t>0x710e5bf3f6759bd93c59fc8788916c16c7302071968dfba2d053e2d10f7858bf</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>L19683494</t>
+          <t>L19683449</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -6272,17 +6296,17 @@
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>1786281243</t>
+          <t>1786288450</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>1786300200</t>
+          <t>1786298400</t>
         </is>
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>48.078139</t>
+          <t>19.058824</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
@@ -6299,7 +6323,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0x8f782cb5f7b30f6c129f6031ec6368ed75ea36897066f1761d9054013f56567d</t>
+          <t>0xad9f4feea88f83ae2e46756e7d54faa300a82e055c196c70c84019780ecb560c</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -6310,17 +6334,17 @@
       <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>21.69</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>1.4187</t>
+          <t>1.4512</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Primera Nacional</t>
+          <t>Under/Over (1.5)</t>
         </is>
       </c>
       <c r="G56" t="inlineStr"/>
@@ -6331,27 +6355,27 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Club Atletico Mitre de Santiago del Estero vs Defensores de Belgrano Buenos Aires</t>
+          <t>CA Los Andes vs Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Club Atletico Mitre de Santiago del Estero</t>
+          <t>CA Los Andes</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano Buenos Aires</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>0x2d371e1a8a9d98624f046ea3d7126e47308ffbc183b66b1e2fba81e5ae69d7dd</t>
+          <t>0x555a8472fba9017aa83a61e5e7cf7b05dc2822d1d1cc6174412760fc412637f7</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>L19683493</t>
+          <t>L19659153</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -6376,17 +6400,17 @@
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>1786280425</t>
+          <t>1786288436</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>1786302000</t>
+          <t>1786296600</t>
         </is>
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>23.880597</t>
+          <t>48.066482</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
@@ -6403,7 +6427,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>0xfe8890b155a19f7eb888456b555a7a6d8c293f8ecabeb69d2abd10210f520589</t>
+          <t>0x168e5ea2716a187c94a1c77c4c8b2523b31163ed118e4986c68c79a21d013932</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -6414,12 +6438,12 @@
       <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>29.38716</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>1.4475</t>
+          <t>1.6113</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -6435,27 +6459,27 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Colon de Santa Fe vs San Telmo</t>
+          <t>CA Los Andes vs Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>Colon de Santa Fe</t>
+          <t>CA Los Andes</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>0xc91217dfcd3944893195656945526d39efcd315aa93101aa312de5303c04d446</t>
+          <t>0x653af58a9c77cb072171a76bcd9ca8adee427601f3ecd186c8154c81f8736395</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>L19683494</t>
+          <t>L19659153</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -6480,17 +6504,17 @@
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>1786280403</t>
+          <t>1786288436</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>1786300200</t>
+          <t>1786296600</t>
         </is>
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>22.346369</t>
+          <t>48.077153</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
@@ -6507,12 +6531,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>0x60e023296ac2f9f58237fa345b3aa08fb4f997dd34c5384f371782bf7bbd5a40</t>
+          <t>0x680d5db234b802aa2845f16e9d23d635dd89870065c6bfb6f6f1bde25c321bae</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -6522,22 +6546,22 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>26.11999</t>
+          <t>24.36</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>1.5488</t>
+          <t>1.475</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
+          <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Over 2.0</t>
+          <t>CA Colegiales -0.5</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -6547,27 +6571,27 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Colon de Santa Fe vs San Telmo</t>
+          <t>CA Colegiales vs Patronato</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>Colon de Santa Fe</t>
+          <t>CA Colegiales</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>0xc91217dfcd3944893195656945526d39efcd315aa93101aa312de5303c04d446</t>
+          <t>0x50a3f0e4e982cdda0b9c4b9e2e1c50c67d93fbf7a068b43dbdf733c0b8d09050</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>L19683494</t>
+          <t>L19683449</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -6592,17 +6616,17 @@
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>1786280403</t>
+          <t>1786287181</t>
         </is>
       </c>
       <c r="S58" t="inlineStr">
         <is>
-          <t>1786300200</t>
+          <t>1786298400</t>
         </is>
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>47.599071</t>
+          <t>51.284211</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
@@ -6619,7 +6643,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>0x2d118800c100a2a41a19c2053cbf355561a08867f99163fb40955a4ab012ce39</t>
+          <t>0x5a5b6f41ac2a593747a9419c020abd417423350c2cf0a14d8cb9ef8a25d04f18</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6630,17 +6654,17 @@
       <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr">
         <is>
-          <t>20.07999</t>
+          <t>8.81755</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>1.7363</t>
+          <t>1.6325</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G59" t="inlineStr"/>
@@ -6651,27 +6675,27 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Godoy Cruz vs Chaco For Ever</t>
+          <t>Quilmes vs Club Almagro</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Club Almagro</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>0x60e111ebf03c4965ff049e67cf10f93f5cca143023c6104aab59162863b5b8a8</t>
+          <t>0x86a790846c1cb1bed065ac37c41b727461e30e0a9e0f9e2370ef61f6213ed31f</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>L19683484</t>
+          <t>L19683499</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -6696,17 +6720,17 @@
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>1786279900</t>
+          <t>1786284071</t>
         </is>
       </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t>1786303800</t>
+          <t>1786305600</t>
         </is>
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>27.273331</t>
+          <t>13.940791</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
@@ -6723,7 +6747,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>0x904e2e53a604aa6663de774d4bd9ddf8af7459ef1c4fa1bb14486300917ac211</t>
+          <t>0x9ae6e679c8fc9ed20977676ba3160d389287dd8808ea2610d0f168f9c3a42c11</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6731,31 +6755,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C60" t="inlineStr"/>
       <c r="D60" t="inlineStr">
         <is>
-          <t>3.96</t>
+          <t>21.58999</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>1.2837</t>
+          <t>1.6325</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr"/>
       <c r="H60" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -6763,27 +6779,27 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Godoy Cruz vs Chaco For Ever</t>
+          <t>Quilmes vs Club Almagro</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Club Almagro</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>0x08dce15d4ca4845359c2f121bce305fd3a0fe7422d497000c713e29463c6be79</t>
+          <t>0x86a790846c1cb1bed065ac37c41b727461e30e0a9e0f9e2370ef61f6213ed31f</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>L19683484</t>
+          <t>L19683499</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
@@ -6808,17 +6824,17 @@
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>1786279851</t>
+          <t>1786284003</t>
         </is>
       </c>
       <c r="S60" t="inlineStr">
         <is>
-          <t>1786303800</t>
+          <t>1786305600</t>
         </is>
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>13.955947</t>
+          <t>34.134372</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
@@ -6835,7 +6851,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>0x19a6c0536a5dea88055519ff16050cdde80d42121bb75c5045e3b562a7c1d4bb</t>
+          <t>0x6771b333646b031b4dc4cfea8f533b040a6ed0a66012cdc416a7aaa5b89f7988</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6846,17 +6862,17 @@
       <c r="C61" t="inlineStr"/>
       <c r="D61" t="inlineStr">
         <is>
-          <t>7.50547</t>
+          <t>19.2</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>1.4287</t>
+          <t>1.5425</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G61" t="inlineStr"/>
@@ -6867,27 +6883,27 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Godoy Cruz vs Chaco For Ever</t>
+          <t>Colon de Santa Fe vs San Telmo</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Colon de Santa Fe</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>0xa5f02d0d08d0dcc4818948397f0f26c77f90b87182cec4d62ab01f77352671a1</t>
+          <t>0x4b323aab38dd8f5096dcd1965ce7dc05c69ab73371e55e810b7a5aee356bf244</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>L19683484</t>
+          <t>L19683494</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
@@ -6912,17 +6928,17 @@
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>1786279821</t>
+          <t>1786283290</t>
         </is>
       </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t>1786303800</t>
+          <t>1786300200</t>
         </is>
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>17.505469</t>
+          <t>35.391705</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
@@ -6939,7 +6955,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>0x4c44e2c0c492a5115b342a42a552a040cb800bd582b07c12f1ea9161b861b487</t>
+          <t>0x8809f3e942a9cc8dca00d48b07cfe53a328d6ba2b60742c63e144e3d8cf2eaa1</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6950,12 +6966,12 @@
       <c r="C62" t="inlineStr"/>
       <c r="D62" t="inlineStr">
         <is>
-          <t>11.30844</t>
+          <t>23.25749</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.4838</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -6971,27 +6987,27 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Deportivo Moron vs Acassuso</t>
+          <t>Colon de Santa Fe vs San Telmo</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>Deportivo Moron</t>
+          <t>Colon de Santa Fe</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>0x108eaba0441fb45ec8e0073e945ae0ac1e138c933e4f2839816cd3198d7dd4d2</t>
+          <t>0xc91217dfcd3944893195656945526d39efcd315aa93101aa312de5303c04d446</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>L19683452</t>
+          <t>L19683494</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
@@ -7016,17 +7032,17 @@
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>1786278950</t>
+          <t>1786281248</t>
         </is>
       </c>
       <c r="S62" t="inlineStr">
         <is>
-          <t>1786298400</t>
+          <t>1786300200</t>
         </is>
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>23.078449</t>
+          <t>48.077499</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
@@ -7043,7 +7059,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>0x5a5ccf0d5f6cbac6813d25e4e1e96b25b5c5a4ff8f6378d7e69d6bd3c29295ae</t>
+          <t>0xe5b95b7ede820952a7e6f5c1b2139a8092b51c4de75567f117f1291461ec6fbe</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -7054,7 +7070,7 @@
       <c r="C63" t="inlineStr"/>
       <c r="D63" t="inlineStr">
         <is>
-          <t>12.25</t>
+          <t>23.55844</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -7075,27 +7091,27 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Deportivo Moron vs Acassuso</t>
+          <t>Colon de Santa Fe vs San Telmo</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>Deportivo Moron</t>
+          <t>Colon de Santa Fe</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>0x108eaba0441fb45ec8e0073e945ae0ac1e138c933e4f2839816cd3198d7dd4d2</t>
+          <t>0xc91217dfcd3944893195656945526d39efcd315aa93101aa312de5303c04d446</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>L19683452</t>
+          <t>L19683494</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
@@ -7120,17 +7136,17 @@
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>1786278094</t>
+          <t>1786281243</t>
         </is>
       </c>
       <c r="S63" t="inlineStr">
         <is>
-          <t>1786298400</t>
+          <t>1786300200</t>
         </is>
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>48.078449</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
@@ -7147,7 +7163,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>0x5f3419242a87ff17c0cb508ade95d27a54429124d36280a1dff2efa2fa0b3510</t>
+          <t>0x4d872ac34cfff98634d3d50362fe725a3f4ea55d64ddd9e3d7d811b073f350ab</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -7158,17 +7174,17 @@
       <c r="C64" t="inlineStr"/>
       <c r="D64" t="inlineStr">
         <is>
-          <t>20.41999</t>
+          <t>17.30813</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>1.7087</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (1.5)</t>
         </is>
       </c>
       <c r="G64" t="inlineStr"/>
@@ -7179,27 +7195,27 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>CA Los Andes vs Ferro Carril Oeste</t>
+          <t>Colon de Santa Fe vs San Telmo</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>CA Los Andes</t>
+          <t>Colon de Santa Fe</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>0x31115553050eabb8d3f6a72cf2865c16175783383dcfc674615e74ed88cabaee</t>
+          <t>0xd638a8ee6393f88ca538cc4fe6ac8cdf722bcfe6277a5ebd9387222eade88ba3</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>L19659153</t>
+          <t>L19683494</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
@@ -7224,17 +7240,17 @@
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>1786277884</t>
+          <t>1786281243</t>
         </is>
       </c>
       <c r="S64" t="inlineStr">
         <is>
-          <t>1786296600</t>
+          <t>1786300200</t>
         </is>
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>28.811273</t>
+          <t>48.078139</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
@@ -7251,7 +7267,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>0xe6b14424302d9ef7ea2000cef83e38549f6a38c12d57faa6dd76dd84e631a5ca</t>
+          <t>0x8f782cb5f7b30f6c129f6031ec6368ed75ea36897066f1761d9054013f56567d</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -7262,17 +7278,17 @@
       <c r="C65" t="inlineStr"/>
       <c r="D65" t="inlineStr">
         <is>
-          <t>12.13</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>1.3613</t>
+          <t>1.4187</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
+          <t>Primera Nacional</t>
         </is>
       </c>
       <c r="G65" t="inlineStr"/>
@@ -7283,27 +7299,27 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Deportivo Moron vs Acassuso</t>
+          <t>Club Atletico Mitre de Santiago del Estero vs Defensores de Belgrano Buenos Aires</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>Deportivo Moron</t>
+          <t>Club Atletico Mitre de Santiago del Estero</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Defensores de Belgrano Buenos Aires</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>0x3f34d112cfb9f093c57a3e094be078f9eea2715f97797e20d86942d58f5cc8d6</t>
+          <t>0x2d371e1a8a9d98624f046ea3d7126e47308ffbc183b66b1e2fba81e5ae69d7dd</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>L19683452</t>
+          <t>L19683493</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
@@ -7328,17 +7344,17 @@
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>1786277708</t>
+          <t>1786280425</t>
         </is>
       </c>
       <c r="S65" t="inlineStr">
         <is>
-          <t>1786298400</t>
+          <t>1786302000</t>
         </is>
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>33.577855</t>
+          <t>23.880597</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
@@ -7355,7 +7371,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>0xd7a2e43ba1564f619200938b384123dd68adb783742fc7b32ee335ee489d1302</t>
+          <t>0xfe8890b155a19f7eb888456b555a7a6d8c293f8ecabeb69d2abd10210f520589</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -7366,12 +7382,12 @@
       <c r="C66" t="inlineStr"/>
       <c r="D66" t="inlineStr">
         <is>
-          <t>10.58</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>1.485</t>
+          <t>1.4475</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -7387,27 +7403,27 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Deportivo Moron vs Acassuso</t>
+          <t>Colon de Santa Fe vs San Telmo</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Deportivo Moron</t>
+          <t>Colon de Santa Fe</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>0x108eaba0441fb45ec8e0073e945ae0ac1e138c933e4f2839816cd3198d7dd4d2</t>
+          <t>0xc91217dfcd3944893195656945526d39efcd315aa93101aa312de5303c04d446</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>L19683452</t>
+          <t>L19683494</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
@@ -7432,17 +7448,17 @@
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>1786277679</t>
+          <t>1786280403</t>
         </is>
       </c>
       <c r="S66" t="inlineStr">
         <is>
-          <t>1786298400</t>
+          <t>1786300200</t>
         </is>
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>21.814433</t>
+          <t>22.346369</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
@@ -7459,7 +7475,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>0xb25fa423ffb1a1464f100f2a2e9a1beac36661b9e37c8b09ecc7d3fd5a80312f</t>
+          <t>0x60e023296ac2f9f58237fa345b3aa08fb4f997dd34c5384f371782bf7bbd5a40</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -7467,15 +7483,19 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr"/>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>25.88</t>
+          <t>26.11999</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>1.6038</t>
+          <t>1.5488</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -7483,7 +7503,11 @@
           <t>Under/Over (2)</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr"/>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Over 2.0</t>
+        </is>
+      </c>
       <c r="H67" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -7491,27 +7515,27 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>CA Colegiales vs Patronato</t>
+          <t>Colon de Santa Fe vs San Telmo</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>CA Colegiales</t>
+          <t>Colon de Santa Fe</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>0x18dd2fdd93f5029a20e6a76c47c4f0e5c3c25768ad7f1b46a833287f8b7fcc13</t>
+          <t>0xc91217dfcd3944893195656945526d39efcd315aa93101aa312de5303c04d446</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>L19683449</t>
+          <t>L19683494</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
@@ -7536,17 +7560,17 @@
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>1786277040</t>
+          <t>1786280403</t>
         </is>
       </c>
       <c r="S67" t="inlineStr">
         <is>
-          <t>1786298400</t>
+          <t>1786300200</t>
         </is>
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>42.865424</t>
+          <t>47.599071</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
@@ -7563,7 +7587,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>0xfe815be8a10a6ad2cda012e463a244232a6f6c80544018f6dda52d723946b659</t>
+          <t>0x2d118800c100a2a41a19c2053cbf355561a08867f99163fb40955a4ab012ce39</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -7574,17 +7598,17 @@
       <c r="C68" t="inlineStr"/>
       <c r="D68" t="inlineStr">
         <is>
-          <t>29.02571</t>
+          <t>20.07999</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>1.6038</t>
+          <t>1.7363</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
+          <t>Asian Handicap (-1.5)</t>
         </is>
       </c>
       <c r="G68" t="inlineStr"/>
@@ -7595,27 +7619,27 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>CA Colegiales vs Patronato</t>
+          <t>Godoy Cruz vs Chaco For Ever</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>CA Colegiales</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>0x18dd2fdd93f5029a20e6a76c47c4f0e5c3c25768ad7f1b46a833287f8b7fcc13</t>
+          <t>0x60e111ebf03c4965ff049e67cf10f93f5cca143023c6104aab59162863b5b8a8</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>L19683449</t>
+          <t>L19683484</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
@@ -7640,17 +7664,17 @@
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>1786276809</t>
+          <t>1786279900</t>
         </is>
       </c>
       <c r="S68" t="inlineStr">
         <is>
-          <t>1786298400</t>
+          <t>1786303800</t>
         </is>
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>48.07571</t>
+          <t>27.273331</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
@@ -7667,7 +7691,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>0xdb83c52876b68624e093c25e35d11910f4fbef2394ff947b658f8ea5cdb3fa88</t>
+          <t>0x904e2e53a604aa6663de774d4bd9ddf8af7459ef1c4fa1bb14486300917ac211</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -7675,23 +7699,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C69" t="inlineStr"/>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>16.96</t>
+          <t>3.96</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>1.4463</t>
+          <t>1.2837</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H69" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -7699,27 +7731,27 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>CA Colegiales vs Patronato</t>
+          <t>Godoy Cruz vs Chaco For Ever</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>CA Colegiales</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>0x30a6561de28b35c5bb0557dcbfc7b23e7a62558d3b0f5cfcafb67d7a07e0dd21</t>
+          <t>0x08dce15d4ca4845359c2f121bce305fd3a0fe7422d497000c713e29463c6be79</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>L19683449</t>
+          <t>L19683484</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
@@ -7744,17 +7776,17 @@
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>1786276809</t>
+          <t>1786279851</t>
         </is>
       </c>
       <c r="S69" t="inlineStr">
         <is>
-          <t>1786298400</t>
+          <t>1786303800</t>
         </is>
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>38.005602</t>
+          <t>13.955947</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
@@ -7771,27 +7803,23 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>0x0847a2541998eecfe02d138796b14ef3d6719061787498f4888f6e14c0d196ff</t>
+          <t>0x19a6c0536a5dea88055519ff16050cdde80d42121bb75c5045e3b562a7c1d4bb</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>0xf068eF8DF8f47185D02d59Bb33d9eC7A057a571E</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr"/>
       <c r="D70" t="inlineStr">
         <is>
-          <t>38.54</t>
+          <t>7.50547</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>1.125</t>
+          <t>1.4287</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -7799,11 +7827,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>Club Almagro</t>
-        </is>
-      </c>
+      <c r="G70" t="inlineStr"/>
       <c r="H70" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -7811,27 +7835,27 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Quilmes vs Club Almagro</t>
+          <t>Godoy Cruz vs Chaco For Ever</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>Club Almagro</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>0x03ed0858b563c1becf38b195ad94b1a84eb89c3ca8ca10b1a34220bff142f9b2</t>
+          <t>0xa5f02d0d08d0dcc4818948397f0f26c77f90b87182cec4d62ab01f77352671a1</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>L19683499</t>
+          <t>L19683484</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
@@ -7856,17 +7880,17 @@
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>1786270828</t>
+          <t>1786279821</t>
         </is>
       </c>
       <c r="S70" t="inlineStr">
         <is>
-          <t>1786305600</t>
+          <t>1786303800</t>
         </is>
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>308.32</t>
+          <t>17.505469</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
@@ -7883,7 +7907,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>0x2121e08c4ea1fe2d49a3bb388fba9e232ef9c06335c04e5eae0bf7766975512a</t>
+          <t>0x4c44e2c0c492a5115b342a42a552a040cb800bd582b07c12f1ea9161b861b487</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -7891,31 +7915,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C71" t="inlineStr"/>
       <c r="D71" t="inlineStr">
         <is>
-          <t>30.06</t>
+          <t>11.30844</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>1.6262</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>Colon de Santa Fe</t>
-        </is>
-      </c>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr"/>
       <c r="H71" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -7923,27 +7939,27 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>Colon de Santa Fe vs San Telmo</t>
+          <t>Deportivo Moron vs Acassuso</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>Colon de Santa Fe</t>
+          <t>Deportivo Moron</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>0x1a11ec80edeaae24566c4f4f891cc2afc56b377b24997a6e8ee533eeaaad5c92</t>
+          <t>0x108eaba0441fb45ec8e0073e945ae0ac1e138c933e4f2839816cd3198d7dd4d2</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>L19683494</t>
+          <t>L19683452</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
@@ -7968,17 +7984,17 @@
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>1786253941</t>
+          <t>1786278950</t>
         </is>
       </c>
       <c r="S71" t="inlineStr">
         <is>
-          <t>1786300200</t>
+          <t>1786298400</t>
         </is>
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>48.0</t>
+          <t>23.078449</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
@@ -7995,39 +8011,31 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>0x4e811c319e5e3a1fc1968ce0f31b4c15eb7222daa616252d99f9abc611408746</t>
+          <t>0x5a5ccf0d5f6cbac6813d25e4e1e96b25b5c5a4ff8f6378d7e69d6bd3c29295ae</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>0x155C76202e45BE70c50bfeD7eAeA3B98e7716Ff7</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr"/>
       <c r="D72" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>12.25</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>1.2925</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr"/>
       <c r="H72" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -8035,27 +8043,27 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>Colon de Santa Fe vs San Telmo</t>
+          <t>Deportivo Moron vs Acassuso</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>Colon de Santa Fe</t>
+          <t>Deportivo Moron</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>0x2e49527408facf21253a0a1eafe51280b82e4c31919e91a396332f19ec366401</t>
+          <t>0x108eaba0441fb45ec8e0073e945ae0ac1e138c933e4f2839816cd3198d7dd4d2</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>L19683494</t>
+          <t>L19683452</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
@@ -8080,17 +8088,17 @@
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>1786243741</t>
+          <t>1786278094</t>
         </is>
       </c>
       <c r="S72" t="inlineStr">
         <is>
-          <t>1786300200</t>
+          <t>1786298400</t>
         </is>
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>3.418803</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
@@ -8107,27 +8115,23 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>0xb8631aeb398192a03386505542f05fa15e34db501204baa8745a4d4b5c1651b7</t>
+          <t>0x5f3419242a87ff17c0cb508ade95d27a54429124d36280a1dff2efa2fa0b3510</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>0x155C76202e45BE70c50bfeD7eAeA3B98e7716Ff7</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr"/>
       <c r="D73" t="inlineStr">
         <is>
-          <t>0.99999</t>
+          <t>20.41999</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>1.6538</t>
+          <t>1.7087</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -8135,11 +8139,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>Deportivo Moron</t>
-        </is>
-      </c>
+      <c r="G73" t="inlineStr"/>
       <c r="H73" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -8147,27 +8147,27 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Deportivo Moron vs Acassuso</t>
+          <t>CA Los Andes vs Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>Deportivo Moron</t>
+          <t>CA Los Andes</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>0x7514a255ce41be3c5db9f8849ba04e78dab80f02d1fe78c2aae82bbc843a9745</t>
+          <t>0x31115553050eabb8d3f6a72cf2865c16175783383dcfc674615e74ed88cabaee</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>L19683452</t>
+          <t>L19659153</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
@@ -8192,17 +8192,17 @@
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>1786243225</t>
+          <t>1786277884</t>
         </is>
       </c>
       <c r="S73" t="inlineStr">
         <is>
-          <t>1786298400</t>
+          <t>1786296600</t>
         </is>
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>1.529621</t>
+          <t>28.811273</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
@@ -8219,28 +8219,28 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>0xd3b94d194e43cc84f0a1b82723594ea6689a6aa2a4a7dccbc8a3d19fc321e49b</t>
+          <t>0xe6b14424302d9ef7ea2000cef83e38549f6a38c12d57faa6dd76dd84e631a5ca</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C74" t="inlineStr"/>
       <c r="D74" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>12.13</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>1.5238</t>
+          <t>1.3613</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
+          <t>Under/Over (1.5)</t>
         </is>
       </c>
       <c r="G74" t="inlineStr"/>
@@ -8266,7 +8266,7 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>0x108eaba0441fb45ec8e0073e945ae0ac1e138c933e4f2839816cd3198d7dd4d2</t>
+          <t>0x3f34d112cfb9f093c57a3e094be078f9eea2715f97797e20d86942d58f5cc8d6</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
@@ -8296,7 +8296,7 @@
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>1786225000</t>
+          <t>1786277708</t>
         </is>
       </c>
       <c r="S74" t="inlineStr">
@@ -8306,7 +8306,7 @@
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>1.909308</t>
+          <t>33.577855</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
@@ -8323,39 +8323,31 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>0x86f4b24298f4c19f9f856cb19af2a260f24dc2d391f252248469436057ea1d1a</t>
+          <t>0xd7a2e43ba1564f619200938b384123dd68adb783742fc7b32ee335ee489d1302</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr"/>
       <c r="D75" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10.58</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>1.5263</t>
+          <t>1.485</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>Deportivo Moron -1</t>
-        </is>
-      </c>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr"/>
       <c r="H75" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -8378,7 +8370,7 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>0xb61b063252c01d0525ae633a0276dc1830eabd418482fddec925fcbd602a2a75</t>
+          <t>0x108eaba0441fb45ec8e0073e945ae0ac1e138c933e4f2839816cd3198d7dd4d2</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
@@ -8408,7 +8400,7 @@
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>1786220171</t>
+          <t>1786277679</t>
         </is>
       </c>
       <c r="S75" t="inlineStr">
@@ -8418,7 +8410,7 @@
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>1.900238</t>
+          <t>21.814433</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
@@ -8435,39 +8427,31 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>0x0a5de930b5a6b8aca1699b666034af3891a3aa920021791d6d13e0297fb7903f</t>
+          <t>0xb25fa423ffb1a1464f100f2a2e9a1beac36661b9e37c8b09ecc7d3fd5a80312f</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>0x4a09916b1325Eed50eE8973B13742a205B0B7c7E</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr"/>
       <c r="D76" t="inlineStr">
         <is>
-          <t>49.99999</t>
+          <t>25.88</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>1.6175</t>
+          <t>1.6038</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>Almirante Brown -1</t>
-        </is>
-      </c>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr"/>
       <c r="H76" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -8475,27 +8459,27 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>Almirante Brown vs Ciudad Bolivar</t>
+          <t>CA Colegiales vs Patronato</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>CA Colegiales</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>Ciudad Bolivar</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>0xa6a338c64f062bfd589e8d5d9cea45a27c9e64065f71f800e5966f81ce53c556</t>
+          <t>0x18dd2fdd93f5029a20e6a76c47c4f0e5c3c25768ad7f1b46a833287f8b7fcc13</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>L19683447</t>
+          <t>L19683449</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
@@ -8520,17 +8504,17 @@
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>1786218515</t>
+          <t>1786277040</t>
         </is>
       </c>
       <c r="S76" t="inlineStr">
         <is>
-          <t>1786212000</t>
+          <t>1786298400</t>
         </is>
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>80.971644</t>
+          <t>42.865424</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
@@ -8547,28 +8531,28 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>0x17d5a08f8fa305f31f27442393c64f497dd3893417da6e76c321c4c2a187320d</t>
+          <t>0xfe815be8a10a6ad2cda012e463a244232a6f6c80544018f6dda52d723946b659</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C77" t="inlineStr"/>
       <c r="D77" t="inlineStr">
         <is>
-          <t>49.18897</t>
+          <t>29.02571</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>1.4737</t>
+          <t>1.6038</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Under/Over (2)</t>
         </is>
       </c>
       <c r="G77" t="inlineStr"/>
@@ -8579,27 +8563,27 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Almirante Brown vs Ciudad Bolivar</t>
+          <t>CA Colegiales vs Patronato</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>CA Colegiales</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>Ciudad Bolivar</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>0xa6a338c64f062bfd589e8d5d9cea45a27c9e64065f71f800e5966f81ce53c556</t>
+          <t>0x18dd2fdd93f5029a20e6a76c47c4f0e5c3c25768ad7f1b46a833287f8b7fcc13</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>L19683447</t>
+          <t>L19683449</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
@@ -8624,17 +8608,17 @@
       </c>
       <c r="R77" t="inlineStr">
         <is>
-          <t>1786218084</t>
+          <t>1786276809</t>
         </is>
       </c>
       <c r="S77" t="inlineStr">
         <is>
-          <t>1786212000</t>
+          <t>1786298400</t>
         </is>
       </c>
       <c r="T77" t="inlineStr">
         <is>
-          <t>103.82896</t>
+          <t>48.07571</t>
         </is>
       </c>
       <c r="U77" t="inlineStr">
@@ -8651,23 +8635,23 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>0x56975f372357be259365cb7d2929c88d4fae157eea7a71d53d57cb234834f2ca</t>
+          <t>0xdb83c52876b68624e093c25e35d11910f4fbef2394ff947b658f8ea5cdb3fa88</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C78" t="inlineStr"/>
       <c r="D78" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>16.96</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>1.4812</t>
+          <t>1.4463</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -8683,27 +8667,27 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Club Atletico Mitre de Santiago del Estero vs Defensores de Belgrano Buenos Aires</t>
+          <t>CA Colegiales vs Patronato</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>Club Atletico Mitre de Santiago del Estero</t>
+          <t>CA Colegiales</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano Buenos Aires</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>0xa8ade64a3adb0ea38de67a61105ef31beb490d5a7287715b76ae124536d359cc</t>
+          <t>0x30a6561de28b35c5bb0557dcbfc7b23e7a62558d3b0f5cfcafb67d7a07e0dd21</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>L19683493</t>
+          <t>L19683449</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
@@ -8728,17 +8712,17 @@
       </c>
       <c r="R78" t="inlineStr">
         <is>
-          <t>1786215674</t>
+          <t>1786276809</t>
         </is>
       </c>
       <c r="S78" t="inlineStr">
         <is>
-          <t>1786302000</t>
+          <t>1786298400</t>
         </is>
       </c>
       <c r="T78" t="inlineStr">
         <is>
-          <t>2.077922</t>
+          <t>38.005602</t>
         </is>
       </c>
       <c r="U78" t="inlineStr">
@@ -8755,12 +8739,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>0xff53df1f3446908699196d44fcdb8b39c1bd15c7ed519f0d730e55a51a6eb38f</t>
+          <t>0x0847a2541998eecfe02d138796b14ef3d6719061787498f4888f6e14c0d196ff</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
+          <t>0xf068eF8DF8f47185D02d59Bb33d9eC7A057a571E</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -8770,12 +8754,12 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>38.54</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>1.3713</t>
+          <t>1.125</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -8785,7 +8769,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Club Almagro</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -8795,27 +8779,27 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Almirante Brown vs Ciudad Bolivar</t>
+          <t>Quilmes vs Club Almagro</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>Ciudad Bolivar</t>
+          <t>Club Almagro</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>0x63a8bf73c1084ef223fdd1096dccd16232e7a455fad77f7f0891be1588ebeb88</t>
+          <t>0x03ed0858b563c1becf38b195ad94b1a84eb89c3ca8ca10b1a34220bff142f9b2</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>L19683447</t>
+          <t>L19683499</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
@@ -8840,17 +8824,17 @@
       </c>
       <c r="R79" t="inlineStr">
         <is>
-          <t>1786215673</t>
+          <t>1786270828</t>
         </is>
       </c>
       <c r="S79" t="inlineStr">
         <is>
-          <t>1786212000</t>
+          <t>1786305600</t>
         </is>
       </c>
       <c r="T79" t="inlineStr">
         <is>
-          <t>2.693603</t>
+          <t>308.32</t>
         </is>
       </c>
       <c r="U79" t="inlineStr">
@@ -8867,7 +8851,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>0x249d52552e7acb9f472d2a4c48ab754622ba572903281739a3e10b4d509dccb0</t>
+          <t>0x2121e08c4ea1fe2d49a3bb388fba9e232ef9c06335c04e5eae0bf7766975512a</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -8882,22 +8866,22 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>30.06</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>1.2288</t>
+          <t>1.6262</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Almirante Brown -1</t>
+          <t>Colon de Santa Fe</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -8907,27 +8891,27 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Almirante Brown vs Ciudad Bolivar</t>
+          <t>Colon de Santa Fe vs San Telmo</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Colon de Santa Fe</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>Ciudad Bolivar</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>0xa6a338c64f062bfd589e8d5d9cea45a27c9e64065f71f800e5966f81ce53c556</t>
+          <t>0x1a11ec80edeaae24566c4f4f891cc2afc56b377b24997a6e8ee533eeaaad5c92</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>L19683447</t>
+          <t>L19683494</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
@@ -8952,17 +8936,17 @@
       </c>
       <c r="R80" t="inlineStr">
         <is>
-          <t>1786214209</t>
+          <t>1786253941</t>
         </is>
       </c>
       <c r="S80" t="inlineStr">
         <is>
-          <t>1786212000</t>
+          <t>1786300200</t>
         </is>
       </c>
       <c r="T80" t="inlineStr">
         <is>
-          <t>6.295082</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="U80" t="inlineStr">
@@ -8979,12 +8963,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>0xf65c55196eeb0d21e7e3866ad26f8c3f2fee2aef273ddde5423e31fb40a51469</t>
+          <t>0x4e811c319e5e3a1fc1968ce0f31b4c15eb7222daa616252d99f9abc611408746</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x155C76202e45BE70c50bfeD7eAeA3B98e7716Ff7</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -8994,12 +8978,12 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>121.81</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>1.4363</t>
+          <t>1.2925</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -9009,7 +8993,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Tie</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -9019,27 +9003,27 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>Almirante Brown vs Ciudad Bolivar</t>
+          <t>Colon de Santa Fe vs San Telmo</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Colon de Santa Fe</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>Ciudad Bolivar</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>0x63a8bf73c1084ef223fdd1096dccd16232e7a455fad77f7f0891be1588ebeb88</t>
+          <t>0x2e49527408facf21253a0a1eafe51280b82e4c31919e91a396332f19ec366401</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>L19683447</t>
+          <t>L19683494</t>
         </is>
       </c>
       <c r="N81" t="inlineStr">
@@ -9064,17 +9048,17 @@
       </c>
       <c r="R81" t="inlineStr">
         <is>
-          <t>1786213844</t>
+          <t>1786243741</t>
         </is>
       </c>
       <c r="S81" t="inlineStr">
         <is>
-          <t>1786212000</t>
+          <t>1786300200</t>
         </is>
       </c>
       <c r="T81" t="inlineStr">
         <is>
-          <t>279.22063</t>
+          <t>3.418803</t>
         </is>
       </c>
       <c r="U81" t="inlineStr">
@@ -9091,12 +9075,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>0x1bb20a2bf22e4fe06b44c06b9c2caa21f3f2a7c9d0cce1a2346f79e76022cd1f</t>
+          <t>0xb8631aeb398192a03386505542f05fa15e34db501204baa8745a4d4b5c1651b7</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x155C76202e45BE70c50bfeD7eAeA3B98e7716Ff7</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -9106,22 +9090,22 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>21.05</t>
+          <t>0.99999</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>1.4363</t>
+          <t>1.6538</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Almirante Brown -0.5</t>
+          <t>Deportivo Moron</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -9131,27 +9115,27 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Almirante Brown vs Ciudad Bolivar</t>
+          <t>Deportivo Moron vs Acassuso</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Deportivo Moron</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>Ciudad Bolivar</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>0xfa00d2f0c7b5053ee336b303a0e7ad9cec0b8d539367773b7efee5c86cb2b59d</t>
+          <t>0x7514a255ce41be3c5db9f8849ba04e78dab80f02d1fe78c2aae82bbc843a9745</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>L19683447</t>
+          <t>L19683452</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
@@ -9176,17 +9160,17 @@
       </c>
       <c r="R82" t="inlineStr">
         <is>
-          <t>1786213843</t>
+          <t>1786243225</t>
         </is>
       </c>
       <c r="S82" t="inlineStr">
         <is>
-          <t>1786212000</t>
+          <t>1786298400</t>
         </is>
       </c>
       <c r="T82" t="inlineStr">
         <is>
-          <t>48.252149</t>
+          <t>1.529621</t>
         </is>
       </c>
       <c r="U82" t="inlineStr">
@@ -9203,28 +9187,28 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>0xc51052f8e449b4d56cc87b697bfc8eb0d3a88ae218dee1da3d725fa94163bc75</t>
+          <t>0xd3b94d194e43cc84f0a1b82723594ea6689a6aa2a4a7dccbc8a3d19fc321e49b</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
         </is>
       </c>
       <c r="C83" t="inlineStr"/>
       <c r="D83" t="inlineStr">
         <is>
-          <t>77.29513</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>1.2588</t>
+          <t>1.5238</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Primera Nacional</t>
+          <t>Under/Over (2)</t>
         </is>
       </c>
       <c r="G83" t="inlineStr"/>
@@ -9235,27 +9219,27 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>Almirante Brown vs Ciudad Bolivar</t>
+          <t>Deportivo Moron vs Acassuso</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Deportivo Moron</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>Ciudad Bolivar</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>0xaa5316c6f6544d74142ad6db34a3745918f237ffb1a657e000693947e81b65d6</t>
+          <t>0x108eaba0441fb45ec8e0073e945ae0ac1e138c933e4f2839816cd3198d7dd4d2</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>L19683447</t>
+          <t>L19683452</t>
         </is>
       </c>
       <c r="N83" t="inlineStr">
@@ -9280,17 +9264,17 @@
       </c>
       <c r="R83" t="inlineStr">
         <is>
-          <t>1786212849</t>
+          <t>1786225000</t>
         </is>
       </c>
       <c r="S83" t="inlineStr">
         <is>
-          <t>1786212000</t>
+          <t>1786298400</t>
         </is>
       </c>
       <c r="T83" t="inlineStr">
         <is>
-          <t>298.72514</t>
+          <t>1.909308</t>
         </is>
       </c>
       <c r="U83" t="inlineStr">
@@ -9307,31 +9291,39 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>0x0aeb4fe40f7d734cf244c144e6c064568b40b222193c9f93c641d1b31af3752e</t>
+          <t>0x86f4b24298f4c19f9f856cb19af2a260f24dc2d391f252248469436057ea1d1a</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr"/>
+          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>16.89162</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>1.2588</t>
+          <t>1.5263</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Primera Nacional</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr"/>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Deportivo Moron -1</t>
+        </is>
+      </c>
       <c r="H84" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -9339,27 +9331,27 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>Almirante Brown vs Ciudad Bolivar</t>
+          <t>Deportivo Moron vs Acassuso</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Deportivo Moron</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>Ciudad Bolivar</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>0xaa5316c6f6544d74142ad6db34a3745918f237ffb1a657e000693947e81b65d6</t>
+          <t>0xb61b063252c01d0525ae633a0276dc1830eabd418482fddec925fcbd602a2a75</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>L19683447</t>
+          <t>L19683452</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">
@@ -9384,17 +9376,17 @@
       </c>
       <c r="R84" t="inlineStr">
         <is>
-          <t>1786212805</t>
+          <t>1786220171</t>
         </is>
       </c>
       <c r="S84" t="inlineStr">
         <is>
-          <t>1786212000</t>
+          <t>1786298400</t>
         </is>
       </c>
       <c r="T84" t="inlineStr">
         <is>
-          <t>65.281623</t>
+          <t>1.900238</t>
         </is>
       </c>
       <c r="U84" t="inlineStr">
@@ -9411,12 +9403,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>0x383b895a5fe529a887369a0f113c516fdc7f6125d54381acf9695997ef22d039</t>
+          <t>0x0a5de930b5a6b8aca1699b666034af3891a3aa920021791d6d13e0297fb7903f</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x4a09916b1325Eed50eE8973B13742a205B0B7c7E</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -9426,39 +9418,39 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>11.26905</t>
+          <t>49.99999</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>1.745</t>
+          <t>1.6175</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Primera Nacional</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
+          <t>Almirante Brown -1</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Primera Nacional</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>Almirante Brown vs Ciudad Bolivar</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
           <t>Almirante Brown</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>Primera Nacional</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>Almirante Brown vs Ciudad Bolivar</t>
-        </is>
-      </c>
-      <c r="J85" t="inlineStr">
-        <is>
-          <t>Almirante Brown</t>
-        </is>
-      </c>
       <c r="K85" t="inlineStr">
         <is>
           <t>Ciudad Bolivar</t>
@@ -9466,7 +9458,7 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>0xaa5316c6f6544d74142ad6db34a3745918f237ffb1a657e000693947e81b65d6</t>
+          <t>0xa6a338c64f062bfd589e8d5d9cea45a27c9e64065f71f800e5966f81ce53c556</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
@@ -9496,7 +9488,7 @@
       </c>
       <c r="R85" t="inlineStr">
         <is>
-          <t>1786211779</t>
+          <t>1786218515</t>
         </is>
       </c>
       <c r="S85" t="inlineStr">
@@ -9506,7 +9498,7 @@
       </c>
       <c r="T85" t="inlineStr">
         <is>
-          <t>15.126242</t>
+          <t>80.971644</t>
         </is>
       </c>
       <c r="U85" t="inlineStr">
@@ -9523,54 +9515,46 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>0xcfb6add6f8610a64ffc187beb9e16bf2bacb27b54a0f0aaefa6bfb437239b893</t>
+          <t>0x17d5a08f8fa305f31f27442393c64f497dd3893417da6e76c321c4c2a187320d</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr"/>
       <c r="D86" t="inlineStr">
         <is>
-          <t>24.89998</t>
+          <t>49.18897</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>1.745</t>
+          <t>1.4737</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Primera Nacional</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr"/>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Primera Nacional</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>Almirante Brown vs Ciudad Bolivar</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
         <is>
           <t>Almirante Brown</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>Primera Nacional</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>Almirante Brown vs Ciudad Bolivar</t>
-        </is>
-      </c>
-      <c r="J86" t="inlineStr">
-        <is>
-          <t>Almirante Brown</t>
-        </is>
-      </c>
       <c r="K86" t="inlineStr">
         <is>
           <t>Ciudad Bolivar</t>
@@ -9578,7 +9562,7 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>0xaa5316c6f6544d74142ad6db34a3745918f237ffb1a657e000693947e81b65d6</t>
+          <t>0xa6a338c64f062bfd589e8d5d9cea45a27c9e64065f71f800e5966f81ce53c556</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
@@ -9608,7 +9592,7 @@
       </c>
       <c r="R86" t="inlineStr">
         <is>
-          <t>1786211777</t>
+          <t>1786218084</t>
         </is>
       </c>
       <c r="S86" t="inlineStr">
@@ -9618,7 +9602,7 @@
       </c>
       <c r="T86" t="inlineStr">
         <is>
-          <t>33.422792</t>
+          <t>103.82896</t>
         </is>
       </c>
       <c r="U86" t="inlineStr">
@@ -9635,19 +9619,15 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>0xd41652604437a4e92e0d78b653d4d49d8dedd2e153d1340dad89b9b93e182a48</t>
+          <t>0x56975f372357be259365cb7d2929c88d4fae157eea7a71d53d57cb234834f2ca</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>0xf4a8B27C9a13e298D65b5Cc072d252816B799C81</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr"/>
       <c r="D87" t="inlineStr">
         <is>
           <t>1</t>
@@ -9655,19 +9635,15 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>1.4163</t>
+          <t>1.4812</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>Atl. Rafaela</t>
-        </is>
-      </c>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr"/>
       <c r="H87" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -9675,27 +9651,27 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>Atl. Rafaela vs Chacarita Juniors</t>
+          <t>Club Atletico Mitre de Santiago del Estero vs Defensores de Belgrano Buenos Aires</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>Atl. Rafaela</t>
+          <t>Club Atletico Mitre de Santiago del Estero</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Defensores de Belgrano Buenos Aires</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>0xe738e9ba05492fab73eaaf6da211b84caadc72b08b26f1cd30fa8737e283bb44</t>
+          <t>0xa8ade64a3adb0ea38de67a61105ef31beb490d5a7287715b76ae124536d359cc</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>L19683450</t>
+          <t>L19683493</t>
         </is>
       </c>
       <c r="N87" t="inlineStr">
@@ -9720,17 +9696,17 @@
       </c>
       <c r="R87" t="inlineStr">
         <is>
-          <t>1786211028</t>
+          <t>1786215674</t>
         </is>
       </c>
       <c r="S87" t="inlineStr">
         <is>
-          <t>1786215600</t>
+          <t>1786302000</t>
         </is>
       </c>
       <c r="T87" t="inlineStr">
         <is>
-          <t>2.402402</t>
+          <t>2.077922</t>
         </is>
       </c>
       <c r="U87" t="inlineStr">
@@ -9747,31 +9723,39 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>0x562fd7c6419c807ed04d3cacac95f861805f96704bd535e265399fb9d2c2b609</t>
+          <t>0xff53df1f3446908699196d44fcdb8b39c1bd15c7ed519f0d730e55a51a6eb38f</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr"/>
+          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>5.32</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>1.405</t>
+          <t>1.3713</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Almirante Brown</t>
+        </is>
+      </c>
       <c r="H88" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -9779,27 +9763,27 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>Estudiantes de Caseros vs Deportivo Madryn</t>
+          <t>Almirante Brown vs Ciudad Bolivar</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>Estudiantes de Caseros</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Ciudad Bolivar</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>0xd61509e26f8645bb9780672f942c72c4b7dab577c2a01f04e1e09bce9b828765</t>
+          <t>0x63a8bf73c1084ef223fdd1096dccd16232e7a455fad77f7f0891be1588ebeb88</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>L19683453</t>
+          <t>L19683447</t>
         </is>
       </c>
       <c r="N88" t="inlineStr">
@@ -9824,7 +9808,7 @@
       </c>
       <c r="R88" t="inlineStr">
         <is>
-          <t>1786210845</t>
+          <t>1786215673</t>
         </is>
       </c>
       <c r="S88" t="inlineStr">
@@ -9834,7 +9818,7 @@
       </c>
       <c r="T88" t="inlineStr">
         <is>
-          <t>13.135802</t>
+          <t>2.693603</t>
         </is>
       </c>
       <c r="U88" t="inlineStr">
@@ -9851,12 +9835,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>0x0bb7a6822220bf40d7b279f99a54f46025f393ba95bb38b6d6dc98192886b3ed</t>
+          <t>0x249d52552e7acb9f472d2a4c48ab754622ba572903281739a3e10b4d509dccb0</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>0xf4a8B27C9a13e298D65b5Cc072d252816B799C81</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -9866,22 +9850,22 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>0.99999</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>1.5513</t>
+          <t>1.2288</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Almirante Brown -1</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -9891,27 +9875,27 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>Agropecuario vs Atletico Guemes</t>
+          <t>Almirante Brown vs Ciudad Bolivar</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>Atletico Guemes</t>
+          <t>Ciudad Bolivar</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>0xae66c7fab3c9c76fbc29d9e9778ef4845d8a6b8d092cff34320f100020113c49</t>
+          <t>0xa6a338c64f062bfd589e8d5d9cea45a27c9e64065f71f800e5966f81ce53c556</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>L19683451</t>
+          <t>L19683447</t>
         </is>
       </c>
       <c r="N89" t="inlineStr">
@@ -9936,7 +9920,7 @@
       </c>
       <c r="R89" t="inlineStr">
         <is>
-          <t>1786205982</t>
+          <t>1786214209</t>
         </is>
       </c>
       <c r="S89" t="inlineStr">
@@ -9946,7 +9930,7 @@
       </c>
       <c r="T89" t="inlineStr">
         <is>
-          <t>1.814041</t>
+          <t>6.295082</t>
         </is>
       </c>
       <c r="U89" t="inlineStr">
@@ -9963,12 +9947,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>0xe17b2546f4b90c8647ba975c279e39dec1fda5a003adfb8a2b39bb12a3519b10</t>
+          <t>0xf65c55196eeb0d21e7e3866ad26f8c3f2fee2aef273ddde5423e31fb40a51469</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>0xf4a8B27C9a13e298D65b5Cc072d252816B799C81</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -9978,12 +9962,12 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>121.81</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>1.3613</t>
+          <t>1.4363</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -9993,7 +9977,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Tie</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -10018,7 +10002,7 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>0xd5906ce08d61f7c5ee45fcebd2c8baeed5558387398ea332817a4b632f439b6d</t>
+          <t>0x63a8bf73c1084ef223fdd1096dccd16232e7a455fad77f7f0891be1588ebeb88</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
@@ -10048,7 +10032,7 @@
       </c>
       <c r="R90" t="inlineStr">
         <is>
-          <t>1786205963</t>
+          <t>1786213844</t>
         </is>
       </c>
       <c r="S90" t="inlineStr">
@@ -10058,7 +10042,7 @@
       </c>
       <c r="T90" t="inlineStr">
         <is>
-          <t>2.768166</t>
+          <t>279.22063</t>
         </is>
       </c>
       <c r="U90" t="inlineStr">
@@ -10075,12 +10059,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>0xcfe218822e89cbef5841f3045f551cc65acf353d8e240f943e2b61c54ea79a68</t>
+          <t>0x1bb20a2bf22e4fe06b44c06b9c2caa21f3f2a7c9d0cce1a2346f79e76022cd1f</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>0xf4a8B27C9a13e298D65b5Cc072d252816B799C81</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -10090,22 +10074,22 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>21.05</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>1.3337</t>
+          <t>1.4363</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Tie</t>
+          <t>Almirante Brown -0.5</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -10115,27 +10099,27 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>Estudiantes de Caseros vs Deportivo Madryn</t>
+          <t>Almirante Brown vs Ciudad Bolivar</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>Estudiantes de Caseros</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Ciudad Bolivar</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>0xf238b96ec9e2421db79973de945f1fc0c3f8bb99c31cda32d011ebaabfd2db86</t>
+          <t>0xfa00d2f0c7b5053ee336b303a0e7ad9cec0b8d539367773b7efee5c86cb2b59d</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>L19683453</t>
+          <t>L19683447</t>
         </is>
       </c>
       <c r="N91" t="inlineStr">
@@ -10160,7 +10144,7 @@
       </c>
       <c r="R91" t="inlineStr">
         <is>
-          <t>1786205938</t>
+          <t>1786213843</t>
         </is>
       </c>
       <c r="S91" t="inlineStr">
@@ -10170,7 +10154,7 @@
       </c>
       <c r="T91" t="inlineStr">
         <is>
-          <t>2.996255</t>
+          <t>48.252149</t>
         </is>
       </c>
       <c r="U91" t="inlineStr">
@@ -10187,28 +10171,28 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>0x1b9fcb29010a212f74af57040114154e78748f06a4d826be4397ddadb45ac31b</t>
+          <t>0xc51052f8e449b4d56cc87b697bfc8eb0d3a88ae218dee1da3d725fa94163bc75</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C92" t="inlineStr"/>
       <c r="D92" t="inlineStr">
         <is>
-          <t>21.69</t>
+          <t>77.29513</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>1.4512</t>
+          <t>1.2588</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
+          <t>Primera Nacional</t>
         </is>
       </c>
       <c r="G92" t="inlineStr"/>
@@ -10234,7 +10218,7 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>0xbbcaa253cd967fbf933ff0d87a6f9744cafec0ed59dad5f1f76332aab01a3fa5</t>
+          <t>0xaa5316c6f6544d74142ad6db34a3745918f237ffb1a657e000693947e81b65d6</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
@@ -10264,7 +10248,7 @@
       </c>
       <c r="R92" t="inlineStr">
         <is>
-          <t>1786190525</t>
+          <t>1786212849</t>
         </is>
       </c>
       <c r="S92" t="inlineStr">
@@ -10274,7 +10258,7 @@
       </c>
       <c r="T92" t="inlineStr">
         <is>
-          <t>48.066482</t>
+          <t>298.72514</t>
         </is>
       </c>
       <c r="U92" t="inlineStr">
@@ -10291,28 +10275,28 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>0x3177792dd6a7185e37ae06612104cf5a35d137d7f535a889a83a7e9b7c174506</t>
+          <t>0x0aeb4fe40f7d734cf244c144e6c064568b40b222193c9f93c641d1b31af3752e</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C93" t="inlineStr"/>
       <c r="D93" t="inlineStr">
         <is>
-          <t>18.35495</t>
+          <t>16.89162</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>1.4963</t>
+          <t>1.2588</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
+          <t>Primera Nacional</t>
         </is>
       </c>
       <c r="G93" t="inlineStr"/>
@@ -10338,7 +10322,7 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>0xbbcaa253cd967fbf933ff0d87a6f9744cafec0ed59dad5f1f76332aab01a3fa5</t>
+          <t>0xaa5316c6f6544d74142ad6db34a3745918f237ffb1a657e000693947e81b65d6</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
@@ -10368,7 +10352,7 @@
       </c>
       <c r="R93" t="inlineStr">
         <is>
-          <t>1786190491</t>
+          <t>1786212805</t>
         </is>
       </c>
       <c r="S93" t="inlineStr">
@@ -10378,7 +10362,7 @@
       </c>
       <c r="T93" t="inlineStr">
         <is>
-          <t>36.987305</t>
+          <t>65.281623</t>
         </is>
       </c>
       <c r="U93" t="inlineStr">
@@ -10395,12 +10379,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>0x54ed4ee2a6ebdab49498137f1accea542ead806f21430a0a771cc4872a044e43</t>
+          <t>0x383b895a5fe529a887369a0f113c516fdc7f6125d54381acf9695997ef22d039</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -10410,22 +10394,22 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>20.10741</t>
+          <t>11.26905</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>1.5437</t>
+          <t>1.745</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
+          <t>Primera Nacional</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Over 1.5</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -10450,7 +10434,7 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>0xbbcaa253cd967fbf933ff0d87a6f9744cafec0ed59dad5f1f76332aab01a3fa5</t>
+          <t>0xaa5316c6f6544d74142ad6db34a3745918f237ffb1a657e000693947e81b65d6</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
@@ -10480,7 +10464,7 @@
       </c>
       <c r="R94" t="inlineStr">
         <is>
-          <t>1786190485</t>
+          <t>1786211779</t>
         </is>
       </c>
       <c r="S94" t="inlineStr">
@@ -10490,7 +10474,7 @@
       </c>
       <c r="T94" t="inlineStr">
         <is>
-          <t>36.979145</t>
+          <t>15.126242</t>
         </is>
       </c>
       <c r="U94" t="inlineStr">
@@ -10507,7 +10491,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>0x544fe5c906328d009917b591611ff3438cef85f8b42d9f67732cbbd5eabbb8dd</t>
+          <t>0xcfb6add6f8610a64ffc187beb9e16bf2bacb27b54a0f0aaefa6bfb437239b893</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -10515,23 +10499,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C95" t="inlineStr"/>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>21.69</t>
+          <t>24.89998</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>1.4512</t>
+          <t>1.745</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr"/>
+          <t>Primera Nacional</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Almirante Brown</t>
+        </is>
+      </c>
       <c r="H95" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -10554,7 +10546,7 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>0xbbcaa253cd967fbf933ff0d87a6f9744cafec0ed59dad5f1f76332aab01a3fa5</t>
+          <t>0xaa5316c6f6544d74142ad6db34a3745918f237ffb1a657e000693947e81b65d6</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
@@ -10584,7 +10576,7 @@
       </c>
       <c r="R95" t="inlineStr">
         <is>
-          <t>1786190485</t>
+          <t>1786211777</t>
         </is>
       </c>
       <c r="S95" t="inlineStr">
@@ -10594,7 +10586,7 @@
       </c>
       <c r="T95" t="inlineStr">
         <is>
-          <t>48.066482</t>
+          <t>33.422792</t>
         </is>
       </c>
       <c r="U95" t="inlineStr">
@@ -10611,31 +10603,39 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>0xb2f3ea804e1760a01d3a93678f0e2119f1ea2a9db0dc4711a06cc7bcba42b0c2</t>
+          <t>0xd41652604437a4e92e0d78b653d4d49d8dedd2e153d1340dad89b9b93e182a48</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr"/>
+          <t>0xf4a8B27C9a13e298D65b5Cc072d252816B799C81</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>17.47</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>1.405</t>
+          <t>1.4163</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Atl. Rafaela</t>
+        </is>
+      </c>
       <c r="H96" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -10643,27 +10643,27 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>Estudiantes de Caseros vs Deportivo Madryn</t>
+          <t>Atl. Rafaela vs Chacarita Juniors</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>Estudiantes de Caseros</t>
+          <t>Atl. Rafaela</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>0xd61509e26f8645bb9780672f942c72c4b7dab577c2a01f04e1e09bce9b828765</t>
+          <t>0xe738e9ba05492fab73eaaf6da211b84caadc72b08b26f1cd30fa8737e283bb44</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>L19683453</t>
+          <t>L19683450</t>
         </is>
       </c>
       <c r="N96" t="inlineStr">
@@ -10688,17 +10688,17 @@
       </c>
       <c r="R96" t="inlineStr">
         <is>
-          <t>1786190461</t>
+          <t>1786211028</t>
         </is>
       </c>
       <c r="S96" t="inlineStr">
         <is>
-          <t>1786212000</t>
+          <t>1786215600</t>
         </is>
       </c>
       <c r="T96" t="inlineStr">
         <is>
-          <t>43.135802</t>
+          <t>2.402402</t>
         </is>
       </c>
       <c r="U96" t="inlineStr">
@@ -10715,7 +10715,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>0xa7eafbb77d425fc2347b4ee3e4f4e1b85f6d0f81420605db76ebfeeaa793a428</t>
+          <t>0x562fd7c6419c807ed04d3cacac95f861805f96704bd535e265399fb9d2c2b609</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -10726,12 +10726,12 @@
       <c r="C97" t="inlineStr"/>
       <c r="D97" t="inlineStr">
         <is>
-          <t>21.69</t>
+          <t>5.32</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>1.4512</t>
+          <t>1.405</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -10747,27 +10747,27 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>Almirante Brown vs Ciudad Bolivar</t>
+          <t>Estudiantes de Caseros vs Deportivo Madryn</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Estudiantes de Caseros</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>Ciudad Bolivar</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>0xbbcaa253cd967fbf933ff0d87a6f9744cafec0ed59dad5f1f76332aab01a3fa5</t>
+          <t>0xd61509e26f8645bb9780672f942c72c4b7dab577c2a01f04e1e09bce9b828765</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>L19683447</t>
+          <t>L19683453</t>
         </is>
       </c>
       <c r="N97" t="inlineStr">
@@ -10792,7 +10792,7 @@
       </c>
       <c r="R97" t="inlineStr">
         <is>
-          <t>1786190458</t>
+          <t>1786210845</t>
         </is>
       </c>
       <c r="S97" t="inlineStr">
@@ -10802,7 +10802,7 @@
       </c>
       <c r="T97" t="inlineStr">
         <is>
-          <t>48.066482</t>
+          <t>13.135802</t>
         </is>
       </c>
       <c r="U97" t="inlineStr">
@@ -10819,110 +10819,1078 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
+          <t>0x0bb7a6822220bf40d7b279f99a54f46025f393ba95bb38b6d6dc98192886b3ed</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>0xf4a8B27C9a13e298D65b5Cc072d252816B799C81</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>0.99999</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>1.5513</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Agropecuario</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Primera Nacional</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>Agropecuario vs Atletico Guemes</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>Agropecuario</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>Atletico Guemes</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>0xae66c7fab3c9c76fbc29d9e9778ef4845d8a6b8d092cff34320f100020113c49</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>L19683451</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O98" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q98" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R98" t="inlineStr">
+        <is>
+          <t>1786205982</t>
+        </is>
+      </c>
+      <c r="S98" t="inlineStr">
+        <is>
+          <t>1786212000</t>
+        </is>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>1.814041</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>0xe17b2546f4b90c8647ba975c279e39dec1fda5a003adfb8a2b39bb12a3519b10</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>0xf4a8B27C9a13e298D65b5Cc072d252816B799C81</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>1.3613</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Primera Nacional</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>Almirante Brown vs Ciudad Bolivar</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>Almirante Brown</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>Ciudad Bolivar</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>0xd5906ce08d61f7c5ee45fcebd2c8baeed5558387398ea332817a4b632f439b6d</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>L19683447</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O99" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q99" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R99" t="inlineStr">
+        <is>
+          <t>1786205963</t>
+        </is>
+      </c>
+      <c r="S99" t="inlineStr">
+        <is>
+          <t>1786212000</t>
+        </is>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>2.768166</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>0xcfe218822e89cbef5841f3045f551cc65acf353d8e240f943e2b61c54ea79a68</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>0xf4a8B27C9a13e298D65b5Cc072d252816B799C81</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>1.3337</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Primera Nacional</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>Estudiantes de Caseros vs Deportivo Madryn</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>Estudiantes de Caseros</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>Deportivo Madryn</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>0xf238b96ec9e2421db79973de945f1fc0c3f8bb99c31cda32d011ebaabfd2db86</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>L19683453</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O100" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q100" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R100" t="inlineStr">
+        <is>
+          <t>1786205938</t>
+        </is>
+      </c>
+      <c r="S100" t="inlineStr">
+        <is>
+          <t>1786212000</t>
+        </is>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>2.996255</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V100" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>0x1b9fcb29010a212f74af57040114154e78748f06a4d826be4397ddadb45ac31b</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr"/>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>21.69</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>1.4512</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr"/>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Primera Nacional</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>Almirante Brown vs Ciudad Bolivar</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>Almirante Brown</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>Ciudad Bolivar</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>0xbbcaa253cd967fbf933ff0d87a6f9744cafec0ed59dad5f1f76332aab01a3fa5</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>L19683447</t>
+        </is>
+      </c>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O101" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q101" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R101" t="inlineStr">
+        <is>
+          <t>1786190525</t>
+        </is>
+      </c>
+      <c r="S101" t="inlineStr">
+        <is>
+          <t>1786212000</t>
+        </is>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>48.066482</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>0x3177792dd6a7185e37ae06612104cf5a35d137d7f535a889a83a7e9b7c174506</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr"/>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>18.35495</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>1.4963</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr"/>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Primera Nacional</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>Almirante Brown vs Ciudad Bolivar</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>Almirante Brown</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>Ciudad Bolivar</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>0xbbcaa253cd967fbf933ff0d87a6f9744cafec0ed59dad5f1f76332aab01a3fa5</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>L19683447</t>
+        </is>
+      </c>
+      <c r="N102" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O102" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q102" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R102" t="inlineStr">
+        <is>
+          <t>1786190491</t>
+        </is>
+      </c>
+      <c r="S102" t="inlineStr">
+        <is>
+          <t>1786212000</t>
+        </is>
+      </c>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t>36.987305</t>
+        </is>
+      </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V102" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>0x54ed4ee2a6ebdab49498137f1accea542ead806f21430a0a771cc4872a044e43</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>20.10741</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>1.5437</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Over 1.5</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Primera Nacional</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>Almirante Brown vs Ciudad Bolivar</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>Almirante Brown</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>Ciudad Bolivar</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>0xbbcaa253cd967fbf933ff0d87a6f9744cafec0ed59dad5f1f76332aab01a3fa5</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>L19683447</t>
+        </is>
+      </c>
+      <c r="N103" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O103" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q103" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R103" t="inlineStr">
+        <is>
+          <t>1786190485</t>
+        </is>
+      </c>
+      <c r="S103" t="inlineStr">
+        <is>
+          <t>1786212000</t>
+        </is>
+      </c>
+      <c r="T103" t="inlineStr">
+        <is>
+          <t>36.979145</t>
+        </is>
+      </c>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V103" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>0x544fe5c906328d009917b591611ff3438cef85f8b42d9f67732cbbd5eabbb8dd</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr"/>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>21.69</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>1.4512</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr"/>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Primera Nacional</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>Almirante Brown vs Ciudad Bolivar</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>Almirante Brown</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>Ciudad Bolivar</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>0xbbcaa253cd967fbf933ff0d87a6f9744cafec0ed59dad5f1f76332aab01a3fa5</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>L19683447</t>
+        </is>
+      </c>
+      <c r="N104" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O104" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q104" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R104" t="inlineStr">
+        <is>
+          <t>1786190485</t>
+        </is>
+      </c>
+      <c r="S104" t="inlineStr">
+        <is>
+          <t>1786212000</t>
+        </is>
+      </c>
+      <c r="T104" t="inlineStr">
+        <is>
+          <t>48.066482</t>
+        </is>
+      </c>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V104" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>0xb2f3ea804e1760a01d3a93678f0e2119f1ea2a9db0dc4711a06cc7bcba42b0c2</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr"/>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>17.47</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>1.405</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr"/>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Primera Nacional</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>Estudiantes de Caseros vs Deportivo Madryn</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>Estudiantes de Caseros</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>Deportivo Madryn</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>0xd61509e26f8645bb9780672f942c72c4b7dab577c2a01f04e1e09bce9b828765</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>L19683453</t>
+        </is>
+      </c>
+      <c r="N105" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O105" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q105" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R105" t="inlineStr">
+        <is>
+          <t>1786190461</t>
+        </is>
+      </c>
+      <c r="S105" t="inlineStr">
+        <is>
+          <t>1786212000</t>
+        </is>
+      </c>
+      <c r="T105" t="inlineStr">
+        <is>
+          <t>43.135802</t>
+        </is>
+      </c>
+      <c r="U105" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V105" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>0xa7eafbb77d425fc2347b4ee3e4f4e1b85f6d0f81420605db76ebfeeaa793a428</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr"/>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>21.69</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>1.4512</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr"/>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>Primera Nacional</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>Almirante Brown vs Ciudad Bolivar</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>Almirante Brown</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>Ciudad Bolivar</t>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>0xbbcaa253cd967fbf933ff0d87a6f9744cafec0ed59dad5f1f76332aab01a3fa5</t>
+        </is>
+      </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>L19683447</t>
+        </is>
+      </c>
+      <c r="N106" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O106" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P106" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q106" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R106" t="inlineStr">
+        <is>
+          <t>1786190458</t>
+        </is>
+      </c>
+      <c r="S106" t="inlineStr">
+        <is>
+          <t>1786212000</t>
+        </is>
+      </c>
+      <c r="T106" t="inlineStr">
+        <is>
+          <t>48.066482</t>
+        </is>
+      </c>
+      <c r="U106" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V106" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
           <t>0x5c5b512ea725fac30531bf5fe91f34f3ccc0eeff23890c18f25c3f329007c589</t>
         </is>
       </c>
-      <c r="B98" t="inlineStr">
+      <c r="B107" t="inlineStr">
         <is>
           <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
         </is>
       </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E98" t="inlineStr">
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
         <is>
           <t>1.3638</t>
         </is>
       </c>
-      <c r="F98" t="inlineStr">
+      <c r="F107" t="inlineStr">
         <is>
           <t>1X2</t>
         </is>
       </c>
-      <c r="G98" t="inlineStr">
+      <c r="G107" t="inlineStr">
         <is>
           <t>Tie</t>
         </is>
       </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>Primera Nacional</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr">
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Primera Nacional</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
         <is>
           <t>Almirante Brown vs Ciudad Bolivar</t>
         </is>
       </c>
-      <c r="J98" t="inlineStr">
+      <c r="J107" t="inlineStr">
         <is>
           <t>Almirante Brown</t>
         </is>
       </c>
-      <c r="K98" t="inlineStr">
+      <c r="K107" t="inlineStr">
         <is>
           <t>Ciudad Bolivar</t>
         </is>
       </c>
-      <c r="L98" t="inlineStr">
+      <c r="L107" t="inlineStr">
         <is>
           <t>0xd5906ce08d61f7c5ee45fcebd2c8baeed5558387398ea332817a4b632f439b6d</t>
         </is>
       </c>
-      <c r="M98" t="inlineStr">
+      <c r="M107" t="inlineStr">
         <is>
           <t>L19683447</t>
         </is>
       </c>
-      <c r="N98" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O98" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P98" t="inlineStr">
+      <c r="N107" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O107" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P107" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q98" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R98" t="inlineStr">
+      <c r="Q107" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R107" t="inlineStr">
         <is>
           <t>1786125660</t>
         </is>
       </c>
-      <c r="S98" t="inlineStr">
+      <c r="S107" t="inlineStr">
         <is>
           <t>1786212000</t>
         </is>
       </c>
-      <c r="T98" t="inlineStr">
+      <c r="T107" t="inlineStr">
         <is>
           <t>2.749141</t>
         </is>
       </c>
-      <c r="U98" t="inlineStr">
+      <c r="U107" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V98" t="inlineStr">
+      <c r="V107" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/Primera Nacional/trades.xlsx
+++ b/data/sxbet/ligas/Primera Nacional/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V107"/>
+  <dimension ref="A1:V109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,23 +531,23 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0xe70516113cb626418e16d5940b7952c123bd3afbc9ae8fb08b6d8a46cfc93917</t>
+          <t>0x494bd95999d6775b2e923d6270b9b160b6a431bcd6ab5b22f79a2cfe4d911f80</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0x49c03d69c92f4aEa65FBF1F149A1ac3Bf31A37C6</t>
+          <t>0xBc04c6a7E9255Cb262632407a40Aa6344137555b</t>
         </is>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>231.99994</t>
+          <t>10.99999</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -563,27 +563,27 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>San Martin Tucuman vs San Martín de San Juan</t>
+          <t>Gimnasia y Esgrima de Jujuy vs Tristan Suarez</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>San Martin Tucuman</t>
+          <t>Gimnasia y Esgrima de Jujuy</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>San Martín de San Juan</t>
+          <t>Tristan Suarez</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0x20f1a35dae3d2a458c7a6a3e312e646a320245e89d843105ba9b217e1cd46c9e</t>
+          <t>0x9967827b768bd980ab7d0757f29afe285ae91ee95ad736a4ddcc46d0f68cf1bb</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>L19682528</t>
+          <t>L19683507</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -608,17 +608,17 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1786315295</t>
+          <t>1786349502</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>1786309200</t>
+          <t>1786384800</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>260.67409</t>
+          <t>15.492944</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -635,28 +635,28 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0x8a82110b5ad97ac1c2de4721106d20fdd9060513206960520e7155a6e2b20612</t>
+          <t>0xdc1f7687d7452dd32612faa80dae516a650d157d1a94f1cd14e780fdbc95c899</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xBc04c6a7E9255Cb262632407a40Aa6344137555b</t>
         </is>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>18.85306</t>
+          <t>10.99999</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.3875</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Primera Nacional</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
@@ -667,27 +667,27 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>San Martin Tucuman vs San Martín de San Juan</t>
+          <t>Gimnasia y Esgrima de Jujuy vs Tristan Suarez</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>San Martin Tucuman</t>
+          <t>Gimnasia y Esgrima de Jujuy</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>San Martín de San Juan</t>
+          <t>Tristan Suarez</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0x710577a276e495ee3f90c1efed84c57aad13b2a5a77b9b1f1045dc6c20df1b82</t>
+          <t>0x9967827b768bd980ab7d0757f29afe285ae91ee95ad736a4ddcc46d0f68cf1bb</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>L19682528</t>
+          <t>L19683507</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -712,17 +712,17 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1786315013</t>
+          <t>1786349464</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>1786309200</t>
+          <t>1786384800</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>48.653058</t>
+          <t>15.492944</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -739,28 +739,28 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0x99cae5762d48bf6225a2833cebf0caac6f2be5141693c86d119bba55fecb00af</t>
+          <t>0xe70516113cb626418e16d5940b7952c123bd3afbc9ae8fb08b6d8a46cfc93917</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x49c03d69c92f4aEa65FBF1F149A1ac3Bf31A37C6</t>
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>117.43306</t>
+          <t>231.99994</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.3875</t>
+          <t>1.89</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Primera Nacional</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G4" t="inlineStr"/>
@@ -786,7 +786,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0x4f02331cd42a68f65ea16d62aac0c6b123d9400d12a4d556f3a72df894da02fb</t>
+          <t>0x20f1a35dae3d2a458c7a6a3e312e646a320245e89d843105ba9b217e1cd46c9e</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -816,7 +816,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1786314895</t>
+          <t>1786315295</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -826,7 +826,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>303.053058</t>
+          <t>260.67409</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -843,23 +843,23 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0x4030f87453819c2a532820e812d084e6b4bb480048daa74b20c2d6e02cb96f44</t>
+          <t>0x8a82110b5ad97ac1c2de4721106d20fdd9060513206960520e7155a6e2b20612</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.25944</t>
+          <t>18.85306</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.3675</t>
+          <t>1.3875</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -920,7 +920,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1786311747</t>
+          <t>1786315013</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.705959</t>
+          <t>48.653058</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -947,39 +947,31 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0x94334ff3be3abb398e288ea2bdc325dbea166976a777d4b3565d6adf6e74cceb</t>
+          <t>0x99cae5762d48bf6225a2833cebf0caac6f2be5141693c86d119bba55fecb00af</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>117.43306</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.545</t>
+          <t>1.3875</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Over 1.5</t>
-        </is>
-      </c>
+          <t>Primera Nacional</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -1002,7 +994,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0x59f5c83d1ebabf219c4e416ecb6303622840a732d32e28a4ca19fdba0d4e206d</t>
+          <t>0x4f02331cd42a68f65ea16d62aac0c6b123d9400d12a4d556f3a72df894da02fb</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -1032,7 +1024,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1786309862</t>
+          <t>1786314895</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1042,7 +1034,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1.834862</t>
+          <t>303.053058</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1059,28 +1051,28 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0xc96803526daa07f4eae1fbfe8d09be9d49a0e7e2ce24d0288f9d3ab9ec387e36</t>
+          <t>0x4030f87453819c2a532820e812d084e6b4bb480048daa74b20c2d6e02cb96f44</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0x4a09916b1325Eed50eE8973B13742a205B0B7c7E</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>0.25944</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.825</t>
+          <t>1.3675</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
+          <t>Primera Nacional</t>
         </is>
       </c>
       <c r="G7" t="inlineStr"/>
@@ -1091,27 +1083,27 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Racing de Cordoba vs San Miguel</t>
+          <t>San Martin Tucuman vs San Martín de San Juan</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Racing de Cordoba</t>
+          <t>San Martin Tucuman</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>San Martín de San Juan</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0xb291f54e66fa1539bf7206876cb79292f9c9cd3cebed6ca59247514b369a28fb</t>
+          <t>0x710577a276e495ee3f90c1efed84c57aad13b2a5a77b9b1f1045dc6c20df1b82</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>L19683501</t>
+          <t>L19682528</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1136,17 +1128,17 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1786307586</t>
+          <t>1786311747</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>1786302000</t>
+          <t>1786309200</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>60.606061</t>
+          <t>0.705959</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1163,12 +1155,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0xe508af858531cbb110be0edc19b46f9f847f5373f422a56dc4f6091f724877c2</t>
+          <t>0x94334ff3be3abb398e288ea2bdc325dbea166976a777d4b3565d6adf6e74cceb</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1178,22 +1170,22 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>42.02</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.545</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>Under/Over (1.5)</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Over 2.5</t>
+          <t>Over 1.5</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1203,27 +1195,27 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Racing de Cordoba vs San Miguel</t>
+          <t>San Martin Tucuman vs San Martín de San Juan</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Racing de Cordoba</t>
+          <t>San Martin Tucuman</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>San Martín de San Juan</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0xb00a08202acc66af81e3cc28141951f5744b2edb09c13699c361640638e0580a</t>
+          <t>0x59f5c83d1ebabf219c4e416ecb6303622840a732d32e28a4ca19fdba0d4e206d</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>L19683501</t>
+          <t>L19682528</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1248,17 +1240,17 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1786306456</t>
+          <t>1786309862</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>1786302000</t>
+          <t>1786309200</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>525.25</t>
+          <t>1.834862</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1275,39 +1267,31 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0x6d0e9cce02624418d7b75dc11802dbf4900745db1d1f0ec0ee6d8804e67faced</t>
+          <t>0xc96803526daa07f4eae1fbfe8d09be9d49a0e7e2ce24d0288f9d3ab9ec387e36</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x4a09916b1325Eed50eE8973B13742a205B0B7c7E</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>42.02</t>
+          <t>50</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.825</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Over 2.5</t>
-        </is>
-      </c>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -1330,7 +1314,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0xb00a08202acc66af81e3cc28141951f5744b2edb09c13699c361640638e0580a</t>
+          <t>0xb291f54e66fa1539bf7206876cb79292f9c9cd3cebed6ca59247514b369a28fb</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1360,7 +1344,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1786306379</t>
+          <t>1786307586</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1370,7 +1354,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>525.25</t>
+          <t>60.606061</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1387,7 +1371,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0xfbf539c8fecb9ae92fbe1749fa31c242f747ee8b7d8b6d79b9eb6a315ac4109a</t>
+          <t>0xe508af858531cbb110be0edc19b46f9f847f5373f422a56dc4f6091f724877c2</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1402,22 +1386,22 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>25.88</t>
+          <t>42.02</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.0962</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Over 2.0</t>
+          <t>Over 2.5</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1442,7 +1426,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0xb291f54e66fa1539bf7206876cb79292f9c9cd3cebed6ca59247514b369a28fb</t>
+          <t>0xb00a08202acc66af81e3cc28141951f5744b2edb09c13699c361640638e0580a</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1472,7 +1456,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1786306378</t>
+          <t>1786306456</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1482,7 +1466,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>268.883117</t>
+          <t>525.25</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1499,31 +1483,39 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0x2ce4118d8299ef054cc6439e8191ab57041190d43c1b322f7656f46a915f66a7</t>
+          <t>0x6d0e9cce02624418d7b75dc11802dbf4900745db1d1f0ec0ee6d8804e67faced</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>11.65</t>
+          <t>42.02</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.0888</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr"/>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Over 2.5</t>
+        </is>
+      </c>
       <c r="H11" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -1531,27 +1523,27 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Godoy Cruz vs Chaco For Ever</t>
+          <t>Racing de Cordoba vs San Miguel</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Racing de Cordoba</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0xa5f02d0d08d0dcc4818948397f0f26c77f90b87182cec4d62ab01f77352671a1</t>
+          <t>0xb00a08202acc66af81e3cc28141951f5744b2edb09c13699c361640638e0580a</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>L19683484</t>
+          <t>L19683501</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1576,17 +1568,17 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1786305067</t>
+          <t>1786306379</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>1786303800</t>
+          <t>1786302000</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>131.267606</t>
+          <t>525.25</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1603,7 +1595,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0x72a01c47ea710f8819c55b38617462ca579e333f91db40e5ab1feff1d3de96c8</t>
+          <t>0xfbf539c8fecb9ae92fbe1749fa31c242f747ee8b7d8b6d79b9eb6a315ac4109a</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1618,22 +1610,22 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>102.18997</t>
+          <t>25.88</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.8087</t>
+          <t>1.0962</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Primera Nacional</t>
+          <t>Under/Over (2)</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Colon de Santa Fe</t>
+          <t>Over 2.0</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1643,27 +1635,27 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Colon de Santa Fe vs San Telmo</t>
+          <t>Racing de Cordoba vs San Miguel</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Colon de Santa Fe</t>
+          <t>Racing de Cordoba</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>0xbca9ed7d23a7df6c8ab98ab2ffc6649f2d4bd3d9007bd0ecf103e453c87addac</t>
+          <t>0xb291f54e66fa1539bf7206876cb79292f9c9cd3cebed6ca59247514b369a28fb</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>L19683494</t>
+          <t>L19683501</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1688,17 +1680,17 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1786305018</t>
+          <t>1786306378</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>1786300200</t>
+          <t>1786302000</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>126.35545</t>
+          <t>268.883117</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1715,39 +1707,31 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0x48ad1a825a577db64992a5c2f61f562d82c8f17820251af179f0cdf9d5e6b577</t>
+          <t>0x2ce4118d8299ef054cc6439e8191ab57041190d43c1b322f7656f46a915f66a7</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>102.18997</t>
+          <t>11.65</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.8087</t>
+          <t>1.0888</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Primera Nacional</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Colon de Santa Fe 0</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -1755,27 +1739,27 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Colon de Santa Fe vs San Telmo</t>
+          <t>Godoy Cruz vs Chaco For Ever</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Colon de Santa Fe</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>0x9c15c50c33bf4b091bef5a468ce1fe4a2593b78db6048cae08ab186caadf08a9</t>
+          <t>0xa5f02d0d08d0dcc4818948397f0f26c77f90b87182cec4d62ab01f77352671a1</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>L19683494</t>
+          <t>L19683484</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1800,17 +1784,17 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1786305018</t>
+          <t>1786305067</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>1786300200</t>
+          <t>1786303800</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>126.35545</t>
+          <t>131.267606</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1827,31 +1811,39 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0x241c6cdee87bcff9c9e1e77941a5ecd05acb972d4c07e1cfc562414003f5c59c</t>
+          <t>0x72a01c47ea710f8819c55b38617462ca579e333f91db40e5ab1feff1d3de96c8</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>63.89997</t>
+          <t>102.18997</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1.8912</t>
+          <t>1.8087</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr"/>
+          <t>Primera Nacional</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Colon de Santa Fe</t>
+        </is>
+      </c>
       <c r="H14" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -1859,27 +1851,27 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Racing de Cordoba vs San Miguel</t>
+          <t>Colon de Santa Fe vs San Telmo</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Racing de Cordoba</t>
+          <t>Colon de Santa Fe</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>0xb00a08202acc66af81e3cc28141951f5744b2edb09c13699c361640638e0580a</t>
+          <t>0xbca9ed7d23a7df6c8ab98ab2ffc6649f2d4bd3d9007bd0ecf103e453c87addac</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>L19683501</t>
+          <t>L19683494</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1904,17 +1896,17 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1786304709</t>
+          <t>1786305018</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>1786302000</t>
+          <t>1786300200</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>71.697021</t>
+          <t>126.35545</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -1931,31 +1923,39 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0xfb092fb802f6de6249f78cd6b0c995923dcd8a18d766d60718068deca14131d2</t>
+          <t>0x48ad1a825a577db64992a5c2f61f562d82c8f17820251af179f0cdf9d5e6b577</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>52.23996</t>
+          <t>102.18997</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1.8912</t>
+          <t>1.8087</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr"/>
+          <t>Primera Nacional</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Colon de Santa Fe 0</t>
+        </is>
+      </c>
       <c r="H15" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -1963,27 +1963,27 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Racing de Cordoba vs San Miguel</t>
+          <t>Colon de Santa Fe vs San Telmo</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Racing de Cordoba</t>
+          <t>Colon de Santa Fe</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>0xb00a08202acc66af81e3cc28141951f5744b2edb09c13699c361640638e0580a</t>
+          <t>0x9c15c50c33bf4b091bef5a468ce1fe4a2593b78db6048cae08ab186caadf08a9</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>L19683501</t>
+          <t>L19683494</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -2008,17 +2008,17 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>1786304687</t>
+          <t>1786305018</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>1786302000</t>
+          <t>1786300200</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>58.614261</t>
+          <t>126.35545</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2035,7 +2035,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0xdaad372a2d56f6f987e31c931aed692c41df131e0f5ffc29a5e5b9202518a8ad</t>
+          <t>0x241c6cdee87bcff9c9e1e77941a5ecd05acb972d4c07e1cfc562414003f5c59c</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2046,17 +2046,17 @@
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>63.89997</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1.2563</t>
+          <t>1.8912</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Asian Handicap (0.5)</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G16" t="inlineStr"/>
@@ -2082,7 +2082,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>0x6dbad77d129f55a581762668ca1964af6cce4241516257e981ed02638805382a</t>
+          <t>0xb00a08202acc66af81e3cc28141951f5744b2edb09c13699c361640638e0580a</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -2112,7 +2112,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1786304596</t>
+          <t>1786304709</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>39.02439</t>
+          <t>71.697021</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2139,7 +2139,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0xd8c270eff581f800f6dfee154ad07fcaa13887305309b80012750a0200954653</t>
+          <t>0xfb092fb802f6de6249f78cd6b0c995923dcd8a18d766d60718068deca14131d2</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2150,17 +2150,17 @@
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>104.40999</t>
+          <t>52.23996</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.685</t>
+          <t>1.8912</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G17" t="inlineStr"/>
@@ -2186,7 +2186,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>0x48447168804e92d195e0c849cfb7ae548e076f102e1005f3756585b3d18ea65c</t>
+          <t>0xb00a08202acc66af81e3cc28141951f5744b2edb09c13699c361640638e0580a</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>1786304566</t>
+          <t>1786304687</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -2226,7 +2226,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>152.423343</t>
+          <t>58.614261</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2243,7 +2243,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0x584df9c83be504ffadc29cf9bc05886a622203a90bdf8fd90fe15998dca2c79a</t>
+          <t>0xdaad372a2d56f6f987e31c931aed692c41df131e0f5ffc29a5e5b9202518a8ad</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2254,17 +2254,17 @@
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>30.76</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.8388</t>
+          <t>1.2563</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (0.5)</t>
         </is>
       </c>
       <c r="G18" t="inlineStr"/>
@@ -2275,27 +2275,27 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Godoy Cruz vs Chaco For Ever</t>
+          <t>Racing de Cordoba vs San Miguel</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Racing de Cordoba</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>0x9c19e4c1fd9646506f8ea14e2b1be19b49a5ab4dc1a7bf40167705a4ae2b338b</t>
+          <t>0x6dbad77d129f55a581762668ca1964af6cce4241516257e981ed02638805382a</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>L19683484</t>
+          <t>L19683501</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -2320,17 +2320,17 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>1786304409</t>
+          <t>1786304596</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>1786303800</t>
+          <t>1786302000</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>36.673621</t>
+          <t>39.02439</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2347,27 +2347,23 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0x80bb89bcfcad865ae79dd791b8e50e1efe79465dcaef80ef22f91624a9a206e0</t>
+          <t>0xd8c270eff581f800f6dfee154ad07fcaa13887305309b80012750a0200954653</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>164.56999</t>
+          <t>104.40999</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1.5875</t>
+          <t>1.685</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -2375,11 +2371,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+      <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -2387,27 +2379,27 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>CA Colegiales vs Patronato</t>
+          <t>Racing de Cordoba vs San Miguel</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>CA Colegiales</t>
+          <t>Racing de Cordoba</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>0x08cf3f4d7a357213e26484ea0db7a018932df0928a98202f91241b88b1990c60</t>
+          <t>0x48447168804e92d195e0c849cfb7ae548e076f102e1005f3756585b3d18ea65c</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>L19683449</t>
+          <t>L19683501</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -2432,17 +2424,17 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>1786304222</t>
+          <t>1786304566</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>1786298400</t>
+          <t>1786302000</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>280.119132</t>
+          <t>152.423343</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2459,39 +2451,31 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0x4a29c98cff774b7281c745ce8241168cf83b95715fb62c195dfe0bdfd4993ffa</t>
+          <t>0x584df9c83be504ffadc29cf9bc05886a622203a90bdf8fd90fe15998dca2c79a</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>50.96999</t>
+          <t>30.76</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.6187</t>
+          <t>1.8388</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Primera Nacional</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>CA Colegiales 0</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -2499,27 +2483,27 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>CA Colegiales vs Patronato</t>
+          <t>Godoy Cruz vs Chaco For Ever</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>CA Colegiales</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0x3fa48fbf2a59e0b45def889e06df3d2da646e9465f9af4f1b88581fea7fb4496</t>
+          <t>0x9c19e4c1fd9646506f8ea14e2b1be19b49a5ab4dc1a7bf40167705a4ae2b338b</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>L19683449</t>
+          <t>L19683484</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -2544,17 +2528,17 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>1786304216</t>
+          <t>1786304409</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>1786298400</t>
+          <t>1786303800</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>82.375741</t>
+          <t>36.673621</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2571,12 +2555,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0x606477ca73e4e38677cfe19e9dbb8d21dd44116004cd1a6b689a66845a1f33c5</t>
+          <t>0x80bb89bcfcad865ae79dd791b8e50e1efe79465dcaef80ef22f91624a9a206e0</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2586,12 +2570,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>47.49</t>
+          <t>164.56999</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.5875</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -2656,7 +2640,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>1786304193</t>
+          <t>1786304222</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -2666,7 +2650,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>79.15</t>
+          <t>280.119132</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -2683,7 +2667,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0x471461bdea5d2a1f048ae19a536ae904425043d9ce35e662e416d1892b8ab682</t>
+          <t>0x4a29c98cff774b7281c745ce8241168cf83b95715fb62c195dfe0bdfd4993ffa</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2698,12 +2682,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>45.36</t>
+          <t>50.96999</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1.6275</t>
+          <t>1.6187</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -2768,7 +2752,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>1786304137</t>
+          <t>1786304216</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -2778,7 +2762,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>72.286853</t>
+          <t>82.375741</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -2795,7 +2779,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0x2b918c36189e27805e61d743881205705b15ab4bdbf93fa4149c03b299488496</t>
+          <t>0x606477ca73e4e38677cfe19e9dbb8d21dd44116004cd1a6b689a66845a1f33c5</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2803,15 +2787,19 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr"/>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>291.91999</t>
+          <t>47.49</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1.8125</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -2819,7 +2807,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H23" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -2872,7 +2864,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>1786304032</t>
+          <t>1786304193</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -2882,7 +2874,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>359.286142</t>
+          <t>79.15</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -2899,12 +2891,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0x0c986442e558e0ecef4ac6ae5c05b398f82bc22bf0a12f073b441ebce3f8f73e</t>
+          <t>0x471461bdea5d2a1f048ae19a536ae904425043d9ce35e662e416d1892b8ab682</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>0x161ba9aad05022c88726A1D1244fDF624e51BFD5</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2914,22 +2906,22 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>45.36</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1.5063</t>
+          <t>1.6275</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Primera Nacional</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Colon de Santa Fe</t>
+          <t>CA Colegiales 0</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2939,27 +2931,27 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Colon de Santa Fe vs San Telmo</t>
+          <t>CA Colegiales vs Patronato</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Colon de Santa Fe</t>
+          <t>CA Colegiales</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0x1a11ec80edeaae24566c4f4f891cc2afc56b377b24997a6e8ee533eeaaad5c92</t>
+          <t>0x3fa48fbf2a59e0b45def889e06df3d2da646e9465f9af4f1b88581fea7fb4496</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>L19683494</t>
+          <t>L19683449</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -2984,17 +2976,17 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>1786303960</t>
+          <t>1786304137</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>1786300200</t>
+          <t>1786298400</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>4.938272</t>
+          <t>72.286853</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -3011,28 +3003,28 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0x2a347762aef526a0953efcb99ce105f109d3055f0d91ab8c6f756cd50ff191d0</t>
+          <t>0x2b918c36189e27805e61d743881205705b15ab4bdbf93fa4149c03b299488496</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1.07999</t>
+          <t>291.91999</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1.5775</t>
+          <t>1.8125</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G25" t="inlineStr"/>
@@ -3043,27 +3035,27 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Godoy Cruz vs Chaco For Ever</t>
+          <t>CA Colegiales vs Patronato</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>CA Colegiales</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0x8a3835f02766a90c02150e223fdcaa0f380cffe1bd489dd896b621cb4de6a216</t>
+          <t>0x08cf3f4d7a357213e26484ea0db7a018932df0928a98202f91241b88b1990c60</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>L19683484</t>
+          <t>L19683449</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -3088,17 +3080,17 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>1786303869</t>
+          <t>1786304032</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>1786303800</t>
+          <t>1786298400</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>1.870113</t>
+          <t>359.286142</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3115,23 +3107,27 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0xf1ea587ba3fa2b6f394d282689f029176ee146013ab745dcfa61570d0ec1af54</t>
+          <t>0x0c986442e558e0ecef4ac6ae5c05b398f82bc22bf0a12f073b441ebce3f8f73e</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr"/>
+          <t>0x161ba9aad05022c88726A1D1244fDF624e51BFD5</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>66.77496</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1.1938</t>
+          <t>1.5063</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -3139,7 +3135,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Colon de Santa Fe</t>
+        </is>
+      </c>
       <c r="H26" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -3147,27 +3147,27 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>CA Colegiales vs Patronato</t>
+          <t>Colon de Santa Fe vs San Telmo</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>CA Colegiales</t>
+          <t>Colon de Santa Fe</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>0x6033340ba69fb7874ae22715f395c0926449aa18c6ec5295e2568fe9a173664d</t>
+          <t>0x1a11ec80edeaae24566c4f4f891cc2afc56b377b24997a6e8ee533eeaaad5c92</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>L19683449</t>
+          <t>L19683494</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -3192,17 +3192,17 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>1786303811</t>
+          <t>1786303960</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>1786298400</t>
+          <t>1786300200</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>344.644955</t>
+          <t>4.938272</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -3219,28 +3219,28 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0x83f468f50e882b1c9b4663834cfdbddae84368823e2297b07a8a228b7252f9d0</t>
+          <t>0x2a347762aef526a0953efcb99ce105f109d3055f0d91ab8c6f756cd50ff191d0</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
         </is>
       </c>
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t>20.75148</t>
+          <t>1.07999</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1.4275</t>
+          <t>1.5775</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Under/Over (2)</t>
         </is>
       </c>
       <c r="G27" t="inlineStr"/>
@@ -3251,27 +3251,27 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>CA Colegiales vs Patronato</t>
+          <t>Godoy Cruz vs Chaco For Ever</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>CA Colegiales</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>0x5063fd7c88c1b369ed4a83e39411f4287c83048fafbc24740f9ecb68019a60ec</t>
+          <t>0x8a3835f02766a90c02150e223fdcaa0f380cffe1bd489dd896b621cb4de6a216</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>L19683449</t>
+          <t>L19683484</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -3296,17 +3296,17 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>1786303811</t>
+          <t>1786303869</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>1786298400</t>
+          <t>1786303800</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>48.541474</t>
+          <t>1.870113</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -3323,28 +3323,28 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0x5d59910b62dd3a569254988b87a126db28ce8123f67bea999e650c42a85e456c</t>
+          <t>0xf1ea587ba3fa2b6f394d282689f029176ee146013ab745dcfa61570d0ec1af54</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
-          <t>64.86487</t>
+          <t>66.77496</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>1.075</t>
+          <t>1.1938</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Under/Over (0.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G28" t="inlineStr"/>
@@ -3355,27 +3355,27 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Club Atletico Mitre de Santiago del Estero vs Defensores de Belgrano Buenos Aires</t>
+          <t>CA Colegiales vs Patronato</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Club Atletico Mitre de Santiago del Estero</t>
+          <t>CA Colegiales</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano Buenos Aires</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>0x7423d14fbc1277a1b44ab6287b237b4f12599476710984e2df8514e1e505203b</t>
+          <t>0x6033340ba69fb7874ae22715f395c0926449aa18c6ec5295e2568fe9a173664d</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>L19683493</t>
+          <t>L19683449</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -3400,17 +3400,17 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>1786303551</t>
+          <t>1786303811</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>1786302000</t>
+          <t>1786298400</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>864.864933</t>
+          <t>344.644955</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -3427,28 +3427,28 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0x54e4c2b9fcb34a87d3118c2c4aa1d528e53ecdeb3b19d58ec93ceabdcf9789a0</t>
+          <t>0x83f468f50e882b1c9b4663834cfdbddae84368823e2297b07a8a228b7252f9d0</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
-          <t>155.22388</t>
+          <t>20.75148</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>1.1625</t>
+          <t>1.4275</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Under/Over (1)</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G29" t="inlineStr"/>
@@ -3459,27 +3459,27 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Club Atletico Mitre de Santiago del Estero vs Defensores de Belgrano Buenos Aires</t>
+          <t>CA Colegiales vs Patronato</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Club Atletico Mitre de Santiago del Estero</t>
+          <t>CA Colegiales</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano Buenos Aires</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>0x4f7afe558099a628e7275525f608e3e5d976f6f0ae76324c03ac2a8d33384e1b</t>
+          <t>0x5063fd7c88c1b369ed4a83e39411f4287c83048fafbc24740f9ecb68019a60ec</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>L19683493</t>
+          <t>L19683449</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -3504,17 +3504,17 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>1786303551</t>
+          <t>1786303811</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>1786302000</t>
+          <t>1786298400</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>955.223877</t>
+          <t>48.541474</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -3531,7 +3531,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0xac12d313bf6318f639126e42c96989b9e78cbb4aeafba2d7a6842ecaab1d4679</t>
+          <t>0x5d59910b62dd3a569254988b87a126db28ce8123f67bea999e650c42a85e456c</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3542,17 +3542,17 @@
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
-          <t>29.36999</t>
+          <t>64.86487</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1.6288</t>
+          <t>1.075</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (0.5)</t>
         </is>
       </c>
       <c r="G30" t="inlineStr"/>
@@ -3563,27 +3563,27 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Racing de Cordoba vs San Miguel</t>
+          <t>Club Atletico Mitre de Santiago del Estero vs Defensores de Belgrano Buenos Aires</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Racing de Cordoba</t>
+          <t>Club Atletico Mitre de Santiago del Estero</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Defensores de Belgrano Buenos Aires</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>0x48447168804e92d195e0c849cfb7ae548e076f102e1005f3756585b3d18ea65c</t>
+          <t>0x7423d14fbc1277a1b44ab6287b237b4f12599476710984e2df8514e1e505203b</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>L19683501</t>
+          <t>L19683493</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -3608,7 +3608,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>1786303457</t>
+          <t>1786303551</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
@@ -3618,7 +3618,7 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>46.711714</t>
+          <t>864.864933</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -3635,39 +3635,31 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0xab77c0bf2f6ec1315e378c5db8b6863eb08357a9b49d9ba43bcce724926da176</t>
+          <t>0x54e4c2b9fcb34a87d3118c2c4aa1d528e53ecdeb3b19d58ec93ceabdcf9789a0</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>155.22388</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1.5175</t>
+          <t>1.1625</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>Colon de Santa Fe -0.5</t>
-        </is>
-      </c>
+          <t>Under/Over (1)</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -3675,27 +3667,27 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Colon de Santa Fe vs San Telmo</t>
+          <t>Club Atletico Mitre de Santiago del Estero vs Defensores de Belgrano Buenos Aires</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Colon de Santa Fe</t>
+          <t>Club Atletico Mitre de Santiago del Estero</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Defensores de Belgrano Buenos Aires</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>0x12375b1d9ef51c6465eb968d63b1ce25f63b0af22de8742ede4e1070f2e04c6b</t>
+          <t>0x4f7afe558099a628e7275525f608e3e5d976f6f0ae76324c03ac2a8d33384e1b</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>L19683494</t>
+          <t>L19683493</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -3720,17 +3712,17 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>1786302968</t>
+          <t>1786303551</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>1786300200</t>
+          <t>1786302000</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>2.801932</t>
+          <t>955.223877</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -3747,39 +3739,31 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0x7262b8ffc279b263369649339936e85dc19d4d92bf11fad680b40a45ad4a7442</t>
+          <t>0xac12d313bf6318f639126e42c96989b9e78cbb4aeafba2d7a6842ecaab1d4679</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
-          <t>23.24</t>
+          <t>29.36999</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>1.3388</t>
+          <t>1.6288</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>Colon de Santa Fe -1</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -3787,27 +3771,27 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Colon de Santa Fe vs San Telmo</t>
+          <t>Racing de Cordoba vs San Miguel</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Colon de Santa Fe</t>
+          <t>Racing de Cordoba</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0x4b323aab38dd8f5096dcd1965ce7dc05c69ab73371e55e810b7a5aee356bf244</t>
+          <t>0x48447168804e92d195e0c849cfb7ae548e076f102e1005f3756585b3d18ea65c</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>L19683494</t>
+          <t>L19683501</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -3832,17 +3816,17 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>1786302417</t>
+          <t>1786303457</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>1786300200</t>
+          <t>1786302000</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>68.605166</t>
+          <t>46.711714</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -3859,31 +3843,39 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0xaef8a42b6335c8c59cb7bb616441203e8516097ce0e7adb9c1dfe622d7b8a46a</t>
+          <t>0xab77c0bf2f6ec1315e378c5db8b6863eb08357a9b49d9ba43bcce724926da176</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr"/>
+          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>14.3554</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>1.0513</t>
+          <t>1.5175</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr"/>
+          <t>Asian Handicap (-0.5)</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Colon de Santa Fe -0.5</t>
+        </is>
+      </c>
       <c r="H33" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -3891,27 +3883,27 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Deportivo Moron vs Acassuso</t>
+          <t>Colon de Santa Fe vs San Telmo</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Deportivo Moron</t>
+          <t>Colon de Santa Fe</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>0x7514a255ce41be3c5db9f8849ba04e78dab80f02d1fe78c2aae82bbc843a9745</t>
+          <t>0x12375b1d9ef51c6465eb968d63b1ce25f63b0af22de8742ede4e1070f2e04c6b</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>L19683452</t>
+          <t>L19683494</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -3936,17 +3928,17 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>1786301685</t>
+          <t>1786302968</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>1786298400</t>
+          <t>1786300200</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>280.105366</t>
+          <t>2.801932</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -3963,7 +3955,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0x9cd0c1e560dfbdd3bb0ca9522422167bdbc75ef5c7813dbe00ce4bee50d0f1be</t>
+          <t>0x7262b8ffc279b263369649339936e85dc19d4d92bf11fad680b40a45ad4a7442</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3971,23 +3963,31 @@
           <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr"/>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>13.80272</t>
+          <t>23.24</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>1.0488</t>
+          <t>1.3388</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr"/>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Colon de Santa Fe -1</t>
+        </is>
+      </c>
       <c r="H34" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -3995,27 +3995,27 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Deportivo Moron vs Acassuso</t>
+          <t>Colon de Santa Fe vs San Telmo</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Deportivo Moron</t>
+          <t>Colon de Santa Fe</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0x7514a255ce41be3c5db9f8849ba04e78dab80f02d1fe78c2aae82bbc843a9745</t>
+          <t>0x4b323aab38dd8f5096dcd1965ce7dc05c69ab73371e55e810b7a5aee356bf244</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>L19683452</t>
+          <t>L19683494</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -4040,17 +4040,17 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>1786301534</t>
+          <t>1786302417</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>1786298400</t>
+          <t>1786300200</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>283.132718</t>
+          <t>68.605166</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -4067,7 +4067,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0x9036645c2b6fdeee93c9912e60b360f0e894db0b98a32ed8106dd074362ac356</t>
+          <t>0xaef8a42b6335c8c59cb7bb616441203e8516097ce0e7adb9c1dfe622d7b8a46a</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4075,19 +4075,15 @@
           <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
-          <t>37.59</t>
+          <t>14.3554</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>1.1225</t>
+          <t>1.0513</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -4095,11 +4091,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>CA Colegiales</t>
-        </is>
-      </c>
+      <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -4107,27 +4099,27 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>CA Colegiales vs Patronato</t>
+          <t>Deportivo Moron vs Acassuso</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>CA Colegiales</t>
+          <t>Deportivo Moron</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>0x6033340ba69fb7874ae22715f395c0926449aa18c6ec5295e2568fe9a173664d</t>
+          <t>0x7514a255ce41be3c5db9f8849ba04e78dab80f02d1fe78c2aae82bbc843a9745</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>L19683449</t>
+          <t>L19683452</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -4152,7 +4144,7 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>1786301228</t>
+          <t>1786301685</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
@@ -4162,7 +4154,7 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>306.857143</t>
+          <t>280.105366</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
@@ -4179,39 +4171,31 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0xd9eff492baa46fea0da1221b63ca70a7e18beec129de6ebec5453a1b9e6bfcf8</t>
+          <t>0x9cd0c1e560dfbdd3bb0ca9522422167bdbc75ef5c7813dbe00ce4bee50d0f1be</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>13.80272</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>1.4263</t>
+          <t>1.0488</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Asian Handicap (0.5)</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>CA Colegiales +0.5</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -4219,27 +4203,27 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>CA Colegiales vs Patronato</t>
+          <t>Deportivo Moron vs Acassuso</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>CA Colegiales</t>
+          <t>Deportivo Moron</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>0xf03b2761ed02376d644cd19d08d1923efb50cd17956a930c587e812207a86746</t>
+          <t>0x7514a255ce41be3c5db9f8849ba04e78dab80f02d1fe78c2aae82bbc843a9745</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>L19683449</t>
+          <t>L19683452</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -4264,7 +4248,7 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>1786301216</t>
+          <t>1786301534</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
@@ -4274,7 +4258,7 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>46.920821</t>
+          <t>283.132718</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
@@ -4291,12 +4275,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0xc72322e8ff04e28165d90bbcfa3c4b34aa19dd5fc1215e13ba7e1ce6362a9292</t>
+          <t>0x9036645c2b6fdeee93c9912e60b360f0e894db0b98a32ed8106dd074362ac356</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -4306,12 +4290,12 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>7.93</t>
+          <t>37.59</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>1.4263</t>
+          <t>1.1225</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -4321,7 +4305,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Racing de Cordoba</t>
+          <t>CA Colegiales</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -4331,27 +4315,27 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Racing de Cordoba vs San Miguel</t>
+          <t>CA Colegiales vs Patronato</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Racing de Cordoba</t>
+          <t>CA Colegiales</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>0x48447168804e92d195e0c849cfb7ae548e076f102e1005f3756585b3d18ea65c</t>
+          <t>0x6033340ba69fb7874ae22715f395c0926449aa18c6ec5295e2568fe9a173664d</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>L19683501</t>
+          <t>L19683449</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -4376,17 +4360,17 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>1786301162</t>
+          <t>1786301228</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>1786302000</t>
+          <t>1786298400</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>18.604106</t>
+          <t>306.857143</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
@@ -4403,12 +4387,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0xd37a1d074e8819ce033a62d6fe3bb026c46529f33aed65aaac63e3d53cb8ce3e</t>
+          <t>0xd9eff492baa46fea0da1221b63ca70a7e18beec129de6ebec5453a1b9e6bfcf8</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>0x5022174051792ac42d3af7Ff6bC9cf78a6aE3f32</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -4418,22 +4402,22 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>1.4287</t>
+          <t>1.4263</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Under/Over (0.5)</t>
+          <t>Asian Handicap (0.5)</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Over 0.5</t>
+          <t>CA Colegiales +0.5</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -4443,27 +4427,27 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Atlanta vs Temperley</t>
+          <t>CA Colegiales vs Patronato</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>CA Colegiales</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>0x84c2bb083fa51c1fc591f5ac9524e09d26434823e44ca466e2af8bd17ae651cb</t>
+          <t>0xf03b2761ed02376d644cd19d08d1923efb50cd17956a930c587e812207a86746</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>L19683448</t>
+          <t>L19683449</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -4488,17 +4472,17 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>1786300699</t>
+          <t>1786301216</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>1786294800</t>
+          <t>1786298400</t>
         </is>
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>11.661808</t>
+          <t>46.920821</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
@@ -4515,31 +4499,39 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0x0199716d54c5764cbf1a6783da6c106cf378f2c6b96892a13d7019f5cb41b3fa</t>
+          <t>0xc72322e8ff04e28165d90bbcfa3c4b34aa19dd5fc1215e13ba7e1ce6362a9292</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>16.84</t>
+          <t>7.93</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>1.1262</t>
+          <t>1.4263</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Under/Over (0.5)</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Racing de Cordoba</t>
+        </is>
+      </c>
       <c r="H39" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -4547,27 +4539,27 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Godoy Cruz vs Chaco For Ever</t>
+          <t>Racing de Cordoba vs San Miguel</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Racing de Cordoba</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>0x9c696117152178b9240c2e3eddca6b53432d4a4937a20042677cd1f666604f23</t>
+          <t>0x48447168804e92d195e0c849cfb7ae548e076f102e1005f3756585b3d18ea65c</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>L19683484</t>
+          <t>L19683501</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -4592,17 +4584,17 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>1786300516</t>
+          <t>1786301162</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>1786303800</t>
+          <t>1786302000</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>133.386139</t>
+          <t>18.604106</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
@@ -4619,31 +4611,39 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0x84f162af96f80a1f61f37a3b12a3dab48dcffde9bd10d0cea022df759f18111f</t>
+          <t>0xd37a1d074e8819ce033a62d6fe3bb026c46529f33aed65aaac63e3d53cb8ce3e</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr"/>
+          <t>0x5022174051792ac42d3af7Ff6bC9cf78a6aE3f32</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>36.84547</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>1.1362</t>
+          <t>1.4287</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Primera Nacional</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr"/>
+          <t>Under/Over (0.5)</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Over 0.5</t>
+        </is>
+      </c>
       <c r="H40" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -4651,27 +4651,27 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Colon de Santa Fe vs San Telmo</t>
+          <t>Atlanta vs Temperley</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Colon de Santa Fe</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>0xbca9ed7d23a7df6c8ab98ab2ffc6649f2d4bd3d9007bd0ecf103e453c87addac</t>
+          <t>0x84c2bb083fa51c1fc591f5ac9524e09d26434823e44ca466e2af8bd17ae651cb</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>L19683494</t>
+          <t>L19683448</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -4696,17 +4696,17 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>1786300513</t>
+          <t>1786300699</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>1786300200</t>
+          <t>1786294800</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>270.425468</t>
+          <t>11.661808</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
@@ -4723,39 +4723,31 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0x2f3773fa15124937ec4965274c782b70d022a4fb2a2c8e85fe36a66e0dcc1a53</t>
+          <t>0x0199716d54c5764cbf1a6783da6c106cf378f2c6b96892a13d7019f5cb41b3fa</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>16.84</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>1.2563</t>
+          <t>1.1262</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>San Miguel</t>
-        </is>
-      </c>
+          <t>Under/Over (0.5)</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -4763,27 +4755,27 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Racing de Cordoba vs San Miguel</t>
+          <t>Godoy Cruz vs Chaco For Ever</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Racing de Cordoba</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>0x8ddab476b71709486e3a0e2118fafcb483076bd09c1c25dcce66244486fed688</t>
+          <t>0x9c696117152178b9240c2e3eddca6b53432d4a4937a20042677cd1f666604f23</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>L19683501</t>
+          <t>L19683484</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -4808,17 +4800,17 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>1786300245</t>
+          <t>1786300516</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>1786302000</t>
+          <t>1786303800</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>3.902439</t>
+          <t>133.386139</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
@@ -4835,27 +4827,23 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0x4334abae5afdbf026c92af25200b83381434248bdfca39224de3957cba46f6e4</t>
+          <t>0x84f162af96f80a1f61f37a3b12a3dab48dcffde9bd10d0cea022df759f18111f</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr">
         <is>
-          <t>52.38</t>
+          <t>36.84547</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>1.675</t>
+          <t>1.1362</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -4863,11 +4851,7 @@
           <t>Primera Nacional</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>CA Colegiales 0</t>
-        </is>
-      </c>
+      <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -4875,27 +4859,27 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>CA Colegiales vs Patronato</t>
+          <t>Colon de Santa Fe vs San Telmo</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>CA Colegiales</t>
+          <t>Colon de Santa Fe</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>0x3fa48fbf2a59e0b45def889e06df3d2da646e9465f9af4f1b88581fea7fb4496</t>
+          <t>0xbca9ed7d23a7df6c8ab98ab2ffc6649f2d4bd3d9007bd0ecf103e453c87addac</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>L19683449</t>
+          <t>L19683494</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -4920,17 +4904,17 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>1786300042</t>
+          <t>1786300513</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>1786298400</t>
+          <t>1786300200</t>
         </is>
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>77.6</t>
+          <t>270.425468</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
@@ -4947,12 +4931,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0xad7255fad3f7d526c2f80d7968fa11121b17d106e3df35095d9b411cead706b0</t>
+          <t>0x2f3773fa15124937ec4965274c782b70d022a4fb2a2c8e85fe36a66e0dcc1a53</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -4962,12 +4946,12 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>3.02932</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>1.2325</t>
+          <t>1.2563</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -5032,7 +5016,7 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>1786298930</t>
+          <t>1786300245</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
@@ -5042,7 +5026,7 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>13.029333</t>
+          <t>3.902439</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
@@ -5059,7 +5043,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0x972e5a678ec56c15f03cbf0d14d7070ad000111adf76887dc34cc27780792e32</t>
+          <t>0x4334abae5afdbf026c92af25200b83381434248bdfca39224de3957cba46f6e4</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5067,23 +5051,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr"/>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>24.07997</t>
+          <t>52.38</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>1.8675</t>
+          <t>1.675</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr"/>
+          <t>Primera Nacional</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>CA Colegiales 0</t>
+        </is>
+      </c>
       <c r="H44" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -5091,27 +5083,27 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Godoy Cruz vs Chaco For Ever</t>
+          <t>CA Colegiales vs Patronato</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>CA Colegiales</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>0x9c19e4c1fd9646506f8ea14e2b1be19b49a5ab4dc1a7bf40167705a4ae2b338b</t>
+          <t>0x3fa48fbf2a59e0b45def889e06df3d2da646e9465f9af4f1b88581fea7fb4496</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>L19683484</t>
+          <t>L19683449</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -5136,17 +5128,17 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>1786297771</t>
+          <t>1786300042</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>1786303800</t>
+          <t>1786298400</t>
         </is>
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>27.75789</t>
+          <t>77.6</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
@@ -5163,12 +5155,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0x1da1f134f1ec859a8260a79216b9030b9f0b715d9a51d09741ff884111dcde2b</t>
+          <t>0xad7255fad3f7d526c2f80d7968fa11121b17d106e3df35095d9b411cead706b0</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>0x311AE302984D8b1cf53D6bfB0a6672f05c423AE6</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -5178,22 +5170,22 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>37.76669</t>
+          <t>3.02932</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>1.5837</t>
+          <t>1.2325</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Godoy Cruz -0.5</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -5203,27 +5195,27 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Godoy Cruz vs Chaco For Ever</t>
+          <t>Racing de Cordoba vs San Miguel</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Racing de Cordoba</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>0xb2c04ce7cffc1005eb6199d3c34d31b109e8af04a357b4f8eb9f6b8362ba33c2</t>
+          <t>0x8ddab476b71709486e3a0e2118fafcb483076bd09c1c25dcce66244486fed688</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>L19683484</t>
+          <t>L19683501</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -5248,17 +5240,17 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>1786297676</t>
+          <t>1786298930</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>1786303800</t>
+          <t>1786302000</t>
         </is>
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>64.696685</t>
+          <t>13.029333</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
@@ -5275,7 +5267,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0xfccc36b3cd4c4e2276a7540f5bb389b40f91c9998d31903af7864027f93d335e</t>
+          <t>0x972e5a678ec56c15f03cbf0d14d7070ad000111adf76887dc34cc27780792e32</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5283,19 +5275,15 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr">
         <is>
-          <t>56.81</t>
+          <t>24.07997</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>1.3588</t>
+          <t>1.8675</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -5303,11 +5291,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+      <c r="G46" t="inlineStr"/>
       <c r="H46" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -5315,27 +5299,27 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>CA Los Andes vs Ferro Carril Oeste</t>
+          <t>Godoy Cruz vs Chaco For Ever</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>CA Los Andes</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>0x834e52f6ff115c72424372c131d41b8d94cffe6e0131918e3f85e2146509d14b</t>
+          <t>0x9c19e4c1fd9646506f8ea14e2b1be19b49a5ab4dc1a7bf40167705a4ae2b338b</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>L19659153</t>
+          <t>L19683484</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -5360,17 +5344,17 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>1786297373</t>
+          <t>1786297771</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>1786296600</t>
+          <t>1786303800</t>
         </is>
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>158.355401</t>
+          <t>27.75789</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
@@ -5387,31 +5371,39 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0x48c1aed95e65b653ffb51380d6066948766a0030b4adf3bf05d152a5766c29cf</t>
+          <t>0x1da1f134f1ec859a8260a79216b9030b9f0b715d9a51d09741ff884111dcde2b</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr"/>
+          <t>0x311AE302984D8b1cf53D6bfB0a6672f05c423AE6</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>37.76669</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>1.6425</t>
+          <t>1.5837</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr"/>
+          <t>Asian Handicap (-0.5)</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Godoy Cruz -0.5</t>
+        </is>
+      </c>
       <c r="H47" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -5419,27 +5411,27 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Colon de Santa Fe vs San Telmo</t>
+          <t>Godoy Cruz vs Chaco For Ever</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Colon de Santa Fe</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>0x79905ae58e04af69981e4a95c3d57b98dc3c1dd1d3e7aeb4e6a7640714001f3b</t>
+          <t>0xb2c04ce7cffc1005eb6199d3c34d31b109e8af04a357b4f8eb9f6b8362ba33c2</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>L19683494</t>
+          <t>L19683484</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -5464,17 +5456,17 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>1786293588</t>
+          <t>1786297676</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>1786300200</t>
+          <t>1786303800</t>
         </is>
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>15.564202</t>
+          <t>64.696685</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
@@ -5491,31 +5483,39 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0x3d4ee2d1cf7066373ffe56d01727fc04ce4ae0e1203194a2877d6ba90d9d4fcb</t>
+          <t>0xfccc36b3cd4c4e2276a7540f5bb389b40f91c9998d31903af7864027f93d335e</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>16.53143</t>
+          <t>56.81</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>1.3438</t>
+          <t>1.3588</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Primera Nacional</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H48" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -5523,27 +5523,27 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Atlanta vs Temperley</t>
+          <t>CA Los Andes vs Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>CA Los Andes</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>0xc67c753c7ce425d2b225c54e0abf1308c3593fa6789a95fd59198b3a0f7a3ddd</t>
+          <t>0x834e52f6ff115c72424372c131d41b8d94cffe6e0131918e3f85e2146509d14b</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>L19683448</t>
+          <t>L19659153</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -5568,17 +5568,17 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>1786293565</t>
+          <t>1786297373</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>1786294800</t>
+          <t>1786296600</t>
         </is>
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>48.091433</t>
+          <t>158.355401</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
@@ -5595,7 +5595,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0x5decd74680fc49716c54620aa922234edac874fb77b6369067e932fb5a40aed8</t>
+          <t>0x48c1aed95e65b653ffb51380d6066948766a0030b4adf3bf05d152a5766c29cf</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5606,17 +5606,17 @@
       <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr">
         <is>
-          <t>16.98847</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.6425</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Primera Nacional</t>
+          <t>Asian Handicap (-1.5)</t>
         </is>
       </c>
       <c r="G49" t="inlineStr"/>
@@ -5627,27 +5627,27 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>San Martin Tucuman vs San Martín de San Juan</t>
+          <t>Colon de Santa Fe vs San Telmo</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>San Martin Tucuman</t>
+          <t>Colon de Santa Fe</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>San Martín de San Juan</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>0x4f02331cd42a68f65ea16d62aac0c6b123d9400d12a4d556f3a72df894da02fb</t>
+          <t>0x79905ae58e04af69981e4a95c3d57b98dc3c1dd1d3e7aeb4e6a7640714001f3b</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>L19682528</t>
+          <t>L19683494</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -5672,17 +5672,17 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>1786293511</t>
+          <t>1786293588</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>1786309200</t>
+          <t>1786300200</t>
         </is>
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>48.538486</t>
+          <t>15.564202</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
@@ -5699,28 +5699,28 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0x6376c34d63b4968409b909753114511b32d1413abbfce5d71dcd6fa7bb384028</t>
+          <t>0x3d4ee2d1cf7066373ffe56d01727fc04ce4ae0e1203194a2877d6ba90d9d4fcb</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr">
         <is>
-          <t>30.89</t>
+          <t>16.53143</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>1.6425</t>
+          <t>1.3438</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
+          <t>Primera Nacional</t>
         </is>
       </c>
       <c r="G50" t="inlineStr"/>
@@ -5731,27 +5731,27 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Colon de Santa Fe vs San Telmo</t>
+          <t>Atlanta vs Temperley</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Colon de Santa Fe</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>0x79905ae58e04af69981e4a95c3d57b98dc3c1dd1d3e7aeb4e6a7640714001f3b</t>
+          <t>0xc67c753c7ce425d2b225c54e0abf1308c3593fa6789a95fd59198b3a0f7a3ddd</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>L19683494</t>
+          <t>L19683448</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -5776,17 +5776,17 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>1786293434</t>
+          <t>1786293565</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>1786300200</t>
+          <t>1786294800</t>
         </is>
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>48.077821</t>
+          <t>48.091433</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
@@ -5803,7 +5803,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0xa534180ddbde4d456a67f71365d2341259c4ca0b20e45041701c1d345202335e</t>
+          <t>0x5decd74680fc49716c54620aa922234edac874fb77b6369067e932fb5a40aed8</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5814,17 +5814,17 @@
       <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr">
         <is>
-          <t>13.52</t>
+          <t>16.98847</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>1.6325</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>Primera Nacional</t>
         </is>
       </c>
       <c r="G51" t="inlineStr"/>
@@ -5835,27 +5835,27 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Quilmes vs Club Almagro</t>
+          <t>San Martin Tucuman vs San Martín de San Juan</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>San Martin Tucuman</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>Club Almagro</t>
+          <t>San Martín de San Juan</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>0x86a790846c1cb1bed065ac37c41b727461e30e0a9e0f9e2370ef61f6213ed31f</t>
+          <t>0x4f02331cd42a68f65ea16d62aac0c6b123d9400d12a4d556f3a72df894da02fb</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>L19683499</t>
+          <t>L19682528</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -5880,17 +5880,17 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>1786293430</t>
+          <t>1786293511</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>1786305600</t>
+          <t>1786309200</t>
         </is>
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>21.375494</t>
+          <t>48.538486</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
@@ -5907,7 +5907,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0xe6cbce05bf55e4a2647eb39e1cb6d7afdafec60905e09f42fb3552a02a5fcbd6</t>
+          <t>0x6376c34d63b4968409b909753114511b32d1413abbfce5d71dcd6fa7bb384028</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5918,17 +5918,17 @@
       <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr">
         <is>
-          <t>16.88999</t>
+          <t>30.89</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>1.6325</t>
+          <t>1.6425</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>Asian Handicap (-1.5)</t>
         </is>
       </c>
       <c r="G52" t="inlineStr"/>
@@ -5939,27 +5939,27 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Quilmes vs Club Almagro</t>
+          <t>Colon de Santa Fe vs San Telmo</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Colon de Santa Fe</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>Club Almagro</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>0x86a790846c1cb1bed065ac37c41b727461e30e0a9e0f9e2370ef61f6213ed31f</t>
+          <t>0x79905ae58e04af69981e4a95c3d57b98dc3c1dd1d3e7aeb4e6a7640714001f3b</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>L19683499</t>
+          <t>L19683494</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -5984,17 +5984,17 @@
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>1786293428</t>
+          <t>1786293434</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>1786305600</t>
+          <t>1786300200</t>
         </is>
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>26.703542</t>
+          <t>48.077821</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
@@ -6011,7 +6011,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0xae3b69e222676c5f5930a25ee6fc677945888fbd4b45894897e8c0b45b324e25</t>
+          <t>0xa534180ddbde4d456a67f71365d2341259c4ca0b20e45041701c1d345202335e</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -6022,17 +6022,17 @@
       <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr">
         <is>
-          <t>12.72</t>
+          <t>13.52</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>1.4512</t>
+          <t>1.6325</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G53" t="inlineStr"/>
@@ -6043,27 +6043,27 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>CA Los Andes vs Ferro Carril Oeste</t>
+          <t>Quilmes vs Club Almagro</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>CA Los Andes</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Club Almagro</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>0x555a8472fba9017aa83a61e5e7cf7b05dc2822d1d1cc6174412760fc412637f7</t>
+          <t>0x86a790846c1cb1bed065ac37c41b727461e30e0a9e0f9e2370ef61f6213ed31f</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>L19659153</t>
+          <t>L19683499</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -6088,17 +6088,17 @@
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>1786288547</t>
+          <t>1786293430</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>1786296600</t>
+          <t>1786305600</t>
         </is>
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>28.188366</t>
+          <t>21.375494</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
@@ -6115,28 +6115,28 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0x4bb954aaa9ecad68c0eb53f2341bb75f7b8daa072a3f151571ab136be22b78df</t>
+          <t>0xe6cbce05bf55e4a2647eb39e1cb6d7afdafec60905e09f42fb3552a02a5fcbd6</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>0x71CE4A2C734a76f4C86A0D80122C4014c1F52F6e</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr">
         <is>
-          <t>29.37999</t>
+          <t>16.88999</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>1.6113</t>
+          <t>1.6325</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G54" t="inlineStr"/>
@@ -6147,27 +6147,27 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>CA Los Andes vs Ferro Carril Oeste</t>
+          <t>Quilmes vs Club Almagro</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>CA Los Andes</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Club Almagro</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>0x653af58a9c77cb072171a76bcd9ca8adee427601f3ecd186c8154c81f8736395</t>
+          <t>0x86a790846c1cb1bed065ac37c41b727461e30e0a9e0f9e2370ef61f6213ed31f</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>L19659153</t>
+          <t>L19683499</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -6192,17 +6192,17 @@
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>1786288517</t>
+          <t>1786293428</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>1786296600</t>
+          <t>1786305600</t>
         </is>
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>48.065423</t>
+          <t>26.703542</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
@@ -6219,7 +6219,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0xd5a2ddd8c8b6cc9bdb1c507276d3a192a5f24d46e2d3c01bfb07011263030bdd</t>
+          <t>0xae3b69e222676c5f5930a25ee6fc677945888fbd4b45894897e8c0b45b324e25</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -6230,17 +6230,17 @@
       <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr">
         <is>
-          <t>5.67</t>
+          <t>12.72</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>1.2975</t>
+          <t>1.4512</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Primera Nacional</t>
+          <t>Under/Over (1.5)</t>
         </is>
       </c>
       <c r="G55" t="inlineStr"/>
@@ -6251,27 +6251,27 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>CA Colegiales vs Patronato</t>
+          <t>CA Los Andes vs Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>CA Colegiales</t>
+          <t>CA Los Andes</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>0x710e5bf3f6759bd93c59fc8788916c16c7302071968dfba2d053e2d10f7858bf</t>
+          <t>0x555a8472fba9017aa83a61e5e7cf7b05dc2822d1d1cc6174412760fc412637f7</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>L19683449</t>
+          <t>L19659153</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -6296,17 +6296,17 @@
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>1786288450</t>
+          <t>1786288547</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>1786298400</t>
+          <t>1786296600</t>
         </is>
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>19.058824</t>
+          <t>28.188366</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
@@ -6323,28 +6323,28 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0xad9f4feea88f83ae2e46756e7d54faa300a82e055c196c70c84019780ecb560c</t>
+          <t>0x4bb954aaa9ecad68c0eb53f2341bb75f7b8daa072a3f151571ab136be22b78df</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x71CE4A2C734a76f4C86A0D80122C4014c1F52F6e</t>
         </is>
       </c>
       <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr">
         <is>
-          <t>21.69</t>
+          <t>29.37999</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>1.4512</t>
+          <t>1.6113</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
+          <t>Under/Over (2)</t>
         </is>
       </c>
       <c r="G56" t="inlineStr"/>
@@ -6370,7 +6370,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>0x555a8472fba9017aa83a61e5e7cf7b05dc2822d1d1cc6174412760fc412637f7</t>
+          <t>0x653af58a9c77cb072171a76bcd9ca8adee427601f3ecd186c8154c81f8736395</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -6400,7 +6400,7 @@
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>1786288436</t>
+          <t>1786288517</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
@@ -6410,7 +6410,7 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>48.066482</t>
+          <t>48.065423</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
@@ -6427,7 +6427,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>0x168e5ea2716a187c94a1c77c4c8b2523b31163ed118e4986c68c79a21d013932</t>
+          <t>0xd5a2ddd8c8b6cc9bdb1c507276d3a192a5f24d46e2d3c01bfb07011263030bdd</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -6438,17 +6438,17 @@
       <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr">
         <is>
-          <t>29.38716</t>
+          <t>5.67</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>1.6113</t>
+          <t>1.2975</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
+          <t>Primera Nacional</t>
         </is>
       </c>
       <c r="G57" t="inlineStr"/>
@@ -6459,27 +6459,27 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>CA Los Andes vs Ferro Carril Oeste</t>
+          <t>CA Colegiales vs Patronato</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>CA Los Andes</t>
+          <t>CA Colegiales</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>0x653af58a9c77cb072171a76bcd9ca8adee427601f3ecd186c8154c81f8736395</t>
+          <t>0x710e5bf3f6759bd93c59fc8788916c16c7302071968dfba2d053e2d10f7858bf</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>L19659153</t>
+          <t>L19683449</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -6504,17 +6504,17 @@
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>1786288436</t>
+          <t>1786288450</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>1786296600</t>
+          <t>1786298400</t>
         </is>
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>48.077153</t>
+          <t>19.058824</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
@@ -6531,39 +6531,31 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>0x680d5db234b802aa2845f16e9d23d635dd89870065c6bfb6f6f1bde25c321bae</t>
+          <t>0xad9f4feea88f83ae2e46756e7d54faa300a82e055c196c70c84019780ecb560c</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr"/>
       <c r="D58" t="inlineStr">
         <is>
-          <t>24.36</t>
+          <t>21.69</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>1.475</t>
+          <t>1.4512</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>CA Colegiales -0.5</t>
-        </is>
-      </c>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr"/>
       <c r="H58" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -6571,27 +6563,27 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>CA Colegiales vs Patronato</t>
+          <t>CA Los Andes vs Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>CA Colegiales</t>
+          <t>CA Los Andes</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>0x50a3f0e4e982cdda0b9c4b9e2e1c50c67d93fbf7a068b43dbdf733c0b8d09050</t>
+          <t>0x555a8472fba9017aa83a61e5e7cf7b05dc2822d1d1cc6174412760fc412637f7</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>L19683449</t>
+          <t>L19659153</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -6616,17 +6608,17 @@
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>1786287181</t>
+          <t>1786288436</t>
         </is>
       </c>
       <c r="S58" t="inlineStr">
         <is>
-          <t>1786298400</t>
+          <t>1786296600</t>
         </is>
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>51.284211</t>
+          <t>48.066482</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
@@ -6643,7 +6635,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>0x5a5b6f41ac2a593747a9419c020abd417423350c2cf0a14d8cb9ef8a25d04f18</t>
+          <t>0x168e5ea2716a187c94a1c77c4c8b2523b31163ed118e4986c68c79a21d013932</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6654,17 +6646,17 @@
       <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr">
         <is>
-          <t>8.81755</t>
+          <t>29.38716</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>1.6325</t>
+          <t>1.6113</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>Under/Over (2)</t>
         </is>
       </c>
       <c r="G59" t="inlineStr"/>
@@ -6675,27 +6667,27 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Quilmes vs Club Almagro</t>
+          <t>CA Los Andes vs Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>CA Los Andes</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>Club Almagro</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>0x86a790846c1cb1bed065ac37c41b727461e30e0a9e0f9e2370ef61f6213ed31f</t>
+          <t>0x653af58a9c77cb072171a76bcd9ca8adee427601f3ecd186c8154c81f8736395</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>L19683499</t>
+          <t>L19659153</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -6720,17 +6712,17 @@
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>1786284071</t>
+          <t>1786288436</t>
         </is>
       </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t>1786305600</t>
+          <t>1786296600</t>
         </is>
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>13.940791</t>
+          <t>48.077153</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
@@ -6747,31 +6739,39 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>0x9ae6e679c8fc9ed20977676ba3160d389287dd8808ea2610d0f168f9c3a42c11</t>
+          <t>0x680d5db234b802aa2845f16e9d23d635dd89870065c6bfb6f6f1bde25c321bae</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr"/>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>21.58999</t>
+          <t>24.36</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>1.6325</t>
+          <t>1.475</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr"/>
+          <t>Asian Handicap (-0.5)</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>CA Colegiales -0.5</t>
+        </is>
+      </c>
       <c r="H60" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -6779,27 +6779,27 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Quilmes vs Club Almagro</t>
+          <t>CA Colegiales vs Patronato</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>CA Colegiales</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>Club Almagro</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>0x86a790846c1cb1bed065ac37c41b727461e30e0a9e0f9e2370ef61f6213ed31f</t>
+          <t>0x50a3f0e4e982cdda0b9c4b9e2e1c50c67d93fbf7a068b43dbdf733c0b8d09050</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>L19683499</t>
+          <t>L19683449</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
@@ -6824,17 +6824,17 @@
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>1786284003</t>
+          <t>1786287181</t>
         </is>
       </c>
       <c r="S60" t="inlineStr">
         <is>
-          <t>1786305600</t>
+          <t>1786298400</t>
         </is>
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>34.134372</t>
+          <t>51.284211</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
@@ -6851,7 +6851,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>0x6771b333646b031b4dc4cfea8f533b040a6ed0a66012cdc416a7aaa5b89f7988</t>
+          <t>0x5a5b6f41ac2a593747a9419c020abd417423350c2cf0a14d8cb9ef8a25d04f18</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6862,17 +6862,17 @@
       <c r="C61" t="inlineStr"/>
       <c r="D61" t="inlineStr">
         <is>
-          <t>19.2</t>
+          <t>8.81755</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>1.5425</t>
+          <t>1.6325</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G61" t="inlineStr"/>
@@ -6883,27 +6883,27 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Colon de Santa Fe vs San Telmo</t>
+          <t>Quilmes vs Club Almagro</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>Colon de Santa Fe</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Club Almagro</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>0x4b323aab38dd8f5096dcd1965ce7dc05c69ab73371e55e810b7a5aee356bf244</t>
+          <t>0x86a790846c1cb1bed065ac37c41b727461e30e0a9e0f9e2370ef61f6213ed31f</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>L19683494</t>
+          <t>L19683499</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
@@ -6928,17 +6928,17 @@
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>1786283290</t>
+          <t>1786284071</t>
         </is>
       </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t>1786300200</t>
+          <t>1786305600</t>
         </is>
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>35.391705</t>
+          <t>13.940791</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
@@ -6955,7 +6955,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>0x8809f3e942a9cc8dca00d48b07cfe53a328d6ba2b60742c63e144e3d8cf2eaa1</t>
+          <t>0x9ae6e679c8fc9ed20977676ba3160d389287dd8808ea2610d0f168f9c3a42c11</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6966,17 +6966,17 @@
       <c r="C62" t="inlineStr"/>
       <c r="D62" t="inlineStr">
         <is>
-          <t>23.25749</t>
+          <t>21.58999</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>1.4838</t>
+          <t>1.6325</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G62" t="inlineStr"/>
@@ -6987,27 +6987,27 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Colon de Santa Fe vs San Telmo</t>
+          <t>Quilmes vs Club Almagro</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>Colon de Santa Fe</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Club Almagro</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>0xc91217dfcd3944893195656945526d39efcd315aa93101aa312de5303c04d446</t>
+          <t>0x86a790846c1cb1bed065ac37c41b727461e30e0a9e0f9e2370ef61f6213ed31f</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>L19683494</t>
+          <t>L19683499</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
@@ -7032,17 +7032,17 @@
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>1786281248</t>
+          <t>1786284003</t>
         </is>
       </c>
       <c r="S62" t="inlineStr">
         <is>
-          <t>1786300200</t>
+          <t>1786305600</t>
         </is>
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>48.077499</t>
+          <t>34.134372</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
@@ -7059,7 +7059,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>0xe5b95b7ede820952a7e6f5c1b2139a8092b51c4de75567f117f1291461ec6fbe</t>
+          <t>0x6771b333646b031b4dc4cfea8f533b040a6ed0a66012cdc416a7aaa5b89f7988</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -7070,17 +7070,17 @@
       <c r="C63" t="inlineStr"/>
       <c r="D63" t="inlineStr">
         <is>
-          <t>23.55844</t>
+          <t>19.2</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.5425</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G63" t="inlineStr"/>
@@ -7106,7 +7106,7 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>0xc91217dfcd3944893195656945526d39efcd315aa93101aa312de5303c04d446</t>
+          <t>0x4b323aab38dd8f5096dcd1965ce7dc05c69ab73371e55e810b7a5aee356bf244</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
@@ -7136,7 +7136,7 @@
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>1786281243</t>
+          <t>1786283290</t>
         </is>
       </c>
       <c r="S63" t="inlineStr">
@@ -7146,7 +7146,7 @@
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>48.078449</t>
+          <t>35.391705</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
@@ -7163,7 +7163,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>0x4d872ac34cfff98634d3d50362fe725a3f4ea55d64ddd9e3d7d811b073f350ab</t>
+          <t>0x8809f3e942a9cc8dca00d48b07cfe53a328d6ba2b60742c63e144e3d8cf2eaa1</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -7174,17 +7174,17 @@
       <c r="C64" t="inlineStr"/>
       <c r="D64" t="inlineStr">
         <is>
-          <t>17.30813</t>
+          <t>23.25749</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.4838</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
+          <t>Under/Over (2)</t>
         </is>
       </c>
       <c r="G64" t="inlineStr"/>
@@ -7210,7 +7210,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>0xd638a8ee6393f88ca538cc4fe6ac8cdf722bcfe6277a5ebd9387222eade88ba3</t>
+          <t>0xc91217dfcd3944893195656945526d39efcd315aa93101aa312de5303c04d446</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
@@ -7240,7 +7240,7 @@
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>1786281243</t>
+          <t>1786281248</t>
         </is>
       </c>
       <c r="S64" t="inlineStr">
@@ -7250,7 +7250,7 @@
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>48.078139</t>
+          <t>48.077499</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
@@ -7267,7 +7267,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>0x8f782cb5f7b30f6c129f6031ec6368ed75ea36897066f1761d9054013f56567d</t>
+          <t>0xe5b95b7ede820952a7e6f5c1b2139a8092b51c4de75567f117f1291461ec6fbe</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -7278,17 +7278,17 @@
       <c r="C65" t="inlineStr"/>
       <c r="D65" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>23.55844</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>1.4187</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Primera Nacional</t>
+          <t>Under/Over (2)</t>
         </is>
       </c>
       <c r="G65" t="inlineStr"/>
@@ -7299,27 +7299,27 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Club Atletico Mitre de Santiago del Estero vs Defensores de Belgrano Buenos Aires</t>
+          <t>Colon de Santa Fe vs San Telmo</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>Club Atletico Mitre de Santiago del Estero</t>
+          <t>Colon de Santa Fe</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano Buenos Aires</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>0x2d371e1a8a9d98624f046ea3d7126e47308ffbc183b66b1e2fba81e5ae69d7dd</t>
+          <t>0xc91217dfcd3944893195656945526d39efcd315aa93101aa312de5303c04d446</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>L19683493</t>
+          <t>L19683494</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
@@ -7344,17 +7344,17 @@
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>1786280425</t>
+          <t>1786281243</t>
         </is>
       </c>
       <c r="S65" t="inlineStr">
         <is>
-          <t>1786302000</t>
+          <t>1786300200</t>
         </is>
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>23.880597</t>
+          <t>48.078449</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
@@ -7371,7 +7371,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>0xfe8890b155a19f7eb888456b555a7a6d8c293f8ecabeb69d2abd10210f520589</t>
+          <t>0x4d872ac34cfff98634d3d50362fe725a3f4ea55d64ddd9e3d7d811b073f350ab</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -7382,17 +7382,17 @@
       <c r="C66" t="inlineStr"/>
       <c r="D66" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>17.30813</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>1.4475</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
+          <t>Under/Over (1.5)</t>
         </is>
       </c>
       <c r="G66" t="inlineStr"/>
@@ -7418,7 +7418,7 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>0xc91217dfcd3944893195656945526d39efcd315aa93101aa312de5303c04d446</t>
+          <t>0xd638a8ee6393f88ca538cc4fe6ac8cdf722bcfe6277a5ebd9387222eade88ba3</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
@@ -7448,7 +7448,7 @@
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>1786280403</t>
+          <t>1786281243</t>
         </is>
       </c>
       <c r="S66" t="inlineStr">
@@ -7458,7 +7458,7 @@
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>22.346369</t>
+          <t>48.078139</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
@@ -7475,7 +7475,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>0x60e023296ac2f9f58237fa345b3aa08fb4f997dd34c5384f371782bf7bbd5a40</t>
+          <t>0x8f782cb5f7b30f6c129f6031ec6368ed75ea36897066f1761d9054013f56567d</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -7483,31 +7483,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C67" t="inlineStr"/>
       <c r="D67" t="inlineStr">
         <is>
-          <t>26.11999</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>1.5488</t>
+          <t>1.4187</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>Over 2.0</t>
-        </is>
-      </c>
+          <t>Primera Nacional</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr"/>
       <c r="H67" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -7515,27 +7507,27 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Colon de Santa Fe vs San Telmo</t>
+          <t>Club Atletico Mitre de Santiago del Estero vs Defensores de Belgrano Buenos Aires</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>Colon de Santa Fe</t>
+          <t>Club Atletico Mitre de Santiago del Estero</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Defensores de Belgrano Buenos Aires</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>0xc91217dfcd3944893195656945526d39efcd315aa93101aa312de5303c04d446</t>
+          <t>0x2d371e1a8a9d98624f046ea3d7126e47308ffbc183b66b1e2fba81e5ae69d7dd</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>L19683494</t>
+          <t>L19683493</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
@@ -7560,17 +7552,17 @@
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>1786280403</t>
+          <t>1786280425</t>
         </is>
       </c>
       <c r="S67" t="inlineStr">
         <is>
-          <t>1786300200</t>
+          <t>1786302000</t>
         </is>
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>47.599071</t>
+          <t>23.880597</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
@@ -7587,7 +7579,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>0x2d118800c100a2a41a19c2053cbf355561a08867f99163fb40955a4ab012ce39</t>
+          <t>0xfe8890b155a19f7eb888456b555a7a6d8c293f8ecabeb69d2abd10210f520589</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -7598,17 +7590,17 @@
       <c r="C68" t="inlineStr"/>
       <c r="D68" t="inlineStr">
         <is>
-          <t>20.07999</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>1.7363</t>
+          <t>1.4475</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
+          <t>Under/Over (2)</t>
         </is>
       </c>
       <c r="G68" t="inlineStr"/>
@@ -7619,27 +7611,27 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Godoy Cruz vs Chaco For Ever</t>
+          <t>Colon de Santa Fe vs San Telmo</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Colon de Santa Fe</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>0x60e111ebf03c4965ff049e67cf10f93f5cca143023c6104aab59162863b5b8a8</t>
+          <t>0xc91217dfcd3944893195656945526d39efcd315aa93101aa312de5303c04d446</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>L19683484</t>
+          <t>L19683494</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
@@ -7664,17 +7656,17 @@
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>1786279900</t>
+          <t>1786280403</t>
         </is>
       </c>
       <c r="S68" t="inlineStr">
         <is>
-          <t>1786303800</t>
+          <t>1786300200</t>
         </is>
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>27.273331</t>
+          <t>22.346369</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
@@ -7691,7 +7683,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>0x904e2e53a604aa6663de774d4bd9ddf8af7459ef1c4fa1bb14486300917ac211</t>
+          <t>0x60e023296ac2f9f58237fa345b3aa08fb4f997dd34c5384f371782bf7bbd5a40</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -7706,22 +7698,22 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>3.96</t>
+          <t>26.11999</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>1.2837</t>
+          <t>1.5488</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (2)</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Tie</t>
+          <t>Over 2.0</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -7731,27 +7723,27 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Godoy Cruz vs Chaco For Ever</t>
+          <t>Colon de Santa Fe vs San Telmo</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Colon de Santa Fe</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>0x08dce15d4ca4845359c2f121bce305fd3a0fe7422d497000c713e29463c6be79</t>
+          <t>0xc91217dfcd3944893195656945526d39efcd315aa93101aa312de5303c04d446</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>L19683484</t>
+          <t>L19683494</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
@@ -7776,17 +7768,17 @@
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>1786279851</t>
+          <t>1786280403</t>
         </is>
       </c>
       <c r="S69" t="inlineStr">
         <is>
-          <t>1786303800</t>
+          <t>1786300200</t>
         </is>
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>13.955947</t>
+          <t>47.599071</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
@@ -7803,7 +7795,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>0x19a6c0536a5dea88055519ff16050cdde80d42121bb75c5045e3b562a7c1d4bb</t>
+          <t>0x2d118800c100a2a41a19c2053cbf355561a08867f99163fb40955a4ab012ce39</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -7814,17 +7806,17 @@
       <c r="C70" t="inlineStr"/>
       <c r="D70" t="inlineStr">
         <is>
-          <t>7.50547</t>
+          <t>20.07999</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>1.4287</t>
+          <t>1.7363</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-1.5)</t>
         </is>
       </c>
       <c r="G70" t="inlineStr"/>
@@ -7850,7 +7842,7 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>0xa5f02d0d08d0dcc4818948397f0f26c77f90b87182cec4d62ab01f77352671a1</t>
+          <t>0x60e111ebf03c4965ff049e67cf10f93f5cca143023c6104aab59162863b5b8a8</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
@@ -7880,7 +7872,7 @@
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>1786279821</t>
+          <t>1786279900</t>
         </is>
       </c>
       <c r="S70" t="inlineStr">
@@ -7890,7 +7882,7 @@
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>17.505469</t>
+          <t>27.273331</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
@@ -7907,7 +7899,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>0x4c44e2c0c492a5115b342a42a552a040cb800bd582b07c12f1ea9161b861b487</t>
+          <t>0x904e2e53a604aa6663de774d4bd9ddf8af7459ef1c4fa1bb14486300917ac211</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -7915,23 +7907,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C71" t="inlineStr"/>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>11.30844</t>
+          <t>3.96</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.2837</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H71" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -7939,27 +7939,27 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>Deportivo Moron vs Acassuso</t>
+          <t>Godoy Cruz vs Chaco For Ever</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>Deportivo Moron</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>0x108eaba0441fb45ec8e0073e945ae0ac1e138c933e4f2839816cd3198d7dd4d2</t>
+          <t>0x08dce15d4ca4845359c2f121bce305fd3a0fe7422d497000c713e29463c6be79</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>L19683452</t>
+          <t>L19683484</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
@@ -7984,17 +7984,17 @@
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>1786278950</t>
+          <t>1786279851</t>
         </is>
       </c>
       <c r="S71" t="inlineStr">
         <is>
-          <t>1786298400</t>
+          <t>1786303800</t>
         </is>
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>23.078449</t>
+          <t>13.955947</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
@@ -8011,7 +8011,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>0x5a5ccf0d5f6cbac6813d25e4e1e96b25b5c5a4ff8f6378d7e69d6bd3c29295ae</t>
+          <t>0x19a6c0536a5dea88055519ff16050cdde80d42121bb75c5045e3b562a7c1d4bb</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -8022,17 +8022,17 @@
       <c r="C72" t="inlineStr"/>
       <c r="D72" t="inlineStr">
         <is>
-          <t>12.25</t>
+          <t>7.50547</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.4287</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G72" t="inlineStr"/>
@@ -8043,27 +8043,27 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>Deportivo Moron vs Acassuso</t>
+          <t>Godoy Cruz vs Chaco For Ever</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>Deportivo Moron</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>0x108eaba0441fb45ec8e0073e945ae0ac1e138c933e4f2839816cd3198d7dd4d2</t>
+          <t>0xa5f02d0d08d0dcc4818948397f0f26c77f90b87182cec4d62ab01f77352671a1</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>L19683452</t>
+          <t>L19683484</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
@@ -8088,17 +8088,17 @@
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>1786278094</t>
+          <t>1786279821</t>
         </is>
       </c>
       <c r="S72" t="inlineStr">
         <is>
-          <t>1786298400</t>
+          <t>1786303800</t>
         </is>
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>17.505469</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
@@ -8115,7 +8115,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>0x5f3419242a87ff17c0cb508ade95d27a54429124d36280a1dff2efa2fa0b3510</t>
+          <t>0x4c44e2c0c492a5115b342a42a552a040cb800bd582b07c12f1ea9161b861b487</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -8126,17 +8126,17 @@
       <c r="C73" t="inlineStr"/>
       <c r="D73" t="inlineStr">
         <is>
-          <t>20.41999</t>
+          <t>11.30844</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>1.7087</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (2)</t>
         </is>
       </c>
       <c r="G73" t="inlineStr"/>
@@ -8147,27 +8147,27 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>CA Los Andes vs Ferro Carril Oeste</t>
+          <t>Deportivo Moron vs Acassuso</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>CA Los Andes</t>
+          <t>Deportivo Moron</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>0x31115553050eabb8d3f6a72cf2865c16175783383dcfc674615e74ed88cabaee</t>
+          <t>0x108eaba0441fb45ec8e0073e945ae0ac1e138c933e4f2839816cd3198d7dd4d2</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>L19659153</t>
+          <t>L19683452</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
@@ -8192,17 +8192,17 @@
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>1786277884</t>
+          <t>1786278950</t>
         </is>
       </c>
       <c r="S73" t="inlineStr">
         <is>
-          <t>1786296600</t>
+          <t>1786298400</t>
         </is>
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>28.811273</t>
+          <t>23.078449</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
@@ -8219,7 +8219,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>0xe6b14424302d9ef7ea2000cef83e38549f6a38c12d57faa6dd76dd84e631a5ca</t>
+          <t>0x5a5ccf0d5f6cbac6813d25e4e1e96b25b5c5a4ff8f6378d7e69d6bd3c29295ae</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -8230,17 +8230,17 @@
       <c r="C74" t="inlineStr"/>
       <c r="D74" t="inlineStr">
         <is>
-          <t>12.13</t>
+          <t>12.25</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>1.3613</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
+          <t>Under/Over (2)</t>
         </is>
       </c>
       <c r="G74" t="inlineStr"/>
@@ -8266,7 +8266,7 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>0x3f34d112cfb9f093c57a3e094be078f9eea2715f97797e20d86942d58f5cc8d6</t>
+          <t>0x108eaba0441fb45ec8e0073e945ae0ac1e138c933e4f2839816cd3198d7dd4d2</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
@@ -8296,7 +8296,7 @@
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>1786277708</t>
+          <t>1786278094</t>
         </is>
       </c>
       <c r="S74" t="inlineStr">
@@ -8306,7 +8306,7 @@
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>33.577855</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
@@ -8323,7 +8323,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>0xd7a2e43ba1564f619200938b384123dd68adb783742fc7b32ee335ee489d1302</t>
+          <t>0x5f3419242a87ff17c0cb508ade95d27a54429124d36280a1dff2efa2fa0b3510</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -8334,17 +8334,17 @@
       <c r="C75" t="inlineStr"/>
       <c r="D75" t="inlineStr">
         <is>
-          <t>10.58</t>
+          <t>20.41999</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>1.485</t>
+          <t>1.7087</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G75" t="inlineStr"/>
@@ -8355,27 +8355,27 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>Deportivo Moron vs Acassuso</t>
+          <t>CA Los Andes vs Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>Deportivo Moron</t>
+          <t>CA Los Andes</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>0x108eaba0441fb45ec8e0073e945ae0ac1e138c933e4f2839816cd3198d7dd4d2</t>
+          <t>0x31115553050eabb8d3f6a72cf2865c16175783383dcfc674615e74ed88cabaee</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>L19683452</t>
+          <t>L19659153</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
@@ -8400,17 +8400,17 @@
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>1786277679</t>
+          <t>1786277884</t>
         </is>
       </c>
       <c r="S75" t="inlineStr">
         <is>
-          <t>1786298400</t>
+          <t>1786296600</t>
         </is>
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>21.814433</t>
+          <t>28.811273</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
@@ -8427,7 +8427,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>0xb25fa423ffb1a1464f100f2a2e9a1beac36661b9e37c8b09ecc7d3fd5a80312f</t>
+          <t>0xe6b14424302d9ef7ea2000cef83e38549f6a38c12d57faa6dd76dd84e631a5ca</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -8438,17 +8438,17 @@
       <c r="C76" t="inlineStr"/>
       <c r="D76" t="inlineStr">
         <is>
-          <t>25.88</t>
+          <t>12.13</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>1.6038</t>
+          <t>1.3613</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
+          <t>Under/Over (1.5)</t>
         </is>
       </c>
       <c r="G76" t="inlineStr"/>
@@ -8459,27 +8459,27 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>CA Colegiales vs Patronato</t>
+          <t>Deportivo Moron vs Acassuso</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>CA Colegiales</t>
+          <t>Deportivo Moron</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>0x18dd2fdd93f5029a20e6a76c47c4f0e5c3c25768ad7f1b46a833287f8b7fcc13</t>
+          <t>0x3f34d112cfb9f093c57a3e094be078f9eea2715f97797e20d86942d58f5cc8d6</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>L19683449</t>
+          <t>L19683452</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
@@ -8504,7 +8504,7 @@
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>1786277040</t>
+          <t>1786277708</t>
         </is>
       </c>
       <c r="S76" t="inlineStr">
@@ -8514,7 +8514,7 @@
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>42.865424</t>
+          <t>33.577855</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
@@ -8531,7 +8531,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>0xfe815be8a10a6ad2cda012e463a244232a6f6c80544018f6dda52d723946b659</t>
+          <t>0xd7a2e43ba1564f619200938b384123dd68adb783742fc7b32ee335ee489d1302</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -8542,12 +8542,12 @@
       <c r="C77" t="inlineStr"/>
       <c r="D77" t="inlineStr">
         <is>
-          <t>29.02571</t>
+          <t>10.58</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>1.6038</t>
+          <t>1.485</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -8563,27 +8563,27 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>CA Colegiales vs Patronato</t>
+          <t>Deportivo Moron vs Acassuso</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>CA Colegiales</t>
+          <t>Deportivo Moron</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>0x18dd2fdd93f5029a20e6a76c47c4f0e5c3c25768ad7f1b46a833287f8b7fcc13</t>
+          <t>0x108eaba0441fb45ec8e0073e945ae0ac1e138c933e4f2839816cd3198d7dd4d2</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>L19683449</t>
+          <t>L19683452</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
@@ -8608,7 +8608,7 @@
       </c>
       <c r="R77" t="inlineStr">
         <is>
-          <t>1786276809</t>
+          <t>1786277679</t>
         </is>
       </c>
       <c r="S77" t="inlineStr">
@@ -8618,7 +8618,7 @@
       </c>
       <c r="T77" t="inlineStr">
         <is>
-          <t>48.07571</t>
+          <t>21.814433</t>
         </is>
       </c>
       <c r="U77" t="inlineStr">
@@ -8635,7 +8635,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>0xdb83c52876b68624e093c25e35d11910f4fbef2394ff947b658f8ea5cdb3fa88</t>
+          <t>0xb25fa423ffb1a1464f100f2a2e9a1beac36661b9e37c8b09ecc7d3fd5a80312f</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -8646,17 +8646,17 @@
       <c r="C78" t="inlineStr"/>
       <c r="D78" t="inlineStr">
         <is>
-          <t>16.96</t>
+          <t>25.88</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>1.4463</t>
+          <t>1.6038</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
+          <t>Under/Over (2)</t>
         </is>
       </c>
       <c r="G78" t="inlineStr"/>
@@ -8682,7 +8682,7 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>0x30a6561de28b35c5bb0557dcbfc7b23e7a62558d3b0f5cfcafb67d7a07e0dd21</t>
+          <t>0x18dd2fdd93f5029a20e6a76c47c4f0e5c3c25768ad7f1b46a833287f8b7fcc13</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
@@ -8712,7 +8712,7 @@
       </c>
       <c r="R78" t="inlineStr">
         <is>
-          <t>1786276809</t>
+          <t>1786277040</t>
         </is>
       </c>
       <c r="S78" t="inlineStr">
@@ -8722,7 +8722,7 @@
       </c>
       <c r="T78" t="inlineStr">
         <is>
-          <t>38.005602</t>
+          <t>42.865424</t>
         </is>
       </c>
       <c r="U78" t="inlineStr">
@@ -8739,39 +8739,31 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>0x0847a2541998eecfe02d138796b14ef3d6719061787498f4888f6e14c0d196ff</t>
+          <t>0xfe815be8a10a6ad2cda012e463a244232a6f6c80544018f6dda52d723946b659</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>0xf068eF8DF8f47185D02d59Bb33d9eC7A057a571E</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr"/>
       <c r="D79" t="inlineStr">
         <is>
-          <t>38.54</t>
+          <t>29.02571</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>1.125</t>
+          <t>1.6038</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>Club Almagro</t>
-        </is>
-      </c>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr"/>
       <c r="H79" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -8779,27 +8771,27 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Quilmes vs Club Almagro</t>
+          <t>CA Colegiales vs Patronato</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>CA Colegiales</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>Club Almagro</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>0x03ed0858b563c1becf38b195ad94b1a84eb89c3ca8ca10b1a34220bff142f9b2</t>
+          <t>0x18dd2fdd93f5029a20e6a76c47c4f0e5c3c25768ad7f1b46a833287f8b7fcc13</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>L19683499</t>
+          <t>L19683449</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
@@ -8824,17 +8816,17 @@
       </c>
       <c r="R79" t="inlineStr">
         <is>
-          <t>1786270828</t>
+          <t>1786276809</t>
         </is>
       </c>
       <c r="S79" t="inlineStr">
         <is>
-          <t>1786305600</t>
+          <t>1786298400</t>
         </is>
       </c>
       <c r="T79" t="inlineStr">
         <is>
-          <t>308.32</t>
+          <t>48.07571</t>
         </is>
       </c>
       <c r="U79" t="inlineStr">
@@ -8851,7 +8843,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>0x2121e08c4ea1fe2d49a3bb388fba9e232ef9c06335c04e5eae0bf7766975512a</t>
+          <t>0xdb83c52876b68624e093c25e35d11910f4fbef2394ff947b658f8ea5cdb3fa88</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -8859,31 +8851,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C80" t="inlineStr"/>
       <c r="D80" t="inlineStr">
         <is>
-          <t>30.06</t>
+          <t>16.96</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>1.6262</t>
+          <t>1.4463</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>Colon de Santa Fe</t>
-        </is>
-      </c>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr"/>
       <c r="H80" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -8891,27 +8875,27 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Colon de Santa Fe vs San Telmo</t>
+          <t>CA Colegiales vs Patronato</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>Colon de Santa Fe</t>
+          <t>CA Colegiales</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>0x1a11ec80edeaae24566c4f4f891cc2afc56b377b24997a6e8ee533eeaaad5c92</t>
+          <t>0x30a6561de28b35c5bb0557dcbfc7b23e7a62558d3b0f5cfcafb67d7a07e0dd21</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>L19683494</t>
+          <t>L19683449</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
@@ -8936,17 +8920,17 @@
       </c>
       <c r="R80" t="inlineStr">
         <is>
-          <t>1786253941</t>
+          <t>1786276809</t>
         </is>
       </c>
       <c r="S80" t="inlineStr">
         <is>
-          <t>1786300200</t>
+          <t>1786298400</t>
         </is>
       </c>
       <c r="T80" t="inlineStr">
         <is>
-          <t>48.0</t>
+          <t>38.005602</t>
         </is>
       </c>
       <c r="U80" t="inlineStr">
@@ -8963,12 +8947,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>0x4e811c319e5e3a1fc1968ce0f31b4c15eb7222daa616252d99f9abc611408746</t>
+          <t>0x0847a2541998eecfe02d138796b14ef3d6719061787498f4888f6e14c0d196ff</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>0x155C76202e45BE70c50bfeD7eAeA3B98e7716Ff7</t>
+          <t>0xf068eF8DF8f47185D02d59Bb33d9eC7A057a571E</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -8978,12 +8962,12 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>38.54</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>1.2925</t>
+          <t>1.125</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -8993,7 +8977,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Tie</t>
+          <t>Club Almagro</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -9003,27 +8987,27 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>Colon de Santa Fe vs San Telmo</t>
+          <t>Quilmes vs Club Almagro</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>Colon de Santa Fe</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Club Almagro</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>0x2e49527408facf21253a0a1eafe51280b82e4c31919e91a396332f19ec366401</t>
+          <t>0x03ed0858b563c1becf38b195ad94b1a84eb89c3ca8ca10b1a34220bff142f9b2</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>L19683494</t>
+          <t>L19683499</t>
         </is>
       </c>
       <c r="N81" t="inlineStr">
@@ -9048,17 +9032,17 @@
       </c>
       <c r="R81" t="inlineStr">
         <is>
-          <t>1786243741</t>
+          <t>1786270828</t>
         </is>
       </c>
       <c r="S81" t="inlineStr">
         <is>
-          <t>1786300200</t>
+          <t>1786305600</t>
         </is>
       </c>
       <c r="T81" t="inlineStr">
         <is>
-          <t>3.418803</t>
+          <t>308.32</t>
         </is>
       </c>
       <c r="U81" t="inlineStr">
@@ -9075,12 +9059,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>0xb8631aeb398192a03386505542f05fa15e34db501204baa8745a4d4b5c1651b7</t>
+          <t>0x2121e08c4ea1fe2d49a3bb388fba9e232ef9c06335c04e5eae0bf7766975512a</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>0x155C76202e45BE70c50bfeD7eAeA3B98e7716Ff7</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -9090,12 +9074,12 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>0.99999</t>
+          <t>30.06</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>1.6538</t>
+          <t>1.6262</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -9105,7 +9089,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Deportivo Moron</t>
+          <t>Colon de Santa Fe</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -9115,27 +9099,27 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Deportivo Moron vs Acassuso</t>
+          <t>Colon de Santa Fe vs San Telmo</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>Deportivo Moron</t>
+          <t>Colon de Santa Fe</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>0x7514a255ce41be3c5db9f8849ba04e78dab80f02d1fe78c2aae82bbc843a9745</t>
+          <t>0x1a11ec80edeaae24566c4f4f891cc2afc56b377b24997a6e8ee533eeaaad5c92</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>L19683452</t>
+          <t>L19683494</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
@@ -9160,17 +9144,17 @@
       </c>
       <c r="R82" t="inlineStr">
         <is>
-          <t>1786243225</t>
+          <t>1786253941</t>
         </is>
       </c>
       <c r="S82" t="inlineStr">
         <is>
-          <t>1786298400</t>
+          <t>1786300200</t>
         </is>
       </c>
       <c r="T82" t="inlineStr">
         <is>
-          <t>1.529621</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="U82" t="inlineStr">
@@ -9187,15 +9171,19 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>0xd3b94d194e43cc84f0a1b82723594ea6689a6aa2a4a7dccbc8a3d19fc321e49b</t>
+          <t>0x4e811c319e5e3a1fc1968ce0f31b4c15eb7222daa616252d99f9abc611408746</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr"/>
+          <t>0x155C76202e45BE70c50bfeD7eAeA3B98e7716Ff7</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D83" t="inlineStr">
         <is>
           <t>1</t>
@@ -9203,15 +9191,19 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>1.5238</t>
+          <t>1.2925</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H83" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -9219,27 +9211,27 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>Deportivo Moron vs Acassuso</t>
+          <t>Colon de Santa Fe vs San Telmo</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>Deportivo Moron</t>
+          <t>Colon de Santa Fe</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>0x108eaba0441fb45ec8e0073e945ae0ac1e138c933e4f2839816cd3198d7dd4d2</t>
+          <t>0x2e49527408facf21253a0a1eafe51280b82e4c31919e91a396332f19ec366401</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>L19683452</t>
+          <t>L19683494</t>
         </is>
       </c>
       <c r="N83" t="inlineStr">
@@ -9264,17 +9256,17 @@
       </c>
       <c r="R83" t="inlineStr">
         <is>
-          <t>1786225000</t>
+          <t>1786243741</t>
         </is>
       </c>
       <c r="S83" t="inlineStr">
         <is>
-          <t>1786298400</t>
+          <t>1786300200</t>
         </is>
       </c>
       <c r="T83" t="inlineStr">
         <is>
-          <t>1.909308</t>
+          <t>3.418803</t>
         </is>
       </c>
       <c r="U83" t="inlineStr">
@@ -9291,12 +9283,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>0x86f4b24298f4c19f9f856cb19af2a260f24dc2d391f252248469436057ea1d1a</t>
+          <t>0xb8631aeb398192a03386505542f05fa15e34db501204baa8745a4d4b5c1651b7</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
+          <t>0x155C76202e45BE70c50bfeD7eAeA3B98e7716Ff7</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -9306,22 +9298,22 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0.99999</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>1.5263</t>
+          <t>1.6538</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Deportivo Moron -1</t>
+          <t>Deportivo Moron</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -9346,7 +9338,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>0xb61b063252c01d0525ae633a0276dc1830eabd418482fddec925fcbd602a2a75</t>
+          <t>0x7514a255ce41be3c5db9f8849ba04e78dab80f02d1fe78c2aae82bbc843a9745</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
@@ -9376,7 +9368,7 @@
       </c>
       <c r="R84" t="inlineStr">
         <is>
-          <t>1786220171</t>
+          <t>1786243225</t>
         </is>
       </c>
       <c r="S84" t="inlineStr">
@@ -9386,7 +9378,7 @@
       </c>
       <c r="T84" t="inlineStr">
         <is>
-          <t>1.900238</t>
+          <t>1.529621</t>
         </is>
       </c>
       <c r="U84" t="inlineStr">
@@ -9403,39 +9395,31 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>0x0a5de930b5a6b8aca1699b666034af3891a3aa920021791d6d13e0297fb7903f</t>
+          <t>0xd3b94d194e43cc84f0a1b82723594ea6689a6aa2a4a7dccbc8a3d19fc321e49b</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>0x4a09916b1325Eed50eE8973B13742a205B0B7c7E</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr"/>
       <c r="D85" t="inlineStr">
         <is>
-          <t>49.99999</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>1.6175</t>
+          <t>1.5238</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>Almirante Brown -1</t>
-        </is>
-      </c>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr"/>
       <c r="H85" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -9443,27 +9427,27 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>Almirante Brown vs Ciudad Bolivar</t>
+          <t>Deportivo Moron vs Acassuso</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Deportivo Moron</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>Ciudad Bolivar</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>0xa6a338c64f062bfd589e8d5d9cea45a27c9e64065f71f800e5966f81ce53c556</t>
+          <t>0x108eaba0441fb45ec8e0073e945ae0ac1e138c933e4f2839816cd3198d7dd4d2</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>L19683447</t>
+          <t>L19683452</t>
         </is>
       </c>
       <c r="N85" t="inlineStr">
@@ -9488,17 +9472,17 @@
       </c>
       <c r="R85" t="inlineStr">
         <is>
-          <t>1786218515</t>
+          <t>1786225000</t>
         </is>
       </c>
       <c r="S85" t="inlineStr">
         <is>
-          <t>1786212000</t>
+          <t>1786298400</t>
         </is>
       </c>
       <c r="T85" t="inlineStr">
         <is>
-          <t>80.971644</t>
+          <t>1.909308</t>
         </is>
       </c>
       <c r="U85" t="inlineStr">
@@ -9515,23 +9499,27 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>0x17d5a08f8fa305f31f27442393c64f497dd3893417da6e76c321c4c2a187320d</t>
+          <t>0x86f4b24298f4c19f9f856cb19af2a260f24dc2d391f252248469436057ea1d1a</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr"/>
+          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>49.18897</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>1.4737</t>
+          <t>1.5263</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -9539,7 +9527,11 @@
           <t>Asian Handicap (-1)</t>
         </is>
       </c>
-      <c r="G86" t="inlineStr"/>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Deportivo Moron -1</t>
+        </is>
+      </c>
       <c r="H86" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -9547,27 +9539,27 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>Almirante Brown vs Ciudad Bolivar</t>
+          <t>Deportivo Moron vs Acassuso</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Deportivo Moron</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>Ciudad Bolivar</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>0xa6a338c64f062bfd589e8d5d9cea45a27c9e64065f71f800e5966f81ce53c556</t>
+          <t>0xb61b063252c01d0525ae633a0276dc1830eabd418482fddec925fcbd602a2a75</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>L19683447</t>
+          <t>L19683452</t>
         </is>
       </c>
       <c r="N86" t="inlineStr">
@@ -9592,17 +9584,17 @@
       </c>
       <c r="R86" t="inlineStr">
         <is>
-          <t>1786218084</t>
+          <t>1786220171</t>
         </is>
       </c>
       <c r="S86" t="inlineStr">
         <is>
-          <t>1786212000</t>
+          <t>1786298400</t>
         </is>
       </c>
       <c r="T86" t="inlineStr">
         <is>
-          <t>103.82896</t>
+          <t>1.900238</t>
         </is>
       </c>
       <c r="U86" t="inlineStr">
@@ -9619,31 +9611,39 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>0x56975f372357be259365cb7d2929c88d4fae157eea7a71d53d57cb234834f2ca</t>
+          <t>0x0a5de930b5a6b8aca1699b666034af3891a3aa920021791d6d13e0297fb7903f</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr"/>
+          <t>0x4a09916b1325Eed50eE8973B13742a205B0B7c7E</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>49.99999</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>1.4812</t>
+          <t>1.6175</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr"/>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Almirante Brown -1</t>
+        </is>
+      </c>
       <c r="H87" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -9651,27 +9651,27 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>Club Atletico Mitre de Santiago del Estero vs Defensores de Belgrano Buenos Aires</t>
+          <t>Almirante Brown vs Ciudad Bolivar</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>Club Atletico Mitre de Santiago del Estero</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano Buenos Aires</t>
+          <t>Ciudad Bolivar</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>0xa8ade64a3adb0ea38de67a61105ef31beb490d5a7287715b76ae124536d359cc</t>
+          <t>0xa6a338c64f062bfd589e8d5d9cea45a27c9e64065f71f800e5966f81ce53c556</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>L19683493</t>
+          <t>L19683447</t>
         </is>
       </c>
       <c r="N87" t="inlineStr">
@@ -9696,17 +9696,17 @@
       </c>
       <c r="R87" t="inlineStr">
         <is>
-          <t>1786215674</t>
+          <t>1786218515</t>
         </is>
       </c>
       <c r="S87" t="inlineStr">
         <is>
-          <t>1786302000</t>
+          <t>1786212000</t>
         </is>
       </c>
       <c r="T87" t="inlineStr">
         <is>
-          <t>2.077922</t>
+          <t>80.971644</t>
         </is>
       </c>
       <c r="U87" t="inlineStr">
@@ -9723,54 +9723,46 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>0xff53df1f3446908699196d44fcdb8b39c1bd15c7ed519f0d730e55a51a6eb38f</t>
+          <t>0x17d5a08f8fa305f31f27442393c64f497dd3893417da6e76c321c4c2a187320d</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr"/>
       <c r="D88" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>49.18897</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>1.3713</t>
+          <t>1.4737</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr"/>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Primera Nacional</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>Almirante Brown vs Ciudad Bolivar</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
         <is>
           <t>Almirante Brown</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>Primera Nacional</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>Almirante Brown vs Ciudad Bolivar</t>
-        </is>
-      </c>
-      <c r="J88" t="inlineStr">
-        <is>
-          <t>Almirante Brown</t>
-        </is>
-      </c>
       <c r="K88" t="inlineStr">
         <is>
           <t>Ciudad Bolivar</t>
@@ -9778,7 +9770,7 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>0x63a8bf73c1084ef223fdd1096dccd16232e7a455fad77f7f0891be1588ebeb88</t>
+          <t>0xa6a338c64f062bfd589e8d5d9cea45a27c9e64065f71f800e5966f81ce53c556</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
@@ -9808,7 +9800,7 @@
       </c>
       <c r="R88" t="inlineStr">
         <is>
-          <t>1786215673</t>
+          <t>1786218084</t>
         </is>
       </c>
       <c r="S88" t="inlineStr">
@@ -9818,7 +9810,7 @@
       </c>
       <c r="T88" t="inlineStr">
         <is>
-          <t>2.693603</t>
+          <t>103.82896</t>
         </is>
       </c>
       <c r="U88" t="inlineStr">
@@ -9835,39 +9827,31 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>0x249d52552e7acb9f472d2a4c48ab754622ba572903281739a3e10b4d509dccb0</t>
+          <t>0x56975f372357be259365cb7d2929c88d4fae157eea7a71d53d57cb234834f2ca</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr"/>
       <c r="D89" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>1.2288</t>
+          <t>1.4812</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>Almirante Brown -1</t>
-        </is>
-      </c>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr"/>
       <c r="H89" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -9875,27 +9859,27 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>Almirante Brown vs Ciudad Bolivar</t>
+          <t>Club Atletico Mitre de Santiago del Estero vs Defensores de Belgrano Buenos Aires</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Club Atletico Mitre de Santiago del Estero</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>Ciudad Bolivar</t>
+          <t>Defensores de Belgrano Buenos Aires</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>0xa6a338c64f062bfd589e8d5d9cea45a27c9e64065f71f800e5966f81ce53c556</t>
+          <t>0xa8ade64a3adb0ea38de67a61105ef31beb490d5a7287715b76ae124536d359cc</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>L19683447</t>
+          <t>L19683493</t>
         </is>
       </c>
       <c r="N89" t="inlineStr">
@@ -9920,17 +9904,17 @@
       </c>
       <c r="R89" t="inlineStr">
         <is>
-          <t>1786214209</t>
+          <t>1786215674</t>
         </is>
       </c>
       <c r="S89" t="inlineStr">
         <is>
-          <t>1786212000</t>
+          <t>1786302000</t>
         </is>
       </c>
       <c r="T89" t="inlineStr">
         <is>
-          <t>6.295082</t>
+          <t>2.077922</t>
         </is>
       </c>
       <c r="U89" t="inlineStr">
@@ -9947,12 +9931,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>0xf65c55196eeb0d21e7e3866ad26f8c3f2fee2aef273ddde5423e31fb40a51469</t>
+          <t>0xff53df1f3446908699196d44fcdb8b39c1bd15c7ed519f0d730e55a51a6eb38f</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -9962,12 +9946,12 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>121.81</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>1.4363</t>
+          <t>1.3713</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -10032,7 +10016,7 @@
       </c>
       <c r="R90" t="inlineStr">
         <is>
-          <t>1786213844</t>
+          <t>1786215673</t>
         </is>
       </c>
       <c r="S90" t="inlineStr">
@@ -10042,7 +10026,7 @@
       </c>
       <c r="T90" t="inlineStr">
         <is>
-          <t>279.22063</t>
+          <t>2.693603</t>
         </is>
       </c>
       <c r="U90" t="inlineStr">
@@ -10059,12 +10043,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>0x1bb20a2bf22e4fe06b44c06b9c2caa21f3f2a7c9d0cce1a2346f79e76022cd1f</t>
+          <t>0x249d52552e7acb9f472d2a4c48ab754622ba572903281739a3e10b4d509dccb0</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -10074,22 +10058,22 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>21.05</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>1.4363</t>
+          <t>1.2288</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Almirante Brown -0.5</t>
+          <t>Almirante Brown -1</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -10114,7 +10098,7 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>0xfa00d2f0c7b5053ee336b303a0e7ad9cec0b8d539367773b7efee5c86cb2b59d</t>
+          <t>0xa6a338c64f062bfd589e8d5d9cea45a27c9e64065f71f800e5966f81ce53c556</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
@@ -10144,7 +10128,7 @@
       </c>
       <c r="R91" t="inlineStr">
         <is>
-          <t>1786213843</t>
+          <t>1786214209</t>
         </is>
       </c>
       <c r="S91" t="inlineStr">
@@ -10154,7 +10138,7 @@
       </c>
       <c r="T91" t="inlineStr">
         <is>
-          <t>48.252149</t>
+          <t>6.295082</t>
         </is>
       </c>
       <c r="U91" t="inlineStr">
@@ -10171,7 +10155,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>0xc51052f8e449b4d56cc87b697bfc8eb0d3a88ae218dee1da3d725fa94163bc75</t>
+          <t>0xf65c55196eeb0d21e7e3866ad26f8c3f2fee2aef273ddde5423e31fb40a51469</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -10179,23 +10163,31 @@
           <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
-      <c r="C92" t="inlineStr"/>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>77.29513</t>
+          <t>121.81</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>1.2588</t>
+          <t>1.4363</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Primera Nacional</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Almirante Brown</t>
+        </is>
+      </c>
       <c r="H92" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -10218,7 +10210,7 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>0xaa5316c6f6544d74142ad6db34a3745918f237ffb1a657e000693947e81b65d6</t>
+          <t>0x63a8bf73c1084ef223fdd1096dccd16232e7a455fad77f7f0891be1588ebeb88</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
@@ -10248,7 +10240,7 @@
       </c>
       <c r="R92" t="inlineStr">
         <is>
-          <t>1786212849</t>
+          <t>1786213844</t>
         </is>
       </c>
       <c r="S92" t="inlineStr">
@@ -10258,7 +10250,7 @@
       </c>
       <c r="T92" t="inlineStr">
         <is>
-          <t>298.72514</t>
+          <t>279.22063</t>
         </is>
       </c>
       <c r="U92" t="inlineStr">
@@ -10275,7 +10267,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>0x0aeb4fe40f7d734cf244c144e6c064568b40b222193c9f93c641d1b31af3752e</t>
+          <t>0x1bb20a2bf22e4fe06b44c06b9c2caa21f3f2a7c9d0cce1a2346f79e76022cd1f</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -10283,23 +10275,31 @@
           <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
-      <c r="C93" t="inlineStr"/>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>16.89162</t>
+          <t>21.05</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>1.2588</t>
+          <t>1.4363</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Primera Nacional</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr"/>
+          <t>Asian Handicap (-0.5)</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Almirante Brown -0.5</t>
+        </is>
+      </c>
       <c r="H93" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -10322,7 +10322,7 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>0xaa5316c6f6544d74142ad6db34a3745918f237ffb1a657e000693947e81b65d6</t>
+          <t>0xfa00d2f0c7b5053ee336b303a0e7ad9cec0b8d539367773b7efee5c86cb2b59d</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
@@ -10352,7 +10352,7 @@
       </c>
       <c r="R93" t="inlineStr">
         <is>
-          <t>1786212805</t>
+          <t>1786213843</t>
         </is>
       </c>
       <c r="S93" t="inlineStr">
@@ -10362,7 +10362,7 @@
       </c>
       <c r="T93" t="inlineStr">
         <is>
-          <t>65.281623</t>
+          <t>48.252149</t>
         </is>
       </c>
       <c r="U93" t="inlineStr">
@@ -10379,7 +10379,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>0x383b895a5fe529a887369a0f113c516fdc7f6125d54381acf9695997ef22d039</t>
+          <t>0xc51052f8e449b4d56cc87b697bfc8eb0d3a88ae218dee1da3d725fa94163bc75</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -10387,19 +10387,15 @@
           <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C94" t="inlineStr"/>
       <c r="D94" t="inlineStr">
         <is>
-          <t>11.26905</t>
+          <t>77.29513</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>1.745</t>
+          <t>1.2588</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -10407,26 +10403,22 @@
           <t>Primera Nacional</t>
         </is>
       </c>
-      <c r="G94" t="inlineStr">
+      <c r="G94" t="inlineStr"/>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Primera Nacional</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>Almirante Brown vs Ciudad Bolivar</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
         <is>
           <t>Almirante Brown</t>
         </is>
       </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>Primera Nacional</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>Almirante Brown vs Ciudad Bolivar</t>
-        </is>
-      </c>
-      <c r="J94" t="inlineStr">
-        <is>
-          <t>Almirante Brown</t>
-        </is>
-      </c>
       <c r="K94" t="inlineStr">
         <is>
           <t>Ciudad Bolivar</t>
@@ -10464,7 +10456,7 @@
       </c>
       <c r="R94" t="inlineStr">
         <is>
-          <t>1786211779</t>
+          <t>1786212849</t>
         </is>
       </c>
       <c r="S94" t="inlineStr">
@@ -10474,7 +10466,7 @@
       </c>
       <c r="T94" t="inlineStr">
         <is>
-          <t>15.126242</t>
+          <t>298.72514</t>
         </is>
       </c>
       <c r="U94" t="inlineStr">
@@ -10491,27 +10483,23 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>0xcfb6add6f8610a64ffc187beb9e16bf2bacb27b54a0f0aaefa6bfb437239b893</t>
+          <t>0x0aeb4fe40f7d734cf244c144e6c064568b40b222193c9f93c641d1b31af3752e</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr"/>
       <c r="D95" t="inlineStr">
         <is>
-          <t>24.89998</t>
+          <t>16.89162</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>1.745</t>
+          <t>1.2588</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -10519,26 +10507,22 @@
           <t>Primera Nacional</t>
         </is>
       </c>
-      <c r="G95" t="inlineStr">
+      <c r="G95" t="inlineStr"/>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Primera Nacional</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>Almirante Brown vs Ciudad Bolivar</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
         <is>
           <t>Almirante Brown</t>
         </is>
       </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>Primera Nacional</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>Almirante Brown vs Ciudad Bolivar</t>
-        </is>
-      </c>
-      <c r="J95" t="inlineStr">
-        <is>
-          <t>Almirante Brown</t>
-        </is>
-      </c>
       <c r="K95" t="inlineStr">
         <is>
           <t>Ciudad Bolivar</t>
@@ -10576,7 +10560,7 @@
       </c>
       <c r="R95" t="inlineStr">
         <is>
-          <t>1786211777</t>
+          <t>1786212805</t>
         </is>
       </c>
       <c r="S95" t="inlineStr">
@@ -10586,7 +10570,7 @@
       </c>
       <c r="T95" t="inlineStr">
         <is>
-          <t>33.422792</t>
+          <t>65.281623</t>
         </is>
       </c>
       <c r="U95" t="inlineStr">
@@ -10603,12 +10587,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>0xd41652604437a4e92e0d78b653d4d49d8dedd2e153d1340dad89b9b93e182a48</t>
+          <t>0x383b895a5fe529a887369a0f113c516fdc7f6125d54381acf9695997ef22d039</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>0xf4a8B27C9a13e298D65b5Cc072d252816B799C81</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -10618,22 +10602,22 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>11.26905</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>1.4163</t>
+          <t>1.745</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Primera Nacional</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Atl. Rafaela</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -10643,27 +10627,27 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>Atl. Rafaela vs Chacarita Juniors</t>
+          <t>Almirante Brown vs Ciudad Bolivar</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>Atl. Rafaela</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Ciudad Bolivar</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>0xe738e9ba05492fab73eaaf6da211b84caadc72b08b26f1cd30fa8737e283bb44</t>
+          <t>0xaa5316c6f6544d74142ad6db34a3745918f237ffb1a657e000693947e81b65d6</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>L19683450</t>
+          <t>L19683447</t>
         </is>
       </c>
       <c r="N96" t="inlineStr">
@@ -10688,17 +10672,17 @@
       </c>
       <c r="R96" t="inlineStr">
         <is>
-          <t>1786211028</t>
+          <t>1786211779</t>
         </is>
       </c>
       <c r="S96" t="inlineStr">
         <is>
-          <t>1786215600</t>
+          <t>1786212000</t>
         </is>
       </c>
       <c r="T96" t="inlineStr">
         <is>
-          <t>2.402402</t>
+          <t>15.126242</t>
         </is>
       </c>
       <c r="U96" t="inlineStr">
@@ -10715,7 +10699,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>0x562fd7c6419c807ed04d3cacac95f861805f96704bd535e265399fb9d2c2b609</t>
+          <t>0xcfb6add6f8610a64ffc187beb9e16bf2bacb27b54a0f0aaefa6bfb437239b893</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -10723,23 +10707,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C97" t="inlineStr"/>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>5.32</t>
+          <t>24.89998</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>1.405</t>
+          <t>1.745</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr"/>
+          <t>Primera Nacional</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Almirante Brown</t>
+        </is>
+      </c>
       <c r="H97" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -10747,27 +10739,27 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>Estudiantes de Caseros vs Deportivo Madryn</t>
+          <t>Almirante Brown vs Ciudad Bolivar</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>Estudiantes de Caseros</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Ciudad Bolivar</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>0xd61509e26f8645bb9780672f942c72c4b7dab577c2a01f04e1e09bce9b828765</t>
+          <t>0xaa5316c6f6544d74142ad6db34a3745918f237ffb1a657e000693947e81b65d6</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>L19683453</t>
+          <t>L19683447</t>
         </is>
       </c>
       <c r="N97" t="inlineStr">
@@ -10792,7 +10784,7 @@
       </c>
       <c r="R97" t="inlineStr">
         <is>
-          <t>1786210845</t>
+          <t>1786211777</t>
         </is>
       </c>
       <c r="S97" t="inlineStr">
@@ -10802,7 +10794,7 @@
       </c>
       <c r="T97" t="inlineStr">
         <is>
-          <t>13.135802</t>
+          <t>33.422792</t>
         </is>
       </c>
       <c r="U97" t="inlineStr">
@@ -10819,7 +10811,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>0x0bb7a6822220bf40d7b279f99a54f46025f393ba95bb38b6d6dc98192886b3ed</t>
+          <t>0xd41652604437a4e92e0d78b653d4d49d8dedd2e153d1340dad89b9b93e182a48</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -10834,12 +10826,12 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>0.99999</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>1.5513</t>
+          <t>1.4163</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -10849,7 +10841,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Atl. Rafaela</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -10859,27 +10851,27 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>Agropecuario vs Atletico Guemes</t>
+          <t>Atl. Rafaela vs Chacarita Juniors</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Atl. Rafaela</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>Atletico Guemes</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>0xae66c7fab3c9c76fbc29d9e9778ef4845d8a6b8d092cff34320f100020113c49</t>
+          <t>0xe738e9ba05492fab73eaaf6da211b84caadc72b08b26f1cd30fa8737e283bb44</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>L19683451</t>
+          <t>L19683450</t>
         </is>
       </c>
       <c r="N98" t="inlineStr">
@@ -10904,17 +10896,17 @@
       </c>
       <c r="R98" t="inlineStr">
         <is>
-          <t>1786205982</t>
+          <t>1786211028</t>
         </is>
       </c>
       <c r="S98" t="inlineStr">
         <is>
-          <t>1786212000</t>
+          <t>1786215600</t>
         </is>
       </c>
       <c r="T98" t="inlineStr">
         <is>
-          <t>1.814041</t>
+          <t>2.402402</t>
         </is>
       </c>
       <c r="U98" t="inlineStr">
@@ -10931,39 +10923,31 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>0xe17b2546f4b90c8647ba975c279e39dec1fda5a003adfb8a2b39bb12a3519b10</t>
+          <t>0x562fd7c6419c807ed04d3cacac95f861805f96704bd535e265399fb9d2c2b609</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>0xf4a8B27C9a13e298D65b5Cc072d252816B799C81</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr"/>
       <c r="D99" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5.32</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>1.3613</t>
+          <t>1.405</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr"/>
       <c r="H99" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -10971,27 +10955,27 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>Almirante Brown vs Ciudad Bolivar</t>
+          <t>Estudiantes de Caseros vs Deportivo Madryn</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Estudiantes de Caseros</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>Ciudad Bolivar</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>0xd5906ce08d61f7c5ee45fcebd2c8baeed5558387398ea332817a4b632f439b6d</t>
+          <t>0xd61509e26f8645bb9780672f942c72c4b7dab577c2a01f04e1e09bce9b828765</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>L19683447</t>
+          <t>L19683453</t>
         </is>
       </c>
       <c r="N99" t="inlineStr">
@@ -11016,7 +11000,7 @@
       </c>
       <c r="R99" t="inlineStr">
         <is>
-          <t>1786205963</t>
+          <t>1786210845</t>
         </is>
       </c>
       <c r="S99" t="inlineStr">
@@ -11026,7 +11010,7 @@
       </c>
       <c r="T99" t="inlineStr">
         <is>
-          <t>2.768166</t>
+          <t>13.135802</t>
         </is>
       </c>
       <c r="U99" t="inlineStr">
@@ -11043,7 +11027,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>0xcfe218822e89cbef5841f3045f551cc65acf353d8e240f943e2b61c54ea79a68</t>
+          <t>0x0bb7a6822220bf40d7b279f99a54f46025f393ba95bb38b6d6dc98192886b3ed</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -11058,12 +11042,12 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0.99999</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>1.3337</t>
+          <t>1.5513</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -11073,7 +11057,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Tie</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -11083,27 +11067,27 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>Estudiantes de Caseros vs Deportivo Madryn</t>
+          <t>Agropecuario vs Atletico Guemes</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>Estudiantes de Caseros</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Atletico Guemes</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>0xf238b96ec9e2421db79973de945f1fc0c3f8bb99c31cda32d011ebaabfd2db86</t>
+          <t>0xae66c7fab3c9c76fbc29d9e9778ef4845d8a6b8d092cff34320f100020113c49</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>L19683453</t>
+          <t>L19683451</t>
         </is>
       </c>
       <c r="N100" t="inlineStr">
@@ -11128,7 +11112,7 @@
       </c>
       <c r="R100" t="inlineStr">
         <is>
-          <t>1786205938</t>
+          <t>1786205982</t>
         </is>
       </c>
       <c r="S100" t="inlineStr">
@@ -11138,7 +11122,7 @@
       </c>
       <c r="T100" t="inlineStr">
         <is>
-          <t>2.996255</t>
+          <t>1.814041</t>
         </is>
       </c>
       <c r="U100" t="inlineStr">
@@ -11155,31 +11139,39 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>0x1b9fcb29010a212f74af57040114154e78748f06a4d826be4397ddadb45ac31b</t>
+          <t>0xe17b2546f4b90c8647ba975c279e39dec1fda5a003adfb8a2b39bb12a3519b10</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr"/>
+          <t>0xf4a8B27C9a13e298D65b5Cc072d252816B799C81</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>21.69</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>1.4512</t>
+          <t>1.3613</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H101" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -11202,7 +11194,7 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>0xbbcaa253cd967fbf933ff0d87a6f9744cafec0ed59dad5f1f76332aab01a3fa5</t>
+          <t>0xd5906ce08d61f7c5ee45fcebd2c8baeed5558387398ea332817a4b632f439b6d</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
@@ -11232,7 +11224,7 @@
       </c>
       <c r="R101" t="inlineStr">
         <is>
-          <t>1786190525</t>
+          <t>1786205963</t>
         </is>
       </c>
       <c r="S101" t="inlineStr">
@@ -11242,7 +11234,7 @@
       </c>
       <c r="T101" t="inlineStr">
         <is>
-          <t>48.066482</t>
+          <t>2.768166</t>
         </is>
       </c>
       <c r="U101" t="inlineStr">
@@ -11259,31 +11251,39 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>0x3177792dd6a7185e37ae06612104cf5a35d137d7f535a889a83a7e9b7c174506</t>
+          <t>0xcfe218822e89cbef5841f3045f551cc65acf353d8e240f943e2b61c54ea79a68</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr"/>
+          <t>0xf4a8B27C9a13e298D65b5Cc072d252816B799C81</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>18.35495</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>1.4963</t>
+          <t>1.3337</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H102" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -11291,27 +11291,27 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>Almirante Brown vs Ciudad Bolivar</t>
+          <t>Estudiantes de Caseros vs Deportivo Madryn</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Estudiantes de Caseros</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>Ciudad Bolivar</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>0xbbcaa253cd967fbf933ff0d87a6f9744cafec0ed59dad5f1f76332aab01a3fa5</t>
+          <t>0xf238b96ec9e2421db79973de945f1fc0c3f8bb99c31cda32d011ebaabfd2db86</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>L19683447</t>
+          <t>L19683453</t>
         </is>
       </c>
       <c r="N102" t="inlineStr">
@@ -11336,7 +11336,7 @@
       </c>
       <c r="R102" t="inlineStr">
         <is>
-          <t>1786190491</t>
+          <t>1786205938</t>
         </is>
       </c>
       <c r="S102" t="inlineStr">
@@ -11346,7 +11346,7 @@
       </c>
       <c r="T102" t="inlineStr">
         <is>
-          <t>36.987305</t>
+          <t>2.996255</t>
         </is>
       </c>
       <c r="U102" t="inlineStr">
@@ -11363,27 +11363,23 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>0x54ed4ee2a6ebdab49498137f1accea542ead806f21430a0a771cc4872a044e43</t>
+          <t>0x1b9fcb29010a212f74af57040114154e78748f06a4d826be4397ddadb45ac31b</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr"/>
       <c r="D103" t="inlineStr">
         <is>
-          <t>20.10741</t>
+          <t>21.69</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>1.5437</t>
+          <t>1.4512</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -11391,11 +11387,7 @@
           <t>Under/Over (1.5)</t>
         </is>
       </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>Over 1.5</t>
-        </is>
-      </c>
+      <c r="G103" t="inlineStr"/>
       <c r="H103" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -11448,7 +11440,7 @@
       </c>
       <c r="R103" t="inlineStr">
         <is>
-          <t>1786190485</t>
+          <t>1786190525</t>
         </is>
       </c>
       <c r="S103" t="inlineStr">
@@ -11458,7 +11450,7 @@
       </c>
       <c r="T103" t="inlineStr">
         <is>
-          <t>36.979145</t>
+          <t>48.066482</t>
         </is>
       </c>
       <c r="U103" t="inlineStr">
@@ -11475,23 +11467,23 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>0x544fe5c906328d009917b591611ff3438cef85f8b42d9f67732cbbd5eabbb8dd</t>
+          <t>0x3177792dd6a7185e37ae06612104cf5a35d137d7f535a889a83a7e9b7c174506</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
         </is>
       </c>
       <c r="C104" t="inlineStr"/>
       <c r="D104" t="inlineStr">
         <is>
-          <t>21.69</t>
+          <t>18.35495</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>1.4512</t>
+          <t>1.4963</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -11552,7 +11544,7 @@
       </c>
       <c r="R104" t="inlineStr">
         <is>
-          <t>1786190485</t>
+          <t>1786190491</t>
         </is>
       </c>
       <c r="S104" t="inlineStr">
@@ -11562,7 +11554,7 @@
       </c>
       <c r="T104" t="inlineStr">
         <is>
-          <t>48.066482</t>
+          <t>36.987305</t>
         </is>
       </c>
       <c r="U104" t="inlineStr">
@@ -11579,23 +11571,27 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>0xb2f3ea804e1760a01d3a93678f0e2119f1ea2a9db0dc4711a06cc7bcba42b0c2</t>
+          <t>0x54ed4ee2a6ebdab49498137f1accea542ead806f21430a0a771cc4872a044e43</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr"/>
+          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>17.47</t>
+          <t>20.10741</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>1.405</t>
+          <t>1.5437</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -11603,7 +11599,11 @@
           <t>Under/Over (1.5)</t>
         </is>
       </c>
-      <c r="G105" t="inlineStr"/>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Over 1.5</t>
+        </is>
+      </c>
       <c r="H105" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -11611,27 +11611,27 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>Estudiantes de Caseros vs Deportivo Madryn</t>
+          <t>Almirante Brown vs Ciudad Bolivar</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>Estudiantes de Caseros</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Ciudad Bolivar</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>0xd61509e26f8645bb9780672f942c72c4b7dab577c2a01f04e1e09bce9b828765</t>
+          <t>0xbbcaa253cd967fbf933ff0d87a6f9744cafec0ed59dad5f1f76332aab01a3fa5</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>L19683453</t>
+          <t>L19683447</t>
         </is>
       </c>
       <c r="N105" t="inlineStr">
@@ -11656,7 +11656,7 @@
       </c>
       <c r="R105" t="inlineStr">
         <is>
-          <t>1786190461</t>
+          <t>1786190485</t>
         </is>
       </c>
       <c r="S105" t="inlineStr">
@@ -11666,7 +11666,7 @@
       </c>
       <c r="T105" t="inlineStr">
         <is>
-          <t>43.135802</t>
+          <t>36.979145</t>
         </is>
       </c>
       <c r="U105" t="inlineStr">
@@ -11683,7 +11683,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>0xa7eafbb77d425fc2347b4ee3e4f4e1b85f6d0f81420605db76ebfeeaa793a428</t>
+          <t>0x544fe5c906328d009917b591611ff3438cef85f8b42d9f67732cbbd5eabbb8dd</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -11760,7 +11760,7 @@
       </c>
       <c r="R106" t="inlineStr">
         <is>
-          <t>1786190458</t>
+          <t>1786190485</t>
         </is>
       </c>
       <c r="S106" t="inlineStr">
@@ -11787,110 +11787,318 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
+          <t>0xb2f3ea804e1760a01d3a93678f0e2119f1ea2a9db0dc4711a06cc7bcba42b0c2</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr"/>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>17.47</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>1.405</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr"/>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Primera Nacional</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>Estudiantes de Caseros vs Deportivo Madryn</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>Estudiantes de Caseros</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>Deportivo Madryn</t>
+        </is>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>0xd61509e26f8645bb9780672f942c72c4b7dab577c2a01f04e1e09bce9b828765</t>
+        </is>
+      </c>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>L19683453</t>
+        </is>
+      </c>
+      <c r="N107" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O107" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q107" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R107" t="inlineStr">
+        <is>
+          <t>1786190461</t>
+        </is>
+      </c>
+      <c r="S107" t="inlineStr">
+        <is>
+          <t>1786212000</t>
+        </is>
+      </c>
+      <c r="T107" t="inlineStr">
+        <is>
+          <t>43.135802</t>
+        </is>
+      </c>
+      <c r="U107" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V107" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>0xa7eafbb77d425fc2347b4ee3e4f4e1b85f6d0f81420605db76ebfeeaa793a428</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr"/>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>21.69</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>1.4512</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr"/>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Primera Nacional</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>Almirante Brown vs Ciudad Bolivar</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>Almirante Brown</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>Ciudad Bolivar</t>
+        </is>
+      </c>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>0xbbcaa253cd967fbf933ff0d87a6f9744cafec0ed59dad5f1f76332aab01a3fa5</t>
+        </is>
+      </c>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>L19683447</t>
+        </is>
+      </c>
+      <c r="N108" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O108" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P108" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q108" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R108" t="inlineStr">
+        <is>
+          <t>1786190458</t>
+        </is>
+      </c>
+      <c r="S108" t="inlineStr">
+        <is>
+          <t>1786212000</t>
+        </is>
+      </c>
+      <c r="T108" t="inlineStr">
+        <is>
+          <t>48.066482</t>
+        </is>
+      </c>
+      <c r="U108" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V108" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
           <t>0x5c5b512ea725fac30531bf5fe91f34f3ccc0eeff23890c18f25c3f329007c589</t>
         </is>
       </c>
-      <c r="B107" t="inlineStr">
+      <c r="B109" t="inlineStr">
         <is>
           <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
         </is>
       </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E107" t="inlineStr">
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
         <is>
           <t>1.3638</t>
         </is>
       </c>
-      <c r="F107" t="inlineStr">
+      <c r="F109" t="inlineStr">
         <is>
           <t>1X2</t>
         </is>
       </c>
-      <c r="G107" t="inlineStr">
+      <c r="G109" t="inlineStr">
         <is>
           <t>Tie</t>
         </is>
       </c>
-      <c r="H107" t="inlineStr">
-        <is>
-          <t>Primera Nacional</t>
-        </is>
-      </c>
-      <c r="I107" t="inlineStr">
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>Primera Nacional</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
         <is>
           <t>Almirante Brown vs Ciudad Bolivar</t>
         </is>
       </c>
-      <c r="J107" t="inlineStr">
+      <c r="J109" t="inlineStr">
         <is>
           <t>Almirante Brown</t>
         </is>
       </c>
-      <c r="K107" t="inlineStr">
+      <c r="K109" t="inlineStr">
         <is>
           <t>Ciudad Bolivar</t>
         </is>
       </c>
-      <c r="L107" t="inlineStr">
+      <c r="L109" t="inlineStr">
         <is>
           <t>0xd5906ce08d61f7c5ee45fcebd2c8baeed5558387398ea332817a4b632f439b6d</t>
         </is>
       </c>
-      <c r="M107" t="inlineStr">
+      <c r="M109" t="inlineStr">
         <is>
           <t>L19683447</t>
         </is>
       </c>
-      <c r="N107" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O107" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P107" t="inlineStr">
+      <c r="N109" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O109" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P109" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q107" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R107" t="inlineStr">
+      <c r="Q109" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R109" t="inlineStr">
         <is>
           <t>1786125660</t>
         </is>
       </c>
-      <c r="S107" t="inlineStr">
+      <c r="S109" t="inlineStr">
         <is>
           <t>1786212000</t>
         </is>
       </c>
-      <c r="T107" t="inlineStr">
+      <c r="T109" t="inlineStr">
         <is>
           <t>2.749141</t>
         </is>
       </c>
-      <c r="U107" t="inlineStr">
+      <c r="U109" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V107" t="inlineStr">
+      <c r="V109" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/Primera Nacional/trades.xlsx
+++ b/data/sxbet/ligas/Primera Nacional/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V109"/>
+  <dimension ref="A1:V110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,23 +531,23 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0x494bd95999d6775b2e923d6270b9b160b6a431bcd6ab5b22f79a2cfe4d911f80</t>
+          <t>0xf8aecc35b8e804254923734b6f89bca2cf00cb30505273b89ffba0a0c348e2c5</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0xBc04c6a7E9255Cb262632407a40Aa6344137555b</t>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
         </is>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>10.99999</t>
+          <t>67.15997</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -563,27 +563,27 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Gimnasia y Esgrima de Jujuy vs Tristan Suarez</t>
+          <t>CA All Boys vs CA Central Norte</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Gimnasia y Esgrima de Jujuy</t>
+          <t>CA All Boys</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Tristan Suarez</t>
+          <t>CA Central Norte</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0x9967827b768bd980ab7d0757f29afe285ae91ee95ad736a4ddcc46d0f68cf1bb</t>
+          <t>0x0ba86ae018e42e74063b250506eeeaed9224313c169502f5f97e0e2fb8ff1302</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>L19683507</t>
+          <t>L19668559</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1786349502</t>
+          <t>1786359536</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>15.492944</t>
+          <t>85.01262</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -635,7 +635,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0xdc1f7687d7452dd32612faa80dae516a650d157d1a94f1cd14e780fdbc95c899</t>
+          <t>0x494bd95999d6775b2e923d6270b9b160b6a431bcd6ab5b22f79a2cfe4d911f80</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -712,7 +712,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1786349464</t>
+          <t>1786349502</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -739,23 +739,23 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0xe70516113cb626418e16d5940b7952c123bd3afbc9ae8fb08b6d8a46cfc93917</t>
+          <t>0xdc1f7687d7452dd32612faa80dae516a650d157d1a94f1cd14e780fdbc95c899</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0x49c03d69c92f4aEa65FBF1F149A1ac3Bf31A37C6</t>
+          <t>0xBc04c6a7E9255Cb262632407a40Aa6344137555b</t>
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>231.99994</t>
+          <t>10.99999</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -771,27 +771,27 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>San Martin Tucuman vs San Martín de San Juan</t>
+          <t>Gimnasia y Esgrima de Jujuy vs Tristan Suarez</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>San Martin Tucuman</t>
+          <t>Gimnasia y Esgrima de Jujuy</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>San Martín de San Juan</t>
+          <t>Tristan Suarez</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0x20f1a35dae3d2a458c7a6a3e312e646a320245e89d843105ba9b217e1cd46c9e</t>
+          <t>0x9967827b768bd980ab7d0757f29afe285ae91ee95ad736a4ddcc46d0f68cf1bb</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>L19682528</t>
+          <t>L19683507</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -816,17 +816,17 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1786315295</t>
+          <t>1786349464</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>1786309200</t>
+          <t>1786384800</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>260.67409</t>
+          <t>15.492944</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -843,28 +843,28 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0x8a82110b5ad97ac1c2de4721106d20fdd9060513206960520e7155a6e2b20612</t>
+          <t>0xe70516113cb626418e16d5940b7952c123bd3afbc9ae8fb08b6d8a46cfc93917</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x49c03d69c92f4aEa65FBF1F149A1ac3Bf31A37C6</t>
         </is>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>18.85306</t>
+          <t>231.99994</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.3875</t>
+          <t>1.89</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Primera Nacional</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
@@ -890,7 +890,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0x710577a276e495ee3f90c1efed84c57aad13b2a5a77b9b1f1045dc6c20df1b82</t>
+          <t>0x20f1a35dae3d2a458c7a6a3e312e646a320245e89d843105ba9b217e1cd46c9e</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -920,7 +920,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1786315013</t>
+          <t>1786315295</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>48.653058</t>
+          <t>260.67409</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -947,7 +947,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0x99cae5762d48bf6225a2833cebf0caac6f2be5141693c86d119bba55fecb00af</t>
+          <t>0x8a82110b5ad97ac1c2de4721106d20fdd9060513206960520e7155a6e2b20612</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -958,7 +958,7 @@
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>117.43306</t>
+          <t>18.85306</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0x4f02331cd42a68f65ea16d62aac0c6b123d9400d12a4d556f3a72df894da02fb</t>
+          <t>0x710577a276e495ee3f90c1efed84c57aad13b2a5a77b9b1f1045dc6c20df1b82</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -1024,7 +1024,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1786314895</t>
+          <t>1786315013</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1034,7 +1034,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>303.053058</t>
+          <t>48.653058</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1051,23 +1051,23 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0x4030f87453819c2a532820e812d084e6b4bb480048daa74b20c2d6e02cb96f44</t>
+          <t>0x99cae5762d48bf6225a2833cebf0caac6f2be5141693c86d119bba55fecb00af</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.25944</t>
+          <t>117.43306</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.3675</t>
+          <t>1.3875</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1098,7 +1098,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0x710577a276e495ee3f90c1efed84c57aad13b2a5a77b9b1f1045dc6c20df1b82</t>
+          <t>0x4f02331cd42a68f65ea16d62aac0c6b123d9400d12a4d556f3a72df894da02fb</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1128,7 +1128,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1786311747</t>
+          <t>1786314895</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1138,7 +1138,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.705959</t>
+          <t>303.053058</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1155,39 +1155,31 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0x94334ff3be3abb398e288ea2bdc325dbea166976a777d4b3565d6adf6e74cceb</t>
+          <t>0x4030f87453819c2a532820e812d084e6b4bb480048daa74b20c2d6e02cb96f44</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0.25944</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.545</t>
+          <t>1.3675</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Over 1.5</t>
-        </is>
-      </c>
+          <t>Primera Nacional</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -1210,7 +1202,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0x59f5c83d1ebabf219c4e416ecb6303622840a732d32e28a4ca19fdba0d4e206d</t>
+          <t>0x710577a276e495ee3f90c1efed84c57aad13b2a5a77b9b1f1045dc6c20df1b82</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1240,7 +1232,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1786309862</t>
+          <t>1786311747</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1250,7 +1242,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1.834862</t>
+          <t>0.705959</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1267,31 +1259,39 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0xc96803526daa07f4eae1fbfe8d09be9d49a0e7e2ce24d0288f9d3ab9ec387e36</t>
+          <t>0x94334ff3be3abb398e288ea2bdc325dbea166976a777d4b3565d6adf6e74cceb</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0x4a09916b1325Eed50eE8973B13742a205B0B7c7E</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr"/>
+          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.825</t>
+          <t>1.545</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr"/>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Over 1.5</t>
+        </is>
+      </c>
       <c r="H9" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -1299,27 +1299,27 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Racing de Cordoba vs San Miguel</t>
+          <t>San Martin Tucuman vs San Martín de San Juan</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Racing de Cordoba</t>
+          <t>San Martin Tucuman</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>San Martín de San Juan</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0xb291f54e66fa1539bf7206876cb79292f9c9cd3cebed6ca59247514b369a28fb</t>
+          <t>0x59f5c83d1ebabf219c4e416ecb6303622840a732d32e28a4ca19fdba0d4e206d</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>L19683501</t>
+          <t>L19682528</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1344,17 +1344,17 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1786307586</t>
+          <t>1786309862</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>1786302000</t>
+          <t>1786309200</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>60.606061</t>
+          <t>1.834862</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1371,39 +1371,31 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0xe508af858531cbb110be0edc19b46f9f847f5373f422a56dc4f6091f724877c2</t>
+          <t>0xc96803526daa07f4eae1fbfe8d09be9d49a0e7e2ce24d0288f9d3ab9ec387e36</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x4a09916b1325Eed50eE8973B13742a205B0B7c7E</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>42.02</t>
+          <t>50</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.825</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Over 2.5</t>
-        </is>
-      </c>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -1426,7 +1418,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0xb00a08202acc66af81e3cc28141951f5744b2edb09c13699c361640638e0580a</t>
+          <t>0xb291f54e66fa1539bf7206876cb79292f9c9cd3cebed6ca59247514b369a28fb</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1456,7 +1448,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1786306456</t>
+          <t>1786307586</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1466,7 +1458,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>525.25</t>
+          <t>60.606061</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1483,7 +1475,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0x6d0e9cce02624418d7b75dc11802dbf4900745db1d1f0ec0ee6d8804e67faced</t>
+          <t>0xe508af858531cbb110be0edc19b46f9f847f5373f422a56dc4f6091f724877c2</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1568,7 +1560,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1786306379</t>
+          <t>1786306456</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1595,7 +1587,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0xfbf539c8fecb9ae92fbe1749fa31c242f747ee8b7d8b6d79b9eb6a315ac4109a</t>
+          <t>0x6d0e9cce02624418d7b75dc11802dbf4900745db1d1f0ec0ee6d8804e67faced</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1610,22 +1602,22 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>25.88</t>
+          <t>42.02</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.0962</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Over 2.0</t>
+          <t>Over 2.5</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1650,7 +1642,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>0xb291f54e66fa1539bf7206876cb79292f9c9cd3cebed6ca59247514b369a28fb</t>
+          <t>0xb00a08202acc66af81e3cc28141951f5744b2edb09c13699c361640638e0580a</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1680,7 +1672,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1786306378</t>
+          <t>1786306379</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -1690,7 +1682,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>268.883117</t>
+          <t>525.25</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1707,31 +1699,39 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0x2ce4118d8299ef054cc6439e8191ab57041190d43c1b322f7656f46a915f66a7</t>
+          <t>0xfbf539c8fecb9ae92fbe1749fa31c242f747ee8b7d8b6d79b9eb6a315ac4109a</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>11.65</t>
+          <t>25.88</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.0888</t>
+          <t>1.0962</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr"/>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Over 2.0</t>
+        </is>
+      </c>
       <c r="H13" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -1739,27 +1739,27 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Godoy Cruz vs Chaco For Ever</t>
+          <t>Racing de Cordoba vs San Miguel</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Racing de Cordoba</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>0xa5f02d0d08d0dcc4818948397f0f26c77f90b87182cec4d62ab01f77352671a1</t>
+          <t>0xb291f54e66fa1539bf7206876cb79292f9c9cd3cebed6ca59247514b369a28fb</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>L19683484</t>
+          <t>L19683501</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1784,17 +1784,17 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1786305067</t>
+          <t>1786306378</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>1786303800</t>
+          <t>1786302000</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>131.267606</t>
+          <t>268.883117</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1811,39 +1811,31 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0x72a01c47ea710f8819c55b38617462ca579e333f91db40e5ab1feff1d3de96c8</t>
+          <t>0x2ce4118d8299ef054cc6439e8191ab57041190d43c1b322f7656f46a915f66a7</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>102.18997</t>
+          <t>11.65</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1.8087</t>
+          <t>1.0888</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Primera Nacional</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Colon de Santa Fe</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -1851,27 +1843,27 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Colon de Santa Fe vs San Telmo</t>
+          <t>Godoy Cruz vs Chaco For Ever</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Colon de Santa Fe</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>0xbca9ed7d23a7df6c8ab98ab2ffc6649f2d4bd3d9007bd0ecf103e453c87addac</t>
+          <t>0xa5f02d0d08d0dcc4818948397f0f26c77f90b87182cec4d62ab01f77352671a1</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>L19683494</t>
+          <t>L19683484</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1896,17 +1888,17 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1786305018</t>
+          <t>1786305067</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>1786300200</t>
+          <t>1786303800</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>126.35545</t>
+          <t>131.267606</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -1923,7 +1915,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0x48ad1a825a577db64992a5c2f61f562d82c8f17820251af179f0cdf9d5e6b577</t>
+          <t>0x72a01c47ea710f8819c55b38617462ca579e333f91db40e5ab1feff1d3de96c8</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1953,7 +1945,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Colon de Santa Fe 0</t>
+          <t>Colon de Santa Fe</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1978,7 +1970,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>0x9c15c50c33bf4b091bef5a468ce1fe4a2593b78db6048cae08ab186caadf08a9</t>
+          <t>0xbca9ed7d23a7df6c8ab98ab2ffc6649f2d4bd3d9007bd0ecf103e453c87addac</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -2035,31 +2027,39 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0x241c6cdee87bcff9c9e1e77941a5ecd05acb972d4c07e1cfc562414003f5c59c</t>
+          <t>0x48ad1a825a577db64992a5c2f61f562d82c8f17820251af179f0cdf9d5e6b577</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>63.89997</t>
+          <t>102.18997</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1.8912</t>
+          <t>1.8087</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr"/>
+          <t>Primera Nacional</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Colon de Santa Fe 0</t>
+        </is>
+      </c>
       <c r="H16" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -2067,27 +2067,27 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Racing de Cordoba vs San Miguel</t>
+          <t>Colon de Santa Fe vs San Telmo</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Racing de Cordoba</t>
+          <t>Colon de Santa Fe</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>0xb00a08202acc66af81e3cc28141951f5744b2edb09c13699c361640638e0580a</t>
+          <t>0x9c15c50c33bf4b091bef5a468ce1fe4a2593b78db6048cae08ab186caadf08a9</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>L19683501</t>
+          <t>L19683494</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -2112,17 +2112,17 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1786304709</t>
+          <t>1786305018</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>1786302000</t>
+          <t>1786300200</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>71.697021</t>
+          <t>126.35545</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2139,7 +2139,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0xfb092fb802f6de6249f78cd6b0c995923dcd8a18d766d60718068deca14131d2</t>
+          <t>0x241c6cdee87bcff9c9e1e77941a5ecd05acb972d4c07e1cfc562414003f5c59c</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2150,7 +2150,7 @@
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>52.23996</t>
+          <t>63.89997</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>1786304687</t>
+          <t>1786304709</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -2226,7 +2226,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>58.614261</t>
+          <t>71.697021</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2243,7 +2243,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0xdaad372a2d56f6f987e31c931aed692c41df131e0f5ffc29a5e5b9202518a8ad</t>
+          <t>0xfb092fb802f6de6249f78cd6b0c995923dcd8a18d766d60718068deca14131d2</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2254,17 +2254,17 @@
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>52.23996</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.2563</t>
+          <t>1.8912</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Asian Handicap (0.5)</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G18" t="inlineStr"/>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>0x6dbad77d129f55a581762668ca1964af6cce4241516257e981ed02638805382a</t>
+          <t>0xb00a08202acc66af81e3cc28141951f5744b2edb09c13699c361640638e0580a</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -2320,7 +2320,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>1786304596</t>
+          <t>1786304687</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>39.02439</t>
+          <t>58.614261</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2347,7 +2347,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0xd8c270eff581f800f6dfee154ad07fcaa13887305309b80012750a0200954653</t>
+          <t>0xdaad372a2d56f6f987e31c931aed692c41df131e0f5ffc29a5e5b9202518a8ad</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2358,17 +2358,17 @@
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>104.40999</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1.685</t>
+          <t>1.2563</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (0.5)</t>
         </is>
       </c>
       <c r="G19" t="inlineStr"/>
@@ -2394,7 +2394,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>0x48447168804e92d195e0c849cfb7ae548e076f102e1005f3756585b3d18ea65c</t>
+          <t>0x6dbad77d129f55a581762668ca1964af6cce4241516257e981ed02638805382a</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -2424,7 +2424,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>1786304566</t>
+          <t>1786304596</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -2434,7 +2434,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>152.423343</t>
+          <t>39.02439</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2451,7 +2451,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0x584df9c83be504ffadc29cf9bc05886a622203a90bdf8fd90fe15998dca2c79a</t>
+          <t>0xd8c270eff581f800f6dfee154ad07fcaa13887305309b80012750a0200954653</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2462,12 +2462,12 @@
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>30.76</t>
+          <t>104.40999</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.8388</t>
+          <t>1.685</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -2483,27 +2483,27 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Godoy Cruz vs Chaco For Ever</t>
+          <t>Racing de Cordoba vs San Miguel</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Racing de Cordoba</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0x9c19e4c1fd9646506f8ea14e2b1be19b49a5ab4dc1a7bf40167705a4ae2b338b</t>
+          <t>0x48447168804e92d195e0c849cfb7ae548e076f102e1005f3756585b3d18ea65c</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>L19683484</t>
+          <t>L19683501</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -2528,17 +2528,17 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>1786304409</t>
+          <t>1786304566</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>1786303800</t>
+          <t>1786302000</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>36.673621</t>
+          <t>152.423343</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2555,27 +2555,23 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0x80bb89bcfcad865ae79dd791b8e50e1efe79465dcaef80ef22f91624a9a206e0</t>
+          <t>0x584df9c83be504ffadc29cf9bc05886a622203a90bdf8fd90fe15998dca2c79a</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>164.56999</t>
+          <t>30.76</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1.5875</t>
+          <t>1.8388</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -2583,11 +2579,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+      <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -2595,27 +2587,27 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>CA Colegiales vs Patronato</t>
+          <t>Godoy Cruz vs Chaco For Ever</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>CA Colegiales</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0x08cf3f4d7a357213e26484ea0db7a018932df0928a98202f91241b88b1990c60</t>
+          <t>0x9c19e4c1fd9646506f8ea14e2b1be19b49a5ab4dc1a7bf40167705a4ae2b338b</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>L19683449</t>
+          <t>L19683484</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -2640,17 +2632,17 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>1786304222</t>
+          <t>1786304409</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>1786298400</t>
+          <t>1786303800</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>280.119132</t>
+          <t>36.673621</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -2667,7 +2659,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0x4a29c98cff774b7281c745ce8241168cf83b95715fb62c195dfe0bdfd4993ffa</t>
+          <t>0x80bb89bcfcad865ae79dd791b8e50e1efe79465dcaef80ef22f91624a9a206e0</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2682,22 +2674,22 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>50.96999</t>
+          <t>164.56999</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1.6187</t>
+          <t>1.5875</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Primera Nacional</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>CA Colegiales 0</t>
+          <t>Tie</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2722,7 +2714,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0x3fa48fbf2a59e0b45def889e06df3d2da646e9465f9af4f1b88581fea7fb4496</t>
+          <t>0x08cf3f4d7a357213e26484ea0db7a018932df0928a98202f91241b88b1990c60</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -2752,7 +2744,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>1786304216</t>
+          <t>1786304222</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -2762,7 +2754,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>82.375741</t>
+          <t>280.119132</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -2779,12 +2771,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0x606477ca73e4e38677cfe19e9dbb8d21dd44116004cd1a6b689a66845a1f33c5</t>
+          <t>0x4a29c98cff774b7281c745ce8241168cf83b95715fb62c195dfe0bdfd4993ffa</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2794,22 +2786,22 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>47.49</t>
+          <t>50.96999</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.6187</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Primera Nacional</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tie</t>
+          <t>CA Colegiales 0</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2834,7 +2826,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0x08cf3f4d7a357213e26484ea0db7a018932df0928a98202f91241b88b1990c60</t>
+          <t>0x3fa48fbf2a59e0b45def889e06df3d2da646e9465f9af4f1b88581fea7fb4496</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -2864,7 +2856,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>1786304193</t>
+          <t>1786304216</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -2874,7 +2866,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>79.15</t>
+          <t>82.375741</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -2891,12 +2883,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0x471461bdea5d2a1f048ae19a536ae904425043d9ce35e662e416d1892b8ab682</t>
+          <t>0x606477ca73e4e38677cfe19e9dbb8d21dd44116004cd1a6b689a66845a1f33c5</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2906,22 +2898,22 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>45.36</t>
+          <t>47.49</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1.6275</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Primera Nacional</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>CA Colegiales 0</t>
+          <t>Tie</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2946,7 +2938,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0x3fa48fbf2a59e0b45def889e06df3d2da646e9465f9af4f1b88581fea7fb4496</t>
+          <t>0x08cf3f4d7a357213e26484ea0db7a018932df0928a98202f91241b88b1990c60</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -2976,7 +2968,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>1786304137</t>
+          <t>1786304193</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -2986,7 +2978,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>72.286853</t>
+          <t>79.15</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -3003,31 +2995,39 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0x2b918c36189e27805e61d743881205705b15ab4bdbf93fa4149c03b299488496</t>
+          <t>0x471461bdea5d2a1f048ae19a536ae904425043d9ce35e662e416d1892b8ab682</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>291.91999</t>
+          <t>45.36</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1.8125</t>
+          <t>1.6275</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr"/>
+          <t>Primera Nacional</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>CA Colegiales 0</t>
+        </is>
+      </c>
       <c r="H25" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -3050,7 +3050,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0x08cf3f4d7a357213e26484ea0db7a018932df0928a98202f91241b88b1990c60</t>
+          <t>0x3fa48fbf2a59e0b45def889e06df3d2da646e9465f9af4f1b88581fea7fb4496</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -3080,7 +3080,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>1786304032</t>
+          <t>1786304137</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
@@ -3090,7 +3090,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>359.286142</t>
+          <t>72.286853</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3107,27 +3107,23 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0x0c986442e558e0ecef4ac6ae5c05b398f82bc22bf0a12f073b441ebce3f8f73e</t>
+          <t>0x2b918c36189e27805e61d743881205705b15ab4bdbf93fa4149c03b299488496</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>0x161ba9aad05022c88726A1D1244fDF624e51BFD5</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>291.91999</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1.5063</t>
+          <t>1.8125</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -3135,11 +3131,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>Colon de Santa Fe</t>
-        </is>
-      </c>
+      <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -3147,27 +3139,27 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Colon de Santa Fe vs San Telmo</t>
+          <t>CA Colegiales vs Patronato</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Colon de Santa Fe</t>
+          <t>CA Colegiales</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>0x1a11ec80edeaae24566c4f4f891cc2afc56b377b24997a6e8ee533eeaaad5c92</t>
+          <t>0x08cf3f4d7a357213e26484ea0db7a018932df0928a98202f91241b88b1990c60</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>L19683494</t>
+          <t>L19683449</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -3192,17 +3184,17 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>1786303960</t>
+          <t>1786304032</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>1786300200</t>
+          <t>1786298400</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>4.938272</t>
+          <t>359.286142</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -3219,31 +3211,39 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0x2a347762aef526a0953efcb99ce105f109d3055f0d91ab8c6f756cd50ff191d0</t>
+          <t>0x0c986442e558e0ecef4ac6ae5c05b398f82bc22bf0a12f073b441ebce3f8f73e</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr"/>
+          <t>0x161ba9aad05022c88726A1D1244fDF624e51BFD5</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1.07999</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1.5775</t>
+          <t>1.5063</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Colon de Santa Fe</t>
+        </is>
+      </c>
       <c r="H27" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -3251,27 +3251,27 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Godoy Cruz vs Chaco For Ever</t>
+          <t>Colon de Santa Fe vs San Telmo</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Colon de Santa Fe</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>0x8a3835f02766a90c02150e223fdcaa0f380cffe1bd489dd896b621cb4de6a216</t>
+          <t>0x1a11ec80edeaae24566c4f4f891cc2afc56b377b24997a6e8ee533eeaaad5c92</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>L19683484</t>
+          <t>L19683494</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -3296,17 +3296,17 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>1786303869</t>
+          <t>1786303960</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>1786303800</t>
+          <t>1786300200</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>1.870113</t>
+          <t>4.938272</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -3323,28 +3323,28 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0xf1ea587ba3fa2b6f394d282689f029176ee146013ab745dcfa61570d0ec1af54</t>
+          <t>0x2a347762aef526a0953efcb99ce105f109d3055f0d91ab8c6f756cd50ff191d0</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
         </is>
       </c>
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
-          <t>66.77496</t>
+          <t>1.07999</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>1.1938</t>
+          <t>1.5775</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (2)</t>
         </is>
       </c>
       <c r="G28" t="inlineStr"/>
@@ -3355,27 +3355,27 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>CA Colegiales vs Patronato</t>
+          <t>Godoy Cruz vs Chaco For Ever</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>CA Colegiales</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>0x6033340ba69fb7874ae22715f395c0926449aa18c6ec5295e2568fe9a173664d</t>
+          <t>0x8a3835f02766a90c02150e223fdcaa0f380cffe1bd489dd896b621cb4de6a216</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>L19683449</t>
+          <t>L19683484</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -3400,17 +3400,17 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>1786303811</t>
+          <t>1786303869</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>1786298400</t>
+          <t>1786303800</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>344.644955</t>
+          <t>1.870113</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -3427,7 +3427,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0x83f468f50e882b1c9b4663834cfdbddae84368823e2297b07a8a228b7252f9d0</t>
+          <t>0xf1ea587ba3fa2b6f394d282689f029176ee146013ab745dcfa61570d0ec1af54</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3438,17 +3438,17 @@
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
-          <t>20.75148</t>
+          <t>66.77496</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>1.4275</t>
+          <t>1.1938</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G29" t="inlineStr"/>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>0x5063fd7c88c1b369ed4a83e39411f4287c83048fafbc24740f9ecb68019a60ec</t>
+          <t>0x6033340ba69fb7874ae22715f395c0926449aa18c6ec5295e2568fe9a173664d</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>48.541474</t>
+          <t>344.644955</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -3531,28 +3531,28 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0x5d59910b62dd3a569254988b87a126db28ce8123f67bea999e650c42a85e456c</t>
+          <t>0x83f468f50e882b1c9b4663834cfdbddae84368823e2297b07a8a228b7252f9d0</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
-          <t>64.86487</t>
+          <t>20.75148</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1.075</t>
+          <t>1.4275</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Under/Over (0.5)</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G30" t="inlineStr"/>
@@ -3563,27 +3563,27 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Club Atletico Mitre de Santiago del Estero vs Defensores de Belgrano Buenos Aires</t>
+          <t>CA Colegiales vs Patronato</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Club Atletico Mitre de Santiago del Estero</t>
+          <t>CA Colegiales</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano Buenos Aires</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>0x7423d14fbc1277a1b44ab6287b237b4f12599476710984e2df8514e1e505203b</t>
+          <t>0x5063fd7c88c1b369ed4a83e39411f4287c83048fafbc24740f9ecb68019a60ec</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>L19683493</t>
+          <t>L19683449</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -3608,17 +3608,17 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>1786303551</t>
+          <t>1786303811</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>1786302000</t>
+          <t>1786298400</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>864.864933</t>
+          <t>48.541474</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -3635,7 +3635,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0x54e4c2b9fcb34a87d3118c2c4aa1d528e53ecdeb3b19d58ec93ceabdcf9789a0</t>
+          <t>0x5d59910b62dd3a569254988b87a126db28ce8123f67bea999e650c42a85e456c</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3646,17 +3646,17 @@
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
-          <t>155.22388</t>
+          <t>64.86487</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1.1625</t>
+          <t>1.075</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Under/Over (1)</t>
+          <t>Under/Over (0.5)</t>
         </is>
       </c>
       <c r="G31" t="inlineStr"/>
@@ -3682,7 +3682,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>0x4f7afe558099a628e7275525f608e3e5d976f6f0ae76324c03ac2a8d33384e1b</t>
+          <t>0x7423d14fbc1277a1b44ab6287b237b4f12599476710984e2df8514e1e505203b</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -3722,7 +3722,7 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>955.223877</t>
+          <t>864.864933</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -3739,7 +3739,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0xac12d313bf6318f639126e42c96989b9e78cbb4aeafba2d7a6842ecaab1d4679</t>
+          <t>0x54e4c2b9fcb34a87d3118c2c4aa1d528e53ecdeb3b19d58ec93ceabdcf9789a0</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3750,17 +3750,17 @@
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
-          <t>29.36999</t>
+          <t>155.22388</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>1.6288</t>
+          <t>1.1625</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (1)</t>
         </is>
       </c>
       <c r="G32" t="inlineStr"/>
@@ -3771,27 +3771,27 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Racing de Cordoba vs San Miguel</t>
+          <t>Club Atletico Mitre de Santiago del Estero vs Defensores de Belgrano Buenos Aires</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Racing de Cordoba</t>
+          <t>Club Atletico Mitre de Santiago del Estero</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Defensores de Belgrano Buenos Aires</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0x48447168804e92d195e0c849cfb7ae548e076f102e1005f3756585b3d18ea65c</t>
+          <t>0x4f7afe558099a628e7275525f608e3e5d976f6f0ae76324c03ac2a8d33384e1b</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>L19683501</t>
+          <t>L19683493</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -3816,7 +3816,7 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>1786303457</t>
+          <t>1786303551</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
@@ -3826,7 +3826,7 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>46.711714</t>
+          <t>955.223877</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -3843,39 +3843,31 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0xab77c0bf2f6ec1315e378c5db8b6863eb08357a9b49d9ba43bcce724926da176</t>
+          <t>0xac12d313bf6318f639126e42c96989b9e78cbb4aeafba2d7a6842ecaab1d4679</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>29.36999</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>1.5175</t>
+          <t>1.6288</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>Colon de Santa Fe -0.5</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -3883,27 +3875,27 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Colon de Santa Fe vs San Telmo</t>
+          <t>Racing de Cordoba vs San Miguel</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Colon de Santa Fe</t>
+          <t>Racing de Cordoba</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>0x12375b1d9ef51c6465eb968d63b1ce25f63b0af22de8742ede4e1070f2e04c6b</t>
+          <t>0x48447168804e92d195e0c849cfb7ae548e076f102e1005f3756585b3d18ea65c</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>L19683494</t>
+          <t>L19683501</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -3928,17 +3920,17 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>1786302968</t>
+          <t>1786303457</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>1786300200</t>
+          <t>1786302000</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>2.801932</t>
+          <t>46.711714</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -3955,12 +3947,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0x7262b8ffc279b263369649339936e85dc19d4d92bf11fad680b40a45ad4a7442</t>
+          <t>0xab77c0bf2f6ec1315e378c5db8b6863eb08357a9b49d9ba43bcce724926da176</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -3970,22 +3962,22 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>23.24</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>1.3388</t>
+          <t>1.5175</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Colon de Santa Fe -1</t>
+          <t>Colon de Santa Fe -0.5</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -4010,7 +4002,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0x4b323aab38dd8f5096dcd1965ce7dc05c69ab73371e55e810b7a5aee356bf244</t>
+          <t>0x12375b1d9ef51c6465eb968d63b1ce25f63b0af22de8742ede4e1070f2e04c6b</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -4040,7 +4032,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>1786302417</t>
+          <t>1786302968</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
@@ -4050,7 +4042,7 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>68.605166</t>
+          <t>2.801932</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -4067,7 +4059,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0xaef8a42b6335c8c59cb7bb616441203e8516097ce0e7adb9c1dfe622d7b8a46a</t>
+          <t>0x7262b8ffc279b263369649339936e85dc19d4d92bf11fad680b40a45ad4a7442</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4075,23 +4067,31 @@
           <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr"/>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>14.3554</t>
+          <t>23.24</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>1.0513</t>
+          <t>1.3388</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr"/>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Colon de Santa Fe -1</t>
+        </is>
+      </c>
       <c r="H35" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -4099,27 +4099,27 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Deportivo Moron vs Acassuso</t>
+          <t>Colon de Santa Fe vs San Telmo</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Deportivo Moron</t>
+          <t>Colon de Santa Fe</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>0x7514a255ce41be3c5db9f8849ba04e78dab80f02d1fe78c2aae82bbc843a9745</t>
+          <t>0x4b323aab38dd8f5096dcd1965ce7dc05c69ab73371e55e810b7a5aee356bf244</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>L19683452</t>
+          <t>L19683494</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -4144,17 +4144,17 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>1786301685</t>
+          <t>1786302417</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>1786298400</t>
+          <t>1786300200</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>280.105366</t>
+          <t>68.605166</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
@@ -4171,7 +4171,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0x9cd0c1e560dfbdd3bb0ca9522422167bdbc75ef5c7813dbe00ce4bee50d0f1be</t>
+          <t>0xaef8a42b6335c8c59cb7bb616441203e8516097ce0e7adb9c1dfe622d7b8a46a</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4182,12 +4182,12 @@
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
-          <t>13.80272</t>
+          <t>14.3554</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>1.0488</t>
+          <t>1.0513</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -4248,7 +4248,7 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>1786301534</t>
+          <t>1786301685</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
@@ -4258,7 +4258,7 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>283.132718</t>
+          <t>280.105366</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
@@ -4275,7 +4275,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0x9036645c2b6fdeee93c9912e60b360f0e894db0b98a32ed8106dd074362ac356</t>
+          <t>0x9cd0c1e560dfbdd3bb0ca9522422167bdbc75ef5c7813dbe00ce4bee50d0f1be</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4283,19 +4283,15 @@
           <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr">
         <is>
-          <t>37.59</t>
+          <t>13.80272</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>1.1225</t>
+          <t>1.0488</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -4303,11 +4299,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>CA Colegiales</t>
-        </is>
-      </c>
+      <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -4315,27 +4307,27 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>CA Colegiales vs Patronato</t>
+          <t>Deportivo Moron vs Acassuso</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>CA Colegiales</t>
+          <t>Deportivo Moron</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>0x6033340ba69fb7874ae22715f395c0926449aa18c6ec5295e2568fe9a173664d</t>
+          <t>0x7514a255ce41be3c5db9f8849ba04e78dab80f02d1fe78c2aae82bbc843a9745</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>L19683449</t>
+          <t>L19683452</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -4360,7 +4352,7 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>1786301228</t>
+          <t>1786301534</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
@@ -4370,7 +4362,7 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>306.857143</t>
+          <t>283.132718</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
@@ -4387,12 +4379,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0xd9eff492baa46fea0da1221b63ca70a7e18beec129de6ebec5453a1b9e6bfcf8</t>
+          <t>0x9036645c2b6fdeee93c9912e60b360f0e894db0b98a32ed8106dd074362ac356</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -4402,22 +4394,22 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>37.59</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>1.4263</t>
+          <t>1.1225</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Asian Handicap (0.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>CA Colegiales +0.5</t>
+          <t>CA Colegiales</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -4442,7 +4434,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>0xf03b2761ed02376d644cd19d08d1923efb50cd17956a930c587e812207a86746</t>
+          <t>0x6033340ba69fb7874ae22715f395c0926449aa18c6ec5295e2568fe9a173664d</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -4472,7 +4464,7 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>1786301216</t>
+          <t>1786301228</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
@@ -4482,7 +4474,7 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>46.920821</t>
+          <t>306.857143</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
@@ -4499,12 +4491,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0xc72322e8ff04e28165d90bbcfa3c4b34aa19dd5fc1215e13ba7e1ce6362a9292</t>
+          <t>0xd9eff492baa46fea0da1221b63ca70a7e18beec129de6ebec5453a1b9e6bfcf8</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -4514,7 +4506,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>7.93</t>
+          <t>20</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -4524,12 +4516,12 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (0.5)</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Racing de Cordoba</t>
+          <t>CA Colegiales +0.5</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -4539,27 +4531,27 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Racing de Cordoba vs San Miguel</t>
+          <t>CA Colegiales vs Patronato</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Racing de Cordoba</t>
+          <t>CA Colegiales</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>0x48447168804e92d195e0c849cfb7ae548e076f102e1005f3756585b3d18ea65c</t>
+          <t>0xf03b2761ed02376d644cd19d08d1923efb50cd17956a930c587e812207a86746</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>L19683501</t>
+          <t>L19683449</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -4584,17 +4576,17 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>1786301162</t>
+          <t>1786301216</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>1786302000</t>
+          <t>1786298400</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>18.604106</t>
+          <t>46.920821</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
@@ -4611,12 +4603,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0xd37a1d074e8819ce033a62d6fe3bb026c46529f33aed65aaac63e3d53cb8ce3e</t>
+          <t>0xc72322e8ff04e28165d90bbcfa3c4b34aa19dd5fc1215e13ba7e1ce6362a9292</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>0x5022174051792ac42d3af7Ff6bC9cf78a6aE3f32</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -4626,22 +4618,22 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7.93</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>1.4287</t>
+          <t>1.4263</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Under/Over (0.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Over 0.5</t>
+          <t>Racing de Cordoba</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -4651,27 +4643,27 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Atlanta vs Temperley</t>
+          <t>Racing de Cordoba vs San Miguel</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Racing de Cordoba</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>0x84c2bb083fa51c1fc591f5ac9524e09d26434823e44ca466e2af8bd17ae651cb</t>
+          <t>0x48447168804e92d195e0c849cfb7ae548e076f102e1005f3756585b3d18ea65c</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>L19683448</t>
+          <t>L19683501</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -4696,17 +4688,17 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>1786300699</t>
+          <t>1786301162</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>1786294800</t>
+          <t>1786302000</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>11.661808</t>
+          <t>18.604106</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
@@ -4723,23 +4715,27 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0x0199716d54c5764cbf1a6783da6c106cf378f2c6b96892a13d7019f5cb41b3fa</t>
+          <t>0xd37a1d074e8819ce033a62d6fe3bb026c46529f33aed65aaac63e3d53cb8ce3e</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr"/>
+          <t>0x5022174051792ac42d3af7Ff6bC9cf78a6aE3f32</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>16.84</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>1.1262</t>
+          <t>1.4287</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -4747,7 +4743,11 @@
           <t>Under/Over (0.5)</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr"/>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Over 0.5</t>
+        </is>
+      </c>
       <c r="H41" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -4755,27 +4755,27 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Godoy Cruz vs Chaco For Ever</t>
+          <t>Atlanta vs Temperley</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>0x9c696117152178b9240c2e3eddca6b53432d4a4937a20042677cd1f666604f23</t>
+          <t>0x84c2bb083fa51c1fc591f5ac9524e09d26434823e44ca466e2af8bd17ae651cb</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>L19683484</t>
+          <t>L19683448</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -4800,17 +4800,17 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>1786300516</t>
+          <t>1786300699</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>1786303800</t>
+          <t>1786294800</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>133.386139</t>
+          <t>11.661808</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
@@ -4827,28 +4827,28 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0x84f162af96f80a1f61f37a3b12a3dab48dcffde9bd10d0cea022df759f18111f</t>
+          <t>0x0199716d54c5764cbf1a6783da6c106cf378f2c6b96892a13d7019f5cb41b3fa</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr">
         <is>
-          <t>36.84547</t>
+          <t>16.84</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>1.1362</t>
+          <t>1.1262</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Primera Nacional</t>
+          <t>Under/Over (0.5)</t>
         </is>
       </c>
       <c r="G42" t="inlineStr"/>
@@ -4859,27 +4859,27 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Colon de Santa Fe vs San Telmo</t>
+          <t>Godoy Cruz vs Chaco For Ever</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Colon de Santa Fe</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>0xbca9ed7d23a7df6c8ab98ab2ffc6649f2d4bd3d9007bd0ecf103e453c87addac</t>
+          <t>0x9c696117152178b9240c2e3eddca6b53432d4a4937a20042677cd1f666604f23</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>L19683494</t>
+          <t>L19683484</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -4904,17 +4904,17 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>1786300513</t>
+          <t>1786300516</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>1786300200</t>
+          <t>1786303800</t>
         </is>
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>270.425468</t>
+          <t>133.386139</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
@@ -4931,39 +4931,31 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0x2f3773fa15124937ec4965274c782b70d022a4fb2a2c8e85fe36a66e0dcc1a53</t>
+          <t>0x84f162af96f80a1f61f37a3b12a3dab48dcffde9bd10d0cea022df759f18111f</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>36.84547</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>1.2563</t>
+          <t>1.1362</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>San Miguel</t>
-        </is>
-      </c>
+          <t>Primera Nacional</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -4971,27 +4963,27 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Racing de Cordoba vs San Miguel</t>
+          <t>Colon de Santa Fe vs San Telmo</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Racing de Cordoba</t>
+          <t>Colon de Santa Fe</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>0x8ddab476b71709486e3a0e2118fafcb483076bd09c1c25dcce66244486fed688</t>
+          <t>0xbca9ed7d23a7df6c8ab98ab2ffc6649f2d4bd3d9007bd0ecf103e453c87addac</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>L19683501</t>
+          <t>L19683494</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -5016,17 +5008,17 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>1786300245</t>
+          <t>1786300513</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>1786302000</t>
+          <t>1786300200</t>
         </is>
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>3.902439</t>
+          <t>270.425468</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
@@ -5043,12 +5035,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0x4334abae5afdbf026c92af25200b83381434248bdfca39224de3957cba46f6e4</t>
+          <t>0x2f3773fa15124937ec4965274c782b70d022a4fb2a2c8e85fe36a66e0dcc1a53</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -5058,22 +5050,22 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>52.38</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>1.675</t>
+          <t>1.2563</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Primera Nacional</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>CA Colegiales 0</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -5083,27 +5075,27 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>CA Colegiales vs Patronato</t>
+          <t>Racing de Cordoba vs San Miguel</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>CA Colegiales</t>
+          <t>Racing de Cordoba</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>0x3fa48fbf2a59e0b45def889e06df3d2da646e9465f9af4f1b88581fea7fb4496</t>
+          <t>0x8ddab476b71709486e3a0e2118fafcb483076bd09c1c25dcce66244486fed688</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>L19683449</t>
+          <t>L19683501</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -5128,17 +5120,17 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>1786300042</t>
+          <t>1786300245</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>1786298400</t>
+          <t>1786302000</t>
         </is>
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>77.6</t>
+          <t>3.902439</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
@@ -5155,7 +5147,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0xad7255fad3f7d526c2f80d7968fa11121b17d106e3df35095d9b411cead706b0</t>
+          <t>0x4334abae5afdbf026c92af25200b83381434248bdfca39224de3957cba46f6e4</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5170,22 +5162,22 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>3.02932</t>
+          <t>52.38</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>1.2325</t>
+          <t>1.675</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Primera Nacional</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>CA Colegiales 0</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -5195,27 +5187,27 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Racing de Cordoba vs San Miguel</t>
+          <t>CA Colegiales vs Patronato</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Racing de Cordoba</t>
+          <t>CA Colegiales</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>0x8ddab476b71709486e3a0e2118fafcb483076bd09c1c25dcce66244486fed688</t>
+          <t>0x3fa48fbf2a59e0b45def889e06df3d2da646e9465f9af4f1b88581fea7fb4496</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>L19683501</t>
+          <t>L19683449</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -5240,17 +5232,17 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>1786298930</t>
+          <t>1786300042</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>1786302000</t>
+          <t>1786298400</t>
         </is>
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>13.029333</t>
+          <t>77.6</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
@@ -5267,7 +5259,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0x972e5a678ec56c15f03cbf0d14d7070ad000111adf76887dc34cc27780792e32</t>
+          <t>0xad7255fad3f7d526c2f80d7968fa11121b17d106e3df35095d9b411cead706b0</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5275,15 +5267,19 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr"/>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>24.07997</t>
+          <t>3.02932</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>1.8675</t>
+          <t>1.2325</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -5291,7 +5287,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr"/>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>San Miguel</t>
+        </is>
+      </c>
       <c r="H46" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -5299,27 +5299,27 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Godoy Cruz vs Chaco For Ever</t>
+          <t>Racing de Cordoba vs San Miguel</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Racing de Cordoba</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>0x9c19e4c1fd9646506f8ea14e2b1be19b49a5ab4dc1a7bf40167705a4ae2b338b</t>
+          <t>0x8ddab476b71709486e3a0e2118fafcb483076bd09c1c25dcce66244486fed688</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>L19683484</t>
+          <t>L19683501</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -5344,17 +5344,17 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>1786297771</t>
+          <t>1786298930</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>1786303800</t>
+          <t>1786302000</t>
         </is>
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>27.75789</t>
+          <t>13.029333</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
@@ -5371,39 +5371,31 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0x1da1f134f1ec859a8260a79216b9030b9f0b715d9a51d09741ff884111dcde2b</t>
+          <t>0x972e5a678ec56c15f03cbf0d14d7070ad000111adf76887dc34cc27780792e32</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>0x311AE302984D8b1cf53D6bfB0a6672f05c423AE6</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr">
         <is>
-          <t>37.76669</t>
+          <t>24.07997</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>1.5837</t>
+          <t>1.8675</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>Godoy Cruz -0.5</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr"/>
       <c r="H47" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -5426,7 +5418,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>0xb2c04ce7cffc1005eb6199d3c34d31b109e8af04a357b4f8eb9f6b8362ba33c2</t>
+          <t>0x9c19e4c1fd9646506f8ea14e2b1be19b49a5ab4dc1a7bf40167705a4ae2b338b</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -5456,7 +5448,7 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>1786297676</t>
+          <t>1786297771</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
@@ -5466,7 +5458,7 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>64.696685</t>
+          <t>27.75789</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
@@ -5483,12 +5475,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0xfccc36b3cd4c4e2276a7540f5bb389b40f91c9998d31903af7864027f93d335e</t>
+          <t>0x1da1f134f1ec859a8260a79216b9030b9f0b715d9a51d09741ff884111dcde2b</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x311AE302984D8b1cf53D6bfB0a6672f05c423AE6</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -5498,22 +5490,22 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>56.81</t>
+          <t>37.76669</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>1.3588</t>
+          <t>1.5837</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Tie</t>
+          <t>Godoy Cruz -0.5</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -5523,27 +5515,27 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>CA Los Andes vs Ferro Carril Oeste</t>
+          <t>Godoy Cruz vs Chaco For Ever</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>CA Los Andes</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>0x834e52f6ff115c72424372c131d41b8d94cffe6e0131918e3f85e2146509d14b</t>
+          <t>0xb2c04ce7cffc1005eb6199d3c34d31b109e8af04a357b4f8eb9f6b8362ba33c2</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>L19659153</t>
+          <t>L19683484</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -5568,17 +5560,17 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>1786297373</t>
+          <t>1786297676</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>1786296600</t>
+          <t>1786303800</t>
         </is>
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>158.355401</t>
+          <t>64.696685</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
@@ -5595,7 +5587,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0x48c1aed95e65b653ffb51380d6066948766a0030b4adf3bf05d152a5766c29cf</t>
+          <t>0xfccc36b3cd4c4e2276a7540f5bb389b40f91c9998d31903af7864027f93d335e</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5603,23 +5595,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr"/>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>56.81</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>1.6425</t>
+          <t>1.3588</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H49" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -5627,27 +5627,27 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Colon de Santa Fe vs San Telmo</t>
+          <t>CA Los Andes vs Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Colon de Santa Fe</t>
+          <t>CA Los Andes</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>0x79905ae58e04af69981e4a95c3d57b98dc3c1dd1d3e7aeb4e6a7640714001f3b</t>
+          <t>0x834e52f6ff115c72424372c131d41b8d94cffe6e0131918e3f85e2146509d14b</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>L19683494</t>
+          <t>L19659153</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -5672,17 +5672,17 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>1786293588</t>
+          <t>1786297373</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>1786300200</t>
+          <t>1786296600</t>
         </is>
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>15.564202</t>
+          <t>158.355401</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
@@ -5699,28 +5699,28 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0x3d4ee2d1cf7066373ffe56d01727fc04ce4ae0e1203194a2877d6ba90d9d4fcb</t>
+          <t>0x48c1aed95e65b653ffb51380d6066948766a0030b4adf3bf05d152a5766c29cf</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr">
         <is>
-          <t>16.53143</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>1.3438</t>
+          <t>1.6425</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Primera Nacional</t>
+          <t>Asian Handicap (-1.5)</t>
         </is>
       </c>
       <c r="G50" t="inlineStr"/>
@@ -5731,27 +5731,27 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Atlanta vs Temperley</t>
+          <t>Colon de Santa Fe vs San Telmo</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Colon de Santa Fe</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>0xc67c753c7ce425d2b225c54e0abf1308c3593fa6789a95fd59198b3a0f7a3ddd</t>
+          <t>0x79905ae58e04af69981e4a95c3d57b98dc3c1dd1d3e7aeb4e6a7640714001f3b</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>L19683448</t>
+          <t>L19683494</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -5776,17 +5776,17 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>1786293565</t>
+          <t>1786293588</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>1786294800</t>
+          <t>1786300200</t>
         </is>
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>48.091433</t>
+          <t>15.564202</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
@@ -5803,23 +5803,23 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0x5decd74680fc49716c54620aa922234edac874fb77b6369067e932fb5a40aed8</t>
+          <t>0x3d4ee2d1cf7066373ffe56d01727fc04ce4ae0e1203194a2877d6ba90d9d4fcb</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr">
         <is>
-          <t>16.98847</t>
+          <t>16.53143</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.3438</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -5835,27 +5835,27 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>San Martin Tucuman vs San Martín de San Juan</t>
+          <t>Atlanta vs Temperley</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>San Martin Tucuman</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>San Martín de San Juan</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>0x4f02331cd42a68f65ea16d62aac0c6b123d9400d12a4d556f3a72df894da02fb</t>
+          <t>0xc67c753c7ce425d2b225c54e0abf1308c3593fa6789a95fd59198b3a0f7a3ddd</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>L19682528</t>
+          <t>L19683448</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -5880,17 +5880,17 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>1786293511</t>
+          <t>1786293565</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>1786309200</t>
+          <t>1786294800</t>
         </is>
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>48.538486</t>
+          <t>48.091433</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
@@ -5907,7 +5907,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0x6376c34d63b4968409b909753114511b32d1413abbfce5d71dcd6fa7bb384028</t>
+          <t>0x5decd74680fc49716c54620aa922234edac874fb77b6369067e932fb5a40aed8</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5918,17 +5918,17 @@
       <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr">
         <is>
-          <t>30.89</t>
+          <t>16.98847</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>1.6425</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
+          <t>Primera Nacional</t>
         </is>
       </c>
       <c r="G52" t="inlineStr"/>
@@ -5939,27 +5939,27 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Colon de Santa Fe vs San Telmo</t>
+          <t>San Martin Tucuman vs San Martín de San Juan</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Colon de Santa Fe</t>
+          <t>San Martin Tucuman</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>San Martín de San Juan</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>0x79905ae58e04af69981e4a95c3d57b98dc3c1dd1d3e7aeb4e6a7640714001f3b</t>
+          <t>0x4f02331cd42a68f65ea16d62aac0c6b123d9400d12a4d556f3a72df894da02fb</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>L19683494</t>
+          <t>L19682528</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -5984,17 +5984,17 @@
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>1786293434</t>
+          <t>1786293511</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>1786300200</t>
+          <t>1786309200</t>
         </is>
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>48.077821</t>
+          <t>48.538486</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
@@ -6011,7 +6011,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0xa534180ddbde4d456a67f71365d2341259c4ca0b20e45041701c1d345202335e</t>
+          <t>0x6376c34d63b4968409b909753114511b32d1413abbfce5d71dcd6fa7bb384028</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -6022,17 +6022,17 @@
       <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr">
         <is>
-          <t>13.52</t>
+          <t>30.89</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>1.6325</t>
+          <t>1.6425</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>Asian Handicap (-1.5)</t>
         </is>
       </c>
       <c r="G53" t="inlineStr"/>
@@ -6043,27 +6043,27 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Quilmes vs Club Almagro</t>
+          <t>Colon de Santa Fe vs San Telmo</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Colon de Santa Fe</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>Club Almagro</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>0x86a790846c1cb1bed065ac37c41b727461e30e0a9e0f9e2370ef61f6213ed31f</t>
+          <t>0x79905ae58e04af69981e4a95c3d57b98dc3c1dd1d3e7aeb4e6a7640714001f3b</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>L19683499</t>
+          <t>L19683494</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -6088,17 +6088,17 @@
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>1786293430</t>
+          <t>1786293434</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>1786305600</t>
+          <t>1786300200</t>
         </is>
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>21.375494</t>
+          <t>48.077821</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
@@ -6115,7 +6115,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0xe6cbce05bf55e4a2647eb39e1cb6d7afdafec60905e09f42fb3552a02a5fcbd6</t>
+          <t>0xa534180ddbde4d456a67f71365d2341259c4ca0b20e45041701c1d345202335e</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -6126,7 +6126,7 @@
       <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr">
         <is>
-          <t>16.88999</t>
+          <t>13.52</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -6192,7 +6192,7 @@
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>1786293428</t>
+          <t>1786293430</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
@@ -6202,7 +6202,7 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>26.703542</t>
+          <t>21.375494</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
@@ -6219,7 +6219,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0xae3b69e222676c5f5930a25ee6fc677945888fbd4b45894897e8c0b45b324e25</t>
+          <t>0xe6cbce05bf55e4a2647eb39e1cb6d7afdafec60905e09f42fb3552a02a5fcbd6</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -6230,17 +6230,17 @@
       <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr">
         <is>
-          <t>12.72</t>
+          <t>16.88999</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>1.4512</t>
+          <t>1.6325</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G55" t="inlineStr"/>
@@ -6251,27 +6251,27 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>CA Los Andes vs Ferro Carril Oeste</t>
+          <t>Quilmes vs Club Almagro</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>CA Los Andes</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Club Almagro</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>0x555a8472fba9017aa83a61e5e7cf7b05dc2822d1d1cc6174412760fc412637f7</t>
+          <t>0x86a790846c1cb1bed065ac37c41b727461e30e0a9e0f9e2370ef61f6213ed31f</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>L19659153</t>
+          <t>L19683499</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -6296,17 +6296,17 @@
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>1786288547</t>
+          <t>1786293428</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>1786296600</t>
+          <t>1786305600</t>
         </is>
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>28.188366</t>
+          <t>26.703542</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
@@ -6323,28 +6323,28 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0x4bb954aaa9ecad68c0eb53f2341bb75f7b8daa072a3f151571ab136be22b78df</t>
+          <t>0xae3b69e222676c5f5930a25ee6fc677945888fbd4b45894897e8c0b45b324e25</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>0x71CE4A2C734a76f4C86A0D80122C4014c1F52F6e</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr">
         <is>
-          <t>29.37999</t>
+          <t>12.72</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>1.6113</t>
+          <t>1.4512</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
+          <t>Under/Over (1.5)</t>
         </is>
       </c>
       <c r="G56" t="inlineStr"/>
@@ -6370,7 +6370,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>0x653af58a9c77cb072171a76bcd9ca8adee427601f3ecd186c8154c81f8736395</t>
+          <t>0x555a8472fba9017aa83a61e5e7cf7b05dc2822d1d1cc6174412760fc412637f7</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -6400,7 +6400,7 @@
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>1786288517</t>
+          <t>1786288547</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
@@ -6410,7 +6410,7 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>48.065423</t>
+          <t>28.188366</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
@@ -6427,28 +6427,28 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>0xd5a2ddd8c8b6cc9bdb1c507276d3a192a5f24d46e2d3c01bfb07011263030bdd</t>
+          <t>0x4bb954aaa9ecad68c0eb53f2341bb75f7b8daa072a3f151571ab136be22b78df</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x71CE4A2C734a76f4C86A0D80122C4014c1F52F6e</t>
         </is>
       </c>
       <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr">
         <is>
-          <t>5.67</t>
+          <t>29.37999</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>1.2975</t>
+          <t>1.6113</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Primera Nacional</t>
+          <t>Under/Over (2)</t>
         </is>
       </c>
       <c r="G57" t="inlineStr"/>
@@ -6459,27 +6459,27 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>CA Colegiales vs Patronato</t>
+          <t>CA Los Andes vs Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>CA Colegiales</t>
+          <t>CA Los Andes</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>0x710e5bf3f6759bd93c59fc8788916c16c7302071968dfba2d053e2d10f7858bf</t>
+          <t>0x653af58a9c77cb072171a76bcd9ca8adee427601f3ecd186c8154c81f8736395</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>L19683449</t>
+          <t>L19659153</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -6504,17 +6504,17 @@
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>1786288450</t>
+          <t>1786288517</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>1786298400</t>
+          <t>1786296600</t>
         </is>
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>19.058824</t>
+          <t>48.065423</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
@@ -6531,7 +6531,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>0xad9f4feea88f83ae2e46756e7d54faa300a82e055c196c70c84019780ecb560c</t>
+          <t>0xd5a2ddd8c8b6cc9bdb1c507276d3a192a5f24d46e2d3c01bfb07011263030bdd</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -6542,17 +6542,17 @@
       <c r="C58" t="inlineStr"/>
       <c r="D58" t="inlineStr">
         <is>
-          <t>21.69</t>
+          <t>5.67</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>1.4512</t>
+          <t>1.2975</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
+          <t>Primera Nacional</t>
         </is>
       </c>
       <c r="G58" t="inlineStr"/>
@@ -6563,27 +6563,27 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>CA Los Andes vs Ferro Carril Oeste</t>
+          <t>CA Colegiales vs Patronato</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>CA Los Andes</t>
+          <t>CA Colegiales</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>0x555a8472fba9017aa83a61e5e7cf7b05dc2822d1d1cc6174412760fc412637f7</t>
+          <t>0x710e5bf3f6759bd93c59fc8788916c16c7302071968dfba2d053e2d10f7858bf</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>L19659153</t>
+          <t>L19683449</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -6608,17 +6608,17 @@
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>1786288436</t>
+          <t>1786288450</t>
         </is>
       </c>
       <c r="S58" t="inlineStr">
         <is>
-          <t>1786296600</t>
+          <t>1786298400</t>
         </is>
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>48.066482</t>
+          <t>19.058824</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
@@ -6635,7 +6635,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>0x168e5ea2716a187c94a1c77c4c8b2523b31163ed118e4986c68c79a21d013932</t>
+          <t>0xad9f4feea88f83ae2e46756e7d54faa300a82e055c196c70c84019780ecb560c</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6646,17 +6646,17 @@
       <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr">
         <is>
-          <t>29.38716</t>
+          <t>21.69</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>1.6113</t>
+          <t>1.4512</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
+          <t>Under/Over (1.5)</t>
         </is>
       </c>
       <c r="G59" t="inlineStr"/>
@@ -6682,7 +6682,7 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>0x653af58a9c77cb072171a76bcd9ca8adee427601f3ecd186c8154c81f8736395</t>
+          <t>0x555a8472fba9017aa83a61e5e7cf7b05dc2822d1d1cc6174412760fc412637f7</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
@@ -6722,7 +6722,7 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>48.077153</t>
+          <t>48.066482</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
@@ -6739,39 +6739,31 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>0x680d5db234b802aa2845f16e9d23d635dd89870065c6bfb6f6f1bde25c321bae</t>
+          <t>0x168e5ea2716a187c94a1c77c4c8b2523b31163ed118e4986c68c79a21d013932</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr"/>
       <c r="D60" t="inlineStr">
         <is>
-          <t>24.36</t>
+          <t>29.38716</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>1.475</t>
+          <t>1.6113</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>CA Colegiales -0.5</t>
-        </is>
-      </c>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr"/>
       <c r="H60" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -6779,27 +6771,27 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>CA Colegiales vs Patronato</t>
+          <t>CA Los Andes vs Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>CA Colegiales</t>
+          <t>CA Los Andes</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>0x50a3f0e4e982cdda0b9c4b9e2e1c50c67d93fbf7a068b43dbdf733c0b8d09050</t>
+          <t>0x653af58a9c77cb072171a76bcd9ca8adee427601f3ecd186c8154c81f8736395</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>L19683449</t>
+          <t>L19659153</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
@@ -6824,17 +6816,17 @@
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>1786287181</t>
+          <t>1786288436</t>
         </is>
       </c>
       <c r="S60" t="inlineStr">
         <is>
-          <t>1786298400</t>
+          <t>1786296600</t>
         </is>
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>51.284211</t>
+          <t>48.077153</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
@@ -6851,31 +6843,39 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>0x5a5b6f41ac2a593747a9419c020abd417423350c2cf0a14d8cb9ef8a25d04f18</t>
+          <t>0x680d5db234b802aa2845f16e9d23d635dd89870065c6bfb6f6f1bde25c321bae</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr"/>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>8.81755</t>
+          <t>24.36</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>1.6325</t>
+          <t>1.475</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr"/>
+          <t>Asian Handicap (-0.5)</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>CA Colegiales -0.5</t>
+        </is>
+      </c>
       <c r="H61" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -6883,27 +6883,27 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Quilmes vs Club Almagro</t>
+          <t>CA Colegiales vs Patronato</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>CA Colegiales</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>Club Almagro</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>0x86a790846c1cb1bed065ac37c41b727461e30e0a9e0f9e2370ef61f6213ed31f</t>
+          <t>0x50a3f0e4e982cdda0b9c4b9e2e1c50c67d93fbf7a068b43dbdf733c0b8d09050</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>L19683499</t>
+          <t>L19683449</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
@@ -6928,17 +6928,17 @@
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>1786284071</t>
+          <t>1786287181</t>
         </is>
       </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t>1786305600</t>
+          <t>1786298400</t>
         </is>
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>13.940791</t>
+          <t>51.284211</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
@@ -6955,7 +6955,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>0x9ae6e679c8fc9ed20977676ba3160d389287dd8808ea2610d0f168f9c3a42c11</t>
+          <t>0x5a5b6f41ac2a593747a9419c020abd417423350c2cf0a14d8cb9ef8a25d04f18</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6966,7 +6966,7 @@
       <c r="C62" t="inlineStr"/>
       <c r="D62" t="inlineStr">
         <is>
-          <t>21.58999</t>
+          <t>8.81755</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -7032,7 +7032,7 @@
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>1786284003</t>
+          <t>1786284071</t>
         </is>
       </c>
       <c r="S62" t="inlineStr">
@@ -7042,7 +7042,7 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>34.134372</t>
+          <t>13.940791</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
@@ -7059,7 +7059,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>0x6771b333646b031b4dc4cfea8f533b040a6ed0a66012cdc416a7aaa5b89f7988</t>
+          <t>0x9ae6e679c8fc9ed20977676ba3160d389287dd8808ea2610d0f168f9c3a42c11</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -7070,17 +7070,17 @@
       <c r="C63" t="inlineStr"/>
       <c r="D63" t="inlineStr">
         <is>
-          <t>19.2</t>
+          <t>21.58999</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>1.5425</t>
+          <t>1.6325</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G63" t="inlineStr"/>
@@ -7091,27 +7091,27 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Colon de Santa Fe vs San Telmo</t>
+          <t>Quilmes vs Club Almagro</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>Colon de Santa Fe</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Club Almagro</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>0x4b323aab38dd8f5096dcd1965ce7dc05c69ab73371e55e810b7a5aee356bf244</t>
+          <t>0x86a790846c1cb1bed065ac37c41b727461e30e0a9e0f9e2370ef61f6213ed31f</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>L19683494</t>
+          <t>L19683499</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
@@ -7136,17 +7136,17 @@
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>1786283290</t>
+          <t>1786284003</t>
         </is>
       </c>
       <c r="S63" t="inlineStr">
         <is>
-          <t>1786300200</t>
+          <t>1786305600</t>
         </is>
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>35.391705</t>
+          <t>34.134372</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
@@ -7163,7 +7163,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>0x8809f3e942a9cc8dca00d48b07cfe53a328d6ba2b60742c63e144e3d8cf2eaa1</t>
+          <t>0x6771b333646b031b4dc4cfea8f533b040a6ed0a66012cdc416a7aaa5b89f7988</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -7174,17 +7174,17 @@
       <c r="C64" t="inlineStr"/>
       <c r="D64" t="inlineStr">
         <is>
-          <t>23.25749</t>
+          <t>19.2</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>1.4838</t>
+          <t>1.5425</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G64" t="inlineStr"/>
@@ -7210,7 +7210,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>0xc91217dfcd3944893195656945526d39efcd315aa93101aa312de5303c04d446</t>
+          <t>0x4b323aab38dd8f5096dcd1965ce7dc05c69ab73371e55e810b7a5aee356bf244</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
@@ -7240,7 +7240,7 @@
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>1786281248</t>
+          <t>1786283290</t>
         </is>
       </c>
       <c r="S64" t="inlineStr">
@@ -7250,7 +7250,7 @@
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>48.077499</t>
+          <t>35.391705</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
@@ -7267,7 +7267,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>0xe5b95b7ede820952a7e6f5c1b2139a8092b51c4de75567f117f1291461ec6fbe</t>
+          <t>0x8809f3e942a9cc8dca00d48b07cfe53a328d6ba2b60742c63e144e3d8cf2eaa1</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -7278,12 +7278,12 @@
       <c r="C65" t="inlineStr"/>
       <c r="D65" t="inlineStr">
         <is>
-          <t>23.55844</t>
+          <t>23.25749</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.4838</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -7344,7 +7344,7 @@
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>1786281243</t>
+          <t>1786281248</t>
         </is>
       </c>
       <c r="S65" t="inlineStr">
@@ -7354,7 +7354,7 @@
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>48.078449</t>
+          <t>48.077499</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
@@ -7371,7 +7371,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>0x4d872ac34cfff98634d3d50362fe725a3f4ea55d64ddd9e3d7d811b073f350ab</t>
+          <t>0xe5b95b7ede820952a7e6f5c1b2139a8092b51c4de75567f117f1291461ec6fbe</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -7382,17 +7382,17 @@
       <c r="C66" t="inlineStr"/>
       <c r="D66" t="inlineStr">
         <is>
-          <t>17.30813</t>
+          <t>23.55844</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
+          <t>Under/Over (2)</t>
         </is>
       </c>
       <c r="G66" t="inlineStr"/>
@@ -7418,7 +7418,7 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>0xd638a8ee6393f88ca538cc4fe6ac8cdf722bcfe6277a5ebd9387222eade88ba3</t>
+          <t>0xc91217dfcd3944893195656945526d39efcd315aa93101aa312de5303c04d446</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
@@ -7458,7 +7458,7 @@
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>48.078139</t>
+          <t>48.078449</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
@@ -7475,7 +7475,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>0x8f782cb5f7b30f6c129f6031ec6368ed75ea36897066f1761d9054013f56567d</t>
+          <t>0x4d872ac34cfff98634d3d50362fe725a3f4ea55d64ddd9e3d7d811b073f350ab</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -7486,17 +7486,17 @@
       <c r="C67" t="inlineStr"/>
       <c r="D67" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>17.30813</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>1.4187</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Primera Nacional</t>
+          <t>Under/Over (1.5)</t>
         </is>
       </c>
       <c r="G67" t="inlineStr"/>
@@ -7507,27 +7507,27 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Club Atletico Mitre de Santiago del Estero vs Defensores de Belgrano Buenos Aires</t>
+          <t>Colon de Santa Fe vs San Telmo</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>Club Atletico Mitre de Santiago del Estero</t>
+          <t>Colon de Santa Fe</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano Buenos Aires</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>0x2d371e1a8a9d98624f046ea3d7126e47308ffbc183b66b1e2fba81e5ae69d7dd</t>
+          <t>0xd638a8ee6393f88ca538cc4fe6ac8cdf722bcfe6277a5ebd9387222eade88ba3</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>L19683493</t>
+          <t>L19683494</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
@@ -7552,17 +7552,17 @@
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>1786280425</t>
+          <t>1786281243</t>
         </is>
       </c>
       <c r="S67" t="inlineStr">
         <is>
-          <t>1786302000</t>
+          <t>1786300200</t>
         </is>
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>23.880597</t>
+          <t>48.078139</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
@@ -7579,7 +7579,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>0xfe8890b155a19f7eb888456b555a7a6d8c293f8ecabeb69d2abd10210f520589</t>
+          <t>0x8f782cb5f7b30f6c129f6031ec6368ed75ea36897066f1761d9054013f56567d</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -7595,12 +7595,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>1.4475</t>
+          <t>1.4187</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
+          <t>Primera Nacional</t>
         </is>
       </c>
       <c r="G68" t="inlineStr"/>
@@ -7611,27 +7611,27 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Colon de Santa Fe vs San Telmo</t>
+          <t>Club Atletico Mitre de Santiago del Estero vs Defensores de Belgrano Buenos Aires</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Colon de Santa Fe</t>
+          <t>Club Atletico Mitre de Santiago del Estero</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Defensores de Belgrano Buenos Aires</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>0xc91217dfcd3944893195656945526d39efcd315aa93101aa312de5303c04d446</t>
+          <t>0x2d371e1a8a9d98624f046ea3d7126e47308ffbc183b66b1e2fba81e5ae69d7dd</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>L19683494</t>
+          <t>L19683493</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
@@ -7656,17 +7656,17 @@
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>1786280403</t>
+          <t>1786280425</t>
         </is>
       </c>
       <c r="S68" t="inlineStr">
         <is>
-          <t>1786300200</t>
+          <t>1786302000</t>
         </is>
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>22.346369</t>
+          <t>23.880597</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
@@ -7683,7 +7683,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>0x60e023296ac2f9f58237fa345b3aa08fb4f997dd34c5384f371782bf7bbd5a40</t>
+          <t>0xfe8890b155a19f7eb888456b555a7a6d8c293f8ecabeb69d2abd10210f520589</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -7691,19 +7691,15 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C69" t="inlineStr"/>
       <c r="D69" t="inlineStr">
         <is>
-          <t>26.11999</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>1.5488</t>
+          <t>1.4475</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -7711,11 +7707,7 @@
           <t>Under/Over (2)</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>Over 2.0</t>
-        </is>
-      </c>
+      <c r="G69" t="inlineStr"/>
       <c r="H69" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -7778,7 +7770,7 @@
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>47.599071</t>
+          <t>22.346369</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
@@ -7795,7 +7787,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>0x2d118800c100a2a41a19c2053cbf355561a08867f99163fb40955a4ab012ce39</t>
+          <t>0x60e023296ac2f9f58237fa345b3aa08fb4f997dd34c5384f371782bf7bbd5a40</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -7803,23 +7795,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C70" t="inlineStr"/>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>20.07999</t>
+          <t>26.11999</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>1.7363</t>
+          <t>1.5488</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr"/>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Over 2.0</t>
+        </is>
+      </c>
       <c r="H70" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -7827,27 +7827,27 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Godoy Cruz vs Chaco For Ever</t>
+          <t>Colon de Santa Fe vs San Telmo</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Colon de Santa Fe</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>0x60e111ebf03c4965ff049e67cf10f93f5cca143023c6104aab59162863b5b8a8</t>
+          <t>0xc91217dfcd3944893195656945526d39efcd315aa93101aa312de5303c04d446</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>L19683484</t>
+          <t>L19683494</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
@@ -7872,17 +7872,17 @@
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>1786279900</t>
+          <t>1786280403</t>
         </is>
       </c>
       <c r="S70" t="inlineStr">
         <is>
-          <t>1786303800</t>
+          <t>1786300200</t>
         </is>
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>27.273331</t>
+          <t>47.599071</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
@@ -7899,7 +7899,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>0x904e2e53a604aa6663de774d4bd9ddf8af7459ef1c4fa1bb14486300917ac211</t>
+          <t>0x2d118800c100a2a41a19c2053cbf355561a08867f99163fb40955a4ab012ce39</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -7907,31 +7907,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C71" t="inlineStr"/>
       <c r="D71" t="inlineStr">
         <is>
-          <t>3.96</t>
+          <t>20.07999</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>1.2837</t>
+          <t>1.7363</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+          <t>Asian Handicap (-1.5)</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr"/>
       <c r="H71" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -7954,7 +7946,7 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>0x08dce15d4ca4845359c2f121bce305fd3a0fe7422d497000c713e29463c6be79</t>
+          <t>0x60e111ebf03c4965ff049e67cf10f93f5cca143023c6104aab59162863b5b8a8</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
@@ -7984,7 +7976,7 @@
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>1786279851</t>
+          <t>1786279900</t>
         </is>
       </c>
       <c r="S71" t="inlineStr">
@@ -7994,7 +7986,7 @@
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>13.955947</t>
+          <t>27.273331</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
@@ -8011,7 +8003,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>0x19a6c0536a5dea88055519ff16050cdde80d42121bb75c5045e3b562a7c1d4bb</t>
+          <t>0x904e2e53a604aa6663de774d4bd9ddf8af7459ef1c4fa1bb14486300917ac211</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -8019,15 +8011,19 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C72" t="inlineStr"/>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>7.50547</t>
+          <t>3.96</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>1.4287</t>
+          <t>1.2837</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -8035,7 +8031,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr"/>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H72" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -8058,7 +8058,7 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>0xa5f02d0d08d0dcc4818948397f0f26c77f90b87182cec4d62ab01f77352671a1</t>
+          <t>0x08dce15d4ca4845359c2f121bce305fd3a0fe7422d497000c713e29463c6be79</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
@@ -8088,7 +8088,7 @@
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>1786279821</t>
+          <t>1786279851</t>
         </is>
       </c>
       <c r="S72" t="inlineStr">
@@ -8098,7 +8098,7 @@
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>17.505469</t>
+          <t>13.955947</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
@@ -8115,7 +8115,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>0x4c44e2c0c492a5115b342a42a552a040cb800bd582b07c12f1ea9161b861b487</t>
+          <t>0x19a6c0536a5dea88055519ff16050cdde80d42121bb75c5045e3b562a7c1d4bb</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -8126,17 +8126,17 @@
       <c r="C73" t="inlineStr"/>
       <c r="D73" t="inlineStr">
         <is>
-          <t>11.30844</t>
+          <t>7.50547</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.4287</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G73" t="inlineStr"/>
@@ -8147,27 +8147,27 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Deportivo Moron vs Acassuso</t>
+          <t>Godoy Cruz vs Chaco For Ever</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>Deportivo Moron</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>0x108eaba0441fb45ec8e0073e945ae0ac1e138c933e4f2839816cd3198d7dd4d2</t>
+          <t>0xa5f02d0d08d0dcc4818948397f0f26c77f90b87182cec4d62ab01f77352671a1</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>L19683452</t>
+          <t>L19683484</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
@@ -8192,17 +8192,17 @@
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>1786278950</t>
+          <t>1786279821</t>
         </is>
       </c>
       <c r="S73" t="inlineStr">
         <is>
-          <t>1786298400</t>
+          <t>1786303800</t>
         </is>
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>23.078449</t>
+          <t>17.505469</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
@@ -8219,7 +8219,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>0x5a5ccf0d5f6cbac6813d25e4e1e96b25b5c5a4ff8f6378d7e69d6bd3c29295ae</t>
+          <t>0x4c44e2c0c492a5115b342a42a552a040cb800bd582b07c12f1ea9161b861b487</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -8230,7 +8230,7 @@
       <c r="C74" t="inlineStr"/>
       <c r="D74" t="inlineStr">
         <is>
-          <t>12.25</t>
+          <t>11.30844</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -8296,7 +8296,7 @@
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>1786278094</t>
+          <t>1786278950</t>
         </is>
       </c>
       <c r="S74" t="inlineStr">
@@ -8306,7 +8306,7 @@
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>23.078449</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
@@ -8323,7 +8323,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>0x5f3419242a87ff17c0cb508ade95d27a54429124d36280a1dff2efa2fa0b3510</t>
+          <t>0x5a5ccf0d5f6cbac6813d25e4e1e96b25b5c5a4ff8f6378d7e69d6bd3c29295ae</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -8334,17 +8334,17 @@
       <c r="C75" t="inlineStr"/>
       <c r="D75" t="inlineStr">
         <is>
-          <t>20.41999</t>
+          <t>12.25</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>1.7087</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (2)</t>
         </is>
       </c>
       <c r="G75" t="inlineStr"/>
@@ -8355,27 +8355,27 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>CA Los Andes vs Ferro Carril Oeste</t>
+          <t>Deportivo Moron vs Acassuso</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>CA Los Andes</t>
+          <t>Deportivo Moron</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>0x31115553050eabb8d3f6a72cf2865c16175783383dcfc674615e74ed88cabaee</t>
+          <t>0x108eaba0441fb45ec8e0073e945ae0ac1e138c933e4f2839816cd3198d7dd4d2</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>L19659153</t>
+          <t>L19683452</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
@@ -8400,17 +8400,17 @@
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>1786277884</t>
+          <t>1786278094</t>
         </is>
       </c>
       <c r="S75" t="inlineStr">
         <is>
-          <t>1786296600</t>
+          <t>1786298400</t>
         </is>
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>28.811273</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
@@ -8427,7 +8427,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>0xe6b14424302d9ef7ea2000cef83e38549f6a38c12d57faa6dd76dd84e631a5ca</t>
+          <t>0x5f3419242a87ff17c0cb508ade95d27a54429124d36280a1dff2efa2fa0b3510</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -8438,17 +8438,17 @@
       <c r="C76" t="inlineStr"/>
       <c r="D76" t="inlineStr">
         <is>
-          <t>12.13</t>
+          <t>20.41999</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>1.3613</t>
+          <t>1.7087</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G76" t="inlineStr"/>
@@ -8459,27 +8459,27 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>Deportivo Moron vs Acassuso</t>
+          <t>CA Los Andes vs Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>Deportivo Moron</t>
+          <t>CA Los Andes</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>0x3f34d112cfb9f093c57a3e094be078f9eea2715f97797e20d86942d58f5cc8d6</t>
+          <t>0x31115553050eabb8d3f6a72cf2865c16175783383dcfc674615e74ed88cabaee</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>L19683452</t>
+          <t>L19659153</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
@@ -8504,17 +8504,17 @@
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>1786277708</t>
+          <t>1786277884</t>
         </is>
       </c>
       <c r="S76" t="inlineStr">
         <is>
-          <t>1786298400</t>
+          <t>1786296600</t>
         </is>
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>33.577855</t>
+          <t>28.811273</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
@@ -8531,7 +8531,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>0xd7a2e43ba1564f619200938b384123dd68adb783742fc7b32ee335ee489d1302</t>
+          <t>0xe6b14424302d9ef7ea2000cef83e38549f6a38c12d57faa6dd76dd84e631a5ca</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -8542,17 +8542,17 @@
       <c r="C77" t="inlineStr"/>
       <c r="D77" t="inlineStr">
         <is>
-          <t>10.58</t>
+          <t>12.13</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>1.485</t>
+          <t>1.3613</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
+          <t>Under/Over (1.5)</t>
         </is>
       </c>
       <c r="G77" t="inlineStr"/>
@@ -8578,7 +8578,7 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>0x108eaba0441fb45ec8e0073e945ae0ac1e138c933e4f2839816cd3198d7dd4d2</t>
+          <t>0x3f34d112cfb9f093c57a3e094be078f9eea2715f97797e20d86942d58f5cc8d6</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
@@ -8608,7 +8608,7 @@
       </c>
       <c r="R77" t="inlineStr">
         <is>
-          <t>1786277679</t>
+          <t>1786277708</t>
         </is>
       </c>
       <c r="S77" t="inlineStr">
@@ -8618,7 +8618,7 @@
       </c>
       <c r="T77" t="inlineStr">
         <is>
-          <t>21.814433</t>
+          <t>33.577855</t>
         </is>
       </c>
       <c r="U77" t="inlineStr">
@@ -8635,7 +8635,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>0xb25fa423ffb1a1464f100f2a2e9a1beac36661b9e37c8b09ecc7d3fd5a80312f</t>
+          <t>0xd7a2e43ba1564f619200938b384123dd68adb783742fc7b32ee335ee489d1302</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -8646,12 +8646,12 @@
       <c r="C78" t="inlineStr"/>
       <c r="D78" t="inlineStr">
         <is>
-          <t>25.88</t>
+          <t>10.58</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>1.6038</t>
+          <t>1.485</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -8667,27 +8667,27 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>CA Colegiales vs Patronato</t>
+          <t>Deportivo Moron vs Acassuso</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>CA Colegiales</t>
+          <t>Deportivo Moron</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>0x18dd2fdd93f5029a20e6a76c47c4f0e5c3c25768ad7f1b46a833287f8b7fcc13</t>
+          <t>0x108eaba0441fb45ec8e0073e945ae0ac1e138c933e4f2839816cd3198d7dd4d2</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>L19683449</t>
+          <t>L19683452</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
@@ -8712,7 +8712,7 @@
       </c>
       <c r="R78" t="inlineStr">
         <is>
-          <t>1786277040</t>
+          <t>1786277679</t>
         </is>
       </c>
       <c r="S78" t="inlineStr">
@@ -8722,7 +8722,7 @@
       </c>
       <c r="T78" t="inlineStr">
         <is>
-          <t>42.865424</t>
+          <t>21.814433</t>
         </is>
       </c>
       <c r="U78" t="inlineStr">
@@ -8739,7 +8739,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>0xfe815be8a10a6ad2cda012e463a244232a6f6c80544018f6dda52d723946b659</t>
+          <t>0xb25fa423ffb1a1464f100f2a2e9a1beac36661b9e37c8b09ecc7d3fd5a80312f</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -8750,7 +8750,7 @@
       <c r="C79" t="inlineStr"/>
       <c r="D79" t="inlineStr">
         <is>
-          <t>29.02571</t>
+          <t>25.88</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -8816,7 +8816,7 @@
       </c>
       <c r="R79" t="inlineStr">
         <is>
-          <t>1786276809</t>
+          <t>1786277040</t>
         </is>
       </c>
       <c r="S79" t="inlineStr">
@@ -8826,7 +8826,7 @@
       </c>
       <c r="T79" t="inlineStr">
         <is>
-          <t>48.07571</t>
+          <t>42.865424</t>
         </is>
       </c>
       <c r="U79" t="inlineStr">
@@ -8843,7 +8843,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>0xdb83c52876b68624e093c25e35d11910f4fbef2394ff947b658f8ea5cdb3fa88</t>
+          <t>0xfe815be8a10a6ad2cda012e463a244232a6f6c80544018f6dda52d723946b659</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -8854,17 +8854,17 @@
       <c r="C80" t="inlineStr"/>
       <c r="D80" t="inlineStr">
         <is>
-          <t>16.96</t>
+          <t>29.02571</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>1.4463</t>
+          <t>1.6038</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
+          <t>Under/Over (2)</t>
         </is>
       </c>
       <c r="G80" t="inlineStr"/>
@@ -8890,7 +8890,7 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>0x30a6561de28b35c5bb0557dcbfc7b23e7a62558d3b0f5cfcafb67d7a07e0dd21</t>
+          <t>0x18dd2fdd93f5029a20e6a76c47c4f0e5c3c25768ad7f1b46a833287f8b7fcc13</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
@@ -8930,7 +8930,7 @@
       </c>
       <c r="T80" t="inlineStr">
         <is>
-          <t>38.005602</t>
+          <t>48.07571</t>
         </is>
       </c>
       <c r="U80" t="inlineStr">
@@ -8947,39 +8947,31 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>0x0847a2541998eecfe02d138796b14ef3d6719061787498f4888f6e14c0d196ff</t>
+          <t>0xdb83c52876b68624e093c25e35d11910f4fbef2394ff947b658f8ea5cdb3fa88</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>0xf068eF8DF8f47185D02d59Bb33d9eC7A057a571E</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr"/>
       <c r="D81" t="inlineStr">
         <is>
-          <t>38.54</t>
+          <t>16.96</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>1.125</t>
+          <t>1.4463</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>Club Almagro</t>
-        </is>
-      </c>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr"/>
       <c r="H81" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -8987,27 +8979,27 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>Quilmes vs Club Almagro</t>
+          <t>CA Colegiales vs Patronato</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>CA Colegiales</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>Club Almagro</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>0x03ed0858b563c1becf38b195ad94b1a84eb89c3ca8ca10b1a34220bff142f9b2</t>
+          <t>0x30a6561de28b35c5bb0557dcbfc7b23e7a62558d3b0f5cfcafb67d7a07e0dd21</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>L19683499</t>
+          <t>L19683449</t>
         </is>
       </c>
       <c r="N81" t="inlineStr">
@@ -9032,17 +9024,17 @@
       </c>
       <c r="R81" t="inlineStr">
         <is>
-          <t>1786270828</t>
+          <t>1786276809</t>
         </is>
       </c>
       <c r="S81" t="inlineStr">
         <is>
-          <t>1786305600</t>
+          <t>1786298400</t>
         </is>
       </c>
       <c r="T81" t="inlineStr">
         <is>
-          <t>308.32</t>
+          <t>38.005602</t>
         </is>
       </c>
       <c r="U81" t="inlineStr">
@@ -9059,12 +9051,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>0x2121e08c4ea1fe2d49a3bb388fba9e232ef9c06335c04e5eae0bf7766975512a</t>
+          <t>0x0847a2541998eecfe02d138796b14ef3d6719061787498f4888f6e14c0d196ff</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0xf068eF8DF8f47185D02d59Bb33d9eC7A057a571E</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -9074,12 +9066,12 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>30.06</t>
+          <t>38.54</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>1.6262</t>
+          <t>1.125</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -9089,7 +9081,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Colon de Santa Fe</t>
+          <t>Club Almagro</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -9099,27 +9091,27 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Colon de Santa Fe vs San Telmo</t>
+          <t>Quilmes vs Club Almagro</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>Colon de Santa Fe</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Club Almagro</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>0x1a11ec80edeaae24566c4f4f891cc2afc56b377b24997a6e8ee533eeaaad5c92</t>
+          <t>0x03ed0858b563c1becf38b195ad94b1a84eb89c3ca8ca10b1a34220bff142f9b2</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>L19683494</t>
+          <t>L19683499</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
@@ -9144,17 +9136,17 @@
       </c>
       <c r="R82" t="inlineStr">
         <is>
-          <t>1786253941</t>
+          <t>1786270828</t>
         </is>
       </c>
       <c r="S82" t="inlineStr">
         <is>
-          <t>1786300200</t>
+          <t>1786305600</t>
         </is>
       </c>
       <c r="T82" t="inlineStr">
         <is>
-          <t>48.0</t>
+          <t>308.32</t>
         </is>
       </c>
       <c r="U82" t="inlineStr">
@@ -9171,12 +9163,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>0x4e811c319e5e3a1fc1968ce0f31b4c15eb7222daa616252d99f9abc611408746</t>
+          <t>0x2121e08c4ea1fe2d49a3bb388fba9e232ef9c06335c04e5eae0bf7766975512a</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>0x155C76202e45BE70c50bfeD7eAeA3B98e7716Ff7</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -9186,12 +9178,12 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>30.06</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>1.2925</t>
+          <t>1.6262</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -9201,7 +9193,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Tie</t>
+          <t>Colon de Santa Fe</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -9226,7 +9218,7 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>0x2e49527408facf21253a0a1eafe51280b82e4c31919e91a396332f19ec366401</t>
+          <t>0x1a11ec80edeaae24566c4f4f891cc2afc56b377b24997a6e8ee533eeaaad5c92</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
@@ -9256,7 +9248,7 @@
       </c>
       <c r="R83" t="inlineStr">
         <is>
-          <t>1786243741</t>
+          <t>1786253941</t>
         </is>
       </c>
       <c r="S83" t="inlineStr">
@@ -9266,7 +9258,7 @@
       </c>
       <c r="T83" t="inlineStr">
         <is>
-          <t>3.418803</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="U83" t="inlineStr">
@@ -9283,7 +9275,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>0xb8631aeb398192a03386505542f05fa15e34db501204baa8745a4d4b5c1651b7</t>
+          <t>0x4e811c319e5e3a1fc1968ce0f31b4c15eb7222daa616252d99f9abc611408746</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -9298,12 +9290,12 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>0.99999</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>1.6538</t>
+          <t>1.2925</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -9313,7 +9305,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Deportivo Moron</t>
+          <t>Tie</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -9323,27 +9315,27 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>Deportivo Moron vs Acassuso</t>
+          <t>Colon de Santa Fe vs San Telmo</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>Deportivo Moron</t>
+          <t>Colon de Santa Fe</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>0x7514a255ce41be3c5db9f8849ba04e78dab80f02d1fe78c2aae82bbc843a9745</t>
+          <t>0x2e49527408facf21253a0a1eafe51280b82e4c31919e91a396332f19ec366401</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>L19683452</t>
+          <t>L19683494</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">
@@ -9368,17 +9360,17 @@
       </c>
       <c r="R84" t="inlineStr">
         <is>
-          <t>1786243225</t>
+          <t>1786243741</t>
         </is>
       </c>
       <c r="S84" t="inlineStr">
         <is>
-          <t>1786298400</t>
+          <t>1786300200</t>
         </is>
       </c>
       <c r="T84" t="inlineStr">
         <is>
-          <t>1.529621</t>
+          <t>3.418803</t>
         </is>
       </c>
       <c r="U84" t="inlineStr">
@@ -9395,31 +9387,39 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>0xd3b94d194e43cc84f0a1b82723594ea6689a6aa2a4a7dccbc8a3d19fc321e49b</t>
+          <t>0xb8631aeb398192a03386505542f05fa15e34db501204baa8745a4d4b5c1651b7</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr"/>
+          <t>0x155C76202e45BE70c50bfeD7eAeA3B98e7716Ff7</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0.99999</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>1.5238</t>
+          <t>1.6538</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Deportivo Moron</t>
+        </is>
+      </c>
       <c r="H85" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -9442,7 +9442,7 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>0x108eaba0441fb45ec8e0073e945ae0ac1e138c933e4f2839816cd3198d7dd4d2</t>
+          <t>0x7514a255ce41be3c5db9f8849ba04e78dab80f02d1fe78c2aae82bbc843a9745</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
@@ -9472,7 +9472,7 @@
       </c>
       <c r="R85" t="inlineStr">
         <is>
-          <t>1786225000</t>
+          <t>1786243225</t>
         </is>
       </c>
       <c r="S85" t="inlineStr">
@@ -9482,7 +9482,7 @@
       </c>
       <c r="T85" t="inlineStr">
         <is>
-          <t>1.909308</t>
+          <t>1.529621</t>
         </is>
       </c>
       <c r="U85" t="inlineStr">
@@ -9499,7 +9499,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>0x86f4b24298f4c19f9f856cb19af2a260f24dc2d391f252248469436057ea1d1a</t>
+          <t>0xd3b94d194e43cc84f0a1b82723594ea6689a6aa2a4a7dccbc8a3d19fc321e49b</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -9507,11 +9507,7 @@
           <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
         </is>
       </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C86" t="inlineStr"/>
       <c r="D86" t="inlineStr">
         <is>
           <t>1</t>
@@ -9519,19 +9515,15 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>1.5263</t>
+          <t>1.5238</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>Deportivo Moron -1</t>
-        </is>
-      </c>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr"/>
       <c r="H86" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -9554,7 +9546,7 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>0xb61b063252c01d0525ae633a0276dc1830eabd418482fddec925fcbd602a2a75</t>
+          <t>0x108eaba0441fb45ec8e0073e945ae0ac1e138c933e4f2839816cd3198d7dd4d2</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
@@ -9584,7 +9576,7 @@
       </c>
       <c r="R86" t="inlineStr">
         <is>
-          <t>1786220171</t>
+          <t>1786225000</t>
         </is>
       </c>
       <c r="S86" t="inlineStr">
@@ -9594,7 +9586,7 @@
       </c>
       <c r="T86" t="inlineStr">
         <is>
-          <t>1.900238</t>
+          <t>1.909308</t>
         </is>
       </c>
       <c r="U86" t="inlineStr">
@@ -9611,12 +9603,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>0x0a5de930b5a6b8aca1699b666034af3891a3aa920021791d6d13e0297fb7903f</t>
+          <t>0x86f4b24298f4c19f9f856cb19af2a260f24dc2d391f252248469436057ea1d1a</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>0x4a09916b1325Eed50eE8973B13742a205B0B7c7E</t>
+          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -9626,12 +9618,12 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>49.99999</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>1.6175</t>
+          <t>1.5263</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -9641,7 +9633,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Almirante Brown -1</t>
+          <t>Deportivo Moron -1</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -9651,27 +9643,27 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>Almirante Brown vs Ciudad Bolivar</t>
+          <t>Deportivo Moron vs Acassuso</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Deportivo Moron</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>Ciudad Bolivar</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>0xa6a338c64f062bfd589e8d5d9cea45a27c9e64065f71f800e5966f81ce53c556</t>
+          <t>0xb61b063252c01d0525ae633a0276dc1830eabd418482fddec925fcbd602a2a75</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>L19683447</t>
+          <t>L19683452</t>
         </is>
       </c>
       <c r="N87" t="inlineStr">
@@ -9696,17 +9688,17 @@
       </c>
       <c r="R87" t="inlineStr">
         <is>
-          <t>1786218515</t>
+          <t>1786220171</t>
         </is>
       </c>
       <c r="S87" t="inlineStr">
         <is>
-          <t>1786212000</t>
+          <t>1786298400</t>
         </is>
       </c>
       <c r="T87" t="inlineStr">
         <is>
-          <t>80.971644</t>
+          <t>1.900238</t>
         </is>
       </c>
       <c r="U87" t="inlineStr">
@@ -9723,23 +9715,27 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>0x17d5a08f8fa305f31f27442393c64f497dd3893417da6e76c321c4c2a187320d</t>
+          <t>0x0a5de930b5a6b8aca1699b666034af3891a3aa920021791d6d13e0297fb7903f</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr"/>
+          <t>0x4a09916b1325Eed50eE8973B13742a205B0B7c7E</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>49.18897</t>
+          <t>49.99999</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>1.4737</t>
+          <t>1.6175</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -9747,7 +9743,11 @@
           <t>Asian Handicap (-1)</t>
         </is>
       </c>
-      <c r="G88" t="inlineStr"/>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Almirante Brown -1</t>
+        </is>
+      </c>
       <c r="H88" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -9800,7 +9800,7 @@
       </c>
       <c r="R88" t="inlineStr">
         <is>
-          <t>1786218084</t>
+          <t>1786218515</t>
         </is>
       </c>
       <c r="S88" t="inlineStr">
@@ -9810,7 +9810,7 @@
       </c>
       <c r="T88" t="inlineStr">
         <is>
-          <t>103.82896</t>
+          <t>80.971644</t>
         </is>
       </c>
       <c r="U88" t="inlineStr">
@@ -9827,28 +9827,28 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>0x56975f372357be259365cb7d2929c88d4fae157eea7a71d53d57cb234834f2ca</t>
+          <t>0x17d5a08f8fa305f31f27442393c64f497dd3893417da6e76c321c4c2a187320d</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C89" t="inlineStr"/>
       <c r="D89" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>49.18897</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>1.4812</t>
+          <t>1.4737</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G89" t="inlineStr"/>
@@ -9859,27 +9859,27 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>Club Atletico Mitre de Santiago del Estero vs Defensores de Belgrano Buenos Aires</t>
+          <t>Almirante Brown vs Ciudad Bolivar</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>Club Atletico Mitre de Santiago del Estero</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano Buenos Aires</t>
+          <t>Ciudad Bolivar</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>0xa8ade64a3adb0ea38de67a61105ef31beb490d5a7287715b76ae124536d359cc</t>
+          <t>0xa6a338c64f062bfd589e8d5d9cea45a27c9e64065f71f800e5966f81ce53c556</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>L19683493</t>
+          <t>L19683447</t>
         </is>
       </c>
       <c r="N89" t="inlineStr">
@@ -9904,17 +9904,17 @@
       </c>
       <c r="R89" t="inlineStr">
         <is>
-          <t>1786215674</t>
+          <t>1786218084</t>
         </is>
       </c>
       <c r="S89" t="inlineStr">
         <is>
-          <t>1786302000</t>
+          <t>1786212000</t>
         </is>
       </c>
       <c r="T89" t="inlineStr">
         <is>
-          <t>2.077922</t>
+          <t>103.82896</t>
         </is>
       </c>
       <c r="U89" t="inlineStr">
@@ -9931,7 +9931,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>0xff53df1f3446908699196d44fcdb8b39c1bd15c7ed519f0d730e55a51a6eb38f</t>
+          <t>0x56975f372357be259365cb7d2929c88d4fae157eea7a71d53d57cb234834f2ca</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -9939,11 +9939,7 @@
           <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
         </is>
       </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C90" t="inlineStr"/>
       <c r="D90" t="inlineStr">
         <is>
           <t>1</t>
@@ -9951,19 +9947,15 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>1.3713</t>
+          <t>1.4812</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>Almirante Brown</t>
-        </is>
-      </c>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr"/>
       <c r="H90" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -9971,27 +9963,27 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>Almirante Brown vs Ciudad Bolivar</t>
+          <t>Club Atletico Mitre de Santiago del Estero vs Defensores de Belgrano Buenos Aires</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Club Atletico Mitre de Santiago del Estero</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>Ciudad Bolivar</t>
+          <t>Defensores de Belgrano Buenos Aires</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>0x63a8bf73c1084ef223fdd1096dccd16232e7a455fad77f7f0891be1588ebeb88</t>
+          <t>0xa8ade64a3adb0ea38de67a61105ef31beb490d5a7287715b76ae124536d359cc</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>L19683447</t>
+          <t>L19683493</t>
         </is>
       </c>
       <c r="N90" t="inlineStr">
@@ -10016,17 +10008,17 @@
       </c>
       <c r="R90" t="inlineStr">
         <is>
-          <t>1786215673</t>
+          <t>1786215674</t>
         </is>
       </c>
       <c r="S90" t="inlineStr">
         <is>
-          <t>1786212000</t>
+          <t>1786302000</t>
         </is>
       </c>
       <c r="T90" t="inlineStr">
         <is>
-          <t>2.693603</t>
+          <t>2.077922</t>
         </is>
       </c>
       <c r="U90" t="inlineStr">
@@ -10043,12 +10035,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>0x249d52552e7acb9f472d2a4c48ab754622ba572903281739a3e10b4d509dccb0</t>
+          <t>0xff53df1f3446908699196d44fcdb8b39c1bd15c7ed519f0d730e55a51a6eb38f</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -10058,22 +10050,22 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>1.2288</t>
+          <t>1.3713</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Almirante Brown -1</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -10098,7 +10090,7 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>0xa6a338c64f062bfd589e8d5d9cea45a27c9e64065f71f800e5966f81ce53c556</t>
+          <t>0x63a8bf73c1084ef223fdd1096dccd16232e7a455fad77f7f0891be1588ebeb88</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
@@ -10128,7 +10120,7 @@
       </c>
       <c r="R91" t="inlineStr">
         <is>
-          <t>1786214209</t>
+          <t>1786215673</t>
         </is>
       </c>
       <c r="S91" t="inlineStr">
@@ -10138,7 +10130,7 @@
       </c>
       <c r="T91" t="inlineStr">
         <is>
-          <t>6.295082</t>
+          <t>2.693603</t>
         </is>
       </c>
       <c r="U91" t="inlineStr">
@@ -10155,12 +10147,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>0xf65c55196eeb0d21e7e3866ad26f8c3f2fee2aef273ddde5423e31fb40a51469</t>
+          <t>0x249d52552e7acb9f472d2a4c48ab754622ba572903281739a3e10b4d509dccb0</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -10170,39 +10162,39 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>121.81</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>1.4363</t>
+          <t>1.2288</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
+          <t>Almirante Brown -1</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Primera Nacional</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>Almirante Brown vs Ciudad Bolivar</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
           <t>Almirante Brown</t>
         </is>
       </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>Primera Nacional</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>Almirante Brown vs Ciudad Bolivar</t>
-        </is>
-      </c>
-      <c r="J92" t="inlineStr">
-        <is>
-          <t>Almirante Brown</t>
-        </is>
-      </c>
       <c r="K92" t="inlineStr">
         <is>
           <t>Ciudad Bolivar</t>
@@ -10210,7 +10202,7 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>0x63a8bf73c1084ef223fdd1096dccd16232e7a455fad77f7f0891be1588ebeb88</t>
+          <t>0xa6a338c64f062bfd589e8d5d9cea45a27c9e64065f71f800e5966f81ce53c556</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
@@ -10240,7 +10232,7 @@
       </c>
       <c r="R92" t="inlineStr">
         <is>
-          <t>1786213844</t>
+          <t>1786214209</t>
         </is>
       </c>
       <c r="S92" t="inlineStr">
@@ -10250,7 +10242,7 @@
       </c>
       <c r="T92" t="inlineStr">
         <is>
-          <t>279.22063</t>
+          <t>6.295082</t>
         </is>
       </c>
       <c r="U92" t="inlineStr">
@@ -10267,7 +10259,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>0x1bb20a2bf22e4fe06b44c06b9c2caa21f3f2a7c9d0cce1a2346f79e76022cd1f</t>
+          <t>0xf65c55196eeb0d21e7e3866ad26f8c3f2fee2aef273ddde5423e31fb40a51469</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -10282,7 +10274,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>21.05</t>
+          <t>121.81</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -10292,12 +10284,12 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Almirante Brown -0.5</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -10322,7 +10314,7 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>0xfa00d2f0c7b5053ee336b303a0e7ad9cec0b8d539367773b7efee5c86cb2b59d</t>
+          <t>0x63a8bf73c1084ef223fdd1096dccd16232e7a455fad77f7f0891be1588ebeb88</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
@@ -10352,7 +10344,7 @@
       </c>
       <c r="R93" t="inlineStr">
         <is>
-          <t>1786213843</t>
+          <t>1786213844</t>
         </is>
       </c>
       <c r="S93" t="inlineStr">
@@ -10362,7 +10354,7 @@
       </c>
       <c r="T93" t="inlineStr">
         <is>
-          <t>48.252149</t>
+          <t>279.22063</t>
         </is>
       </c>
       <c r="U93" t="inlineStr">
@@ -10379,7 +10371,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>0xc51052f8e449b4d56cc87b697bfc8eb0d3a88ae218dee1da3d725fa94163bc75</t>
+          <t>0x1bb20a2bf22e4fe06b44c06b9c2caa21f3f2a7c9d0cce1a2346f79e76022cd1f</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -10387,23 +10379,31 @@
           <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
-      <c r="C94" t="inlineStr"/>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>77.29513</t>
+          <t>21.05</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>1.2588</t>
+          <t>1.4363</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Primera Nacional</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr"/>
+          <t>Asian Handicap (-0.5)</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Almirante Brown -0.5</t>
+        </is>
+      </c>
       <c r="H94" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -10426,7 +10426,7 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>0xaa5316c6f6544d74142ad6db34a3745918f237ffb1a657e000693947e81b65d6</t>
+          <t>0xfa00d2f0c7b5053ee336b303a0e7ad9cec0b8d539367773b7efee5c86cb2b59d</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
@@ -10456,7 +10456,7 @@
       </c>
       <c r="R94" t="inlineStr">
         <is>
-          <t>1786212849</t>
+          <t>1786213843</t>
         </is>
       </c>
       <c r="S94" t="inlineStr">
@@ -10466,7 +10466,7 @@
       </c>
       <c r="T94" t="inlineStr">
         <is>
-          <t>298.72514</t>
+          <t>48.252149</t>
         </is>
       </c>
       <c r="U94" t="inlineStr">
@@ -10483,7 +10483,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>0x0aeb4fe40f7d734cf244c144e6c064568b40b222193c9f93c641d1b31af3752e</t>
+          <t>0xc51052f8e449b4d56cc87b697bfc8eb0d3a88ae218dee1da3d725fa94163bc75</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -10494,7 +10494,7 @@
       <c r="C95" t="inlineStr"/>
       <c r="D95" t="inlineStr">
         <is>
-          <t>16.89162</t>
+          <t>77.29513</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -10560,7 +10560,7 @@
       </c>
       <c r="R95" t="inlineStr">
         <is>
-          <t>1786212805</t>
+          <t>1786212849</t>
         </is>
       </c>
       <c r="S95" t="inlineStr">
@@ -10570,7 +10570,7 @@
       </c>
       <c r="T95" t="inlineStr">
         <is>
-          <t>65.281623</t>
+          <t>298.72514</t>
         </is>
       </c>
       <c r="U95" t="inlineStr">
@@ -10587,7 +10587,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>0x383b895a5fe529a887369a0f113c516fdc7f6125d54381acf9695997ef22d039</t>
+          <t>0x0aeb4fe40f7d734cf244c144e6c064568b40b222193c9f93c641d1b31af3752e</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -10595,19 +10595,15 @@
           <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C96" t="inlineStr"/>
       <c r="D96" t="inlineStr">
         <is>
-          <t>11.26905</t>
+          <t>16.89162</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>1.745</t>
+          <t>1.2588</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -10615,26 +10611,22 @@
           <t>Primera Nacional</t>
         </is>
       </c>
-      <c r="G96" t="inlineStr">
+      <c r="G96" t="inlineStr"/>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Primera Nacional</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>Almirante Brown vs Ciudad Bolivar</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
         <is>
           <t>Almirante Brown</t>
         </is>
       </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>Primera Nacional</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>Almirante Brown vs Ciudad Bolivar</t>
-        </is>
-      </c>
-      <c r="J96" t="inlineStr">
-        <is>
-          <t>Almirante Brown</t>
-        </is>
-      </c>
       <c r="K96" t="inlineStr">
         <is>
           <t>Ciudad Bolivar</t>
@@ -10672,7 +10664,7 @@
       </c>
       <c r="R96" t="inlineStr">
         <is>
-          <t>1786211779</t>
+          <t>1786212805</t>
         </is>
       </c>
       <c r="S96" t="inlineStr">
@@ -10682,7 +10674,7 @@
       </c>
       <c r="T96" t="inlineStr">
         <is>
-          <t>15.126242</t>
+          <t>65.281623</t>
         </is>
       </c>
       <c r="U96" t="inlineStr">
@@ -10699,12 +10691,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>0xcfb6add6f8610a64ffc187beb9e16bf2bacb27b54a0f0aaefa6bfb437239b893</t>
+          <t>0x383b895a5fe529a887369a0f113c516fdc7f6125d54381acf9695997ef22d039</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -10714,7 +10706,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>24.89998</t>
+          <t>11.26905</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -10784,7 +10776,7 @@
       </c>
       <c r="R97" t="inlineStr">
         <is>
-          <t>1786211777</t>
+          <t>1786211779</t>
         </is>
       </c>
       <c r="S97" t="inlineStr">
@@ -10794,7 +10786,7 @@
       </c>
       <c r="T97" t="inlineStr">
         <is>
-          <t>33.422792</t>
+          <t>15.126242</t>
         </is>
       </c>
       <c r="U97" t="inlineStr">
@@ -10811,12 +10803,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>0xd41652604437a4e92e0d78b653d4d49d8dedd2e153d1340dad89b9b93e182a48</t>
+          <t>0xcfb6add6f8610a64ffc187beb9e16bf2bacb27b54a0f0aaefa6bfb437239b893</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>0xf4a8B27C9a13e298D65b5Cc072d252816B799C81</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -10826,22 +10818,22 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>24.89998</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>1.4163</t>
+          <t>1.745</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Primera Nacional</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Atl. Rafaela</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -10851,27 +10843,27 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>Atl. Rafaela vs Chacarita Juniors</t>
+          <t>Almirante Brown vs Ciudad Bolivar</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>Atl. Rafaela</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Ciudad Bolivar</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>0xe738e9ba05492fab73eaaf6da211b84caadc72b08b26f1cd30fa8737e283bb44</t>
+          <t>0xaa5316c6f6544d74142ad6db34a3745918f237ffb1a657e000693947e81b65d6</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>L19683450</t>
+          <t>L19683447</t>
         </is>
       </c>
       <c r="N98" t="inlineStr">
@@ -10896,17 +10888,17 @@
       </c>
       <c r="R98" t="inlineStr">
         <is>
-          <t>1786211028</t>
+          <t>1786211777</t>
         </is>
       </c>
       <c r="S98" t="inlineStr">
         <is>
-          <t>1786215600</t>
+          <t>1786212000</t>
         </is>
       </c>
       <c r="T98" t="inlineStr">
         <is>
-          <t>2.402402</t>
+          <t>33.422792</t>
         </is>
       </c>
       <c r="U98" t="inlineStr">
@@ -10923,31 +10915,39 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>0x562fd7c6419c807ed04d3cacac95f861805f96704bd535e265399fb9d2c2b609</t>
+          <t>0xd41652604437a4e92e0d78b653d4d49d8dedd2e153d1340dad89b9b93e182a48</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr"/>
+          <t>0xf4a8B27C9a13e298D65b5Cc072d252816B799C81</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>5.32</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>1.405</t>
+          <t>1.4163</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Atl. Rafaela</t>
+        </is>
+      </c>
       <c r="H99" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -10955,27 +10955,27 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>Estudiantes de Caseros vs Deportivo Madryn</t>
+          <t>Atl. Rafaela vs Chacarita Juniors</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>Estudiantes de Caseros</t>
+          <t>Atl. Rafaela</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>0xd61509e26f8645bb9780672f942c72c4b7dab577c2a01f04e1e09bce9b828765</t>
+          <t>0xe738e9ba05492fab73eaaf6da211b84caadc72b08b26f1cd30fa8737e283bb44</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>L19683453</t>
+          <t>L19683450</t>
         </is>
       </c>
       <c r="N99" t="inlineStr">
@@ -11000,17 +11000,17 @@
       </c>
       <c r="R99" t="inlineStr">
         <is>
-          <t>1786210845</t>
+          <t>1786211028</t>
         </is>
       </c>
       <c r="S99" t="inlineStr">
         <is>
-          <t>1786212000</t>
+          <t>1786215600</t>
         </is>
       </c>
       <c r="T99" t="inlineStr">
         <is>
-          <t>13.135802</t>
+          <t>2.402402</t>
         </is>
       </c>
       <c r="U99" t="inlineStr">
@@ -11027,39 +11027,31 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>0x0bb7a6822220bf40d7b279f99a54f46025f393ba95bb38b6d6dc98192886b3ed</t>
+          <t>0x562fd7c6419c807ed04d3cacac95f861805f96704bd535e265399fb9d2c2b609</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>0xf4a8B27C9a13e298D65b5Cc072d252816B799C81</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr"/>
       <c r="D100" t="inlineStr">
         <is>
-          <t>0.99999</t>
+          <t>5.32</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>1.5513</t>
+          <t>1.405</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>Agropecuario</t>
-        </is>
-      </c>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr"/>
       <c r="H100" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -11067,27 +11059,27 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>Agropecuario vs Atletico Guemes</t>
+          <t>Estudiantes de Caseros vs Deportivo Madryn</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Estudiantes de Caseros</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>Atletico Guemes</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>0xae66c7fab3c9c76fbc29d9e9778ef4845d8a6b8d092cff34320f100020113c49</t>
+          <t>0xd61509e26f8645bb9780672f942c72c4b7dab577c2a01f04e1e09bce9b828765</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>L19683451</t>
+          <t>L19683453</t>
         </is>
       </c>
       <c r="N100" t="inlineStr">
@@ -11112,7 +11104,7 @@
       </c>
       <c r="R100" t="inlineStr">
         <is>
-          <t>1786205982</t>
+          <t>1786210845</t>
         </is>
       </c>
       <c r="S100" t="inlineStr">
@@ -11122,7 +11114,7 @@
       </c>
       <c r="T100" t="inlineStr">
         <is>
-          <t>1.814041</t>
+          <t>13.135802</t>
         </is>
       </c>
       <c r="U100" t="inlineStr">
@@ -11139,7 +11131,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>0xe17b2546f4b90c8647ba975c279e39dec1fda5a003adfb8a2b39bb12a3519b10</t>
+          <t>0x0bb7a6822220bf40d7b279f99a54f46025f393ba95bb38b6d6dc98192886b3ed</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -11154,12 +11146,12 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0.99999</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>1.3613</t>
+          <t>1.5513</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -11169,7 +11161,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Tie</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -11179,27 +11171,27 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>Almirante Brown vs Ciudad Bolivar</t>
+          <t>Agropecuario vs Atletico Guemes</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>Ciudad Bolivar</t>
+          <t>Atletico Guemes</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>0xd5906ce08d61f7c5ee45fcebd2c8baeed5558387398ea332817a4b632f439b6d</t>
+          <t>0xae66c7fab3c9c76fbc29d9e9778ef4845d8a6b8d092cff34320f100020113c49</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>L19683447</t>
+          <t>L19683451</t>
         </is>
       </c>
       <c r="N101" t="inlineStr">
@@ -11224,7 +11216,7 @@
       </c>
       <c r="R101" t="inlineStr">
         <is>
-          <t>1786205963</t>
+          <t>1786205982</t>
         </is>
       </c>
       <c r="S101" t="inlineStr">
@@ -11234,7 +11226,7 @@
       </c>
       <c r="T101" t="inlineStr">
         <is>
-          <t>2.768166</t>
+          <t>1.814041</t>
         </is>
       </c>
       <c r="U101" t="inlineStr">
@@ -11251,7 +11243,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>0xcfe218822e89cbef5841f3045f551cc65acf353d8e240f943e2b61c54ea79a68</t>
+          <t>0xe17b2546f4b90c8647ba975c279e39dec1fda5a003adfb8a2b39bb12a3519b10</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -11271,7 +11263,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>1.3337</t>
+          <t>1.3613</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -11291,27 +11283,27 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>Estudiantes de Caseros vs Deportivo Madryn</t>
+          <t>Almirante Brown vs Ciudad Bolivar</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>Estudiantes de Caseros</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Ciudad Bolivar</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>0xf238b96ec9e2421db79973de945f1fc0c3f8bb99c31cda32d011ebaabfd2db86</t>
+          <t>0xd5906ce08d61f7c5ee45fcebd2c8baeed5558387398ea332817a4b632f439b6d</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>L19683453</t>
+          <t>L19683447</t>
         </is>
       </c>
       <c r="N102" t="inlineStr">
@@ -11336,7 +11328,7 @@
       </c>
       <c r="R102" t="inlineStr">
         <is>
-          <t>1786205938</t>
+          <t>1786205963</t>
         </is>
       </c>
       <c r="S102" t="inlineStr">
@@ -11346,7 +11338,7 @@
       </c>
       <c r="T102" t="inlineStr">
         <is>
-          <t>2.996255</t>
+          <t>2.768166</t>
         </is>
       </c>
       <c r="U102" t="inlineStr">
@@ -11363,31 +11355,39 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>0x1b9fcb29010a212f74af57040114154e78748f06a4d826be4397ddadb45ac31b</t>
+          <t>0xcfe218822e89cbef5841f3045f551cc65acf353d8e240f943e2b61c54ea79a68</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr"/>
+          <t>0xf4a8B27C9a13e298D65b5Cc072d252816B799C81</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>21.69</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>1.4512</t>
+          <t>1.3337</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H103" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -11395,27 +11395,27 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>Almirante Brown vs Ciudad Bolivar</t>
+          <t>Estudiantes de Caseros vs Deportivo Madryn</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Estudiantes de Caseros</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>Ciudad Bolivar</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>0xbbcaa253cd967fbf933ff0d87a6f9744cafec0ed59dad5f1f76332aab01a3fa5</t>
+          <t>0xf238b96ec9e2421db79973de945f1fc0c3f8bb99c31cda32d011ebaabfd2db86</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>L19683447</t>
+          <t>L19683453</t>
         </is>
       </c>
       <c r="N103" t="inlineStr">
@@ -11440,7 +11440,7 @@
       </c>
       <c r="R103" t="inlineStr">
         <is>
-          <t>1786190525</t>
+          <t>1786205938</t>
         </is>
       </c>
       <c r="S103" t="inlineStr">
@@ -11450,7 +11450,7 @@
       </c>
       <c r="T103" t="inlineStr">
         <is>
-          <t>48.066482</t>
+          <t>2.996255</t>
         </is>
       </c>
       <c r="U103" t="inlineStr">
@@ -11467,23 +11467,23 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>0x3177792dd6a7185e37ae06612104cf5a35d137d7f535a889a83a7e9b7c174506</t>
+          <t>0x1b9fcb29010a212f74af57040114154e78748f06a4d826be4397ddadb45ac31b</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C104" t="inlineStr"/>
       <c r="D104" t="inlineStr">
         <is>
-          <t>18.35495</t>
+          <t>21.69</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>1.4963</t>
+          <t>1.4512</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -11544,7 +11544,7 @@
       </c>
       <c r="R104" t="inlineStr">
         <is>
-          <t>1786190491</t>
+          <t>1786190525</t>
         </is>
       </c>
       <c r="S104" t="inlineStr">
@@ -11554,7 +11554,7 @@
       </c>
       <c r="T104" t="inlineStr">
         <is>
-          <t>36.987305</t>
+          <t>48.066482</t>
         </is>
       </c>
       <c r="U104" t="inlineStr">
@@ -11571,7 +11571,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>0x54ed4ee2a6ebdab49498137f1accea542ead806f21430a0a771cc4872a044e43</t>
+          <t>0x3177792dd6a7185e37ae06612104cf5a35d137d7f535a889a83a7e9b7c174506</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -11579,19 +11579,15 @@
           <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
         </is>
       </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C105" t="inlineStr"/>
       <c r="D105" t="inlineStr">
         <is>
-          <t>20.10741</t>
+          <t>18.35495</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>1.5437</t>
+          <t>1.4963</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -11599,11 +11595,7 @@
           <t>Under/Over (1.5)</t>
         </is>
       </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>Over 1.5</t>
-        </is>
-      </c>
+      <c r="G105" t="inlineStr"/>
       <c r="H105" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -11656,7 +11648,7 @@
       </c>
       <c r="R105" t="inlineStr">
         <is>
-          <t>1786190485</t>
+          <t>1786190491</t>
         </is>
       </c>
       <c r="S105" t="inlineStr">
@@ -11666,7 +11658,7 @@
       </c>
       <c r="T105" t="inlineStr">
         <is>
-          <t>36.979145</t>
+          <t>36.987305</t>
         </is>
       </c>
       <c r="U105" t="inlineStr">
@@ -11683,23 +11675,27 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>0x544fe5c906328d009917b591611ff3438cef85f8b42d9f67732cbbd5eabbb8dd</t>
+          <t>0x54ed4ee2a6ebdab49498137f1accea542ead806f21430a0a771cc4872a044e43</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr"/>
+          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>21.69</t>
+          <t>20.10741</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>1.4512</t>
+          <t>1.5437</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -11707,7 +11703,11 @@
           <t>Under/Over (1.5)</t>
         </is>
       </c>
-      <c r="G106" t="inlineStr"/>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Over 1.5</t>
+        </is>
+      </c>
       <c r="H106" t="inlineStr">
         <is>
           <t>Primera Nacional</t>
@@ -11770,7 +11770,7 @@
       </c>
       <c r="T106" t="inlineStr">
         <is>
-          <t>48.066482</t>
+          <t>36.979145</t>
         </is>
       </c>
       <c r="U106" t="inlineStr">
@@ -11787,7 +11787,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>0xb2f3ea804e1760a01d3a93678f0e2119f1ea2a9db0dc4711a06cc7bcba42b0c2</t>
+          <t>0x544fe5c906328d009917b591611ff3438cef85f8b42d9f67732cbbd5eabbb8dd</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -11798,12 +11798,12 @@
       <c r="C107" t="inlineStr"/>
       <c r="D107" t="inlineStr">
         <is>
-          <t>17.47</t>
+          <t>21.69</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>1.405</t>
+          <t>1.4512</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -11819,27 +11819,27 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>Estudiantes de Caseros vs Deportivo Madryn</t>
+          <t>Almirante Brown vs Ciudad Bolivar</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>Estudiantes de Caseros</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Ciudad Bolivar</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>0xd61509e26f8645bb9780672f942c72c4b7dab577c2a01f04e1e09bce9b828765</t>
+          <t>0xbbcaa253cd967fbf933ff0d87a6f9744cafec0ed59dad5f1f76332aab01a3fa5</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>L19683453</t>
+          <t>L19683447</t>
         </is>
       </c>
       <c r="N107" t="inlineStr">
@@ -11864,7 +11864,7 @@
       </c>
       <c r="R107" t="inlineStr">
         <is>
-          <t>1786190461</t>
+          <t>1786190485</t>
         </is>
       </c>
       <c r="S107" t="inlineStr">
@@ -11874,7 +11874,7 @@
       </c>
       <c r="T107" t="inlineStr">
         <is>
-          <t>43.135802</t>
+          <t>48.066482</t>
         </is>
       </c>
       <c r="U107" t="inlineStr">
@@ -11891,7 +11891,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>0xa7eafbb77d425fc2347b4ee3e4f4e1b85f6d0f81420605db76ebfeeaa793a428</t>
+          <t>0xb2f3ea804e1760a01d3a93678f0e2119f1ea2a9db0dc4711a06cc7bcba42b0c2</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -11902,12 +11902,12 @@
       <c r="C108" t="inlineStr"/>
       <c r="D108" t="inlineStr">
         <is>
-          <t>21.69</t>
+          <t>17.47</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>1.4512</t>
+          <t>1.405</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -11923,27 +11923,27 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>Almirante Brown vs Ciudad Bolivar</t>
+          <t>Estudiantes de Caseros vs Deportivo Madryn</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Estudiantes de Caseros</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>Ciudad Bolivar</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>0xbbcaa253cd967fbf933ff0d87a6f9744cafec0ed59dad5f1f76332aab01a3fa5</t>
+          <t>0xd61509e26f8645bb9780672f942c72c4b7dab577c2a01f04e1e09bce9b828765</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>L19683447</t>
+          <t>L19683453</t>
         </is>
       </c>
       <c r="N108" t="inlineStr">
@@ -11968,7 +11968,7 @@
       </c>
       <c r="R108" t="inlineStr">
         <is>
-          <t>1786190458</t>
+          <t>1786190461</t>
         </is>
       </c>
       <c r="S108" t="inlineStr">
@@ -11978,7 +11978,7 @@
       </c>
       <c r="T108" t="inlineStr">
         <is>
-          <t>48.066482</t>
+          <t>43.135802</t>
         </is>
       </c>
       <c r="U108" t="inlineStr">
@@ -11995,110 +11995,214 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
+          <t>0xa7eafbb77d425fc2347b4ee3e4f4e1b85f6d0f81420605db76ebfeeaa793a428</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr"/>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>21.69</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>1.4512</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr"/>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>Primera Nacional</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>Almirante Brown vs Ciudad Bolivar</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>Almirante Brown</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>Ciudad Bolivar</t>
+        </is>
+      </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>0xbbcaa253cd967fbf933ff0d87a6f9744cafec0ed59dad5f1f76332aab01a3fa5</t>
+        </is>
+      </c>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>L19683447</t>
+        </is>
+      </c>
+      <c r="N109" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O109" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P109" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q109" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R109" t="inlineStr">
+        <is>
+          <t>1786190458</t>
+        </is>
+      </c>
+      <c r="S109" t="inlineStr">
+        <is>
+          <t>1786212000</t>
+        </is>
+      </c>
+      <c r="T109" t="inlineStr">
+        <is>
+          <t>48.066482</t>
+        </is>
+      </c>
+      <c r="U109" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V109" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
           <t>0x5c5b512ea725fac30531bf5fe91f34f3ccc0eeff23890c18f25c3f329007c589</t>
         </is>
       </c>
-      <c r="B109" t="inlineStr">
+      <c r="B110" t="inlineStr">
         <is>
           <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
         </is>
       </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E109" t="inlineStr">
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
         <is>
           <t>1.3638</t>
         </is>
       </c>
-      <c r="F109" t="inlineStr">
+      <c r="F110" t="inlineStr">
         <is>
           <t>1X2</t>
         </is>
       </c>
-      <c r="G109" t="inlineStr">
+      <c r="G110" t="inlineStr">
         <is>
           <t>Tie</t>
         </is>
       </c>
-      <c r="H109" t="inlineStr">
-        <is>
-          <t>Primera Nacional</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr">
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Primera Nacional</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
         <is>
           <t>Almirante Brown vs Ciudad Bolivar</t>
         </is>
       </c>
-      <c r="J109" t="inlineStr">
+      <c r="J110" t="inlineStr">
         <is>
           <t>Almirante Brown</t>
         </is>
       </c>
-      <c r="K109" t="inlineStr">
+      <c r="K110" t="inlineStr">
         <is>
           <t>Ciudad Bolivar</t>
         </is>
       </c>
-      <c r="L109" t="inlineStr">
+      <c r="L110" t="inlineStr">
         <is>
           <t>0xd5906ce08d61f7c5ee45fcebd2c8baeed5558387398ea332817a4b632f439b6d</t>
         </is>
       </c>
-      <c r="M109" t="inlineStr">
+      <c r="M110" t="inlineStr">
         <is>
           <t>L19683447</t>
         </is>
       </c>
-      <c r="N109" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O109" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P109" t="inlineStr">
+      <c r="N110" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O110" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P110" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q109" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R109" t="inlineStr">
+      <c r="Q110" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R110" t="inlineStr">
         <is>
           <t>1786125660</t>
         </is>
       </c>
-      <c r="S109" t="inlineStr">
+      <c r="S110" t="inlineStr">
         <is>
           <t>1786212000</t>
         </is>
       </c>
-      <c r="T109" t="inlineStr">
+      <c r="T110" t="inlineStr">
         <is>
           <t>2.749141</t>
         </is>
       </c>
-      <c r="U109" t="inlineStr">
+      <c r="U110" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V109" t="inlineStr">
+      <c r="V110" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/Primera Nacional/trades.xlsx
+++ b/data/sxbet/ligas/Primera Nacional/trades.xlsx
@@ -613,7 +613,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>1786905000</t>
+          <t>1786824000</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">

--- a/data/sxbet/ligas/Primera Nacional/trades.xlsx
+++ b/data/sxbet/ligas/Primera Nacional/trades.xlsx
@@ -613,7 +613,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>1786824000</t>
+          <t>1786905000</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">

--- a/data/sxbet/ligas/Primera Nacional/trades.xlsx
+++ b/data/sxbet/ligas/Primera Nacional/trades.xlsx
@@ -613,7 +613,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>1786905000</t>
+          <t>1786822200</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
